--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -444,7 +444,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4061828584639809</v>
+        <v>0.4053637167595583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,19 +695,19 @@
         <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>22.44565259532895</v>
+        <v>21.42119502374098</v>
       </c>
       <c r="K2" t="n">
-        <v>10.54836414351199</v>
+        <v>10.3254232351534</v>
       </c>
       <c r="L2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>44.44444444444444</v>
+        <v>60</v>
       </c>
       <c r="N2" t="n">
-        <v>13.8510473854692</v>
+        <v>11.35176187055035</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
@@ -737,25 +737,25 @@
         <v>64.91228070175438</v>
       </c>
       <c r="X2" t="n">
-        <v>11.78040893158552</v>
+        <v>11.79582706077868</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.102201002706649</v>
+        <v>1.315258238418759</v>
       </c>
       <c r="Z2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA2" t="n">
-        <v>43.13725490196079</v>
+        <v>44.23076923076923</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.431276922283271</v>
+        <v>9.484952980269453</v>
       </c>
       <c r="AC2" t="n">
         <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>8.996963620532005</v>
+        <v>8.80049094374008</v>
       </c>
       <c r="AE2" t="n">
         <v>46</v>
@@ -764,10 +764,10 @@
         <v>52.17391304347826</v>
       </c>
       <c r="AG2" t="n">
-        <v>36.47780344576684</v>
+        <v>36.43599742569995</v>
       </c>
       <c r="AH2" t="n">
-        <v>15.69610959771142</v>
+        <v>15.73791561777831</v>
       </c>
       <c r="AI2" t="n">
         <v>38.13741307280403</v>
@@ -786,10 +786,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7037210856141322</v>
+        <v>0.7190012767620263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,19 +814,19 @@
         <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>17.26506156790429</v>
+        <v>16.83732632822199</v>
       </c>
       <c r="K3" t="n">
-        <v>11.93583900416053</v>
+        <v>14.36634883433114</v>
       </c>
       <c r="L3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>62.5</v>
       </c>
       <c r="N3" t="n">
-        <v>12.73834834951395</v>
+        <v>12.50024164736539</v>
       </c>
       <c r="O3" t="n">
         <v>10</v>
@@ -850,31 +850,31 @@
         <v>43.5727090128925</v>
       </c>
       <c r="V3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="W3" t="n">
-        <v>65.27777777777777</v>
+        <v>66.19718309859155</v>
       </c>
       <c r="X3" t="n">
         <v>17.17248092970491</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.469173891338851</v>
+        <v>2.394872988186736</v>
       </c>
       <c r="Z3" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="AA3" t="n">
-        <v>38.88888888888889</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.29239792580097</v>
+        <v>13.29156748372895</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.78957215587158</v>
+        <v>7.79172902555908</v>
       </c>
       <c r="AE3" t="n">
         <v>35</v>
@@ -883,10 +883,10 @@
         <v>60</v>
       </c>
       <c r="AG3" t="n">
-        <v>33.12664250601361</v>
+        <v>33.02274640211751</v>
       </c>
       <c r="AH3" t="n">
-        <v>26.87335749398639</v>
+        <v>26.97725359788249</v>
       </c>
       <c r="AI3" t="n">
         <v>43.5727090128925</v>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C4" t="n">
-        <v>1.495921626926832</v>
+        <v>1.500318779178578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,31 +959,31 @@
         <v>45.09442218134437</v>
       </c>
       <c r="V4" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W4" t="n">
-        <v>63.01369863013699</v>
+        <v>62.5</v>
       </c>
       <c r="X4" t="n">
-        <v>17.1164133241122</v>
+        <v>16.66966699739723</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.984276352313932</v>
+        <v>4.704984579490901</v>
       </c>
       <c r="Z4" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="AA4" t="n">
-        <v>48.48484848484848</v>
+        <v>48.71794871794872</v>
       </c>
       <c r="AB4" t="n">
-        <v>14.3086512365087</v>
+        <v>13.80131041509941</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>5.278835391796976</v>
+        <v>5.556445315784608</v>
       </c>
       <c r="AE4" t="n">
         <v>40</v>
@@ -992,10 +992,10 @@
         <v>60</v>
       </c>
       <c r="AG4" t="n">
-        <v>39.36172689245832</v>
+        <v>39.35090438163581</v>
       </c>
       <c r="AH4" t="n">
-        <v>20.63827310754168</v>
+        <v>20.64909561836419</v>
       </c>
       <c r="AI4" t="n">
         <v>44.59589366034619</v>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2343679305932897</v>
+        <v>0.2305493285070851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,19 +1042,19 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>22.0841895732196</v>
+        <v>19.13427219952423</v>
       </c>
       <c r="K5" t="n">
-        <v>7.666302463632357</v>
+        <v>5.912074544476398</v>
       </c>
       <c r="L5" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>66.66666666666667</v>
+        <v>51.85185185185185</v>
       </c>
       <c r="N5" t="n">
-        <v>11.26430726773086</v>
+        <v>10.96675712460524</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -1087,22 +1087,22 @@
         <v>10.55954734904581</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.616910936039951</v>
+        <v>4.203592467592998</v>
       </c>
       <c r="Z5" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="AA5" t="n">
-        <v>45.28301886792453</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.42096596643775</v>
+        <v>9.169312298228352</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>7.581489902328853</v>
+        <v>6.050756684634684</v>
       </c>
       <c r="AE5" t="n">
         <v>45</v>
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C6" t="n">
-        <v>1.64613115783833</v>
+        <v>1.618575571231722</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %82.35: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %82.61: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1168,22 +1168,22 @@
         <v>24.35210179737853</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5239591835591</v>
+        <v>1.791008920417481</v>
       </c>
       <c r="L6" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="M6" t="n">
-        <v>82.35294117647059</v>
+        <v>82.60869565217391</v>
       </c>
       <c r="N6" t="n">
-        <v>9.785390954755409</v>
+        <v>12.20680140660389</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.2053138895065976</v>
       </c>
       <c r="Q6" t="n">
         <v>34</v>
@@ -1214,29 +1214,29 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF6" t="n">
-        <v>48.93617021276596</v>
+        <v>46.93877551020408</v>
       </c>
       <c r="AG6" t="n">
-        <v>40.63467394198483</v>
+        <v>39.29345237727971</v>
       </c>
       <c r="AH6" t="n">
-        <v>8.301496270781129</v>
+        <v>7.645323132924368</v>
       </c>
       <c r="AI6" t="n">
-        <v>35.27555503368215</v>
+        <v>33.70350369317515</v>
       </c>
       <c r="AJ6" t="n">
         <v>80</v>
       </c>
       <c r="AK6" t="n">
-        <v>46.25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C7" t="n">
-        <v>2.415697505610008</v>
+        <v>2.369249120786459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,22 +1309,22 @@
         <v>18.9234494530097</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.358474287770684</v>
+        <v>4.235899400189636</v>
       </c>
       <c r="Z7" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AA7" t="n">
-        <v>36.95652173913044</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.59896040856028</v>
+        <v>11.6098330229977</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.705330230105651</v>
+        <v>0.7978987898643486</v>
       </c>
       <c r="AE7" t="n">
         <v>45</v>
@@ -1355,29 +1355,29 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3598854196497778</v>
+        <v>0.3488061205602287</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>AL_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VERİ_YETERSİZ</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1390,22 +1390,22 @@
         <v>20.70550141590351</v>
       </c>
       <c r="K8" t="n">
-        <v>10.52133658700249</v>
+        <v>7.118867698388609</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N8" t="n">
-        <v>12.73012866683162</v>
+        <v>12.69508729544503</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.822574323780545</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1429,13 +1429,13 @@
         <v>50</v>
       </c>
       <c r="X8" t="n">
-        <v>28.59040308110081</v>
+        <v>28.52170855483174</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.36266032489478</v>
+        <v>15.06063096960105</v>
       </c>
       <c r="Z8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5452809460339468</v>
+        <v>0.5470662032371512</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,16 +1505,16 @@
         <v>14.50739888386581</v>
       </c>
       <c r="K9" t="n">
-        <v>2.555360537091489</v>
+        <v>2.891128176613345</v>
       </c>
       <c r="L9" t="n">
         <v>41</v>
       </c>
       <c r="M9" t="n">
-        <v>51.21951219512195</v>
+        <v>48.78048780487805</v>
       </c>
       <c r="N9" t="n">
-        <v>14.30681178446265</v>
+        <v>14.70543065115051</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C10" t="n">
-        <v>1.971242124270151</v>
+        <v>1.94763794911873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,22 +1614,22 @@
         <v>13.50421550203786</v>
       </c>
       <c r="K10" t="n">
-        <v>7.507948066429848</v>
+        <v>6.220619429786911</v>
       </c>
       <c r="L10" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M10" t="n">
-        <v>64.28571428571429</v>
+        <v>58.06451612903226</v>
       </c>
       <c r="N10" t="n">
-        <v>8.841242299291709</v>
+        <v>9.099753605249541</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>2.318016461471584</v>
+        <v>3.558047948224696</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1692,24 +1692,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C11" t="n">
-        <v>8.102051792485531</v>
+        <v>7.748390679308147</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1720,25 +1720,25 @@
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>10.07811036816124</v>
+        <v>10.16694412204168</v>
       </c>
       <c r="K11" t="n">
-        <v>4.948502758255935</v>
+        <v>0.4666666666666819</v>
       </c>
       <c r="L11" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="M11" t="n">
-        <v>55.17241379310344</v>
+        <v>51.02040816326531</v>
       </c>
       <c r="N11" t="n">
-        <v>14.66967228148977</v>
+        <v>13.43296590678878</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.521566025215649</v>
       </c>
       <c r="Q11" t="n">
         <v>49</v>
@@ -1747,10 +1747,10 @@
         <v>61.22448979591837</v>
       </c>
       <c r="S11" t="n">
-        <v>52.04378180160862</v>
+        <v>51.94286231293403</v>
       </c>
       <c r="T11" t="n">
-        <v>9.180707994309749</v>
+        <v>9.281627482984341</v>
       </c>
       <c r="U11" t="n">
         <v>47.24599944352045</v>
@@ -1762,19 +1762,19 @@
         <v>61.19402985074627</v>
       </c>
       <c r="X11" t="n">
-        <v>23.01205774394926</v>
+        <v>21.29068828859215</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.628323179453831</v>
+        <v>9.747723194611202</v>
       </c>
       <c r="Z11" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="AA11" t="n">
-        <v>37.93103448275862</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB11" t="n">
-        <v>13.99845876356964</v>
+        <v>14.28978979873238</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C12" t="n">
-        <v>6.049532005055863</v>
+        <v>5.887131604384757</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,25 +1839,25 @@
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>21.7920720434985</v>
+        <v>21.83099560311669</v>
       </c>
       <c r="K12" t="n">
-        <v>4.070796460176984</v>
+        <v>1.327433628318597</v>
       </c>
       <c r="L12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M12" t="n">
-        <v>42.85714285714285</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N12" t="n">
-        <v>19.19009338186235</v>
+        <v>16.71174840656363</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8928571428571619</v>
+        <v>3.624454148471612</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1920,14 +1920,14 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1796340531338536</v>
+        <v>0.1727577483906793</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1937,14 +1937,10 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %100.00: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>VERİ_YETERSİZ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>5</v>
       </c>
@@ -1952,13 +1948,13 @@
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>49.69579459166445</v>
+        <v>47.07727092024744</v>
       </c>
       <c r="K13" t="n">
-        <v>11.23337310305517</v>
+        <v>6.975413335828451</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1991,22 +1987,22 @@
         <v>20.61663781635479</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.779411599572306</v>
+        <v>11.30957115658938</v>
       </c>
       <c r="Z13" t="n">
         <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.724702694447725</v>
+        <v>11.69944783412234</v>
       </c>
       <c r="AC13" t="n">
         <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.407909599086222</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2027,10 +2023,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C14" t="n">
-        <v>8.945694010877675</v>
+        <v>8.828126606749892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,10 +2083,10 @@
         <v>58.69565217391305</v>
       </c>
       <c r="X14" t="n">
-        <v>16.10010659889793</v>
+        <v>16.11612055393703</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.6285714285714339</v>
+        <v>1.94806963420604</v>
       </c>
       <c r="Z14" t="n">
         <v>38</v>
@@ -2099,13 +2095,13 @@
         <v>47.36842105263158</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.89665709925152</v>
+        <v>11.74181387011352</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.380103507763075</v>
+        <v>0.05296210446875671</v>
       </c>
       <c r="AE14" t="n">
         <v>38</v>
@@ -2114,10 +2110,10 @@
         <v>52.63157894736842</v>
       </c>
       <c r="AG14" t="n">
-        <v>27.1172429607868</v>
+        <v>26.88536957101867</v>
       </c>
       <c r="AH14" t="n">
-        <v>25.51433598658162</v>
+        <v>25.74620937634975</v>
       </c>
       <c r="AI14" t="n">
         <v>37.25897138449667</v>
@@ -2136,24 +2132,24 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C15" t="n">
-        <v>14.42422427055837</v>
+        <v>14.08798305328754</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AL_BEKLE_EŞİK</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -2167,22 +2163,22 @@
         <v>11.36450127270662</v>
       </c>
       <c r="K15" t="n">
-        <v>2.945887978172301</v>
+        <v>0.5461297632740614</v>
       </c>
       <c r="L15" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="M15" t="n">
-        <v>59.09090909090909</v>
+        <v>56.41025641025641</v>
       </c>
       <c r="N15" t="n">
-        <v>18.9902115547917</v>
+        <v>19.70774925476212</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>4.909484119365048</v>
+        <v>7.41338354273342</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2206,25 +2202,25 @@
         <v>80.43478260869566</v>
       </c>
       <c r="X15" t="n">
-        <v>44.78170386419063</v>
+        <v>41.12870069280461</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.75339877130623</v>
+        <v>10.88043643333048</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.647592626561634</v>
+        <v>8.377386456231811</v>
       </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.366189219003755</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>31</v>
@@ -2255,10 +2251,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C16" t="n">
-        <v>35.57700964878091</v>
+        <v>34.90117845464081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2286,22 +2282,22 @@
         <v>16.99349200873118</v>
       </c>
       <c r="K16" t="n">
-        <v>5.910979750759271</v>
+        <v>3.899064060707547</v>
       </c>
       <c r="L16" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="M16" t="n">
-        <v>58.53658536585366</v>
+        <v>66.07142857142857</v>
       </c>
       <c r="N16" t="n">
-        <v>17.46914077436472</v>
+        <v>17.28957398612863</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>3.860808632743695</v>
+        <v>5.871983539454906</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2364,10 +2360,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4288171697033809</v>
+        <v>0.4031014129115851</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2381,7 +2377,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2392,25 +2388,21 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>46.98262980625316</v>
+        <v>50.1132355061795</v>
       </c>
       <c r="K17" t="n">
-        <v>3.805240179516467</v>
+        <v>3.703705788751765</v>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
-      </c>
-      <c r="M17" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N17" t="n">
-        <v>20.47703180716612</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>4.040990429027769</v>
+        <v>4.142855048979599</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2433,47 +2425,37 @@
       <c r="W17" t="n">
         <v>73.03370786516854</v>
       </c>
-      <c r="X17" t="n">
-        <v>11.57568732431979</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>6.964283466358367</v>
-      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>37</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>51.35135135135135</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>13.78945611666684</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
         <v>8</v>
       </c>
-      <c r="AD17" t="n">
-        <v>1.113246151296221</v>
-      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AF17" t="n">
-        <v>57.14285714285715</v>
+        <v>55.81395348837209</v>
       </c>
       <c r="AG17" t="n">
-        <v>39.27989336365132</v>
+        <v>39.16582607612455</v>
       </c>
       <c r="AH17" t="n">
-        <v>17.86296377920583</v>
+        <v>16.64812741224755</v>
       </c>
       <c r="AI17" t="n">
-        <v>42.20623987810458</v>
+        <v>41.1076144528241</v>
       </c>
       <c r="AJ17" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AK17" t="n">
-        <v>52.32558139534883</v>
+        <v>51.72413793103448</v>
       </c>
     </row>
     <row r="18">
@@ -2483,10 +2465,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C18" t="n">
-        <v>0.08045466219124593</v>
+        <v>0.0787693067067026</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2514,22 +2496,22 @@
         <v>31.38464440531301</v>
       </c>
       <c r="K18" t="n">
-        <v>7.635675496250993</v>
+        <v>5.380935110927831</v>
       </c>
       <c r="L18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="N18" t="n">
-        <v>10.42324035066446</v>
+        <v>13.03244577611671</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>2.19659930859204</v>
+        <v>4.383207346006168</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2556,22 +2538,22 @@
         <v>11.24971294890111</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.248581373248238</v>
+        <v>5.275319533335699</v>
       </c>
       <c r="Z18" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="AA18" t="n">
-        <v>35.29411764705883</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB18" t="n">
-        <v>14.85782527415318</v>
+        <v>15.38699885804945</v>
       </c>
       <c r="AC18" t="n">
         <v>8</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.910954996000427</v>
+        <v>2.876420858049944</v>
       </c>
       <c r="AE18" t="n">
         <v>36</v>
@@ -2602,10 +2584,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02716116513316442</v>
+        <v>0.02735331016185756</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,64 +2615,64 @@
         <v>10.11859020594628</v>
       </c>
       <c r="K19" t="n">
-        <v>1.955791317076683</v>
+        <v>2.677052660321921</v>
       </c>
       <c r="L19" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="M19" t="n">
-        <v>50</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N19" t="n">
-        <v>20.25961926302971</v>
+        <v>16.51958978675003</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>7.889898728662015</v>
+        <v>7.13201942395445</v>
       </c>
       <c r="Q19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R19" t="n">
-        <v>84.61538461538461</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="S19" t="n">
-        <v>61.42274616970974</v>
+        <v>62.5711214433019</v>
       </c>
       <c r="T19" t="n">
-        <v>23.19263844567487</v>
+        <v>16.00030712812667</v>
       </c>
       <c r="U19" t="n">
-        <v>57.76536898051745</v>
+        <v>52.41076941339971</v>
       </c>
       <c r="V19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W19" t="n">
-        <v>74.07407407407408</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="X19" t="n">
         <v>20.26411217973316</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.360697397528071</v>
+        <v>7.712417533919725</v>
       </c>
       <c r="Z19" t="n">
         <v>13</v>
       </c>
       <c r="AA19" t="n">
-        <v>61.53846153846154</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AB19" t="n">
-        <v>12.91319905850556</v>
+        <v>12.39536789924539</v>
       </c>
       <c r="AC19" t="n">
         <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.788864118251932</v>
+        <v>2.478754351292123</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -2721,10 +2703,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C20" t="n">
-        <v>1.650246422974175</v>
+        <v>1.654566768813113</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2749,25 +2731,25 @@
         <v>10</v>
       </c>
       <c r="J20" t="n">
-        <v>19.59957469698169</v>
+        <v>18.49305897009618</v>
       </c>
       <c r="K20" t="n">
-        <v>5.87669567287139</v>
+        <v>6.153880907284082</v>
       </c>
       <c r="L20" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M20" t="n">
-        <v>54.54545454545455</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N20" t="n">
-        <v>10.20800881878863</v>
+        <v>10.46843494182912</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>3.894439943487127</v>
+        <v>3.62315448087589</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
@@ -2830,10 +2812,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9395293552497309</v>
+        <v>0.9238426259177757</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2929,10 +2911,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3102957216063941</v>
+        <v>0.3006807477942537</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2946,10 +2928,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>BAND</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>5</v>
       </c>
@@ -2957,25 +2943,25 @@
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>15.88173620271654</v>
+        <v>18.72614792016484</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5333328000000082</v>
+        <v>0.8275862068965356</v>
       </c>
       <c r="L22" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M22" t="n">
-        <v>71.42857142857143</v>
+        <v>75</v>
       </c>
       <c r="N22" t="n">
-        <v>15.43176950097447</v>
+        <v>16.08506486629521</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>9.416446203800778</v>
+        <v>9.097127222982238</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -2998,23 +2984,17 @@
       <c r="W22" t="n">
         <v>75</v>
       </c>
-      <c r="X22" t="n">
-        <v>21.77609909780096</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>15.43310591109509</v>
-      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
         <v>5</v>
       </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="n">
         <v>0</v>
       </c>
@@ -3036,10 +3016,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6218260306755479</v>
+        <v>0.6087653990909653</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3053,14 +3033,10 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>BAND</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>5</v>
       </c>
@@ -3068,10 +3044,10 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>39.74770788214735</v>
+        <v>40.10847332624524</v>
       </c>
       <c r="K23" t="n">
-        <v>1.602475705917583</v>
+        <v>0.06761325219744041</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -3082,7 +3058,7 @@
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>3.343938492125287</v>
+        <v>4.929054054054038</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3105,27 +3081,17 @@
       <c r="W23" t="n">
         <v>82.35294117647059</v>
       </c>
-      <c r="X23" t="n">
-        <v>13.08038213682108</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>10.15021899821302</v>
-      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>9.675690124459654</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
         <v>6</v>
       </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="n">
         <v>11</v>
       </c>
@@ -3142,10 +3108,10 @@
         <v>43.43546988238708</v>
       </c>
       <c r="AJ23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>50</v>
+        <v>52.94117647058823</v>
       </c>
     </row>
     <row r="24">
@@ -3155,10 +3121,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1687284397688673</v>
+        <v>0.1682331406947329</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3186,7 +3152,7 @@
         <v>23.31817459365587</v>
       </c>
       <c r="K24" t="n">
-        <v>11.5630145663989</v>
+        <v>11.23552349318049</v>
       </c>
       <c r="L24" t="n">
         <v>6</v>
@@ -3228,7 +3194,7 @@
         <v>17.82705440547527</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.316300123671169</v>
+        <v>5.59424229482266</v>
       </c>
       <c r="Z24" t="n">
         <v>19</v>
@@ -3237,7 +3203,7 @@
         <v>31.57894736842105</v>
       </c>
       <c r="AB24" t="n">
-        <v>16.71836589047568</v>
+        <v>14.55376143260952</v>
       </c>
       <c r="AC24" t="n">
         <v>2</v>
@@ -3274,10 +3240,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C25" t="n">
-        <v>3.397203302506354</v>
+        <v>3.346153055138515</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3305,22 +3271,22 @@
         <v>20.95143919294578</v>
       </c>
       <c r="K25" t="n">
-        <v>3.410568018149296</v>
+        <v>1.85660300408006</v>
       </c>
       <c r="L25" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M25" t="n">
-        <v>54.05405405405406</v>
+        <v>48.71794871794872</v>
       </c>
       <c r="N25" t="n">
-        <v>19.67293334572595</v>
+        <v>19.29093100429186</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>4.438068632448888</v>
+        <v>6.031417517108695</v>
       </c>
       <c r="Q25" t="n">
         <v>44</v>
@@ -3383,10 +3349,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4502168543844061</v>
+        <v>0.4467021779816137</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3446,22 +3412,22 @@
         <v>11.40992936035117</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.47790222600506</v>
+        <v>6.215801270328813</v>
       </c>
       <c r="Z26" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AA26" t="n">
-        <v>45</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="AB26" t="n">
-        <v>10.85079422192864</v>
+        <v>10.78541321235292</v>
       </c>
       <c r="AC26" t="n">
         <v>10</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.784169924801507</v>
+        <v>4.035006729202828</v>
       </c>
       <c r="AE26" t="n">
         <v>36</v>
@@ -3492,10 +3458,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C27" t="n">
-        <v>51.95601466927229</v>
+        <v>51.10750056557596</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3545,20 +3511,22 @@
         <v>59.78102685472641</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.353592287580951</v>
+        <v>2.964625557853495</v>
       </c>
       <c r="Z27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>30.47755955003824</v>
+      </c>
       <c r="AC27" t="n">
         <v>6</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.710164130826322</v>
+        <v>3.12811122706208</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3579,10 +3547,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C28" t="n">
-        <v>1.487691096655141</v>
+        <v>1.456101022150011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3591,7 +3559,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3610,22 +3578,22 @@
         <v>13.72882306486436</v>
       </c>
       <c r="K28" t="n">
-        <v>2.904988110044715</v>
+        <v>0.7198730356487548</v>
       </c>
       <c r="L28" t="n">
         <v>58</v>
       </c>
       <c r="M28" t="n">
-        <v>56.89655172413793</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="N28" t="n">
-        <v>11.97943300995943</v>
+        <v>12.64980473839546</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.270977539753404</v>
       </c>
       <c r="Q28" t="n">
         <v>39</v>
@@ -3649,19 +3617,19 @@
         <v>66.12903225806451</v>
       </c>
       <c r="X28" t="n">
-        <v>19.7827392720493</v>
+        <v>19.25959158767157</v>
       </c>
       <c r="Y28" t="n">
-        <v>11.22265563250302</v>
+        <v>13.10778012457149</v>
       </c>
       <c r="Z28" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AA28" t="n">
-        <v>41.66666666666666</v>
+        <v>37.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>9.818557091661756</v>
+        <v>10.14666280301502</v>
       </c>
       <c r="AC28" t="n">
         <v>6</v>
@@ -3698,10 +3666,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4127673769223423</v>
+        <v>0.4125619562758365</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3729,7 +3697,7 @@
         <v>27.65210909859499</v>
       </c>
       <c r="K29" t="n">
-        <v>24.64516782873802</v>
+        <v>24.5831360588096</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3764,25 +3732,25 @@
         <v>80</v>
       </c>
       <c r="X29" t="n">
-        <v>26.38498501083495</v>
+        <v>31.16629801654502</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.376601169789093</v>
+        <v>5.018943171595058</v>
       </c>
       <c r="Z29" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AA29" t="n">
-        <v>36.36363636363637</v>
+        <v>50</v>
       </c>
       <c r="AB29" t="n">
-        <v>14.10696912734857</v>
+        <v>16.48525139570154</v>
       </c>
       <c r="AC29" t="n">
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>8.743765609880128</v>
+        <v>5.244263429710871</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3813,10 +3781,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4304632994208545</v>
+        <v>0.4298377311149045</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3858,10 +3826,10 @@
         <v>62.5</v>
       </c>
       <c r="S30" t="n">
-        <v>38.01893084905794</v>
+        <v>38.03099315950735</v>
       </c>
       <c r="T30" t="n">
-        <v>24.48106915094206</v>
+        <v>24.46900684049265</v>
       </c>
       <c r="U30" t="n">
         <v>48.36276351921527</v>
@@ -3876,7 +3844,7 @@
         <v>26.71344279693404</v>
       </c>
       <c r="Y30" t="n">
-        <v>7.199348139924256</v>
+        <v>7.334210151745635</v>
       </c>
       <c r="Z30" t="n">
         <v>14</v>
@@ -3885,13 +3853,13 @@
         <v>42.85714285714285</v>
       </c>
       <c r="AB30" t="n">
-        <v>15.99184991708219</v>
+        <v>13.20275114201591</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.017922615779201</v>
+        <v>2.876778855087458</v>
       </c>
       <c r="AE30" t="n">
         <v>46</v>
@@ -3900,10 +3868,10 @@
         <v>58.69565217391305</v>
       </c>
       <c r="AG30" t="n">
-        <v>41.20455998576611</v>
+        <v>41.16919076561428</v>
       </c>
       <c r="AH30" t="n">
-        <v>17.49109218814694</v>
+        <v>17.52646140829876</v>
       </c>
       <c r="AI30" t="n">
         <v>44.33949777984616</v>
@@ -3922,10 +3890,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C31" t="n">
-        <v>0.250623475159644</v>
+        <v>0.2529667030006376</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3982,25 +3950,25 @@
         <v>88.88888888888889</v>
       </c>
       <c r="X31" t="n">
-        <v>43.92873683590442</v>
+        <v>46.69172443138287</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>0.9661842127781872</v>
       </c>
       <c r="Z31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA31" t="n">
-        <v>40</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB31" t="n">
-        <v>15.92235005554299</v>
+        <v>13.1925943754797</v>
       </c>
       <c r="AC31" t="n">
         <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>9.999999999999998</v>
+        <v>9.121950634146348</v>
       </c>
       <c r="AE31" t="n">
         <v>10</v>
@@ -4031,10 +3999,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C32" t="n">
-        <v>2.413639872939202</v>
+        <v>2.367192480924665</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4094,22 +4062,22 @@
         <v>13.38656892008534</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.326752372719565</v>
+        <v>4.206348277949901</v>
       </c>
       <c r="Z32" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA32" t="n">
-        <v>38</v>
+        <v>31.81818181818182</v>
       </c>
       <c r="AB32" t="n">
-        <v>11.5745421240656</v>
+        <v>10.42723561662574</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>5.808394586130127</v>
+        <v>3.960232910900563</v>
       </c>
       <c r="AE32" t="n">
         <v>26</v>
@@ -4140,10 +4108,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C33" t="n">
-        <v>1.877618351909345</v>
+        <v>1.862287394854287</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4200,25 +4168,25 @@
         <v>62.06896551724138</v>
       </c>
       <c r="X33" t="n">
-        <v>15.08075747393909</v>
+        <v>15.09663082780621</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.4364446517429288</v>
+        <v>1.263010877035187</v>
       </c>
       <c r="Z33" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="AA33" t="n">
-        <v>44.18604651162791</v>
+        <v>46.80851063829788</v>
       </c>
       <c r="AB33" t="n">
-        <v>10.11579997979067</v>
+        <v>8.859407456327904</v>
       </c>
       <c r="AC33" t="n">
         <v>8</v>
       </c>
       <c r="AD33" t="n">
-        <v>7.596710786191785</v>
+        <v>6.823166457481012</v>
       </c>
       <c r="AE33" t="n">
         <v>29</v>
@@ -4249,10 +4217,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8107196267176359</v>
+        <v>0.8000329062377887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4277,19 +4245,19 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>17.17128775901768</v>
+        <v>15.41713612942789</v>
       </c>
       <c r="K34" t="n">
-        <v>7.848700041481282</v>
+        <v>6.427063172858127</v>
       </c>
       <c r="L34" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M34" t="n">
-        <v>61.53846153846154</v>
+        <v>63.33333333333334</v>
       </c>
       <c r="N34" t="n">
-        <v>11.00031860865239</v>
+        <v>12.85729889708578</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4322,16 +4290,16 @@
         <v>10.81830054752258</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.67970226160239</v>
+        <v>3.962556141872386</v>
       </c>
       <c r="Z34" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="AA34" t="n">
-        <v>44.68085106382978</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AB34" t="n">
-        <v>9.711710378926163</v>
+        <v>9.854642237875723</v>
       </c>
       <c r="AC34" t="n">
         <v>2</v>
@@ -4346,10 +4314,10 @@
         <v>57.57575757575758</v>
       </c>
       <c r="AG34" t="n">
-        <v>22.65805843121085</v>
+        <v>22.71196365752987</v>
       </c>
       <c r="AH34" t="n">
-        <v>34.91769914454672</v>
+        <v>34.8637939182277</v>
       </c>
       <c r="AI34" t="n">
         <v>40.80726333731245</v>
@@ -4368,19 +4336,19 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C35" t="n">
-        <v>1.510325368798926</v>
+        <v>1.467412541389877</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4399,10 +4367,10 @@
         <v>38.83766461406507</v>
       </c>
       <c r="K35" t="n">
-        <v>9.002305826275304</v>
+        <v>5.905226724153634</v>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4410,7 +4378,7 @@
         <v>6</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>0.08948876158230146</v>
       </c>
       <c r="Q35" t="n">
         <v>7</v>
@@ -4437,16 +4405,16 @@
         <v>13.94161507705984</v>
       </c>
       <c r="Y35" t="n">
-        <v>4.334947549623591</v>
+        <v>7.053075689221289</v>
       </c>
       <c r="Z35" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AA35" t="n">
-        <v>38.46153846153846</v>
+        <v>60</v>
       </c>
       <c r="AB35" t="n">
-        <v>13.51388623429965</v>
+        <v>12.113484413092</v>
       </c>
       <c r="AC35" t="n">
         <v>2</v>
@@ -4483,10 +4451,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08086619456917273</v>
+        <v>0.07959196265142011</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4503,11 +4471,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.27: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>5</v>
       </c>
@@ -4518,16 +4482,16 @@
         <v>11.49958181785439</v>
       </c>
       <c r="K36" t="n">
-        <v>4.715021295834587</v>
+        <v>3.064996546751586</v>
       </c>
       <c r="L36" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M36" t="n">
-        <v>77.27272727272727</v>
+        <v>62.06896551724138</v>
       </c>
       <c r="N36" t="n">
-        <v>20.77526017963306</v>
+        <v>19.64013762079417</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4568,25 +4532,25 @@
       </c>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF36" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AG36" t="n">
-        <v>60.45454545454546</v>
+        <v>64.26767676767678</v>
       </c>
       <c r="AH36" t="n">
-        <v>-0.4545454545454604</v>
+        <v>-14.26767676767678</v>
       </c>
       <c r="AI36" t="n">
-        <v>23.07242812760128</v>
+        <v>18.76163064826506</v>
       </c>
       <c r="AJ36" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK36" t="n">
-        <v>50</v>
+        <v>47.82608695652174</v>
       </c>
     </row>
     <row r="37">
@@ -4596,10 +4560,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C37" t="n">
-        <v>0.06070108747412039</v>
+        <v>0.05964255599202024</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4624,25 +4588,25 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>19.23788603874993</v>
+        <v>19.28857966930738</v>
       </c>
       <c r="K37" t="n">
-        <v>2.774093365115959</v>
+        <v>1.045300040063757</v>
       </c>
       <c r="L37" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="M37" t="n">
-        <v>55.10204081632653</v>
+        <v>63.33333333333334</v>
       </c>
       <c r="N37" t="n">
-        <v>16.7544449270143</v>
+        <v>17.5010023167375</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>7.030863905763929</v>
+        <v>8.862064793103475</v>
       </c>
       <c r="Q37" t="n">
         <v>30</v>
@@ -4705,10 +4669,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C38" t="n">
-        <v>1.704774548854062</v>
+        <v>1.702897805565267</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4768,22 +4732,22 @@
         <v>12.11239445105858</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.629744653639055</v>
+        <v>2.736937111065374</v>
       </c>
       <c r="Z38" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="AA38" t="n">
-        <v>53.44827586206897</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB38" t="n">
-        <v>12.39433008043723</v>
+        <v>11.82499297704789</v>
       </c>
       <c r="AC38" t="n">
         <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>7.569308840922528</v>
+        <v>7.467442082538945</v>
       </c>
       <c r="AE38" t="n">
         <v>30</v>
@@ -4814,10 +4778,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C39" t="n">
-        <v>2.761384954515048</v>
+        <v>2.766180614112663</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4877,22 +4841,22 @@
         <v>10.27889366548247</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.239507217631699</v>
+        <v>3.071464589195216</v>
       </c>
       <c r="Z39" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AA39" t="n">
-        <v>36.58536585365854</v>
+        <v>39.53488372093023</v>
       </c>
       <c r="AB39" t="n">
-        <v>13.81425650134411</v>
+        <v>13.73331422453536</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.852913108428612</v>
+        <v>3.021334634215822</v>
       </c>
       <c r="AE39" t="n">
         <v>40</v>
@@ -4901,10 +4865,10 @@
         <v>60</v>
       </c>
       <c r="AG39" t="n">
-        <v>40.65867006314829</v>
+        <v>40.53816623440648</v>
       </c>
       <c r="AH39" t="n">
-        <v>19.34132993685171</v>
+        <v>19.46183376559352</v>
       </c>
       <c r="AI39" t="n">
         <v>44.59589366034619</v>
@@ -4923,10 +4887,10 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C40" t="n">
-        <v>0.24794850955896</v>
+        <v>0.2430948316640273</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4954,16 +4918,16 @@
         <v>15.29580504962521</v>
       </c>
       <c r="K40" t="n">
-        <v>11.08345360075209</v>
+        <v>8.90895654814312</v>
       </c>
       <c r="L40" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M40" t="n">
-        <v>55.55555555555556</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N40" t="n">
-        <v>13.7128941953404</v>
+        <v>12.70962245278844</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4996,16 +4960,16 @@
         <v>37.29449902814472</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.907654904409831</v>
+        <v>7.74954512704189</v>
       </c>
       <c r="Z40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AA40" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="AB40" t="n">
-        <v>24.60025056300582</v>
+        <v>16.01331603323763</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
@@ -5042,10 +5006,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C41" t="n">
-        <v>1.263405695123177</v>
+        <v>1.24735207617794</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5073,22 +5037,22 @@
         <v>40.38073481248902</v>
       </c>
       <c r="K41" t="n">
-        <v>4.936719128710898</v>
+        <v>3.603327876195328</v>
       </c>
       <c r="L41" t="n">
         <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>33.33333333333334</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N41" t="n">
-        <v>32.97150766357895</v>
+        <v>21.36094221486254</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>4.825080213417676</v>
+        <v>6.174195612180156</v>
       </c>
       <c r="Q41" t="n">
         <v>11</v>
@@ -5115,16 +5079,16 @@
         <v>14.15095011586145</v>
       </c>
       <c r="Y41" t="n">
-        <v>8.071970472254719</v>
+        <v>9.240065219746718</v>
       </c>
       <c r="Z41" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA41" t="n">
-        <v>37.03703703703704</v>
+        <v>37.5</v>
       </c>
       <c r="AB41" t="n">
-        <v>14.37117526549674</v>
+        <v>13.53212031871867</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
@@ -5161,10 +5125,10 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C42" t="n">
-        <v>3.642065186717305</v>
+        <v>3.557986960903277</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5192,13 +5156,17 @@
         <v>17.9384880883827</v>
       </c>
       <c r="K42" t="n">
-        <v>14.7591804589905</v>
+        <v>12.10992851148196</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M42" t="n">
+        <v>20</v>
+      </c>
+      <c r="N42" t="n">
+        <v>9.959430284360081</v>
+      </c>
       <c r="O42" t="n">
         <v>2</v>
       </c>
@@ -5225,21 +5193,25 @@
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="n">
-        <v>25.05719957835557</v>
+        <v>23.7260422361657</v>
       </c>
       <c r="Y42" t="n">
-        <v>5.826881457971112</v>
+        <v>8.000897660444583</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>17.57607561221978</v>
+      </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.431326695596738</v>
+        <v>2.172958527548474</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5268,10 +5240,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C43" t="n">
-        <v>6.142126882684269</v>
+        <v>6.06194599263723</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5290,7 +5262,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -5300,25 +5272,25 @@
         <v>10</v>
       </c>
       <c r="J43" t="n">
-        <v>21.22543766944611</v>
+        <v>20.13868121382601</v>
       </c>
       <c r="K43" t="n">
-        <v>2.524994545854198</v>
+        <v>1.186607131890227</v>
       </c>
       <c r="L43" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M43" t="n">
-        <v>85.71428571428571</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N43" t="n">
-        <v>17.42685962857633</v>
+        <v>17.32461006185299</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>1.438678890625167</v>
+        <v>2.780400438214814</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5381,10 +5353,10 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C44" t="n">
-        <v>4.707935174176374</v>
+        <v>4.752894720605475</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5409,10 +5381,10 @@
         <v>10</v>
       </c>
       <c r="J44" t="n">
-        <v>26.23855258451538</v>
+        <v>25.31049029846984</v>
       </c>
       <c r="K44" t="n">
-        <v>22.5832446046945</v>
+        <v>23.7538824476845</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5447,25 +5419,25 @@
         <v>50</v>
       </c>
       <c r="X44" t="n">
-        <v>25.5835288660526</v>
+        <v>26.00298103586976</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.389074656882928</v>
+        <v>1.784956649196257</v>
       </c>
       <c r="Z44" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA44" t="n">
-        <v>33.33333333333334</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB44" t="n">
-        <v>10.54415424791634</v>
+        <v>12.30426359661034</v>
       </c>
       <c r="AC44" t="n">
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>7.797206425780234</v>
+        <v>8.364343251839045</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5475,10 +5447,10 @@
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK44" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45">
@@ -5488,10 +5460,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02119393803986932</v>
+        <v>0.02097772659029678</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5519,22 +5491,22 @@
         <v>15.15550562104173</v>
       </c>
       <c r="K45" t="n">
-        <v>2.763685035928143</v>
+        <v>1.7153340752319</v>
       </c>
       <c r="L45" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="M45" t="n">
-        <v>63.63636363636363</v>
+        <v>58.66666666666666</v>
       </c>
       <c r="N45" t="n">
-        <v>16.4803454247224</v>
+        <v>15.43285327996341</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>7.041704432399354</v>
+        <v>8.14495277441698</v>
       </c>
       <c r="Q45" t="n">
         <v>38</v>
@@ -5561,16 +5533,16 @@
         <v>20.3749963300697</v>
       </c>
       <c r="Y45" t="n">
-        <v>12.81067102608155</v>
+        <v>13.70013909800125</v>
       </c>
       <c r="Z45" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AA45" t="n">
-        <v>58.33333333333334</v>
+        <v>50</v>
       </c>
       <c r="AB45" t="n">
-        <v>8.31103767842373</v>
+        <v>8.271693522313809</v>
       </c>
       <c r="AC45" t="n">
         <v>5</v>
@@ -5579,25 +5551,25 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF45" t="n">
-        <v>55.55555555555556</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="AG45" t="n">
-        <v>43.31878046274331</v>
+        <v>42.8964297882336</v>
       </c>
       <c r="AH45" t="n">
-        <v>12.23677509281224</v>
+        <v>14.99830705387166</v>
       </c>
       <c r="AI45" t="n">
-        <v>33.71641564204278</v>
+        <v>36.27590353425504</v>
       </c>
       <c r="AJ45" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AK45" t="n">
-        <v>62.76595744680851</v>
+        <v>63.1578947368421</v>
       </c>
     </row>
     <row r="46">
@@ -5607,10 +5579,10 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C46" t="n">
-        <v>10.33976133517201</v>
+        <v>9.974703329699937</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5667,19 +5639,19 @@
         <v>65.47619047619048</v>
       </c>
       <c r="X46" t="n">
-        <v>31.25332736924942</v>
+        <v>27.45411700532656</v>
       </c>
       <c r="Y46" t="n">
-        <v>4.596171497149726</v>
+        <v>7.964521134890267</v>
       </c>
       <c r="Z46" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AA46" t="n">
-        <v>40</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB46" t="n">
-        <v>11.35131831309704</v>
+        <v>11.25888400386826</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
@@ -5716,10 +5688,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C47" t="n">
-        <v>1.028831973648956</v>
+        <v>0.981428542048002</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5744,25 +5716,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>10.51409731847847</v>
+        <v>13.69562606453565</v>
       </c>
       <c r="K47" t="n">
-        <v>2.43384943017575</v>
+        <v>1.31635148649718</v>
       </c>
       <c r="L47" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="M47" t="n">
-        <v>52.83018867924528</v>
+        <v>57.35294117647059</v>
       </c>
       <c r="N47" t="n">
-        <v>13.07807997167045</v>
+        <v>14.10046870176711</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>7.386377268757971</v>
+        <v>8.570826313914527</v>
       </c>
       <c r="Q47" t="n">
         <v>51</v>
@@ -5789,7 +5761,7 @@
         <v>66.65983471422588</v>
       </c>
       <c r="Y47" t="n">
-        <v>8.33614518597663</v>
+        <v>12.55955715532406</v>
       </c>
       <c r="Z47" t="n">
         <v>2</v>
@@ -5809,19 +5781,19 @@
         <v>53.65853658536585</v>
       </c>
       <c r="AG47" t="n">
-        <v>31.41720204727116</v>
+        <v>31.32339341687716</v>
       </c>
       <c r="AH47" t="n">
-        <v>22.24133453809469</v>
+        <v>22.33514316848869</v>
       </c>
       <c r="AI47" t="n">
         <v>38.74647126766948</v>
       </c>
       <c r="AJ47" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AK47" t="n">
-        <v>52</v>
+        <v>52.63157894736842</v>
       </c>
     </row>
     <row r="48">
@@ -5831,10 +5803,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05843765425136316</v>
+        <v>0.05758591613022643</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5843,7 +5815,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5858,17 +5830,27 @@
       <c r="I48" t="n">
         <v>10</v>
       </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="J48" t="n">
+        <v>10.39336704032353</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1.449275729888666</v>
+      </c>
       <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="M48" t="n">
+        <v>56.06060606060606</v>
+      </c>
+      <c r="N48" t="n">
+        <v>15.59794251040301</v>
+      </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
-      <c r="P48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>8.428571035714306</v>
+      </c>
       <c r="Q48" t="n">
         <v>47</v>
       </c>
@@ -5876,10 +5858,10 @@
         <v>63.82978723404256</v>
       </c>
       <c r="S48" t="n">
-        <v>48.33899796908207</v>
+        <v>48.3518668777986</v>
       </c>
       <c r="T48" t="n">
-        <v>15.49078926496049</v>
+        <v>15.47792035624396</v>
       </c>
       <c r="U48" t="n">
         <v>49.53589653479511</v>
@@ -5894,16 +5876,16 @@
         <v>19.37342145735985</v>
       </c>
       <c r="Y48" t="n">
-        <v>7.750163796341536</v>
+        <v>9.094719856468513</v>
       </c>
       <c r="Z48" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA48" t="n">
-        <v>61.11111111111111</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="AB48" t="n">
-        <v>14.06492007635003</v>
+        <v>11.70781901458699</v>
       </c>
       <c r="AC48" t="n">
         <v>6</v>
@@ -5940,10 +5922,10 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2866325942373575</v>
+        <v>0.2852559488308002</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5994,31 +5976,31 @@
         <v>59.10955707120475</v>
       </c>
       <c r="V49" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="W49" t="n">
-        <v>67.6056338028169</v>
+        <v>67.14285714285714</v>
       </c>
       <c r="X49" t="n">
         <v>22.46912765663718</v>
       </c>
       <c r="Y49" t="n">
-        <v>5.823022365854269</v>
+        <v>6.275337651240587</v>
       </c>
       <c r="Z49" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA49" t="n">
-        <v>56.52173913043478</v>
+        <v>47.61904761904762</v>
       </c>
       <c r="AB49" t="n">
-        <v>9.80850458894038</v>
+        <v>8.814786576143803</v>
       </c>
       <c r="AC49" t="n">
         <v>10</v>
       </c>
       <c r="AD49" t="n">
-        <v>4.435242815258156</v>
+        <v>3.974047230919375</v>
       </c>
       <c r="AE49" t="n">
         <v>45</v>
@@ -6027,10 +6009,10 @@
         <v>62.22222222222222</v>
       </c>
       <c r="AG49" t="n">
-        <v>35.78966959361963</v>
+        <v>35.7721257339705</v>
       </c>
       <c r="AH49" t="n">
-        <v>26.43255262860259</v>
+        <v>26.45009648825172</v>
       </c>
       <c r="AI49" t="n">
         <v>47.62993448088954</v>
@@ -6049,14 +6031,14 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7341745027746533</v>
+        <v>0.7214692635172655</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6066,7 +6048,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -6112,22 +6094,22 @@
         <v>15.51990994893744</v>
       </c>
       <c r="Y50" t="n">
-        <v>4.81441508125312</v>
+        <v>6.461646939178712</v>
       </c>
       <c r="Z50" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AA50" t="n">
-        <v>47.5</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="AB50" t="n">
-        <v>13.14115705107153</v>
+        <v>11.75200790891181</v>
       </c>
       <c r="AC50" t="n">
         <v>5</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.1949716639397692</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
         <v>42</v>
@@ -6158,10 +6140,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1452710734446342</v>
+        <v>0.1441704543117455</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6180,7 +6162,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -6193,16 +6175,16 @@
         <v>31.62908307640215</v>
       </c>
       <c r="K51" t="n">
-        <v>9.076960151412683</v>
+        <v>8.250558952238318</v>
       </c>
       <c r="L51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M51" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N51" t="n">
-        <v>18.55049099402528</v>
+        <v>16.83520922432485</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
@@ -6235,22 +6217,22 @@
         <v>15.73461610040814</v>
       </c>
       <c r="Y51" t="n">
-        <v>5.752519145369139</v>
+        <v>6.466567566679315</v>
       </c>
       <c r="Z51" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AA51" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="AB51" t="n">
-        <v>14.67756923495132</v>
+        <v>13.2147918597851</v>
       </c>
       <c r="AC51" t="n">
         <v>10</v>
       </c>
       <c r="AD51" t="n">
-        <v>4.506731443763734</v>
+        <v>3.777721335993567</v>
       </c>
       <c r="AE51" t="n">
         <v>12</v>
@@ -6281,10 +6263,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C52" t="n">
-        <v>4.640032201156793</v>
+        <v>4.637722888345023</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6341,25 +6323,25 @@
         <v>67.9245283018868</v>
       </c>
       <c r="X52" t="n">
-        <v>17.91269838085297</v>
+        <v>17.68393155583896</v>
       </c>
       <c r="Y52" t="n">
-        <v>3.281571370711567</v>
+        <v>3.329707481989475</v>
       </c>
       <c r="Z52" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA52" t="n">
-        <v>42.42424242424242</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="AB52" t="n">
-        <v>10.26390610313524</v>
+        <v>10.21277776758257</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>4.878520770197447</v>
+        <v>4.831155876703697</v>
       </c>
       <c r="AE52" t="n">
         <v>37</v>
@@ -6368,10 +6350,10 @@
         <v>67.56756756756756</v>
       </c>
       <c r="AG52" t="n">
-        <v>39.9900855762727</v>
+        <v>39.9823855685727</v>
       </c>
       <c r="AH52" t="n">
-        <v>27.57748199129486</v>
+        <v>27.58518199899486</v>
       </c>
       <c r="AI52" t="n">
         <v>51.4636672419722</v>
@@ -6390,10 +6372,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C53" t="n">
-        <v>1.279866990857548</v>
+        <v>1.263805195072291</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6418,25 +6400,25 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>27.62577208921607</v>
+        <v>27.61578934530905</v>
       </c>
       <c r="K53" t="n">
-        <v>2.894954471461286</v>
+        <v>1.589653305366023</v>
       </c>
       <c r="L53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M53" t="n">
-        <v>42.85714285714285</v>
+        <v>50</v>
       </c>
       <c r="N53" t="n">
-        <v>14.5774480486538</v>
+        <v>11.29718397440806</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>4.9614148281242</v>
+        <v>6.310038951865771</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6491,14 +6473,14 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C54" t="n">
-        <v>0.07201823815542693</v>
+        <v>0.07198239516278306</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6508,7 +6490,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -6519,19 +6501,19 @@
         <v>10</v>
       </c>
       <c r="J54" t="n">
-        <v>33.70709684948975</v>
+        <v>29.5817777621179</v>
       </c>
       <c r="K54" t="n">
-        <v>14.75410024187047</v>
+        <v>14.68116966036195</v>
       </c>
       <c r="L54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M54" t="n">
-        <v>50</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N54" t="n">
-        <v>23.40347094180937</v>
+        <v>26.80962063787916</v>
       </c>
       <c r="O54" t="n">
         <v>10</v>
@@ -6560,17 +6542,27 @@
       <c r="W54" t="n">
         <v>69.09090909090909</v>
       </c>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
+      <c r="X54" t="n">
+        <v>14.75410024187049</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0.06355379141557149</v>
+      </c>
       <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>44.44444444444444</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>15.4251043447565</v>
+      </c>
       <c r="AC54" t="n">
         <v>2</v>
       </c>
-      <c r="AD54" t="inlineStr"/>
+      <c r="AD54" t="n">
+        <v>1.937677676213079</v>
+      </c>
       <c r="AE54" t="n">
         <v>7</v>
       </c>
@@ -6600,10 +6592,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9465254157570397</v>
+        <v>0.931657857392592</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6663,16 +6655,16 @@
         <v>23.0932342837701</v>
       </c>
       <c r="Y55" t="n">
-        <v>5.302317133073542</v>
+        <v>6.789782026846014</v>
       </c>
       <c r="Z55" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA55" t="n">
-        <v>54.16666666666666</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="AB55" t="n">
-        <v>13.85762791170396</v>
+        <v>9.365455206540789</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6681,19 +6673,19 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AF55" t="n">
-        <v>57.77777777777778</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="AG55" t="n">
-        <v>40.75068408788739</v>
+        <v>39.21176783834306</v>
       </c>
       <c r="AH55" t="n">
-        <v>17.02709368989039</v>
+        <v>19.87914125256603</v>
       </c>
       <c r="AI55" t="n">
-        <v>43.30078870920313</v>
+        <v>44.4097537410319</v>
       </c>
       <c r="AJ55" t="n">
         <v>70</v>
@@ -6709,10 +6701,10 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7745046972111842</v>
+        <v>0.69678958517574</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6740,7 +6732,7 @@
         <v>55.30631598314248</v>
       </c>
       <c r="K56" t="n">
-        <v>20.53596550970374</v>
+        <v>8.441182743870046</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6767,10 +6759,10 @@
         <v>100</v>
       </c>
       <c r="X56" t="n">
-        <v>44.681589993367</v>
+        <v>44.70154625822338</v>
       </c>
       <c r="Y56" t="n">
-        <v>16.68880227592897</v>
+        <v>25.05872566810435</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -6804,10 +6796,10 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C57" t="n">
-        <v>1.494892889194192</v>
+        <v>1.459185981942702</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6864,25 +6856,25 @@
         <v>78.94736842105263</v>
       </c>
       <c r="X57" t="n">
-        <v>20.60896542669768</v>
+        <v>20.62560129901716</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.824322256756761</v>
+        <v>4.182555966228851</v>
       </c>
       <c r="Z57" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AA57" t="n">
-        <v>33.33333333333334</v>
+        <v>45.65217391304348</v>
       </c>
       <c r="AB57" t="n">
-        <v>15.38906972645917</v>
+        <v>14.65689458546553</v>
       </c>
       <c r="AC57" t="n">
         <v>5</v>
       </c>
       <c r="AD57" t="n">
-        <v>3.234688892648674</v>
+        <v>0.85312652827918</v>
       </c>
       <c r="AE57" t="n">
         <v>44</v>
@@ -6913,10 +6905,10 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7407590210272486</v>
+        <v>0.7338091026880283</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6930,10 +6922,14 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+          <t>BAZ_ORAN_YETERSİZ</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6944,16 +6940,16 @@
         <v>18.04392839464337</v>
       </c>
       <c r="K58" t="n">
-        <v>13.54048211491103</v>
+        <v>12.47522734717288</v>
       </c>
       <c r="L58" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M58" t="n">
-        <v>70</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="N58" t="n">
-        <v>11.43434035720937</v>
+        <v>15.05992327858505</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
@@ -6986,22 +6982,22 @@
         <v>20.50322102897642</v>
       </c>
       <c r="Y58" t="n">
-        <v>5.778052117288301</v>
+        <v>6.662057340254091</v>
       </c>
       <c r="Z58" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AA58" t="n">
         <v>50</v>
       </c>
       <c r="AB58" t="n">
-        <v>13.51897332578328</v>
+        <v>9.219813182547147</v>
       </c>
       <c r="AC58" t="n">
         <v>6</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.23555858024501</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>4</v>
@@ -7032,10 +7028,10 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7716239802367172</v>
+        <v>0.7535528453612489</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7063,22 +7059,22 @@
         <v>11.95882015364728</v>
       </c>
       <c r="K59" t="n">
-        <v>5.332104740194143</v>
+        <v>2.865267627520351</v>
       </c>
       <c r="L59" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="M59" t="n">
-        <v>73.17073170731707</v>
+        <v>66.10169491525424</v>
       </c>
       <c r="N59" t="n">
-        <v>12.12870417056454</v>
+        <v>12.81977562584208</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>2.532841498217797</v>
+        <v>4.991706618674008</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7141,10 +7137,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C60" t="n">
-        <v>11.26571011145607</v>
+        <v>11.13670485161343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7161,11 +7157,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>5</v>
       </c>
@@ -7176,22 +7168,22 @@
         <v>24.49246832941995</v>
       </c>
       <c r="K60" t="n">
-        <v>6.044164576171362</v>
+        <v>4.829837661081227</v>
       </c>
       <c r="L60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M60" t="n">
-        <v>75</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N60" t="n">
-        <v>11.3882026633556</v>
+        <v>12.28631987346338</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>1.844359311656207</v>
+        <v>3.024103069937056</v>
       </c>
       <c r="Q60" t="n">
         <v>46</v>
@@ -7200,10 +7192,10 @@
         <v>65.21739130434783</v>
       </c>
       <c r="S60" t="n">
-        <v>52.12379041597301</v>
+        <v>52.22209604257147</v>
       </c>
       <c r="T60" t="n">
-        <v>13.09360088837482</v>
+        <v>12.99529526177636</v>
       </c>
       <c r="U60" t="n">
         <v>50.77005884206276</v>
@@ -7232,10 +7224,10 @@
         <v>62.5</v>
       </c>
       <c r="AG60" t="n">
-        <v>22.92091994553108</v>
+        <v>23.22819855873075</v>
       </c>
       <c r="AH60" t="n">
-        <v>39.57908005446892</v>
+        <v>39.27180144126925</v>
       </c>
       <c r="AI60" t="n">
         <v>45.25440735307745</v>
@@ -7254,19 +7246,19 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7695663477716777</v>
+        <v>0.7868704111223084</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7274,11 +7266,7 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>5</v>
       </c>
@@ -7289,22 +7277,22 @@
         <v>14.0586191907223</v>
       </c>
       <c r="K61" t="n">
-        <v>7.790672973423152</v>
+        <v>10.21439724247424</v>
       </c>
       <c r="L61" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M61" t="n">
-        <v>75</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N61" t="n">
-        <v>28.22107408220757</v>
+        <v>15.5281052002875</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>2.049645823365065</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
@@ -7331,16 +7319,16 @@
         <v>49.99145178651283</v>
       </c>
       <c r="Y61" t="n">
-        <v>7.363207263027228</v>
+        <v>5.28022515919514</v>
       </c>
       <c r="Z61" t="n">
         <v>3</v>
       </c>
       <c r="AA61" t="n">
-        <v>33.33333333333334</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB61" t="n">
-        <v>17.71288688573473</v>
+        <v>13.92348961705937</v>
       </c>
       <c r="AC61" t="n">
         <v>4</v>
@@ -7377,10 +7365,10 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C62" t="n">
-        <v>9.115451286529753</v>
+        <v>9.090348189128601</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7440,43 +7428,43 @@
         <v>11.69351808836483</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.459754980938889</v>
+        <v>2.728371662031137</v>
       </c>
       <c r="Z62" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AA62" t="n">
-        <v>50</v>
+        <v>45.28301886792453</v>
       </c>
       <c r="AB62" t="n">
-        <v>14.29934569810199</v>
+        <v>15.47237123452912</v>
       </c>
       <c r="AC62" t="n">
         <v>5</v>
       </c>
       <c r="AD62" t="n">
-        <v>2.604304529442902</v>
+        <v>2.335345235587227</v>
       </c>
       <c r="AE62" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF62" t="n">
-        <v>46.15384615384615</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AG62" t="n">
-        <v>45.83395123004851</v>
+        <v>44.95944274827716</v>
       </c>
       <c r="AH62" t="n">
-        <v>0.3198949237976478</v>
+        <v>-0.5149983038327193</v>
       </c>
       <c r="AI62" t="n">
-        <v>28.75585353039122</v>
+        <v>27.585858177023</v>
       </c>
       <c r="AJ62" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AK62" t="n">
-        <v>41.26984126984127</v>
+        <v>40.625</v>
       </c>
     </row>
     <row r="63">
@@ -7486,10 +7474,10 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1123484523455316</v>
+        <v>0.1127038644263003</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7517,16 +7505,16 @@
         <v>14.68172212919103</v>
       </c>
       <c r="K63" t="n">
-        <v>7.318032655591145</v>
+        <v>7.657531104335447</v>
       </c>
       <c r="L63" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M63" t="n">
-        <v>70</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N63" t="n">
-        <v>16.50892123190014</v>
+        <v>16.64786066066635</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
@@ -7559,7 +7547,7 @@
         <v>24.85614965143601</v>
       </c>
       <c r="Y63" t="n">
-        <v>8.438102693417237</v>
+        <v>8.148448463550494</v>
       </c>
       <c r="Z63" t="n">
         <v>4</v>
@@ -7574,7 +7562,7 @@
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.705837638284136</v>
+        <v>2.015808666786378</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7605,10 +7593,10 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1522671341577095</v>
+        <v>0.1501347099109475</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7617,7 +7605,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7632,27 +7620,17 @@
       <c r="I64" t="n">
         <v>10</v>
       </c>
-      <c r="J64" t="n">
-        <v>13.75031229705044</v>
-      </c>
-      <c r="K64" t="n">
-        <v>5.028496249803416</v>
-      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="n">
-        <v>60</v>
-      </c>
-      <c r="M64" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N64" t="n">
-        <v>17.30854255432677</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
         <v>5</v>
       </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
+      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="n">
         <v>55</v>
       </c>
@@ -7678,16 +7656,16 @@
         <v>14.28923074155179</v>
       </c>
       <c r="Y64" t="n">
-        <v>8.102893362446528</v>
+        <v>9.389865889283611</v>
       </c>
       <c r="Z64" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="AA64" t="n">
-        <v>58.53658536585366</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB64" t="n">
-        <v>12.94627544016335</v>
+        <v>14.80997747696459</v>
       </c>
       <c r="AC64" t="n">
         <v>2</v>
@@ -7702,10 +7680,10 @@
         <v>65.21739130434783</v>
       </c>
       <c r="AG64" t="n">
-        <v>35.142051862499</v>
+        <v>35.10227718069645</v>
       </c>
       <c r="AH64" t="n">
-        <v>30.07533944184883</v>
+        <v>30.11511412365138</v>
       </c>
       <c r="AI64" t="n">
         <v>50.77005884206276</v>
@@ -7724,10 +7702,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C65" t="n">
-        <v>6.58452463135332</v>
+        <v>6.540114760504289</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7787,16 +7765,16 @@
         <v>24.47056390537039</v>
       </c>
       <c r="Y65" t="n">
-        <v>6.621641673760315</v>
+        <v>7.251439732927201</v>
       </c>
       <c r="Z65" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AA65" t="n">
-        <v>36.8421052631579</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AB65" t="n">
-        <v>12.65472361368451</v>
+        <v>9.143786421853511</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
@@ -7833,14 +7811,14 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4592705866581358</v>
+        <v>0.4504041297328425</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7850,7 +7828,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -7864,22 +7842,22 @@
         <v>10.41136575766793</v>
       </c>
       <c r="K66" t="n">
-        <v>5.868665108348758</v>
+        <v>3.824815608314913</v>
       </c>
       <c r="L66" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="M66" t="n">
-        <v>44.82758620689656</v>
+        <v>50</v>
       </c>
       <c r="N66" t="n">
-        <v>17.34145782177475</v>
+        <v>21.68499124327241</v>
       </c>
       <c r="O66" t="n">
         <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>0.1240545458061959</v>
+        <v>2.095052496785654</v>
       </c>
       <c r="Q66" t="n">
         <v>35</v>
@@ -7906,22 +7884,22 @@
         <v>14.59585890675015</v>
       </c>
       <c r="Y66" t="n">
-        <v>5.153708838842008</v>
+        <v>6.984765691891049</v>
       </c>
       <c r="Z66" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AA66" t="n">
-        <v>45.23809523809524</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="AB66" t="n">
-        <v>10.30785411855192</v>
+        <v>11.59209911118779</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.8922764936796779</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
         <v>40</v>
@@ -7930,10 +7908,10 @@
         <v>42.5</v>
       </c>
       <c r="AG66" t="n">
-        <v>40.7661290257951</v>
+        <v>40.7036290257951</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.733870974204898</v>
+        <v>1.796370974204898</v>
       </c>
       <c r="AI66" t="n">
         <v>28.50939255995037</v>
@@ -7952,10 +7930,10 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02757269751109121</v>
+        <v>0.02755897414803694</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7983,7 +7961,7 @@
         <v>11.46300958938384</v>
       </c>
       <c r="K67" t="n">
-        <v>4.323675419603124</v>
+        <v>4.271751893718023</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
@@ -8041,10 +8019,10 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C68" t="n">
-        <v>1.928031055859394</v>
+        <v>1.734775723423071</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8069,10 +8047,10 @@
         <v>10</v>
       </c>
       <c r="J68" t="n">
-        <v>65.47234600206727</v>
+        <v>68.93321055495181</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>1.813870809108664e-06</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -8083,7 +8061,7 @@
         <v>2</v>
       </c>
       <c r="P68" t="n">
-        <v>2.000000000000002</v>
+        <v>1.999998149851812</v>
       </c>
       <c r="Q68" t="n">
         <v>5</v>
@@ -8133,10 +8111,10 @@
         <v>30.06418425824019</v>
       </c>
       <c r="AJ68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK68" t="n">
-        <v>55.55555555555556</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69">
@@ -8146,10 +8124,10 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5197659178200797</v>
+        <v>0.5322583962322358</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8198,25 +8176,21 @@
         <v>75</v>
       </c>
       <c r="X69" t="n">
-        <v>35.62614614434849</v>
+        <v>45.32573627045717</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>4.431314623338256</v>
       </c>
       <c r="Z69" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>10.75287791700739</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
         <v>6</v>
       </c>
       <c r="AD69" t="n">
-        <v>6.000000000000005</v>
+        <v>1.641421947449773</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -8239,10 +8213,10 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C70" t="n">
-        <v>0.5078314685718831</v>
+        <v>0.4931822388581536</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8251,7 +8225,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -8259,28 +8233,34 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %83.33: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>5</v>
       </c>
       <c r="I70" t="n">
         <v>10</v>
       </c>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="J70" t="n">
+        <v>11.14419642238965</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.4187604690117253</v>
+      </c>
       <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="M70" t="n">
+        <v>50</v>
+      </c>
+      <c r="N70" t="n">
+        <v>12.19381899531639</v>
+      </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
-      <c r="P70" t="inlineStr"/>
+      <c r="P70" t="n">
+        <v>7.549624687239365</v>
+      </c>
       <c r="Q70" t="n">
         <v>31</v>
       </c>
@@ -8297,25 +8277,25 @@
         <v>37.77216763735451</v>
       </c>
       <c r="V70" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="W70" t="n">
-        <v>67.79661016949153</v>
+        <v>67.24137931034483</v>
       </c>
       <c r="X70" t="n">
         <v>44.93251946562029</v>
       </c>
       <c r="Y70" t="n">
-        <v>8.121724230695005</v>
+        <v>10.77210344258391</v>
       </c>
       <c r="Z70" t="n">
         <v>6</v>
       </c>
       <c r="AA70" t="n">
-        <v>83.33333333333333</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB70" t="n">
-        <v>9.232894104121055</v>
+        <v>8.505081411414517</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
@@ -8324,19 +8304,19 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AF70" t="n">
-        <v>51.16279069767442</v>
+        <v>52.38095238095238</v>
       </c>
       <c r="AG70" t="n">
-        <v>32.82426759501791</v>
+        <v>32.38479655485045</v>
       </c>
       <c r="AH70" t="n">
-        <v>18.33852310265651</v>
+        <v>19.99615582610193</v>
       </c>
       <c r="AI70" t="n">
-        <v>36.75230846944931</v>
+        <v>37.72246413134498</v>
       </c>
       <c r="AJ70" t="n">
         <v>56</v>
@@ -8352,10 +8332,10 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C71" t="n">
-        <v>3.172917743974631</v>
+        <v>3.14871562840631</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8451,10 +8431,10 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C72" t="n">
-        <v>0.06419911289226453</v>
+        <v>0.06478415564650475</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8486,16 +8466,16 @@
         <v>29.77666337790048</v>
       </c>
       <c r="K72" t="n">
-        <v>7.583272725979784</v>
+        <v>8.563672786824972</v>
       </c>
       <c r="L72" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M72" t="n">
         <v>100</v>
       </c>
       <c r="N72" t="n">
-        <v>17.9012886820146</v>
+        <v>22.47171058340287</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
@@ -8528,22 +8508,22 @@
         <v>12.03392243896149</v>
       </c>
       <c r="Y72" t="n">
-        <v>3.972591172469686</v>
+        <v>3.097499022251216</v>
       </c>
       <c r="Z72" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA72" t="n">
-        <v>42.42424242424242</v>
+        <v>38.23529411764706</v>
       </c>
       <c r="AB72" t="n">
-        <v>12.55739309258082</v>
+        <v>12.81395919933085</v>
       </c>
       <c r="AC72" t="n">
         <v>8</v>
       </c>
       <c r="AD72" t="n">
-        <v>4.194020099786011</v>
+        <v>5.059209956690913</v>
       </c>
       <c r="AE72" t="n">
         <v>10</v>
@@ -8574,10 +8554,10 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C73" t="n">
-        <v>0.06234721698582756</v>
+        <v>0.0621105238261728</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8609,22 +8589,22 @@
         <v>19.59098648410814</v>
       </c>
       <c r="K73" t="n">
-        <v>2.130007687398394</v>
+        <v>1.742284299190211</v>
       </c>
       <c r="L73" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M73" t="n">
         <v>75</v>
       </c>
       <c r="N73" t="n">
-        <v>12.3596071563907</v>
+        <v>14.97241292837137</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>7.70585696682824</v>
+        <v>8.116306565839038</v>
       </c>
       <c r="Q73" t="n">
         <v>14</v>
@@ -8659,25 +8639,25 @@
       </c>
       <c r="AD73" t="inlineStr"/>
       <c r="AE73" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF73" t="n">
-        <v>92.85714285714286</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="AG73" t="n">
-        <v>39.03305028305028</v>
+        <v>39.39380989380989</v>
       </c>
       <c r="AH73" t="n">
-        <v>53.82409257409258</v>
+        <v>53.93952343952343</v>
       </c>
       <c r="AI73" t="n">
-        <v>68.5312955758489</v>
+        <v>70.18347012621999</v>
       </c>
       <c r="AJ73" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AK73" t="n">
-        <v>69.6969696969697</v>
+        <v>70.58823529411765</v>
       </c>
     </row>
     <row r="74">
@@ -8687,19 +8667,19 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C74" t="n">
-        <v>5.416800341261755</v>
+        <v>5.475803632025996</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8714,31 +8694,41 @@
       <c r="I74" t="n">
         <v>10</v>
       </c>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="J74" t="n">
+        <v>10.38264080673934</v>
+      </c>
+      <c r="K74" t="n">
+        <v>2.998065764023217</v>
+      </c>
       <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="M74" t="n">
+        <v>69.49152542372882</v>
+      </c>
+      <c r="N74" t="n">
+        <v>14.87070545691084</v>
+      </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
-      <c r="P74" t="inlineStr"/>
+      <c r="P74" t="n">
+        <v>4.856338028169005</v>
+      </c>
       <c r="Q74" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R74" t="n">
-        <v>74.19354838709677</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="S74" t="n">
-        <v>63.60620966367966</v>
+        <v>65.58898631460762</v>
       </c>
       <c r="T74" t="n">
-        <v>10.5873387234171</v>
+        <v>11.07768035205905</v>
       </c>
       <c r="U74" t="n">
-        <v>56.7538641905662</v>
+        <v>59.07167384187784</v>
       </c>
       <c r="V74" t="n">
         <v>115</v>
@@ -8750,37 +8740,37 @@
         <v>25.51128431523497</v>
       </c>
       <c r="Y74" t="n">
-        <v>8.690456018147231</v>
+        <v>7.695853442144484</v>
       </c>
       <c r="Z74" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA74" t="n">
-        <v>47.05882352941177</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB74" t="n">
-        <v>14.21730098732097</v>
+        <v>13.55476783829268</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>1.434180836685628</v>
+        <v>2.496254657867714</v>
       </c>
       <c r="AE74" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AF74" t="n">
-        <v>50</v>
+        <v>51.35135135135135</v>
       </c>
       <c r="AG74" t="n">
-        <v>31.49600270292994</v>
+        <v>29.50438925148781</v>
       </c>
       <c r="AH74" t="n">
-        <v>18.50399729707006</v>
+        <v>21.84696209986354</v>
       </c>
       <c r="AI74" t="n">
-        <v>34.8499283643951</v>
+        <v>35.89489666561879</v>
       </c>
       <c r="AJ74" t="n">
         <v>90</v>
@@ -8796,10 +8786,10 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1113196164623211</v>
+        <v>0.1092075766612508</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8816,7 +8806,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %81.82: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>5</v>
       </c>
@@ -8824,25 +8818,25 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>27.52764323146838</v>
+        <v>28.79453108040966</v>
       </c>
       <c r="K75" t="n">
-        <v>0.7211083052176326</v>
+        <v>0.5681818181817899</v>
       </c>
       <c r="L75" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M75" t="n">
-        <v>58.33333333333334</v>
+        <v>81.81818181818181</v>
       </c>
       <c r="N75" t="n">
-        <v>25.80761441427322</v>
+        <v>15.72994592528538</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>5.241097703954578</v>
+        <v>5.401129943502858</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8905,10 +8899,10 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C76" t="n">
-        <v>1.960953804533661</v>
+        <v>1.957921148427699</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8965,25 +8959,25 @@
         <v>60.71428571428572</v>
       </c>
       <c r="X76" t="n">
-        <v>13.07996475682189</v>
+        <v>12.76370567693843</v>
       </c>
       <c r="Y76" t="n">
-        <v>3.420833648329114</v>
+        <v>3.570195350714933</v>
       </c>
       <c r="Z76" t="n">
         <v>49</v>
       </c>
       <c r="AA76" t="n">
-        <v>40.81632653061224</v>
+        <v>34.69387755102041</v>
       </c>
       <c r="AB76" t="n">
-        <v>9.244615958876594</v>
+        <v>9.460511236049042</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.5996804213053486</v>
+        <v>0.4457176397362539</v>
       </c>
       <c r="AE76" t="n">
         <v>32</v>
@@ -9014,24 +9008,24 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4996008206018144</v>
+        <v>0.4861896633280546</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AL_BEKLE_EŞİK</t>
-        </is>
-      </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -9045,22 +9039,22 @@
         <v>15.97566139565814</v>
       </c>
       <c r="K77" t="n">
-        <v>4.022433800365999</v>
+        <v>1.230082062401494</v>
       </c>
       <c r="L77" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="M77" t="n">
-        <v>61.22448979591837</v>
+        <v>64.15094339622641</v>
       </c>
       <c r="N77" t="n">
-        <v>14.31128721336326</v>
+        <v>15.94290778922146</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>3.823758062868943</v>
+        <v>6.687654301638624</v>
       </c>
       <c r="Q77" t="n">
         <v>27</v>
@@ -9087,22 +9081,22 @@
         <v>15.48402810769924</v>
       </c>
       <c r="Y77" t="n">
-        <v>9.924830727799227</v>
+        <v>12.34278564651786</v>
       </c>
       <c r="Z77" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="AA77" t="n">
-        <v>42.85714285714285</v>
+        <v>50</v>
       </c>
       <c r="AB77" t="n">
-        <v>12.87219899014971</v>
+        <v>11.72863146980229</v>
       </c>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.08345171350565561</v>
+        <v>0</v>
       </c>
       <c r="AE77" t="n">
         <v>46</v>
@@ -9133,10 +9127,10 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05802612187343636</v>
+        <v>0.05881990004730272</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9164,16 +9158,16 @@
         <v>10.6248408751511</v>
       </c>
       <c r="K78" t="n">
-        <v>7.386646859614832</v>
+        <v>8.855660705271795</v>
       </c>
       <c r="L78" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M78" t="n">
-        <v>58.06451612903226</v>
+        <v>59.25925925925926</v>
       </c>
       <c r="N78" t="n">
-        <v>15.9870417988924</v>
+        <v>16.87180111065342</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
@@ -9206,22 +9200,22 @@
         <v>31.30012859028892</v>
       </c>
       <c r="Y78" t="n">
-        <v>4.023013490379679</v>
+        <v>2.710080028257711</v>
       </c>
       <c r="Z78" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA78" t="n">
-        <v>15.38461538461539</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="AB78" t="n">
-        <v>24.13546980577716</v>
+        <v>9.430677653834037</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>6.227520499428485</v>
+        <v>7.492985885752224</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9252,24 +9246,24 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C79" t="n">
-        <v>0.925537234029347</v>
+        <v>0.9057441951339901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AL_BEKLE_EŞİK</t>
-        </is>
-      </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -9280,25 +9274,25 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>10.44132241771839</v>
+        <v>10.42896938309872</v>
       </c>
       <c r="K79" t="n">
-        <v>3.736159841350162</v>
+        <v>1.503713770959236</v>
       </c>
       <c r="L79" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="M79" t="n">
-        <v>51.42857142857143</v>
+        <v>54.71698113207547</v>
       </c>
       <c r="N79" t="n">
-        <v>10.22453857935032</v>
+        <v>10.40261815720138</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>1.218321712103765</v>
+        <v>3.444490944370826</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9316,31 +9310,31 @@
         <v>41.04052722210609</v>
       </c>
       <c r="V79" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="W79" t="n">
-        <v>58.62068965517241</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="X79" t="n">
         <v>25.65117214954458</v>
       </c>
       <c r="Y79" t="n">
-        <v>7.095267071444922</v>
+        <v>9.082077460922267</v>
       </c>
       <c r="Z79" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA79" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AB79" t="n">
-        <v>12.03685269040846</v>
+        <v>9.501837951994744</v>
       </c>
       <c r="AC79" t="n">
         <v>8</v>
       </c>
       <c r="AD79" t="n">
-        <v>0.9738286737779323</v>
+        <v>0</v>
       </c>
       <c r="AE79" t="n">
         <v>36</v>
@@ -9371,10 +9365,10 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1335423854470074</v>
+        <v>0.132036279127162</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9391,11 +9385,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.86: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>5</v>
       </c>
@@ -9403,25 +9393,25 @@
         <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>16.34243584006749</v>
+        <v>10.48668504530712</v>
       </c>
       <c r="K80" t="n">
-        <v>9.335126555005345</v>
+        <v>3.289416608438467</v>
       </c>
       <c r="L80" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="M80" t="n">
-        <v>75.86206896551724</v>
+        <v>48.93617021276596</v>
       </c>
       <c r="N80" t="n">
-        <v>13.46167125698282</v>
+        <v>18.37249874375921</v>
       </c>
       <c r="O80" t="n">
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>0.6081059819875723</v>
+        <v>6.496874134743935</v>
       </c>
       <c r="Q80" t="n">
         <v>39</v>
@@ -9448,22 +9438,22 @@
         <v>16.92042739318289</v>
       </c>
       <c r="Y80" t="n">
-        <v>6.487575359838093</v>
+        <v>7.542219196423627</v>
       </c>
       <c r="Z80" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AA80" t="n">
-        <v>46.875</v>
+        <v>44</v>
       </c>
       <c r="AB80" t="n">
-        <v>15.31214417494626</v>
+        <v>11.59503040169198</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.617351540163514</v>
+        <v>0.4951241524484673</v>
       </c>
       <c r="AE80" t="n">
         <v>24</v>
@@ -9494,10 +9484,10 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C81" t="n">
-        <v>1.263405695123177</v>
+        <v>1.254550315694219</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9554,25 +9544,25 @@
         <v>65.30612244897959</v>
       </c>
       <c r="X81" t="n">
-        <v>23.62491956752233</v>
+        <v>23.75585078567732</v>
       </c>
       <c r="Y81" t="n">
-        <v>0.653255656236873</v>
+        <v>1.45396043255962</v>
       </c>
       <c r="Z81" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AA81" t="n">
-        <v>39.1304347826087</v>
+        <v>29.62962962962963</v>
       </c>
       <c r="AB81" t="n">
-        <v>12.69010541141389</v>
+        <v>11.88627599152127</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>9.408203968336581</v>
+        <v>8.672128890163933</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9603,10 +9593,10 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C82" t="n">
-        <v>4.831395011014249</v>
+        <v>4.78580089566666</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9634,7 +9624,7 @@
         <v>16.34835816551005</v>
       </c>
       <c r="K82" t="n">
-        <v>3.307759249029973</v>
+        <v>2.332838779732138</v>
       </c>
       <c r="L82" t="n">
         <v>9</v>
@@ -9649,7 +9639,7 @@
         <v>4</v>
       </c>
       <c r="P82" t="n">
-        <v>0.67007624209654</v>
+        <v>1.629155645585456</v>
       </c>
       <c r="Q82" t="n">
         <v>8</v>
@@ -9712,10 +9702,10 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C83" t="n">
-        <v>5.64828753533277</v>
+        <v>5.532361228225326</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9743,22 +9733,22 @@
         <v>13.10783674393532</v>
       </c>
       <c r="K83" t="n">
-        <v>6.735829933366699</v>
+        <v>4.545167626814273</v>
       </c>
       <c r="L83" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="M83" t="n">
-        <v>51.06382978723404</v>
+        <v>48.27586206896552</v>
       </c>
       <c r="N83" t="n">
-        <v>12.86430364214105</v>
+        <v>12.32886771240047</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>3.05817649862381</v>
+        <v>5.217680067870156</v>
       </c>
       <c r="Q83" t="n">
         <v>41</v>
@@ -9789,29 +9779,29 @@
       <c r="AA83" t="inlineStr"/>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD83" t="inlineStr"/>
       <c r="AE83" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="AF83" t="n">
-        <v>60.52631578947368</v>
+        <v>58.53658536585366</v>
       </c>
       <c r="AG83" t="n">
-        <v>31.04350647987885</v>
+        <v>28.57396001216165</v>
       </c>
       <c r="AH83" t="n">
-        <v>29.48280930959483</v>
+        <v>29.96262535369202</v>
       </c>
       <c r="AI83" t="n">
-        <v>44.71786799604255</v>
+        <v>43.36710313403013</v>
       </c>
       <c r="AJ83" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AK83" t="n">
-        <v>57.57575757575758</v>
+        <v>56.71641791044776</v>
       </c>
     </row>
     <row r="84">
@@ -9821,10 +9811,10 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C84" t="n">
-        <v>2.133797450589185</v>
+        <v>2.118339057647615</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9852,16 +9842,16 @@
         <v>14.96371051984784</v>
       </c>
       <c r="K84" t="n">
-        <v>10.04714696073417</v>
+        <v>9.249905385931466</v>
       </c>
       <c r="L84" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M84" t="n">
-        <v>53.57142857142857</v>
+        <v>48.14814814814815</v>
       </c>
       <c r="N84" t="n">
-        <v>9.977412972829143</v>
+        <v>10.7315592997849</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9891,25 +9881,25 @@
         <v>56.89655172413793</v>
       </c>
       <c r="X84" t="n">
-        <v>11.8512034636421</v>
+        <v>11.86663135768809</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.612907547744324</v>
+        <v>2.339147912114892</v>
       </c>
       <c r="Z84" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="AA84" t="n">
-        <v>39.34426229508197</v>
+        <v>39.6551724137931</v>
       </c>
       <c r="AB84" t="n">
-        <v>11.85690040892197</v>
+        <v>11.91637634624385</v>
       </c>
       <c r="AC84" t="n">
         <v>5</v>
       </c>
       <c r="AD84" t="n">
-        <v>3.44261870925735</v>
+        <v>2.72458414093153</v>
       </c>
       <c r="AE84" t="n">
         <v>39</v>
@@ -9918,10 +9908,10 @@
         <v>41.02564102564103</v>
       </c>
       <c r="AG84" t="n">
-        <v>26.25641367291723</v>
+        <v>26.22167829335427</v>
       </c>
       <c r="AH84" t="n">
-        <v>14.7692273527238</v>
+        <v>14.80396273228676</v>
       </c>
       <c r="AI84" t="n">
         <v>27.07931000072518</v>
@@ -9940,10 +9930,10 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C85" t="n">
-        <v>6.178136001761982</v>
+        <v>6.10822038952759</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9971,22 +9961,22 @@
         <v>12.5637553307017</v>
       </c>
       <c r="K85" t="n">
-        <v>3.198684339354241</v>
+        <v>2.030824131143882</v>
       </c>
       <c r="L85" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M85" t="n">
-        <v>55</v>
+        <v>55.38461538461539</v>
       </c>
       <c r="N85" t="n">
-        <v>12.85941490182948</v>
+        <v>13.28660371288908</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>4.652496968718434</v>
+        <v>5.850365239806088</v>
       </c>
       <c r="Q85" t="n">
         <v>32</v>
@@ -10021,19 +10011,19 @@
       </c>
       <c r="AD85" t="inlineStr"/>
       <c r="AE85" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AF85" t="n">
-        <v>44.11764705882353</v>
+        <v>42.42424242424242</v>
       </c>
       <c r="AG85" t="n">
-        <v>28.55236884973044</v>
+        <v>26.9933497239647</v>
       </c>
       <c r="AH85" t="n">
-        <v>15.56527820909309</v>
+        <v>15.43089270027772</v>
       </c>
       <c r="AI85" t="n">
-        <v>28.88348224624216</v>
+        <v>27.23559663341021</v>
       </c>
       <c r="AJ85" t="n">
         <v>54</v>
@@ -10049,10 +10039,10 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C86" t="n">
-        <v>4.471303820237114</v>
+        <v>4.481418258848693</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10080,22 +10070,22 @@
         <v>18.73514495170452</v>
       </c>
       <c r="K86" t="n">
-        <v>7.253496004965299</v>
+        <v>7.496111793297477</v>
       </c>
       <c r="L86" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M86" t="n">
-        <v>52</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="N86" t="n">
-        <v>16.76297731540263</v>
+        <v>16.75519292329755</v>
       </c>
       <c r="O86" t="n">
         <v>8</v>
       </c>
       <c r="P86" t="n">
-        <v>0.6960183330528835</v>
+        <v>0.4687501699330854</v>
       </c>
       <c r="Q86" t="n">
         <v>52</v>
@@ -10119,16 +10109,20 @@
         <v>70.12987012987013</v>
       </c>
       <c r="X86" t="n">
-        <v>57.8326129204237</v>
+        <v>48.61770380947655</v>
       </c>
       <c r="Y86" t="n">
-        <v>12.84060193733557</v>
+        <v>12.64344056862314</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA86" t="inlineStr"/>
-      <c r="AB86" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>14.34516657732499</v>
+      </c>
       <c r="AC86" t="n">
         <v>6</v>
       </c>
@@ -10164,10 +10158,10 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C87" t="n">
-        <v>6.167847682025493</v>
+        <v>5.984821997819962</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10224,25 +10218,25 @@
         <v>63.07692307692308</v>
       </c>
       <c r="X87" t="n">
-        <v>15.87369484319654</v>
+        <v>15.88967756874082</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>2.980797842541894</v>
       </c>
       <c r="Z87" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AA87" t="n">
-        <v>42.5531914893617</v>
+        <v>52.27272727272727</v>
       </c>
       <c r="AB87" t="n">
-        <v>13.07032055767968</v>
+        <v>12.61337018943614</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
       </c>
       <c r="AD87" t="n">
-        <v>4.000000000000004</v>
+        <v>1.050515913132322</v>
       </c>
       <c r="AE87" t="n">
         <v>43</v>
@@ -10273,10 +10267,10 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C88" t="n">
-        <v>1.103936739207589</v>
+        <v>1.073566007856364</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10293,11 +10287,7 @@
           <t>SATMA_BEKLE</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %84.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>5</v>
       </c>
@@ -10308,16 +10298,16 @@
         <v>16.8583060727446</v>
       </c>
       <c r="K88" t="n">
-        <v>11.04200331842031</v>
+        <v>7.987093800773315</v>
       </c>
       <c r="L88" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M88" t="n">
-        <v>84</v>
+        <v>70.96774193548387</v>
       </c>
       <c r="N88" t="n">
-        <v>13.7182441559816</v>
+        <v>13.58201913365737</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
@@ -10347,19 +10337,19 @@
         <v>61.53846153846154</v>
       </c>
       <c r="X88" t="n">
-        <v>29.76847434368583</v>
+        <v>25.70907945955605</v>
       </c>
       <c r="Y88" t="n">
-        <v>7.677797470306191</v>
+        <v>10.21770099122287</v>
       </c>
       <c r="Z88" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AA88" t="n">
-        <v>41.66666666666666</v>
+        <v>40.90909090909091</v>
       </c>
       <c r="AB88" t="n">
-        <v>13.64795941187776</v>
+        <v>13.51336303619622</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
@@ -10374,10 +10364,10 @@
         <v>51.51515151515152</v>
       </c>
       <c r="AG88" t="n">
-        <v>53.26196085893953</v>
+        <v>52.72953912272798</v>
       </c>
       <c r="AH88" t="n">
-        <v>-1.746809343788016</v>
+        <v>-1.214387607576462</v>
       </c>
       <c r="AI88" t="n">
         <v>35.21837544891414</v>
@@ -10396,10 +10386,10 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C89" t="n">
-        <v>2.22845011768239</v>
+        <v>2.180038253501429</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10456,25 +10446,25 @@
         <v>76.08695652173913</v>
       </c>
       <c r="X89" t="n">
-        <v>23.25882416441496</v>
+        <v>21.45830694080864</v>
       </c>
       <c r="Y89" t="n">
-        <v>4.829488516782209</v>
+        <v>6.897016005685474</v>
       </c>
       <c r="Z89" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA89" t="n">
-        <v>42.85714285714285</v>
+        <v>36.8421052631579</v>
       </c>
       <c r="AB89" t="n">
-        <v>14.3750902618885</v>
+        <v>14.81466677324567</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>5.432892397693534</v>
+        <v>3.33285128058195</v>
       </c>
       <c r="AE89" t="n">
         <v>22</v>
@@ -10505,10 +10495,10 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C90" t="n">
-        <v>2.880729526217078</v>
+        <v>2.803200131624952</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10536,22 +10526,22 @@
         <v>12.8208334231333</v>
       </c>
       <c r="K90" t="n">
-        <v>5.769650639365809</v>
+        <v>2.923060251180654</v>
       </c>
       <c r="L90" t="n">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="M90" t="n">
-        <v>62.06896551724138</v>
+        <v>65.88235294117646</v>
       </c>
       <c r="N90" t="n">
-        <v>12.79952939806312</v>
+        <v>15.18234473664055</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>2.108685570153623</v>
+        <v>4.932752423440601</v>
       </c>
       <c r="Q90" t="n">
         <v>43</v>
@@ -10575,19 +10565,19 @@
         <v>70.78651685393258</v>
       </c>
       <c r="X90" t="n">
-        <v>22.2243383493276</v>
+        <v>20.63086277737274</v>
       </c>
       <c r="Y90" t="n">
-        <v>7.790900081337348</v>
+        <v>10.27253385761435</v>
       </c>
       <c r="Z90" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AA90" t="n">
-        <v>41.66666666666666</v>
+        <v>45</v>
       </c>
       <c r="AB90" t="n">
-        <v>14.71209317900743</v>
+        <v>10.97878543820853</v>
       </c>
       <c r="AC90" t="n">
         <v>2</v>
@@ -10624,10 +10614,10 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2337506174169854</v>
+        <v>0.2365135841062872</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10723,10 +10713,10 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C92" t="n">
-        <v>1.252088480448522</v>
+        <v>1.204162639080271</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10783,25 +10773,25 @@
         <v>67.14285714285714</v>
       </c>
       <c r="X92" t="n">
-        <v>21.58730378654392</v>
+        <v>21.60407460332612</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>3.840935535973944</v>
       </c>
       <c r="Z92" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AA92" t="n">
-        <v>43.75</v>
+        <v>40</v>
       </c>
       <c r="AB92" t="n">
-        <v>12.72526224543457</v>
+        <v>16.45981091086437</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
       </c>
       <c r="AD92" t="n">
-        <v>4.000000000000004</v>
+        <v>0.1654180652782555</v>
       </c>
       <c r="AE92" t="n">
         <v>52</v>
@@ -10832,10 +10822,10 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04197634370181183</v>
+        <v>0.04174978919441416</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10895,16 +10885,16 @@
         <v>11.4419372600254</v>
       </c>
       <c r="Y93" t="n">
-        <v>4.492786129240889</v>
+        <v>5.00825717515001</v>
       </c>
       <c r="Z93" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA93" t="n">
-        <v>45</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="AB93" t="n">
-        <v>15.44736513139534</v>
+        <v>14.42170474454301</v>
       </c>
       <c r="AC93" t="n">
         <v>2</v>
@@ -10919,10 +10909,10 @@
         <v>60</v>
       </c>
       <c r="AG93" t="n">
-        <v>27.27054553767293</v>
+        <v>26.87723585530293</v>
       </c>
       <c r="AH93" t="n">
-        <v>32.72945446232707</v>
+        <v>33.12276414469707</v>
       </c>
       <c r="AI93" t="n">
         <v>40.739457358967</v>
@@ -10941,10 +10931,10 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C94" t="n">
-        <v>8.508440422076868</v>
+        <v>8.586471422989121</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10986,10 +10976,10 @@
         <v>61.90476190476191</v>
       </c>
       <c r="S94" t="n">
-        <v>40.41165727488056</v>
+        <v>40.21324457646786</v>
       </c>
       <c r="T94" t="n">
-        <v>21.49310462988134</v>
+        <v>21.69151732829405</v>
       </c>
       <c r="U94" t="n">
         <v>46.81404026715268</v>
@@ -11004,22 +10994,22 @@
         <v>46.54975901226545</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.47013931921729</v>
+        <v>1.575691891694908</v>
       </c>
       <c r="Z94" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA94" t="n">
-        <v>42.85714285714285</v>
+        <v>30</v>
       </c>
       <c r="AB94" t="n">
-        <v>11.014852533138</v>
+        <v>11.5296957311535</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>3.619261481707658</v>
+        <v>4.495137627420897</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -11050,10 +11040,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1244886727210852</v>
+        <v>0.1223700678691154</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11081,22 +11071,22 @@
         <v>18.89669242033002</v>
       </c>
       <c r="K95" t="n">
-        <v>2.708249121316375</v>
+        <v>0.9603134242809785</v>
       </c>
       <c r="L95" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="M95" t="n">
-        <v>68.18181818181819</v>
+        <v>62.96296296296296</v>
       </c>
       <c r="N95" t="n">
-        <v>17.74639578448414</v>
+        <v>14.90353298748101</v>
       </c>
       <c r="O95" t="n">
         <v>10</v>
       </c>
       <c r="P95" t="n">
-        <v>7.099479293109945</v>
+        <v>8.953702964183741</v>
       </c>
       <c r="Q95" t="n">
         <v>21</v>
@@ -11159,10 +11149,10 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1271636284449823</v>
+        <v>0.1277173354173951</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11258,10 +11248,10 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C97" t="n">
-        <v>1.939348270328282</v>
+        <v>1.923986590708101</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11289,16 +11279,16 @@
         <v>12.87370897365936</v>
       </c>
       <c r="K97" t="n">
-        <v>6.007276062249511</v>
+        <v>5.167586854699002</v>
       </c>
       <c r="L97" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M97" t="n">
-        <v>55.55555555555556</v>
+        <v>52.5</v>
       </c>
       <c r="N97" t="n">
-        <v>14.7502935508201</v>
+        <v>16.50075824133667</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11331,16 +11321,16 @@
         <v>16.31583297271808</v>
       </c>
       <c r="Y97" t="n">
-        <v>7.639792148908153</v>
+        <v>8.371382211595391</v>
       </c>
       <c r="Z97" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA97" t="n">
-        <v>47.82608695652174</v>
+        <v>50</v>
       </c>
       <c r="AB97" t="n">
-        <v>11.61744814557274</v>
+        <v>10.29457166100521</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
@@ -11377,10 +11367,10 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7835584687862953</v>
+        <v>0.7593114369742715</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11437,25 +11427,25 @@
         <v>72.46376811594203</v>
       </c>
       <c r="X98" t="n">
-        <v>30.83973655286976</v>
+        <v>30.85778357900837</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>3.107840947786611</v>
       </c>
       <c r="Z98" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA98" t="n">
-        <v>33.33333333333334</v>
+        <v>30</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.06367621873108</v>
+        <v>11.24407736888147</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>7.999999999999996</v>
+        <v>5.049076313365141</v>
       </c>
       <c r="AE98" t="n">
         <v>51</v>
@@ -11464,10 +11454,10 @@
         <v>56.86274509803921</v>
       </c>
       <c r="AG98" t="n">
-        <v>37.60313004302709</v>
+        <v>37.51172668937328</v>
       </c>
       <c r="AH98" t="n">
-        <v>19.25961505501213</v>
+        <v>19.35101840866594</v>
       </c>
       <c r="AI98" t="n">
         <v>43.26530210930225</v>
@@ -11486,10 +11476,10 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5321119093229902</v>
+        <v>0.5162166053102442</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11498,7 +11488,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -11513,17 +11503,27 @@
       <c r="I99" t="n">
         <v>10</v>
       </c>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
+      <c r="J99" t="n">
+        <v>12.54207936754466</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.7223113964686778</v>
+      </c>
       <c r="L99" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="M99" t="n">
+        <v>55.12820512820513</v>
+      </c>
+      <c r="N99" t="n">
+        <v>15.91650966270182</v>
+      </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
-      <c r="P99" t="inlineStr"/>
+      <c r="P99" t="n">
+        <v>3.254183266932298</v>
+      </c>
       <c r="Q99" t="n">
         <v>34</v>
       </c>
@@ -11549,43 +11549,41 @@
         <v>33.04241514445872</v>
       </c>
       <c r="Y99" t="n">
-        <v>9.197911103637091</v>
+        <v>11.91036083970189</v>
       </c>
       <c r="Z99" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF99" t="n">
         <v>50</v>
       </c>
-      <c r="AB99" t="n">
-        <v>7.626400770282054</v>
-      </c>
-      <c r="AC99" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE99" t="n">
-        <v>41</v>
-      </c>
-      <c r="AF99" t="n">
-        <v>43.90243902439025</v>
-      </c>
       <c r="AG99" t="n">
-        <v>29.29946437862367</v>
+        <v>36.08873902035259</v>
       </c>
       <c r="AH99" t="n">
-        <v>14.60297464576658</v>
+        <v>13.91126097964741</v>
       </c>
       <c r="AI99" t="n">
-        <v>29.89013173655036</v>
+        <v>34.8499283643951</v>
       </c>
       <c r="AJ99" t="n">
         <v>78</v>
       </c>
       <c r="AK99" t="n">
-        <v>47.43589743589744</v>
+        <v>48.71794871794872</v>
       </c>
     </row>
     <row r="100">
@@ -11595,10 +11593,10 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C100" t="n">
-        <v>350.3732699546829</v>
+        <v>348.2493817226415</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11640,10 +11638,10 @@
         <v>60.41666666666666</v>
       </c>
       <c r="S100" t="n">
-        <v>36.72377229300231</v>
+        <v>36.64353580651581</v>
       </c>
       <c r="T100" t="n">
-        <v>23.69289437366436</v>
+        <v>23.77313086015085</v>
       </c>
       <c r="U100" t="n">
         <v>46.31040849254725</v>
@@ -11658,22 +11656,22 @@
         <v>16.86980163304483</v>
       </c>
       <c r="Y100" t="n">
-        <v>3.828820917645737</v>
+        <v>4.411790147978212</v>
       </c>
       <c r="Z100" t="n">
         <v>36</v>
       </c>
       <c r="AA100" t="n">
-        <v>41.66666666666666</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB100" t="n">
-        <v>13.74490575731567</v>
+        <v>13.01847294205303</v>
       </c>
       <c r="AC100" t="n">
         <v>8</v>
       </c>
       <c r="AD100" t="n">
-        <v>4.33724440331792</v>
+        <v>3.753820536629593</v>
       </c>
       <c r="AE100" t="n">
         <v>39</v>
@@ -11704,10 +11702,10 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C101" t="n">
-        <v>354.8935396839071</v>
+        <v>350.2994467638772</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11764,25 +11762,25 @@
         <v>52.63157894736842</v>
       </c>
       <c r="X101" t="n">
-        <v>13.42727168813178</v>
+        <v>13.07599096065748</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.808954965927123</v>
+        <v>3.080036950691201</v>
       </c>
       <c r="Z101" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AA101" t="n">
-        <v>39.53488372093023</v>
+        <v>40</v>
       </c>
       <c r="AB101" t="n">
-        <v>13.86107259678498</v>
+        <v>11.90979741970219</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>4.268255860418401</v>
+        <v>3.012757080626671</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11813,10 +11811,10 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C102" t="n">
-        <v>412.8799565137252</v>
+        <v>408.2814540571335</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11873,40 +11871,40 @@
         <v>47.22222222222222</v>
       </c>
       <c r="X102" t="n">
-        <v>11.05216375209621</v>
+        <v>10.81355469301844</v>
       </c>
       <c r="Y102" t="n">
-        <v>3.142996393741748</v>
+        <v>4.221753456163324</v>
       </c>
       <c r="Z102" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AA102" t="n">
-        <v>28</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="AB102" t="n">
-        <v>12.88503880112606</v>
+        <v>12.21514703280352</v>
       </c>
       <c r="AC102" t="n">
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>1.917263116880341</v>
+        <v>0.8125504192441957</v>
       </c>
       <c r="AE102" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF102" t="n">
-        <v>54.16666666666666</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="AG102" t="n">
-        <v>24.28286990786991</v>
+        <v>30.10812270427655</v>
       </c>
       <c r="AH102" t="n">
-        <v>29.88379675879676</v>
+        <v>23.7380311418773</v>
       </c>
       <c r="AI102" t="n">
-        <v>35.07486535891948</v>
+        <v>35.45793874685879</v>
       </c>
       <c r="AJ102" t="n">
         <v>35</v>
@@ -11922,10 +11920,10 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C103" t="n">
-        <v>0.75516268429658</v>
+        <v>0.7494395656376612</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11985,37 +11983,37 @@
         <v>14.28440963201156</v>
       </c>
       <c r="Y103" t="n">
-        <v>4.441336312187982</v>
+        <v>5.165542609116547</v>
       </c>
       <c r="Z103" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="AA103" t="n">
-        <v>43.90243902439025</v>
+        <v>45.71428571428572</v>
       </c>
       <c r="AB103" t="n">
-        <v>10.96541638459621</v>
+        <v>11.21113198199012</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>3.724061796676115</v>
+        <v>2.988847586484877</v>
       </c>
       <c r="AE103" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AF103" t="n">
-        <v>61.76470588235294</v>
+        <v>60.60606060606061</v>
       </c>
       <c r="AG103" t="n">
-        <v>36.77601734695161</v>
+        <v>34.83100155560049</v>
       </c>
       <c r="AH103" t="n">
-        <v>24.98868853540133</v>
+        <v>25.77505905046012</v>
       </c>
       <c r="AI103" t="n">
-        <v>45.0410173444307</v>
+        <v>43.68344081994023</v>
       </c>
       <c r="AJ103" t="n">
         <v>60</v>
@@ -12031,10 +12029,10 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C104" t="n">
-        <v>0.05082430011555762</v>
+        <v>0.04997634864158938</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12094,37 +12092,37 @@
         <v>12.98853157526716</v>
       </c>
       <c r="Y104" t="n">
-        <v>3.359483155667586</v>
+        <v>4.971831353613965</v>
       </c>
       <c r="Z104" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="AA104" t="n">
-        <v>52.45901639344262</v>
+        <v>52</v>
       </c>
       <c r="AB104" t="n">
-        <v>13.60500706252713</v>
+        <v>12.55123502002542</v>
       </c>
       <c r="AC104" t="n">
         <v>5</v>
       </c>
       <c r="AD104" t="n">
-        <v>1.697545602922368</v>
+        <v>0.02964241738768747</v>
       </c>
       <c r="AE104" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AF104" t="n">
-        <v>55.81395348837209</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AG104" t="n">
-        <v>31.64353678209794</v>
+        <v>30.33484174711939</v>
       </c>
       <c r="AH104" t="n">
-        <v>24.17041670627415</v>
+        <v>26.80801539573775</v>
       </c>
       <c r="AI104" t="n">
-        <v>41.1076144528241</v>
+        <v>42.20623987810458</v>
       </c>
       <c r="AJ104" t="n">
         <v>77</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -670,7 +670,7 @@
         <v>46279</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4053637167595583</v>
+        <v>0.4047550491547036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>21.42119502374098</v>
       </c>
       <c r="K2" t="n">
-        <v>10.3254232351534</v>
+        <v>10.15976580618585</v>
       </c>
       <c r="L2" t="n">
         <v>10</v>
@@ -740,22 +740,22 @@
         <v>11.79582706077868</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.315258238418759</v>
+        <v>1.463436782576311</v>
       </c>
       <c r="Z2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA2" t="n">
-        <v>44.23076923076923</v>
+        <v>39.62264150943396</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.484952980269453</v>
+        <v>9.487446274259018</v>
       </c>
       <c r="AC2" t="n">
         <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>8.80049094374008</v>
+        <v>8.663345806558652</v>
       </c>
       <c r="AE2" t="n">
         <v>46</v>
@@ -789,7 +789,7 @@
         <v>46279</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7190012767620263</v>
+        <v>0.719016064333018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>16.83732632822199</v>
       </c>
       <c r="K3" t="n">
-        <v>14.36634883433114</v>
+        <v>14.36870098662504</v>
       </c>
       <c r="L3" t="n">
         <v>8</v>
@@ -859,7 +859,7 @@
         <v>17.17248092970491</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.394872988186736</v>
+        <v>2.392865560951918</v>
       </c>
       <c r="Z3" t="n">
         <v>45</v>
@@ -874,7 +874,7 @@
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>7.79172902555908</v>
+        <v>7.793625417615802</v>
       </c>
       <c r="AE3" t="n">
         <v>35</v>
@@ -908,7 +908,7 @@
         <v>46279</v>
       </c>
       <c r="C4" t="n">
-        <v>1.500318779178578</v>
+        <v>1.491094566245732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -968,22 +968,22 @@
         <v>16.66966699739723</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.704984579490901</v>
+        <v>5.290874408956903</v>
       </c>
       <c r="Z4" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="AA4" t="n">
-        <v>48.71794871794872</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.80131041509941</v>
+        <v>13.75331618842234</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>5.556445315784608</v>
+        <v>4.972198361726243</v>
       </c>
       <c r="AE4" t="n">
         <v>40</v>
@@ -1017,7 +1017,7 @@
         <v>46279</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2305493285070851</v>
+        <v>0.2280860515815886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,16 +1045,16 @@
         <v>19.13427219952423</v>
       </c>
       <c r="K5" t="n">
-        <v>5.912074544476398</v>
+        <v>4.78046955978062</v>
       </c>
       <c r="L5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M5" t="n">
-        <v>51.85185185185185</v>
+        <v>50</v>
       </c>
       <c r="N5" t="n">
-        <v>10.96675712460524</v>
+        <v>11.68319257573849</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -1087,22 +1087,22 @@
         <v>10.55954734904581</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.203592467592998</v>
+        <v>5.227117809211135</v>
       </c>
       <c r="Z5" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="AA5" t="n">
-        <v>43.47826086956522</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.169312298228352</v>
+        <v>9.491367762561834</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>6.050756684634684</v>
+        <v>5.036126453536038</v>
       </c>
       <c r="AE5" t="n">
         <v>45</v>
@@ -1136,7 +1136,7 @@
         <v>46279</v>
       </c>
       <c r="C6" t="n">
-        <v>1.618575571231722</v>
+        <v>1.613467154785899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>24.35210179737853</v>
       </c>
       <c r="K6" t="n">
-        <v>1.791008920417481</v>
+        <v>1.469744425111785</v>
       </c>
       <c r="L6" t="n">
         <v>23</v>
@@ -1177,13 +1177,13 @@
         <v>82.60869565217391</v>
       </c>
       <c r="N6" t="n">
-        <v>12.20680140660389</v>
+        <v>12.42767093254801</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2053138895065976</v>
+        <v>0.5225750571191901</v>
       </c>
       <c r="Q6" t="n">
         <v>34</v>
@@ -1249,11 +1249,11 @@
         <v>46279</v>
       </c>
       <c r="C7" t="n">
-        <v>2.369249120786459</v>
+        <v>2.321994159022665</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1309,22 +1309,22 @@
         <v>18.9234494530097</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.235899400189636</v>
+        <v>6.145926029506709</v>
       </c>
       <c r="Z7" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AA7" t="n">
-        <v>35.29411764705883</v>
+        <v>40.74074074074074</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.6098330229977</v>
+        <v>12.98106105691283</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.7978987898643486</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>45</v>
@@ -1358,7 +1358,7 @@
         <v>46279</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3488061205602287</v>
+        <v>0.3424375796964337</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,11 +1375,7 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>5</v>
       </c>
@@ -1390,22 +1386,22 @@
         <v>20.70550141590351</v>
       </c>
       <c r="K8" t="n">
-        <v>7.118867698388609</v>
+        <v>5.163079522639413</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M8" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N8" t="n">
-        <v>12.69508729544503</v>
+        <v>17.38979657077811</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>0.822574323780545</v>
+        <v>2.697639219237447</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1432,10 +1428,10 @@
         <v>28.52170855483174</v>
       </c>
       <c r="Y8" t="n">
-        <v>15.06063096960105</v>
+        <v>16.61146339692843</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
@@ -1477,7 +1473,7 @@
         <v>46279</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5470662032371512</v>
+        <v>0.5466661182180905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,7 +1501,7 @@
         <v>14.50739888386581</v>
       </c>
       <c r="K9" t="n">
-        <v>2.891128176613345</v>
+        <v>2.815880978497054</v>
       </c>
       <c r="L9" t="n">
         <v>41</v>
@@ -1586,7 +1582,7 @@
         <v>46279</v>
       </c>
       <c r="C10" t="n">
-        <v>1.94763794911873</v>
+        <v>1.940479618279791</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,22 +1610,22 @@
         <v>13.50421550203786</v>
       </c>
       <c r="K10" t="n">
-        <v>6.220619429786911</v>
+        <v>5.830217129328807</v>
       </c>
       <c r="L10" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M10" t="n">
-        <v>58.06451612903226</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N10" t="n">
-        <v>9.099753605249541</v>
+        <v>9.125705552342156</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>3.558047948224696</v>
+        <v>3.940068331878743</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1695,7 +1691,7 @@
         <v>46279</v>
       </c>
       <c r="C11" t="n">
-        <v>7.748390679308147</v>
+        <v>7.655999341861708</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,25 +1716,25 @@
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>10.16694412204168</v>
+        <v>11.18322544746914</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4666666666666819</v>
+        <v>0.4045853000674171</v>
       </c>
       <c r="L11" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="M11" t="n">
-        <v>51.02040816326531</v>
+        <v>50.87719298245614</v>
       </c>
       <c r="N11" t="n">
-        <v>13.43296590678878</v>
+        <v>13.65224315283608</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.521566025215649</v>
+        <v>2.584956346541323</v>
       </c>
       <c r="Q11" t="n">
         <v>49</v>
@@ -1765,16 +1761,16 @@
         <v>21.29068828859215</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.747723194611202</v>
+        <v>10.82388583363557</v>
       </c>
       <c r="Z11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA11" t="n">
-        <v>52.94117647058823</v>
+        <v>50</v>
       </c>
       <c r="AB11" t="n">
-        <v>14.28978979873238</v>
+        <v>12.72981121511715</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
@@ -1814,7 +1810,7 @@
         <v>46279</v>
       </c>
       <c r="C12" t="n">
-        <v>5.887131604384757</v>
+        <v>5.861544156965983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,7 +1827,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>5</v>
       </c>
@@ -1839,25 +1839,25 @@
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>21.83099560311669</v>
+        <v>21.82938791514835</v>
       </c>
       <c r="K12" t="n">
-        <v>1.327433628318597</v>
+        <v>0.8849557522123908</v>
       </c>
       <c r="L12" t="n">
         <v>17</v>
       </c>
       <c r="M12" t="n">
-        <v>64.70588235294117</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="N12" t="n">
-        <v>16.71174840656363</v>
+        <v>15.24631637135638</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>3.624454148471612</v>
+        <v>4.078947368421049</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1923,24 +1923,28 @@
         <v>46279</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1727577483906793</v>
+        <v>0.1707046193081321</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>AL_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VERİ_YETERSİZ</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>5</v>
       </c>
@@ -1951,7 +1955,7 @@
         <v>47.07727092024744</v>
       </c>
       <c r="K13" t="n">
-        <v>6.975413335828451</v>
+        <v>5.704070462450606</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
@@ -1962,7 +1966,7 @@
         <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.2799603991168187</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1987,13 +1991,13 @@
         <v>20.61663781635479</v>
       </c>
       <c r="Y13" t="n">
-        <v>11.30957115658938</v>
+        <v>12.36360723021427</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA13" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AB13" t="n">
         <v>11.69944783412234</v>
@@ -2026,7 +2030,7 @@
         <v>46279</v>
       </c>
       <c r="C14" t="n">
-        <v>8.828126606749892</v>
+        <v>8.843733289457447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,22 +2090,22 @@
         <v>16.11612055393703</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.94806963420604</v>
+        <v>1.774729872074376</v>
       </c>
       <c r="Z14" t="n">
         <v>38</v>
       </c>
       <c r="AA14" t="n">
-        <v>47.36842105263158</v>
+        <v>50</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.74181387011352</v>
+        <v>11.34793740359749</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.05296210446875671</v>
+        <v>0.2293402987156412</v>
       </c>
       <c r="AE14" t="n">
         <v>38</v>
@@ -2135,7 +2139,7 @@
         <v>46279</v>
       </c>
       <c r="C15" t="n">
-        <v>14.08798305328754</v>
+        <v>14.03685574431327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,25 +2164,25 @@
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>11.36450127270662</v>
+        <v>11.59417678351645</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5461297632740614</v>
+        <v>0.4415011037527616</v>
       </c>
       <c r="L15" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M15" t="n">
-        <v>56.41025641025641</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N15" t="n">
-        <v>19.70774925476212</v>
+        <v>19.87042946503383</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>7.41338354273342</v>
+        <v>7.525274725274733</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2205,7 +2209,7 @@
         <v>41.12870069280461</v>
       </c>
       <c r="Y15" t="n">
-        <v>10.88043643333048</v>
+        <v>11.20386409823397</v>
       </c>
       <c r="Z15" t="n">
         <v>5</v>
@@ -2254,7 +2258,7 @@
         <v>46279</v>
       </c>
       <c r="C16" t="n">
-        <v>34.90117845464081</v>
+        <v>34.86076261774505</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2282,22 +2286,22 @@
         <v>16.99349200873118</v>
       </c>
       <c r="K16" t="n">
-        <v>3.899064060707547</v>
+        <v>3.778748134064647</v>
       </c>
       <c r="L16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M16" t="n">
-        <v>66.07142857142857</v>
+        <v>67.24137931034483</v>
       </c>
       <c r="N16" t="n">
-        <v>17.28957398612863</v>
+        <v>16.59883356053895</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>5.871983539454906</v>
+        <v>5.994726259270888</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2363,7 +2367,7 @@
         <v>46279</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4031014129115851</v>
+        <v>0.3928262926247378</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2388,10 +2392,10 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>50.1132355061795</v>
+        <v>50.11220949399377</v>
       </c>
       <c r="K17" t="n">
-        <v>3.703705788751765</v>
+        <v>1.058203090059107</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2402,7 +2406,7 @@
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>4.142855048979599</v>
+        <v>6.869107798952889</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2468,11 +2472,11 @@
         <v>46279</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0787693067067026</v>
+        <v>0.07712558101271029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2496,22 +2500,22 @@
         <v>31.38464440531301</v>
       </c>
       <c r="K18" t="n">
-        <v>5.380935110927831</v>
+        <v>3.181888833375313</v>
       </c>
       <c r="L18" t="n">
         <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N18" t="n">
-        <v>13.03244577611671</v>
+        <v>16.11227766267315</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>4.383207346006168</v>
+        <v>6.607856517954436</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2538,22 +2542,22 @@
         <v>11.24971294890111</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.275319533335699</v>
+        <v>7.251995444906456</v>
       </c>
       <c r="Z18" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="AA18" t="n">
-        <v>42.85714285714285</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB18" t="n">
-        <v>15.38699885804945</v>
+        <v>13.23592115851729</v>
       </c>
       <c r="AC18" t="n">
         <v>8</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.876420858049944</v>
+        <v>0.8064912648866884</v>
       </c>
       <c r="AE18" t="n">
         <v>36</v>
@@ -2587,7 +2591,7 @@
         <v>46279</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02735331016185756</v>
+        <v>0.02735387273250792</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2615,7 +2619,7 @@
         <v>10.11859020594628</v>
       </c>
       <c r="K19" t="n">
-        <v>2.677052660321921</v>
+        <v>2.679164400946732</v>
       </c>
       <c r="L19" t="n">
         <v>28</v>
@@ -2630,7 +2634,7 @@
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>7.13201942395445</v>
+        <v>7.129816104138231</v>
       </c>
       <c r="Q19" t="n">
         <v>14</v>
@@ -2657,7 +2661,7 @@
         <v>20.26411217973316</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.712417533919725</v>
+        <v>7.710519471674937</v>
       </c>
       <c r="Z19" t="n">
         <v>13</v>
@@ -2672,7 +2676,7 @@
         <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.478754351292123</v>
+        <v>2.480760012103855</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -2706,7 +2710,7 @@
         <v>46279</v>
       </c>
       <c r="C20" t="n">
-        <v>1.654566768813113</v>
+        <v>1.654600797992678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2734,7 +2738,7 @@
         <v>18.49305897009618</v>
       </c>
       <c r="K20" t="n">
-        <v>6.153880907284082</v>
+        <v>6.156064155215191</v>
       </c>
       <c r="L20" t="n">
         <v>26</v>
@@ -2749,7 +2753,7 @@
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>3.62315448087589</v>
+        <v>3.621023325774808</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
@@ -2815,7 +2819,7 @@
         <v>46279</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9238426259177757</v>
+        <v>0.9218049442639135</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2914,7 +2918,7 @@
         <v>46279</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3006807477942537</v>
+        <v>0.2934885442803669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2931,11 +2935,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>5</v>
       </c>
@@ -2943,25 +2943,25 @@
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>18.72614792016484</v>
+        <v>20.29393476258275</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8275862068965356</v>
+        <v>0.3516174402250272</v>
       </c>
       <c r="L22" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M22" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="N22" t="n">
-        <v>16.08506486629521</v>
+        <v>14.82049516308756</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>9.097127222982238</v>
+        <v>9.614576033637023</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -3019,7 +3019,7 @@
         <v>46279</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6087653990909653</v>
+        <v>0.6034305458434454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3044,10 +3044,10 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>40.10847332624524</v>
+        <v>40.79566405884426</v>
       </c>
       <c r="K23" t="n">
-        <v>0.06761325219744041</v>
+        <v>0.3419972640218871</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -3058,7 +3058,7 @@
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.929054054054038</v>
+        <v>4.642126789366063</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3124,16 +3124,16 @@
         <v>46279</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1682331406947329</v>
+        <v>0.1624778906667764</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3152,22 +3152,22 @@
         <v>23.31817459365587</v>
       </c>
       <c r="K24" t="n">
-        <v>11.23552349318049</v>
+        <v>7.430160013368003</v>
       </c>
       <c r="L24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M24" t="n">
         <v>50</v>
       </c>
       <c r="N24" t="n">
-        <v>11.74852739357807</v>
+        <v>13.50219384884019</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.392102912545435</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3194,16 +3194,16 @@
         <v>17.82705440547527</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.59424229482266</v>
+        <v>8.823860058767741</v>
       </c>
       <c r="Z24" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AA24" t="n">
-        <v>31.57894736842105</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="AB24" t="n">
-        <v>14.55376143260952</v>
+        <v>16.83939367695796</v>
       </c>
       <c r="AC24" t="n">
         <v>2</v>
@@ -3243,7 +3243,7 @@
         <v>46279</v>
       </c>
       <c r="C25" t="n">
-        <v>3.346153055138515</v>
+        <v>3.350335239192135</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,22 +3271,22 @@
         <v>20.95143919294578</v>
       </c>
       <c r="K25" t="n">
-        <v>1.85660300408006</v>
+        <v>1.983908316724237</v>
       </c>
       <c r="L25" t="n">
         <v>39</v>
       </c>
       <c r="M25" t="n">
-        <v>48.71794871794872</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N25" t="n">
-        <v>19.29093100429186</v>
+        <v>18.6072341317862</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>6.031417517108695</v>
+        <v>5.899059746359225</v>
       </c>
       <c r="Q25" t="n">
         <v>44</v>
@@ -3352,7 +3352,7 @@
         <v>46279</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4467021779816137</v>
+        <v>0.4471227016576858</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3412,22 +3412,22 @@
         <v>11.40992936035117</v>
       </c>
       <c r="Y26" t="n">
-        <v>6.215801270328813</v>
+        <v>6.127513193952105</v>
       </c>
       <c r="Z26" t="n">
         <v>34</v>
       </c>
       <c r="AA26" t="n">
-        <v>44.11764705882353</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="AB26" t="n">
-        <v>10.78541321235292</v>
+        <v>9.649827332319148</v>
       </c>
       <c r="AC26" t="n">
         <v>10</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.035006729202828</v>
+        <v>4.125262830257093</v>
       </c>
       <c r="AE26" t="n">
         <v>36</v>
@@ -3461,7 +3461,7 @@
         <v>46279</v>
       </c>
       <c r="C27" t="n">
-        <v>51.10750056557596</v>
+        <v>52.54822919665995</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,25 +3508,25 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>59.78102685472641</v>
+        <v>60.35073545432527</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.964625557853495</v>
+        <v>0.5836575875486361</v>
       </c>
       <c r="Z27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA27" t="n">
-        <v>20</v>
+        <v>14.28571428571429</v>
       </c>
       <c r="AB27" t="n">
-        <v>30.47755955003824</v>
+        <v>9.659661880762883</v>
       </c>
       <c r="AC27" t="n">
         <v>6</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.12811122706208</v>
+        <v>5.448140900195697</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3550,7 +3550,7 @@
         <v>46279</v>
       </c>
       <c r="C28" t="n">
-        <v>1.456101022150011</v>
+        <v>1.440705853317428</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3575,25 +3575,25 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>13.72882306486436</v>
+        <v>14.27194368631205</v>
       </c>
       <c r="K28" t="n">
-        <v>0.7198730356487548</v>
+        <v>0.286327845382961</v>
       </c>
       <c r="L28" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M28" t="n">
-        <v>58.62068965517241</v>
+        <v>58.92857142857143</v>
       </c>
       <c r="N28" t="n">
-        <v>12.64980473839546</v>
+        <v>13.71737698329092</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>1.270977539753404</v>
+        <v>1.708779443254826</v>
       </c>
       <c r="Q28" t="n">
         <v>39</v>
@@ -3620,16 +3620,16 @@
         <v>19.25959158767157</v>
       </c>
       <c r="Y28" t="n">
-        <v>13.10778012457149</v>
+        <v>14.02648038978038</v>
       </c>
       <c r="Z28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA28" t="n">
-        <v>37.5</v>
+        <v>20</v>
       </c>
       <c r="AB28" t="n">
-        <v>10.14666280301502</v>
+        <v>12.1022945001129</v>
       </c>
       <c r="AC28" t="n">
         <v>6</v>
@@ -3669,7 +3669,7 @@
         <v>46279</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4125619562758365</v>
+        <v>0.4179178149808729</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>27.65210909859499</v>
       </c>
       <c r="K29" t="n">
-        <v>24.5831360588096</v>
+        <v>26.20046810702974</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3732,25 +3732,25 @@
         <v>80</v>
       </c>
       <c r="X29" t="n">
-        <v>31.16629801654502</v>
+        <v>31.16899569039671</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.018943171595058</v>
+        <v>3.787882614497085</v>
       </c>
       <c r="Z29" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AA29" t="n">
-        <v>50</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AB29" t="n">
-        <v>16.48525139570154</v>
+        <v>13.76339599716079</v>
       </c>
       <c r="AC29" t="n">
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>5.244263429710871</v>
+        <v>6.456689192913389</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3784,7 +3784,7 @@
         <v>46279</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4298377311149045</v>
+        <v>0.4236765250298219</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3844,22 +3844,22 @@
         <v>26.71344279693404</v>
       </c>
       <c r="Y30" t="n">
-        <v>7.334210151745635</v>
+        <v>8.662462622302758</v>
       </c>
       <c r="Z30" t="n">
         <v>14</v>
       </c>
       <c r="AA30" t="n">
-        <v>42.85714285714285</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="AB30" t="n">
-        <v>13.20275114201591</v>
+        <v>15.54106172116325</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.876778855087458</v>
+        <v>1.46438957749242</v>
       </c>
       <c r="AE30" t="n">
         <v>46</v>
@@ -3893,7 +3893,7 @@
         <v>46279</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2529667030006376</v>
+        <v>0.2542059150178931</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3950,10 +3950,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="X31" t="n">
-        <v>46.69172443138287</v>
+        <v>46.69474141390997</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.9661842127781872</v>
+        <v>0.4830924284502824</v>
       </c>
       <c r="Z31" t="n">
         <v>3</v>
@@ -3968,7 +3968,7 @@
         <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>9.121950634146348</v>
+        <v>9.563106213592242</v>
       </c>
       <c r="AE31" t="n">
         <v>10</v>
@@ -4002,7 +4002,7 @@
         <v>46279</v>
       </c>
       <c r="C32" t="n">
-        <v>2.367192480924665</v>
+        <v>2.35078770926741</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4062,22 +4062,22 @@
         <v>13.38656892008534</v>
       </c>
       <c r="Y32" t="n">
-        <v>4.206348277949901</v>
+        <v>4.870203454653177</v>
       </c>
       <c r="Z32" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="AA32" t="n">
-        <v>31.81818181818182</v>
+        <v>28.2051282051282</v>
       </c>
       <c r="AB32" t="n">
-        <v>10.42723561662574</v>
+        <v>10.21846166513093</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.960232910900563</v>
+        <v>3.29002758232001</v>
       </c>
       <c r="AE32" t="n">
         <v>26</v>
@@ -4111,7 +4111,7 @@
         <v>46279</v>
       </c>
       <c r="C33" t="n">
-        <v>1.862287394854287</v>
+        <v>1.831475463781827</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4171,22 +4171,22 @@
         <v>15.09663082780621</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.263010877035187</v>
+        <v>2.896634834092071</v>
       </c>
       <c r="Z33" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA33" t="n">
-        <v>46.80851063829788</v>
+        <v>36.95652173913044</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.859407456327904</v>
+        <v>11.50750222125849</v>
       </c>
       <c r="AC33" t="n">
         <v>8</v>
       </c>
       <c r="AD33" t="n">
-        <v>6.823166457481012</v>
+        <v>5.255600727316157</v>
       </c>
       <c r="AE33" t="n">
         <v>29</v>
@@ -4220,7 +4220,7 @@
         <v>46279</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8000329062377887</v>
+        <v>0.7979926782115091</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4248,16 +4248,16 @@
         <v>15.41713612942789</v>
       </c>
       <c r="K34" t="n">
-        <v>6.427063172858127</v>
+        <v>6.15565499033599</v>
       </c>
       <c r="L34" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M34" t="n">
-        <v>63.33333333333334</v>
+        <v>59.375</v>
       </c>
       <c r="N34" t="n">
-        <v>12.85729889708578</v>
+        <v>13.41939859320348</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4290,16 +4290,16 @@
         <v>10.81830054752258</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.962556141872386</v>
+        <v>4.207468923589097</v>
       </c>
       <c r="Z34" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AA34" t="n">
-        <v>35.29411764705883</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB34" t="n">
-        <v>9.854642237875723</v>
+        <v>9.769890717174794</v>
       </c>
       <c r="AC34" t="n">
         <v>2</v>
@@ -4339,16 +4339,16 @@
         <v>46279</v>
       </c>
       <c r="C35" t="n">
-        <v>1.467412541389877</v>
+        <v>1.488009543005224</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4367,7 +4367,7 @@
         <v>38.83766461406507</v>
       </c>
       <c r="K35" t="n">
-        <v>5.905226724153634</v>
+        <v>7.391741296153254</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
@@ -4378,7 +4378,7 @@
         <v>6</v>
       </c>
       <c r="P35" t="n">
-        <v>0.08948876158230146</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>7</v>
@@ -4405,16 +4405,16 @@
         <v>13.94161507705984</v>
       </c>
       <c r="Y35" t="n">
-        <v>7.053075689221289</v>
+        <v>5.748447374979582</v>
       </c>
       <c r="Z35" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA35" t="n">
-        <v>60</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="AB35" t="n">
-        <v>12.113484413092</v>
+        <v>13.30735100238293</v>
       </c>
       <c r="AC35" t="n">
         <v>2</v>
@@ -4454,7 +4454,7 @@
         <v>46279</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07959196265142011</v>
+        <v>0.07877092674098145</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4482,16 +4482,16 @@
         <v>11.49958181785439</v>
       </c>
       <c r="K36" t="n">
-        <v>3.064996546751586</v>
+        <v>2.001823074767728</v>
       </c>
       <c r="L36" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M36" t="n">
-        <v>62.06896551724138</v>
+        <v>63.33333333333334</v>
       </c>
       <c r="N36" t="n">
-        <v>19.64013762079417</v>
+        <v>18.68547865450064</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4563,7 +4563,7 @@
         <v>46279</v>
       </c>
       <c r="C37" t="n">
-        <v>0.05964255599202024</v>
+        <v>0.05984945086586319</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4588,10 +4588,10 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>19.28857966930738</v>
+        <v>19.28691969192409</v>
       </c>
       <c r="K37" t="n">
-        <v>1.045300040063757</v>
+        <v>1.393732109167445</v>
       </c>
       <c r="L37" t="n">
         <v>60</v>
@@ -4600,13 +4600,13 @@
         <v>63.33333333333334</v>
       </c>
       <c r="N37" t="n">
-        <v>17.5010023167375</v>
+        <v>17.34497026082843</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>8.862064793103475</v>
+        <v>8.487968350515462</v>
       </c>
       <c r="Q37" t="n">
         <v>30</v>
@@ -4672,7 +4672,7 @@
         <v>46279</v>
       </c>
       <c r="C38" t="n">
-        <v>1.702897805565267</v>
+        <v>1.681337666077084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4732,22 +4732,22 @@
         <v>12.11239445105858</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.736937111065374</v>
+        <v>3.968370492493256</v>
       </c>
       <c r="Z38" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="AA38" t="n">
-        <v>54.54545454545455</v>
+        <v>46.93877551020408</v>
       </c>
       <c r="AB38" t="n">
-        <v>11.82499297704789</v>
+        <v>11.9668255635051</v>
       </c>
       <c r="AC38" t="n">
         <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>7.467442082538945</v>
+        <v>6.280878017419511</v>
       </c>
       <c r="AE38" t="n">
         <v>30</v>
@@ -4781,7 +4781,7 @@
         <v>46279</v>
       </c>
       <c r="C39" t="n">
-        <v>2.766180614112663</v>
+        <v>2.749784048373164</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4841,22 +4841,22 @@
         <v>10.27889366548247</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.071464589195216</v>
+        <v>3.646009539292916</v>
       </c>
       <c r="Z39" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="AA39" t="n">
-        <v>39.53488372093023</v>
+        <v>40.54054054054054</v>
       </c>
       <c r="AB39" t="n">
-        <v>13.73331422453536</v>
+        <v>13.8319937724761</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.021334634215822</v>
+        <v>2.443064837742281</v>
       </c>
       <c r="AE39" t="n">
         <v>40</v>
@@ -4890,7 +4890,7 @@
         <v>46279</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2430948316640273</v>
+        <v>0.242894163136029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>15.29580504962521</v>
       </c>
       <c r="K40" t="n">
-        <v>8.90895654814312</v>
+        <v>8.819055007058285</v>
       </c>
       <c r="L40" t="n">
         <v>21</v>
@@ -4960,7 +4960,7 @@
         <v>37.29449902814472</v>
       </c>
       <c r="Y40" t="n">
-        <v>7.74954512704189</v>
+        <v>7.825695503665775</v>
       </c>
       <c r="Z40" t="n">
         <v>5</v>
@@ -5009,7 +5009,7 @@
         <v>46279</v>
       </c>
       <c r="C41" t="n">
-        <v>1.24735207617794</v>
+        <v>1.265887869688618</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5037,22 +5037,22 @@
         <v>40.38073481248902</v>
       </c>
       <c r="K41" t="n">
-        <v>3.603327876195328</v>
+        <v>5.142885094407901</v>
       </c>
       <c r="L41" t="n">
         <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>66.66666666666667</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N41" t="n">
-        <v>21.36094221486254</v>
+        <v>32.97150766357895</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>6.174195612180156</v>
+        <v>4.619537404961727</v>
       </c>
       <c r="Q41" t="n">
         <v>11</v>
@@ -5079,16 +5079,16 @@
         <v>14.15095011586145</v>
       </c>
       <c r="Y41" t="n">
-        <v>9.240065219746718</v>
+        <v>7.891362281532044</v>
       </c>
       <c r="Z41" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AA41" t="n">
-        <v>37.5</v>
+        <v>37.93103448275862</v>
       </c>
       <c r="AB41" t="n">
-        <v>13.53212031871867</v>
+        <v>13.45788424469266</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
@@ -5128,7 +5128,7 @@
         <v>46279</v>
       </c>
       <c r="C42" t="n">
-        <v>3.557986960903277</v>
+        <v>3.514869812019251</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>17.9384880883827</v>
       </c>
       <c r="K42" t="n">
-        <v>12.10992851148196</v>
+        <v>10.75133430298045</v>
       </c>
       <c r="L42" t="n">
         <v>5</v>
@@ -5196,22 +5196,18 @@
         <v>23.7260422361657</v>
       </c>
       <c r="Y42" t="n">
-        <v>8.000897660444583</v>
+        <v>9.115780608684599</v>
       </c>
       <c r="Z42" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>17.57607561221978</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.172958527548474</v>
+        <v>0.9729075049962899</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5243,7 +5239,7 @@
         <v>46279</v>
       </c>
       <c r="C43" t="n">
-        <v>6.06194599263723</v>
+        <v>6.077495783801571</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5262,7 +5258,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -5275,22 +5271,22 @@
         <v>20.13868121382601</v>
       </c>
       <c r="K43" t="n">
-        <v>1.186607131890227</v>
+        <v>1.446165796952603</v>
       </c>
       <c r="L43" t="n">
         <v>18</v>
       </c>
       <c r="M43" t="n">
-        <v>83.33333333333333</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N43" t="n">
-        <v>17.32461006185299</v>
+        <v>18.20199884422525</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.780400438214814</v>
+        <v>2.51742802005841</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5356,7 +5352,7 @@
         <v>46279</v>
       </c>
       <c r="C44" t="n">
-        <v>4.752894720605475</v>
+        <v>4.820862983834479</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5384,7 +5380,7 @@
         <v>25.31049029846984</v>
       </c>
       <c r="K44" t="n">
-        <v>23.7538824476845</v>
+        <v>25.52361162374837</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5419,25 +5415,25 @@
         <v>50</v>
       </c>
       <c r="X44" t="n">
-        <v>26.00298103586976</v>
+        <v>28.14761203738472</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.784956649196257</v>
+        <v>2.047638946928532</v>
       </c>
       <c r="Z44" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA44" t="n">
-        <v>28.57142857142857</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="AB44" t="n">
-        <v>12.30426359661034</v>
+        <v>13.79357295589038</v>
       </c>
       <c r="AC44" t="n">
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>8.364343251839045</v>
+        <v>8.118600682593868</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5463,7 +5459,7 @@
         <v>46279</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02097772659029678</v>
+        <v>0.02077248981942331</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5491,22 +5487,22 @@
         <v>15.15550562104173</v>
       </c>
       <c r="K45" t="n">
-        <v>1.7153340752319</v>
+        <v>0.7201963693389768</v>
       </c>
       <c r="L45" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M45" t="n">
-        <v>58.66666666666666</v>
+        <v>64.86486486486487</v>
       </c>
       <c r="N45" t="n">
-        <v>15.43285327996341</v>
+        <v>13.76299784511018</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>8.14495277441698</v>
+        <v>9.213448707578141</v>
       </c>
       <c r="Q45" t="n">
         <v>38</v>
@@ -5533,16 +5529,16 @@
         <v>20.3749963300697</v>
       </c>
       <c r="Y45" t="n">
-        <v>13.70013909800125</v>
+        <v>14.54445865294046</v>
       </c>
       <c r="Z45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA45" t="n">
-        <v>50</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB45" t="n">
-        <v>8.271693522313809</v>
+        <v>9.005922820261524</v>
       </c>
       <c r="AC45" t="n">
         <v>5</v>
@@ -5582,7 +5578,7 @@
         <v>46279</v>
       </c>
       <c r="C46" t="n">
-        <v>9.974703329699937</v>
+        <v>9.882357780428613</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5642,16 +5638,16 @@
         <v>27.45411700532656</v>
       </c>
       <c r="Y46" t="n">
-        <v>7.964521134890267</v>
+        <v>8.816583253163168</v>
       </c>
       <c r="Z46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA46" t="n">
-        <v>55.55555555555556</v>
+        <v>60</v>
       </c>
       <c r="AB46" t="n">
-        <v>11.25888400386826</v>
+        <v>15.10080616517297</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
@@ -5691,7 +5687,7 @@
         <v>46279</v>
       </c>
       <c r="C47" t="n">
-        <v>0.981428542048002</v>
+        <v>0.9686972975196414</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5716,25 +5712,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>13.69562606453565</v>
+        <v>14.28021701350416</v>
       </c>
       <c r="K47" t="n">
-        <v>1.31635148649718</v>
+        <v>0.6840530141085877</v>
       </c>
       <c r="L47" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M47" t="n">
-        <v>57.35294117647059</v>
+        <v>56.92307692307692</v>
       </c>
       <c r="N47" t="n">
-        <v>14.10046870176711</v>
+        <v>14.40511994186442</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>8.570826313914527</v>
+        <v>9.252653927813181</v>
       </c>
       <c r="Q47" t="n">
         <v>51</v>
@@ -5761,10 +5757,10 @@
         <v>66.65983471422588</v>
       </c>
       <c r="Y47" t="n">
-        <v>12.55955715532406</v>
+        <v>13.69384825429769</v>
       </c>
       <c r="Z47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr"/>
@@ -5806,7 +5802,7 @@
         <v>46279</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05758591613022643</v>
+        <v>0.05840977335362593</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5831,25 +5827,25 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>10.39336704032353</v>
+        <v>10.39152411668899</v>
       </c>
       <c r="K48" t="n">
-        <v>1.449275729888666</v>
+        <v>2.898551097458513</v>
       </c>
       <c r="L48" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="M48" t="n">
-        <v>56.06060606060606</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="N48" t="n">
-        <v>15.59794251040301</v>
+        <v>16.25360952265471</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>8.428571035714306</v>
+        <v>6.901408063380288</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5876,16 +5872,16 @@
         <v>19.37342145735985</v>
       </c>
       <c r="Y48" t="n">
-        <v>9.094719856468513</v>
+        <v>7.794176655557417</v>
       </c>
       <c r="Z48" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA48" t="n">
-        <v>41.1764705882353</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="AB48" t="n">
-        <v>11.70781901458699</v>
+        <v>14.06492007635003</v>
       </c>
       <c r="AC48" t="n">
         <v>6</v>
@@ -5925,7 +5921,7 @@
         <v>46279</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2852559488308002</v>
+        <v>0.2846448109909094</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5985,22 +5981,22 @@
         <v>22.46912765663718</v>
       </c>
       <c r="Y49" t="n">
-        <v>6.275337651240587</v>
+        <v>6.476135173350428</v>
       </c>
       <c r="Z49" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA49" t="n">
-        <v>47.61904761904762</v>
+        <v>50</v>
       </c>
       <c r="AB49" t="n">
-        <v>8.814786576143803</v>
+        <v>9.058713821243058</v>
       </c>
       <c r="AC49" t="n">
         <v>10</v>
       </c>
       <c r="AD49" t="n">
-        <v>3.974047230919375</v>
+        <v>3.767877678260201</v>
       </c>
       <c r="AE49" t="n">
         <v>45</v>
@@ -6034,7 +6030,7 @@
         <v>46279</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7214692635172655</v>
+        <v>0.7218954382789684</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6094,7 +6090,7 @@
         <v>15.51990994893744</v>
       </c>
       <c r="Y50" t="n">
-        <v>6.461646939178712</v>
+        <v>6.406393462223314</v>
       </c>
       <c r="Z50" t="n">
         <v>30</v>
@@ -6143,7 +6139,7 @@
         <v>46279</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1441704543117455</v>
+        <v>0.1412940644152853</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6160,11 +6156,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>5</v>
       </c>
@@ -6175,16 +6167,16 @@
         <v>31.62908307640215</v>
       </c>
       <c r="K51" t="n">
-        <v>8.250558952238318</v>
+        <v>6.090818140274878</v>
       </c>
       <c r="L51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M51" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="N51" t="n">
-        <v>16.83520922432485</v>
+        <v>20.64820354085114</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
@@ -6217,22 +6209,22 @@
         <v>15.73461610040814</v>
       </c>
       <c r="Y51" t="n">
-        <v>6.466567566679315</v>
+        <v>8.332682377212496</v>
       </c>
       <c r="Z51" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AA51" t="n">
-        <v>37.5</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB51" t="n">
-        <v>13.2147918597851</v>
+        <v>12.13109930543536</v>
       </c>
       <c r="AC51" t="n">
         <v>10</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.777721335993567</v>
+        <v>1.818879035654275</v>
       </c>
       <c r="AE51" t="n">
         <v>12</v>
@@ -6266,7 +6258,7 @@
         <v>46279</v>
       </c>
       <c r="C52" t="n">
-        <v>4.637722888345023</v>
+        <v>4.629591542922957</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6326,22 +6318,22 @@
         <v>17.68393155583896</v>
       </c>
       <c r="Y52" t="n">
-        <v>3.329707481989475</v>
+        <v>3.499200045353168</v>
       </c>
       <c r="Z52" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AA52" t="n">
-        <v>44.11764705882353</v>
+        <v>48.48484848484848</v>
       </c>
       <c r="AB52" t="n">
-        <v>10.21277776758257</v>
+        <v>11.26514743419562</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>4.831155876703697</v>
+        <v>4.664002740663397</v>
       </c>
       <c r="AE52" t="n">
         <v>37</v>
@@ -6375,7 +6367,7 @@
         <v>46279</v>
       </c>
       <c r="C53" t="n">
-        <v>1.263805195072291</v>
+        <v>1.202130722718111</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6400,25 +6392,25 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>27.61578934530905</v>
+        <v>30.11351257643013</v>
       </c>
       <c r="K53" t="n">
-        <v>1.589653305366023</v>
+        <v>0.08561643835618415</v>
       </c>
       <c r="L53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M53" t="n">
-        <v>50</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N53" t="n">
-        <v>11.29718397440806</v>
+        <v>12.24769996038692</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>6.310038951865771</v>
+        <v>7.907613344739084</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6476,7 +6468,7 @@
         <v>46279</v>
       </c>
       <c r="C54" t="n">
-        <v>0.07198239516278306</v>
+        <v>0.07198387561186294</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6504,7 +6496,7 @@
         <v>29.5817777621179</v>
       </c>
       <c r="K54" t="n">
-        <v>14.68116966036195</v>
+        <v>14.6835282875196</v>
       </c>
       <c r="L54" t="n">
         <v>7</v>
@@ -6546,7 +6538,7 @@
         <v>14.75410024187049</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.06355379141557149</v>
+        <v>0.06149841635474385</v>
       </c>
       <c r="Z54" t="n">
         <v>27</v>
@@ -6561,7 +6553,7 @@
         <v>2</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.937677676213079</v>
+        <v>1.939694465023367</v>
       </c>
       <c r="AE54" t="n">
         <v>7</v>
@@ -6595,7 +6587,7 @@
         <v>46279</v>
       </c>
       <c r="C55" t="n">
-        <v>0.931657857392592</v>
+        <v>0.9312656822014727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6655,13 +6647,13 @@
         <v>23.0932342837701</v>
       </c>
       <c r="Y55" t="n">
-        <v>6.789782026846014</v>
+        <v>6.829018249411889</v>
       </c>
       <c r="Z55" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA55" t="n">
-        <v>38.09523809523809</v>
+        <v>40</v>
       </c>
       <c r="AB55" t="n">
         <v>9.365455206540789</v>
@@ -6704,7 +6696,7 @@
         <v>46279</v>
       </c>
       <c r="C56" t="n">
-        <v>0.69678958517574</v>
+        <v>0.6968039159228333</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6732,7 +6724,7 @@
         <v>55.30631598314248</v>
       </c>
       <c r="K56" t="n">
-        <v>8.441182743870046</v>
+        <v>8.443413034330005</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6762,7 +6754,7 @@
         <v>44.70154625822338</v>
       </c>
       <c r="Y56" t="n">
-        <v>25.05872566810435</v>
+        <v>25.05718436428445</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -6799,7 +6791,7 @@
         <v>46279</v>
       </c>
       <c r="C57" t="n">
-        <v>1.459185981942702</v>
+        <v>1.494179589486241</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6859,22 +6851,22 @@
         <v>20.62560129901716</v>
       </c>
       <c r="Y57" t="n">
-        <v>4.182555966228851</v>
+        <v>1.884700810110418</v>
       </c>
       <c r="Z57" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AA57" t="n">
-        <v>45.65217391304348</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB57" t="n">
-        <v>14.65689458546553</v>
+        <v>15.38906972645917</v>
       </c>
       <c r="AC57" t="n">
         <v>5</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.85312652827918</v>
+        <v>3.175141099921963</v>
       </c>
       <c r="AE57" t="n">
         <v>44</v>
@@ -6908,7 +6900,7 @@
         <v>46279</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7338091026880283</v>
+        <v>0.7214841018469006</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6927,7 +6919,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6940,16 +6932,16 @@
         <v>18.04392839464337</v>
       </c>
       <c r="K58" t="n">
-        <v>12.47522734717288</v>
+        <v>10.58610214201814</v>
       </c>
       <c r="L58" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M58" t="n">
-        <v>76.47058823529412</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="N58" t="n">
-        <v>15.05992327858505</v>
+        <v>21.94783451677582</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
@@ -6982,16 +6974,16 @@
         <v>20.50322102897642</v>
       </c>
       <c r="Y58" t="n">
-        <v>6.662057340254091</v>
+        <v>8.22975419434937</v>
       </c>
       <c r="Z58" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA58" t="n">
-        <v>50</v>
+        <v>43.75</v>
       </c>
       <c r="AB58" t="n">
-        <v>9.219813182547147</v>
+        <v>8.538618238015498</v>
       </c>
       <c r="AC58" t="n">
         <v>6</v>
@@ -7031,7 +7023,7 @@
         <v>46279</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7535528453612489</v>
+        <v>0.7708444736950351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7059,22 +7051,22 @@
         <v>11.95882015364728</v>
       </c>
       <c r="K59" t="n">
-        <v>2.865267627520351</v>
+        <v>5.225696610331543</v>
       </c>
       <c r="L59" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="M59" t="n">
-        <v>66.10169491525424</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N59" t="n">
-        <v>12.81977562584208</v>
+        <v>13.01293594074701</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>4.991706618674008</v>
+        <v>2.636526513045734</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7140,7 +7132,7 @@
         <v>46279</v>
       </c>
       <c r="C60" t="n">
-        <v>11.13670485161343</v>
+        <v>11.11636707663198</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7168,22 +7160,22 @@
         <v>24.49246832941995</v>
       </c>
       <c r="K60" t="n">
-        <v>4.829837661081227</v>
+        <v>4.638398121459697</v>
       </c>
       <c r="L60" t="n">
         <v>15</v>
       </c>
       <c r="M60" t="n">
-        <v>66.66666666666667</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N60" t="n">
-        <v>12.28631987346338</v>
+        <v>12.32924210467809</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>3.024103069937056</v>
+        <v>3.212589201373572</v>
       </c>
       <c r="Q60" t="n">
         <v>46</v>
@@ -7249,7 +7241,7 @@
         <v>46279</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7868704111223084</v>
+        <v>0.7914112952984245</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7277,16 +7269,16 @@
         <v>14.0586191907223</v>
       </c>
       <c r="K61" t="n">
-        <v>10.21439724247424</v>
+        <v>10.8504242239752</v>
       </c>
       <c r="L61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M61" t="n">
-        <v>64.70588235294117</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N61" t="n">
-        <v>15.5281052002875</v>
+        <v>15.21675647587978</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
@@ -7319,13 +7311,13 @@
         <v>49.99145178651283</v>
       </c>
       <c r="Y61" t="n">
-        <v>5.28022515919514</v>
+        <v>4.733614788973661</v>
       </c>
       <c r="Z61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA61" t="n">
-        <v>66.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="AB61" t="n">
         <v>13.92348961705937</v>
@@ -7368,7 +7360,7 @@
         <v>46279</v>
       </c>
       <c r="C62" t="n">
-        <v>9.090348189128601</v>
+        <v>9.054543210892188</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7428,7 +7420,7 @@
         <v>11.69351808836483</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.728371662031137</v>
+        <v>3.111504239925866</v>
       </c>
       <c r="Z62" t="n">
         <v>53</v>
@@ -7437,13 +7429,13 @@
         <v>45.28301886792453</v>
       </c>
       <c r="AB62" t="n">
-        <v>15.47237123452912</v>
+        <v>15.41942847330274</v>
       </c>
       <c r="AC62" t="n">
         <v>5</v>
       </c>
       <c r="AD62" t="n">
-        <v>2.335345235587227</v>
+        <v>1.949143440879331</v>
       </c>
       <c r="AE62" t="n">
         <v>27</v>
@@ -7477,7 +7469,7 @@
         <v>46279</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1127038644263003</v>
+        <v>0.1116778413064045</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7505,16 +7497,16 @@
         <v>14.68172212919103</v>
       </c>
       <c r="K63" t="n">
-        <v>7.657531104335447</v>
+        <v>6.67744833160866</v>
       </c>
       <c r="L63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M63" t="n">
-        <v>57.14285714285715</v>
+        <v>70</v>
       </c>
       <c r="N63" t="n">
-        <v>16.64786066066635</v>
+        <v>14.93116161136219</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
@@ -7547,13 +7539,13 @@
         <v>24.85614965143601</v>
       </c>
       <c r="Y63" t="n">
-        <v>8.148448463550494</v>
+        <v>8.984638206949459</v>
       </c>
       <c r="Z63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA63" t="n">
-        <v>25</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB63" t="n">
         <v>12.72793373689106</v>
@@ -7562,7 +7554,7 @@
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>2.015808666786378</v>
+        <v>1.115593865746811</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7596,7 +7588,7 @@
         <v>46279</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1501347099109475</v>
+        <v>0.1489037884085394</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7605,7 +7597,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7620,17 +7612,27 @@
       <c r="I64" t="n">
         <v>10</v>
       </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="J64" t="n">
+        <v>10.25688449628873</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.138312586445366</v>
+      </c>
       <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+        <v>69</v>
+      </c>
+      <c r="M64" t="n">
+        <v>56.52173913043478</v>
+      </c>
+      <c r="N64" t="n">
+        <v>15.5775382363878</v>
+      </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
-      <c r="P64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>4.854972375690614</v>
+      </c>
       <c r="Q64" t="n">
         <v>55</v>
       </c>
@@ -7656,16 +7658,16 @@
         <v>14.28923074155179</v>
       </c>
       <c r="Y64" t="n">
-        <v>9.389865889283611</v>
+        <v>10.13275847207891</v>
       </c>
       <c r="Z64" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA64" t="n">
-        <v>52.94117647058823</v>
+        <v>56.25</v>
       </c>
       <c r="AB64" t="n">
-        <v>14.80997747696459</v>
+        <v>16.12578144354295</v>
       </c>
       <c r="AC64" t="n">
         <v>2</v>
@@ -7705,7 +7707,7 @@
         <v>46279</v>
       </c>
       <c r="C65" t="n">
-        <v>6.540114760504289</v>
+        <v>6.44769857266258</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7765,16 +7767,16 @@
         <v>24.47056390537039</v>
       </c>
       <c r="Y65" t="n">
-        <v>7.251439732927201</v>
+        <v>8.562038809789406</v>
       </c>
       <c r="Z65" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA65" t="n">
-        <v>35.29411764705883</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB65" t="n">
-        <v>9.143786421853511</v>
+        <v>11.44316310099862</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
@@ -7814,7 +7816,7 @@
         <v>46279</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4504041297328425</v>
+        <v>0.448768047385957</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7842,22 +7844,22 @@
         <v>10.41136575766793</v>
       </c>
       <c r="K66" t="n">
-        <v>3.824815608314913</v>
+        <v>3.447674421607405</v>
       </c>
       <c r="L66" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M66" t="n">
-        <v>50</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N66" t="n">
-        <v>21.68499124327241</v>
+        <v>20.54606781361603</v>
       </c>
       <c r="O66" t="n">
         <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>2.095052496785654</v>
+        <v>2.467262403590098</v>
       </c>
       <c r="Q66" t="n">
         <v>35</v>
@@ -7884,16 +7886,16 @@
         <v>14.59585890675015</v>
       </c>
       <c r="Y66" t="n">
-        <v>6.984765691891049</v>
+        <v>7.322641330227631</v>
       </c>
       <c r="Z66" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA66" t="n">
-        <v>44.11764705882353</v>
+        <v>46.875</v>
       </c>
       <c r="AB66" t="n">
-        <v>11.59209911118779</v>
+        <v>10.96998186648398</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
@@ -7933,16 +7935,16 @@
         <v>46279</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02755897414803694</v>
+        <v>0.02735387273250792</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7961,22 +7963,22 @@
         <v>11.46300958938384</v>
       </c>
       <c r="K67" t="n">
-        <v>4.271751893718023</v>
+        <v>3.49573302602677</v>
       </c>
       <c r="L67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M67" t="n">
-        <v>33.33333333333334</v>
+        <v>20</v>
       </c>
       <c r="N67" t="n">
-        <v>6.727646988993397</v>
+        <v>7.104188996989391</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>0.4872345547293433</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -8022,7 +8024,7 @@
         <v>46279</v>
       </c>
       <c r="C68" t="n">
-        <v>1.734775723423071</v>
+        <v>1.734811402245897</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8047,7 +8049,7 @@
         <v>10</v>
       </c>
       <c r="J68" t="n">
-        <v>68.93321055495181</v>
+        <v>68.93257160983551</v>
       </c>
       <c r="K68" t="n">
         <v>1.813870809108664e-06</v>
@@ -8127,11 +8129,11 @@
         <v>46279</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5322583962322358</v>
+        <v>0.5067664843075151</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -8141,7 +8143,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -8176,13 +8178,13 @@
         <v>75</v>
       </c>
       <c r="X69" t="n">
-        <v>45.32573627045717</v>
+        <v>45.32872515894941</v>
       </c>
       <c r="Y69" t="n">
-        <v>4.431314623338256</v>
+        <v>9.010339734121109</v>
       </c>
       <c r="Z69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA69" t="inlineStr"/>
       <c r="AB69" t="inlineStr"/>
@@ -8190,7 +8192,7 @@
         <v>6</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.641421947449773</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -8216,7 +8218,7 @@
         <v>46279</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4931822388581536</v>
+        <v>0.4899016905927358</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8241,25 +8243,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>11.14419642238965</v>
+        <v>11.36562932047446</v>
       </c>
       <c r="K70" t="n">
-        <v>0.4187604690117253</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M70" t="n">
         <v>50</v>
       </c>
       <c r="N70" t="n">
-        <v>12.19381899531639</v>
+        <v>12.22267739008541</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>7.549624687239365</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q70" t="n">
         <v>31</v>
@@ -8286,16 +8288,16 @@
         <v>44.93251946562029</v>
       </c>
       <c r="Y70" t="n">
-        <v>10.77210344258391</v>
+        <v>11.36562932047446</v>
       </c>
       <c r="Z70" t="n">
         <v>6</v>
       </c>
       <c r="AA70" t="n">
-        <v>66.66666666666667</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB70" t="n">
-        <v>8.505081411414517</v>
+        <v>10.37117321374181</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
@@ -8335,7 +8337,7 @@
         <v>46279</v>
       </c>
       <c r="C71" t="n">
-        <v>3.14871562840631</v>
+        <v>3.233104356052815</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8434,7 +8436,7 @@
         <v>46279</v>
       </c>
       <c r="C72" t="n">
-        <v>0.06478415564650475</v>
+        <v>0.0629344741063716</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8451,11 +8453,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>5</v>
       </c>
@@ -8466,16 +8464,16 @@
         <v>29.77666337790048</v>
       </c>
       <c r="K72" t="n">
-        <v>8.563672786824972</v>
+        <v>5.46402257947245</v>
       </c>
       <c r="L72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M72" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N72" t="n">
-        <v>22.47171058340287</v>
+        <v>20.40933767641903</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
@@ -8508,22 +8506,22 @@
         <v>12.03392243896149</v>
       </c>
       <c r="Y72" t="n">
-        <v>3.097499022251216</v>
+        <v>5.864205873063543</v>
       </c>
       <c r="Z72" t="n">
         <v>34</v>
       </c>
       <c r="AA72" t="n">
-        <v>38.23529411764706</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="AB72" t="n">
-        <v>12.81395919933085</v>
+        <v>11.90415789566501</v>
       </c>
       <c r="AC72" t="n">
         <v>8</v>
       </c>
       <c r="AD72" t="n">
-        <v>5.059209956690913</v>
+        <v>2.268843798201203</v>
       </c>
       <c r="AE72" t="n">
         <v>10</v>
@@ -8557,7 +8555,7 @@
         <v>46279</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0621105238261728</v>
+        <v>0.06231746945826992</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8589,22 +8587,22 @@
         <v>19.59098648410814</v>
       </c>
       <c r="K73" t="n">
-        <v>1.742284299190211</v>
+        <v>2.081278724583036</v>
       </c>
       <c r="L73" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M73" t="n">
         <v>75</v>
       </c>
       <c r="N73" t="n">
-        <v>14.97241292837137</v>
+        <v>12.3596071563907</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>8.116306565839038</v>
+        <v>7.757270847656428</v>
       </c>
       <c r="Q73" t="n">
         <v>14</v>
@@ -8670,7 +8668,7 @@
         <v>46279</v>
       </c>
       <c r="C74" t="n">
-        <v>5.475803632025996</v>
+        <v>5.527333305910904</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8695,25 +8693,25 @@
         <v>10</v>
       </c>
       <c r="J74" t="n">
-        <v>10.38264080673934</v>
+        <v>10.38079766250025</v>
       </c>
       <c r="K74" t="n">
-        <v>2.998065764023217</v>
+        <v>3.965183752417789</v>
       </c>
       <c r="L74" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="M74" t="n">
-        <v>69.49152542372882</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N74" t="n">
-        <v>14.87070545691084</v>
+        <v>15.05047855147138</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>4.856338028169005</v>
+        <v>3.880930232558155</v>
       </c>
       <c r="Q74" t="n">
         <v>30</v>
@@ -8740,22 +8738,22 @@
         <v>25.51128431523497</v>
       </c>
       <c r="Y74" t="n">
-        <v>7.695853442144484</v>
+        <v>6.82723161236728</v>
       </c>
       <c r="Z74" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA74" t="n">
-        <v>44.44444444444444</v>
+        <v>50</v>
       </c>
       <c r="AB74" t="n">
-        <v>13.55476783829268</v>
+        <v>14.1840709499142</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>2.496254657867714</v>
+        <v>3.405252889377341</v>
       </c>
       <c r="AE74" t="n">
         <v>37</v>
@@ -8789,7 +8787,7 @@
         <v>46279</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1092075766612508</v>
+        <v>0.1094154909300317</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8818,10 +8816,10 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>28.79453108040966</v>
+        <v>28.79306661023321</v>
       </c>
       <c r="K75" t="n">
-        <v>0.5681818181817899</v>
+        <v>0.7575757575757569</v>
       </c>
       <c r="L75" t="n">
         <v>11</v>
@@ -8836,7 +8834,7 @@
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>5.401129943502858</v>
+        <v>5.203007518797009</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8902,7 +8900,7 @@
         <v>46279</v>
       </c>
       <c r="C76" t="n">
-        <v>1.957921148427699</v>
+        <v>1.952819711241825</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8962,22 +8960,22 @@
         <v>12.76370567693843</v>
       </c>
       <c r="Y76" t="n">
-        <v>3.570195350714933</v>
+        <v>3.821446833267994</v>
       </c>
       <c r="Z76" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="AA76" t="n">
-        <v>34.69387755102041</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="AB76" t="n">
-        <v>9.460511236049042</v>
+        <v>9.654522659042094</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.4457176397362539</v>
+        <v>0.1856475907081601</v>
       </c>
       <c r="AE76" t="n">
         <v>32</v>
@@ -9011,11 +9009,11 @@
         <v>46279</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4861896633280546</v>
+        <v>0.4812636255193122</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -9025,7 +9023,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -9036,25 +9034,25 @@
         <v>10</v>
       </c>
       <c r="J77" t="n">
-        <v>15.97566139565814</v>
+        <v>16.01978097023047</v>
       </c>
       <c r="K77" t="n">
-        <v>1.230082062401494</v>
+        <v>0.2570694087403513</v>
       </c>
       <c r="L77" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M77" t="n">
-        <v>64.15094339622641</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N77" t="n">
-        <v>15.94290778922146</v>
+        <v>15.10224736770855</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>6.687654301638624</v>
+        <v>7.723076923076944</v>
       </c>
       <c r="Q77" t="n">
         <v>27</v>
@@ -9077,27 +9075,17 @@
       <c r="W77" t="n">
         <v>66.21621621621621</v>
       </c>
-      <c r="X77" t="n">
-        <v>15.48402810769924</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>12.34278564651786</v>
-      </c>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA77" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB77" t="n">
-        <v>11.72863146980229</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
         <v>10</v>
       </c>
-      <c r="AD77" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="n">
         <v>46</v>
       </c>
@@ -9130,16 +9118,16 @@
         <v>46279</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05881990004730272</v>
+        <v>0.05984945086586319</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -9154,27 +9142,17 @@
       <c r="I78" t="n">
         <v>10</v>
       </c>
-      <c r="J78" t="n">
-        <v>10.6248408751511</v>
-      </c>
-      <c r="K78" t="n">
-        <v>8.855660705271795</v>
-      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="n">
-        <v>27</v>
-      </c>
-      <c r="M78" t="n">
-        <v>59.25925925925926</v>
-      </c>
-      <c r="N78" t="n">
-        <v>16.87180111065342</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="n">
         <v>4</v>
       </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
+      <c r="P78" t="inlineStr"/>
       <c r="Q78" t="n">
         <v>46</v>
       </c>
@@ -9197,25 +9175,25 @@
         <v>64.1025641025641</v>
       </c>
       <c r="X78" t="n">
-        <v>31.30012859028892</v>
+        <v>32.21100528735843</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.710080028257711</v>
+        <v>1.689189189189189</v>
       </c>
       <c r="Z78" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA78" t="n">
-        <v>16.66666666666667</v>
+        <v>9.523809523809524</v>
       </c>
       <c r="AB78" t="n">
-        <v>9.430677653834037</v>
+        <v>9.720875045681026</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>7.492985885752224</v>
+        <v>8.453608247422684</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9249,7 +9227,7 @@
         <v>46279</v>
       </c>
       <c r="C79" t="n">
-        <v>0.9057441951339901</v>
+        <v>0.8983587676360495</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9277,22 +9255,22 @@
         <v>10.42896938309872</v>
       </c>
       <c r="K79" t="n">
-        <v>1.503713770959236</v>
+        <v>0.6760536845302534</v>
       </c>
       <c r="L79" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M79" t="n">
-        <v>54.71698113207547</v>
+        <v>51.92307692307692</v>
       </c>
       <c r="N79" t="n">
-        <v>10.40261815720138</v>
+        <v>10.60447963980444</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>3.444490944370826</v>
+        <v>4.294910415359432</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9319,16 +9297,16 @@
         <v>25.65117214954458</v>
       </c>
       <c r="Y79" t="n">
-        <v>9.082077460922267</v>
+        <v>9.823421130341426</v>
       </c>
       <c r="Z79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA79" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AB79" t="n">
-        <v>9.501837951994744</v>
+        <v>9.128747513977077</v>
       </c>
       <c r="AC79" t="n">
         <v>8</v>
@@ -9368,7 +9346,7 @@
         <v>46279</v>
       </c>
       <c r="C80" t="n">
-        <v>0.132036279127162</v>
+        <v>0.1332730039899634</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9396,22 +9374,22 @@
         <v>10.48668504530712</v>
       </c>
       <c r="K80" t="n">
-        <v>3.289416608438467</v>
+        <v>4.256882447587707</v>
       </c>
       <c r="L80" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="M80" t="n">
-        <v>48.93617021276596</v>
+        <v>59.45945945945946</v>
       </c>
       <c r="N80" t="n">
-        <v>18.37249874375921</v>
+        <v>18.41888372789451</v>
       </c>
       <c r="O80" t="n">
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>6.496874134743935</v>
+        <v>5.508621989823537</v>
       </c>
       <c r="Q80" t="n">
         <v>39</v>
@@ -9438,22 +9416,22 @@
         <v>16.92042739318289</v>
       </c>
       <c r="Y80" t="n">
-        <v>7.542219196423627</v>
+        <v>6.676208452746901</v>
       </c>
       <c r="Z80" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AA80" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AB80" t="n">
-        <v>11.59503040169198</v>
+        <v>15.2833189605872</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.4951241524484673</v>
+        <v>1.418493103747087</v>
       </c>
       <c r="AE80" t="n">
         <v>24</v>
@@ -9487,7 +9465,7 @@
         <v>46279</v>
       </c>
       <c r="C81" t="n">
-        <v>1.254550315694219</v>
+        <v>1.239151001604212</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9544,25 +9522,25 @@
         <v>65.30612244897959</v>
       </c>
       <c r="X81" t="n">
-        <v>23.75585078567732</v>
+        <v>23.75839605018282</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.45396043255962</v>
+        <v>2.66559206658552</v>
       </c>
       <c r="Z81" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA81" t="n">
-        <v>29.62962962962963</v>
+        <v>32</v>
       </c>
       <c r="AB81" t="n">
-        <v>11.88627599152127</v>
+        <v>12.2306799472837</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>8.672128890163933</v>
+        <v>7.535267424066394</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9596,7 +9574,7 @@
         <v>46279</v>
       </c>
       <c r="C82" t="n">
-        <v>4.78580089566666</v>
+        <v>4.785899324379911</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9624,7 +9602,7 @@
         <v>16.34835816551005</v>
       </c>
       <c r="K82" t="n">
-        <v>2.332838779732138</v>
+        <v>2.334943440971515</v>
       </c>
       <c r="L82" t="n">
         <v>9</v>
@@ -9639,7 +9617,7 @@
         <v>4</v>
       </c>
       <c r="P82" t="n">
-        <v>1.629155645585456</v>
+        <v>1.627065499859226</v>
       </c>
       <c r="Q82" t="n">
         <v>8</v>
@@ -9705,7 +9683,7 @@
         <v>46279</v>
       </c>
       <c r="C83" t="n">
-        <v>5.532361228225326</v>
+        <v>5.511908189708363</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9733,22 +9711,22 @@
         <v>13.10783674393532</v>
       </c>
       <c r="K83" t="n">
-        <v>4.545167626814273</v>
+        <v>4.158666049635174</v>
       </c>
       <c r="L83" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="M83" t="n">
-        <v>48.27586206896552</v>
+        <v>41.93548387096774</v>
       </c>
       <c r="N83" t="n">
-        <v>12.32886771240047</v>
+        <v>12.84910722114932</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>5.217680067870156</v>
+        <v>5.608111328519927</v>
       </c>
       <c r="Q83" t="n">
         <v>41</v>
@@ -9814,7 +9792,7 @@
         <v>46279</v>
       </c>
       <c r="C84" t="n">
-        <v>2.118339057647615</v>
+        <v>2.108099214347415</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9842,16 +9820,16 @@
         <v>14.96371051984784</v>
       </c>
       <c r="K84" t="n">
-        <v>9.249905385931466</v>
+        <v>8.72180205531734</v>
       </c>
       <c r="L84" t="n">
         <v>27</v>
       </c>
       <c r="M84" t="n">
-        <v>48.14814814814815</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N84" t="n">
-        <v>10.7315592997849</v>
+        <v>10.33046342082408</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9884,22 +9862,22 @@
         <v>11.86663135768809</v>
       </c>
       <c r="Y84" t="n">
-        <v>2.339147912114892</v>
+        <v>2.811230895400174</v>
       </c>
       <c r="Z84" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AA84" t="n">
-        <v>39.6551724137931</v>
+        <v>36.8421052631579</v>
       </c>
       <c r="AB84" t="n">
-        <v>11.91637634624385</v>
+        <v>11.87023114330644</v>
       </c>
       <c r="AC84" t="n">
         <v>5</v>
       </c>
       <c r="AD84" t="n">
-        <v>2.72458414093153</v>
+        <v>2.252080281255708</v>
       </c>
       <c r="AE84" t="n">
         <v>39</v>
@@ -9933,7 +9911,7 @@
         <v>46279</v>
       </c>
       <c r="C85" t="n">
-        <v>6.10822038952759</v>
+        <v>6.087779194603266</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9961,22 +9939,22 @@
         <v>12.5637553307017</v>
       </c>
       <c r="K85" t="n">
-        <v>2.030824131143882</v>
+        <v>1.689377387026747</v>
       </c>
       <c r="L85" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M85" t="n">
-        <v>55.38461538461539</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N85" t="n">
-        <v>13.28660371288908</v>
+        <v>14.71541237919241</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>5.850365239806088</v>
+        <v>6.205783509673002</v>
       </c>
       <c r="Q85" t="n">
         <v>32</v>
@@ -10042,7 +10020,7 @@
         <v>46279</v>
       </c>
       <c r="C86" t="n">
-        <v>4.481418258848693</v>
+        <v>4.46711365225618</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10070,22 +10048,22 @@
         <v>18.73514495170452</v>
       </c>
       <c r="K86" t="n">
-        <v>7.496111793297477</v>
+        <v>7.152986135166417</v>
       </c>
       <c r="L86" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M86" t="n">
-        <v>52.17391304347826</v>
+        <v>52</v>
       </c>
       <c r="N86" t="n">
-        <v>16.75519292329755</v>
+        <v>16.80834062621504</v>
       </c>
       <c r="O86" t="n">
         <v>8</v>
       </c>
       <c r="P86" t="n">
-        <v>0.4687501699330854</v>
+        <v>0.7904715448294963</v>
       </c>
       <c r="Q86" t="n">
         <v>52</v>
@@ -10112,7 +10090,7 @@
         <v>48.61770380947655</v>
       </c>
       <c r="Y86" t="n">
-        <v>12.64344056862314</v>
+        <v>12.92228113733684</v>
       </c>
       <c r="Z86" t="n">
         <v>3</v>
@@ -10161,11 +10139,11 @@
         <v>46279</v>
       </c>
       <c r="C87" t="n">
-        <v>5.984821997819962</v>
+        <v>5.887252683970219</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -10175,7 +10153,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -10221,22 +10199,22 @@
         <v>15.88967756874082</v>
       </c>
       <c r="Y87" t="n">
-        <v>2.980797842541894</v>
+        <v>4.562481807111074</v>
       </c>
       <c r="Z87" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AA87" t="n">
-        <v>52.27272727272727</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB87" t="n">
-        <v>12.61337018943614</v>
+        <v>10.9807118926863</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
       </c>
       <c r="AD87" t="n">
-        <v>1.050515913132322</v>
+        <v>0</v>
       </c>
       <c r="AE87" t="n">
         <v>43</v>
@@ -10270,7 +10248,7 @@
         <v>46279</v>
       </c>
       <c r="C88" t="n">
-        <v>1.073566007856364</v>
+        <v>1.076673110937436</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10298,7 +10276,7 @@
         <v>16.8583060727446</v>
       </c>
       <c r="K88" t="n">
-        <v>7.987093800773315</v>
+        <v>8.299628874917708</v>
       </c>
       <c r="L88" t="n">
         <v>31</v>
@@ -10307,7 +10285,7 @@
         <v>70.96774193548387</v>
       </c>
       <c r="N88" t="n">
-        <v>13.58201913365737</v>
+        <v>13.62701040529383</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
@@ -10340,16 +10318,16 @@
         <v>25.70907945955605</v>
       </c>
       <c r="Y88" t="n">
-        <v>10.21770099122287</v>
+        <v>9.957854036462399</v>
       </c>
       <c r="Z88" t="n">
         <v>22</v>
       </c>
       <c r="AA88" t="n">
-        <v>40.90909090909091</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB88" t="n">
-        <v>13.51336303619622</v>
+        <v>14.2055834366375</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
@@ -10389,7 +10367,7 @@
         <v>46279</v>
       </c>
       <c r="C89" t="n">
-        <v>2.180038253501429</v>
+        <v>2.178026407798939</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10449,22 +10427,22 @@
         <v>21.45830694080864</v>
       </c>
       <c r="Y89" t="n">
-        <v>6.897016005685474</v>
+        <v>6.982935983436855</v>
       </c>
       <c r="Z89" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA89" t="n">
-        <v>36.8421052631579</v>
+        <v>40.54054054054054</v>
       </c>
       <c r="AB89" t="n">
-        <v>14.81466677324567</v>
+        <v>16.66848020226589</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>3.33285128058195</v>
+        <v>3.243559715049604</v>
       </c>
       <c r="AE89" t="n">
         <v>22</v>
@@ -10498,7 +10476,7 @@
         <v>46279</v>
       </c>
       <c r="C90" t="n">
-        <v>2.803200131624952</v>
+        <v>2.819711241824688</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10526,22 +10504,22 @@
         <v>12.8208334231333</v>
       </c>
       <c r="K90" t="n">
-        <v>2.923060251180654</v>
+        <v>3.529286674592047</v>
       </c>
       <c r="L90" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="M90" t="n">
-        <v>65.88235294117646</v>
+        <v>62.33766233766234</v>
       </c>
       <c r="N90" t="n">
-        <v>15.18234473664055</v>
+        <v>15.1054787554164</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>4.932752423440601</v>
+        <v>4.318307861484727</v>
       </c>
       <c r="Q90" t="n">
         <v>43</v>
@@ -10568,16 +10546,16 @@
         <v>20.63086277737274</v>
       </c>
       <c r="Y90" t="n">
-        <v>10.27253385761435</v>
+        <v>9.744030714115548</v>
       </c>
       <c r="Z90" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA90" t="n">
-        <v>45</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="AB90" t="n">
-        <v>10.97878543820853</v>
+        <v>11.67938000705534</v>
       </c>
       <c r="AC90" t="n">
         <v>2</v>
@@ -10617,7 +10595,7 @@
         <v>46279</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2365135841062872</v>
+        <v>0.2356957755748427</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10716,11 +10694,11 @@
         <v>46279</v>
       </c>
       <c r="C92" t="n">
-        <v>1.204162639080271</v>
+        <v>1.1856772654354</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -10730,7 +10708,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -10776,22 +10754,22 @@
         <v>21.60407460332612</v>
       </c>
       <c r="Y92" t="n">
-        <v>3.840935535973944</v>
+        <v>5.317095132917126</v>
       </c>
       <c r="Z92" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AA92" t="n">
-        <v>40</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AB92" t="n">
-        <v>16.45981091086437</v>
+        <v>12.79838806403724</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
       </c>
       <c r="AD92" t="n">
-        <v>0.1654180652782555</v>
+        <v>0</v>
       </c>
       <c r="AE92" t="n">
         <v>52</v>
@@ -10825,7 +10803,7 @@
         <v>46279</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04174978919441416</v>
+        <v>0.04216198428694829</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10885,16 +10863,16 @@
         <v>11.4419372600254</v>
       </c>
       <c r="Y93" t="n">
-        <v>5.00825717515001</v>
+        <v>4.070405009206468</v>
       </c>
       <c r="Z93" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="AA93" t="n">
-        <v>52.63157894736842</v>
+        <v>44.18604651162791</v>
       </c>
       <c r="AB93" t="n">
-        <v>14.42170474454301</v>
+        <v>13.26309491661619</v>
       </c>
       <c r="AC93" t="n">
         <v>2</v>
@@ -10934,7 +10912,7 @@
         <v>46279</v>
       </c>
       <c r="C94" t="n">
-        <v>8.586471422989121</v>
+        <v>8.60721484101847</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10994,22 +10972,22 @@
         <v>46.54975901226545</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.575691891694908</v>
+        <v>1.337915922176891</v>
       </c>
       <c r="Z94" t="n">
         <v>10</v>
       </c>
       <c r="AA94" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AB94" t="n">
-        <v>11.5296957311535</v>
+        <v>9.178759695939807</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>4.495137627420897</v>
+        <v>4.725304681528653</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -11043,7 +11021,7 @@
         <v>46279</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1223700678691154</v>
+        <v>0.1223725846324709</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11071,7 +11049,7 @@
         <v>18.89669242033002</v>
       </c>
       <c r="K95" t="n">
-        <v>0.9603134242809785</v>
+        <v>0.9623898570362055</v>
       </c>
       <c r="L95" t="n">
         <v>27</v>
@@ -11086,7 +11064,7 @@
         <v>10</v>
       </c>
       <c r="P95" t="n">
-        <v>8.953702964183741</v>
+        <v>8.951462178897662</v>
       </c>
       <c r="Q95" t="n">
         <v>21</v>
@@ -11152,7 +11130,7 @@
         <v>46279</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1277173354173951</v>
+        <v>0.1271029575089466</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11251,7 +11229,7 @@
         <v>46279</v>
       </c>
       <c r="C97" t="n">
-        <v>1.923986590708101</v>
+        <v>1.913742750195385</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11279,16 +11257,16 @@
         <v>12.87370897365936</v>
       </c>
       <c r="K97" t="n">
-        <v>5.167586854699002</v>
+        <v>4.607645329092902</v>
       </c>
       <c r="L97" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M97" t="n">
-        <v>52.5</v>
+        <v>59.52380952380953</v>
       </c>
       <c r="N97" t="n">
-        <v>16.50075824133667</v>
+        <v>15.00415549181639</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11321,16 +11299,16 @@
         <v>16.31583297271808</v>
       </c>
       <c r="Y97" t="n">
-        <v>8.371382211595391</v>
+        <v>8.859238494772292</v>
       </c>
       <c r="Z97" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AA97" t="n">
-        <v>50</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB97" t="n">
-        <v>10.29457166100521</v>
+        <v>11.08203790087885</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
@@ -11370,7 +11348,7 @@
         <v>46279</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7593114369742715</v>
+        <v>0.7375262226975443</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11430,22 +11408,22 @@
         <v>30.85778357900837</v>
       </c>
       <c r="Y98" t="n">
-        <v>3.107840947786611</v>
+        <v>5.887749617539373</v>
       </c>
       <c r="Z98" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AA98" t="n">
-        <v>30</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="AB98" t="n">
-        <v>11.24407736888147</v>
+        <v>10.34887947774709</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>5.049076313365141</v>
+        <v>2.244394724253962</v>
       </c>
       <c r="AE98" t="n">
         <v>51</v>
@@ -11479,21 +11457,21 @@
         <v>46279</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5162166053102442</v>
+        <v>0.5417300810332771</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -11504,25 +11482,25 @@
         <v>10</v>
       </c>
       <c r="J99" t="n">
-        <v>12.54207936754466</v>
+        <v>12.54028063609323</v>
       </c>
       <c r="K99" t="n">
-        <v>0.7223113964686778</v>
+        <v>5.69823434991974</v>
       </c>
       <c r="L99" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="M99" t="n">
-        <v>55.12820512820513</v>
+        <v>58.18181818181818</v>
       </c>
       <c r="N99" t="n">
-        <v>15.91650966270182</v>
+        <v>14.98905401797758</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>3.254183266932298</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>34</v>
@@ -11549,20 +11527,22 @@
         <v>33.04241514445872</v>
       </c>
       <c r="Y99" t="n">
-        <v>11.91036083970189</v>
+        <v>7.556620864955677</v>
       </c>
       <c r="Z99" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB99" t="inlineStr"/>
+        <v>66.66666666666667</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>12.01251736130811</v>
+      </c>
       <c r="AC99" t="n">
         <v>10</v>
       </c>
       <c r="AD99" t="n">
-        <v>0</v>
+        <v>2.643108849877662</v>
       </c>
       <c r="AE99" t="n">
         <v>38</v>
@@ -11596,7 +11576,7 @@
         <v>46279</v>
       </c>
       <c r="C100" t="n">
-        <v>348.2493817226415</v>
+        <v>348.2565441055489</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11656,7 +11636,7 @@
         <v>16.86980163304483</v>
       </c>
       <c r="Y100" t="n">
-        <v>4.411790147978212</v>
+        <v>4.409824202318791</v>
       </c>
       <c r="Z100" t="n">
         <v>36</v>
@@ -11671,7 +11651,7 @@
         <v>8</v>
       </c>
       <c r="AD100" t="n">
-        <v>3.753820536629593</v>
+        <v>3.755799973921892</v>
       </c>
       <c r="AE100" t="n">
         <v>39</v>
@@ -11705,7 +11685,7 @@
         <v>46279</v>
       </c>
       <c r="C101" t="n">
-        <v>350.2994467638772</v>
+        <v>349.7782896631154</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11765,22 +11745,22 @@
         <v>13.07599096065748</v>
       </c>
       <c r="Y101" t="n">
-        <v>3.080036950691201</v>
+        <v>3.224229376386822</v>
       </c>
       <c r="Z101" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA101" t="n">
-        <v>40</v>
+        <v>43.58974358974359</v>
       </c>
       <c r="AB101" t="n">
-        <v>11.90979741970219</v>
+        <v>11.51404947830189</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>3.012757080626671</v>
+        <v>2.868249568798475</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11814,7 +11794,7 @@
         <v>46279</v>
       </c>
       <c r="C102" t="n">
-        <v>408.2814540571335</v>
+        <v>408.289851108963</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11874,7 +11854,7 @@
         <v>10.81355469301844</v>
       </c>
       <c r="Y102" t="n">
-        <v>4.221753456163324</v>
+        <v>4.219783602053173</v>
       </c>
       <c r="Z102" t="n">
         <v>17</v>
@@ -11889,7 +11869,7 @@
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>0.8125504192441957</v>
+        <v>0.8145903478701699</v>
       </c>
       <c r="AE102" t="n">
         <v>26</v>
@@ -11923,7 +11903,7 @@
         <v>46279</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7494395656376612</v>
+        <v>0.751922997819917</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11983,22 +11963,22 @@
         <v>14.28440963201156</v>
       </c>
       <c r="Y103" t="n">
-        <v>5.165542609116547</v>
+        <v>4.8512878589408</v>
       </c>
       <c r="Z103" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="AA103" t="n">
-        <v>45.71428571428572</v>
+        <v>48.64864864864865</v>
       </c>
       <c r="AB103" t="n">
-        <v>11.21113198199012</v>
+        <v>10.95821207278935</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>2.988847586484877</v>
+        <v>3.30925355709617</v>
       </c>
       <c r="AE103" t="n">
         <v>33</v>
@@ -12032,7 +12012,7 @@
         <v>46279</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04997634864158938</v>
+        <v>0.05018304471227016</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12092,22 +12072,22 @@
         <v>12.98853157526716</v>
       </c>
       <c r="Y104" t="n">
-        <v>4.971831353613965</v>
+        <v>4.578806460897944</v>
       </c>
       <c r="Z104" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AA104" t="n">
-        <v>52</v>
+        <v>51.78571428571428</v>
       </c>
       <c r="AB104" t="n">
-        <v>12.55123502002542</v>
+        <v>12.61850589849145</v>
       </c>
       <c r="AC104" t="n">
         <v>5</v>
       </c>
       <c r="AD104" t="n">
-        <v>0.02964241738768747</v>
+        <v>0.4414046015149276</v>
       </c>
       <c r="AE104" t="n">
         <v>42</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -444,7 +444,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -670,7 +670,7 @@
         <v>46279</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4047550491547036</v>
+        <v>0.4051864147864263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>21.42119502374098</v>
       </c>
       <c r="K2" t="n">
-        <v>10.15976580618585</v>
+        <v>10.27716801541496</v>
       </c>
       <c r="L2" t="n">
         <v>10</v>
@@ -740,22 +740,22 @@
         <v>11.79582706077868</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.463436782576311</v>
+        <v>1.35842194229493</v>
       </c>
       <c r="Z2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AA2" t="n">
-        <v>39.62264150943396</v>
+        <v>44.23076923076923</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.487446274259018</v>
+        <v>9.484952980269453</v>
       </c>
       <c r="AC2" t="n">
         <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>8.663345806558652</v>
+        <v>8.760583749633211</v>
       </c>
       <c r="AE2" t="n">
         <v>46</v>
@@ -789,7 +789,7 @@
         <v>46279</v>
       </c>
       <c r="C3" t="n">
-        <v>0.719016064333018</v>
+        <v>0.7091790282474195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>16.83732632822199</v>
       </c>
       <c r="K3" t="n">
-        <v>14.36870098662504</v>
+        <v>12.80399458508994</v>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M3" t="n">
-        <v>62.5</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N3" t="n">
-        <v>12.50024164736539</v>
+        <v>14.82629685373418</v>
       </c>
       <c r="O3" t="n">
         <v>10</v>
@@ -859,22 +859,22 @@
         <v>17.17248092970491</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.392865560951918</v>
+        <v>3.728252837145052</v>
       </c>
       <c r="Z3" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="AA3" t="n">
-        <v>33.33333333333334</v>
+        <v>30.95238095238095</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.29156748372895</v>
+        <v>13.14862511052788</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>7.793625417615802</v>
+        <v>6.514629003507699</v>
       </c>
       <c r="AE3" t="n">
         <v>35</v>
@@ -908,7 +908,7 @@
         <v>46279</v>
       </c>
       <c r="C4" t="n">
-        <v>1.491094566245732</v>
+        <v>1.492196674847935</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -968,22 +968,22 @@
         <v>16.66966699739723</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.290874408956903</v>
+        <v>5.220872314935631</v>
       </c>
       <c r="Z4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AA4" t="n">
-        <v>44.11764705882353</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.75331618842234</v>
+        <v>13.84876785599352</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.972198361726243</v>
+        <v>5.042384121686194</v>
       </c>
       <c r="AE4" t="n">
         <v>40</v>
@@ -1017,7 +1017,7 @@
         <v>46279</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2280860515815886</v>
+        <v>0.2280973211880946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>19.13427219952423</v>
       </c>
       <c r="K5" t="n">
-        <v>4.78046955978062</v>
+        <v>4.785646705218816</v>
       </c>
       <c r="L5" t="n">
         <v>28</v>
@@ -1087,7 +1087,7 @@
         <v>10.55954734904581</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.227117809211135</v>
+        <v>5.222435133167025</v>
       </c>
       <c r="Z5" t="n">
         <v>39</v>
@@ -1102,7 +1102,7 @@
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.036126453536038</v>
+        <v>5.040818334534847</v>
       </c>
       <c r="AE5" t="n">
         <v>45</v>
@@ -1136,7 +1136,7 @@
         <v>46279</v>
       </c>
       <c r="C6" t="n">
-        <v>1.613467154785899</v>
+        <v>1.606348078886301</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>24.35210179737853</v>
       </c>
       <c r="K6" t="n">
-        <v>1.469744425111785</v>
+        <v>1.022031058321193</v>
       </c>
       <c r="L6" t="n">
         <v>23</v>
@@ -1177,13 +1177,13 @@
         <v>82.60869565217391</v>
       </c>
       <c r="N6" t="n">
-        <v>12.42767093254801</v>
+        <v>12.17768755901921</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5225750571191901</v>
+        <v>0.9680749153758494</v>
       </c>
       <c r="Q6" t="n">
         <v>34</v>
@@ -1249,7 +1249,7 @@
         <v>46279</v>
       </c>
       <c r="C7" t="n">
-        <v>2.321994159022665</v>
+        <v>2.328279144594555</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,16 +1309,16 @@
         <v>18.9234494530097</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.145926029506709</v>
+        <v>5.891889429769559</v>
       </c>
       <c r="Z7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA7" t="n">
-        <v>40.74074074074074</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB7" t="n">
-        <v>12.98106105691283</v>
+        <v>13.61597622322071</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1358,7 +1358,7 @@
         <v>46279</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3424375796964337</v>
+        <v>0.3418374768685538</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>20.70550141590351</v>
       </c>
       <c r="K8" t="n">
-        <v>5.163079522639413</v>
+        <v>4.978787070081947</v>
       </c>
       <c r="L8" t="n">
         <v>5</v>
@@ -1401,7 +1401,7 @@
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.697639219237447</v>
+        <v>2.877927069114605</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1428,7 +1428,7 @@
         <v>28.52170855483174</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.61146339692843</v>
+        <v>16.7575971731122</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1473,7 +1473,7 @@
         <v>46279</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5466661182180905</v>
+        <v>0.5471044858624551</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>14.50739888386581</v>
       </c>
       <c r="K9" t="n">
-        <v>2.815880978497054</v>
+        <v>2.898328296971298</v>
       </c>
       <c r="L9" t="n">
         <v>41</v>
@@ -1582,7 +1582,7 @@
         <v>46279</v>
       </c>
       <c r="C10" t="n">
-        <v>1.940479618279791</v>
+        <v>1.940575438595267</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>13.50421550203786</v>
       </c>
       <c r="K10" t="n">
-        <v>5.830217129328807</v>
+        <v>5.83544299446892</v>
       </c>
       <c r="L10" t="n">
         <v>33</v>
@@ -1625,7 +1625,7 @@
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>3.940068331878743</v>
+        <v>3.934936055163241</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1691,7 +1691,7 @@
         <v>46279</v>
       </c>
       <c r="C11" t="n">
-        <v>7.655999341861708</v>
+        <v>7.661519476405531</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,10 +1716,10 @@
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>11.18322544746914</v>
+        <v>11.17883826079963</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4045853000674171</v>
+        <v>0.472016183411994</v>
       </c>
       <c r="L11" t="n">
         <v>57</v>
@@ -1734,7 +1734,7 @@
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.584956346541323</v>
+        <v>2.516107382550348</v>
       </c>
       <c r="Q11" t="n">
         <v>49</v>
@@ -1761,7 +1761,7 @@
         <v>21.29068828859215</v>
       </c>
       <c r="Y11" t="n">
-        <v>10.82388583363557</v>
+        <v>10.75958800309605</v>
       </c>
       <c r="Z11" t="n">
         <v>16</v>
@@ -1810,7 +1810,7 @@
         <v>46279</v>
       </c>
       <c r="C12" t="n">
-        <v>5.861544156965983</v>
+        <v>5.810414099555873</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,11 +1827,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>5</v>
       </c>
@@ -1839,25 +1835,25 @@
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>21.82938791514835</v>
+        <v>21.96388850532709</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8849557522123908</v>
+        <v>0.1773049645390046</v>
       </c>
       <c r="L12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M12" t="n">
-        <v>76.47058823529412</v>
+        <v>68.75</v>
       </c>
       <c r="N12" t="n">
-        <v>15.24631637135638</v>
+        <v>14.63099286473414</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>4.078947368421049</v>
+        <v>4.814159292035414</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1923,7 +1919,7 @@
         <v>46279</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1707046193081321</v>
+        <v>0.1688619468664435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,11 +1936,7 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>5</v>
       </c>
@@ -1955,7 +1947,7 @@
         <v>47.07727092024744</v>
       </c>
       <c r="K13" t="n">
-        <v>5.704070462450606</v>
+        <v>4.563046989243436</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
@@ -1966,7 +1958,7 @@
         <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2799603991168187</v>
+        <v>1.374245540974339</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1991,17 +1983,13 @@
         <v>20.61663781635479</v>
       </c>
       <c r="Y13" t="n">
-        <v>12.36360723021427</v>
+        <v>13.30959900536591</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>11.69944783412234</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
         <v>10</v>
       </c>
@@ -2030,7 +2018,7 @@
         <v>46279</v>
       </c>
       <c r="C14" t="n">
-        <v>8.843733289457447</v>
+        <v>8.83902817445712</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2090,7 +2078,7 @@
         <v>16.11612055393703</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.774729872074376</v>
+        <v>1.826988480148983</v>
       </c>
       <c r="Z14" t="n">
         <v>38</v>
@@ -2099,13 +2087,13 @@
         <v>50</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.34793740359749</v>
+        <v>11.58856214112849</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.2293402987156412</v>
+        <v>0.1762312443843395</v>
       </c>
       <c r="AE14" t="n">
         <v>38</v>
@@ -2139,7 +2127,7 @@
         <v>46279</v>
       </c>
       <c r="C15" t="n">
-        <v>14.03685574431327</v>
+        <v>14.03754910777658</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2152,7 @@
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>11.59417678351645</v>
+        <v>11.58980989616802</v>
       </c>
       <c r="K15" t="n">
         <v>0.4415011037527616</v>
@@ -2209,7 +2197,7 @@
         <v>41.12870069280461</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.20386409823397</v>
+        <v>11.1994779310297</v>
       </c>
       <c r="Z15" t="n">
         <v>5</v>
@@ -2258,7 +2246,7 @@
         <v>46279</v>
       </c>
       <c r="C16" t="n">
-        <v>34.86076261774505</v>
+        <v>34.73907757221193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2286,22 +2274,22 @@
         <v>16.99349200873118</v>
       </c>
       <c r="K16" t="n">
-        <v>3.778748134064647</v>
+        <v>3.416497834765786</v>
       </c>
       <c r="L16" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M16" t="n">
-        <v>67.24137931034483</v>
+        <v>68.85245901639344</v>
       </c>
       <c r="N16" t="n">
-        <v>16.59883356053895</v>
+        <v>16.44345666370971</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>5.994726259270888</v>
+        <v>6.366007651654426</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2367,7 +2355,7 @@
         <v>46279</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3928262926247378</v>
+        <v>0.3928457044583169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,10 +2380,10 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>50.11220949399377</v>
+        <v>50.10974524047206</v>
       </c>
       <c r="K17" t="n">
-        <v>1.058203090059107</v>
+        <v>1.058205100641163</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2406,7 +2394,7 @@
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>6.869107798952889</v>
+        <v>6.869105672761244</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2472,7 +2460,7 @@
         <v>46279</v>
       </c>
       <c r="C18" t="n">
-        <v>0.07712558101271029</v>
+        <v>0.07651235619348767</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2500,7 +2488,7 @@
         <v>31.38464440531301</v>
       </c>
       <c r="K18" t="n">
-        <v>3.181888833375313</v>
+        <v>2.361490538852684</v>
       </c>
       <c r="L18" t="n">
         <v>10</v>
@@ -2509,13 +2497,13 @@
         <v>40</v>
       </c>
       <c r="N18" t="n">
-        <v>16.11227766267315</v>
+        <v>15.12169699331323</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>6.607856517954436</v>
+        <v>7.462288230599801</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2542,22 +2530,22 @@
         <v>11.24971294890111</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.251995444906456</v>
+        <v>7.989434016904795</v>
       </c>
       <c r="Z18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA18" t="n">
-        <v>45.45454545454545</v>
+        <v>52.38095238095238</v>
       </c>
       <c r="AB18" t="n">
-        <v>13.23592115851729</v>
+        <v>12.65459099545795</v>
       </c>
       <c r="AC18" t="n">
         <v>8</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.8064912648866884</v>
+        <v>0.01148344538728363</v>
       </c>
       <c r="AE18" t="n">
         <v>36</v>
@@ -2591,7 +2579,7 @@
         <v>46279</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02735387273250792</v>
+        <v>0.0271495465555202</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,22 +2607,22 @@
         <v>10.11859020594628</v>
       </c>
       <c r="K19" t="n">
-        <v>2.679164400946732</v>
+        <v>1.912178266167874</v>
       </c>
       <c r="L19" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="M19" t="n">
-        <v>42.85714285714285</v>
+        <v>50</v>
       </c>
       <c r="N19" t="n">
-        <v>16.51958978675003</v>
+        <v>20.25961926302971</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>7.129816104138231</v>
+        <v>7.936069929453238</v>
       </c>
       <c r="Q19" t="n">
         <v>14</v>
@@ -2661,22 +2649,22 @@
         <v>20.26411217973316</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.710519471674937</v>
+        <v>8.399897422539105</v>
       </c>
       <c r="Z19" t="n">
         <v>13</v>
       </c>
       <c r="AA19" t="n">
-        <v>46.15384615384615</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="AB19" t="n">
-        <v>12.39536789924539</v>
+        <v>12.91319905850556</v>
       </c>
       <c r="AC19" t="n">
         <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.480760012103855</v>
+        <v>1.746834918779461</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -2710,7 +2698,7 @@
         <v>46279</v>
       </c>
       <c r="C20" t="n">
-        <v>1.654600797992678</v>
+        <v>1.658796127501291</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,7 +2726,7 @@
         <v>18.49305897009618</v>
       </c>
       <c r="K20" t="n">
-        <v>6.156064155215191</v>
+        <v>6.42522857784138</v>
       </c>
       <c r="L20" t="n">
         <v>26</v>
@@ -2747,13 +2735,13 @@
         <v>61.53846153846154</v>
       </c>
       <c r="N20" t="n">
-        <v>10.46843494182912</v>
+        <v>10.71505126365717</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>3.621023325774808</v>
+        <v>3.35895113398228</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
@@ -2819,7 +2807,7 @@
         <v>46279</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9218049442639135</v>
+        <v>0.9222618375067166</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2918,7 +2906,7 @@
         <v>46279</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2934885442803669</v>
+        <v>0.2916519424174536</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2943,25 +2931,25 @@
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>20.29393476258275</v>
+        <v>20.51421528613189</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3516174402250272</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M22" t="n">
-        <v>70</v>
+        <v>72.22222222222223</v>
       </c>
       <c r="N22" t="n">
-        <v>14.82049516308756</v>
+        <v>14.69752885316862</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>9.614576033637023</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -3019,7 +3007,7 @@
         <v>46279</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6034305458434454</v>
+        <v>0.6059284744330443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3044,10 +3032,10 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>40.79566405884426</v>
+        <v>40.79274007167037</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3419972640218871</v>
+        <v>0.7523916269852826</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -3058,7 +3046,7 @@
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.642126789366063</v>
+        <v>4.215888381826804</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3124,7 +3112,7 @@
         <v>46279</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1624778906667764</v>
+        <v>0.1604291365681929</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3152,22 +3140,22 @@
         <v>23.31817459365587</v>
       </c>
       <c r="K24" t="n">
-        <v>7.430160013368003</v>
+        <v>6.075526593795466</v>
       </c>
       <c r="L24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M24" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N24" t="n">
-        <v>13.50219384884019</v>
+        <v>12.2081847296207</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>2.392102912545435</v>
+        <v>3.699697312116945</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3194,16 +3182,16 @@
         <v>17.82705440547527</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.823860058767741</v>
+        <v>9.973539499035233</v>
       </c>
       <c r="Z24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA24" t="n">
-        <v>27.27272727272727</v>
+        <v>30</v>
       </c>
       <c r="AB24" t="n">
-        <v>16.83939367695796</v>
+        <v>16.40635689394259</v>
       </c>
       <c r="AC24" t="n">
         <v>2</v>
@@ -3243,7 +3231,7 @@
         <v>46279</v>
       </c>
       <c r="C25" t="n">
-        <v>3.350335239192135</v>
+        <v>3.356671020622143</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,22 +3259,22 @@
         <v>20.95143919294578</v>
       </c>
       <c r="K25" t="n">
-        <v>1.983908316724237</v>
+        <v>2.176768943002494</v>
       </c>
       <c r="L25" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="M25" t="n">
-        <v>53.84615384615385</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N25" t="n">
-        <v>18.6072341317862</v>
+        <v>19.74294086415057</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>5.899059746359225</v>
+        <v>5.699173224244247</v>
       </c>
       <c r="Q25" t="n">
         <v>44</v>
@@ -3352,7 +3340,7 @@
         <v>46279</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4471227016576858</v>
+        <v>0.4471447829661926</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3412,7 +3400,7 @@
         <v>11.40992936035117</v>
       </c>
       <c r="Y26" t="n">
-        <v>6.127513193952105</v>
+        <v>6.122877268883253</v>
       </c>
       <c r="Z26" t="n">
         <v>34</v>
@@ -3427,7 +3415,7 @@
         <v>10</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.125262830257093</v>
+        <v>4.129997403330754</v>
       </c>
       <c r="AE26" t="n">
         <v>36</v>
@@ -3461,7 +3449,7 @@
         <v>46279</v>
       </c>
       <c r="C27" t="n">
-        <v>52.54822919665995</v>
+        <v>53.57921674103734</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,25 +3496,23 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>60.35073545432527</v>
+        <v>62.54252887592284</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.5836575875486361</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AA27" t="n">
-        <v>14.28571428571429</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>9.659661880762883</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
         <v>6</v>
       </c>
       <c r="AD27" t="n">
-        <v>5.448140900195697</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3550,7 +3536,7 @@
         <v>46279</v>
       </c>
       <c r="C28" t="n">
-        <v>1.440705853317428</v>
+        <v>1.428436253070415</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3575,25 +3561,25 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>14.27194368631205</v>
+        <v>14.7586636560711</v>
       </c>
       <c r="K28" t="n">
-        <v>0.286327845382961</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M28" t="n">
-        <v>58.92857142857143</v>
+        <v>58</v>
       </c>
       <c r="N28" t="n">
-        <v>13.71737698329092</v>
+        <v>13.24016720455243</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>1.708779443254826</v>
+        <v>2.000000000000002</v>
       </c>
       <c r="Q28" t="n">
         <v>39</v>
@@ -3620,17 +3606,13 @@
         <v>19.25959158767157</v>
       </c>
       <c r="Y28" t="n">
-        <v>14.02648038978038</v>
+        <v>14.7586636560711</v>
       </c>
       <c r="Z28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>12.1022945001129</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
         <v>6</v>
       </c>
@@ -3669,7 +3651,7 @@
         <v>46279</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4179178149808729</v>
+        <v>0.4175270860356442</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3697,7 +3679,7 @@
         <v>27.65210909859499</v>
       </c>
       <c r="K29" t="n">
-        <v>26.20046810702974</v>
+        <v>26.08247798068617</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3732,10 +3714,10 @@
         <v>80</v>
       </c>
       <c r="X29" t="n">
-        <v>31.16899569039671</v>
+        <v>31.1754749041741</v>
       </c>
       <c r="Y29" t="n">
-        <v>3.787882614497085</v>
+        <v>3.882583178912413</v>
       </c>
       <c r="Z29" t="n">
         <v>9</v>
@@ -3750,7 +3732,7 @@
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>6.456689192913389</v>
+        <v>6.364524790001913</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3784,7 +3766,7 @@
         <v>46279</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4236765250298219</v>
+        <v>0.4232860945275282</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3844,7 +3826,7 @@
         <v>26.71344279693404</v>
       </c>
       <c r="Y30" t="n">
-        <v>8.662462622302758</v>
+        <v>8.746632875998406</v>
       </c>
       <c r="Z30" t="n">
         <v>14</v>
@@ -3853,13 +3835,13 @@
         <v>64.28571428571429</v>
       </c>
       <c r="AB30" t="n">
-        <v>15.54106172116325</v>
+        <v>15.51985827645638</v>
       </c>
       <c r="AC30" t="n">
         <v>10</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.46438957749242</v>
+        <v>1.373502330383525</v>
       </c>
       <c r="AE30" t="n">
         <v>46</v>
@@ -3893,7 +3875,7 @@
         <v>46279</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2542059150178931</v>
+        <v>0.2550411774390636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3950,10 +3932,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="X31" t="n">
-        <v>46.69474141390997</v>
+        <v>46.70198753624732</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.4830924284502824</v>
+        <v>0.1610342984796564</v>
       </c>
       <c r="Z31" t="n">
         <v>3</v>
@@ -3968,7 +3950,7 @@
         <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>9.563106213592242</v>
+        <v>9.854835366519143</v>
       </c>
       <c r="AE31" t="n">
         <v>10</v>
@@ -4002,7 +3984,7 @@
         <v>46279</v>
       </c>
       <c r="C32" t="n">
-        <v>2.35078770926741</v>
+        <v>2.350903891330971</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4062,22 +4044,22 @@
         <v>13.38656892008534</v>
       </c>
       <c r="Y32" t="n">
-        <v>4.870203454653177</v>
+        <v>4.865501891842894</v>
       </c>
       <c r="Z32" t="n">
         <v>39</v>
       </c>
       <c r="AA32" t="n">
-        <v>28.2051282051282</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="AB32" t="n">
-        <v>10.21846166513093</v>
+        <v>9.795855975533653</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.29002758232001</v>
+        <v>3.29480700533421</v>
       </c>
       <c r="AE32" t="n">
         <v>26</v>
@@ -4111,7 +4093,7 @@
         <v>46279</v>
       </c>
       <c r="C33" t="n">
-        <v>1.831475463781827</v>
+        <v>1.836707953317177</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4171,22 +4153,22 @@
         <v>15.09663082780621</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.896634834092071</v>
+        <v>2.619212421329487</v>
       </c>
       <c r="Z33" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AA33" t="n">
-        <v>36.95652173913044</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB33" t="n">
-        <v>11.50750222125849</v>
+        <v>12.37741275254759</v>
       </c>
       <c r="AC33" t="n">
         <v>8</v>
       </c>
       <c r="AD33" t="n">
-        <v>5.255600727316157</v>
+        <v>5.525512488100959</v>
       </c>
       <c r="AE33" t="n">
         <v>29</v>
@@ -4220,7 +4202,7 @@
         <v>46279</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7979926782115091</v>
+        <v>0.7992661785950224</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4248,7 +4230,7 @@
         <v>15.41713612942789</v>
       </c>
       <c r="K34" t="n">
-        <v>6.15565499033599</v>
+        <v>6.32506665416892</v>
       </c>
       <c r="L34" t="n">
         <v>32</v>
@@ -4257,7 +4239,7 @@
         <v>59.375</v>
       </c>
       <c r="N34" t="n">
-        <v>13.41939859320348</v>
+        <v>13.2905720570966</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4290,13 +4272,13 @@
         <v>10.81830054752258</v>
       </c>
       <c r="Y34" t="n">
-        <v>4.207468923589097</v>
+        <v>4.054595559716978</v>
       </c>
       <c r="Z34" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA34" t="n">
-        <v>36.36363636363637</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AB34" t="n">
         <v>9.769890717174794</v>
@@ -4339,7 +4321,7 @@
         <v>46279</v>
       </c>
       <c r="C35" t="n">
-        <v>1.488009543005224</v>
+        <v>1.480884301479727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4367,7 +4349,7 @@
         <v>38.83766461406507</v>
       </c>
       <c r="K35" t="n">
-        <v>7.391741296153254</v>
+        <v>6.877502595080576</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
@@ -4405,16 +4387,16 @@
         <v>13.94161507705984</v>
       </c>
       <c r="Y35" t="n">
-        <v>5.748447374979582</v>
+        <v>6.199765096538035</v>
       </c>
       <c r="Z35" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA35" t="n">
-        <v>38.88888888888889</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB35" t="n">
-        <v>13.30735100238293</v>
+        <v>11.96300134878404</v>
       </c>
       <c r="AC35" t="n">
         <v>2</v>
@@ -4454,16 +4436,16 @@
         <v>46279</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07877092674098145</v>
+        <v>0.07836345971923196</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4482,22 +4464,22 @@
         <v>11.49958181785439</v>
       </c>
       <c r="K36" t="n">
-        <v>2.001823074767728</v>
+        <v>1.474187044815189</v>
       </c>
       <c r="L36" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="M36" t="n">
-        <v>63.33333333333334</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N36" t="n">
-        <v>18.68547865450064</v>
+        <v>17.10540519030475</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>0.5181740997369122</v>
       </c>
       <c r="Q36" t="n">
         <v>10</v>
@@ -4563,7 +4545,7 @@
         <v>46279</v>
       </c>
       <c r="C37" t="n">
-        <v>0.05984945086586319</v>
+        <v>0.05944105249117834</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4588,25 +4570,25 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>19.28691969192409</v>
+        <v>19.28293279472178</v>
       </c>
       <c r="K37" t="n">
-        <v>1.393732109167445</v>
+        <v>0.6968714552807898</v>
       </c>
       <c r="L37" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M37" t="n">
-        <v>63.33333333333334</v>
+        <v>60.3448275862069</v>
       </c>
       <c r="N37" t="n">
-        <v>17.34497026082843</v>
+        <v>17.50894189590544</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>8.487968350515462</v>
+        <v>9.238746358520888</v>
       </c>
       <c r="Q37" t="n">
         <v>30</v>
@@ -4672,7 +4654,7 @@
         <v>46279</v>
       </c>
       <c r="C38" t="n">
-        <v>1.681337666077084</v>
+        <v>1.681420717305107</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4732,7 +4714,7 @@
         <v>12.11239445105858</v>
       </c>
       <c r="Y38" t="n">
-        <v>3.968370492493256</v>
+        <v>3.963626921394792</v>
       </c>
       <c r="Z38" t="n">
         <v>49</v>
@@ -4747,7 +4729,7 @@
         <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>6.280878017419511</v>
+        <v>6.285507131412038</v>
       </c>
       <c r="AE38" t="n">
         <v>30</v>
@@ -4781,7 +4763,7 @@
         <v>46279</v>
       </c>
       <c r="C39" t="n">
-        <v>2.749784048373164</v>
+        <v>2.754033318538072</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4841,22 +4823,22 @@
         <v>10.27889366548247</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.646009539292916</v>
+        <v>3.49711270603914</v>
       </c>
       <c r="Z39" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AA39" t="n">
-        <v>40.54054054054054</v>
+        <v>39.47368421052632</v>
       </c>
       <c r="AB39" t="n">
-        <v>13.8319937724761</v>
+        <v>13.64670841558058</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.443064837742281</v>
+        <v>2.593587989068902</v>
       </c>
       <c r="AE39" t="n">
         <v>40</v>
@@ -4890,7 +4872,7 @@
         <v>46279</v>
       </c>
       <c r="C40" t="n">
-        <v>0.242894163136029</v>
+        <v>0.2406436950825665</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4918,16 +4900,16 @@
         <v>15.29580504962521</v>
       </c>
       <c r="K40" t="n">
-        <v>8.819055007058285</v>
+        <v>7.8108224347333</v>
       </c>
       <c r="L40" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M40" t="n">
-        <v>66.66666666666667</v>
+        <v>73.68421052631579</v>
       </c>
       <c r="N40" t="n">
-        <v>12.70962245278844</v>
+        <v>13.44349228041417</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4960,7 +4942,7 @@
         <v>37.29449902814472</v>
       </c>
       <c r="Y40" t="n">
-        <v>7.825695503665775</v>
+        <v>8.679710787281103</v>
       </c>
       <c r="Z40" t="n">
         <v>5</v>
@@ -5009,7 +4991,7 @@
         <v>46279</v>
       </c>
       <c r="C41" t="n">
-        <v>1.265887869688618</v>
+        <v>1.256694841036921</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5037,22 +5019,22 @@
         <v>40.38073481248902</v>
       </c>
       <c r="K41" t="n">
-        <v>5.142885094407901</v>
+        <v>4.379324925818295</v>
       </c>
       <c r="L41" t="n">
         <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>33.33333333333334</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N41" t="n">
-        <v>32.97150766357895</v>
+        <v>20.46121479619964</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>4.619537404961727</v>
+        <v>5.384854786305904</v>
       </c>
       <c r="Q41" t="n">
         <v>11</v>
@@ -5079,16 +5061,16 @@
         <v>14.15095011586145</v>
       </c>
       <c r="Y41" t="n">
-        <v>7.891362281532044</v>
+        <v>8.560266191499155</v>
       </c>
       <c r="Z41" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA41" t="n">
-        <v>37.93103448275862</v>
+        <v>44</v>
       </c>
       <c r="AB41" t="n">
-        <v>13.45788424469266</v>
+        <v>14.44518067703431</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
@@ -5128,7 +5110,7 @@
         <v>46279</v>
       </c>
       <c r="C42" t="n">
-        <v>3.514869812019251</v>
+        <v>3.512986711242145</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5156,7 +5138,7 @@
         <v>17.9384880883827</v>
       </c>
       <c r="K42" t="n">
-        <v>10.75133430298045</v>
+        <v>10.69199898336826</v>
       </c>
       <c r="L42" t="n">
         <v>5</v>
@@ -5196,7 +5178,7 @@
         <v>23.7260422361657</v>
       </c>
       <c r="Y42" t="n">
-        <v>9.115780608684599</v>
+        <v>9.16447206905595</v>
       </c>
       <c r="Z42" t="n">
         <v>2</v>
@@ -5207,7 +5189,7 @@
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.9729075049962899</v>
+        <v>0.9198250398007701</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5239,7 +5221,7 @@
         <v>46279</v>
       </c>
       <c r="C43" t="n">
-        <v>6.077495783801571</v>
+        <v>6.067512068562769</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5271,7 +5253,7 @@
         <v>20.13868121382601</v>
       </c>
       <c r="K43" t="n">
-        <v>1.446165796952603</v>
+        <v>1.279516626403687</v>
       </c>
       <c r="L43" t="n">
         <v>18</v>
@@ -5286,7 +5268,7 @@
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.51742802005841</v>
+        <v>2.686114097119496</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5352,7 +5334,7 @@
         <v>46279</v>
       </c>
       <c r="C44" t="n">
-        <v>4.820862983834479</v>
+        <v>4.827271403341594</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5380,7 +5362,7 @@
         <v>25.31049029846984</v>
       </c>
       <c r="K44" t="n">
-        <v>25.52361162374837</v>
+        <v>25.69047136733174</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5415,25 +5397,25 @@
         <v>50</v>
       </c>
       <c r="X44" t="n">
-        <v>28.14761203738472</v>
+        <v>28.15394364051107</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.047638946928532</v>
+        <v>1.922275821717745</v>
       </c>
       <c r="Z44" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA44" t="n">
-        <v>58.33333333333334</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AB44" t="n">
-        <v>13.79357295589038</v>
+        <v>14.80772746396136</v>
       </c>
       <c r="AC44" t="n">
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>8.118600682593868</v>
+        <v>8.236043654111358</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5459,7 +5441,7 @@
         <v>46279</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02077248981942331</v>
+        <v>0.02077351569007891</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5487,7 +5469,7 @@
         <v>15.15550562104173</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7201963693389768</v>
+        <v>0.7251705392521623</v>
       </c>
       <c r="L45" t="n">
         <v>74</v>
@@ -5496,13 +5478,13 @@
         <v>64.86486486486487</v>
       </c>
       <c r="N45" t="n">
-        <v>13.76299784511018</v>
+        <v>13.77033218132339</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>9.213448707578141</v>
+        <v>9.208055356067613</v>
       </c>
       <c r="Q45" t="n">
         <v>38</v>
@@ -5529,7 +5511,7 @@
         <v>20.3749963300697</v>
       </c>
       <c r="Y45" t="n">
-        <v>14.54445865294046</v>
+        <v>14.54023834362808</v>
       </c>
       <c r="Z45" t="n">
         <v>7</v>
@@ -5578,7 +5560,7 @@
         <v>46279</v>
       </c>
       <c r="C46" t="n">
-        <v>9.882357780428613</v>
+        <v>9.846852212964155</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5638,16 +5620,16 @@
         <v>27.45411700532656</v>
       </c>
       <c r="Y46" t="n">
-        <v>8.816583253163168</v>
+        <v>9.14418917746559</v>
       </c>
       <c r="Z46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA46" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AB46" t="n">
-        <v>15.10080616517297</v>
+        <v>17.001466400711</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
@@ -5687,7 +5669,7 @@
         <v>46279</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9686972975196414</v>
+        <v>0.9683338281067196</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5712,10 +5694,10 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>14.28021701350416</v>
+        <v>14.27598504123684</v>
       </c>
       <c r="K47" t="n">
-        <v>0.6840530141085877</v>
+        <v>0.6413062373320733</v>
       </c>
       <c r="L47" t="n">
         <v>65</v>
@@ -5730,7 +5712,7 @@
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>9.252653927813181</v>
+        <v>9.299058321638132</v>
       </c>
       <c r="Q47" t="n">
         <v>51</v>
@@ -5757,7 +5739,7 @@
         <v>66.65983471422588</v>
       </c>
       <c r="Y47" t="n">
-        <v>13.69384825429769</v>
+        <v>13.72623158641482</v>
       </c>
       <c r="Z47" t="n">
         <v>1</v>
@@ -5802,7 +5784,7 @@
         <v>46279</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05840977335362593</v>
+        <v>0.05841265670726162</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5827,10 +5809,10 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>10.39152411668899</v>
+        <v>10.38709782320051</v>
       </c>
       <c r="K48" t="n">
-        <v>2.898551097458513</v>
+        <v>2.898547836588961</v>
       </c>
       <c r="L48" t="n">
         <v>56</v>
@@ -5845,7 +5827,7 @@
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>6.901408063380288</v>
+        <v>6.901411451101058</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5872,7 +5854,7 @@
         <v>19.37342145735985</v>
       </c>
       <c r="Y48" t="n">
-        <v>7.794176655557417</v>
+        <v>7.789624985850308</v>
       </c>
       <c r="Z48" t="n">
         <v>18</v>
@@ -5921,7 +5903,7 @@
         <v>46279</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2846448109909094</v>
+        <v>0.284658874369612</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5981,7 +5963,7 @@
         <v>22.46912765663718</v>
       </c>
       <c r="Y49" t="n">
-        <v>6.476135173350428</v>
+        <v>6.471514461930439</v>
       </c>
       <c r="Z49" t="n">
         <v>20</v>
@@ -5996,7 +5978,7 @@
         <v>10</v>
       </c>
       <c r="AD49" t="n">
-        <v>3.767877678260201</v>
+        <v>3.772631961022543</v>
       </c>
       <c r="AE49" t="n">
         <v>45</v>
@@ -6030,7 +6012,7 @@
         <v>46279</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7218954382789684</v>
+        <v>0.7190515807960791</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6090,16 +6072,16 @@
         <v>15.51990994893744</v>
       </c>
       <c r="Y50" t="n">
-        <v>6.406393462223314</v>
+        <v>6.77509904503959</v>
       </c>
       <c r="Z50" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA50" t="n">
-        <v>53.33333333333334</v>
+        <v>48.27586206896552</v>
       </c>
       <c r="AB50" t="n">
-        <v>11.75200790891181</v>
+        <v>12.49614700114313</v>
       </c>
       <c r="AC50" t="n">
         <v>5</v>
@@ -6139,7 +6121,7 @@
         <v>46279</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1412940644152853</v>
+        <v>0.1398612990476411</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6167,7 +6149,7 @@
         <v>31.62908307640215</v>
       </c>
       <c r="K51" t="n">
-        <v>6.090818140274878</v>
+        <v>5.015024541403945</v>
       </c>
       <c r="L51" t="n">
         <v>6</v>
@@ -6176,7 +6158,7 @@
         <v>50</v>
       </c>
       <c r="N51" t="n">
-        <v>20.64820354085114</v>
+        <v>21.39549877456197</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
@@ -6209,22 +6191,22 @@
         <v>15.73461610040814</v>
       </c>
       <c r="Y51" t="n">
-        <v>8.332682377212496</v>
+        <v>9.262217234733095</v>
       </c>
       <c r="Z51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA51" t="n">
-        <v>36.36363636363637</v>
+        <v>40</v>
       </c>
       <c r="AB51" t="n">
-        <v>12.13109930543536</v>
+        <v>11.6363761696779</v>
       </c>
       <c r="AC51" t="n">
         <v>10</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.818879035654275</v>
+        <v>0.8130932261982915</v>
       </c>
       <c r="AE51" t="n">
         <v>12</v>
@@ -6258,7 +6240,7 @@
         <v>46279</v>
       </c>
       <c r="C52" t="n">
-        <v>4.629591542922957</v>
+        <v>4.638047360884422</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6318,22 +6300,22 @@
         <v>17.68393155583896</v>
       </c>
       <c r="Y52" t="n">
-        <v>3.499200045353168</v>
+        <v>3.322944064671751</v>
       </c>
       <c r="Z52" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA52" t="n">
-        <v>48.48484848484848</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="AB52" t="n">
-        <v>11.26514743419562</v>
+        <v>10.21277776758257</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>4.664002740663397</v>
+        <v>4.837813781231548</v>
       </c>
       <c r="AE52" t="n">
         <v>37</v>
@@ -6367,7 +6349,7 @@
         <v>46279</v>
       </c>
       <c r="C53" t="n">
-        <v>1.202130722718111</v>
+        <v>1.203218494952278</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6392,10 +6374,10 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>30.11351257643013</v>
+        <v>30.11005863776933</v>
       </c>
       <c r="K53" t="n">
-        <v>0.08561643835618415</v>
+        <v>0.1712302523633191</v>
       </c>
       <c r="L53" t="n">
         <v>9</v>
@@ -6410,7 +6392,7 @@
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>7.907613344739084</v>
+        <v>7.81538744000001</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6468,7 +6450,7 @@
         <v>46279</v>
       </c>
       <c r="C54" t="n">
-        <v>0.07198387561186294</v>
+        <v>0.07157607498287688</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6485,7 +6467,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H54" t="n">
         <v>5</v>
       </c>
@@ -6496,16 +6482,16 @@
         <v>29.5817777621179</v>
       </c>
       <c r="K54" t="n">
-        <v>14.6835282875196</v>
+        <v>14.03382702355649</v>
       </c>
       <c r="L54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M54" t="n">
-        <v>71.42857142857143</v>
+        <v>75</v>
       </c>
       <c r="N54" t="n">
-        <v>26.80962063787916</v>
+        <v>26.58918607430863</v>
       </c>
       <c r="O54" t="n">
         <v>10</v>
@@ -6538,22 +6524,22 @@
         <v>14.75410024187049</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.06149841635474385</v>
+        <v>0.6276666513840068</v>
       </c>
       <c r="Z54" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AA54" t="n">
-        <v>44.44444444444444</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="AB54" t="n">
-        <v>15.4251043447565</v>
+        <v>15.05166065777288</v>
       </c>
       <c r="AC54" t="n">
         <v>2</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.939694465023367</v>
+        <v>1.381001434072804</v>
       </c>
       <c r="AE54" t="n">
         <v>7</v>
@@ -6587,7 +6573,7 @@
         <v>46279</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9312656822014727</v>
+        <v>0.9358366071851051</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6647,16 +6633,16 @@
         <v>23.0932342837701</v>
       </c>
       <c r="Y55" t="n">
-        <v>6.829018249411889</v>
+        <v>6.371707756420708</v>
       </c>
       <c r="Z55" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA55" t="n">
-        <v>40</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="AB55" t="n">
-        <v>9.365455206540789</v>
+        <v>14.28198200849551</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6696,7 +6682,7 @@
         <v>46279</v>
       </c>
       <c r="C56" t="n">
-        <v>0.6968039159228333</v>
+        <v>0.6968383572038798</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6724,7 +6710,7 @@
         <v>55.30631598314248</v>
       </c>
       <c r="K56" t="n">
-        <v>8.443413034330005</v>
+        <v>8.448773121982489</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6754,7 +6740,7 @@
         <v>44.70154625822338</v>
       </c>
       <c r="Y56" t="n">
-        <v>25.05718436428445</v>
+        <v>25.05348012767391</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -6791,7 +6777,7 @@
         <v>46279</v>
       </c>
       <c r="C57" t="n">
-        <v>1.494179589486241</v>
+        <v>1.495281725012209</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6851,7 +6837,7 @@
         <v>20.62560129901716</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.884700810110418</v>
+        <v>1.812329083419051</v>
       </c>
       <c r="Z57" t="n">
         <v>60</v>
@@ -6866,7 +6852,7 @@
         <v>5</v>
       </c>
       <c r="AD57" t="n">
-        <v>3.175141099921963</v>
+        <v>3.246508331264075</v>
       </c>
       <c r="AE57" t="n">
         <v>44</v>
@@ -6900,7 +6886,7 @@
         <v>46279</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7214841018469006</v>
+        <v>0.722753797925808</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6917,11 +6903,7 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6932,13 +6914,13 @@
         <v>18.04392839464337</v>
       </c>
       <c r="K58" t="n">
-        <v>10.58610214201814</v>
+        <v>10.78071591093133</v>
       </c>
       <c r="L58" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M58" t="n">
-        <v>78.57142857142857</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N58" t="n">
         <v>21.94783451677582</v>
@@ -6974,7 +6956,7 @@
         <v>20.50322102897642</v>
       </c>
       <c r="Y58" t="n">
-        <v>8.22975419434937</v>
+        <v>8.068253308936201</v>
       </c>
       <c r="Z58" t="n">
         <v>16</v>
@@ -6983,7 +6965,7 @@
         <v>43.75</v>
       </c>
       <c r="AB58" t="n">
-        <v>8.538618238015498</v>
+        <v>8.807341170160358</v>
       </c>
       <c r="AC58" t="n">
         <v>6</v>
@@ -7023,7 +7005,7 @@
         <v>46279</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7708444736950351</v>
+        <v>0.7717052732323073</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7051,22 +7033,22 @@
         <v>11.95882015364728</v>
       </c>
       <c r="K59" t="n">
-        <v>5.225696610331543</v>
+        <v>5.343201806311138</v>
       </c>
       <c r="L59" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M59" t="n">
-        <v>71.42857142857143</v>
+        <v>73.17073170731707</v>
       </c>
       <c r="N59" t="n">
-        <v>13.01293594074701</v>
+        <v>12.12870417056454</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>2.636526513045734</v>
+        <v>2.522040481144461</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7132,7 +7114,7 @@
         <v>46279</v>
       </c>
       <c r="C60" t="n">
-        <v>11.11636707663198</v>
+        <v>11.07578050481712</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7160,7 +7142,7 @@
         <v>24.49246832941995</v>
       </c>
       <c r="K60" t="n">
-        <v>4.638398121459697</v>
+        <v>4.256356593803101</v>
       </c>
       <c r="L60" t="n">
         <v>15</v>
@@ -7169,13 +7151,13 @@
         <v>73.33333333333333</v>
       </c>
       <c r="N60" t="n">
-        <v>12.32924210467809</v>
+        <v>12.49400271589765</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>3.212589201373572</v>
+        <v>3.590805902399463</v>
       </c>
       <c r="Q60" t="n">
         <v>46</v>
@@ -7241,7 +7223,7 @@
         <v>46279</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7914112952984245</v>
+        <v>0.7922731107528591</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7269,7 +7251,7 @@
         <v>14.0586191907223</v>
       </c>
       <c r="K61" t="n">
-        <v>10.8504242239752</v>
+        <v>10.97113593139507</v>
       </c>
       <c r="L61" t="n">
         <v>18</v>
@@ -7311,7 +7293,7 @@
         <v>49.99145178651283</v>
       </c>
       <c r="Y61" t="n">
-        <v>4.733614788973661</v>
+        <v>4.629873480818558</v>
       </c>
       <c r="Z61" t="n">
         <v>4</v>
@@ -7360,7 +7342,7 @@
         <v>46279</v>
       </c>
       <c r="C62" t="n">
-        <v>9.054543210892188</v>
+        <v>9.018996752761947</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7420,22 +7402,22 @@
         <v>11.69351808836483</v>
       </c>
       <c r="Y62" t="n">
-        <v>3.111504239925866</v>
+        <v>3.491870513256423</v>
       </c>
       <c r="Z62" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA62" t="n">
-        <v>45.28301886792453</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB62" t="n">
-        <v>15.41942847330274</v>
+        <v>14.74641715838048</v>
       </c>
       <c r="AC62" t="n">
         <v>5</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.949143440879331</v>
+        <v>1.562696836799371</v>
       </c>
       <c r="AE62" t="n">
         <v>27</v>
@@ -7469,7 +7451,7 @@
         <v>46279</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1116778413064045</v>
+        <v>0.1112719979010094</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7497,7 +7479,7 @@
         <v>14.68172212919103</v>
       </c>
       <c r="K63" t="n">
-        <v>6.67744833160866</v>
+        <v>6.289776628759602</v>
       </c>
       <c r="L63" t="n">
         <v>10</v>
@@ -7506,7 +7488,7 @@
         <v>70</v>
       </c>
       <c r="N63" t="n">
-        <v>14.93116161136219</v>
+        <v>13.72369998618861</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
@@ -7539,7 +7521,7 @@
         <v>24.85614965143601</v>
       </c>
       <c r="Y63" t="n">
-        <v>8.984638206949459</v>
+        <v>9.315393027612707</v>
       </c>
       <c r="Z63" t="n">
         <v>3</v>
@@ -7554,7 +7536,7 @@
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.115593865746811</v>
+        <v>0.7549318404122873</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7588,7 +7570,7 @@
         <v>46279</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1489037884085394</v>
+        <v>0.1482941093458917</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7613,25 +7595,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>10.25688449628873</v>
+        <v>10.62485037725133</v>
       </c>
       <c r="K64" t="n">
-        <v>0.138312586445366</v>
+        <v>0.1388920869985544</v>
       </c>
       <c r="L64" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M64" t="n">
-        <v>56.52173913043478</v>
+        <v>56.94444444444444</v>
       </c>
       <c r="N64" t="n">
-        <v>15.5775382363878</v>
+        <v>15.34087839849153</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.854972375690614</v>
+        <v>4.85436558333221</v>
       </c>
       <c r="Q64" t="n">
         <v>55</v>
@@ -7658,16 +7640,16 @@
         <v>14.28923074155179</v>
       </c>
       <c r="Y64" t="n">
-        <v>10.13275847207891</v>
+        <v>10.50071536668221</v>
       </c>
       <c r="Z64" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AA64" t="n">
-        <v>56.25</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB64" t="n">
-        <v>16.12578144354295</v>
+        <v>16.21570005940892</v>
       </c>
       <c r="AC64" t="n">
         <v>2</v>
@@ -7707,7 +7689,7 @@
         <v>46279</v>
       </c>
       <c r="C65" t="n">
-        <v>6.44769857266258</v>
+        <v>6.448017062692977</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7767,7 +7749,7 @@
         <v>24.47056390537039</v>
       </c>
       <c r="Y65" t="n">
-        <v>8.562038809789406</v>
+        <v>8.557522147183249</v>
       </c>
       <c r="Z65" t="n">
         <v>18</v>
@@ -7816,7 +7798,7 @@
         <v>46279</v>
       </c>
       <c r="C66" t="n">
-        <v>0.448768047385957</v>
+        <v>0.4479675153894253</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7844,22 +7826,22 @@
         <v>10.41136575766793</v>
       </c>
       <c r="K66" t="n">
-        <v>3.447674421607405</v>
+        <v>3.263139952578964</v>
       </c>
       <c r="L66" t="n">
         <v>45</v>
       </c>
       <c r="M66" t="n">
-        <v>55.55555555555556</v>
+        <v>51.11111111111111</v>
       </c>
       <c r="N66" t="n">
-        <v>20.54606781361603</v>
+        <v>22.18070974416615</v>
       </c>
       <c r="O66" t="n">
         <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>2.467262403590098</v>
+        <v>2.650374614482831</v>
       </c>
       <c r="Q66" t="n">
         <v>35</v>
@@ -7886,13 +7868,13 @@
         <v>14.59585890675015</v>
       </c>
       <c r="Y66" t="n">
-        <v>7.322641330227631</v>
+        <v>7.48796324073655</v>
       </c>
       <c r="Z66" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA66" t="n">
-        <v>46.875</v>
+        <v>50</v>
       </c>
       <c r="AB66" t="n">
         <v>10.96998186648398</v>
@@ -7935,7 +7917,7 @@
         <v>46279</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02735387273250792</v>
+        <v>0.0271495465555202</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7963,7 +7945,7 @@
         <v>11.46300958938384</v>
       </c>
       <c r="K67" t="n">
-        <v>3.49573302602677</v>
+        <v>2.722647340115159</v>
       </c>
       <c r="L67" t="n">
         <v>5</v>
@@ -7972,13 +7954,13 @@
         <v>20</v>
       </c>
       <c r="N67" t="n">
-        <v>7.104188996989391</v>
+        <v>6.573256403145478</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>0.4872345547293433</v>
+        <v>1.243496631911678</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -8024,7 +8006,7 @@
         <v>46279</v>
       </c>
       <c r="C68" t="n">
-        <v>1.734811402245897</v>
+        <v>1.73489706338975</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8049,10 +8031,10 @@
         <v>10</v>
       </c>
       <c r="J68" t="n">
-        <v>68.93257160983551</v>
+        <v>68.93103700549554</v>
       </c>
       <c r="K68" t="n">
-        <v>1.813870809108664e-06</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -8063,7 +8045,7 @@
         <v>2</v>
       </c>
       <c r="P68" t="n">
-        <v>1.999998149851812</v>
+        <v>2.000000000000002</v>
       </c>
       <c r="Q68" t="n">
         <v>5</v>
@@ -8129,7 +8111,7 @@
         <v>46279</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5067664843075151</v>
+        <v>0.4705921051932408</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8178,13 +8160,13 @@
         <v>75</v>
       </c>
       <c r="X69" t="n">
-        <v>45.32872515894941</v>
+        <v>45.33590337629856</v>
       </c>
       <c r="Y69" t="n">
-        <v>9.010339734121109</v>
+        <v>15.50960403400178</v>
       </c>
       <c r="Z69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA69" t="inlineStr"/>
       <c r="AB69" t="inlineStr"/>
@@ -8218,7 +8200,7 @@
         <v>46279</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4899016905927358</v>
+        <v>0.486635032651079</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8243,25 +8225,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>11.36562932047446</v>
+        <v>12.25433707230089</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>0.3392702725675045</v>
       </c>
       <c r="L70" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="M70" t="n">
-        <v>50</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="N70" t="n">
-        <v>12.22267739008541</v>
+        <v>12.1067993174524</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>8.000000000000007</v>
+        <v>7.634827028961277</v>
       </c>
       <c r="Q70" t="n">
         <v>31</v>
@@ -8288,16 +8270,16 @@
         <v>44.93251946562029</v>
       </c>
       <c r="Y70" t="n">
-        <v>11.36562932047446</v>
+        <v>11.95664212251992</v>
       </c>
       <c r="Z70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA70" t="n">
-        <v>33.33333333333334</v>
+        <v>40</v>
       </c>
       <c r="AB70" t="n">
-        <v>10.37117321374181</v>
+        <v>8.42308193419985</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
@@ -8337,7 +8319,7 @@
         <v>46279</v>
       </c>
       <c r="C71" t="n">
-        <v>3.233104356052815</v>
+        <v>3.220923481182214</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8436,7 +8418,7 @@
         <v>46279</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0629344741063716</v>
+        <v>0.06314325974834528</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8464,16 +8446,16 @@
         <v>29.77666337790048</v>
       </c>
       <c r="K72" t="n">
-        <v>5.46402257947245</v>
+        <v>5.813900352696799</v>
       </c>
       <c r="L72" t="n">
         <v>10</v>
       </c>
       <c r="M72" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="N72" t="n">
-        <v>20.40933767641903</v>
+        <v>18.39061517377225</v>
       </c>
       <c r="O72" t="n">
         <v>5</v>
@@ -8506,22 +8488,22 @@
         <v>12.03392243896149</v>
       </c>
       <c r="Y72" t="n">
-        <v>5.864205873063543</v>
+        <v>5.551909592073323</v>
       </c>
       <c r="Z72" t="n">
         <v>34</v>
       </c>
       <c r="AA72" t="n">
-        <v>58.8235294117647</v>
+        <v>50</v>
       </c>
       <c r="AB72" t="n">
-        <v>11.90415789566501</v>
+        <v>11.97540425375395</v>
       </c>
       <c r="AC72" t="n">
         <v>8</v>
       </c>
       <c r="AD72" t="n">
-        <v>2.268843798201203</v>
+        <v>2.591995663811975</v>
       </c>
       <c r="AE72" t="n">
         <v>10</v>
@@ -8555,7 +8537,7 @@
         <v>46279</v>
       </c>
       <c r="C73" t="n">
-        <v>0.06231746945826992</v>
+        <v>0.062731903409291</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8569,12 +8551,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H73" t="n">
@@ -8587,22 +8569,22 @@
         <v>19.59098648410814</v>
       </c>
       <c r="K73" t="n">
-        <v>2.081278724583036</v>
+        <v>2.760156542230008</v>
       </c>
       <c r="L73" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M73" t="n">
-        <v>75</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N73" t="n">
-        <v>12.3596071563907</v>
+        <v>13.08601002425486</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>7.757270847656428</v>
+        <v>7.045379942365826</v>
       </c>
       <c r="Q73" t="n">
         <v>14</v>
@@ -8625,17 +8607,27 @@
       <c r="W73" t="n">
         <v>73.91304347826087</v>
       </c>
-      <c r="X73" t="inlineStr"/>
-      <c r="Y73" t="inlineStr"/>
+      <c r="X73" t="n">
+        <v>12.19387497524824</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>8.408407709511289</v>
+      </c>
       <c r="Z73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA73" t="inlineStr"/>
-      <c r="AB73" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>61.90476190476191</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>12.62687064053817</v>
+      </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
-      <c r="AD73" t="inlineStr"/>
+      <c r="AD73" t="n">
+        <v>1.737705667831246</v>
+      </c>
       <c r="AE73" t="n">
         <v>15</v>
       </c>
@@ -8668,7 +8660,7 @@
         <v>46279</v>
       </c>
       <c r="C74" t="n">
-        <v>5.527333305910904</v>
+        <v>5.553316130548976</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8693,25 +8685,25 @@
         <v>10</v>
       </c>
       <c r="J74" t="n">
-        <v>10.38079766250025</v>
+        <v>10.37637083916865</v>
       </c>
       <c r="K74" t="n">
-        <v>3.965183752417789</v>
+        <v>4.448742746615086</v>
       </c>
       <c r="L74" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M74" t="n">
-        <v>72.72727272727273</v>
+        <v>67.9245283018868</v>
       </c>
       <c r="N74" t="n">
-        <v>15.05047855147138</v>
+        <v>16.2706300590606</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>3.880930232558155</v>
+        <v>3.400000000000003</v>
       </c>
       <c r="Q74" t="n">
         <v>30</v>
@@ -8738,22 +8730,22 @@
         <v>25.51128431523497</v>
       </c>
       <c r="Y74" t="n">
-        <v>6.82723161236728</v>
+        <v>6.389246137622962</v>
       </c>
       <c r="Z74" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA74" t="n">
-        <v>50</v>
+        <v>52.38095238095238</v>
       </c>
       <c r="AB74" t="n">
-        <v>14.1840709499142</v>
+        <v>15.63580669470952</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>3.405252889377341</v>
+        <v>3.857199855142102</v>
       </c>
       <c r="AE74" t="n">
         <v>37</v>
@@ -8787,7 +8779,7 @@
         <v>46279</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1094154909300317</v>
+        <v>0.1085981864277592</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8804,11 +8796,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.82: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>5</v>
       </c>
@@ -8816,25 +8804,25 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>28.79306661023321</v>
+        <v>28.78954644571032</v>
       </c>
       <c r="K75" t="n">
-        <v>0.7575757575757569</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
         <v>11</v>
       </c>
       <c r="M75" t="n">
-        <v>81.81818181818181</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N75" t="n">
-        <v>15.72994592528538</v>
+        <v>17.30552880567455</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>5.203007518797009</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8900,7 +8888,7 @@
         <v>46279</v>
       </c>
       <c r="C76" t="n">
-        <v>1.952819711241825</v>
+        <v>1.952916109844485</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8960,7 +8948,7 @@
         <v>12.76370567693843</v>
       </c>
       <c r="Y76" t="n">
-        <v>3.821446833267994</v>
+        <v>3.816699094356002</v>
       </c>
       <c r="Z76" t="n">
         <v>46</v>
@@ -8969,13 +8957,13 @@
         <v>39.1304347826087</v>
       </c>
       <c r="AB76" t="n">
-        <v>9.654522659042094</v>
+        <v>9.524414452486621</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.1856475907081601</v>
+        <v>0.1905745632745703</v>
       </c>
       <c r="AE76" t="n">
         <v>32</v>
@@ -9009,7 +8997,7 @@
         <v>46279</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4812636255193122</v>
+        <v>0.4816987563767492</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9034,25 +9022,25 @@
         <v>10</v>
       </c>
       <c r="J77" t="n">
-        <v>16.01978097023047</v>
+        <v>16.01563214994599</v>
       </c>
       <c r="K77" t="n">
-        <v>0.2570694087403513</v>
+        <v>0.3427589095366779</v>
       </c>
       <c r="L77" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M77" t="n">
-        <v>71.42857142857143</v>
+        <v>68</v>
       </c>
       <c r="N77" t="n">
-        <v>15.10224736770855</v>
+        <v>15.2790852513776</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>7.723076923076944</v>
+        <v>7.631084867186733</v>
       </c>
       <c r="Q77" t="n">
         <v>27</v>
@@ -9118,7 +9106,7 @@
         <v>46279</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05984945086586319</v>
+        <v>0.06046944354449243</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9175,25 +9163,25 @@
         <v>64.1025641025641</v>
       </c>
       <c r="X78" t="n">
-        <v>32.21100528735843</v>
+        <v>32.21753775888643</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.689189189189189</v>
+        <v>0.6756749908692572</v>
       </c>
       <c r="Z78" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA78" t="n">
-        <v>9.523809523809524</v>
+        <v>15</v>
       </c>
       <c r="AB78" t="n">
-        <v>9.720875045681026</v>
+        <v>9.674269180691789</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>8.453608247422684</v>
+        <v>9.387755726780489</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9227,7 +9215,7 @@
         <v>46279</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8983587676360495</v>
+        <v>0.8951122983556179</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9255,22 +9243,22 @@
         <v>10.42896938309872</v>
       </c>
       <c r="K79" t="n">
-        <v>0.6760536845302534</v>
+        <v>0.3122327620474152</v>
       </c>
       <c r="L79" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M79" t="n">
-        <v>51.92307692307692</v>
+        <v>54.90196078431372</v>
       </c>
       <c r="N79" t="n">
-        <v>10.60447963980444</v>
+        <v>10.42121004791757</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>4.294910415359432</v>
+        <v>4.673176051292294</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9297,16 +9285,16 @@
         <v>25.65117214954458</v>
       </c>
       <c r="Y79" t="n">
-        <v>9.823421130341426</v>
+        <v>10.14929928020923</v>
       </c>
       <c r="Z79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA79" t="n">
-        <v>60</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB79" t="n">
-        <v>9.128747513977077</v>
+        <v>8.267177553195101</v>
       </c>
       <c r="AC79" t="n">
         <v>8</v>
@@ -9346,7 +9334,7 @@
         <v>46279</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1332730039899634</v>
+        <v>0.1332795875445322</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9374,7 +9362,7 @@
         <v>10.48668504530712</v>
       </c>
       <c r="K80" t="n">
-        <v>4.256882447587707</v>
+        <v>4.262032634453883</v>
       </c>
       <c r="L80" t="n">
         <v>37</v>
@@ -9389,7 +9377,7 @@
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>5.508621989823537</v>
+        <v>5.503410225718142</v>
       </c>
       <c r="Q80" t="n">
         <v>39</v>
@@ -9416,7 +9404,7 @@
         <v>16.92042739318289</v>
       </c>
       <c r="Y80" t="n">
-        <v>6.676208452746901</v>
+        <v>6.671598349756625</v>
       </c>
       <c r="Z80" t="n">
         <v>30</v>
@@ -9431,7 +9419,7 @@
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.418493103747087</v>
+        <v>1.423362692122032</v>
       </c>
       <c r="AE80" t="n">
         <v>24</v>
@@ -9465,7 +9453,7 @@
         <v>46279</v>
       </c>
       <c r="C81" t="n">
-        <v>1.239151001604212</v>
+        <v>1.242297417710118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9522,25 +9510,25 @@
         <v>65.30612244897959</v>
       </c>
       <c r="X81" t="n">
-        <v>23.75839605018282</v>
+        <v>23.76450921054161</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.66559206658552</v>
+        <v>2.423263268051801</v>
       </c>
       <c r="Z81" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA81" t="n">
-        <v>32</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="AB81" t="n">
-        <v>12.2306799472837</v>
+        <v>10.57166715745348</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>7.535267424066394</v>
+        <v>7.764900718869249</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9574,7 +9562,7 @@
         <v>46279</v>
       </c>
       <c r="C82" t="n">
-        <v>4.785899324379911</v>
+        <v>4.769681395552144</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9602,22 +9590,22 @@
         <v>16.34835816551005</v>
       </c>
       <c r="K82" t="n">
-        <v>2.334943440971515</v>
+        <v>1.988162049046971</v>
       </c>
       <c r="L82" t="n">
         <v>9</v>
       </c>
       <c r="M82" t="n">
-        <v>11.11111111111111</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="N82" t="n">
-        <v>15.45744852260049</v>
+        <v>13.12629555041259</v>
       </c>
       <c r="O82" t="n">
         <v>4</v>
       </c>
       <c r="P82" t="n">
-        <v>1.627065499859226</v>
+        <v>1.972619086895122</v>
       </c>
       <c r="Q82" t="n">
         <v>8</v>
@@ -9683,7 +9671,7 @@
         <v>46279</v>
       </c>
       <c r="C83" t="n">
-        <v>5.511908189708363</v>
+        <v>5.522464374268148</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9711,22 +9699,22 @@
         <v>13.10783674393532</v>
       </c>
       <c r="K83" t="n">
-        <v>4.158666049635174</v>
+        <v>4.358146531616724</v>
       </c>
       <c r="L83" t="n">
         <v>62</v>
       </c>
       <c r="M83" t="n">
-        <v>41.93548387096774</v>
+        <v>43.54838709677419</v>
       </c>
       <c r="N83" t="n">
-        <v>12.84910722114932</v>
+        <v>12.37564002522255</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>5.608111328519927</v>
+        <v>5.406241540207901</v>
       </c>
       <c r="Q83" t="n">
         <v>41</v>
@@ -9792,7 +9780,7 @@
         <v>46279</v>
       </c>
       <c r="C84" t="n">
-        <v>2.108099214347415</v>
+        <v>2.106146593573292</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9820,16 +9808,16 @@
         <v>14.96371051984784</v>
       </c>
       <c r="K84" t="n">
-        <v>8.72180205531734</v>
+        <v>8.621098801955984</v>
       </c>
       <c r="L84" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M84" t="n">
-        <v>55.55555555555556</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N84" t="n">
-        <v>10.33046342082408</v>
+        <v>10.27404726378175</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9862,13 +9850,13 @@
         <v>11.86663135768809</v>
       </c>
       <c r="Y84" t="n">
-        <v>2.811230895400174</v>
+        <v>2.901251710489672</v>
       </c>
       <c r="Z84" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AA84" t="n">
-        <v>36.8421052631579</v>
+        <v>37.5</v>
       </c>
       <c r="AB84" t="n">
         <v>11.87023114330644</v>
@@ -9877,7 +9865,7 @@
         <v>5</v>
       </c>
       <c r="AD84" t="n">
-        <v>2.252080281255708</v>
+        <v>2.161457615553075</v>
       </c>
       <c r="AE84" t="n">
         <v>39</v>
@@ -9911,7 +9899,7 @@
         <v>46279</v>
       </c>
       <c r="C85" t="n">
-        <v>6.087779194603266</v>
+        <v>6.077795987323046</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9939,22 +9927,22 @@
         <v>12.5637553307017</v>
       </c>
       <c r="K85" t="n">
-        <v>1.689377387026747</v>
+        <v>1.522619346007237</v>
       </c>
       <c r="L85" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M85" t="n">
-        <v>57.14285714285715</v>
+        <v>55.88235294117647</v>
       </c>
       <c r="N85" t="n">
-        <v>14.71541237919241</v>
+        <v>14.62215108340677</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>6.205783509673002</v>
+        <v>6.380233977136363</v>
       </c>
       <c r="Q85" t="n">
         <v>32</v>
@@ -10020,7 +10008,7 @@
         <v>46279</v>
       </c>
       <c r="C86" t="n">
-        <v>4.46711365225618</v>
+        <v>4.44882331842725</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10048,22 +10036,22 @@
         <v>18.73514495170452</v>
       </c>
       <c r="K86" t="n">
-        <v>7.152986135166417</v>
+        <v>6.714254542521791</v>
       </c>
       <c r="L86" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M86" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N86" t="n">
-        <v>16.80834062621504</v>
+        <v>16.83369757944945</v>
       </c>
       <c r="O86" t="n">
         <v>8</v>
       </c>
       <c r="P86" t="n">
-        <v>0.7904715448294963</v>
+        <v>1.204848839538952</v>
       </c>
       <c r="Q86" t="n">
         <v>52</v>
@@ -10090,7 +10078,7 @@
         <v>48.61770380947655</v>
       </c>
       <c r="Y86" t="n">
-        <v>12.92228113733684</v>
+        <v>13.27881573015058</v>
       </c>
       <c r="Z86" t="n">
         <v>3</v>
@@ -10139,7 +10127,7 @@
         <v>46279</v>
       </c>
       <c r="C87" t="n">
-        <v>5.887252683970219</v>
+        <v>5.846407815216838</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10199,16 +10187,16 @@
         <v>15.88967756874082</v>
       </c>
       <c r="Y87" t="n">
-        <v>4.562481807111074</v>
+        <v>5.224612874688783</v>
       </c>
       <c r="Z87" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AA87" t="n">
-        <v>44.44444444444444</v>
+        <v>45.71428571428572</v>
       </c>
       <c r="AB87" t="n">
-        <v>10.9807118926863</v>
+        <v>12.87424470283853</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
@@ -10248,7 +10236,7 @@
         <v>46279</v>
       </c>
       <c r="C88" t="n">
-        <v>1.076673110937436</v>
+        <v>1.07466951044883</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10276,16 +10264,16 @@
         <v>16.8583060727446</v>
       </c>
       <c r="K88" t="n">
-        <v>8.299628874917708</v>
+        <v>8.098092134448054</v>
       </c>
       <c r="L88" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M88" t="n">
-        <v>70.96774193548387</v>
+        <v>71.875</v>
       </c>
       <c r="N88" t="n">
-        <v>13.62701040529383</v>
+        <v>13.53184149474504</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
@@ -10318,16 +10306,16 @@
         <v>25.70907945955605</v>
       </c>
       <c r="Y88" t="n">
-        <v>9.957854036462399</v>
+        <v>10.12541509637465</v>
       </c>
       <c r="Z88" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA88" t="n">
-        <v>36.36363636363637</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="AB88" t="n">
-        <v>14.2055834366375</v>
+        <v>13.51336303619622</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
@@ -10367,7 +10355,7 @@
         <v>46279</v>
       </c>
       <c r="C89" t="n">
-        <v>2.178026407798939</v>
+        <v>2.178134024895223</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10427,7 +10415,7 @@
         <v>21.45830694080864</v>
       </c>
       <c r="Y89" t="n">
-        <v>6.982935983436855</v>
+        <v>6.978339975648118</v>
       </c>
       <c r="Z89" t="n">
         <v>37</v>
@@ -10442,7 +10430,7 @@
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>3.243559715049604</v>
+        <v>3.248340250604909</v>
       </c>
       <c r="AE89" t="n">
         <v>22</v>
@@ -10476,7 +10464,7 @@
         <v>46279</v>
       </c>
       <c r="C90" t="n">
-        <v>2.819711241824688</v>
+        <v>2.807509821555315</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10504,22 +10492,22 @@
         <v>12.8208334231333</v>
       </c>
       <c r="K90" t="n">
-        <v>3.529286674592047</v>
+        <v>3.081296001586953</v>
       </c>
       <c r="L90" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="M90" t="n">
-        <v>62.33766233766234</v>
+        <v>63.95348837209303</v>
       </c>
       <c r="N90" t="n">
-        <v>15.1054787554164</v>
+        <v>15.31969993210813</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>4.318307861484727</v>
+        <v>4.771674580359697</v>
       </c>
       <c r="Q90" t="n">
         <v>43</v>
@@ -10546,16 +10534,16 @@
         <v>20.63086277737274</v>
       </c>
       <c r="Y90" t="n">
-        <v>9.744030714115548</v>
+        <v>10.13458524918348</v>
       </c>
       <c r="Z90" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA90" t="n">
-        <v>42.10526315789474</v>
+        <v>45</v>
       </c>
       <c r="AB90" t="n">
-        <v>11.67938000705534</v>
+        <v>11.08028764123533</v>
       </c>
       <c r="AC90" t="n">
         <v>2</v>
@@ -10595,7 +10583,7 @@
         <v>46279</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2356957755748427</v>
+        <v>0.2363244483805371</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10694,7 +10682,7 @@
         <v>46279</v>
       </c>
       <c r="C92" t="n">
-        <v>1.1856772654354</v>
+        <v>1.180593905148462</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10754,16 +10742,16 @@
         <v>21.60407460332612</v>
       </c>
       <c r="Y92" t="n">
-        <v>5.317095132917126</v>
+        <v>5.723029641812715</v>
       </c>
       <c r="Z92" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA92" t="n">
-        <v>35.29411764705883</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB92" t="n">
-        <v>12.79838806403724</v>
+        <v>12.61693254762918</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10803,7 +10791,7 @@
         <v>46279</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04216198428694829</v>
+        <v>0.04195838771921209</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10863,16 +10851,16 @@
         <v>11.4419372600254</v>
       </c>
       <c r="Y93" t="n">
-        <v>4.070405009206468</v>
+        <v>4.533640708729648</v>
       </c>
       <c r="Z93" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AA93" t="n">
-        <v>44.18604651162791</v>
+        <v>45</v>
       </c>
       <c r="AB93" t="n">
-        <v>13.26309491661619</v>
+        <v>15.44736513139534</v>
       </c>
       <c r="AC93" t="n">
         <v>2</v>
@@ -10912,7 +10900,7 @@
         <v>46279</v>
       </c>
       <c r="C94" t="n">
-        <v>8.60721484101847</v>
+        <v>8.551078449169395</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10972,22 +10960,22 @@
         <v>46.54975901226545</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.337915922176891</v>
+        <v>1.981391600981208</v>
       </c>
       <c r="Z94" t="n">
         <v>10</v>
       </c>
       <c r="AA94" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AB94" t="n">
-        <v>9.178759695939807</v>
+        <v>10.75358476998065</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>4.725304681528653</v>
+        <v>4.099842330610992</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -11021,7 +11009,7 @@
         <v>46279</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1223725846324709</v>
+        <v>0.121144560322231</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11046,25 +11034,25 @@
         <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>18.89669242033002</v>
+        <v>19.07550043933058</v>
       </c>
       <c r="K95" t="n">
-        <v>0.9623898570362055</v>
+        <v>0.1700639423967587</v>
       </c>
       <c r="L95" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="M95" t="n">
-        <v>62.96296296296296</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N95" t="n">
-        <v>14.90353298748101</v>
+        <v>16.13870371541334</v>
       </c>
       <c r="O95" t="n">
         <v>10</v>
       </c>
       <c r="P95" t="n">
-        <v>8.951462178897662</v>
+        <v>9.813247262431624</v>
       </c>
       <c r="Q95" t="n">
         <v>21</v>
@@ -11130,7 +11118,7 @@
         <v>46279</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1271029575089466</v>
+        <v>0.1273149154862857</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11229,7 +11217,7 @@
         <v>46279</v>
       </c>
       <c r="C97" t="n">
-        <v>1.913742750195385</v>
+        <v>1.91692239418352</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11257,16 +11245,16 @@
         <v>12.87370897365936</v>
       </c>
       <c r="K97" t="n">
-        <v>4.607645329092902</v>
+        <v>4.781448767694907</v>
       </c>
       <c r="L97" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M97" t="n">
-        <v>59.52380952380953</v>
+        <v>56.09756097560975</v>
       </c>
       <c r="N97" t="n">
-        <v>15.00415549181639</v>
+        <v>15.57778215297127</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11299,13 +11287,13 @@
         <v>16.31583297271808</v>
       </c>
       <c r="Y97" t="n">
-        <v>8.859238494772292</v>
+        <v>8.707810005042127</v>
       </c>
       <c r="Z97" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA97" t="n">
-        <v>42.85714285714285</v>
+        <v>40</v>
       </c>
       <c r="AB97" t="n">
         <v>11.08203790087885</v>
@@ -11348,7 +11336,7 @@
         <v>46279</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7375262226975443</v>
+        <v>0.7350945475384869</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11408,7 +11396,7 @@
         <v>30.85778357900837</v>
       </c>
       <c r="Y98" t="n">
-        <v>5.887749617539373</v>
+        <v>6.198044240801693</v>
       </c>
       <c r="Z98" t="n">
         <v>11</v>
@@ -11417,13 +11405,13 @@
         <v>27.27272727272727</v>
       </c>
       <c r="AB98" t="n">
-        <v>10.34887947774709</v>
+        <v>8.732156502971499</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>2.244394724253962</v>
+        <v>1.92102152307374</v>
       </c>
       <c r="AE98" t="n">
         <v>51</v>
@@ -11457,7 +11445,7 @@
         <v>46279</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5417300810332771</v>
+        <v>0.5401114180202918</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11482,19 +11470,19 @@
         <v>10</v>
       </c>
       <c r="J99" t="n">
-        <v>12.54028063609323</v>
+        <v>12.53596020163561</v>
       </c>
       <c r="K99" t="n">
-        <v>5.69823434991974</v>
+        <v>5.377207647264171</v>
       </c>
       <c r="L99" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="M99" t="n">
-        <v>58.18181818181818</v>
+        <v>54.23728813559322</v>
       </c>
       <c r="N99" t="n">
-        <v>14.98905401797758</v>
+        <v>14.27418325742021</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
@@ -11527,7 +11515,7 @@
         <v>33.04241514445872</v>
       </c>
       <c r="Y99" t="n">
-        <v>7.556620864955677</v>
+        <v>7.832837164991791</v>
       </c>
       <c r="Z99" t="n">
         <v>6</v>
@@ -11542,7 +11530,7 @@
         <v>10</v>
       </c>
       <c r="AD99" t="n">
-        <v>2.643108849877662</v>
+        <v>2.35133942322574</v>
       </c>
       <c r="AE99" t="n">
         <v>38</v>
@@ -11576,7 +11564,7 @@
         <v>46279</v>
       </c>
       <c r="C100" t="n">
-        <v>348.2565441055489</v>
+        <v>347.2301296629448</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11636,22 +11624,22 @@
         <v>16.86980163304483</v>
       </c>
       <c r="Y100" t="n">
-        <v>4.409824202318791</v>
+        <v>4.691556559313859</v>
       </c>
       <c r="Z100" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA100" t="n">
-        <v>44.44444444444444</v>
+        <v>38.23529411764706</v>
       </c>
       <c r="AB100" t="n">
-        <v>13.01847294205303</v>
+        <v>13.21766654686114</v>
       </c>
       <c r="AC100" t="n">
         <v>8</v>
       </c>
       <c r="AD100" t="n">
-        <v>3.755799973921892</v>
+        <v>3.471301514587322</v>
       </c>
       <c r="AE100" t="n">
         <v>39</v>
@@ -11685,7 +11673,7 @@
         <v>46279</v>
       </c>
       <c r="C101" t="n">
-        <v>349.7782896631154</v>
+        <v>349.8949099402464</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11745,7 +11733,7 @@
         <v>13.07599096065748</v>
       </c>
       <c r="Y101" t="n">
-        <v>3.224229376386822</v>
+        <v>3.191963173700085</v>
       </c>
       <c r="Z101" t="n">
         <v>39</v>
@@ -11760,7 +11748,7 @@
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>2.868249568798475</v>
+        <v>2.900623665510649</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11794,7 +11782,7 @@
         <v>46279</v>
       </c>
       <c r="C102" t="n">
-        <v>408.289851108963</v>
+        <v>408.5060561648955</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11854,7 +11842,7 @@
         <v>10.81355469301844</v>
       </c>
       <c r="Y102" t="n">
-        <v>4.219783602053173</v>
+        <v>4.169064322631232</v>
       </c>
       <c r="Z102" t="n">
         <v>17</v>
@@ -11869,7 +11857,7 @@
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>0.8145903478701699</v>
+        <v>0.867085009131352</v>
       </c>
       <c r="AE102" t="n">
         <v>26</v>
@@ -11903,7 +11891,7 @@
         <v>46279</v>
       </c>
       <c r="C103" t="n">
-        <v>0.751922997819917</v>
+        <v>0.7536055542066357</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11963,22 +11951,22 @@
         <v>14.28440963201156</v>
       </c>
       <c r="Y103" t="n">
-        <v>4.8512878589408</v>
+        <v>4.638376332407946</v>
       </c>
       <c r="Z103" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AA103" t="n">
-        <v>48.64864864864865</v>
+        <v>45</v>
       </c>
       <c r="AB103" t="n">
-        <v>10.95821207278935</v>
+        <v>10.86873296387317</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>3.30925355709617</v>
+        <v>3.525132583008306</v>
       </c>
       <c r="AE103" t="n">
         <v>33</v>
@@ -12012,11 +12000,11 @@
         <v>46279</v>
       </c>
       <c r="C104" t="n">
-        <v>0.05018304471227016</v>
+        <v>0.04956849027563512</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -12026,7 +12014,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -12072,22 +12060,22 @@
         <v>12.98853157526716</v>
       </c>
       <c r="Y104" t="n">
-        <v>4.578806460897944</v>
+        <v>5.74735887087413</v>
       </c>
       <c r="Z104" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="AA104" t="n">
-        <v>51.78571428571428</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="AB104" t="n">
-        <v>12.61850589849145</v>
+        <v>11.19798827024807</v>
       </c>
       <c r="AC104" t="n">
         <v>5</v>
       </c>
       <c r="AD104" t="n">
-        <v>0.4414046015149276</v>
+        <v>0</v>
       </c>
       <c r="AE104" t="n">
         <v>42</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -667,19 +667,19 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4051864147864263</v>
+        <v>0.3957648026315789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -698,22 +698,22 @@
         <v>21.42119502374098</v>
       </c>
       <c r="K2" t="n">
-        <v>10.27716801541496</v>
+        <v>7.712944071421624</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M2" t="n">
         <v>60</v>
       </c>
       <c r="N2" t="n">
-        <v>11.35176187055035</v>
+        <v>15.62940110231521</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.123287918917049</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -740,22 +740,22 @@
         <v>11.79582706077868</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.35842194229493</v>
+        <v>3.652088898754124</v>
       </c>
       <c r="Z2" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AA2" t="n">
-        <v>44.23076923076923</v>
+        <v>45</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.484952980269453</v>
+        <v>11.75926858937931</v>
       </c>
       <c r="AC2" t="n">
         <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>8.760583749633211</v>
+        <v>6.588530076770693</v>
       </c>
       <c r="AE2" t="n">
         <v>46</v>
@@ -789,7 +789,7 @@
         <v>46279</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7091790282474195</v>
+        <v>0.7092213188717587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>16.83732632822199</v>
       </c>
       <c r="K3" t="n">
-        <v>12.80399458508994</v>
+        <v>12.8107214497728</v>
       </c>
       <c r="L3" t="n">
         <v>15</v>
@@ -859,7 +859,7 @@
         <v>17.17248092970491</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.728252837145052</v>
+        <v>3.722511843500897</v>
       </c>
       <c r="Z3" t="n">
         <v>42</v>
@@ -874,7 +874,7 @@
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>6.514629003507699</v>
+        <v>6.520203504161892</v>
       </c>
       <c r="AE3" t="n">
         <v>35</v>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C4" t="n">
-        <v>1.492196674847935</v>
+        <v>1.469983552631579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -968,22 +968,22 @@
         <v>16.66966699739723</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.220872314935631</v>
+        <v>6.63177235399548</v>
       </c>
       <c r="Z4" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="AA4" t="n">
-        <v>42.85714285714285</v>
+        <v>59.25925925925926</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.84876785599352</v>
+        <v>11.46243236260763</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>5.042384121686194</v>
+        <v>3.607466619988531</v>
       </c>
       <c r="AE4" t="n">
         <v>40</v>
@@ -992,10 +992,10 @@
         <v>60</v>
       </c>
       <c r="AG4" t="n">
-        <v>39.35090438163581</v>
+        <v>39.23594521098629</v>
       </c>
       <c r="AH4" t="n">
-        <v>20.64909561836419</v>
+        <v>20.76405478901371</v>
       </c>
       <c r="AI4" t="n">
         <v>44.59589366034619</v>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2280973211880946</v>
+        <v>0.229235197368421</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,16 +1045,16 @@
         <v>19.13427219952423</v>
       </c>
       <c r="K5" t="n">
-        <v>4.785646705218816</v>
+        <v>5.308375735112336</v>
       </c>
       <c r="L5" t="n">
         <v>28</v>
       </c>
       <c r="M5" t="n">
-        <v>50</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N5" t="n">
-        <v>11.68319257573849</v>
+        <v>10.7662014468071</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -1087,22 +1087,22 @@
         <v>10.55954734904581</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.222435133167025</v>
+        <v>4.749631976472434</v>
       </c>
       <c r="Z5" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA5" t="n">
-        <v>33.33333333333334</v>
+        <v>43.90243902439025</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.491367762561834</v>
+        <v>9.164656365945994</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.040818334534847</v>
+        <v>5.512176102280975</v>
       </c>
       <c r="AE5" t="n">
         <v>45</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C6" t="n">
-        <v>1.606348078886301</v>
+        <v>1.599506578947368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>24.35210179737853</v>
       </c>
       <c r="K6" t="n">
-        <v>1.022031058321193</v>
+        <v>0.5917742364027756</v>
       </c>
       <c r="L6" t="n">
         <v>23</v>
@@ -1177,34 +1177,34 @@
         <v>82.60869565217391</v>
       </c>
       <c r="N6" t="n">
-        <v>12.17768755901921</v>
+        <v>12.34555220948897</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9680749153758494</v>
+        <v>1.399941271825789</v>
       </c>
       <c r="Q6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R6" t="n">
-        <v>67.64705882352941</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="S6" t="n">
-        <v>55.78043504354592</v>
+        <v>56.18670832801604</v>
       </c>
       <c r="T6" t="n">
-        <v>11.86662377998348</v>
+        <v>12.38472024341253</v>
       </c>
       <c r="U6" t="n">
-        <v>50.84289459390821</v>
+        <v>52.02023638793081</v>
       </c>
       <c r="V6" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W6" t="n">
-        <v>74.35897435897436</v>
+        <v>74.68354430379746</v>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
@@ -1224,10 +1224,10 @@
         <v>46.93877551020408</v>
       </c>
       <c r="AG6" t="n">
-        <v>39.29345237727971</v>
+        <v>39.03634327378123</v>
       </c>
       <c r="AH6" t="n">
-        <v>7.645323132924368</v>
+        <v>7.902432236422854</v>
       </c>
       <c r="AI6" t="n">
         <v>33.70350369317515</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C7" t="n">
-        <v>2.328279144594555</v>
+        <v>2.300575657894737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,16 +1309,16 @@
         <v>18.9234494530097</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.891889429769559</v>
+        <v>7.011653267185791</v>
       </c>
       <c r="Z7" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AA7" t="n">
-        <v>42.85714285714285</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="AB7" t="n">
-        <v>13.61597622322071</v>
+        <v>11.00548278227541</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3418374768685538</v>
+        <v>0.3470394736842105</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,22 +1386,22 @@
         <v>20.70550141590351</v>
       </c>
       <c r="K8" t="n">
-        <v>4.978787070081947</v>
+        <v>6.576327869448617</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>60</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N8" t="n">
-        <v>17.38979657077811</v>
+        <v>12.06937941087031</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.877927069114605</v>
+        <v>1.335823966739902</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1425,13 +1425,13 @@
         <v>50</v>
       </c>
       <c r="X8" t="n">
-        <v>28.52170855483174</v>
+        <v>26.93179943319606</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.7575971731122</v>
+        <v>15.49083520657804</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5471044858624551</v>
+        <v>0.5489309210526315</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>14.50739888386581</v>
       </c>
       <c r="K9" t="n">
-        <v>2.898328296971298</v>
+        <v>3.241840610740132</v>
       </c>
       <c r="L9" t="n">
         <v>41</v>
@@ -1510,7 +1510,7 @@
         <v>48.78048780487805</v>
       </c>
       <c r="N9" t="n">
-        <v>14.70543065115051</v>
+        <v>14.69366495460834</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C10" t="n">
-        <v>1.940575438595267</v>
+        <v>1.918174342105263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,22 +1610,22 @@
         <v>13.50421550203786</v>
       </c>
       <c r="K10" t="n">
-        <v>5.83544299446892</v>
+        <v>4.61372807247773</v>
       </c>
       <c r="L10" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M10" t="n">
-        <v>54.54545454545455</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N10" t="n">
-        <v>9.125705552342156</v>
+        <v>9.785313373390345</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>3.934936055163241</v>
+        <v>5.148723811649836</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1643,10 +1643,10 @@
         <v>36.75230846944931</v>
       </c>
       <c r="V10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="W10" t="n">
-        <v>62.26415094339622</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C11" t="n">
-        <v>7.661519476405531</v>
+        <v>7.596628289473684</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,25 +1716,25 @@
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>11.17883826079963</v>
+        <v>11.69503567664335</v>
       </c>
       <c r="K11" t="n">
-        <v>0.472016183411994</v>
+        <v>0.2033898305084714</v>
       </c>
       <c r="L11" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M11" t="n">
-        <v>50.87719298245614</v>
+        <v>58.92857142857143</v>
       </c>
       <c r="N11" t="n">
-        <v>13.65224315283608</v>
+        <v>13.28632006090635</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.516107382550348</v>
+        <v>2.79093369418133</v>
       </c>
       <c r="Q11" t="n">
         <v>49</v>
@@ -1743,10 +1743,10 @@
         <v>61.22448979591837</v>
       </c>
       <c r="S11" t="n">
-        <v>51.94286231293403</v>
+        <v>51.82512290948034</v>
       </c>
       <c r="T11" t="n">
-        <v>9.281627482984341</v>
+        <v>9.399366886438024</v>
       </c>
       <c r="U11" t="n">
         <v>47.24599944352045</v>
@@ -1758,19 +1758,19 @@
         <v>61.19402985074627</v>
       </c>
       <c r="X11" t="n">
-        <v>21.29068828859215</v>
+        <v>19.5857262818246</v>
       </c>
       <c r="Y11" t="n">
-        <v>10.75958800309605</v>
+        <v>11.5154323593755</v>
       </c>
       <c r="Z11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AA11" t="n">
-        <v>50</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.72981121511715</v>
+        <v>8.995558859822591</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C12" t="n">
-        <v>5.810414099555873</v>
+        <v>5.586965460526316</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,7 +1827,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %91.67: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>5</v>
       </c>
@@ -1835,25 +1839,25 @@
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>21.96388850532709</v>
+        <v>24.90100121795005</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1773049645390046</v>
+        <v>0.09208103130755596</v>
       </c>
       <c r="L12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M12" t="n">
-        <v>68.75</v>
+        <v>91.66666666666667</v>
       </c>
       <c r="N12" t="n">
-        <v>14.63099286473414</v>
+        <v>14.42416201834824</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>4.814159292035414</v>
+        <v>4.903403863845446</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1916,10 +1920,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1688619468664435</v>
+        <v>0.1685855263157895</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1951,7 @@
         <v>47.07727092024744</v>
       </c>
       <c r="K13" t="n">
-        <v>4.563046989243436</v>
+        <v>4.391881279246679</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
@@ -1958,7 +1962,7 @@
         <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>1.374245540974339</v>
+        <v>1.540463397198133</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1983,7 +1987,7 @@
         <v>20.61663781635479</v>
       </c>
       <c r="Y13" t="n">
-        <v>13.30959900536591</v>
+        <v>13.45150787722269</v>
       </c>
       <c r="Z13" t="n">
         <v>2</v>
@@ -2015,14 +2019,14 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C14" t="n">
-        <v>8.83902817445712</v>
+        <v>8.629728618421053</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2032,7 +2036,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -2078,37 +2082,37 @@
         <v>16.11612055393703</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.826988480148983</v>
+        <v>4.151629528947365</v>
       </c>
       <c r="Z14" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AA14" t="n">
-        <v>50</v>
+        <v>37.03703703703704</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.58856214112849</v>
+        <v>12.88432945699038</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.1762312443843395</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AF14" t="n">
-        <v>52.63157894736842</v>
+        <v>54.05405405405406</v>
       </c>
       <c r="AG14" t="n">
-        <v>26.88536957101867</v>
+        <v>27.02641559546062</v>
       </c>
       <c r="AH14" t="n">
-        <v>25.74620937634975</v>
+        <v>27.02763845859343</v>
       </c>
       <c r="AI14" t="n">
-        <v>37.25897138449667</v>
+        <v>38.38404689217949</v>
       </c>
       <c r="AJ14" t="n">
         <v>43</v>
@@ -2124,10 +2128,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C15" t="n">
-        <v>14.03754910777658</v>
+        <v>13.3532072368421</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2152,25 +2156,25 @@
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>11.58980989616802</v>
+        <v>15.72365931533905</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4415011037527616</v>
+        <v>0.2314814814814659</v>
       </c>
       <c r="L15" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="M15" t="n">
-        <v>57.14285714285715</v>
+        <v>65.625</v>
       </c>
       <c r="N15" t="n">
-        <v>19.87042946503383</v>
+        <v>17.37827400492326</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>7.525274725274733</v>
+        <v>7.750577367205569</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2194,20 +2198,16 @@
         <v>80.43478260869566</v>
       </c>
       <c r="X15" t="n">
-        <v>41.12870069280461</v>
+        <v>36.34743205418309</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.1994779310297</v>
+        <v>15.52857519338381</v>
       </c>
       <c r="Z15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>8.377386456231811</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
@@ -2243,10 +2243,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C16" t="n">
-        <v>34.73907757221193</v>
+        <v>34.27220394736842</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,22 +2274,22 @@
         <v>16.99349200873118</v>
       </c>
       <c r="K16" t="n">
-        <v>3.416497834765786</v>
+        <v>2.026638385781476</v>
       </c>
       <c r="L16" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M16" t="n">
-        <v>68.85245901639344</v>
+        <v>66.17647058823529</v>
       </c>
       <c r="N16" t="n">
-        <v>16.44345666370971</v>
+        <v>18.05819349894421</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>6.366007651654426</v>
+        <v>7.814980225134716</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3928457044583169</v>
+        <v>0.3834292763157894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,10 +2380,10 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>50.10974524047206</v>
+        <v>50.84308925225287</v>
       </c>
       <c r="K17" t="n">
-        <v>1.058205100641163</v>
+        <v>0.1073537305421368</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2394,7 +2394,7 @@
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>6.869105672761244</v>
+        <v>7.884182305630039</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2412,10 +2412,10 @@
         <v>50.77005884206276</v>
       </c>
       <c r="V17" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="W17" t="n">
-        <v>73.03370786516854</v>
+        <v>73.86363636363636</v>
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
@@ -2457,14 +2457,14 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C18" t="n">
-        <v>0.07651235619348767</v>
+        <v>0.0756578947368421</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2488,22 +2488,22 @@
         <v>31.38464440531301</v>
       </c>
       <c r="K18" t="n">
-        <v>2.361490538852684</v>
+        <v>1.21835559096195</v>
       </c>
       <c r="L18" t="n">
         <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="N18" t="n">
-        <v>15.12169699331323</v>
+        <v>7.773339325178243</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>7.462288230599801</v>
+        <v>8.675940601649334</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2530,22 +2530,22 @@
         <v>11.24971294890111</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.989434016904795</v>
+        <v>9.016973700010134</v>
       </c>
       <c r="Z18" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AA18" t="n">
-        <v>52.38095238095238</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="AB18" t="n">
-        <v>12.65459099545795</v>
+        <v>13.08681286252515</v>
       </c>
       <c r="AC18" t="n">
         <v>8</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.01148344538728363</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>36</v>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0271495465555202</v>
+        <v>0.02734375</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2607,22 +2607,22 @@
         <v>10.11859020594628</v>
       </c>
       <c r="K19" t="n">
-        <v>1.912178266167874</v>
+        <v>2.641166354910185</v>
       </c>
       <c r="L19" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="M19" t="n">
-        <v>50</v>
+        <v>39.28571428571428</v>
       </c>
       <c r="N19" t="n">
-        <v>20.25961926302971</v>
+        <v>17.40676917955083</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>7.936069929453238</v>
+        <v>7.169475860830166</v>
       </c>
       <c r="Q19" t="n">
         <v>14</v>
@@ -2649,22 +2649,22 @@
         <v>20.26411217973316</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.399897422539105</v>
+        <v>7.744672651146778</v>
       </c>
       <c r="Z19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA19" t="n">
-        <v>61.53846153846154</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB19" t="n">
-        <v>12.91319905850556</v>
+        <v>12.39536789924539</v>
       </c>
       <c r="AC19" t="n">
         <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.746834918779461</v>
+        <v>2.444658117492715</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C20" t="n">
-        <v>1.658796127501291</v>
+        <v>1.581003289473684</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,22 +2726,22 @@
         <v>18.49305897009618</v>
       </c>
       <c r="K20" t="n">
-        <v>6.42522857784138</v>
+        <v>1.434186923266156</v>
       </c>
       <c r="L20" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M20" t="n">
-        <v>61.53846153846154</v>
+        <v>59.375</v>
       </c>
       <c r="N20" t="n">
-        <v>10.71505126365717</v>
+        <v>15.26272061275122</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>3.35895113398228</v>
+        <v>8.444700289473218</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9222618375067166</v>
+        <v>0.9099506578947368</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2916519424174536</v>
+        <v>0.2958470394736842</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2931,25 +2931,25 @@
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>20.51421528613189</v>
+        <v>20.50947529336879</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1.432342868683434</v>
       </c>
       <c r="L22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M22" t="n">
-        <v>72.22222222222223</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N22" t="n">
-        <v>14.69752885316862</v>
+        <v>14.42455347331679</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>10.00000000000001</v>
+        <v>8.446671829722451</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6059284744330443</v>
+        <v>0.5995065789473684</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,10 +3032,10 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>40.79274007167037</v>
+        <v>41.01997583737742</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7523916269852826</v>
+        <v>0.06863417982152509</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -3046,7 +3046,7 @@
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.215888381826804</v>
+        <v>4.927983539094671</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3109,10 +3109,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1604291365681929</v>
+        <v>0.1587171052631579</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,22 +3140,22 @@
         <v>23.31817459365587</v>
       </c>
       <c r="K24" t="n">
-        <v>6.075526593795466</v>
+        <v>4.943533826699475</v>
       </c>
       <c r="L24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M24" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N24" t="n">
-        <v>12.2081847296207</v>
+        <v>12.45279767872284</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>3.699697312116945</v>
+        <v>4.818273207428514</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3182,16 +3182,16 @@
         <v>17.82705440547527</v>
       </c>
       <c r="Y24" t="n">
-        <v>9.973539499035233</v>
+        <v>10.9342634794553</v>
       </c>
       <c r="Z24" t="n">
         <v>10</v>
       </c>
       <c r="AA24" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AB24" t="n">
-        <v>16.40635689394259</v>
+        <v>14.00127512333066</v>
       </c>
       <c r="AC24" t="n">
         <v>2</v>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C25" t="n">
-        <v>3.356671020622143</v>
+        <v>3.338815789473684</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3259,22 +3259,22 @@
         <v>20.95143919294578</v>
       </c>
       <c r="K25" t="n">
-        <v>2.176768943002494</v>
+        <v>1.633257286283185</v>
       </c>
       <c r="L25" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M25" t="n">
-        <v>52.94117647058823</v>
+        <v>50</v>
       </c>
       <c r="N25" t="n">
-        <v>19.74294086415057</v>
+        <v>18.90967598469118</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>5.699173224244247</v>
+        <v>6.264428479137307</v>
       </c>
       <c r="Q25" t="n">
         <v>44</v>
@@ -3292,10 +3292,10 @@
         <v>53.44310393781777</v>
       </c>
       <c r="V25" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="W25" t="n">
-        <v>76.92307692307692</v>
+        <v>76.62337662337663</v>
       </c>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4471447829661926</v>
+        <v>0.4424342105263158</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3391,31 +3391,31 @@
         <v>45.25440735307745</v>
       </c>
       <c r="V26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="W26" t="n">
-        <v>66.10169491525424</v>
+        <v>67.24137931034483</v>
       </c>
       <c r="X26" t="n">
         <v>11.40992936035117</v>
       </c>
       <c r="Y26" t="n">
-        <v>6.122877268883253</v>
+        <v>7.111852213729186</v>
       </c>
       <c r="Z26" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AA26" t="n">
-        <v>47.05882352941177</v>
+        <v>50</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.649827332319148</v>
+        <v>9.770743011220027</v>
       </c>
       <c r="AC26" t="n">
         <v>10</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.129997403330754</v>
+        <v>3.109274816111351</v>
       </c>
       <c r="AE26" t="n">
         <v>36</v>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C27" t="n">
-        <v>53.57921674103734</v>
+        <v>53.86513157894737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3496,23 +3496,25 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>62.54252887592284</v>
+        <v>64.65730861892453</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>0.7575757575757569</v>
       </c>
       <c r="Z27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="inlineStr"/>
+        <v>14.28571428571429</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>5.328374938728119</v>
+      </c>
       <c r="AC27" t="n">
         <v>6</v>
       </c>
       <c r="AD27" t="n">
-        <v>6.000000000000005</v>
+        <v>5.28244274809161</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3533,14 +3535,14 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C28" t="n">
-        <v>1.428436253070415</v>
+        <v>1.403166118421053</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3550,7 +3552,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3561,25 +3563,25 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>14.7586636560711</v>
+        <v>16.51202083781934</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>0.2939015429830993</v>
       </c>
       <c r="L28" t="n">
         <v>50</v>
       </c>
       <c r="M28" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="N28" t="n">
-        <v>13.24016720455243</v>
+        <v>13.90399291760403</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.000000000000002</v>
+        <v>1.701098901098907</v>
       </c>
       <c r="Q28" t="n">
         <v>39</v>
@@ -3602,23 +3604,17 @@
       <c r="W28" t="n">
         <v>66.12903225806451</v>
       </c>
-      <c r="X28" t="n">
-        <v>19.25959158767157</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>14.7586636560711</v>
-      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
         <v>6</v>
       </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="n">
         <v>46</v>
       </c>
@@ -3648,10 +3644,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4175270860356442</v>
+        <v>0.4272203947368421</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3679,7 +3675,7 @@
         <v>27.65210909859499</v>
       </c>
       <c r="K29" t="n">
-        <v>26.08247798068617</v>
+        <v>29.00960875077097</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3714,25 +3710,25 @@
         <v>80</v>
       </c>
       <c r="X29" t="n">
-        <v>31.1754749041741</v>
+        <v>31.18329731926355</v>
       </c>
       <c r="Y29" t="n">
-        <v>3.882583178912413</v>
+        <v>1.656985769463037</v>
       </c>
       <c r="Z29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA29" t="n">
-        <v>22.22222222222222</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="AB29" t="n">
-        <v>13.76339599716079</v>
+        <v>19.10029836259243</v>
       </c>
       <c r="AC29" t="n">
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>6.364524790001913</v>
+        <v>8.483586044026637</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3763,24 +3759,24 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4232860945275282</v>
+        <v>0.412828947368421</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3790,17 +3786,27 @@
       <c r="I30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>11.08966243761319</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.09970089730808596</v>
+      </c>
       <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="M30" t="n">
+        <v>44.82758620689656</v>
+      </c>
+      <c r="N30" t="n">
+        <v>13.60110875801091</v>
+      </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
-      <c r="P30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>4.895418326693224</v>
+      </c>
       <c r="Q30" t="n">
         <v>48</v>
       </c>
@@ -3826,43 +3832,43 @@
         <v>26.71344279693404</v>
       </c>
       <c r="Y30" t="n">
-        <v>8.746632875998406</v>
+        <v>11.00101803326385</v>
       </c>
       <c r="Z30" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AA30" t="n">
-        <v>64.28571428571429</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="AB30" t="n">
-        <v>15.51985827645638</v>
+        <v>16.0019560318442</v>
       </c>
       <c r="AC30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.373502330383525</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="AF30" t="n">
-        <v>58.69565217391305</v>
+        <v>58.53658536585366</v>
       </c>
       <c r="AG30" t="n">
-        <v>41.16919076561428</v>
+        <v>40.08867490531909</v>
       </c>
       <c r="AH30" t="n">
-        <v>17.52646140829876</v>
+        <v>18.44791046053457</v>
       </c>
       <c r="AI30" t="n">
-        <v>44.33949777984616</v>
+        <v>43.36710313403013</v>
       </c>
       <c r="AJ30" t="n">
         <v>63</v>
       </c>
       <c r="AK30" t="n">
-        <v>58.73015873015873</v>
+        <v>52.38095238095238</v>
       </c>
     </row>
     <row r="31">
@@ -3872,10 +3878,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2550411774390636</v>
+        <v>0.2571957236842105</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3932,25 +3938,25 @@
         <v>88.88888888888889</v>
       </c>
       <c r="X31" t="n">
-        <v>46.70198753624732</v>
+        <v>50.77283370106378</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.1610342984796564</v>
+        <v>2.036021926389975</v>
       </c>
       <c r="Z31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA31" t="n">
-        <v>66.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="AB31" t="n">
-        <v>13.1925943754797</v>
+        <v>11.83810352260999</v>
       </c>
       <c r="AC31" t="n">
         <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>9.854835366519143</v>
+        <v>8.129496402877701</v>
       </c>
       <c r="AE31" t="n">
         <v>10</v>
@@ -3981,10 +3987,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C32" t="n">
-        <v>2.350903891330971</v>
+        <v>2.335526315789473</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4044,22 +4050,22 @@
         <v>13.38656892008534</v>
       </c>
       <c r="Y32" t="n">
-        <v>4.865501891842894</v>
+        <v>5.487789317821989</v>
       </c>
       <c r="Z32" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AA32" t="n">
-        <v>30.76923076923077</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.795855975533653</v>
+        <v>11.60016728532967</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.29480700533421</v>
+        <v>2.658080542233821</v>
       </c>
       <c r="AE32" t="n">
         <v>26</v>
@@ -4090,10 +4096,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C33" t="n">
-        <v>1.836707953317177</v>
+        <v>1.794819078947368</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4153,22 +4159,22 @@
         <v>15.09663082780621</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.619212421329487</v>
+        <v>4.840127058056975</v>
       </c>
       <c r="Z33" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="AA33" t="n">
-        <v>33.33333333333334</v>
+        <v>34.21052631578947</v>
       </c>
       <c r="AB33" t="n">
-        <v>12.37741275254759</v>
+        <v>10.78870747941093</v>
       </c>
       <c r="AC33" t="n">
         <v>8</v>
       </c>
       <c r="AD33" t="n">
-        <v>5.525512488100959</v>
+        <v>3.320593906079361</v>
       </c>
       <c r="AE33" t="n">
         <v>29</v>
@@ -4199,10 +4205,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7992661785950224</v>
+        <v>0.8001644736842105</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4230,16 +4236,16 @@
         <v>15.41713612942789</v>
       </c>
       <c r="K34" t="n">
-        <v>6.32506665416892</v>
+        <v>6.444565374108424</v>
       </c>
       <c r="L34" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M34" t="n">
-        <v>59.375</v>
+        <v>63.33333333333334</v>
       </c>
       <c r="N34" t="n">
-        <v>13.2905720570966</v>
+        <v>12.85729889708578</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4272,7 +4278,7 @@
         <v>10.81830054752258</v>
       </c>
       <c r="Y34" t="n">
-        <v>4.054595559716978</v>
+        <v>3.946762539945792</v>
       </c>
       <c r="Z34" t="n">
         <v>34</v>
@@ -4281,7 +4287,7 @@
         <v>35.29411764705883</v>
       </c>
       <c r="AB34" t="n">
-        <v>9.769890717174794</v>
+        <v>9.854642237875723</v>
       </c>
       <c r="AC34" t="n">
         <v>2</v>
@@ -4296,10 +4302,10 @@
         <v>57.57575757575758</v>
       </c>
       <c r="AG34" t="n">
-        <v>22.71196365752987</v>
+        <v>22.73879956671873</v>
       </c>
       <c r="AH34" t="n">
-        <v>34.8637939182277</v>
+        <v>34.83695800903885</v>
       </c>
       <c r="AI34" t="n">
         <v>40.80726333731245</v>
@@ -4318,10 +4324,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C35" t="n">
-        <v>1.480884301479727</v>
+        <v>1.476151315789474</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4349,7 +4355,7 @@
         <v>38.83766461406507</v>
       </c>
       <c r="K35" t="n">
-        <v>6.877502595080576</v>
+        <v>6.535916361850158</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
@@ -4387,13 +4393,13 @@
         <v>13.94161507705984</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.199765096538035</v>
+        <v>6.499555680513347</v>
       </c>
       <c r="Z35" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA35" t="n">
-        <v>52.94117647058823</v>
+        <v>56.25</v>
       </c>
       <c r="AB35" t="n">
         <v>11.96300134878404</v>
@@ -4433,10 +4439,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07836345971923196</v>
+        <v>0.07874177631578948</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4464,22 +4470,22 @@
         <v>11.49958181785439</v>
       </c>
       <c r="K36" t="n">
-        <v>1.474187044815189</v>
+        <v>1.964075689583811</v>
       </c>
       <c r="L36" t="n">
         <v>39</v>
       </c>
       <c r="M36" t="n">
-        <v>66.66666666666667</v>
+        <v>58.97435897435897</v>
       </c>
       <c r="N36" t="n">
-        <v>17.10540519030475</v>
+        <v>18.13013090931801</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>0.5181740997369122</v>
+        <v>0.03523232096522833</v>
       </c>
       <c r="Q36" t="n">
         <v>10</v>
@@ -4542,10 +4548,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C37" t="n">
-        <v>0.05944105249117834</v>
+        <v>0.05736019736842105</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4570,25 +4576,25 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>19.28293279472178</v>
+        <v>22.69029993401852</v>
       </c>
       <c r="K37" t="n">
-        <v>0.6968714552807898</v>
+        <v>1.454545454545464</v>
       </c>
       <c r="L37" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="M37" t="n">
-        <v>60.3448275862069</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N37" t="n">
-        <v>17.50894189590544</v>
+        <v>14.7166222045367</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>9.238746358520888</v>
+        <v>8.422939068100366</v>
       </c>
       <c r="Q37" t="n">
         <v>30</v>
@@ -4651,10 +4657,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C38" t="n">
-        <v>1.681420717305107</v>
+        <v>1.658100328947369</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4714,22 +4720,22 @@
         <v>12.11239445105858</v>
       </c>
       <c r="Y38" t="n">
-        <v>3.963626921394792</v>
+        <v>5.29559904093142</v>
       </c>
       <c r="Z38" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="AA38" t="n">
-        <v>46.93877551020408</v>
+        <v>43.90243902439025</v>
       </c>
       <c r="AB38" t="n">
-        <v>11.9668255635051</v>
+        <v>12.25836751823044</v>
       </c>
       <c r="AC38" t="n">
         <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>6.285507131412038</v>
+        <v>4.967457595874381</v>
       </c>
       <c r="AE38" t="n">
         <v>30</v>
@@ -4738,10 +4744,10 @@
         <v>56.66666666666666</v>
       </c>
       <c r="AG38" t="n">
-        <v>15.89260833039586</v>
+        <v>15.76102938302744</v>
       </c>
       <c r="AH38" t="n">
-        <v>40.7740583362708</v>
+        <v>40.90563728363922</v>
       </c>
       <c r="AI38" t="n">
         <v>39.19730700081361</v>
@@ -4760,10 +4766,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C39" t="n">
-        <v>2.754033318538072</v>
+        <v>2.699424342105263</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4823,22 +4829,22 @@
         <v>10.27889366548247</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.49711270603914</v>
+        <v>5.410642169339663</v>
       </c>
       <c r="Z39" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AA39" t="n">
-        <v>39.47368421052632</v>
+        <v>48.27586206896552</v>
       </c>
       <c r="AB39" t="n">
-        <v>13.64670841558058</v>
+        <v>10.52661733838753</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.593587989068902</v>
+        <v>0.6230699141815177</v>
       </c>
       <c r="AE39" t="n">
         <v>40</v>
@@ -4847,19 +4853,19 @@
         <v>60</v>
       </c>
       <c r="AG39" t="n">
-        <v>40.53816623440648</v>
+        <v>40.3540954710737</v>
       </c>
       <c r="AH39" t="n">
-        <v>19.46183376559352</v>
+        <v>19.6459045289263</v>
       </c>
       <c r="AI39" t="n">
         <v>44.59589366034619</v>
       </c>
       <c r="AJ39" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AK39" t="n">
-        <v>57.57575757575758</v>
+        <v>56.92307692307692</v>
       </c>
     </row>
     <row r="40">
@@ -4869,10 +4875,10 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2406436950825665</v>
+        <v>0.2347861842105263</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4900,16 +4906,16 @@
         <v>15.29580504962521</v>
       </c>
       <c r="K40" t="n">
-        <v>7.8108224347333</v>
+        <v>5.186598000686238</v>
       </c>
       <c r="L40" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M40" t="n">
-        <v>73.68421052631579</v>
+        <v>72</v>
       </c>
       <c r="N40" t="n">
-        <v>13.44349228041417</v>
+        <v>13.29470523336766</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -4918,40 +4924,40 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R40" t="n">
-        <v>82.14285714285714</v>
+        <v>82.75862068965517</v>
       </c>
       <c r="S40" t="n">
-        <v>47.08446016613533</v>
+        <v>47.35740981557894</v>
       </c>
       <c r="T40" t="n">
-        <v>35.05839697672181</v>
+        <v>35.40121087407623</v>
       </c>
       <c r="U40" t="n">
-        <v>64.40857521065705</v>
+        <v>65.45156010980476</v>
       </c>
       <c r="V40" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W40" t="n">
-        <v>77.14285714285714</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="X40" t="n">
         <v>37.29449902814472</v>
       </c>
       <c r="Y40" t="n">
-        <v>8.679710787281103</v>
+        <v>10.9025389678317</v>
       </c>
       <c r="Z40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA40" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AB40" t="n">
-        <v>16.01331603323763</v>
+        <v>13.7765185983196</v>
       </c>
       <c r="AC40" t="n">
         <v>5</v>
@@ -4988,10 +4994,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C41" t="n">
-        <v>1.256694841036921</v>
+        <v>1.251027960526316</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5019,7 +5025,7 @@
         <v>40.38073481248902</v>
       </c>
       <c r="K41" t="n">
-        <v>4.379324925818295</v>
+        <v>3.908641715529781</v>
       </c>
       <c r="L41" t="n">
         <v>3</v>
@@ -5028,13 +5034,13 @@
         <v>66.66666666666667</v>
       </c>
       <c r="N41" t="n">
-        <v>20.46121479619964</v>
+        <v>21.27827544303003</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>5.384854786305904</v>
+        <v>5.862224915947323</v>
       </c>
       <c r="Q41" t="n">
         <v>11</v>
@@ -5061,16 +5067,16 @@
         <v>14.15095011586145</v>
       </c>
       <c r="Y41" t="n">
-        <v>8.560266191499155</v>
+        <v>8.972600219214899</v>
       </c>
       <c r="Z41" t="n">
         <v>25</v>
       </c>
       <c r="AA41" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB41" t="n">
-        <v>14.44518067703431</v>
+        <v>14.29560451668042</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
@@ -5107,14 +5113,14 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C42" t="n">
-        <v>3.512986711242145</v>
+        <v>3.472450657894737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5124,7 +5130,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -5138,16 +5144,16 @@
         <v>17.9384880883827</v>
       </c>
       <c r="K42" t="n">
-        <v>10.69199898336826</v>
+        <v>9.414733469792047</v>
       </c>
       <c r="L42" t="n">
         <v>5</v>
       </c>
       <c r="M42" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N42" t="n">
-        <v>9.959430284360081</v>
+        <v>9.440541403262504</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
@@ -5175,21 +5181,25 @@
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="n">
-        <v>23.7260422361657</v>
+        <v>23.05415424937474</v>
       </c>
       <c r="Y42" t="n">
-        <v>9.16447206905595</v>
+        <v>10.21261546062227</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>9.963868928768417</v>
+      </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.9198250398007701</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5218,10 +5228,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C43" t="n">
-        <v>6.067512068562769</v>
+        <v>6.183182565789473</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,11 +5248,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>5</v>
       </c>
@@ -5253,22 +5259,22 @@
         <v>20.13868121382601</v>
       </c>
       <c r="K43" t="n">
-        <v>1.279516626403687</v>
+        <v>3.210300103169206</v>
       </c>
       <c r="L43" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M43" t="n">
-        <v>77.77777777777777</v>
+        <v>62.5</v>
       </c>
       <c r="N43" t="n">
-        <v>18.20199884422525</v>
+        <v>23.3116765368109</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.686114097119496</v>
+        <v>0.7651367121705999</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5331,10 +5337,10 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C44" t="n">
-        <v>4.827271403341594</v>
+        <v>4.814967105263158</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5362,7 +5368,7 @@
         <v>25.31049029846984</v>
       </c>
       <c r="K44" t="n">
-        <v>25.69047136733174</v>
+        <v>25.37009720642329</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5397,25 +5403,25 @@
         <v>50</v>
       </c>
       <c r="X44" t="n">
-        <v>28.15394364051107</v>
+        <v>28.16158587198183</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.922275821717745</v>
+        <v>2.178100907979474</v>
       </c>
       <c r="Z44" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA44" t="n">
-        <v>46.15384615384615</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="AB44" t="n">
-        <v>14.80772746396136</v>
+        <v>13.79357295589038</v>
       </c>
       <c r="AC44" t="n">
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>8.236043654111358</v>
+        <v>7.996061377486141</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5438,10 +5444,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02077351569007891</v>
+        <v>0.02076480263157895</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5466,25 +5472,25 @@
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>15.15550562104173</v>
+        <v>15.42186418347916</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7251705392521623</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M45" t="n">
-        <v>64.86486486486487</v>
+        <v>57.53424657534246</v>
       </c>
       <c r="N45" t="n">
-        <v>13.77033218132339</v>
+        <v>14.41603372498879</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>9.208055356067613</v>
+        <v>8.910891089108919</v>
       </c>
       <c r="Q45" t="n">
         <v>38</v>
@@ -5502,25 +5508,25 @@
         <v>47.28395955700901</v>
       </c>
       <c r="V45" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="W45" t="n">
-        <v>61.22448979591837</v>
+        <v>61.85567010309278</v>
       </c>
       <c r="X45" t="n">
-        <v>20.3749963300697</v>
+        <v>19.20467487893223</v>
       </c>
       <c r="Y45" t="n">
-        <v>14.54023834362808</v>
+        <v>14.57608282531396</v>
       </c>
       <c r="Z45" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA45" t="n">
-        <v>42.85714285714285</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB45" t="n">
-        <v>9.005922820261524</v>
+        <v>12.33518822913915</v>
       </c>
       <c r="AC45" t="n">
         <v>5</v>
@@ -5557,10 +5563,10 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C46" t="n">
-        <v>9.846852212964155</v>
+        <v>9.652549342105264</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5569,7 +5575,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5584,17 +5590,27 @@
       <c r="I46" t="n">
         <v>10</v>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="J46" t="n">
+        <v>11.2215464940971</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.3205128205128194</v>
+      </c>
       <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="M46" t="n">
+        <v>52.30769230769231</v>
+      </c>
+      <c r="N46" t="n">
+        <v>15.60882143722779</v>
+      </c>
       <c r="O46" t="n">
         <v>8</v>
       </c>
-      <c r="P46" t="inlineStr"/>
+      <c r="P46" t="n">
+        <v>7.654952076677324</v>
+      </c>
       <c r="Q46" t="n">
         <v>51</v>
       </c>
@@ -5611,25 +5627,25 @@
         <v>47.08515898394834</v>
       </c>
       <c r="V46" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="W46" t="n">
-        <v>65.47619047619048</v>
+        <v>65.06024096385542</v>
       </c>
       <c r="X46" t="n">
-        <v>27.45411700532656</v>
+        <v>26.79655122306823</v>
       </c>
       <c r="Y46" t="n">
-        <v>9.14418917746559</v>
+        <v>10.93700016875766</v>
       </c>
       <c r="Z46" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AA46" t="n">
-        <v>50</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB46" t="n">
-        <v>17.001466400711</v>
+        <v>14.8915289459438</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
@@ -5666,10 +5682,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9683338281067196</v>
+        <v>0.9617598684210527</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5694,25 +5710,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>14.27598504123684</v>
+        <v>14.78818728107186</v>
       </c>
       <c r="K47" t="n">
-        <v>0.6413062373320733</v>
+        <v>0.5588993981083368</v>
       </c>
       <c r="L47" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="M47" t="n">
-        <v>56.92307692307692</v>
+        <v>57.37704918032787</v>
       </c>
       <c r="N47" t="n">
-        <v>14.40511994186442</v>
+        <v>15.95273903714644</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>9.299058321638132</v>
+        <v>9.388627618640456</v>
       </c>
       <c r="Q47" t="n">
         <v>51</v>
@@ -5730,16 +5746,16 @@
         <v>61.13171816155626</v>
       </c>
       <c r="V47" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="W47" t="n">
-        <v>72.85714285714286</v>
+        <v>72.46376811594203</v>
       </c>
       <c r="X47" t="n">
         <v>66.65983471422588</v>
       </c>
       <c r="Y47" t="n">
-        <v>13.72623158641482</v>
+        <v>14.31193897266858</v>
       </c>
       <c r="Z47" t="n">
         <v>1</v>
@@ -5759,10 +5775,10 @@
         <v>53.65853658536585</v>
       </c>
       <c r="AG47" t="n">
-        <v>31.32339341687716</v>
+        <v>31.00855848715134</v>
       </c>
       <c r="AH47" t="n">
-        <v>22.33514316848869</v>
+        <v>22.64997809821451</v>
       </c>
       <c r="AI47" t="n">
         <v>38.74647126766948</v>
@@ -5781,10 +5797,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05841265670726162</v>
+        <v>0.05859375</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5809,25 +5825,25 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>10.38709782320051</v>
+        <v>10.38175391788048</v>
       </c>
       <c r="K48" t="n">
-        <v>2.898547836588961</v>
+        <v>3.211403269674484</v>
       </c>
       <c r="L48" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M48" t="n">
-        <v>53.57142857142857</v>
+        <v>60.37735849056604</v>
       </c>
       <c r="N48" t="n">
-        <v>16.25360952265471</v>
+        <v>15.86771086172708</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>6.901411451101058</v>
+        <v>6.577370828481066</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5836,34 +5852,34 @@
         <v>63.82978723404256</v>
       </c>
       <c r="S48" t="n">
-        <v>48.3518668777986</v>
+        <v>48.36559371376292</v>
       </c>
       <c r="T48" t="n">
-        <v>15.47792035624396</v>
+        <v>15.46419352027964</v>
       </c>
       <c r="U48" t="n">
         <v>49.53589653479511</v>
       </c>
       <c r="V48" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="W48" t="n">
-        <v>71.60493827160494</v>
+        <v>72.5</v>
       </c>
       <c r="X48" t="n">
         <v>19.37342145735985</v>
       </c>
       <c r="Y48" t="n">
-        <v>7.789624985850308</v>
+        <v>7.503750632974371</v>
       </c>
       <c r="Z48" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA48" t="n">
-        <v>61.11111111111111</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="AB48" t="n">
-        <v>14.06492007635003</v>
+        <v>14.38574514248125</v>
       </c>
       <c r="AC48" t="n">
         <v>6</v>
@@ -5900,10 +5916,10 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C49" t="n">
-        <v>0.284658874369612</v>
+        <v>0.2804276315789474</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5963,37 +5979,37 @@
         <v>22.46912765663718</v>
       </c>
       <c r="Y49" t="n">
-        <v>6.471514461930439</v>
+        <v>7.861745948762255</v>
       </c>
       <c r="Z49" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AA49" t="n">
-        <v>50</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="AB49" t="n">
-        <v>9.058713821243058</v>
+        <v>9.63685023892678</v>
       </c>
       <c r="AC49" t="n">
         <v>10</v>
       </c>
       <c r="AD49" t="n">
-        <v>3.772631961022543</v>
+        <v>2.320701725093111</v>
       </c>
       <c r="AE49" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AF49" t="n">
-        <v>62.22222222222222</v>
+        <v>61.36363636363637</v>
       </c>
       <c r="AG49" t="n">
-        <v>35.7721257339705</v>
+        <v>34.894538479918</v>
       </c>
       <c r="AH49" t="n">
-        <v>26.45009648825172</v>
+        <v>26.46909788371836</v>
       </c>
       <c r="AI49" t="n">
-        <v>47.62993448088954</v>
+        <v>46.62357539237828</v>
       </c>
       <c r="AJ49" t="n">
         <v>65</v>
@@ -6009,10 +6025,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7190515807960791</v>
+        <v>0.7142269736842105</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6072,16 +6088,16 @@
         <v>15.51990994893744</v>
       </c>
       <c r="Y50" t="n">
-        <v>6.77509904503959</v>
+        <v>7.400608441253686</v>
       </c>
       <c r="Z50" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AA50" t="n">
-        <v>48.27586206896552</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="AB50" t="n">
-        <v>12.49614700114313</v>
+        <v>12.16127348655176</v>
       </c>
       <c r="AC50" t="n">
         <v>5</v>
@@ -6118,24 +6134,24 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1398612990476411</v>
+        <v>0.1381578947368421</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -6149,22 +6165,22 @@
         <v>31.62908307640215</v>
       </c>
       <c r="K51" t="n">
-        <v>5.015024541403945</v>
+        <v>3.736021366683273</v>
       </c>
       <c r="L51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M51" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N51" t="n">
-        <v>21.39549877456197</v>
+        <v>17.54885844674024</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>0.2544715228508965</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6191,22 +6207,22 @@
         <v>15.73461610040814</v>
       </c>
       <c r="Y51" t="n">
-        <v>9.262217234733095</v>
+        <v>10.36733445706099</v>
       </c>
       <c r="Z51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA51" t="n">
-        <v>40</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB51" t="n">
-        <v>11.6363761696779</v>
+        <v>12.74817222949423</v>
       </c>
       <c r="AC51" t="n">
         <v>10</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.8130932261982915</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
         <v>12</v>
@@ -6237,10 +6253,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C52" t="n">
-        <v>4.638047360884422</v>
+        <v>4.562088815789473</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6297,25 +6313,25 @@
         <v>67.9245283018868</v>
       </c>
       <c r="X52" t="n">
-        <v>17.68393155583896</v>
+        <v>16.62696858241317</v>
       </c>
       <c r="Y52" t="n">
-        <v>3.322944064671751</v>
+        <v>4.906250128952694</v>
       </c>
       <c r="Z52" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AA52" t="n">
-        <v>44.11764705882353</v>
+        <v>52</v>
       </c>
       <c r="AB52" t="n">
-        <v>10.21277776758257</v>
+        <v>13.44481707492098</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>4.837813781231548</v>
+        <v>3.253368255266631</v>
       </c>
       <c r="AE52" t="n">
         <v>37</v>
@@ -6324,10 +6340,10 @@
         <v>67.56756756756756</v>
       </c>
       <c r="AG52" t="n">
-        <v>39.9823855685727</v>
+        <v>39.84536943155656</v>
       </c>
       <c r="AH52" t="n">
-        <v>27.58518199899486</v>
+        <v>27.722198136011</v>
       </c>
       <c r="AI52" t="n">
         <v>51.4636672419722</v>
@@ -6346,10 +6362,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C53" t="n">
-        <v>1.203218494952278</v>
+        <v>1.199629934210526</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6366,7 +6382,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H53" t="n">
         <v>5</v>
       </c>
@@ -6374,16 +6394,16 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>30.11005863776933</v>
+        <v>30.25899953214985</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1712302523633191</v>
+        <v>0.08576329331047017</v>
       </c>
       <c r="L53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M53" t="n">
-        <v>66.66666666666667</v>
+        <v>75</v>
       </c>
       <c r="N53" t="n">
         <v>12.24769996038692</v>
@@ -6392,7 +6412,7 @@
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>7.81538744000001</v>
+        <v>7.907455012853459</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6450,7 +6470,7 @@
         <v>46279</v>
       </c>
       <c r="C54" t="n">
-        <v>0.07157607498287688</v>
+        <v>0.07158034329423156</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6482,7 +6502,7 @@
         <v>29.5817777621179</v>
       </c>
       <c r="K54" t="n">
-        <v>14.03382702355649</v>
+        <v>14.04062722709962</v>
       </c>
       <c r="L54" t="n">
         <v>8</v>
@@ -6524,7 +6544,7 @@
         <v>14.75410024187049</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.6276666513840068</v>
+        <v>0.6217407598221314</v>
       </c>
       <c r="Z54" t="n">
         <v>30</v>
@@ -6539,7 +6559,7 @@
         <v>2</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.381001434072804</v>
+        <v>1.386882051180716</v>
       </c>
       <c r="AE54" t="n">
         <v>7</v>
@@ -6570,10 +6590,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9358366071851051</v>
+        <v>0.9387335526315789</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6633,7 +6653,7 @@
         <v>23.0932342837701</v>
       </c>
       <c r="Y55" t="n">
-        <v>6.371707756420708</v>
+        <v>6.081875051871988</v>
       </c>
       <c r="Z55" t="n">
         <v>23</v>
@@ -6657,10 +6677,10 @@
         <v>59.09090909090909</v>
       </c>
       <c r="AG55" t="n">
-        <v>39.21176783834306</v>
+        <v>39.06110949838082</v>
       </c>
       <c r="AH55" t="n">
-        <v>19.87914125256603</v>
+        <v>20.02979959252827</v>
       </c>
       <c r="AI55" t="n">
         <v>44.4097537410319</v>
@@ -6679,24 +6699,24 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C56" t="n">
-        <v>0.6968383572038798</v>
+        <v>0.6270559210526315</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -6707,13 +6727,13 @@
         <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>55.30631598314248</v>
+        <v>56.38408153574323</v>
       </c>
       <c r="K56" t="n">
-        <v>8.448773121982489</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
@@ -6721,7 +6741,7 @@
         <v>4</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>4.000000000000004</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -6736,12 +6756,8 @@
       <c r="W56" t="n">
         <v>100</v>
       </c>
-      <c r="X56" t="n">
-        <v>44.70154625822338</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>25.05348012767391</v>
-      </c>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
         <v>0</v>
       </c>
@@ -6750,9 +6766,7 @@
       <c r="AC56" t="n">
         <v>10</v>
       </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD56" t="inlineStr"/>
       <c r="AE56" t="n">
         <v>0</v>
       </c>
@@ -6761,10 +6775,10 @@
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="inlineStr"/>
       <c r="AJ56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK56" t="n">
-        <v>28.57142857142857</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="57">
@@ -6774,14 +6788,14 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C57" t="n">
-        <v>1.495281725012209</v>
+        <v>1.443256578947368</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6791,7 +6805,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -6837,22 +6851,22 @@
         <v>20.62560129901716</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.812329083419051</v>
+        <v>5.228560176031294</v>
       </c>
       <c r="Z57" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AA57" t="n">
-        <v>33.33333333333334</v>
+        <v>48.88888888888889</v>
       </c>
       <c r="AB57" t="n">
-        <v>15.38906972645917</v>
+        <v>13.42789464309919</v>
       </c>
       <c r="AC57" t="n">
         <v>5</v>
       </c>
       <c r="AD57" t="n">
-        <v>3.246508331264075</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
         <v>44</v>
@@ -6883,10 +6897,10 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C58" t="n">
-        <v>0.722753797925808</v>
+        <v>0.7232730263157895</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6903,7 +6917,11 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6914,16 +6932,16 @@
         <v>18.04392839464337</v>
       </c>
       <c r="K58" t="n">
-        <v>10.78071591093133</v>
+        <v>10.86030109322786</v>
       </c>
       <c r="L58" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M58" t="n">
-        <v>73.33333333333333</v>
+        <v>75</v>
       </c>
       <c r="N58" t="n">
-        <v>21.94783451677582</v>
+        <v>21.43269864112183</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
@@ -6956,16 +6974,16 @@
         <v>20.50322102897642</v>
       </c>
       <c r="Y58" t="n">
-        <v>8.068253308936201</v>
+        <v>8.002209279891204</v>
       </c>
       <c r="Z58" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA58" t="n">
-        <v>43.75</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="AB58" t="n">
-        <v>8.807341170160358</v>
+        <v>8.41957537447376</v>
       </c>
       <c r="AC58" t="n">
         <v>6</v>
@@ -7002,10 +7020,10 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7717052732323073</v>
+        <v>0.7619243421052632</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7033,22 +7051,22 @@
         <v>11.95882015364728</v>
       </c>
       <c r="K59" t="n">
-        <v>5.343201806311138</v>
+        <v>4.008035859790948</v>
       </c>
       <c r="L59" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="M59" t="n">
-        <v>73.17073170731707</v>
+        <v>72.91666666666667</v>
       </c>
       <c r="N59" t="n">
-        <v>12.12870417056454</v>
+        <v>12.54496914631846</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>2.522040481144461</v>
+        <v>3.838130493676917</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7111,10 +7129,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C60" t="n">
-        <v>11.07578050481712</v>
+        <v>10.87582236842105</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7131,7 +7149,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H60" t="n">
         <v>5</v>
       </c>
@@ -7142,22 +7164,22 @@
         <v>24.49246832941995</v>
       </c>
       <c r="K60" t="n">
-        <v>4.256356593803101</v>
+        <v>2.37415002941026</v>
       </c>
       <c r="L60" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M60" t="n">
-        <v>73.33333333333333</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N60" t="n">
-        <v>12.49400271589765</v>
+        <v>12.78067502005031</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>3.590805902399463</v>
+        <v>5.495381372127173</v>
       </c>
       <c r="Q60" t="n">
         <v>46</v>
@@ -7166,10 +7188,10 @@
         <v>65.21739130434783</v>
       </c>
       <c r="S60" t="n">
-        <v>52.22209604257147</v>
+        <v>52.31626103505344</v>
       </c>
       <c r="T60" t="n">
-        <v>12.99529526177636</v>
+        <v>12.90113026929439</v>
       </c>
       <c r="U60" t="n">
         <v>50.77005884206276</v>
@@ -7198,10 +7220,10 @@
         <v>62.5</v>
       </c>
       <c r="AG60" t="n">
-        <v>23.22819855873075</v>
+        <v>23.09901146722748</v>
       </c>
       <c r="AH60" t="n">
-        <v>39.27180144126925</v>
+        <v>39.40098853277252</v>
       </c>
       <c r="AI60" t="n">
         <v>45.25440735307745</v>
@@ -7220,19 +7242,19 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7922731107528591</v>
+        <v>0.7537006578947367</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7251,22 +7273,22 @@
         <v>14.0586191907223</v>
       </c>
       <c r="K61" t="n">
-        <v>10.97113593139507</v>
+        <v>5.5684170315216</v>
       </c>
       <c r="L61" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="M61" t="n">
-        <v>66.66666666666667</v>
+        <v>62.96296296296296</v>
       </c>
       <c r="N61" t="n">
-        <v>15.21675647587978</v>
+        <v>23.90189858170725</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>4.197830272623282</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
@@ -7293,16 +7315,16 @@
         <v>49.99145178651283</v>
       </c>
       <c r="Y61" t="n">
-        <v>4.629873480818558</v>
+        <v>9.273044704613643</v>
       </c>
       <c r="Z61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA61" t="n">
-        <v>50</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB61" t="n">
-        <v>13.92348961705937</v>
+        <v>14.40298598384542</v>
       </c>
       <c r="AC61" t="n">
         <v>4</v>
@@ -7339,10 +7361,10 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C62" t="n">
-        <v>9.018996752761947</v>
+        <v>8.88671875</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7402,22 +7424,22 @@
         <v>11.69351808836483</v>
       </c>
       <c r="Y62" t="n">
-        <v>3.491870513256423</v>
+        <v>4.907316484548996</v>
       </c>
       <c r="Z62" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="AA62" t="n">
-        <v>44.44444444444444</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AB62" t="n">
-        <v>14.74641715838048</v>
+        <v>16.86033419604064</v>
       </c>
       <c r="AC62" t="n">
         <v>5</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.562696836799371</v>
+        <v>0.09746650533418721</v>
       </c>
       <c r="AE62" t="n">
         <v>27</v>
@@ -7448,24 +7470,24 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1112719979010094</v>
+        <v>0.1097861842105263</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>AL_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>VERİ_YETERSİZ</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -7479,22 +7501,22 @@
         <v>14.68172212919103</v>
       </c>
       <c r="K63" t="n">
-        <v>6.289776628759602</v>
+        <v>4.870490480829592</v>
       </c>
       <c r="L63" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M63" t="n">
-        <v>70</v>
+        <v>56.25</v>
       </c>
       <c r="N63" t="n">
-        <v>13.72369998618861</v>
+        <v>14.52878225473388</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>0.1234947205611459</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7521,22 +7543,18 @@
         <v>24.85614965143601</v>
       </c>
       <c r="Y63" t="n">
-        <v>9.315393027612707</v>
+        <v>10.52630352708555</v>
       </c>
       <c r="Z63" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>12.72793373689106</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.7549318404122873</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -7567,10 +7585,10 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1482941093458917</v>
+        <v>0.149671052631579</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7595,25 +7613,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>10.62485037725133</v>
+        <v>10.61952064988008</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1388920869985544</v>
+        <v>1.062676940963181</v>
       </c>
       <c r="L64" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="M64" t="n">
-        <v>56.94444444444444</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N64" t="n">
-        <v>15.34087839849153</v>
+        <v>16.93272537747344</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.85436558333221</v>
+        <v>3.895921994364793</v>
       </c>
       <c r="Q64" t="n">
         <v>55</v>
@@ -7640,16 +7658,16 @@
         <v>14.28923074155179</v>
       </c>
       <c r="Y64" t="n">
-        <v>10.50071536668221</v>
+        <v>9.669694906103988</v>
       </c>
       <c r="Z64" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA64" t="n">
-        <v>54.54545454545455</v>
+        <v>55.88235294117647</v>
       </c>
       <c r="AB64" t="n">
-        <v>16.21570005940892</v>
+        <v>16.02637799751902</v>
       </c>
       <c r="AC64" t="n">
         <v>2</v>
@@ -7664,19 +7682,19 @@
         <v>65.21739130434783</v>
       </c>
       <c r="AG64" t="n">
-        <v>35.10227718069645</v>
+        <v>35.02591540028634</v>
       </c>
       <c r="AH64" t="n">
-        <v>30.11511412365138</v>
+        <v>30.19147590406148</v>
       </c>
       <c r="AI64" t="n">
         <v>50.77005884206276</v>
       </c>
       <c r="AJ64" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AK64" t="n">
-        <v>54.45544554455446</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65">
@@ -7686,10 +7704,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C65" t="n">
-        <v>6.448017062692977</v>
+        <v>6.352796052631579</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7749,16 +7767,16 @@
         <v>24.47056390537039</v>
       </c>
       <c r="Y65" t="n">
-        <v>8.557522147183249</v>
+        <v>9.907897777241793</v>
       </c>
       <c r="Z65" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA65" t="n">
-        <v>33.33333333333334</v>
+        <v>40</v>
       </c>
       <c r="AB65" t="n">
-        <v>11.44316310099862</v>
+        <v>12.5316772036164</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
@@ -7795,10 +7813,10 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4479675153894253</v>
+        <v>0.4432565789473684</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7826,22 +7844,22 @@
         <v>10.41136575766793</v>
       </c>
       <c r="K66" t="n">
-        <v>3.263139952578964</v>
+        <v>2.177199404633368</v>
       </c>
       <c r="L66" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="M66" t="n">
-        <v>51.11111111111111</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N66" t="n">
-        <v>22.18070974416615</v>
+        <v>17.66934610953342</v>
       </c>
       <c r="O66" t="n">
         <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>2.650374614482831</v>
+        <v>3.741344074452368</v>
       </c>
       <c r="Q66" t="n">
         <v>35</v>
@@ -7868,16 +7886,16 @@
         <v>14.59585890675015</v>
       </c>
       <c r="Y66" t="n">
-        <v>7.48796324073655</v>
+        <v>8.460842546324709</v>
       </c>
       <c r="Z66" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA66" t="n">
-        <v>50</v>
+        <v>44.82758620689656</v>
       </c>
       <c r="AB66" t="n">
-        <v>10.96998186648398</v>
+        <v>10.68423274679701</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
@@ -7886,25 +7904,25 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AF66" t="n">
-        <v>42.5</v>
+        <v>41.46341463414634</v>
       </c>
       <c r="AG66" t="n">
-        <v>40.7036290257951</v>
+        <v>40.07671124467814</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.796370974204898</v>
+        <v>1.386703389468195</v>
       </c>
       <c r="AI66" t="n">
-        <v>28.50939255995037</v>
+        <v>27.75654945425213</v>
       </c>
       <c r="AJ66" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK66" t="n">
-        <v>51.38888888888889</v>
+        <v>50.68493150684932</v>
       </c>
     </row>
     <row r="67">
@@ -7914,10 +7932,10 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0271495465555202</v>
+        <v>0.02713815789473684</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7945,7 +7963,7 @@
         <v>11.46300958938384</v>
       </c>
       <c r="K67" t="n">
-        <v>2.722647340115159</v>
+        <v>2.67955736132186</v>
       </c>
       <c r="L67" t="n">
         <v>5</v>
@@ -7954,13 +7972,13 @@
         <v>20</v>
       </c>
       <c r="N67" t="n">
-        <v>6.573256403145478</v>
+        <v>7.966768450054484</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>1.243496631911678</v>
+        <v>1.285983960791337</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -8003,10 +8021,10 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C68" t="n">
-        <v>1.73489706338975</v>
+        <v>1.561472039473684</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8031,7 +8049,7 @@
         <v>10</v>
       </c>
       <c r="J68" t="n">
-        <v>68.93103700549554</v>
+        <v>72.03677495621962</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -8108,19 +8126,19 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4705921051932408</v>
+        <v>0.4609375000000001</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -8135,17 +8153,27 @@
       <c r="I69" t="n">
         <v>10</v>
       </c>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
+      <c r="J69" t="n">
+        <v>17.83849147064036</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.7187780772686558</v>
+      </c>
       <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="M69" t="n">
+        <v>70.83333333333333</v>
+      </c>
+      <c r="N69" t="n">
+        <v>19.56180727983456</v>
+      </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
-      <c r="P69" t="inlineStr"/>
+      <c r="P69" t="n">
+        <v>7.229259589652082</v>
+      </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
@@ -8160,10 +8188,10 @@
         <v>75</v>
       </c>
       <c r="X69" t="n">
-        <v>45.33590337629856</v>
+        <v>45.3445702232411</v>
       </c>
       <c r="Y69" t="n">
-        <v>15.50960403400178</v>
+        <v>17.24793255937811</v>
       </c>
       <c r="Z69" t="n">
         <v>1</v>
@@ -8197,10 +8225,10 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C70" t="n">
-        <v>0.486635032651079</v>
+        <v>0.4860197368421053</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8225,25 +8253,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>12.25433707230089</v>
+        <v>13.55581486783012</v>
       </c>
       <c r="K70" t="n">
-        <v>0.3392702725675045</v>
+        <v>1.721170395869187</v>
       </c>
       <c r="L70" t="n">
         <v>57</v>
       </c>
       <c r="M70" t="n">
-        <v>57.89473684210526</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N70" t="n">
-        <v>12.1067993174524</v>
+        <v>13.38056879992976</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>7.634827028961277</v>
+        <v>6.172588832487325</v>
       </c>
       <c r="Q70" t="n">
         <v>31</v>
@@ -8270,7 +8298,7 @@
         <v>44.93251946562029</v>
       </c>
       <c r="Y70" t="n">
-        <v>11.95664212251992</v>
+        <v>12.06796314438485</v>
       </c>
       <c r="Z70" t="n">
         <v>5</v>
@@ -8316,10 +8344,10 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C71" t="n">
-        <v>3.220923481182214</v>
+        <v>3.139391447368421</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8415,19 +8443,19 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C72" t="n">
-        <v>0.06314325974834528</v>
+        <v>0.06229440789473684</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8446,64 +8474,64 @@
         <v>29.77666337790048</v>
       </c>
       <c r="K72" t="n">
-        <v>5.813900352696799</v>
+        <v>4.391415580610269</v>
       </c>
       <c r="L72" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M72" t="n">
-        <v>70</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N72" t="n">
-        <v>18.39061517377225</v>
+        <v>16.15545700593165</v>
       </c>
       <c r="O72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>5.372649070994573</v>
       </c>
       <c r="Q72" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="R72" t="n">
-        <v>83.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="S72" t="n">
-        <v>45.51959442944098</v>
+        <v>48.12540481455289</v>
       </c>
       <c r="T72" t="n">
-        <v>37.81373890389235</v>
+        <v>31.87459518544711</v>
       </c>
       <c r="U72" t="n">
-        <v>55.19691377470266</v>
+        <v>54.81455128483065</v>
       </c>
       <c r="V72" t="n">
         <v>27</v>
       </c>
       <c r="W72" t="n">
-        <v>74.07407407407408</v>
+        <v>85.18518518518519</v>
       </c>
       <c r="X72" t="n">
         <v>12.03392243896149</v>
       </c>
       <c r="Y72" t="n">
-        <v>5.551909592073323</v>
+        <v>6.821600718760013</v>
       </c>
       <c r="Z72" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AA72" t="n">
-        <v>50</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="AB72" t="n">
-        <v>11.97540425375395</v>
+        <v>11.98292987346552</v>
       </c>
       <c r="AC72" t="n">
         <v>8</v>
       </c>
       <c r="AD72" t="n">
-        <v>2.591995663811975</v>
+        <v>1.264670020444569</v>
       </c>
       <c r="AE72" t="n">
         <v>10</v>
@@ -8534,10 +8562,10 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C73" t="n">
-        <v>0.062731903409291</v>
+        <v>0.06270559210526315</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8569,7 +8597,7 @@
         <v>19.59098648410814</v>
       </c>
       <c r="K73" t="n">
-        <v>2.760156542230008</v>
+        <v>2.717056403802975</v>
       </c>
       <c r="L73" t="n">
         <v>18</v>
@@ -8584,7 +8612,7 @@
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>7.045379942365826</v>
+        <v>7.090296247943684</v>
       </c>
       <c r="Q73" t="n">
         <v>14</v>
@@ -8608,10 +8636,10 @@
         <v>73.91304347826087</v>
       </c>
       <c r="X73" t="n">
-        <v>12.19387497524824</v>
+        <v>12.20056545653823</v>
       </c>
       <c r="Y73" t="n">
-        <v>8.408407709511289</v>
+        <v>8.452282761809037</v>
       </c>
       <c r="Z73" t="n">
         <v>21</v>
@@ -8620,13 +8648,13 @@
         <v>61.90476190476191</v>
       </c>
       <c r="AB73" t="n">
-        <v>12.62687064053817</v>
+        <v>12.56634401674117</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.737705667831246</v>
+        <v>1.690612595138852</v>
       </c>
       <c r="AE73" t="n">
         <v>15</v>
@@ -8657,10 +8685,10 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C74" t="n">
-        <v>5.553316130548976</v>
+        <v>5.46875</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8685,40 +8713,40 @@
         <v>10</v>
       </c>
       <c r="J74" t="n">
-        <v>10.37637083916865</v>
+        <v>10.3710262941641</v>
       </c>
       <c r="K74" t="n">
-        <v>4.448742746615086</v>
+        <v>2.852059520067707</v>
       </c>
       <c r="L74" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M74" t="n">
-        <v>67.9245283018868</v>
+        <v>68.96551724137932</v>
       </c>
       <c r="N74" t="n">
-        <v>16.2706300590606</v>
+        <v>15.37522658799305</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>3.400000000000003</v>
+        <v>5.005189496402718</v>
       </c>
       <c r="Q74" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="R74" t="n">
-        <v>76.66666666666667</v>
+        <v>75</v>
       </c>
       <c r="S74" t="n">
-        <v>65.58898631460762</v>
+        <v>69.79093646861928</v>
       </c>
       <c r="T74" t="n">
-        <v>11.07768035205905</v>
+        <v>5.209063531380721</v>
       </c>
       <c r="U74" t="n">
-        <v>59.07167384187784</v>
+        <v>56.64432968100104</v>
       </c>
       <c r="V74" t="n">
         <v>115</v>
@@ -8727,25 +8755,25 @@
         <v>77.39130434782609</v>
       </c>
       <c r="X74" t="n">
-        <v>25.51128431523497</v>
+        <v>24.51464461150628</v>
       </c>
       <c r="Y74" t="n">
-        <v>6.389246137622962</v>
+        <v>7.81475461684783</v>
       </c>
       <c r="Z74" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AA74" t="n">
-        <v>52.38095238095238</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="AB74" t="n">
-        <v>15.63580669470952</v>
+        <v>16.19517978112393</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>3.857199855142102</v>
+        <v>2.370493644692895</v>
       </c>
       <c r="AE74" t="n">
         <v>37</v>
@@ -8754,10 +8782,10 @@
         <v>51.35135135135135</v>
       </c>
       <c r="AG74" t="n">
-        <v>29.50438925148781</v>
+        <v>29.14297368845935</v>
       </c>
       <c r="AH74" t="n">
-        <v>21.84696209986354</v>
+        <v>22.20837766289201</v>
       </c>
       <c r="AI74" t="n">
         <v>35.89489666561879</v>
@@ -8776,19 +8804,19 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1085981864277592</v>
+        <v>0.1192434210526316</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8796,7 +8824,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>5</v>
       </c>
@@ -8804,25 +8836,25 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>28.78954644571032</v>
+        <v>26.72158757960922</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>9.795858043717853</v>
       </c>
       <c r="L75" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M75" t="n">
-        <v>72.72727272727273</v>
+        <v>75</v>
       </c>
       <c r="N75" t="n">
-        <v>17.30552880567455</v>
+        <v>7.64301986624898</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>6.000000000000005</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8885,14 +8917,14 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C76" t="n">
-        <v>1.952916109844485</v>
+        <v>1.910978618421053</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8902,7 +8934,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -8939,31 +8971,31 @@
         <v>45.72685693412379</v>
       </c>
       <c r="V76" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="W76" t="n">
-        <v>60.71428571428572</v>
+        <v>60</v>
       </c>
       <c r="X76" t="n">
-        <v>12.76370567693843</v>
+        <v>12.60650925728801</v>
       </c>
       <c r="Y76" t="n">
-        <v>3.816699094356002</v>
+        <v>5.882167414512929</v>
       </c>
       <c r="Z76" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="AA76" t="n">
-        <v>39.1304347826087</v>
+        <v>48.38709677419355</v>
       </c>
       <c r="AB76" t="n">
-        <v>9.524414452486621</v>
+        <v>11.16550151644106</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.1905745632745703</v>
+        <v>0</v>
       </c>
       <c r="AE76" t="n">
         <v>32</v>
@@ -8972,10 +9004,10 @@
         <v>56.25</v>
       </c>
       <c r="AG76" t="n">
-        <v>27.0436008041787</v>
+        <v>26.85420686478476</v>
       </c>
       <c r="AH76" t="n">
-        <v>29.2063991958213</v>
+        <v>29.39579313521524</v>
       </c>
       <c r="AI76" t="n">
         <v>39.32559113685198</v>
@@ -8994,10 +9026,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4816987563767492</v>
+        <v>0.4753289473684211</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9022,25 +9054,25 @@
         <v>10</v>
       </c>
       <c r="J77" t="n">
-        <v>16.01563214994599</v>
+        <v>16.91408941611843</v>
       </c>
       <c r="K77" t="n">
-        <v>0.3427589095366779</v>
+        <v>0.08658008658009031</v>
       </c>
       <c r="L77" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="M77" t="n">
-        <v>68</v>
+        <v>69.56521739130434</v>
       </c>
       <c r="N77" t="n">
-        <v>15.2790852513776</v>
+        <v>15.25920687533237</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>7.631084867186733</v>
+        <v>7.906574394463672</v>
       </c>
       <c r="Q77" t="n">
         <v>27</v>
@@ -9049,10 +9081,10 @@
         <v>59.25925925925926</v>
       </c>
       <c r="S77" t="n">
-        <v>37.5200475813221</v>
+        <v>37.69335518757989</v>
       </c>
       <c r="T77" t="n">
-        <v>21.73921167793716</v>
+        <v>21.56590407167937</v>
       </c>
       <c r="U77" t="n">
         <v>40.72670096806468</v>
@@ -9075,25 +9107,25 @@
       </c>
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF77" t="n">
-        <v>50</v>
+        <v>51.06382978723404</v>
       </c>
       <c r="AG77" t="n">
-        <v>25.5580544596169</v>
+        <v>25.54618096047612</v>
       </c>
       <c r="AH77" t="n">
-        <v>24.4419455403831</v>
+        <v>25.51764882675792</v>
       </c>
       <c r="AI77" t="n">
-        <v>36.11893708270325</v>
+        <v>37.24245374822684</v>
       </c>
       <c r="AJ77" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK77" t="n">
-        <v>45.67901234567901</v>
+        <v>46.34146341463415</v>
       </c>
     </row>
     <row r="78">
@@ -9103,10 +9135,10 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C78" t="n">
-        <v>0.06046944354449243</v>
+        <v>0.06229440789473684</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9163,25 +9195,25 @@
         <v>64.1025641025641</v>
       </c>
       <c r="X78" t="n">
-        <v>32.21753775888643</v>
+        <v>36.6270136023539</v>
       </c>
       <c r="Y78" t="n">
-        <v>0.6756749908692572</v>
+        <v>0.9803921568627527</v>
       </c>
       <c r="Z78" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA78" t="n">
-        <v>15</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB78" t="n">
-        <v>9.674269180691789</v>
+        <v>13.6227572469659</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>9.387755726780489</v>
+        <v>9.108910891089096</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9212,10 +9244,10 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8951122983556179</v>
+        <v>0.8943256578947368</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9243,22 +9275,22 @@
         <v>10.42896938309872</v>
       </c>
       <c r="K79" t="n">
-        <v>0.3122327620474152</v>
+        <v>0.2240766042592712</v>
       </c>
       <c r="L79" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M79" t="n">
-        <v>54.90196078431372</v>
+        <v>54</v>
       </c>
       <c r="N79" t="n">
-        <v>10.42121004791757</v>
+        <v>10.46975513357592</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>4.673176051292294</v>
+        <v>4.765245595226331</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9285,7 +9317,7 @@
         <v>25.65117214954458</v>
       </c>
       <c r="Y79" t="n">
-        <v>10.14929928020923</v>
+        <v>10.22826165929234</v>
       </c>
       <c r="Z79" t="n">
         <v>6</v>
@@ -9309,10 +9341,10 @@
         <v>52.77777777777778</v>
       </c>
       <c r="AG79" t="n">
-        <v>26.42317470748843</v>
+        <v>26.34016065895714</v>
       </c>
       <c r="AH79" t="n">
-        <v>26.35460307028935</v>
+        <v>26.43761711882064</v>
       </c>
       <c r="AI79" t="n">
         <v>37.00593802298759</v>
@@ -9331,10 +9363,10 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1332795875445322</v>
+        <v>0.1334292763157895</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9362,22 +9394,22 @@
         <v>10.48668504530712</v>
       </c>
       <c r="K80" t="n">
-        <v>4.262032634453883</v>
+        <v>4.379131252789747</v>
       </c>
       <c r="L80" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M80" t="n">
-        <v>59.45945945945946</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N80" t="n">
-        <v>18.41888372789451</v>
+        <v>18.99122853136501</v>
       </c>
       <c r="O80" t="n">
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>5.503410225718142</v>
+        <v>5.385050325430862</v>
       </c>
       <c r="Q80" t="n">
         <v>39</v>
@@ -9395,22 +9427,22 @@
         <v>61.66374277165825</v>
       </c>
       <c r="V80" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="W80" t="n">
-        <v>74.68354430379746</v>
+        <v>74.35897435897436</v>
       </c>
       <c r="X80" t="n">
         <v>16.92042739318289</v>
       </c>
       <c r="Y80" t="n">
-        <v>6.671598349756625</v>
+        <v>6.566779494718045</v>
       </c>
       <c r="Z80" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA80" t="n">
-        <v>50</v>
+        <v>46.875</v>
       </c>
       <c r="AB80" t="n">
         <v>15.2833189605872</v>
@@ -9419,7 +9451,7 @@
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.423362692122032</v>
+        <v>1.533951733153549</v>
       </c>
       <c r="AE80" t="n">
         <v>24</v>
@@ -9450,10 +9482,10 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C81" t="n">
-        <v>1.242297417710118</v>
+        <v>1.222245065789474</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9510,25 +9542,25 @@
         <v>65.30612244897959</v>
       </c>
       <c r="X81" t="n">
-        <v>23.76450921054161</v>
+        <v>23.77188968593224</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.423263268051801</v>
+        <v>4.0040076447863</v>
       </c>
       <c r="Z81" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AA81" t="n">
-        <v>38.46153846153846</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="AB81" t="n">
-        <v>10.57166715745348</v>
+        <v>11.01125755024417</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>7.764900718869249</v>
+        <v>6.246086120998406</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9562,7 +9594,7 @@
         <v>46279</v>
       </c>
       <c r="C82" t="n">
-        <v>4.769681395552144</v>
+        <v>4.769965826980715</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9590,7 +9622,7 @@
         <v>16.34835816551005</v>
       </c>
       <c r="K82" t="n">
-        <v>1.988162049046971</v>
+        <v>1.994243930879991</v>
       </c>
       <c r="L82" t="n">
         <v>9</v>
@@ -9605,7 +9637,7 @@
         <v>4</v>
       </c>
       <c r="P82" t="n">
-        <v>1.972619086895122</v>
+        <v>1.966538494544157</v>
       </c>
       <c r="Q82" t="n">
         <v>8</v>
@@ -9668,10 +9700,10 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C83" t="n">
-        <v>5.522464374268148</v>
+        <v>5.417351973684211</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9699,22 +9731,22 @@
         <v>13.10783674393532</v>
       </c>
       <c r="K83" t="n">
-        <v>4.358146531616724</v>
+        <v>2.371834885399493</v>
       </c>
       <c r="L83" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M83" t="n">
-        <v>43.54838709677419</v>
+        <v>54.28571428571428</v>
       </c>
       <c r="N83" t="n">
-        <v>12.37564002522255</v>
+        <v>11.55700610672134</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>5.406241540207901</v>
+        <v>7.45142951002089</v>
       </c>
       <c r="Q83" t="n">
         <v>41</v>
@@ -9732,10 +9764,10 @@
         <v>45.72685693412379</v>
       </c>
       <c r="V83" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="W83" t="n">
-        <v>60.9375</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
@@ -9755,10 +9787,10 @@
         <v>58.53658536585366</v>
       </c>
       <c r="AG83" t="n">
-        <v>28.57396001216165</v>
+        <v>28.12792354245498</v>
       </c>
       <c r="AH83" t="n">
-        <v>29.96262535369202</v>
+        <v>30.40866182339868</v>
       </c>
       <c r="AI83" t="n">
         <v>43.36710313403013</v>
@@ -9777,24 +9809,24 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C84" t="n">
-        <v>2.106146593573292</v>
+        <v>2.068256578947368</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -9805,19 +9837,19 @@
         <v>10</v>
       </c>
       <c r="J84" t="n">
-        <v>14.96371051984784</v>
+        <v>14.20091622675307</v>
       </c>
       <c r="K84" t="n">
-        <v>8.621098801955984</v>
+        <v>6.666982675923494</v>
       </c>
       <c r="L84" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="M84" t="n">
-        <v>57.14285714285715</v>
+        <v>62.85714285714285</v>
       </c>
       <c r="N84" t="n">
-        <v>10.27404726378175</v>
+        <v>9.407327680389011</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9850,43 +9882,43 @@
         <v>11.86663135768809</v>
       </c>
       <c r="Y84" t="n">
-        <v>2.901251710489672</v>
+        <v>4.648078357825025</v>
       </c>
       <c r="Z84" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="AA84" t="n">
-        <v>37.5</v>
+        <v>31.70731707317073</v>
       </c>
       <c r="AB84" t="n">
-        <v>11.87023114330644</v>
+        <v>11.99860234384794</v>
       </c>
       <c r="AC84" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AD84" t="n">
-        <v>2.161457615553075</v>
+        <v>0</v>
       </c>
       <c r="AE84" t="n">
         <v>39</v>
       </c>
       <c r="AF84" t="n">
-        <v>41.02564102564103</v>
+        <v>43.58974358974359</v>
       </c>
       <c r="AG84" t="n">
-        <v>26.22167829335427</v>
+        <v>28.72591724014846</v>
       </c>
       <c r="AH84" t="n">
-        <v>14.80396273228676</v>
+        <v>14.86382634959513</v>
       </c>
       <c r="AI84" t="n">
-        <v>27.07931000072518</v>
+        <v>29.30475387568963</v>
       </c>
       <c r="AJ84" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AK84" t="n">
-        <v>45.6140350877193</v>
+        <v>51.78571428571428</v>
       </c>
     </row>
     <row r="85">
@@ -9896,10 +9928,10 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C85" t="n">
-        <v>6.077795987323046</v>
+        <v>6.003289473684211</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9924,25 +9956,25 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>12.5637553307017</v>
+        <v>10.58907718287831</v>
       </c>
       <c r="K85" t="n">
-        <v>1.522619346007237</v>
+        <v>0.2780733890961118</v>
       </c>
       <c r="L85" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="M85" t="n">
-        <v>55.88235294117647</v>
+        <v>55.73770491803279</v>
       </c>
       <c r="N85" t="n">
-        <v>14.62215108340677</v>
+        <v>12.40455796654371</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>6.380233977136363</v>
+        <v>7.700513531947806</v>
       </c>
       <c r="Q85" t="n">
         <v>32</v>
@@ -9983,10 +10015,10 @@
         <v>42.42424242424242</v>
       </c>
       <c r="AG85" t="n">
-        <v>26.9933497239647</v>
+        <v>26.91759214820712</v>
       </c>
       <c r="AH85" t="n">
-        <v>15.43089270027772</v>
+        <v>15.5066502760353</v>
       </c>
       <c r="AI85" t="n">
         <v>27.23559663341021</v>
@@ -10005,27 +10037,31 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C86" t="n">
-        <v>4.44882331842725</v>
+        <v>4.658717105263158</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
+          <t>ÇELİŞKİLİ_BEKLE</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H86" t="n">
         <v>5</v>
       </c>
@@ -10036,22 +10072,22 @@
         <v>18.73514495170452</v>
       </c>
       <c r="K86" t="n">
-        <v>6.714254542521791</v>
+        <v>11.74899235791773</v>
       </c>
       <c r="L86" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="M86" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N86" t="n">
-        <v>16.83369757944945</v>
+        <v>16.52493490543912</v>
       </c>
       <c r="O86" t="n">
         <v>8</v>
       </c>
       <c r="P86" t="n">
-        <v>1.204848839538952</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>52</v>
@@ -10075,19 +10111,19 @@
         <v>70.12987012987013</v>
       </c>
       <c r="X86" t="n">
-        <v>48.61770380947655</v>
+        <v>44.99483923332605</v>
       </c>
       <c r="Y86" t="n">
-        <v>13.27881573015058</v>
+        <v>9.187343342407372</v>
       </c>
       <c r="Z86" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AA86" t="n">
         <v>33.33333333333334</v>
       </c>
       <c r="AB86" t="n">
-        <v>14.34516657732499</v>
+        <v>19.4387621860991</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
@@ -10124,10 +10160,10 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C87" t="n">
-        <v>5.846407815216838</v>
+        <v>5.890213815789473</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10187,16 +10223,16 @@
         <v>15.88967756874082</v>
       </c>
       <c r="Y87" t="n">
-        <v>5.224612874688783</v>
+        <v>4.5144792689083</v>
       </c>
       <c r="Z87" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA87" t="n">
-        <v>45.71428571428572</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB87" t="n">
-        <v>12.87424470283853</v>
+        <v>11.04384941659857</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
@@ -10233,10 +10269,10 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C88" t="n">
-        <v>1.07466951044883</v>
+        <v>1.051603618421053</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10264,16 +10300,16 @@
         <v>16.8583060727446</v>
       </c>
       <c r="K88" t="n">
-        <v>8.098092134448054</v>
+        <v>5.777956597579137</v>
       </c>
       <c r="L88" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M88" t="n">
-        <v>71.875</v>
+        <v>74.28571428571429</v>
       </c>
       <c r="N88" t="n">
-        <v>13.53184149474504</v>
+        <v>13.98786437648149</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
@@ -10303,19 +10339,19 @@
         <v>61.53846153846154</v>
       </c>
       <c r="X88" t="n">
-        <v>25.70907945955605</v>
+        <v>22.33299319731812</v>
       </c>
       <c r="Y88" t="n">
-        <v>10.12541509637465</v>
+        <v>12.05441508313568</v>
       </c>
       <c r="Z88" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AA88" t="n">
-        <v>39.1304347826087</v>
+        <v>40</v>
       </c>
       <c r="AB88" t="n">
-        <v>13.51336303619622</v>
+        <v>12.45830595672115</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
@@ -10330,10 +10366,10 @@
         <v>51.51515151515152</v>
       </c>
       <c r="AG88" t="n">
-        <v>52.72953912272798</v>
+        <v>52.44979361570975</v>
       </c>
       <c r="AH88" t="n">
-        <v>-1.214387607576462</v>
+        <v>-0.9346421005582357</v>
       </c>
       <c r="AI88" t="n">
         <v>35.21837544891414</v>
@@ -10352,10 +10388,10 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C89" t="n">
-        <v>2.178134024895223</v>
+        <v>2.177220394736842</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10412,25 +10448,25 @@
         <v>76.08695652173913</v>
       </c>
       <c r="X89" t="n">
-        <v>21.45830694080864</v>
+        <v>21.41032003314154</v>
       </c>
       <c r="Y89" t="n">
-        <v>6.978339975648118</v>
+        <v>7.017358416666686</v>
       </c>
       <c r="Z89" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA89" t="n">
-        <v>40.54054054054054</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB89" t="n">
-        <v>16.66848020226589</v>
+        <v>16.48426081594873</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>3.248340250604909</v>
+        <v>3.20774021101583</v>
       </c>
       <c r="AE89" t="n">
         <v>22</v>
@@ -10461,10 +10497,10 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C90" t="n">
-        <v>2.807509821555315</v>
+        <v>2.783717105263158</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10492,22 +10528,22 @@
         <v>12.8208334231333</v>
       </c>
       <c r="K90" t="n">
-        <v>3.081296001586953</v>
+        <v>2.20771614374875</v>
       </c>
       <c r="L90" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M90" t="n">
-        <v>63.95348837209303</v>
+        <v>66.29213483146067</v>
       </c>
       <c r="N90" t="n">
-        <v>15.31969993210813</v>
+        <v>14.17641525480765</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>4.771674580359697</v>
+        <v>5.667168854555737</v>
       </c>
       <c r="Q90" t="n">
         <v>43</v>
@@ -10525,25 +10561,25 @@
         <v>62.25547970219101</v>
       </c>
       <c r="V90" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="W90" t="n">
-        <v>70.78651685393258</v>
+        <v>70.45454545454545</v>
       </c>
       <c r="X90" t="n">
         <v>20.63086277737274</v>
       </c>
       <c r="Y90" t="n">
-        <v>10.13458524918348</v>
+        <v>10.89616488863021</v>
       </c>
       <c r="Z90" t="n">
         <v>20</v>
       </c>
       <c r="AA90" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AB90" t="n">
-        <v>11.08028764123533</v>
+        <v>11.64511465808553</v>
       </c>
       <c r="AC90" t="n">
         <v>2</v>
@@ -10567,10 +10603,10 @@
         <v>44.51849774816486</v>
       </c>
       <c r="AJ90" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AK90" t="n">
-        <v>46.42857142857143</v>
+        <v>45.78313253012048</v>
       </c>
     </row>
     <row r="91">
@@ -10580,10 +10616,10 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2363244483805371</v>
+        <v>0.2319078947368421</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10634,10 +10670,10 @@
         <v>46.62357539237828</v>
       </c>
       <c r="V91" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="W91" t="n">
-        <v>66.66666666666667</v>
+        <v>66.25</v>
       </c>
       <c r="X91" t="inlineStr"/>
       <c r="Y91" t="inlineStr"/>
@@ -10679,10 +10715,10 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C92" t="n">
-        <v>1.180593905148462</v>
+        <v>1.162623355263158</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10742,16 +10778,16 @@
         <v>21.60407460332612</v>
       </c>
       <c r="Y92" t="n">
-        <v>5.723029641812715</v>
+        <v>7.15807770657817</v>
       </c>
       <c r="Z92" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA92" t="n">
-        <v>33.33333333333334</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="AB92" t="n">
-        <v>12.61693254762918</v>
+        <v>15.78239274433468</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10766,19 +10802,19 @@
         <v>51.92307692307692</v>
       </c>
       <c r="AG92" t="n">
-        <v>40.43872705205762</v>
+        <v>40.32778030649548</v>
       </c>
       <c r="AH92" t="n">
-        <v>11.4843498710193</v>
+        <v>11.59529661658144</v>
       </c>
       <c r="AI92" t="n">
         <v>38.68568276805605</v>
       </c>
       <c r="AJ92" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AK92" t="n">
-        <v>47.14285714285715</v>
+        <v>46.3768115942029</v>
       </c>
     </row>
     <row r="93">
@@ -10788,10 +10824,10 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04195838771921209</v>
+        <v>0.04214638157894737</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10851,16 +10887,16 @@
         <v>11.4419372600254</v>
       </c>
       <c r="Y93" t="n">
-        <v>4.533640708729648</v>
+        <v>4.105905270510624</v>
       </c>
       <c r="Z93" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA93" t="n">
-        <v>45</v>
+        <v>45.23809523809524</v>
       </c>
       <c r="AB93" t="n">
-        <v>15.44736513139534</v>
+        <v>13.26309491661619</v>
       </c>
       <c r="AC93" t="n">
         <v>2</v>
@@ -10869,19 +10905,19 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF93" t="n">
-        <v>60</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="AG93" t="n">
-        <v>26.87723585530293</v>
+        <v>24.71494548232858</v>
       </c>
       <c r="AH93" t="n">
-        <v>33.12276414469707</v>
+        <v>33.61838785100475</v>
       </c>
       <c r="AI93" t="n">
-        <v>40.739457358967</v>
+        <v>38.83466586522876</v>
       </c>
       <c r="AJ93" t="n">
         <v>89</v>
@@ -10897,10 +10933,10 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C94" t="n">
-        <v>8.551078449169395</v>
+        <v>8.403577302631579</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10942,10 +10978,10 @@
         <v>61.90476190476191</v>
       </c>
       <c r="S94" t="n">
-        <v>40.21324457646786</v>
+        <v>40.27276838599167</v>
       </c>
       <c r="T94" t="n">
-        <v>21.69151732829405</v>
+        <v>21.63199351877024</v>
       </c>
       <c r="U94" t="n">
         <v>46.81404026715268</v>
@@ -10957,25 +10993,25 @@
         <v>70.90909090909091</v>
       </c>
       <c r="X94" t="n">
-        <v>46.54975901226545</v>
+        <v>40.43377921558155</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.981391600981208</v>
+        <v>3.672155778486907</v>
       </c>
       <c r="Z94" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA94" t="n">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="AB94" t="n">
-        <v>10.75358476998065</v>
+        <v>14.14910941095578</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>4.099842330610992</v>
+        <v>2.41658498674594</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -11009,7 +11045,7 @@
         <v>46279</v>
       </c>
       <c r="C95" t="n">
-        <v>0.121144560322231</v>
+        <v>0.1211517845616504</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11034,7 +11070,7 @@
         <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>19.07550043933058</v>
+        <v>19.07067465137798</v>
       </c>
       <c r="K95" t="n">
         <v>0.1700639423967587</v>
@@ -11115,10 +11151,10 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1273149154862857</v>
+        <v>0.1264391447368421</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11214,19 +11250,19 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C97" t="n">
-        <v>1.91692239418352</v>
+        <v>1.868832236842105</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -11245,22 +11281,22 @@
         <v>12.87370897365936</v>
       </c>
       <c r="K97" t="n">
-        <v>4.781448767694907</v>
+        <v>2.152778784502352</v>
       </c>
       <c r="L97" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="M97" t="n">
-        <v>56.09756097560975</v>
+        <v>55.93220338983051</v>
       </c>
       <c r="N97" t="n">
-        <v>15.57778215297127</v>
+        <v>13.83994361589519</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.808292674440581</v>
       </c>
       <c r="Q97" t="n">
         <v>50</v>
@@ -11287,16 +11323,16 @@
         <v>16.31583297271808</v>
       </c>
       <c r="Y97" t="n">
-        <v>8.707810005042127</v>
+        <v>10.99807266472052</v>
       </c>
       <c r="Z97" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AA97" t="n">
-        <v>40</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="AB97" t="n">
-        <v>11.08203790087885</v>
+        <v>12.78373293291585</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
@@ -11333,10 +11369,10 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7350945475384869</v>
+        <v>0.7236842105263158</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11387,31 +11423,31 @@
         <v>53.37920531457014</v>
       </c>
       <c r="V98" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="W98" t="n">
-        <v>72.46376811594203</v>
+        <v>72.05882352941177</v>
       </c>
       <c r="X98" t="n">
         <v>30.85778357900837</v>
       </c>
       <c r="Y98" t="n">
-        <v>6.198044240801693</v>
+        <v>7.65406364836937</v>
       </c>
       <c r="Z98" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AA98" t="n">
-        <v>27.27272727272727</v>
+        <v>50</v>
       </c>
       <c r="AB98" t="n">
-        <v>8.732156502971499</v>
+        <v>9.329134053398002</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>1.92102152307374</v>
+        <v>0.3746091764269766</v>
       </c>
       <c r="AE98" t="n">
         <v>51</v>
@@ -11420,10 +11456,10 @@
         <v>56.86274509803921</v>
       </c>
       <c r="AG98" t="n">
-        <v>37.51172668937328</v>
+        <v>37.46666034773386</v>
       </c>
       <c r="AH98" t="n">
-        <v>19.35101840866594</v>
+        <v>19.39608475030535</v>
       </c>
       <c r="AI98" t="n">
         <v>43.26530210930225</v>
@@ -11442,10 +11478,10 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5401114180202918</v>
+        <v>0.5616776315789473</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11462,7 +11498,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H99" t="n">
         <v>5</v>
       </c>
@@ -11470,19 +11510,19 @@
         <v>10</v>
       </c>
       <c r="J99" t="n">
-        <v>12.53596020163561</v>
+        <v>12.53074443988439</v>
       </c>
       <c r="K99" t="n">
-        <v>5.377207647264171</v>
+        <v>9.5783001019784</v>
       </c>
       <c r="L99" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="M99" t="n">
-        <v>54.23728813559322</v>
+        <v>75</v>
       </c>
       <c r="N99" t="n">
-        <v>14.27418325742021</v>
+        <v>12.87930960772016</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
@@ -11515,22 +11555,22 @@
         <v>33.04241514445872</v>
       </c>
       <c r="Y99" t="n">
-        <v>7.832837164991791</v>
+        <v>4.152676645370102</v>
       </c>
       <c r="Z99" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AA99" t="n">
-        <v>66.66666666666667</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="AB99" t="n">
-        <v>12.01251736130811</v>
+        <v>16.01798172400412</v>
       </c>
       <c r="AC99" t="n">
         <v>10</v>
       </c>
       <c r="AD99" t="n">
-        <v>2.35133942322574</v>
+        <v>6.10066421259895</v>
       </c>
       <c r="AE99" t="n">
         <v>38</v>
@@ -11539,10 +11579,10 @@
         <v>50</v>
       </c>
       <c r="AG99" t="n">
-        <v>36.08873902035259</v>
+        <v>36.14854763279278</v>
       </c>
       <c r="AH99" t="n">
-        <v>13.91126097964741</v>
+        <v>13.85145236720722</v>
       </c>
       <c r="AI99" t="n">
         <v>34.8499283643951</v>
@@ -11564,7 +11604,7 @@
         <v>46279</v>
       </c>
       <c r="C100" t="n">
-        <v>347.2301296629448</v>
+        <v>347.2508361113702</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11606,10 +11646,10 @@
         <v>60.41666666666666</v>
       </c>
       <c r="S100" t="n">
-        <v>36.64353580651581</v>
+        <v>36.6138185892986</v>
       </c>
       <c r="T100" t="n">
-        <v>23.77313086015085</v>
+        <v>23.80284807736807</v>
       </c>
       <c r="U100" t="n">
         <v>46.31040849254725</v>
@@ -11624,7 +11664,7 @@
         <v>16.86980163304483</v>
       </c>
       <c r="Y100" t="n">
-        <v>4.691556559313859</v>
+        <v>4.685873010566133</v>
       </c>
       <c r="Z100" t="n">
         <v>34</v>
@@ -11639,7 +11679,7 @@
         <v>8</v>
       </c>
       <c r="AD100" t="n">
-        <v>3.471301514587322</v>
+        <v>3.47705748781737</v>
       </c>
       <c r="AE100" t="n">
         <v>39</v>
@@ -11670,10 +11710,10 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C101" t="n">
-        <v>349.8949099402464</v>
+        <v>345.0684621710527</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11730,25 +11770,25 @@
         <v>52.63157894736842</v>
       </c>
       <c r="X101" t="n">
-        <v>13.07599096065748</v>
+        <v>12.90626814318425</v>
       </c>
       <c r="Y101" t="n">
-        <v>3.191963173700085</v>
+        <v>4.527332509196025</v>
       </c>
       <c r="Z101" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="AA101" t="n">
-        <v>43.58974358974359</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB101" t="n">
-        <v>11.51404947830189</v>
+        <v>11.34254663831077</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>2.900623665510649</v>
+        <v>1.542501670382079</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11782,7 +11822,7 @@
         <v>46279</v>
       </c>
       <c r="C102" t="n">
-        <v>408.5060561648955</v>
+        <v>408.5304166937231</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11824,10 +11864,10 @@
         <v>48.27586206896552</v>
       </c>
       <c r="S102" t="n">
-        <v>25.8369017019065</v>
+        <v>26.00931549500995</v>
       </c>
       <c r="T102" t="n">
-        <v>22.43896036705901</v>
+        <v>22.26654657395557</v>
       </c>
       <c r="U102" t="n">
         <v>31.38609015268349</v>
@@ -11842,7 +11882,7 @@
         <v>10.81355469301844</v>
       </c>
       <c r="Y102" t="n">
-        <v>4.169064322631232</v>
+        <v>4.163349615992463</v>
       </c>
       <c r="Z102" t="n">
         <v>17</v>
@@ -11857,7 +11897,7 @@
         <v>5</v>
       </c>
       <c r="AD102" t="n">
-        <v>0.867085009131352</v>
+        <v>0.872996270899673</v>
       </c>
       <c r="AE102" t="n">
         <v>26</v>
@@ -11888,10 +11928,10 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7536055542066357</v>
+        <v>0.735608552631579</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11942,31 +11982,31 @@
         <v>52.51621096752947</v>
       </c>
       <c r="V103" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="W103" t="n">
-        <v>68.18181818181819</v>
+        <v>67.69230769230769</v>
       </c>
       <c r="X103" t="n">
         <v>14.28440963201156</v>
       </c>
       <c r="Y103" t="n">
-        <v>4.638376332407946</v>
+        <v>6.915725911064364</v>
       </c>
       <c r="Z103" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AA103" t="n">
-        <v>45</v>
+        <v>39.28571428571428</v>
       </c>
       <c r="AB103" t="n">
-        <v>10.86873296387317</v>
+        <v>10.57021134040605</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>3.525132583008306</v>
+        <v>1.164830579115528</v>
       </c>
       <c r="AE103" t="n">
         <v>33</v>
@@ -11975,10 +12015,10 @@
         <v>60.60606060606061</v>
       </c>
       <c r="AG103" t="n">
-        <v>34.83100155560049</v>
+        <v>34.5730577450251</v>
       </c>
       <c r="AH103" t="n">
-        <v>25.77505905046012</v>
+        <v>26.03300286103551</v>
       </c>
       <c r="AI103" t="n">
         <v>43.68344081994023</v>
@@ -11997,14 +12037,14 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C104" t="n">
-        <v>0.04956849027563512</v>
+        <v>0.05448190789473684</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -12014,7 +12054,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -12057,25 +12097,25 @@
         <v>63.23529411764706</v>
       </c>
       <c r="X104" t="n">
-        <v>12.98853157526716</v>
+        <v>17.0508331466374</v>
       </c>
       <c r="Y104" t="n">
-        <v>5.74735887087413</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA104" t="n">
-        <v>56.52173913043478</v>
+        <v>47.61904761904762</v>
       </c>
       <c r="AB104" t="n">
-        <v>11.19798827024807</v>
+        <v>11.29611233976692</v>
       </c>
       <c r="AC104" t="n">
         <v>5</v>
       </c>
       <c r="AD104" t="n">
-        <v>0</v>
+        <v>5.000000000000004</v>
       </c>
       <c r="AE104" t="n">
         <v>42</v>
@@ -12084,10 +12124,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="AG104" t="n">
-        <v>30.33484174711939</v>
+        <v>30.16212875485753</v>
       </c>
       <c r="AH104" t="n">
-        <v>26.80801539573775</v>
+        <v>26.98072838799961</v>
       </c>
       <c r="AI104" t="n">
         <v>42.20623987810458</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -444,7 +444,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -670,7 +670,7 @@
         <v>46280</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3957648026315789</v>
+        <v>0.3961759868421053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,22 +698,22 @@
         <v>21.42119502374098</v>
       </c>
       <c r="K2" t="n">
-        <v>7.712944071421624</v>
+        <v>7.82485362370362</v>
       </c>
       <c r="L2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M2" t="n">
-        <v>60</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N2" t="n">
-        <v>15.62940110231521</v>
+        <v>15.34014576009059</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>2.123287918917049</v>
+        <v>2.01729592315274</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -740,22 +740,22 @@
         <v>11.79582706077868</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.652088898754124</v>
+        <v>3.551987172934645</v>
       </c>
       <c r="Z2" t="n">
         <v>40</v>
       </c>
       <c r="AA2" t="n">
-        <v>45</v>
+        <v>42.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.75926858937931</v>
+        <v>12.09916543615478</v>
       </c>
       <c r="AC2" t="n">
         <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.588530076770693</v>
+        <v>6.685480227184016</v>
       </c>
       <c r="AE2" t="n">
         <v>46</v>
@@ -786,10 +786,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7092213188717587</v>
+        <v>0.692434216899671</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>16.83732632822199</v>
       </c>
       <c r="K3" t="n">
-        <v>12.8107214497728</v>
+        <v>10.14051818017179</v>
       </c>
       <c r="L3" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="M3" t="n">
-        <v>73.33333333333333</v>
+        <v>54.16666666666666</v>
       </c>
       <c r="N3" t="n">
-        <v>14.82629685373418</v>
+        <v>13.22808084587165</v>
       </c>
       <c r="O3" t="n">
         <v>10</v>
@@ -859,22 +859,22 @@
         <v>17.17248092970491</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.722511843500897</v>
+        <v>6.001377365861005</v>
       </c>
       <c r="Z3" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AA3" t="n">
-        <v>30.95238095238095</v>
+        <v>37.93103448275862</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.14862511052788</v>
+        <v>11.97793792370923</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>6.520203504161892</v>
+        <v>4.253916198009</v>
       </c>
       <c r="AE3" t="n">
         <v>35</v>
@@ -908,7 +908,7 @@
         <v>46280</v>
       </c>
       <c r="C4" t="n">
-        <v>1.469983552631579</v>
+        <v>1.448396381578947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -968,22 +968,22 @@
         <v>16.66966699739723</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.63177235399548</v>
+        <v>8.00291415858716</v>
       </c>
       <c r="Z4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AA4" t="n">
-        <v>59.25925925925926</v>
+        <v>65</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.46243236260763</v>
+        <v>9.600578880172892</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.607466619988531</v>
+        <v>2.170814241720076</v>
       </c>
       <c r="AE4" t="n">
         <v>40</v>
@@ -1017,7 +1017,7 @@
         <v>46280</v>
       </c>
       <c r="C5" t="n">
-        <v>0.229235197368421</v>
+        <v>0.2275904605263158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,16 +1045,16 @@
         <v>19.13427219952423</v>
       </c>
       <c r="K5" t="n">
-        <v>5.308375735112336</v>
+        <v>4.55279994508464</v>
       </c>
       <c r="L5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M5" t="n">
-        <v>57.14285714285715</v>
+        <v>50</v>
       </c>
       <c r="N5" t="n">
-        <v>10.7662014468071</v>
+        <v>11.62858653100384</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -1087,22 +1087,22 @@
         <v>10.55954734904581</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.749631976472434</v>
+        <v>5.433042688748868</v>
       </c>
       <c r="Z5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA5" t="n">
-        <v>43.90243902439025</v>
+        <v>37.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.164656365945994</v>
+        <v>9.511831957833676</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.512176102280975</v>
+        <v>4.829337266525091</v>
       </c>
       <c r="AE5" t="n">
         <v>45</v>
@@ -1136,7 +1136,7 @@
         <v>46280</v>
       </c>
       <c r="C6" t="n">
-        <v>1.599506578947368</v>
+        <v>1.56969572368421</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %82.61: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %92.86: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1165,25 +1165,25 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>24.35210179737853</v>
+        <v>25.66500274978247</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5917742364027756</v>
+        <v>0.4605263157894557</v>
       </c>
       <c r="L6" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="M6" t="n">
-        <v>82.60869565217391</v>
+        <v>92.85714285714286</v>
       </c>
       <c r="N6" t="n">
-        <v>12.34555220948897</v>
+        <v>12.16769408284637</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.399941271825789</v>
+        <v>1.532416502946976</v>
       </c>
       <c r="Q6" t="n">
         <v>35</v>
@@ -1249,7 +1249,7 @@
         <v>46280</v>
       </c>
       <c r="C7" t="n">
-        <v>2.300575657894737</v>
+        <v>2.255345394736842</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,16 +1309,16 @@
         <v>18.9234494530097</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.011653267185791</v>
+        <v>8.839842389725483</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
-        <v>43.47826086956522</v>
+        <v>62.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.00548278227541</v>
+        <v>12.56450013246144</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1358,7 +1358,7 @@
         <v>46280</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3470394736842105</v>
+        <v>0.3425164473684211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,22 +1386,22 @@
         <v>20.70550141590351</v>
       </c>
       <c r="K8" t="n">
-        <v>6.576327869448617</v>
+        <v>5.187299899586151</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M8" t="n">
-        <v>66.66666666666667</v>
+        <v>60</v>
       </c>
       <c r="N8" t="n">
-        <v>12.06937941087031</v>
+        <v>17.38979657077811</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>1.335823966739902</v>
+        <v>2.673992110358303</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1428,10 +1428,10 @@
         <v>26.93179943319606</v>
       </c>
       <c r="Y8" t="n">
-        <v>15.49083520657804</v>
+        <v>16.59225797047333</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
         <v>46280</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5489309210526315</v>
+        <v>0.5485197368421052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,16 +1501,16 @@
         <v>14.50739888386581</v>
       </c>
       <c r="K9" t="n">
-        <v>3.241840610740132</v>
+        <v>3.164505898672165</v>
       </c>
       <c r="L9" t="n">
         <v>41</v>
       </c>
       <c r="M9" t="n">
-        <v>48.78048780487805</v>
+        <v>46.34146341463415</v>
       </c>
       <c r="N9" t="n">
-        <v>14.69366495460834</v>
+        <v>15.07354306966153</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1582,7 +1582,7 @@
         <v>46280</v>
       </c>
       <c r="C10" t="n">
-        <v>1.918174342105263</v>
+        <v>1.912006578947368</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,22 +1610,22 @@
         <v>13.50421550203786</v>
       </c>
       <c r="K10" t="n">
-        <v>4.61372807247773</v>
+        <v>4.277349525620888</v>
       </c>
       <c r="L10" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M10" t="n">
-        <v>55.55555555555556</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N10" t="n">
-        <v>9.785313373390345</v>
+        <v>9.618994333024993</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>5.148723811649836</v>
+        <v>5.487913243300335</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1691,7 +1691,7 @@
         <v>46280</v>
       </c>
       <c r="C11" t="n">
-        <v>7.596628289473684</v>
+        <v>7.678865131578947</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,25 +1716,25 @@
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>11.69503567664335</v>
+        <v>11.81477122148857</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2033898305084714</v>
+        <v>1.425661914460274</v>
       </c>
       <c r="L11" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="M11" t="n">
-        <v>58.92857142857143</v>
+        <v>55.73770491803279</v>
       </c>
       <c r="N11" t="n">
-        <v>13.28632006090635</v>
+        <v>13.27181238264338</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.79093369418133</v>
+        <v>1.552208835341373</v>
       </c>
       <c r="Q11" t="n">
         <v>49</v>
@@ -1761,16 +1761,16 @@
         <v>19.5857262818246</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.5154323593755</v>
+        <v>10.55754800061367</v>
       </c>
       <c r="Z11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA11" t="n">
-        <v>38.46153846153846</v>
+        <v>50</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.995558859822591</v>
+        <v>9.100922825874459</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
@@ -1810,7 +1810,7 @@
         <v>46280</v>
       </c>
       <c r="C12" t="n">
-        <v>5.586965460526316</v>
+        <v>5.653782894736842</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,11 +1827,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %91.67: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>5</v>
       </c>
@@ -1839,25 +1835,25 @@
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>24.90100121795005</v>
+        <v>25.10845701569052</v>
       </c>
       <c r="K12" t="n">
-        <v>0.09208103130755596</v>
+        <v>1.569713758079416</v>
       </c>
       <c r="L12" t="n">
         <v>12</v>
       </c>
       <c r="M12" t="n">
-        <v>91.66666666666667</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N12" t="n">
-        <v>14.42416201834824</v>
+        <v>14.40850509582597</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>4.903403863845446</v>
+        <v>3.377272727272729</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1923,7 +1919,7 @@
         <v>46280</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1685855263157895</v>
+        <v>0.1673519736842105</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,10 +1947,10 @@
         <v>47.07727092024744</v>
       </c>
       <c r="K13" t="n">
-        <v>4.391881279246679</v>
+        <v>3.628038245496112</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1962,7 +1958,7 @@
         <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>1.540463397198133</v>
+        <v>2.288918901354364</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1987,7 +1983,7 @@
         <v>20.61663781635479</v>
       </c>
       <c r="Y13" t="n">
-        <v>13.45150787722269</v>
+        <v>14.08478952690153</v>
       </c>
       <c r="Z13" t="n">
         <v>2</v>
@@ -2022,7 +2018,7 @@
         <v>46280</v>
       </c>
       <c r="C14" t="n">
-        <v>8.629728618421053</v>
+        <v>8.598889802631579</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,16 +2078,16 @@
         <v>16.11612055393703</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.151629528947365</v>
+        <v>4.494149018421057</v>
       </c>
       <c r="Z14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA14" t="n">
-        <v>37.03703703703704</v>
+        <v>42.30769230769231</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.88432945699038</v>
+        <v>11.99236835369544</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2131,7 +2127,7 @@
         <v>46280</v>
       </c>
       <c r="C15" t="n">
-        <v>13.3532072368421</v>
+        <v>13.46628289473684</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2159,22 +2155,22 @@
         <v>15.72365931533905</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2314814814814659</v>
+        <v>1.080246913580241</v>
       </c>
       <c r="L15" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="M15" t="n">
-        <v>65.625</v>
+        <v>65.67164179104478</v>
       </c>
       <c r="N15" t="n">
-        <v>17.37827400492326</v>
+        <v>17.61476075240802</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>7.750577367205569</v>
+        <v>6.845801526717565</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2201,10 +2197,10 @@
         <v>36.34743205418309</v>
       </c>
       <c r="Y15" t="n">
-        <v>15.52857519338381</v>
+        <v>14.81326674621462</v>
       </c>
       <c r="Z15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
@@ -2246,7 +2242,7 @@
         <v>46280</v>
       </c>
       <c r="C16" t="n">
-        <v>34.27220394736842</v>
+        <v>34.29276315789474</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,7 +2270,7 @@
         <v>16.99349200873118</v>
       </c>
       <c r="K16" t="n">
-        <v>2.026638385781476</v>
+        <v>2.087842128064521</v>
       </c>
       <c r="L16" t="n">
         <v>68</v>
@@ -2283,13 +2279,13 @@
         <v>66.17647058823529</v>
       </c>
       <c r="N16" t="n">
-        <v>18.05819349894421</v>
+        <v>18.04422109402139</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>7.814980225134716</v>
+        <v>7.750342946822264</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2355,7 +2351,7 @@
         <v>46280</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3834292763157894</v>
+        <v>0.3817845394736842</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,10 +2376,10 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>50.84308925225287</v>
+        <v>51.08056225103426</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1073537305421368</v>
+        <v>0.1618122977346426</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2394,7 +2390,7 @@
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>7.884182305630039</v>
+        <v>7.825525040387715</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2460,7 +2456,7 @@
         <v>46280</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0756578947368421</v>
+        <v>0.07504111842105263</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2488,22 +2484,22 @@
         <v>31.38464440531301</v>
       </c>
       <c r="K18" t="n">
-        <v>1.21835559096195</v>
+        <v>0.3932059529921483</v>
       </c>
       <c r="L18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M18" t="n">
-        <v>70</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N18" t="n">
-        <v>7.773339325178243</v>
+        <v>10.09916471732394</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>8.675940601649334</v>
+        <v>9.569167510703981</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2530,7 +2526,7 @@
         <v>11.24971294890111</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.016973700010134</v>
+        <v>9.758683153542657</v>
       </c>
       <c r="Z18" t="n">
         <v>17</v>
@@ -2539,7 +2535,7 @@
         <v>64.70588235294117</v>
       </c>
       <c r="AB18" t="n">
-        <v>13.08681286252515</v>
+        <v>11.44232129361223</v>
       </c>
       <c r="AC18" t="n">
         <v>8</v>
@@ -2579,7 +2575,7 @@
         <v>46280</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02734375</v>
+        <v>0.02672697368421053</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,25 +2600,25 @@
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>10.11859020594628</v>
+        <v>10.51926896239048</v>
       </c>
       <c r="K19" t="n">
-        <v>2.641166354910185</v>
+        <v>0.7751937984496138</v>
       </c>
       <c r="L19" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="M19" t="n">
-        <v>39.28571428571428</v>
+        <v>48.64864864864865</v>
       </c>
       <c r="N19" t="n">
-        <v>17.40676917955083</v>
+        <v>21.86850646288045</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>7.169475860830166</v>
+        <v>9.153846153846157</v>
       </c>
       <c r="Q19" t="n">
         <v>14</v>
@@ -2649,22 +2645,22 @@
         <v>20.26411217973316</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.744672651146778</v>
+        <v>9.825619884579561</v>
       </c>
       <c r="Z19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA19" t="n">
-        <v>42.85714285714285</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="AB19" t="n">
-        <v>12.39536789924539</v>
+        <v>15.54347334588223</v>
       </c>
       <c r="AC19" t="n">
         <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.444658117492715</v>
+        <v>0.1933809971271572</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -2698,7 +2694,7 @@
         <v>46280</v>
       </c>
       <c r="C20" t="n">
-        <v>1.581003289473684</v>
+        <v>1.6015625</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,22 +2722,22 @@
         <v>18.49305897009618</v>
       </c>
       <c r="K20" t="n">
-        <v>1.434186923266156</v>
+        <v>2.753227065311226</v>
       </c>
       <c r="L20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M20" t="n">
-        <v>59.375</v>
+        <v>45.16129032258065</v>
       </c>
       <c r="N20" t="n">
-        <v>15.26272061275122</v>
+        <v>14.5273195776619</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>8.444700289473218</v>
+        <v>7.052598873690497</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
@@ -2807,7 +2803,7 @@
         <v>46280</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9099506578947368</v>
+        <v>0.8992598684210527</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2906,7 +2902,7 @@
         <v>46280</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2958470394736842</v>
+        <v>0.2937911184210526</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2923,7 +2919,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>5</v>
       </c>
@@ -2931,25 +2931,25 @@
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>20.50947529336879</v>
+        <v>20.49639372369575</v>
       </c>
       <c r="K22" t="n">
-        <v>1.432342868683434</v>
+        <v>0.7108883429579604</v>
       </c>
       <c r="L22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M22" t="n">
-        <v>66.66666666666667</v>
+        <v>75</v>
       </c>
       <c r="N22" t="n">
-        <v>14.42455347331679</v>
+        <v>14.12177217454367</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>8.446671829722451</v>
+        <v>9.223542568117526</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -3007,7 +3007,7 @@
         <v>46280</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5995065789473684</v>
+        <v>0.6007401315789473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,10 +3032,10 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>41.01997583737742</v>
+        <v>41.58670221917339</v>
       </c>
       <c r="K23" t="n">
-        <v>0.06863417982152509</v>
+        <v>1.247401247401236</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -3046,7 +3046,7 @@
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.927983539094671</v>
+        <v>3.7063655030801</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3112,7 +3112,7 @@
         <v>46280</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1587171052631579</v>
+        <v>0.1548108552631579</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,7 +3129,11 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %83.33: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>5</v>
       </c>
@@ -3140,7 +3144,7 @@
         <v>23.31817459365587</v>
       </c>
       <c r="K24" t="n">
-        <v>4.943533826699475</v>
+        <v>2.360726647026845</v>
       </c>
       <c r="L24" t="n">
         <v>12</v>
@@ -3149,13 +3153,13 @@
         <v>50</v>
       </c>
       <c r="N24" t="n">
-        <v>12.45279767872284</v>
+        <v>11.72987778538172</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>4.818273207428514</v>
+        <v>7.463090194070099</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3182,16 +3186,16 @@
         <v>17.82705440547527</v>
       </c>
       <c r="Y24" t="n">
-        <v>10.9342634794553</v>
+        <v>13.12629585496091</v>
       </c>
       <c r="Z24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA24" t="n">
-        <v>50</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="AB24" t="n">
-        <v>14.00127512333066</v>
+        <v>13.54560099901865</v>
       </c>
       <c r="AC24" t="n">
         <v>2</v>
@@ -3231,7 +3235,7 @@
         <v>46280</v>
       </c>
       <c r="C25" t="n">
-        <v>3.338815789473684</v>
+        <v>3.316200657894737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3259,22 +3263,22 @@
         <v>20.95143919294578</v>
       </c>
       <c r="K25" t="n">
-        <v>1.633257286283185</v>
+        <v>0.9448546815115755</v>
       </c>
       <c r="L25" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M25" t="n">
-        <v>50</v>
+        <v>52.77777777777778</v>
       </c>
       <c r="N25" t="n">
-        <v>18.90967598469118</v>
+        <v>17.2679554084823</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>6.264428479137307</v>
+        <v>6.989108400569721</v>
       </c>
       <c r="Q25" t="n">
         <v>44</v>
@@ -3340,7 +3344,7 @@
         <v>46280</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4424342105263158</v>
+        <v>0.4416118421052632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3400,22 +3404,22 @@
         <v>11.40992936035117</v>
       </c>
       <c r="Y26" t="n">
-        <v>7.111852213729186</v>
+        <v>7.284506763517795</v>
       </c>
       <c r="Z26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA26" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.770743011220027</v>
+        <v>9.073612270240432</v>
       </c>
       <c r="AC26" t="n">
         <v>10</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.109274816111351</v>
+        <v>2.928845160275428</v>
       </c>
       <c r="AE26" t="n">
         <v>36</v>
@@ -3449,7 +3453,7 @@
         <v>46280</v>
       </c>
       <c r="C27" t="n">
-        <v>53.86513157894737</v>
+        <v>54.01932565789473</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3496,10 +3500,10 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>64.65730861892453</v>
+        <v>65.12508506386467</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.7575757575757569</v>
+        <v>0.7554296506138036</v>
       </c>
       <c r="Z27" t="n">
         <v>7</v>
@@ -3514,7 +3518,7 @@
         <v>6</v>
       </c>
       <c r="AD27" t="n">
-        <v>5.28244274809161</v>
+        <v>5.284490960989519</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3538,7 +3542,7 @@
         <v>46280</v>
       </c>
       <c r="C28" t="n">
-        <v>1.403166118421053</v>
+        <v>1.402138157894737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3563,25 +3567,25 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>16.51202083781934</v>
+        <v>16.9414263829347</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2939015429830993</v>
+        <v>0.7385569756661825</v>
       </c>
       <c r="L28" t="n">
         <v>50</v>
       </c>
       <c r="M28" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N28" t="n">
-        <v>13.90399291760403</v>
+        <v>14.7575783019116</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>1.701098901098907</v>
+        <v>1.25219485190613</v>
       </c>
       <c r="Q28" t="n">
         <v>39</v>
@@ -3647,7 +3651,7 @@
         <v>46280</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4272203947368421</v>
+        <v>0.4214638157894737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3675,7 +3679,7 @@
         <v>27.65210909859499</v>
       </c>
       <c r="K29" t="n">
-        <v>29.00960875077097</v>
+        <v>27.2712694605777</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3710,25 +3714,25 @@
         <v>80</v>
       </c>
       <c r="X29" t="n">
-        <v>31.18329731926355</v>
+        <v>31.20488584758381</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.656985769463037</v>
+        <v>2.99807157454155</v>
       </c>
       <c r="Z29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA29" t="n">
-        <v>27.27272727272727</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="AB29" t="n">
-        <v>19.10029836259243</v>
+        <v>14.3245685944975</v>
       </c>
       <c r="AC29" t="n">
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>8.483586044026637</v>
+        <v>7.2183394073852</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3762,7 +3766,7 @@
         <v>46280</v>
       </c>
       <c r="C30" t="n">
-        <v>0.412828947368421</v>
+        <v>0.4066611842105263</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,25 +3791,25 @@
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>11.08966243761319</v>
+        <v>12.46365070502794</v>
       </c>
       <c r="K30" t="n">
-        <v>0.09970089730808596</v>
+        <v>0.1518987341772249</v>
       </c>
       <c r="L30" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M30" t="n">
-        <v>44.82758620689656</v>
+        <v>44.06779661016949</v>
       </c>
       <c r="N30" t="n">
-        <v>13.60110875801091</v>
+        <v>14.17614401638845</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>4.895418326693224</v>
+        <v>4.840748230535885</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3832,16 +3836,16 @@
         <v>26.71344279693404</v>
       </c>
       <c r="Y30" t="n">
-        <v>11.00101803326385</v>
+        <v>12.33068409850392</v>
       </c>
       <c r="Z30" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AA30" t="n">
-        <v>63.63636363636363</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB30" t="n">
-        <v>16.0019560318442</v>
+        <v>11.98915066855684</v>
       </c>
       <c r="AC30" t="n">
         <v>8</v>
@@ -3938,10 +3942,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="X31" t="n">
-        <v>50.77283370106378</v>
+        <v>50.77283913219171</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.036021926389975</v>
+        <v>2.036025455241064</v>
       </c>
       <c r="Z31" t="n">
         <v>4</v>
@@ -3956,7 +3960,7 @@
         <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>8.129496402877701</v>
+        <v>8.129493093525175</v>
       </c>
       <c r="AE31" t="n">
         <v>10</v>
@@ -3990,7 +3994,7 @@
         <v>46280</v>
       </c>
       <c r="C32" t="n">
-        <v>2.335526315789473</v>
+        <v>2.290296052631579</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4050,22 +4054,22 @@
         <v>13.38656892008534</v>
       </c>
       <c r="Y32" t="n">
-        <v>5.487789317821989</v>
+        <v>7.318131426103591</v>
       </c>
       <c r="Z32" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AA32" t="n">
-        <v>27.77777777777778</v>
+        <v>37.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>11.60016728532967</v>
+        <v>12.35050329533333</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.658080542233821</v>
+        <v>0.7357087037501264</v>
       </c>
       <c r="AE32" t="n">
         <v>26</v>
@@ -4099,7 +4103,7 @@
         <v>46280</v>
       </c>
       <c r="C33" t="n">
-        <v>1.794819078947368</v>
+        <v>1.779399671052631</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4159,22 +4163,22 @@
         <v>15.09663082780621</v>
       </c>
       <c r="Y33" t="n">
-        <v>4.840127058056975</v>
+        <v>5.657651739688796</v>
       </c>
       <c r="Z33" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA33" t="n">
-        <v>34.21052631578947</v>
+        <v>29.72972972972973</v>
       </c>
       <c r="AB33" t="n">
-        <v>10.78870747941093</v>
+        <v>12.24828462139434</v>
       </c>
       <c r="AC33" t="n">
         <v>8</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.320593906079361</v>
+        <v>2.482817423463057</v>
       </c>
       <c r="AE33" t="n">
         <v>29</v>
@@ -4208,7 +4212,7 @@
         <v>46280</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8001644736842105</v>
+        <v>0.7923519736842105</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4236,16 +4240,16 @@
         <v>15.41713612942789</v>
       </c>
       <c r="K34" t="n">
-        <v>6.444565374108424</v>
+        <v>5.405281333970668</v>
       </c>
       <c r="L34" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="M34" t="n">
-        <v>63.33333333333334</v>
+        <v>62.85714285714285</v>
       </c>
       <c r="N34" t="n">
-        <v>12.85729889708578</v>
+        <v>13.67460151352577</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4278,16 +4282,16 @@
         <v>10.81830054752258</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.946762539945792</v>
+        <v>4.884589627171398</v>
       </c>
       <c r="Z34" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AA34" t="n">
-        <v>35.29411764705883</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="AB34" t="n">
-        <v>9.854642237875723</v>
+        <v>10.79959715099529</v>
       </c>
       <c r="AC34" t="n">
         <v>2</v>
@@ -4327,7 +4331,7 @@
         <v>46280</v>
       </c>
       <c r="C35" t="n">
-        <v>1.476151315789474</v>
+        <v>1.495682565789474</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4355,7 +4359,7 @@
         <v>38.83766461406507</v>
       </c>
       <c r="K35" t="n">
-        <v>6.535916361850158</v>
+        <v>7.945514141011123</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
@@ -4393,16 +4397,16 @@
         <v>13.94161507705984</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.499555680513347</v>
+        <v>5.262432809990891</v>
       </c>
       <c r="Z35" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA35" t="n">
-        <v>56.25</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB35" t="n">
-        <v>11.96300134878404</v>
+        <v>10.81081479976208</v>
       </c>
       <c r="AC35" t="n">
         <v>2</v>
@@ -4442,7 +4446,7 @@
         <v>46280</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07874177631578948</v>
+        <v>0.07833059210526316</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4470,22 +4474,22 @@
         <v>11.49958181785439</v>
       </c>
       <c r="K36" t="n">
-        <v>1.964075689583811</v>
+        <v>1.431626208176073</v>
       </c>
       <c r="L36" t="n">
         <v>39</v>
       </c>
       <c r="M36" t="n">
-        <v>58.97435897435897</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N36" t="n">
-        <v>18.13013090931801</v>
+        <v>16.86056520364298</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>0.03523232096522833</v>
+        <v>0.56035165073407</v>
       </c>
       <c r="Q36" t="n">
         <v>10</v>
@@ -4551,7 +4555,7 @@
         <v>46280</v>
       </c>
       <c r="C37" t="n">
-        <v>0.05736019736842105</v>
+        <v>0.05756578947368421</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4579,22 +4583,22 @@
         <v>22.69029993401852</v>
       </c>
       <c r="K37" t="n">
-        <v>1.454545454545464</v>
+        <v>1.81818181818183</v>
       </c>
       <c r="L37" t="n">
         <v>42</v>
       </c>
       <c r="M37" t="n">
-        <v>66.66666666666667</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N37" t="n">
-        <v>14.7166222045367</v>
+        <v>14.41584131925982</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>8.422939068100366</v>
+        <v>8.035714285714279</v>
       </c>
       <c r="Q37" t="n">
         <v>30</v>
@@ -4660,7 +4664,7 @@
         <v>46280</v>
       </c>
       <c r="C38" t="n">
-        <v>1.658100328947369</v>
+        <v>1.645764802631579</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4720,22 +4724,22 @@
         <v>12.11239445105858</v>
       </c>
       <c r="Y38" t="n">
-        <v>5.29559904093142</v>
+        <v>6.000157510558735</v>
       </c>
       <c r="Z38" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="AA38" t="n">
-        <v>43.90243902439025</v>
+        <v>51.35135135135135</v>
       </c>
       <c r="AB38" t="n">
-        <v>12.25836751823044</v>
+        <v>11.56887025161974</v>
       </c>
       <c r="AC38" t="n">
         <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.967457595874381</v>
+        <v>4.25515871464418</v>
       </c>
       <c r="AE38" t="n">
         <v>30</v>
@@ -4769,11 +4773,11 @@
         <v>46280</v>
       </c>
       <c r="C39" t="n">
-        <v>2.699424342105263</v>
+        <v>2.676809210526315</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4783,7 +4787,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4829,22 +4833,22 @@
         <v>10.27889366548247</v>
       </c>
       <c r="Y39" t="n">
-        <v>5.410642169339663</v>
+        <v>6.203089188484578</v>
       </c>
       <c r="Z39" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AA39" t="n">
-        <v>48.27586206896552</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="AB39" t="n">
-        <v>10.52661733838753</v>
+        <v>9.719662106532926</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.6230699141815177</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
         <v>40</v>
@@ -4997,7 +5001,7 @@
         <v>46280</v>
       </c>
       <c r="C41" t="n">
-        <v>1.251027960526316</v>
+        <v>1.253083881578947</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5025,7 +5029,7 @@
         <v>40.38073481248902</v>
       </c>
       <c r="K41" t="n">
-        <v>3.908641715529781</v>
+        <v>4.079403657543801</v>
       </c>
       <c r="L41" t="n">
         <v>3</v>
@@ -5034,13 +5038,13 @@
         <v>66.66666666666667</v>
       </c>
       <c r="N41" t="n">
-        <v>21.27827544303003</v>
+        <v>20.80389226397487</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>5.862224915947323</v>
+        <v>5.688537918546266</v>
       </c>
       <c r="Q41" t="n">
         <v>11</v>
@@ -5067,16 +5071,16 @@
         <v>14.15095011586145</v>
       </c>
       <c r="Y41" t="n">
-        <v>8.972600219214899</v>
+        <v>8.823007121793713</v>
       </c>
       <c r="Z41" t="n">
         <v>25</v>
       </c>
       <c r="AA41" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AB41" t="n">
-        <v>14.29560451668042</v>
+        <v>14.107400835227</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
@@ -5116,7 +5120,7 @@
         <v>46280</v>
       </c>
       <c r="C42" t="n">
-        <v>3.472450657894737</v>
+        <v>3.42516447368421</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5133,7 +5137,11 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir. SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H42" t="n">
         <v>5</v>
       </c>
@@ -5144,16 +5152,16 @@
         <v>17.9384880883827</v>
       </c>
       <c r="K42" t="n">
-        <v>9.414733469792047</v>
+        <v>7.924775583584109</v>
       </c>
       <c r="L42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M42" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="N42" t="n">
-        <v>9.440541403262504</v>
+        <v>8.47558445240162</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
@@ -5184,16 +5192,16 @@
         <v>23.05415424937474</v>
       </c>
       <c r="Y42" t="n">
-        <v>10.21261546062227</v>
+        <v>11.43529742889089</v>
       </c>
       <c r="Z42" t="n">
         <v>4</v>
       </c>
       <c r="AA42" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AB42" t="n">
-        <v>9.963868928768417</v>
+        <v>11.85948658534362</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
@@ -5231,7 +5239,7 @@
         <v>46280</v>
       </c>
       <c r="C43" t="n">
-        <v>6.183182565789473</v>
+        <v>6.162623355263158</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5259,22 +5267,22 @@
         <v>20.13868121382601</v>
       </c>
       <c r="K43" t="n">
-        <v>3.210300103169206</v>
+        <v>2.867123710473707</v>
       </c>
       <c r="L43" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M43" t="n">
-        <v>62.5</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N43" t="n">
-        <v>23.3116765368109</v>
+        <v>22.101174673634</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>0.7651367121705999</v>
+        <v>1.101300637815883</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5340,7 +5348,7 @@
         <v>46280</v>
       </c>
       <c r="C44" t="n">
-        <v>4.814967105263158</v>
+        <v>4.638157894736842</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5368,7 +5376,7 @@
         <v>25.31049029846984</v>
       </c>
       <c r="K44" t="n">
-        <v>25.37009720642329</v>
+        <v>20.76641302207129</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5403,25 +5411,25 @@
         <v>50</v>
       </c>
       <c r="X44" t="n">
-        <v>28.16158587198183</v>
+        <v>28.18267712431886</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.178100907979474</v>
+        <v>5.785699182312176</v>
       </c>
       <c r="Z44" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AA44" t="n">
-        <v>58.33333333333334</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB44" t="n">
-        <v>13.79357295589038</v>
+        <v>22.8628972099581</v>
       </c>
       <c r="AC44" t="n">
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>7.996061377486141</v>
+        <v>4.473100984788747</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5566,7 +5574,7 @@
         <v>46280</v>
       </c>
       <c r="C46" t="n">
-        <v>9.652549342105264</v>
+        <v>9.678248355263158</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5591,25 +5599,25 @@
         <v>10</v>
       </c>
       <c r="J46" t="n">
-        <v>11.2215464940971</v>
+        <v>11.55351720699311</v>
       </c>
       <c r="K46" t="n">
-        <v>0.3205128205128194</v>
+        <v>0.965147453083115</v>
       </c>
       <c r="L46" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M46" t="n">
-        <v>52.30769230769231</v>
+        <v>51.42857142857143</v>
       </c>
       <c r="N46" t="n">
-        <v>15.60882143722779</v>
+        <v>16.97705620942317</v>
       </c>
       <c r="O46" t="n">
         <v>8</v>
       </c>
       <c r="P46" t="n">
-        <v>7.654952076677324</v>
+        <v>6.967604885820511</v>
       </c>
       <c r="Q46" t="n">
         <v>51</v>
@@ -5636,7 +5644,7 @@
         <v>26.79655122306823</v>
       </c>
       <c r="Y46" t="n">
-        <v>10.93700016875766</v>
+        <v>10.69987823097481</v>
       </c>
       <c r="Z46" t="n">
         <v>11</v>
@@ -5685,7 +5693,7 @@
         <v>46280</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9617598684210527</v>
+        <v>0.9391447368421052</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5710,25 +5718,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>14.78818728107186</v>
+        <v>16.58327705889968</v>
       </c>
       <c r="K47" t="n">
-        <v>0.5588993981083368</v>
+        <v>0.3074220465524746</v>
       </c>
       <c r="L47" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="M47" t="n">
-        <v>57.37704918032787</v>
+        <v>65.45454545454545</v>
       </c>
       <c r="N47" t="n">
-        <v>15.95273903714644</v>
+        <v>15.6667579279566</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>9.388627618640456</v>
+        <v>9.662872154115609</v>
       </c>
       <c r="Q47" t="n">
         <v>51</v>
@@ -5755,10 +5763,10 @@
         <v>66.65983471422588</v>
       </c>
       <c r="Y47" t="n">
-        <v>14.31193897266858</v>
+        <v>16.32683566206714</v>
       </c>
       <c r="Z47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr"/>
@@ -5800,7 +5808,7 @@
         <v>46280</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05859375</v>
+        <v>0.05736019736842105</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5825,25 +5833,25 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>10.38175391788048</v>
+        <v>10.36700565279574</v>
       </c>
       <c r="K48" t="n">
-        <v>3.211403269674484</v>
+        <v>1.021906683062301</v>
       </c>
       <c r="L48" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M48" t="n">
-        <v>60.37735849056604</v>
+        <v>56.45161290322581</v>
       </c>
       <c r="N48" t="n">
-        <v>15.86771086172708</v>
+        <v>13.60756106086803</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>6.577370828481066</v>
+        <v>8.887273673327932</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5870,16 +5878,16 @@
         <v>19.37342145735985</v>
       </c>
       <c r="Y48" t="n">
-        <v>7.503750632974371</v>
+        <v>9.451040093332807</v>
       </c>
       <c r="Z48" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA48" t="n">
-        <v>63.1578947368421</v>
+        <v>50</v>
       </c>
       <c r="AB48" t="n">
-        <v>14.38574514248125</v>
+        <v>11.78809840197876</v>
       </c>
       <c r="AC48" t="n">
         <v>6</v>
@@ -5919,7 +5927,7 @@
         <v>46280</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2804276315789474</v>
+        <v>0.2769325657894737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5979,22 +5987,22 @@
         <v>22.46912765663718</v>
       </c>
       <c r="Y49" t="n">
-        <v>7.861745948762255</v>
+        <v>9.010096622421393</v>
       </c>
       <c r="Z49" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA49" t="n">
-        <v>58.8235294117647</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB49" t="n">
-        <v>9.63685023892678</v>
+        <v>10.4994260586429</v>
       </c>
       <c r="AC49" t="n">
         <v>10</v>
       </c>
       <c r="AD49" t="n">
-        <v>2.320701725093111</v>
+        <v>1.087926616946522</v>
       </c>
       <c r="AE49" t="n">
         <v>44</v>
@@ -6028,7 +6036,7 @@
         <v>46280</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7142269736842105</v>
+        <v>0.7014802631578947</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6088,16 +6096,16 @@
         <v>15.51990994893744</v>
       </c>
       <c r="Y50" t="n">
-        <v>7.400608441253686</v>
+        <v>9.053217041323425</v>
       </c>
       <c r="Z50" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA50" t="n">
-        <v>59.09090909090909</v>
+        <v>62.5</v>
       </c>
       <c r="AB50" t="n">
-        <v>12.16127348655176</v>
+        <v>11.3903374870045</v>
       </c>
       <c r="AC50" t="n">
         <v>5</v>
@@ -6137,7 +6145,7 @@
         <v>46280</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1381578947368421</v>
+        <v>0.1361019736842105</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6165,22 +6173,22 @@
         <v>31.62908307640215</v>
       </c>
       <c r="K51" t="n">
-        <v>3.736021366683273</v>
+        <v>2.192330572536205</v>
       </c>
       <c r="L51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M51" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N51" t="n">
-        <v>17.54885844674024</v>
+        <v>19.88394943304391</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>0.2544715228508965</v>
+        <v>1.768889521685502</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6207,16 +6215,16 @@
         <v>15.73461610040814</v>
       </c>
       <c r="Y51" t="n">
-        <v>10.36733445706099</v>
+        <v>11.70115388478328</v>
       </c>
       <c r="Z51" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA51" t="n">
-        <v>54.54545454545455</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB51" t="n">
-        <v>12.74817222949423</v>
+        <v>13.08784891453666</v>
       </c>
       <c r="AC51" t="n">
         <v>10</v>
@@ -6256,7 +6264,7 @@
         <v>46280</v>
       </c>
       <c r="C52" t="n">
-        <v>4.562088815789473</v>
+        <v>4.500411184210527</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6316,22 +6324,22 @@
         <v>16.62696858241317</v>
       </c>
       <c r="Y52" t="n">
-        <v>4.906250128952694</v>
+        <v>6.191879915402176</v>
       </c>
       <c r="Z52" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AA52" t="n">
-        <v>52</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="AB52" t="n">
-        <v>13.44481707492098</v>
+        <v>12.77300814854131</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.253368255266631</v>
+        <v>1.927466495402774</v>
       </c>
       <c r="AE52" t="n">
         <v>37</v>
@@ -6365,7 +6373,7 @@
         <v>46280</v>
       </c>
       <c r="C53" t="n">
-        <v>1.199629934210526</v>
+        <v>1.172902960526316</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6382,11 +6390,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>5</v>
       </c>
@@ -6394,25 +6398,25 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>30.25899953214985</v>
+        <v>31.87392835944998</v>
       </c>
       <c r="K53" t="n">
-        <v>0.08576329331047017</v>
+        <v>0.1755926251097328</v>
       </c>
       <c r="L53" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M53" t="n">
-        <v>75</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N53" t="n">
-        <v>12.24769996038692</v>
+        <v>18.43986724978525</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>7.907455012853459</v>
+        <v>7.810692375109585</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6467,14 +6471,14 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C54" t="n">
-        <v>0.07158034329423156</v>
+        <v>0.06969572574013158</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6484,14 +6488,10 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>BAZ_ORAN_YETERSİZ</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>5</v>
       </c>
@@ -6502,16 +6502,16 @@
         <v>29.5817777621179</v>
       </c>
       <c r="K54" t="n">
-        <v>14.04062722709962</v>
+        <v>11.03808549480698</v>
       </c>
       <c r="L54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M54" t="n">
-        <v>75</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N54" t="n">
-        <v>26.58918607430863</v>
+        <v>13.33340404686651</v>
       </c>
       <c r="O54" t="n">
         <v>10</v>
@@ -6544,22 +6544,22 @@
         <v>14.75410024187049</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.6217407598221314</v>
+        <v>3.238241369355122</v>
       </c>
       <c r="Z54" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA54" t="n">
-        <v>46.66666666666666</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="AB54" t="n">
-        <v>15.05166065777288</v>
+        <v>14.91104764783718</v>
       </c>
       <c r="AC54" t="n">
         <v>2</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.386882051180716</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
         <v>7</v>
@@ -6593,7 +6593,7 @@
         <v>46280</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9387335526315789</v>
+        <v>0.9239309210526315</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6653,16 +6653,16 @@
         <v>23.0932342837701</v>
       </c>
       <c r="Y55" t="n">
-        <v>6.081875051871988</v>
+        <v>7.562844170633531</v>
       </c>
       <c r="Z55" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA55" t="n">
-        <v>52.17391304347826</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="AB55" t="n">
-        <v>14.28198200849551</v>
+        <v>9.175890922370419</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6791,11 +6791,11 @@
         <v>46280</v>
       </c>
       <c r="C57" t="n">
-        <v>1.443256578947368</v>
+        <v>1.455592105263158</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -6851,22 +6851,22 @@
         <v>20.62560129901716</v>
       </c>
       <c r="Y57" t="n">
-        <v>5.228560176031294</v>
+        <v>4.418547869843536</v>
       </c>
       <c r="Z57" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AA57" t="n">
-        <v>48.88888888888889</v>
+        <v>44.68085106382978</v>
       </c>
       <c r="AB57" t="n">
-        <v>13.42789464309919</v>
+        <v>14.58664704587881</v>
       </c>
       <c r="AC57" t="n">
         <v>5</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>0.6083315509422094</v>
       </c>
       <c r="AE57" t="n">
         <v>44</v>
@@ -6900,7 +6900,7 @@
         <v>46280</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7232730263157895</v>
+        <v>0.7072368421052632</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6917,11 +6917,7 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6932,16 +6928,16 @@
         <v>18.04392839464337</v>
       </c>
       <c r="K58" t="n">
-        <v>10.86030109322786</v>
+        <v>8.402341034878869</v>
       </c>
       <c r="L58" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M58" t="n">
-        <v>75</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N58" t="n">
-        <v>21.43269864112183</v>
+        <v>27.49886566761452</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
@@ -6974,16 +6970,16 @@
         <v>20.50322102897642</v>
       </c>
       <c r="Y58" t="n">
-        <v>8.002209279891204</v>
+        <v>10.04195563468612</v>
       </c>
       <c r="Z58" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA58" t="n">
-        <v>47.05882352941177</v>
+        <v>50</v>
       </c>
       <c r="AB58" t="n">
-        <v>8.41957537447376</v>
+        <v>7.94428332794203</v>
       </c>
       <c r="AC58" t="n">
         <v>6</v>
@@ -7023,7 +7019,7 @@
         <v>46280</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7619243421052632</v>
+        <v>0.7434210526315789</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7051,22 +7047,22 @@
         <v>11.95882015364728</v>
       </c>
       <c r="K59" t="n">
-        <v>4.008035859790948</v>
+        <v>1.482206602537506</v>
       </c>
       <c r="L59" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="M59" t="n">
-        <v>72.91666666666667</v>
+        <v>60.9375</v>
       </c>
       <c r="N59" t="n">
-        <v>12.54496914631846</v>
+        <v>14.3457197144375</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>3.838130493676917</v>
+        <v>6.422597237158945</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7132,7 +7128,7 @@
         <v>46280</v>
       </c>
       <c r="C60" t="n">
-        <v>10.87582236842105</v>
+        <v>10.76274671052632</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7151,7 +7147,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -7164,22 +7160,22 @@
         <v>24.49246832941995</v>
       </c>
       <c r="K60" t="n">
-        <v>2.37415002941026</v>
+        <v>1.30976850736535</v>
       </c>
       <c r="L60" t="n">
         <v>18</v>
       </c>
       <c r="M60" t="n">
-        <v>88.88888888888889</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N60" t="n">
-        <v>12.78067502005031</v>
+        <v>13.91148315552294</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>5.495381372127173</v>
+        <v>6.603737814432242</v>
       </c>
       <c r="Q60" t="n">
         <v>46</v>
@@ -7245,7 +7241,7 @@
         <v>46280</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7537006578947367</v>
+        <v>0.7483552631578947</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7273,22 +7269,22 @@
         <v>14.0586191907223</v>
       </c>
       <c r="K61" t="n">
-        <v>5.5684170315216</v>
+        <v>4.819704853993079</v>
       </c>
       <c r="L61" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M61" t="n">
-        <v>62.96296296296296</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N61" t="n">
-        <v>23.90189858170725</v>
+        <v>20.98672965159386</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>4.197830272623282</v>
+        <v>4.942100488856305</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
@@ -7315,7 +7311,7 @@
         <v>49.99145178651283</v>
       </c>
       <c r="Y61" t="n">
-        <v>9.273044704613643</v>
+        <v>9.91649828826886</v>
       </c>
       <c r="Z61" t="n">
         <v>3</v>
@@ -7364,11 +7360,11 @@
         <v>46280</v>
       </c>
       <c r="C62" t="n">
-        <v>8.88671875</v>
+        <v>8.794202302631579</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7378,7 +7374,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -7424,22 +7420,22 @@
         <v>11.69351808836483</v>
       </c>
       <c r="Y62" t="n">
-        <v>4.907316484548996</v>
+        <v>5.897292368457685</v>
       </c>
       <c r="Z62" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AA62" t="n">
-        <v>46.15384615384615</v>
+        <v>36.11111111111111</v>
       </c>
       <c r="AB62" t="n">
-        <v>16.86033419604064</v>
+        <v>20.39839785042583</v>
       </c>
       <c r="AC62" t="n">
         <v>5</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.09746650533418721</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
         <v>27</v>
@@ -7473,7 +7469,7 @@
         <v>46280</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1097861842105263</v>
+        <v>0.1095805921052632</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7501,7 +7497,7 @@
         <v>14.68172212919103</v>
       </c>
       <c r="K63" t="n">
-        <v>4.870490480829592</v>
+        <v>4.6741037945359</v>
       </c>
       <c r="L63" t="n">
         <v>16</v>
@@ -7510,13 +7506,13 @@
         <v>56.25</v>
       </c>
       <c r="N63" t="n">
-        <v>14.52878225473388</v>
+        <v>14.75235065850451</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>0.1234947205611459</v>
+        <v>0.311343678761089</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7543,7 +7539,7 @@
         <v>24.85614965143601</v>
       </c>
       <c r="Y63" t="n">
-        <v>10.52630352708555</v>
+        <v>10.69385726579886</v>
       </c>
       <c r="Z63" t="n">
         <v>2</v>
@@ -7588,7 +7584,7 @@
         <v>46280</v>
       </c>
       <c r="C64" t="n">
-        <v>0.149671052631579</v>
+        <v>0.1467927631578947</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7613,25 +7609,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>10.61952064988008</v>
+        <v>11.53089624732437</v>
       </c>
       <c r="K64" t="n">
-        <v>1.062676940963181</v>
+        <v>0.1402524544179329</v>
       </c>
       <c r="L64" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="M64" t="n">
-        <v>58.8235294117647</v>
+        <v>58.22784810126582</v>
       </c>
       <c r="N64" t="n">
-        <v>16.93272537747344</v>
+        <v>15.76271671383996</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>3.895921994364793</v>
+        <v>4.852941176470615</v>
       </c>
       <c r="Q64" t="n">
         <v>55</v>
@@ -7658,16 +7654,16 @@
         <v>14.28923074155179</v>
       </c>
       <c r="Y64" t="n">
-        <v>9.669694906103988</v>
+        <v>11.40681615790969</v>
       </c>
       <c r="Z64" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA64" t="n">
-        <v>55.88235294117647</v>
+        <v>53.125</v>
       </c>
       <c r="AB64" t="n">
-        <v>16.02637799751902</v>
+        <v>16.91675138180393</v>
       </c>
       <c r="AC64" t="n">
         <v>2</v>
@@ -7707,7 +7703,7 @@
         <v>46280</v>
       </c>
       <c r="C65" t="n">
-        <v>6.352796052631579</v>
+        <v>6.285978618421052</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7716,7 +7712,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7731,17 +7727,27 @@
       <c r="I65" t="n">
         <v>10</v>
       </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="J65" t="n">
+        <v>11.21991868339847</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.4105090311986803</v>
+      </c>
       <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="M65" t="n">
+        <v>50.84745762711864</v>
+      </c>
+      <c r="N65" t="n">
+        <v>12.68335268993171</v>
+      </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
-      <c r="P65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>9.550286181520873</v>
+      </c>
       <c r="Q65" t="n">
         <v>50</v>
       </c>
@@ -7767,16 +7773,16 @@
         <v>24.47056390537039</v>
       </c>
       <c r="Y65" t="n">
-        <v>9.907897777241793</v>
+        <v>10.85546843168829</v>
       </c>
       <c r="Z65" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA65" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AB65" t="n">
-        <v>12.5316772036164</v>
+        <v>15.00601971697285</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
@@ -7816,7 +7822,7 @@
         <v>46280</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4432565789473684</v>
+        <v>0.4399671052631579</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7844,22 +7850,22 @@
         <v>10.41136575766793</v>
       </c>
       <c r="K66" t="n">
-        <v>2.177199404633368</v>
+        <v>1.418927052836461</v>
       </c>
       <c r="L66" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M66" t="n">
-        <v>57.14285714285715</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N66" t="n">
-        <v>17.66934610953342</v>
+        <v>16.81393866347435</v>
       </c>
       <c r="O66" t="n">
         <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>3.741344074452368</v>
+        <v>4.516980291831452</v>
       </c>
       <c r="Q66" t="n">
         <v>35</v>
@@ -7886,16 +7892,16 @@
         <v>14.59585890675015</v>
       </c>
       <c r="Y66" t="n">
-        <v>8.460842546324709</v>
+        <v>9.140168390136772</v>
       </c>
       <c r="Z66" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AA66" t="n">
-        <v>44.82758620689656</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="AB66" t="n">
-        <v>10.68423274679701</v>
+        <v>7.980056818083106</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
@@ -8049,10 +8055,10 @@
         <v>10</v>
       </c>
       <c r="J68" t="n">
-        <v>72.03677495621962</v>
+        <v>72.03677607916677</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>4.015800048051688e-06</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -8063,7 +8069,7 @@
         <v>2</v>
       </c>
       <c r="P68" t="n">
-        <v>2.000000000000002</v>
+        <v>1.999995903884111</v>
       </c>
       <c r="Q68" t="n">
         <v>5</v>
@@ -8129,7 +8135,7 @@
         <v>46280</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4609375000000001</v>
+        <v>0.4444901315789474</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8154,25 +8160,25 @@
         <v>10</v>
       </c>
       <c r="J69" t="n">
-        <v>17.83849147064036</v>
+        <v>21.76381940295035</v>
       </c>
       <c r="K69" t="n">
-        <v>0.7187780772686558</v>
+        <v>1.981132075471725</v>
       </c>
       <c r="L69" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="M69" t="n">
-        <v>70.83333333333333</v>
+        <v>62.5</v>
       </c>
       <c r="N69" t="n">
-        <v>19.56180727983456</v>
+        <v>23.29418610693553</v>
       </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>7.229259589652082</v>
+        <v>5.90194264569841</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8188,13 +8194,13 @@
         <v>75</v>
       </c>
       <c r="X69" t="n">
-        <v>45.3445702232411</v>
+        <v>45.36848923911108</v>
       </c>
       <c r="Y69" t="n">
-        <v>17.24793255937811</v>
+        <v>20.21385733451822</v>
       </c>
       <c r="Z69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="inlineStr"/>
       <c r="AB69" t="inlineStr"/>
@@ -8228,7 +8234,7 @@
         <v>46280</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4860197368421053</v>
+        <v>0.4712171052631579</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8253,25 +8259,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>13.55581486783012</v>
+        <v>14.89488141893085</v>
       </c>
       <c r="K70" t="n">
-        <v>1.721170395869187</v>
+        <v>0.1748251748251883</v>
       </c>
       <c r="L70" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="M70" t="n">
-        <v>52.63157894736842</v>
+        <v>47.91666666666666</v>
       </c>
       <c r="N70" t="n">
-        <v>13.38056879992976</v>
+        <v>13.45489858645554</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>6.172588832487325</v>
+        <v>7.811518324607314</v>
       </c>
       <c r="Q70" t="n">
         <v>31</v>
@@ -8298,16 +8304,16 @@
         <v>44.93251946562029</v>
       </c>
       <c r="Y70" t="n">
-        <v>12.06796314438485</v>
+        <v>14.74609624658633</v>
       </c>
       <c r="Z70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA70" t="n">
-        <v>40</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB70" t="n">
-        <v>8.42308193419985</v>
+        <v>10.10431955682505</v>
       </c>
       <c r="AC70" t="n">
         <v>8</v>
@@ -8347,7 +8353,7 @@
         <v>46280</v>
       </c>
       <c r="C71" t="n">
-        <v>3.139391447368421</v>
+        <v>3.122944078947369</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8446,11 +8452,11 @@
         <v>46280</v>
       </c>
       <c r="C72" t="n">
-        <v>0.06229440789473684</v>
+        <v>0.06064967105263158</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -8460,7 +8466,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -8474,22 +8480,22 @@
         <v>29.77666337790048</v>
       </c>
       <c r="K72" t="n">
-        <v>4.391415580610269</v>
+        <v>1.635206588382943</v>
       </c>
       <c r="L72" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M72" t="n">
-        <v>58.33333333333334</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N72" t="n">
-        <v>16.15545700593165</v>
+        <v>28.32418695070399</v>
       </c>
       <c r="O72" t="n">
         <v>10</v>
       </c>
       <c r="P72" t="n">
-        <v>5.372649070994573</v>
+        <v>8.230212435631712</v>
       </c>
       <c r="Q72" t="n">
         <v>15</v>
@@ -8516,22 +8522,22 @@
         <v>12.03392243896149</v>
       </c>
       <c r="Y72" t="n">
-        <v>6.821600718760013</v>
+        <v>9.281756475360392</v>
       </c>
       <c r="Z72" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AA72" t="n">
-        <v>64.28571428571429</v>
+        <v>72.22222222222223</v>
       </c>
       <c r="AB72" t="n">
-        <v>11.98292987346552</v>
+        <v>11.95910730857625</v>
       </c>
       <c r="AC72" t="n">
         <v>8</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.264670020444569</v>
+        <v>0</v>
       </c>
       <c r="AE72" t="n">
         <v>10</v>
@@ -8565,7 +8571,7 @@
         <v>46280</v>
       </c>
       <c r="C73" t="n">
-        <v>0.06270559210526315</v>
+        <v>0.06188322368421052</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8584,7 +8590,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H73" t="n">
@@ -8597,22 +8603,22 @@
         <v>19.59098648410814</v>
       </c>
       <c r="K73" t="n">
-        <v>2.717056403802975</v>
+        <v>1.369947467359678</v>
       </c>
       <c r="L73" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="M73" t="n">
-        <v>77.77777777777777</v>
+        <v>75</v>
       </c>
       <c r="N73" t="n">
-        <v>13.08601002425486</v>
+        <v>14.98687719878846</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>7.090296247943684</v>
+        <v>8.513423108381435</v>
       </c>
       <c r="Q73" t="n">
         <v>14</v>
@@ -8636,25 +8642,25 @@
         <v>73.91304347826087</v>
       </c>
       <c r="X73" t="n">
-        <v>12.20056545653823</v>
+        <v>12.21903004108828</v>
       </c>
       <c r="Y73" t="n">
-        <v>8.452282761809037</v>
+        <v>9.667774324690104</v>
       </c>
       <c r="Z73" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA73" t="n">
-        <v>61.90476190476191</v>
+        <v>60</v>
       </c>
       <c r="AB73" t="n">
-        <v>12.56634401674117</v>
+        <v>13.8062690275649</v>
       </c>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.690612595138852</v>
+        <v>0.3677820100481566</v>
       </c>
       <c r="AE73" t="n">
         <v>15</v>
@@ -8688,7 +8694,7 @@
         <v>46280</v>
       </c>
       <c r="C74" t="n">
-        <v>5.46875</v>
+        <v>5.355674342105263</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8713,25 +8719,25 @@
         <v>10</v>
       </c>
       <c r="J74" t="n">
-        <v>10.3710262941641</v>
+        <v>10.76052373623427</v>
       </c>
       <c r="K74" t="n">
-        <v>2.852059520067707</v>
+        <v>1.165048543689307</v>
       </c>
       <c r="L74" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="M74" t="n">
-        <v>68.96551724137932</v>
+        <v>74.02597402597402</v>
       </c>
       <c r="N74" t="n">
-        <v>15.37522658799305</v>
+        <v>15.07095239639585</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>5.005189496402718</v>
+        <v>6.756238003838799</v>
       </c>
       <c r="Q74" t="n">
         <v>28</v>
@@ -8758,7 +8764,7 @@
         <v>24.51464461150628</v>
       </c>
       <c r="Y74" t="n">
-        <v>7.81475461684783</v>
+        <v>9.720840517627295</v>
       </c>
       <c r="Z74" t="n">
         <v>17</v>
@@ -8767,13 +8773,13 @@
         <v>47.05882352941177</v>
       </c>
       <c r="AB74" t="n">
-        <v>16.19517978112393</v>
+        <v>19.05515588362151</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>2.370493644692895</v>
+        <v>0.309218078649931</v>
       </c>
       <c r="AE74" t="n">
         <v>37</v>
@@ -8807,16 +8813,16 @@
         <v>46280</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1192434210526316</v>
+        <v>0.1151315789473684</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8824,11 +8830,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>5</v>
       </c>
@@ -8836,25 +8838,25 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>26.72158757960922</v>
+        <v>26.70952832272112</v>
       </c>
       <c r="K75" t="n">
-        <v>9.795858043717853</v>
+        <v>5.992351060013146</v>
       </c>
       <c r="L75" t="n">
         <v>4</v>
       </c>
       <c r="M75" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="N75" t="n">
-        <v>7.64301986624898</v>
+        <v>13.26881515701794</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>0.007216501861084801</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8920,7 +8922,7 @@
         <v>46280</v>
       </c>
       <c r="C76" t="n">
-        <v>1.910978618421053</v>
+        <v>1.877055921052631</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8980,16 +8982,16 @@
         <v>12.60650925728801</v>
       </c>
       <c r="Y76" t="n">
-        <v>5.882167414512929</v>
+        <v>7.552898170468325</v>
       </c>
       <c r="Z76" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="AA76" t="n">
-        <v>48.38709677419355</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB76" t="n">
-        <v>11.16550151644106</v>
+        <v>10.21650177017549</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
@@ -9029,7 +9031,7 @@
         <v>46280</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4753289473684211</v>
+        <v>0.4683388157894737</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9054,25 +9056,25 @@
         <v>10</v>
       </c>
       <c r="J77" t="n">
-        <v>16.91408941611843</v>
+        <v>18.49667872866365</v>
       </c>
       <c r="K77" t="n">
-        <v>0.08658008658009031</v>
+        <v>0.5295681853237255</v>
       </c>
       <c r="L77" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="M77" t="n">
-        <v>69.56521739130434</v>
+        <v>67.56756756756756</v>
       </c>
       <c r="N77" t="n">
-        <v>15.25920687533237</v>
+        <v>13.22991500687594</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>7.906574394463672</v>
+        <v>7.431079183494282</v>
       </c>
       <c r="Q77" t="n">
         <v>27</v>
@@ -9138,7 +9140,7 @@
         <v>46280</v>
       </c>
       <c r="C78" t="n">
-        <v>0.06229440789473684</v>
+        <v>0.06167763157894737</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9198,22 +9200,22 @@
         <v>36.6270136023539</v>
       </c>
       <c r="Y78" t="n">
-        <v>0.9803921568627527</v>
+        <v>1.960784313725494</v>
       </c>
       <c r="Z78" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA78" t="n">
-        <v>33.33333333333334</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="AB78" t="n">
-        <v>13.6227572469659</v>
+        <v>13.19983451314134</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>9.108910891089096</v>
+        <v>8.199999999999996</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9247,7 +9249,7 @@
         <v>46280</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8943256578947368</v>
+        <v>0.8782894736842105</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9272,25 +9274,25 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>10.42896938309872</v>
+        <v>12.12688233224525</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2240766042592712</v>
+        <v>0.3287928604978951</v>
       </c>
       <c r="L79" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M79" t="n">
-        <v>54</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="N79" t="n">
-        <v>10.46975513357592</v>
+        <v>10.84358950105503</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>4.765245595226331</v>
+        <v>4.655898876404496</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9317,16 +9319,16 @@
         <v>25.65117214954458</v>
       </c>
       <c r="Y79" t="n">
-        <v>10.22826165929234</v>
+        <v>11.83796179505675</v>
       </c>
       <c r="Z79" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA79" t="n">
-        <v>66.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="AB79" t="n">
-        <v>8.267177553195101</v>
+        <v>9.291824236449653</v>
       </c>
       <c r="AC79" t="n">
         <v>8</v>
@@ -9366,7 +9368,7 @@
         <v>46280</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1334292763157895</v>
+        <v>0.1319901315789474</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9394,22 +9396,22 @@
         <v>10.48668504530712</v>
       </c>
       <c r="K80" t="n">
-        <v>4.379131252789747</v>
+        <v>3.253316277798191</v>
       </c>
       <c r="L80" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="M80" t="n">
-        <v>55.55555555555556</v>
+        <v>50</v>
       </c>
       <c r="N80" t="n">
-        <v>18.99122853136501</v>
+        <v>18.03620210753327</v>
       </c>
       <c r="O80" t="n">
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>5.385050325430862</v>
+        <v>6.534108506549252</v>
       </c>
       <c r="Q80" t="n">
         <v>39</v>
@@ -9436,22 +9438,22 @@
         <v>16.92042739318289</v>
       </c>
       <c r="Y80" t="n">
-        <v>6.566779494718045</v>
+        <v>7.574533799089345</v>
       </c>
       <c r="Z80" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AA80" t="n">
-        <v>46.875</v>
+        <v>40</v>
       </c>
       <c r="AB80" t="n">
-        <v>15.2833189605872</v>
+        <v>11.85500933413414</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.533951733153549</v>
+        <v>0.4603343844496122</v>
       </c>
       <c r="AE80" t="n">
         <v>24</v>
@@ -9485,7 +9487,7 @@
         <v>46280</v>
       </c>
       <c r="C81" t="n">
-        <v>1.222245065789474</v>
+        <v>1.209909539473684</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9542,25 +9544,25 @@
         <v>65.30612244897959</v>
       </c>
       <c r="X81" t="n">
-        <v>23.77188968593224</v>
+        <v>23.79225853623819</v>
       </c>
       <c r="Y81" t="n">
-        <v>4.0040076447863</v>
+        <v>4.988484433349949</v>
       </c>
       <c r="Z81" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA81" t="n">
-        <v>41.1764705882353</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB81" t="n">
-        <v>11.01125755024417</v>
+        <v>9.586500143562752</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>6.246086120998406</v>
+        <v>5.274640170469125</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9591,10 +9593,10 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C82" t="n">
-        <v>4.769965826980715</v>
+        <v>4.710115256990131</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9619,25 +9621,25 @@
         <v>10</v>
       </c>
       <c r="J82" t="n">
-        <v>16.34835816551005</v>
+        <v>16.59648495929817</v>
       </c>
       <c r="K82" t="n">
-        <v>1.994243930879991</v>
+        <v>1.014110678602131</v>
       </c>
       <c r="L82" t="n">
         <v>9</v>
       </c>
       <c r="M82" t="n">
-        <v>22.22222222222222</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="N82" t="n">
-        <v>13.12629555041259</v>
+        <v>8.08000535343627</v>
       </c>
       <c r="O82" t="n">
         <v>4</v>
       </c>
       <c r="P82" t="n">
-        <v>1.966538494544157</v>
+        <v>2.955913091090911</v>
       </c>
       <c r="Q82" t="n">
         <v>8</v>
@@ -9703,7 +9705,7 @@
         <v>46280</v>
       </c>
       <c r="C83" t="n">
-        <v>5.417351973684211</v>
+        <v>5.376233552631579</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9731,22 +9733,22 @@
         <v>13.10783674393532</v>
       </c>
       <c r="K83" t="n">
-        <v>2.371834885399493</v>
+        <v>1.594819060842378</v>
       </c>
       <c r="L83" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M83" t="n">
-        <v>54.28571428571428</v>
+        <v>54.92957746478874</v>
       </c>
       <c r="N83" t="n">
-        <v>11.55700610672134</v>
+        <v>12.57247505236158</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>7.45142951002089</v>
+        <v>8.273237766311681</v>
       </c>
       <c r="Q83" t="n">
         <v>41</v>
@@ -9812,7 +9814,7 @@
         <v>46280</v>
       </c>
       <c r="C84" t="n">
-        <v>2.068256578947368</v>
+        <v>2.051809210526315</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9840,16 +9842,16 @@
         <v>14.20091622675307</v>
       </c>
       <c r="K84" t="n">
-        <v>6.666982675923494</v>
+        <v>5.818736292814752</v>
       </c>
       <c r="L84" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M84" t="n">
-        <v>62.85714285714285</v>
+        <v>60</v>
       </c>
       <c r="N84" t="n">
-        <v>9.407327680389011</v>
+        <v>10.22920434941103</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9882,16 +9884,16 @@
         <v>11.86663135768809</v>
       </c>
       <c r="Y84" t="n">
-        <v>4.648078357825025</v>
+        <v>5.406344136291629</v>
       </c>
       <c r="Z84" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AA84" t="n">
-        <v>31.70731707317073</v>
+        <v>41.02564102564103</v>
       </c>
       <c r="AB84" t="n">
-        <v>11.99860234384794</v>
+        <v>11.13153188861626</v>
       </c>
       <c r="AC84" t="n">
         <v>2</v>
@@ -9931,7 +9933,7 @@
         <v>46280</v>
       </c>
       <c r="C85" t="n">
-        <v>6.003289473684211</v>
+        <v>5.987870065789473</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9956,25 +9958,25 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>10.58907718287831</v>
+        <v>10.95455571191028</v>
       </c>
       <c r="K85" t="n">
-        <v>0.2780733890961118</v>
+        <v>0.4310344827586299</v>
       </c>
       <c r="L85" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M85" t="n">
-        <v>55.73770491803279</v>
+        <v>59.375</v>
       </c>
       <c r="N85" t="n">
-        <v>12.40455796654371</v>
+        <v>11.97117941249298</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>7.700513531947806</v>
+        <v>7.536480686695279</v>
       </c>
       <c r="Q85" t="n">
         <v>32</v>
@@ -10040,7 +10042,7 @@
         <v>46280</v>
       </c>
       <c r="C86" t="n">
-        <v>4.658717105263158</v>
+        <v>4.761513157894736</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10059,7 +10061,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -10072,16 +10074,16 @@
         <v>18.73514495170452</v>
       </c>
       <c r="K86" t="n">
-        <v>11.74899235791773</v>
+        <v>14.21476888832189</v>
       </c>
       <c r="L86" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M86" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N86" t="n">
-        <v>16.52493490543912</v>
+        <v>11.59313326334698</v>
       </c>
       <c r="O86" t="n">
         <v>8</v>
@@ -10114,16 +10116,16 @@
         <v>44.99483923332605</v>
       </c>
       <c r="Y86" t="n">
-        <v>9.187343342407372</v>
+        <v>7.183533619159521</v>
       </c>
       <c r="Z86" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA86" t="n">
-        <v>33.33333333333334</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB86" t="n">
-        <v>19.4387621860991</v>
+        <v>15.39519764941737</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
@@ -10163,7 +10165,7 @@
         <v>46280</v>
       </c>
       <c r="C87" t="n">
-        <v>5.890213815789473</v>
+        <v>5.895353618421052</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10223,16 +10225,16 @@
         <v>15.88967756874082</v>
       </c>
       <c r="Y87" t="n">
-        <v>4.5144792689083</v>
+        <v>4.431158570190075</v>
       </c>
       <c r="Z87" t="n">
         <v>36</v>
       </c>
       <c r="AA87" t="n">
-        <v>44.44444444444444</v>
+        <v>47.22222222222222</v>
       </c>
       <c r="AB87" t="n">
-        <v>11.04384941659857</v>
+        <v>10.77883709639034</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
@@ -10272,7 +10274,7 @@
         <v>46280</v>
       </c>
       <c r="C88" t="n">
-        <v>1.051603618421053</v>
+        <v>1.053659539473684</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10300,16 +10302,16 @@
         <v>16.8583060727446</v>
       </c>
       <c r="K88" t="n">
-        <v>5.777956597579137</v>
+        <v>5.984756121719093</v>
       </c>
       <c r="L88" t="n">
         <v>35</v>
       </c>
       <c r="M88" t="n">
-        <v>74.28571428571429</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N88" t="n">
-        <v>13.98786437648149</v>
+        <v>13.50801971257277</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
@@ -10342,16 +10344,16 @@
         <v>22.33299319731812</v>
       </c>
       <c r="Y88" t="n">
-        <v>12.05441508313568</v>
+        <v>11.88247845573224</v>
       </c>
       <c r="Z88" t="n">
         <v>15</v>
       </c>
       <c r="AA88" t="n">
-        <v>40</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB88" t="n">
-        <v>12.45830595672115</v>
+        <v>13.04416571402357</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
@@ -10391,7 +10393,7 @@
         <v>46280</v>
       </c>
       <c r="C89" t="n">
-        <v>2.177220394736842</v>
+        <v>2.160773026315789</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10451,22 +10453,22 @@
         <v>21.41032003314154</v>
       </c>
       <c r="Y89" t="n">
-        <v>7.017358416666686</v>
+        <v>7.719776861111127</v>
       </c>
       <c r="Z89" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA89" t="n">
-        <v>41.66666666666666</v>
+        <v>34.375</v>
       </c>
       <c r="AB89" t="n">
-        <v>16.48426081594873</v>
+        <v>17.43017018367781</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>3.20774021101583</v>
+        <v>2.470977053725754</v>
       </c>
       <c r="AE89" t="n">
         <v>22</v>
@@ -10500,7 +10502,7 @@
         <v>46280</v>
       </c>
       <c r="C90" t="n">
-        <v>2.783717105263158</v>
+        <v>2.761101973684211</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10528,22 +10530,22 @@
         <v>12.8208334231333</v>
       </c>
       <c r="K90" t="n">
-        <v>2.20771614374875</v>
+        <v>1.377372807278121</v>
       </c>
       <c r="L90" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="M90" t="n">
-        <v>66.29213483146067</v>
+        <v>66.30434782608695</v>
       </c>
       <c r="N90" t="n">
-        <v>14.17641525480765</v>
+        <v>14.01635044001331</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>5.667168854555737</v>
+        <v>6.532648271830577</v>
       </c>
       <c r="Q90" t="n">
         <v>43</v>
@@ -10570,16 +10572,16 @@
         <v>20.63086277737274</v>
       </c>
       <c r="Y90" t="n">
-        <v>10.89616488863021</v>
+        <v>11.62005128909185</v>
       </c>
       <c r="Z90" t="n">
         <v>20</v>
       </c>
       <c r="AA90" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="AB90" t="n">
-        <v>11.64511465808553</v>
+        <v>11.07727095335549</v>
       </c>
       <c r="AC90" t="n">
         <v>2</v>
@@ -10619,7 +10621,7 @@
         <v>46280</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2319078947368421</v>
+        <v>0.2300575657894737</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10718,7 +10720,7 @@
         <v>46280</v>
       </c>
       <c r="C92" t="n">
-        <v>1.162623355263158</v>
+        <v>1.156455592105263</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10778,16 +10780,16 @@
         <v>21.60407460332612</v>
       </c>
       <c r="Y92" t="n">
-        <v>7.15807770657817</v>
+        <v>7.650607798320452</v>
       </c>
       <c r="Z92" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA92" t="n">
-        <v>47.05882352941177</v>
+        <v>50</v>
       </c>
       <c r="AB92" t="n">
-        <v>15.78239274433468</v>
+        <v>15.7448586692875</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10827,7 +10829,7 @@
         <v>46280</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04214638157894737</v>
+        <v>0.04194078947368421</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10887,16 +10889,16 @@
         <v>11.4419372600254</v>
       </c>
       <c r="Y93" t="n">
-        <v>4.105905270510624</v>
+        <v>4.573681342361791</v>
       </c>
       <c r="Z93" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA93" t="n">
-        <v>45.23809523809524</v>
+        <v>45</v>
       </c>
       <c r="AB93" t="n">
-        <v>13.26309491661619</v>
+        <v>15.44736513139534</v>
       </c>
       <c r="AC93" t="n">
         <v>2</v>
@@ -10936,7 +10938,7 @@
         <v>46280</v>
       </c>
       <c r="C94" t="n">
-        <v>8.403577302631579</v>
+        <v>8.383018092105264</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10996,22 +10998,22 @@
         <v>40.43377921558155</v>
       </c>
       <c r="Y94" t="n">
-        <v>3.672155778486907</v>
+        <v>3.907820229181724</v>
       </c>
       <c r="Z94" t="n">
         <v>8</v>
       </c>
       <c r="AA94" t="n">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="AB94" t="n">
-        <v>14.14910941095578</v>
+        <v>17.4269499551429</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>2.41658498674594</v>
+        <v>2.1772633067625</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -11042,10 +11044,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1211517845616504</v>
+        <v>0.1215049311266447</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11070,25 +11072,25 @@
         <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>19.07067465137798</v>
+        <v>19.52215329413863</v>
       </c>
       <c r="K95" t="n">
-        <v>0.1700639423967587</v>
+        <v>1.025640188472488</v>
       </c>
       <c r="L95" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M95" t="n">
-        <v>58.33333333333334</v>
+        <v>60</v>
       </c>
       <c r="N95" t="n">
-        <v>16.13870371541334</v>
+        <v>17.7408548510624</v>
       </c>
       <c r="O95" t="n">
         <v>10</v>
       </c>
       <c r="P95" t="n">
-        <v>9.813247262431624</v>
+        <v>8.883249633246603</v>
       </c>
       <c r="Q95" t="n">
         <v>21</v>
@@ -11154,7 +11156,7 @@
         <v>46280</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1264391447368421</v>
+        <v>0.1262335526315789</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11253,7 +11255,7 @@
         <v>46280</v>
       </c>
       <c r="C97" t="n">
-        <v>1.868832236842105</v>
+        <v>1.856496710526316</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11281,22 +11283,22 @@
         <v>12.87370897365936</v>
       </c>
       <c r="K97" t="n">
-        <v>2.152778784502352</v>
+        <v>1.478503016947874</v>
       </c>
       <c r="L97" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M97" t="n">
-        <v>55.93220338983051</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N97" t="n">
-        <v>13.83994361589519</v>
+        <v>13.3315532081546</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>1.808292674440581</v>
+        <v>2.484759735400321</v>
       </c>
       <c r="Q97" t="n">
         <v>50</v>
@@ -11323,7 +11325,7 @@
         <v>16.31583297271808</v>
       </c>
       <c r="Y97" t="n">
-        <v>10.99807266472052</v>
+        <v>11.58554413228012</v>
       </c>
       <c r="Z97" t="n">
         <v>11</v>
@@ -11372,11 +11374,11 @@
         <v>46280</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7236842105263158</v>
+        <v>0.7125822368421052</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -11386,7 +11388,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -11432,22 +11434,22 @@
         <v>30.85778357900837</v>
       </c>
       <c r="Y98" t="n">
-        <v>7.65406364836937</v>
+        <v>9.070734262854629</v>
       </c>
       <c r="Z98" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA98" t="n">
         <v>50</v>
       </c>
       <c r="AB98" t="n">
-        <v>9.329134053398002</v>
+        <v>9.12047942398932</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
       <c r="AD98" t="n">
-        <v>0.3746091764269766</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
         <v>51</v>
@@ -11481,7 +11483,7 @@
         <v>46280</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5616776315789473</v>
+        <v>0.5604440789473685</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11500,7 +11502,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %76.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H99" t="n">
@@ -11510,19 +11512,19 @@
         <v>10</v>
       </c>
       <c r="J99" t="n">
-        <v>12.53074443988439</v>
+        <v>12.51634982914205</v>
       </c>
       <c r="K99" t="n">
-        <v>9.5783001019784</v>
+        <v>9.31965449752974</v>
       </c>
       <c r="L99" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="M99" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N99" t="n">
-        <v>12.87930960772016</v>
+        <v>13.44442617194759</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
@@ -11555,7 +11557,7 @@
         <v>33.04241514445872</v>
       </c>
       <c r="Y99" t="n">
-        <v>4.152676645370102</v>
+        <v>4.363175891390503</v>
       </c>
       <c r="Z99" t="n">
         <v>11</v>
@@ -11564,13 +11566,13 @@
         <v>27.27272727272727</v>
       </c>
       <c r="AB99" t="n">
-        <v>16.01798172400412</v>
+        <v>15.93679849313842</v>
       </c>
       <c r="AC99" t="n">
         <v>10</v>
       </c>
       <c r="AD99" t="n">
-        <v>6.10066421259895</v>
+        <v>5.893989225539387</v>
       </c>
       <c r="AE99" t="n">
         <v>38</v>
@@ -11601,10 +11603,10 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C100" t="n">
-        <v>347.2508361113702</v>
+        <v>337.8016020123355</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11664,22 +11666,22 @@
         <v>16.86980163304483</v>
       </c>
       <c r="Y100" t="n">
-        <v>4.685873010566133</v>
+        <v>7.27951831018302</v>
       </c>
       <c r="Z100" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AA100" t="n">
-        <v>38.23529411764706</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="AB100" t="n">
-        <v>13.21766654686114</v>
+        <v>12.00550094398526</v>
       </c>
       <c r="AC100" t="n">
         <v>8</v>
       </c>
       <c r="AD100" t="n">
-        <v>3.47705748781737</v>
+        <v>0.7770469659845403</v>
       </c>
       <c r="AE100" t="n">
         <v>39</v>
@@ -11713,7 +11715,7 @@
         <v>46280</v>
       </c>
       <c r="C101" t="n">
-        <v>345.0684621710527</v>
+        <v>343.6484375</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11773,22 +11775,22 @@
         <v>12.90626814318425</v>
       </c>
       <c r="Y101" t="n">
-        <v>4.527332509196025</v>
+        <v>4.920221335938313</v>
       </c>
       <c r="Z101" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="AA101" t="n">
-        <v>36.36363636363637</v>
+        <v>35.48387096774194</v>
       </c>
       <c r="AB101" t="n">
-        <v>11.34254663831077</v>
+        <v>13.3985840727138</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>1.542501670382079</v>
+        <v>1.13565542456382</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11819,14 +11821,14 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C102" t="n">
-        <v>408.5304166937231</v>
+        <v>404.2588484913651</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -11836,7 +11838,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -11878,27 +11880,17 @@
       <c r="W102" t="n">
         <v>47.22222222222222</v>
       </c>
-      <c r="X102" t="n">
-        <v>10.81355469301844</v>
-      </c>
-      <c r="Y102" t="n">
-        <v>4.163349615992463</v>
-      </c>
+      <c r="X102" t="inlineStr"/>
+      <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA102" t="n">
-        <v>47.05882352941177</v>
-      </c>
-      <c r="AB102" t="n">
-        <v>12.21514703280352</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA102" t="inlineStr"/>
+      <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="n">
         <v>5</v>
       </c>
-      <c r="AD102" t="n">
-        <v>0.872996270899673</v>
-      </c>
+      <c r="AD102" t="inlineStr"/>
       <c r="AE102" t="n">
         <v>26</v>
       </c>
@@ -11931,7 +11923,7 @@
         <v>46280</v>
       </c>
       <c r="C103" t="n">
-        <v>0.735608552631579</v>
+        <v>0.7277960526315789</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11991,22 +11983,22 @@
         <v>14.28440963201156</v>
       </c>
       <c r="Y103" t="n">
-        <v>6.915725911064364</v>
+        <v>7.90432356768248</v>
       </c>
       <c r="Z103" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AA103" t="n">
-        <v>39.28571428571428</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="AB103" t="n">
-        <v>10.57021134040605</v>
+        <v>9.823858635767134</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>1.164830579115528</v>
+        <v>0.103888082507142</v>
       </c>
       <c r="AE103" t="n">
         <v>33</v>
@@ -12097,10 +12089,10 @@
         <v>63.23529411764706</v>
       </c>
       <c r="X104" t="n">
-        <v>17.0508331466374</v>
+        <v>17.05083756364998</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>3.773584777988503e-06</v>
       </c>
       <c r="Z104" t="n">
         <v>42</v>
@@ -12115,7 +12107,7 @@
         <v>5</v>
       </c>
       <c r="AD104" t="n">
-        <v>5.000000000000004</v>
+        <v>4.999996415094332</v>
       </c>
       <c r="AE104" t="n">
         <v>42</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -670,7 +670,7 @@
         <v>46280</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3961759868421053</v>
+        <v>0.393297697368421</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,22 +698,22 @@
         <v>21.42119502374098</v>
       </c>
       <c r="K2" t="n">
-        <v>7.82485362370362</v>
+        <v>7.041486757729642</v>
       </c>
       <c r="L2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M2" t="n">
-        <v>57.14285714285715</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N2" t="n">
-        <v>15.34014576009059</v>
+        <v>15.02926611302887</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>2.01729592315274</v>
+        <v>2.763894011456003</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -740,22 +740,22 @@
         <v>11.79582706077868</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.551987172934645</v>
+        <v>4.252699253670988</v>
       </c>
       <c r="Z2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA2" t="n">
-        <v>42.5</v>
+        <v>50</v>
       </c>
       <c r="AB2" t="n">
-        <v>12.09916543615478</v>
+        <v>10.28945017419879</v>
       </c>
       <c r="AC2" t="n">
         <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.685480227184016</v>
+        <v>6.002572084570613</v>
       </c>
       <c r="AE2" t="n">
         <v>46</v>
@@ -908,7 +908,7 @@
         <v>46280</v>
       </c>
       <c r="C4" t="n">
-        <v>1.448396381578947</v>
+        <v>1.43811677631579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -968,22 +968,22 @@
         <v>16.66966699739723</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.00291415858716</v>
+        <v>8.65583882744032</v>
       </c>
       <c r="Z4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>65</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.600578880172892</v>
+        <v>11.76431425412891</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.170814241720076</v>
+        <v>1.471534858172707</v>
       </c>
       <c r="AE4" t="n">
         <v>40</v>
@@ -1017,7 +1017,7 @@
         <v>46280</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2275904605263158</v>
+        <v>0.2253289473684211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,16 +1045,16 @@
         <v>19.13427219952423</v>
       </c>
       <c r="K5" t="n">
-        <v>4.55279994508464</v>
+        <v>3.513883233796533</v>
       </c>
       <c r="L5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M5" t="n">
-        <v>50</v>
+        <v>51.61290322580645</v>
       </c>
       <c r="N5" t="n">
-        <v>11.62858653100384</v>
+        <v>12.40479182691615</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -1087,22 +1087,22 @@
         <v>10.55954734904581</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.433042688748868</v>
+        <v>6.372732418128946</v>
       </c>
       <c r="Z5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA5" t="n">
-        <v>37.5</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.511831957833676</v>
+        <v>9.929312891751019</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.829337266525091</v>
+        <v>3.874157257338773</v>
       </c>
       <c r="AE5" t="n">
         <v>45</v>
@@ -1136,7 +1136,7 @@
         <v>46280</v>
       </c>
       <c r="C6" t="n">
-        <v>1.56969572368421</v>
+        <v>1.51110197368421</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %92.86: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %90.91: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1165,25 +1165,25 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>25.66500274978247</v>
+        <v>28.20804212939517</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4605263157894557</v>
+        <v>0.1362397820163341</v>
       </c>
       <c r="L6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M6" t="n">
-        <v>92.85714285714286</v>
+        <v>90.90909090909091</v>
       </c>
       <c r="N6" t="n">
-        <v>12.16769408284637</v>
+        <v>13.70526345225087</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.532416502946976</v>
+        <v>1.861224489795932</v>
       </c>
       <c r="Q6" t="n">
         <v>35</v>
@@ -1358,7 +1358,7 @@
         <v>46280</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3425164473684211</v>
+        <v>0.34375</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>20.70550141590351</v>
       </c>
       <c r="K8" t="n">
-        <v>5.187299899586151</v>
+        <v>5.566125709548642</v>
       </c>
       <c r="L8" t="n">
         <v>5</v>
@@ -1401,7 +1401,7 @@
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.673992110358303</v>
+        <v>2.305544770249357</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1428,7 +1428,7 @@
         <v>26.93179943319606</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.59225797047333</v>
+        <v>16.29186994395644</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1473,7 +1473,7 @@
         <v>46280</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5485197368421052</v>
+        <v>0.5555098684210527</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,16 +1501,16 @@
         <v>14.50739888386581</v>
       </c>
       <c r="K9" t="n">
-        <v>3.164505898672165</v>
+        <v>4.479196003827668</v>
       </c>
       <c r="L9" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M9" t="n">
-        <v>46.34146341463415</v>
+        <v>51.16279069767442</v>
       </c>
       <c r="N9" t="n">
-        <v>15.07354306966153</v>
+        <v>13.70637024885155</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1582,7 +1582,7 @@
         <v>46280</v>
       </c>
       <c r="C10" t="n">
-        <v>1.912006578947368</v>
+        <v>1.881167763157895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,22 +1610,22 @@
         <v>13.50421550203786</v>
       </c>
       <c r="K10" t="n">
-        <v>4.277349525620888</v>
+        <v>2.595456791336681</v>
       </c>
       <c r="L10" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M10" t="n">
-        <v>53.84615384615385</v>
+        <v>55.31914893617022</v>
       </c>
       <c r="N10" t="n">
-        <v>9.618994333024993</v>
+        <v>10.09697779894922</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>5.487913243300335</v>
+        <v>7.217223296469188</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1691,7 +1691,7 @@
         <v>46280</v>
       </c>
       <c r="C11" t="n">
-        <v>7.678865131578947</v>
+        <v>7.725123355263158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1719,22 +1719,22 @@
         <v>11.81477122148857</v>
       </c>
       <c r="K11" t="n">
-        <v>1.425661914460274</v>
+        <v>2.036659877800395</v>
       </c>
       <c r="L11" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="M11" t="n">
-        <v>55.73770491803279</v>
+        <v>56.89655172413793</v>
       </c>
       <c r="N11" t="n">
-        <v>13.27181238264338</v>
+        <v>13.03197690775713</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.552208835341373</v>
+        <v>0.9441117764471096</v>
       </c>
       <c r="Q11" t="n">
         <v>49</v>
@@ -1761,16 +1761,16 @@
         <v>19.5857262818246</v>
       </c>
       <c r="Y11" t="n">
-        <v>10.55754800061367</v>
+        <v>10.01873804881014</v>
       </c>
       <c r="Z11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA11" t="n">
-        <v>50</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.100922825874459</v>
+        <v>9.208098680161603</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
@@ -1810,7 +1810,7 @@
         <v>46280</v>
       </c>
       <c r="C12" t="n">
-        <v>5.653782894736842</v>
+        <v>5.597245065789473</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,7 +1827,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %90.91: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>5</v>
       </c>
@@ -1838,22 +1842,22 @@
         <v>25.10845701569052</v>
       </c>
       <c r="K12" t="n">
-        <v>1.569713758079416</v>
+        <v>0.5540166204986097</v>
       </c>
       <c r="L12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M12" t="n">
-        <v>66.66666666666667</v>
+        <v>90.90909090909091</v>
       </c>
       <c r="N12" t="n">
-        <v>14.40850509582597</v>
+        <v>12.16767143682461</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>3.377272727272729</v>
+        <v>4.421487603305785</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1919,7 +1923,7 @@
         <v>46280</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1673519736842105</v>
+        <v>0.1659128289473684</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,10 +1951,10 @@
         <v>47.07727092024744</v>
       </c>
       <c r="K13" t="n">
-        <v>3.628038245496112</v>
+        <v>2.736888039453733</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1958,7 +1962,7 @@
         <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>2.288918901354364</v>
+        <v>3.176183377574326</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1983,7 +1987,7 @@
         <v>20.61663781635479</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.08478952690153</v>
+        <v>14.82361811819354</v>
       </c>
       <c r="Z13" t="n">
         <v>2</v>
@@ -2018,7 +2022,7 @@
         <v>46280</v>
       </c>
       <c r="C14" t="n">
-        <v>8.598889802631579</v>
+        <v>8.562911184210526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2078,16 +2082,16 @@
         <v>16.11612055393703</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.494149018421057</v>
+        <v>4.893755089473695</v>
       </c>
       <c r="Z14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>42.30769230769231</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.99236835369544</v>
+        <v>13.56861547631727</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2127,7 +2131,7 @@
         <v>46280</v>
       </c>
       <c r="C15" t="n">
-        <v>13.46628289473684</v>
+        <v>13.37376644736842</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,22 +2159,22 @@
         <v>15.72365931533905</v>
       </c>
       <c r="K15" t="n">
-        <v>1.080246913580241</v>
+        <v>0.3858024691357986</v>
       </c>
       <c r="L15" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M15" t="n">
-        <v>65.67164179104478</v>
+        <v>64.0625</v>
       </c>
       <c r="N15" t="n">
-        <v>17.61476075240802</v>
+        <v>17.3128965068103</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>6.845801526717565</v>
+        <v>7.584934665641829</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2197,10 +2201,10 @@
         <v>36.34743205418309</v>
       </c>
       <c r="Y15" t="n">
-        <v>14.81326674621462</v>
+        <v>15.39851911208032</v>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
@@ -2242,7 +2246,7 @@
         <v>46280</v>
       </c>
       <c r="C16" t="n">
-        <v>34.29276315789474</v>
+        <v>34.08717105263158</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,22 +2274,22 @@
         <v>16.99349200873118</v>
       </c>
       <c r="K16" t="n">
-        <v>2.087842128064521</v>
+        <v>1.475804705234363</v>
       </c>
       <c r="L16" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="M16" t="n">
-        <v>66.17647058823529</v>
+        <v>69.73684210526316</v>
       </c>
       <c r="N16" t="n">
-        <v>18.04422109402139</v>
+        <v>17.73594465531578</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>7.750342946822264</v>
+        <v>8.400224387997346</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2351,7 +2355,7 @@
         <v>46280</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3817845394736842</v>
+        <v>0.3881578947368421</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2383,7 @@
         <v>51.08056225103426</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1618122977346426</v>
+        <v>1.833872707659134</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2390,7 +2394,7 @@
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>7.825525040387715</v>
+        <v>6.055084745762707</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2456,11 +2460,11 @@
         <v>46280</v>
       </c>
       <c r="C18" t="n">
-        <v>0.07504111842105263</v>
+        <v>0.07298519736842105</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2470,7 +2474,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2481,25 +2485,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>31.38464440531301</v>
+        <v>33.00210927005214</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3932059529921483</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M18" t="n">
-        <v>66.66666666666667</v>
+        <v>62.5</v>
       </c>
       <c r="N18" t="n">
-        <v>10.09916471732394</v>
+        <v>9.509462556470817</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>9.569167510703981</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2522,27 +2526,17 @@
       <c r="W18" t="n">
         <v>75.28089887640449</v>
       </c>
-      <c r="X18" t="n">
-        <v>11.24971294890111</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>9.758683153542657</v>
-      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>64.70588235294117</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>11.44232129361223</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
         <v>8</v>
       </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="n">
         <v>36</v>
       </c>
@@ -2575,11 +2569,11 @@
         <v>46280</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02672697368421053</v>
+        <v>0.02652138157894737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2589,7 +2583,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2600,25 +2594,25 @@
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>10.51926896239048</v>
+        <v>11.21291804020141</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7751937984496138</v>
+        <v>0.78125</v>
       </c>
       <c r="L19" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M19" t="n">
-        <v>48.64864864864865</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N19" t="n">
-        <v>21.86850646288045</v>
+        <v>20.70961954883646</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>9.153846153846157</v>
+        <v>9.147286821705425</v>
       </c>
       <c r="Q19" t="n">
         <v>14</v>
@@ -2645,22 +2639,22 @@
         <v>20.26411217973316</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.825619884579561</v>
+        <v>10.51926896239048</v>
       </c>
       <c r="Z19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA19" t="n">
-        <v>69.23076923076923</v>
+        <v>50</v>
       </c>
       <c r="AB19" t="n">
-        <v>15.54347334588223</v>
+        <v>15.15125969989996</v>
       </c>
       <c r="AC19" t="n">
         <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.1933809971271572</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -2694,7 +2688,7 @@
         <v>46280</v>
       </c>
       <c r="C20" t="n">
-        <v>1.6015625</v>
+        <v>1.593338815789474</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2722,22 +2716,22 @@
         <v>18.49305897009618</v>
       </c>
       <c r="K20" t="n">
-        <v>2.753227065311226</v>
+        <v>2.225611008493211</v>
       </c>
       <c r="L20" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M20" t="n">
-        <v>45.16129032258065</v>
+        <v>43.75</v>
       </c>
       <c r="N20" t="n">
-        <v>14.5273195776619</v>
+        <v>16.46570377238519</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>7.052598873690497</v>
+        <v>7.605128416264373</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
@@ -2803,16 +2797,16 @@
         <v>46280</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8992598684210527</v>
+        <v>0.8898026315789473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2827,17 +2821,27 @@
       <c r="I21" t="n">
         <v>10</v>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>10.08775786440359</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.2780352177942591</v>
+      </c>
       <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="M21" t="n">
+        <v>54</v>
+      </c>
+      <c r="N21" t="n">
+        <v>12.53959404921769</v>
+      </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
-      <c r="P21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>7.700554528650638</v>
+      </c>
       <c r="Q21" t="n">
         <v>40</v>
       </c>
@@ -2902,7 +2906,7 @@
         <v>46280</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2937911184210526</v>
+        <v>0.2915296052631579</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2921,7 +2925,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2931,25 +2935,25 @@
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>20.49639372369575</v>
+        <v>20.82771333123346</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7108883429579604</v>
+        <v>0.3538570417551457</v>
       </c>
       <c r="L22" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M22" t="n">
-        <v>75</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="N22" t="n">
-        <v>14.12177217454367</v>
+        <v>12.47389722984058</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>9.223542568117526</v>
+        <v>9.612129760225653</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -3007,7 +3011,7 @@
         <v>46280</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6007401315789473</v>
+        <v>0.5916940789473685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,10 +3036,10 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>41.58670221917339</v>
+        <v>41.91054586591394</v>
       </c>
       <c r="K23" t="n">
-        <v>1.247401247401236</v>
+        <v>0.2787456445993097</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -3046,7 +3050,7 @@
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>3.7063655030801</v>
+        <v>4.708130646282127</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3235,7 +3239,7 @@
         <v>46280</v>
       </c>
       <c r="C25" t="n">
-        <v>3.316200657894737</v>
+        <v>3.295641447368421</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3263,22 +3267,22 @@
         <v>20.95143919294578</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9448546815115755</v>
+        <v>0.3190341317191869</v>
       </c>
       <c r="L25" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M25" t="n">
-        <v>52.77777777777778</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N25" t="n">
-        <v>17.2679554084823</v>
+        <v>16.56288562475776</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>6.989108400569721</v>
+        <v>7.656538895894571</v>
       </c>
       <c r="Q25" t="n">
         <v>44</v>
@@ -3344,7 +3348,7 @@
         <v>46280</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4416118421052632</v>
+        <v>0.4370888157894737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3404,22 +3408,22 @@
         <v>11.40992936035117</v>
       </c>
       <c r="Y26" t="n">
-        <v>7.284506763517795</v>
+        <v>8.234106787355122</v>
       </c>
       <c r="Z26" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA26" t="n">
-        <v>48</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.073612270240432</v>
+        <v>10.68664353651355</v>
       </c>
       <c r="AC26" t="n">
         <v>10</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.928845160275428</v>
+        <v>1.924345909817338</v>
       </c>
       <c r="AE26" t="n">
         <v>36</v>
@@ -3453,7 +3457,7 @@
         <v>46280</v>
       </c>
       <c r="C27" t="n">
-        <v>54.01932565789473</v>
+        <v>55.40707236842105</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3500,16 +3504,16 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>65.12508506386467</v>
+        <v>68.86729662338568</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.7554296506138036</v>
+        <v>0.4616805170821747</v>
       </c>
       <c r="Z27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AA27" t="n">
-        <v>14.28571428571429</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB27" t="n">
         <v>5.328374938728119</v>
@@ -3518,7 +3522,7 @@
         <v>6</v>
       </c>
       <c r="AD27" t="n">
-        <v>5.284490960989519</v>
+        <v>5.564007421150285</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3542,7 +3546,7 @@
         <v>46280</v>
       </c>
       <c r="C28" t="n">
-        <v>1.402138157894737</v>
+        <v>1.38671875</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3567,25 +3571,25 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>16.9414263829347</v>
+        <v>17.9842555915977</v>
       </c>
       <c r="K28" t="n">
-        <v>0.7385569756661825</v>
+        <v>0.8975317875841604</v>
       </c>
       <c r="L28" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="M28" t="n">
-        <v>66</v>
+        <v>69.76744186046511</v>
       </c>
       <c r="N28" t="n">
-        <v>14.7575783019116</v>
+        <v>15.37615913867865</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>1.25219485190613</v>
+        <v>1.092661230541125</v>
       </c>
       <c r="Q28" t="n">
         <v>39</v>
@@ -3651,7 +3655,7 @@
         <v>46280</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4214638157894737</v>
+        <v>0.4157072368421053</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3679,7 +3683,7 @@
         <v>27.65210909859499</v>
       </c>
       <c r="K29" t="n">
-        <v>27.2712694605777</v>
+        <v>25.53293017038445</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3717,22 +3721,22 @@
         <v>31.20488584758381</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.99807157454155</v>
+        <v>4.322975962791709</v>
       </c>
       <c r="Z29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA29" t="n">
-        <v>22.22222222222222</v>
+        <v>25</v>
       </c>
       <c r="AB29" t="n">
-        <v>14.3245685944975</v>
+        <v>12.69230558699323</v>
       </c>
       <c r="AC29" t="n">
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>7.2183394073852</v>
+        <v>5.933529072769361</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3766,7 +3770,7 @@
         <v>46280</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4066611842105263</v>
+        <v>0.4089226973684211</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3794,22 +3798,22 @@
         <v>12.46365070502794</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1518987341772249</v>
+        <v>0.7088607594936791</v>
       </c>
       <c r="L30" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="M30" t="n">
-        <v>44.06779661016949</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N30" t="n">
-        <v>14.17614401638845</v>
+        <v>13.93181964189898</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>4.840748230535885</v>
+        <v>4.260935143288069</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3836,16 +3840,16 @@
         <v>26.71344279693404</v>
       </c>
       <c r="Y30" t="n">
-        <v>12.33068409850392</v>
+        <v>11.84313987458255</v>
       </c>
       <c r="Z30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA30" t="n">
-        <v>57.14285714285715</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB30" t="n">
-        <v>11.98915066855684</v>
+        <v>15.13668580481328</v>
       </c>
       <c r="AC30" t="n">
         <v>8</v>
@@ -3885,7 +3889,7 @@
         <v>46280</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2571957236842105</v>
+        <v>0.2606907894736842</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3945,22 +3949,22 @@
         <v>50.77283913219171</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.036025455241064</v>
+        <v>0.7047803974785549</v>
       </c>
       <c r="Z31" t="n">
         <v>4</v>
       </c>
       <c r="AA31" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AB31" t="n">
-        <v>11.83810352260999</v>
+        <v>10.17739856018577</v>
       </c>
       <c r="AC31" t="n">
         <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>8.129493093525175</v>
+        <v>9.361195473186113</v>
       </c>
       <c r="AE31" t="n">
         <v>10</v>
@@ -3994,7 +3998,7 @@
         <v>46280</v>
       </c>
       <c r="C32" t="n">
-        <v>2.290296052631579</v>
+        <v>2.312911184210526</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4054,22 +4058,22 @@
         <v>13.38656892008534</v>
       </c>
       <c r="Y32" t="n">
-        <v>7.318131426103591</v>
+        <v>6.402960371962796</v>
       </c>
       <c r="Z32" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="AA32" t="n">
-        <v>37.5</v>
+        <v>35.48387096774194</v>
       </c>
       <c r="AB32" t="n">
-        <v>12.35050329533333</v>
+        <v>10.48364730798535</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.7357087037501264</v>
+        <v>1.706292885313443</v>
       </c>
       <c r="AE32" t="n">
         <v>26</v>
@@ -4103,7 +4107,7 @@
         <v>46280</v>
       </c>
       <c r="C33" t="n">
-        <v>1.779399671052631</v>
+        <v>1.769120065789474</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4163,22 +4167,22 @@
         <v>15.09663082780621</v>
       </c>
       <c r="Y33" t="n">
-        <v>5.657651739688796</v>
+        <v>6.202668194109995</v>
       </c>
       <c r="Z33" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="AA33" t="n">
-        <v>29.72972972972973</v>
+        <v>25.71428571428572</v>
       </c>
       <c r="AB33" t="n">
-        <v>12.24828462139434</v>
+        <v>11.22884089524853</v>
       </c>
       <c r="AC33" t="n">
         <v>8</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.482817423463057</v>
+        <v>1.916186496231587</v>
       </c>
       <c r="AE33" t="n">
         <v>29</v>
@@ -4212,7 +4216,7 @@
         <v>46280</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7923519736842105</v>
+        <v>0.7907072368421053</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4240,16 +4244,16 @@
         <v>15.41713612942789</v>
       </c>
       <c r="K34" t="n">
-        <v>5.405281333970668</v>
+        <v>5.186484693941673</v>
       </c>
       <c r="L34" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M34" t="n">
-        <v>62.85714285714285</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N34" t="n">
-        <v>13.67460151352577</v>
+        <v>13.27608657086676</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4282,16 +4286,16 @@
         <v>10.81830054752258</v>
       </c>
       <c r="Y34" t="n">
-        <v>4.884589627171398</v>
+        <v>5.082026908692572</v>
       </c>
       <c r="Z34" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA34" t="n">
-        <v>34.61538461538461</v>
+        <v>32</v>
       </c>
       <c r="AB34" t="n">
-        <v>10.79959715099529</v>
+        <v>10.55285401940977</v>
       </c>
       <c r="AC34" t="n">
         <v>2</v>
@@ -4331,16 +4335,16 @@
         <v>46280</v>
       </c>
       <c r="C35" t="n">
-        <v>1.495682565789474</v>
+        <v>1.4453125</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4359,10 +4363,10 @@
         <v>38.83766461406507</v>
       </c>
       <c r="K35" t="n">
-        <v>7.945514141011123</v>
+        <v>4.310235657911776</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4370,7 +4374,7 @@
         <v>6</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.619941064681174</v>
       </c>
       <c r="Q35" t="n">
         <v>7</v>
@@ -4397,16 +4401,16 @@
         <v>13.94161507705984</v>
       </c>
       <c r="Y35" t="n">
-        <v>5.262432809990891</v>
+        <v>8.452907581338277</v>
       </c>
       <c r="Z35" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AA35" t="n">
-        <v>33.33333333333334</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB35" t="n">
-        <v>10.81081479976208</v>
+        <v>11.84409368984752</v>
       </c>
       <c r="AC35" t="n">
         <v>2</v>
@@ -4446,7 +4450,7 @@
         <v>46280</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07833059210526316</v>
+        <v>0.07750822368421052</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,22 +4478,22 @@
         <v>11.49958181785439</v>
       </c>
       <c r="K36" t="n">
-        <v>1.431626208176073</v>
+        <v>0.3667272453605541</v>
       </c>
       <c r="L36" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="M36" t="n">
-        <v>66.66666666666667</v>
+        <v>60</v>
       </c>
       <c r="N36" t="n">
-        <v>16.86056520364298</v>
+        <v>16.84443346837099</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>0.56035165073407</v>
+        <v>1.627304983898381</v>
       </c>
       <c r="Q36" t="n">
         <v>10</v>
@@ -4555,7 +4559,7 @@
         <v>46280</v>
       </c>
       <c r="C37" t="n">
-        <v>0.05756578947368421</v>
+        <v>0.05633223684210527</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4580,25 +4584,25 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>22.69029993401852</v>
+        <v>22.97142611607663</v>
       </c>
       <c r="K37" t="n">
-        <v>1.81818181818183</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="M37" t="n">
-        <v>71.42857142857143</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="N37" t="n">
-        <v>14.41584131925982</v>
+        <v>15.40609297681062</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>8.035714285714279</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q37" t="n">
         <v>30</v>
@@ -4664,7 +4668,7 @@
         <v>46280</v>
       </c>
       <c r="C38" t="n">
-        <v>1.645764802631579</v>
+        <v>1.624177631578947</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4724,22 +4728,22 @@
         <v>12.11239445105858</v>
       </c>
       <c r="Y38" t="n">
-        <v>6.000157510558735</v>
+        <v>7.233134832406485</v>
       </c>
       <c r="Z38" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="AA38" t="n">
-        <v>51.35135135135135</v>
+        <v>56.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>11.56887025161974</v>
+        <v>9.174291248616079</v>
       </c>
       <c r="AC38" t="n">
         <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.25515871464418</v>
+        <v>2.982600697560345</v>
       </c>
       <c r="AE38" t="n">
         <v>30</v>
@@ -4773,7 +4777,7 @@
         <v>46280</v>
       </c>
       <c r="C39" t="n">
-        <v>2.676809210526315</v>
+        <v>2.645970394736842</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4833,16 +4837,16 @@
         <v>10.27889366548247</v>
       </c>
       <c r="Y39" t="n">
-        <v>6.203089188484578</v>
+        <v>7.283698760045809</v>
       </c>
       <c r="Z39" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AA39" t="n">
-        <v>57.69230769230769</v>
+        <v>50</v>
       </c>
       <c r="AB39" t="n">
-        <v>9.719662106532926</v>
+        <v>10.57423961341057</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
@@ -4882,21 +4886,21 @@
         <v>46280</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2347861842105263</v>
+        <v>0.2284128289473684</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4910,22 +4914,22 @@
         <v>15.29580504962521</v>
       </c>
       <c r="K40" t="n">
-        <v>5.186598000686238</v>
+        <v>2.331270033942578</v>
       </c>
       <c r="L40" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="M40" t="n">
-        <v>72</v>
+        <v>67.56756756756756</v>
       </c>
       <c r="N40" t="n">
-        <v>13.29470523336766</v>
+        <v>14.07086531497261</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>0.6534952276421535</v>
       </c>
       <c r="Q40" t="n">
         <v>29</v>
@@ -4952,17 +4956,13 @@
         <v>37.29449902814472</v>
       </c>
       <c r="Y40" t="n">
-        <v>10.9025389678317</v>
+        <v>13.32112153525483</v>
       </c>
       <c r="Z40" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>13.7765185983196</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
         <v>5</v>
       </c>
@@ -5001,7 +5001,7 @@
         <v>46280</v>
       </c>
       <c r="C41" t="n">
-        <v>1.253083881578947</v>
+        <v>1.224300986842105</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5018,7 +5018,11 @@
           <t>SATMA_BEKLE</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H41" t="n">
         <v>5</v>
       </c>
@@ -5029,22 +5033,22 @@
         <v>40.38073481248902</v>
       </c>
       <c r="K41" t="n">
-        <v>4.079403657543801</v>
+        <v>1.688736469347552</v>
       </c>
       <c r="L41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M41" t="n">
-        <v>66.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="N41" t="n">
-        <v>20.80389226397487</v>
+        <v>19.55681544402417</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>5.688537918546266</v>
+        <v>8.173239061887404</v>
       </c>
       <c r="Q41" t="n">
         <v>11</v>
@@ -5071,16 +5075,16 @@
         <v>14.15095011586145</v>
       </c>
       <c r="Y41" t="n">
-        <v>8.823007121793713</v>
+        <v>10.91731048569018</v>
       </c>
       <c r="Z41" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AA41" t="n">
-        <v>44</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="AB41" t="n">
-        <v>14.107400835227</v>
+        <v>16.78789596480024</v>
       </c>
       <c r="AC41" t="n">
         <v>3</v>
@@ -5120,7 +5124,7 @@
         <v>46280</v>
       </c>
       <c r="C42" t="n">
-        <v>3.42516447368421</v>
+        <v>3.392269736842105</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5139,7 +5143,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir. SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
+          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -5152,16 +5156,16 @@
         <v>17.9384880883827</v>
       </c>
       <c r="K42" t="n">
-        <v>7.924775583584109</v>
+        <v>6.88828314100467</v>
       </c>
       <c r="L42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="N42" t="n">
-        <v>8.47558445240162</v>
+        <v>9.903369075310865</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
@@ -5192,7 +5196,7 @@
         <v>23.05415424937474</v>
       </c>
       <c r="Y42" t="n">
-        <v>11.43529742889089</v>
+        <v>12.28585879812122</v>
       </c>
       <c r="Z42" t="n">
         <v>4</v>
@@ -5239,7 +5243,7 @@
         <v>46280</v>
       </c>
       <c r="C43" t="n">
-        <v>6.162623355263158</v>
+        <v>6.064967105263158</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5256,7 +5260,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H43" t="n">
         <v>5</v>
       </c>
@@ -5267,22 +5275,22 @@
         <v>20.13868121382601</v>
       </c>
       <c r="K43" t="n">
-        <v>2.867123710473707</v>
+        <v>1.23703584517012</v>
       </c>
       <c r="L43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M43" t="n">
-        <v>64.70588235294117</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N43" t="n">
-        <v>22.101174673634</v>
+        <v>17.32461006185299</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>1.101300637815883</v>
+        <v>2.729202936221387</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5348,7 +5356,7 @@
         <v>46280</v>
       </c>
       <c r="C44" t="n">
-        <v>4.638157894736842</v>
+        <v>4.681332236842105</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5376,7 +5384,7 @@
         <v>25.31049029846984</v>
       </c>
       <c r="K44" t="n">
-        <v>20.76641302207129</v>
+        <v>21.89056846243633</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5414,22 +5422,22 @@
         <v>28.18267712431886</v>
       </c>
       <c r="Y44" t="n">
-        <v>5.785699182312176</v>
+        <v>4.908704360870919</v>
       </c>
       <c r="Z44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA44" t="n">
-        <v>42.85714285714285</v>
+        <v>37.5</v>
       </c>
       <c r="AB44" t="n">
-        <v>22.8628972099581</v>
+        <v>22.38906282491685</v>
       </c>
       <c r="AC44" t="n">
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>4.473100984788747</v>
+        <v>5.354113228670809</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5574,7 +5582,7 @@
         <v>46280</v>
       </c>
       <c r="C46" t="n">
-        <v>9.678248355263158</v>
+        <v>9.498355263157894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5599,25 +5607,25 @@
         <v>10</v>
       </c>
       <c r="J46" t="n">
-        <v>11.55351720699311</v>
+        <v>12.45458057056798</v>
       </c>
       <c r="K46" t="n">
-        <v>0.965147453083115</v>
+        <v>0.1083423618634782</v>
       </c>
       <c r="L46" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="M46" t="n">
-        <v>51.42857142857143</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N46" t="n">
-        <v>16.97705620942317</v>
+        <v>15.08343420142066</v>
       </c>
       <c r="O46" t="n">
         <v>8</v>
       </c>
       <c r="P46" t="n">
-        <v>6.967604885820511</v>
+        <v>7.883116883116892</v>
       </c>
       <c r="Q46" t="n">
         <v>51</v>
@@ -5644,16 +5652,16 @@
         <v>26.79655122306823</v>
       </c>
       <c r="Y46" t="n">
-        <v>10.69987823097481</v>
+        <v>12.35973179545484</v>
       </c>
       <c r="Z46" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA46" t="n">
-        <v>45.45454545454545</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB46" t="n">
-        <v>14.8915289459438</v>
+        <v>14.79451359380145</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
@@ -5693,7 +5701,7 @@
         <v>46280</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9391447368421052</v>
+        <v>0.947779605263158</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5721,22 +5729,22 @@
         <v>16.58327705889968</v>
       </c>
       <c r="K47" t="n">
-        <v>0.3074220465524746</v>
+        <v>1.229688186209943</v>
       </c>
       <c r="L47" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M47" t="n">
-        <v>65.45454545454545</v>
+        <v>62.5</v>
       </c>
       <c r="N47" t="n">
-        <v>15.6667579279566</v>
+        <v>16.5910468481701</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>9.662872154115609</v>
+        <v>8.663774403470704</v>
       </c>
       <c r="Q47" t="n">
         <v>51</v>
@@ -5763,7 +5771,7 @@
         <v>66.65983471422588</v>
       </c>
       <c r="Y47" t="n">
-        <v>16.32683566206714</v>
+        <v>15.5575114715695</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -5808,7 +5816,7 @@
         <v>46280</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05736019736842105</v>
+        <v>0.05571546052631579</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5833,25 +5841,25 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>10.36700565279574</v>
+        <v>12.37197428387045</v>
       </c>
       <c r="K48" t="n">
-        <v>1.021906683062301</v>
+        <v>0.3703703703703765</v>
       </c>
       <c r="L48" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M48" t="n">
-        <v>56.45161290322581</v>
+        <v>60</v>
       </c>
       <c r="N48" t="n">
-        <v>13.60756106086803</v>
+        <v>14.21858183766153</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>8.887273673327932</v>
+        <v>9.594095940959413</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5878,16 +5886,16 @@
         <v>19.37342145735985</v>
       </c>
       <c r="Y48" t="n">
-        <v>9.451040093332807</v>
+        <v>12.04742604047738</v>
       </c>
       <c r="Z48" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AA48" t="n">
-        <v>50</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="AB48" t="n">
-        <v>11.78809840197876</v>
+        <v>11.05787043682041</v>
       </c>
       <c r="AC48" t="n">
         <v>6</v>
@@ -5927,7 +5935,7 @@
         <v>46280</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2769325657894737</v>
+        <v>0.2754934210526316</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5987,22 +5995,22 @@
         <v>22.46912765663718</v>
       </c>
       <c r="Y49" t="n">
-        <v>9.010096622421393</v>
+        <v>9.48294689981044</v>
       </c>
       <c r="Z49" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA49" t="n">
-        <v>57.14285714285715</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AB49" t="n">
-        <v>10.4994260586429</v>
+        <v>11.24788808776712</v>
       </c>
       <c r="AC49" t="n">
         <v>10</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.087926616946522</v>
+        <v>0.571221755990281</v>
       </c>
       <c r="AE49" t="n">
         <v>44</v>
@@ -6036,7 +6044,7 @@
         <v>46280</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7014802631578947</v>
+        <v>0.6949013157894737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6045,7 +6053,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6060,17 +6068,27 @@
       <c r="I50" t="n">
         <v>10</v>
       </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="J50" t="n">
+        <v>10.17272609298356</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.2967359050445095</v>
+      </c>
       <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="M50" t="n">
+        <v>42.5531914893617</v>
+      </c>
+      <c r="N50" t="n">
+        <v>13.51691102693656</v>
+      </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
-      <c r="P50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>3.692307692307706</v>
+      </c>
       <c r="Q50" t="n">
         <v>40</v>
       </c>
@@ -6096,16 +6114,16 @@
         <v>15.51990994893744</v>
       </c>
       <c r="Y50" t="n">
-        <v>9.053217041323425</v>
+        <v>9.906176318778769</v>
       </c>
       <c r="Z50" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA50" t="n">
-        <v>62.5</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="AB50" t="n">
-        <v>11.3903374870045</v>
+        <v>11.36764529003039</v>
       </c>
       <c r="AC50" t="n">
         <v>5</v>
@@ -6145,7 +6163,7 @@
         <v>46280</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1361019736842105</v>
+        <v>0.1332236842105263</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6159,7 +6177,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -6170,25 +6188,25 @@
         <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>31.62908307640215</v>
+        <v>31.71331988759807</v>
       </c>
       <c r="K51" t="n">
-        <v>2.192330572536205</v>
+        <v>0.1545595054095905</v>
       </c>
       <c r="L51" t="n">
         <v>6</v>
       </c>
       <c r="M51" t="n">
-        <v>50</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N51" t="n">
-        <v>19.88394943304391</v>
+        <v>13.94407786065021</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>1.768889521685502</v>
+        <v>3.839506172839502</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6211,27 +6229,17 @@
       <c r="W51" t="n">
         <v>84.61538461538461</v>
       </c>
-      <c r="X51" t="n">
-        <v>15.73461610040814</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>11.70115388478328</v>
-      </c>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>57.14285714285715</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>13.08784891453666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
         <v>10</v>
       </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="n">
         <v>12</v>
       </c>
@@ -6264,7 +6272,7 @@
         <v>46280</v>
       </c>
       <c r="C52" t="n">
-        <v>4.500411184210527</v>
+        <v>4.498355263157895</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6324,7 +6332,7 @@
         <v>16.62696858241317</v>
       </c>
       <c r="Y52" t="n">
-        <v>6.191879915402176</v>
+        <v>6.234734241617168</v>
       </c>
       <c r="Z52" t="n">
         <v>19</v>
@@ -6339,7 +6347,7 @@
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.927466495402774</v>
+        <v>1.88264358246647</v>
       </c>
       <c r="AE52" t="n">
         <v>37</v>
@@ -6373,7 +6381,7 @@
         <v>46280</v>
       </c>
       <c r="C53" t="n">
-        <v>1.172902960526316</v>
+        <v>1.143092105263158</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6390,7 +6398,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H53" t="n">
         <v>5</v>
       </c>
@@ -6398,25 +6410,25 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>31.87392835944998</v>
+        <v>33.48885718675011</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1755926251097328</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
         <v>6</v>
       </c>
       <c r="M53" t="n">
-        <v>66.66666666666667</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N53" t="n">
-        <v>18.43986724978525</v>
+        <v>20.66638207787801</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>7.810692375109585</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6593,7 +6605,7 @@
         <v>46280</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9239309210526315</v>
+        <v>0.907483552631579</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6653,16 +6665,16 @@
         <v>23.0932342837701</v>
       </c>
       <c r="Y55" t="n">
-        <v>7.562844170633531</v>
+        <v>9.208365413701912</v>
       </c>
       <c r="Z55" t="n">
         <v>17</v>
       </c>
       <c r="AA55" t="n">
-        <v>41.1764705882353</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="AB55" t="n">
-        <v>9.175890922370419</v>
+        <v>8.623281246978431</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6791,7 +6803,7 @@
         <v>46280</v>
       </c>
       <c r="C57" t="n">
-        <v>1.455592105263158</v>
+        <v>1.448396381578947</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6851,22 +6863,22 @@
         <v>20.62560129901716</v>
       </c>
       <c r="Y57" t="n">
-        <v>4.418547869843536</v>
+        <v>4.891055048453063</v>
       </c>
       <c r="Z57" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA57" t="n">
-        <v>44.68085106382978</v>
+        <v>51.11111111111111</v>
       </c>
       <c r="AB57" t="n">
-        <v>14.58664704587881</v>
+        <v>13.25929480822831</v>
       </c>
       <c r="AC57" t="n">
         <v>5</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.6083315509422094</v>
+        <v>0.1145475345168068</v>
       </c>
       <c r="AE57" t="n">
         <v>44</v>
@@ -6900,16 +6912,16 @@
         <v>46280</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7072368421052632</v>
+        <v>0.6977796052631579</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6917,7 +6929,11 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6928,22 +6944,22 @@
         <v>18.04392839464337</v>
       </c>
       <c r="K58" t="n">
-        <v>8.402341034878869</v>
+        <v>6.952774846621756</v>
       </c>
       <c r="L58" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M58" t="n">
-        <v>61.53846153846154</v>
+        <v>75</v>
       </c>
       <c r="N58" t="n">
-        <v>27.49886566761452</v>
+        <v>20.38572926033141</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>0.979147249690393</v>
       </c>
       <c r="Q58" t="n">
         <v>25</v>
@@ -6970,16 +6986,16 @@
         <v>20.50322102897642</v>
       </c>
       <c r="Y58" t="n">
-        <v>10.04195563468612</v>
+        <v>11.24488297212928</v>
       </c>
       <c r="Z58" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA58" t="n">
-        <v>50</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB58" t="n">
-        <v>7.94428332794203</v>
+        <v>7.686577986255374</v>
       </c>
       <c r="AC58" t="n">
         <v>6</v>
@@ -7019,7 +7035,7 @@
         <v>46280</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7434210526315789</v>
+        <v>0.7417763157894737</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7047,22 +7063,22 @@
         <v>11.95882015364728</v>
       </c>
       <c r="K59" t="n">
-        <v>1.482206602537506</v>
+        <v>1.257688446337202</v>
       </c>
       <c r="L59" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M59" t="n">
-        <v>60.9375</v>
+        <v>60.31746031746032</v>
       </c>
       <c r="N59" t="n">
-        <v>14.3457197144375</v>
+        <v>14.14795892831695</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>6.422597237158945</v>
+        <v>6.658567519281244</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7128,7 +7144,7 @@
         <v>46280</v>
       </c>
       <c r="C60" t="n">
-        <v>10.76274671052632</v>
+        <v>10.6188322368421</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7147,7 +7163,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -7157,25 +7173,25 @@
         <v>10</v>
       </c>
       <c r="J60" t="n">
-        <v>24.49246832941995</v>
+        <v>24.5994329337105</v>
       </c>
       <c r="K60" t="n">
-        <v>1.30976850736535</v>
+        <v>0.09689922480620172</v>
       </c>
       <c r="L60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M60" t="n">
-        <v>77.77777777777777</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="N60" t="n">
-        <v>13.91148315552294</v>
+        <v>14.08422267691191</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>6.603737814432242</v>
+        <v>7.895450145208138</v>
       </c>
       <c r="Q60" t="n">
         <v>46</v>
@@ -7241,7 +7257,7 @@
         <v>46280</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7483552631578947</v>
+        <v>0.7129934210526315</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7266,25 +7282,25 @@
         <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>14.0586191907223</v>
+        <v>14.17319122629571</v>
       </c>
       <c r="K61" t="n">
-        <v>4.819704853993079</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="M61" t="n">
-        <v>72.72727272727273</v>
+        <v>69.76744186046511</v>
       </c>
       <c r="N61" t="n">
-        <v>20.98672965159386</v>
+        <v>19.03584639174238</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>4.942100488856305</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
@@ -7311,17 +7327,13 @@
         <v>49.99145178651283</v>
       </c>
       <c r="Y61" t="n">
-        <v>9.91649828826886</v>
+        <v>14.17319122629571</v>
       </c>
       <c r="Z61" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>14.40298598384542</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
         <v>4</v>
       </c>
@@ -7360,7 +7372,7 @@
         <v>46280</v>
       </c>
       <c r="C62" t="n">
-        <v>8.794202302631579</v>
+        <v>8.825041118421053</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7420,16 +7432,16 @@
         <v>11.69351808836483</v>
       </c>
       <c r="Y62" t="n">
-        <v>5.897292368457685</v>
+        <v>5.567300407154785</v>
       </c>
       <c r="Z62" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA62" t="n">
-        <v>36.11111111111111</v>
+        <v>40.54054054054054</v>
       </c>
       <c r="AB62" t="n">
-        <v>20.39839785042583</v>
+        <v>18.54763979228057</v>
       </c>
       <c r="AC62" t="n">
         <v>5</v>
@@ -7469,7 +7481,7 @@
         <v>46280</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1095805921052632</v>
+        <v>0.1071134868421053</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7497,22 +7509,22 @@
         <v>14.68172212919103</v>
       </c>
       <c r="K63" t="n">
-        <v>4.6741037945359</v>
+        <v>2.317463559011634</v>
       </c>
       <c r="L63" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M63" t="n">
-        <v>56.25</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N63" t="n">
-        <v>14.75235065850451</v>
+        <v>16.20841068106916</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>0.311343678761089</v>
+        <v>2.621777698233507</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7539,10 +7551,10 @@
         <v>24.85614965143601</v>
       </c>
       <c r="Y63" t="n">
-        <v>10.69385726579886</v>
+        <v>12.70450213035874</v>
       </c>
       <c r="Z63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="inlineStr"/>
       <c r="AB63" t="inlineStr"/>
@@ -7584,11 +7596,11 @@
         <v>46280</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1467927631578947</v>
+        <v>0.1441200657894737</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7598,7 +7610,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -7609,25 +7621,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>11.53089624732437</v>
+        <v>13.14393740971537</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1402524544179329</v>
+        <v>0.1428571428571335</v>
       </c>
       <c r="L64" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M64" t="n">
-        <v>58.22784810126582</v>
+        <v>63.41463414634146</v>
       </c>
       <c r="N64" t="n">
-        <v>15.76271671383996</v>
+        <v>15.97763719216314</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.852941176470615</v>
+        <v>4.850213980028539</v>
       </c>
       <c r="Q64" t="n">
         <v>55</v>
@@ -7650,27 +7662,17 @@
       <c r="W64" t="n">
         <v>72.27722772277228</v>
       </c>
-      <c r="X64" t="n">
-        <v>14.28923074155179</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>11.40681615790969</v>
-      </c>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>53.125</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>16.91675138180393</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
         <v>2</v>
       </c>
-      <c r="AD64" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD64" t="inlineStr"/>
       <c r="AE64" t="n">
         <v>46</v>
       </c>
@@ -7703,7 +7705,7 @@
         <v>46280</v>
       </c>
       <c r="C65" t="n">
-        <v>6.285978618421052</v>
+        <v>6.275699013157895</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7728,25 +7730,25 @@
         <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>11.21991868339847</v>
+        <v>11.51147888476662</v>
       </c>
       <c r="K65" t="n">
-        <v>0.4105090311986803</v>
+        <v>0.5766062602965416</v>
       </c>
       <c r="L65" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M65" t="n">
-        <v>50.84745762711864</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N65" t="n">
-        <v>12.68335268993171</v>
+        <v>12.68036029155311</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>9.550286181520873</v>
+        <v>9.369369369369384</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7773,16 +7775,16 @@
         <v>24.47056390537039</v>
       </c>
       <c r="Y65" t="n">
-        <v>10.85546843168829</v>
+        <v>11.00124853237235</v>
       </c>
       <c r="Z65" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA65" t="n">
-        <v>25</v>
+        <v>23.07692307692308</v>
       </c>
       <c r="AB65" t="n">
-        <v>15.00601971697285</v>
+        <v>16.35606305772624</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
@@ -7822,7 +7824,7 @@
         <v>46280</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4399671052631579</v>
+        <v>0.4342105263157895</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7847,25 +7849,25 @@
         <v>10</v>
       </c>
       <c r="J66" t="n">
-        <v>10.41136575766793</v>
+        <v>10.41390434728438</v>
       </c>
       <c r="K66" t="n">
-        <v>1.418927052836461</v>
+        <v>0.09478672985783199</v>
       </c>
       <c r="L66" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M66" t="n">
-        <v>58.33333333333334</v>
+        <v>56.36363636363637</v>
       </c>
       <c r="N66" t="n">
-        <v>16.81393866347435</v>
+        <v>13.79370518048586</v>
       </c>
       <c r="O66" t="n">
         <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>4.516980291831452</v>
+        <v>5.899621212121198</v>
       </c>
       <c r="Q66" t="n">
         <v>35</v>
@@ -7892,16 +7894,16 @@
         <v>14.59585890675015</v>
       </c>
       <c r="Y66" t="n">
-        <v>9.140168390136772</v>
+        <v>10.32898861680787</v>
       </c>
       <c r="Z66" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AA66" t="n">
-        <v>53.84615384615385</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="AB66" t="n">
-        <v>7.980056818083106</v>
+        <v>8.938200137593423</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
@@ -7941,7 +7943,7 @@
         <v>46280</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02713815789473684</v>
+        <v>0.02672697368421053</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7969,7 +7971,7 @@
         <v>11.46300958938384</v>
       </c>
       <c r="K67" t="n">
-        <v>2.67955736132186</v>
+        <v>1.12380649221091</v>
       </c>
       <c r="L67" t="n">
         <v>5</v>
@@ -7978,13 +7980,13 @@
         <v>20</v>
       </c>
       <c r="N67" t="n">
-        <v>7.966768450054484</v>
+        <v>7.356482034271883</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>1.285983960791337</v>
+        <v>2.844229867880443</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -8135,16 +8137,16 @@
         <v>46280</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4444901315789474</v>
+        <v>0.5172697368421053</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -8160,25 +8162,21 @@
         <v>10</v>
       </c>
       <c r="J69" t="n">
-        <v>21.76381940295035</v>
+        <v>22.28047342576105</v>
       </c>
       <c r="K69" t="n">
-        <v>1.981132075471725</v>
+        <v>19.46818613485281</v>
       </c>
       <c r="L69" t="n">
-        <v>16</v>
-      </c>
-      <c r="M69" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="N69" t="n">
-        <v>23.29418610693553</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>5.90194264569841</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8197,10 +8195,10 @@
         <v>45.36848923911108</v>
       </c>
       <c r="Y69" t="n">
-        <v>20.21385733451822</v>
+        <v>7.149891329161806</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA69" t="inlineStr"/>
       <c r="AB69" t="inlineStr"/>
@@ -8234,7 +8232,7 @@
         <v>46280</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4712171052631579</v>
+        <v>0.4666940789473684</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8259,25 +8257,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>14.89488141893085</v>
+        <v>15.78759245299801</v>
       </c>
       <c r="K70" t="n">
-        <v>0.1748251748251883</v>
+        <v>0.2650176678445249</v>
       </c>
       <c r="L70" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M70" t="n">
-        <v>47.91666666666666</v>
+        <v>50</v>
       </c>
       <c r="N70" t="n">
-        <v>13.45489858645554</v>
+        <v>12.5088238905108</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>7.811518324607314</v>
+        <v>7.714537444933933</v>
       </c>
       <c r="Q70" t="n">
         <v>31</v>
@@ -8304,17 +8302,13 @@
         <v>44.93251946562029</v>
       </c>
       <c r="Y70" t="n">
-        <v>14.74609624658633</v>
+        <v>15.56441469448122</v>
       </c>
       <c r="Z70" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>10.10431955682505</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
         <v>8</v>
       </c>
@@ -8353,7 +8347,7 @@
         <v>46280</v>
       </c>
       <c r="C71" t="n">
-        <v>3.122944078947369</v>
+        <v>3.090049342105263</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8452,7 +8446,7 @@
         <v>46280</v>
       </c>
       <c r="C72" t="n">
-        <v>0.06064967105263158</v>
+        <v>0.05962171052631578</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8460,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -8477,25 +8471,25 @@
         <v>10</v>
       </c>
       <c r="J72" t="n">
-        <v>29.77666337790048</v>
+        <v>29.83805545001131</v>
       </c>
       <c r="K72" t="n">
-        <v>1.635206588382943</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
         <v>15</v>
       </c>
       <c r="M72" t="n">
-        <v>66.66666666666667</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N72" t="n">
-        <v>28.32418695070399</v>
+        <v>24.04684220636248</v>
       </c>
       <c r="O72" t="n">
         <v>10</v>
       </c>
       <c r="P72" t="n">
-        <v>8.230212435631712</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q72" t="n">
         <v>15</v>
@@ -8518,27 +8512,17 @@
       <c r="W72" t="n">
         <v>85.18518518518519</v>
       </c>
-      <c r="X72" t="n">
-        <v>12.03392243896149</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>9.281756475360392</v>
-      </c>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>72.22222222222223</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>11.95910730857625</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
         <v>8</v>
       </c>
-      <c r="AD72" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="n">
         <v>10</v>
       </c>
@@ -8571,7 +8555,7 @@
         <v>46280</v>
       </c>
       <c r="C73" t="n">
-        <v>0.06188322368421052</v>
+        <v>0.05941611842105263</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8585,14 +8569,10 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>BAND</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>5</v>
       </c>
@@ -8600,25 +8580,25 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>19.59098648410814</v>
+        <v>21.73901626025376</v>
       </c>
       <c r="K73" t="n">
-        <v>1.369947467359678</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M73" t="n">
-        <v>75</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N73" t="n">
-        <v>14.98687719878846</v>
+        <v>15.80723394580061</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>8.513423108381435</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q73" t="n">
         <v>14</v>
@@ -8641,27 +8621,17 @@
       <c r="W73" t="n">
         <v>73.91304347826087</v>
       </c>
-      <c r="X73" t="n">
-        <v>12.21903004108828</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>9.667774324690104</v>
-      </c>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA73" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>13.8062690275649</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
         <v>10</v>
       </c>
-      <c r="AD73" t="n">
-        <v>0.3677820100481566</v>
-      </c>
+      <c r="AD73" t="inlineStr"/>
       <c r="AE73" t="n">
         <v>15</v>
       </c>
@@ -8694,7 +8664,7 @@
         <v>46280</v>
       </c>
       <c r="C74" t="n">
-        <v>5.355674342105263</v>
+        <v>5.473889802631579</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8722,22 +8692,22 @@
         <v>10.76052373623427</v>
       </c>
       <c r="K74" t="n">
-        <v>1.165048543689307</v>
+        <v>3.398058252427183</v>
       </c>
       <c r="L74" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="M74" t="n">
-        <v>74.02597402597402</v>
+        <v>71.1864406779661</v>
       </c>
       <c r="N74" t="n">
-        <v>15.07095239639585</v>
+        <v>15.62851530762487</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>6.756238003838799</v>
+        <v>4.45070422535212</v>
       </c>
       <c r="Q74" t="n">
         <v>28</v>
@@ -8764,7 +8734,7 @@
         <v>24.51464461150628</v>
       </c>
       <c r="Y74" t="n">
-        <v>9.720840517627295</v>
+        <v>7.728114348630588</v>
       </c>
       <c r="Z74" t="n">
         <v>17</v>
@@ -8773,13 +8743,13 @@
         <v>47.05882352941177</v>
       </c>
       <c r="AB74" t="n">
-        <v>19.05515588362151</v>
+        <v>16.67758587258489</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.309218078649931</v>
+        <v>2.462164542679091</v>
       </c>
       <c r="AE74" t="n">
         <v>37</v>
@@ -8922,7 +8892,7 @@
         <v>46280</v>
       </c>
       <c r="C76" t="n">
-        <v>1.877055921052631</v>
+        <v>1.868832236842105</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8982,16 +8952,16 @@
         <v>12.60650925728801</v>
       </c>
       <c r="Y76" t="n">
-        <v>7.552898170468325</v>
+        <v>7.95792380827568</v>
       </c>
       <c r="Z76" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA76" t="n">
-        <v>42.85714285714285</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB76" t="n">
-        <v>10.21650177017549</v>
+        <v>10.20955438135788</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
@@ -9031,7 +9001,7 @@
         <v>46280</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4683388157894737</v>
+        <v>0.4621710526315789</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9056,25 +9026,25 @@
         <v>10</v>
       </c>
       <c r="J77" t="n">
-        <v>18.49667872866365</v>
+        <v>19.35990842897727</v>
       </c>
       <c r="K77" t="n">
-        <v>0.5295681853237255</v>
+        <v>0.2676181980374448</v>
       </c>
       <c r="L77" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="M77" t="n">
-        <v>67.56756756756756</v>
+        <v>63.33333333333334</v>
       </c>
       <c r="N77" t="n">
-        <v>13.22991500687594</v>
+        <v>10.85781526974314</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>7.431079183494282</v>
+        <v>7.711743772242019</v>
       </c>
       <c r="Q77" t="n">
         <v>27</v>
@@ -9140,7 +9110,7 @@
         <v>46280</v>
       </c>
       <c r="C78" t="n">
-        <v>0.06167763157894737</v>
+        <v>0.05797697368421052</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9200,22 +9170,22 @@
         <v>36.6270136023539</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.960784313725494</v>
+        <v>7.843137254901967</v>
       </c>
       <c r="Z78" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AA78" t="n">
-        <v>27.27272727272727</v>
+        <v>60</v>
       </c>
       <c r="AB78" t="n">
-        <v>13.19983451314134</v>
+        <v>15.45343681464298</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>8.199999999999996</v>
+        <v>2.34042553191488</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9249,7 +9219,7 @@
         <v>46280</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8782894736842105</v>
+        <v>0.873766447368421</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9274,25 +9244,25 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>12.12688233224525</v>
+        <v>12.33325414452273</v>
       </c>
       <c r="K79" t="n">
-        <v>0.3287928604978951</v>
+        <v>0.04708097928436406</v>
       </c>
       <c r="L79" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M79" t="n">
-        <v>57.89473684210526</v>
+        <v>57.4074074074074</v>
       </c>
       <c r="N79" t="n">
-        <v>10.84358950105503</v>
+        <v>11.22714428107698</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>4.655898876404496</v>
+        <v>4.950588235294129</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9319,7 +9289,7 @@
         <v>25.65117214954458</v>
       </c>
       <c r="Y79" t="n">
-        <v>11.83796179505675</v>
+        <v>12.29197978206723</v>
       </c>
       <c r="Z79" t="n">
         <v>4</v>
@@ -9368,21 +9338,21 @@
         <v>46280</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1319901315789474</v>
+        <v>0.1307565789473684</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AL_BEKLE_EŞİK</t>
-        </is>
-      </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -9396,22 +9366,22 @@
         <v>10.48668504530712</v>
       </c>
       <c r="K80" t="n">
-        <v>3.253316277798191</v>
+        <v>2.288332013519701</v>
       </c>
       <c r="L80" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="M80" t="n">
-        <v>50</v>
+        <v>45.90163934426229</v>
       </c>
       <c r="N80" t="n">
-        <v>18.03620210753327</v>
+        <v>16.33556957547754</v>
       </c>
       <c r="O80" t="n">
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>6.534108506549252</v>
+        <v>7.53914726604501</v>
       </c>
       <c r="Q80" t="n">
         <v>39</v>
@@ -9438,22 +9408,22 @@
         <v>16.92042739318289</v>
       </c>
       <c r="Y80" t="n">
-        <v>7.574533799089345</v>
+        <v>8.438323202836173</v>
       </c>
       <c r="Z80" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AA80" t="n">
-        <v>40</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB80" t="n">
-        <v>11.85500933413414</v>
+        <v>12.13601999736521</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.4603343844496122</v>
+        <v>0</v>
       </c>
       <c r="AE80" t="n">
         <v>24</v>
@@ -9487,7 +9457,7 @@
         <v>46280</v>
       </c>
       <c r="C81" t="n">
-        <v>1.209909539473684</v>
+        <v>1.195518092105263</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9547,22 +9517,22 @@
         <v>23.79225853623819</v>
       </c>
       <c r="Y81" t="n">
-        <v>4.988484433349949</v>
+        <v>6.118612910778253</v>
       </c>
       <c r="Z81" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AA81" t="n">
-        <v>42.85714285714285</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB81" t="n">
-        <v>9.586500143562752</v>
+        <v>9.995501637126122</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>5.274640170469125</v>
+        <v>4.134352089976046</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9705,7 +9675,7 @@
         <v>46280</v>
       </c>
       <c r="C83" t="n">
-        <v>5.376233552631579</v>
+        <v>5.293996710526316</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9730,25 +9700,25 @@
         <v>10</v>
       </c>
       <c r="J83" t="n">
-        <v>13.10783674393532</v>
+        <v>13.24118714424848</v>
       </c>
       <c r="K83" t="n">
-        <v>1.594819060842378</v>
+        <v>0.1945525291828787</v>
       </c>
       <c r="L83" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="M83" t="n">
-        <v>54.92957746478874</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N83" t="n">
-        <v>12.57247505236158</v>
+        <v>12.21524903691012</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>8.273237766311681</v>
+        <v>9.78640776699029</v>
       </c>
       <c r="Q83" t="n">
         <v>41</v>
@@ -9814,7 +9784,7 @@
         <v>46280</v>
       </c>
       <c r="C84" t="n">
-        <v>2.051809210526315</v>
+        <v>2.047697368421053</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9842,16 +9812,16 @@
         <v>14.20091622675307</v>
       </c>
       <c r="K84" t="n">
-        <v>5.818736292814752</v>
+        <v>5.606674697037572</v>
       </c>
       <c r="L84" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M84" t="n">
-        <v>60</v>
+        <v>64.1025641025641</v>
       </c>
       <c r="N84" t="n">
-        <v>10.22920434941103</v>
+        <v>10.36085951392524</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9884,16 +9854,16 @@
         <v>11.86663135768809</v>
       </c>
       <c r="Y84" t="n">
-        <v>5.406344136291629</v>
+        <v>5.595910580908258</v>
       </c>
       <c r="Z84" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AA84" t="n">
-        <v>41.02564102564103</v>
+        <v>39.47368421052632</v>
       </c>
       <c r="AB84" t="n">
-        <v>11.13153188861626</v>
+        <v>11.35542624868099</v>
       </c>
       <c r="AC84" t="n">
         <v>2</v>
@@ -9933,7 +9903,7 @@
         <v>46280</v>
       </c>
       <c r="C85" t="n">
-        <v>5.987870065789473</v>
+        <v>5.915912828947368</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9958,25 +9928,25 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>10.95455571191028</v>
+        <v>11.72218885232484</v>
       </c>
       <c r="K85" t="n">
-        <v>0.4310344827586299</v>
+        <v>0.08695652173913437</v>
       </c>
       <c r="L85" t="n">
         <v>64</v>
       </c>
       <c r="M85" t="n">
-        <v>59.375</v>
+        <v>65.625</v>
       </c>
       <c r="N85" t="n">
-        <v>11.97117941249298</v>
+        <v>12.4522586403547</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>7.536480686695279</v>
+        <v>7.906168549087744</v>
       </c>
       <c r="Q85" t="n">
         <v>32</v>
@@ -10042,7 +10012,7 @@
         <v>46280</v>
       </c>
       <c r="C86" t="n">
-        <v>4.761513157894736</v>
+        <v>4.745065789473684</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10074,7 +10044,7 @@
         <v>18.73514495170452</v>
       </c>
       <c r="K86" t="n">
-        <v>14.21476888832189</v>
+        <v>13.82024464345724</v>
       </c>
       <c r="L86" t="n">
         <v>4</v>
@@ -10116,13 +10086,13 @@
         <v>44.99483923332605</v>
       </c>
       <c r="Y86" t="n">
-        <v>7.183533619159521</v>
+        <v>7.504143174879174</v>
       </c>
       <c r="Z86" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA86" t="n">
-        <v>42.85714285714285</v>
+        <v>50</v>
       </c>
       <c r="AB86" t="n">
         <v>15.39519764941737</v>
@@ -10165,7 +10135,7 @@
         <v>46280</v>
       </c>
       <c r="C87" t="n">
-        <v>5.895353618421052</v>
+        <v>5.869654605263158</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10225,16 +10195,16 @@
         <v>15.88967756874082</v>
       </c>
       <c r="Y87" t="n">
-        <v>4.431158570190075</v>
+        <v>4.847762063781225</v>
       </c>
       <c r="Z87" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA87" t="n">
-        <v>47.22222222222222</v>
+        <v>45.94594594594594</v>
       </c>
       <c r="AB87" t="n">
-        <v>10.77883709639034</v>
+        <v>12.72306316839886</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
@@ -10274,7 +10244,7 @@
         <v>46280</v>
       </c>
       <c r="C88" t="n">
-        <v>1.053659539473684</v>
+        <v>1.036184210526316</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10302,16 +10272,16 @@
         <v>16.8583060727446</v>
       </c>
       <c r="K88" t="n">
-        <v>5.984756121719093</v>
+        <v>4.226960166529592</v>
       </c>
       <c r="L88" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M88" t="n">
-        <v>71.42857142857143</v>
+        <v>62.7906976744186</v>
       </c>
       <c r="N88" t="n">
-        <v>13.50801971257277</v>
+        <v>16.59722997270471</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
@@ -10344,16 +10314,16 @@
         <v>22.33299319731812</v>
       </c>
       <c r="Y88" t="n">
-        <v>11.88247845573224</v>
+        <v>13.34393978866156</v>
       </c>
       <c r="Z88" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA88" t="n">
-        <v>33.33333333333334</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB88" t="n">
-        <v>13.04416571402357</v>
+        <v>13.4099918685533</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
@@ -10393,7 +10363,7 @@
         <v>46280</v>
       </c>
       <c r="C89" t="n">
-        <v>2.160773026315789</v>
+        <v>2.131990131578947</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10453,22 +10423,22 @@
         <v>21.41032003314154</v>
       </c>
       <c r="Y89" t="n">
-        <v>7.719776861111127</v>
+        <v>8.949009138888897</v>
       </c>
       <c r="Z89" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA89" t="n">
-        <v>34.375</v>
+        <v>29.62962962962963</v>
       </c>
       <c r="AB89" t="n">
-        <v>17.43017018367781</v>
+        <v>15.33714453561096</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>2.470977053725754</v>
+        <v>1.154288219349831</v>
       </c>
       <c r="AE89" t="n">
         <v>22</v>
@@ -10502,7 +10472,7 @@
         <v>46280</v>
       </c>
       <c r="C90" t="n">
-        <v>2.761101973684211</v>
+        <v>2.730263157894737</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10530,22 +10500,22 @@
         <v>12.8208334231333</v>
       </c>
       <c r="K90" t="n">
-        <v>1.377372807278121</v>
+        <v>0.2450864393636287</v>
       </c>
       <c r="L90" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="M90" t="n">
-        <v>66.30434782608695</v>
+        <v>65.11627906976744</v>
       </c>
       <c r="N90" t="n">
-        <v>14.01635044001331</v>
+        <v>14.40993195910616</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>6.532648271830577</v>
+        <v>7.735953786949135</v>
       </c>
       <c r="Q90" t="n">
         <v>43</v>
@@ -10572,16 +10542,16 @@
         <v>20.63086277737274</v>
       </c>
       <c r="Y90" t="n">
-        <v>11.62005128909185</v>
+        <v>12.60716910790318</v>
       </c>
       <c r="Z90" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AA90" t="n">
-        <v>35</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB90" t="n">
-        <v>11.07727095335549</v>
+        <v>10.84558309221278</v>
       </c>
       <c r="AC90" t="n">
         <v>2</v>
@@ -10621,7 +10591,7 @@
         <v>46280</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2300575657894737</v>
+        <v>0.2302631578947368</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10720,7 +10690,7 @@
         <v>46280</v>
       </c>
       <c r="C92" t="n">
-        <v>1.156455592105263</v>
+        <v>1.131784539473684</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10780,16 +10750,16 @@
         <v>21.60407460332612</v>
       </c>
       <c r="Y92" t="n">
-        <v>7.650607798320452</v>
+        <v>9.620728165289627</v>
       </c>
       <c r="Z92" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AA92" t="n">
-        <v>50</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="AB92" t="n">
-        <v>15.7448586692875</v>
+        <v>12.84590382592824</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10829,7 +10799,7 @@
         <v>46280</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04194078947368421</v>
+        <v>0.04111842105263158</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10889,16 +10859,16 @@
         <v>11.4419372600254</v>
       </c>
       <c r="Y93" t="n">
-        <v>4.573681342361791</v>
+        <v>6.444785629766447</v>
       </c>
       <c r="Z93" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AA93" t="n">
-        <v>45</v>
+        <v>46.875</v>
       </c>
       <c r="AB93" t="n">
-        <v>15.44736513139534</v>
+        <v>13.0285354938626</v>
       </c>
       <c r="AC93" t="n">
         <v>2</v>
@@ -10938,7 +10908,7 @@
         <v>46280</v>
       </c>
       <c r="C94" t="n">
-        <v>8.383018092105264</v>
+        <v>8.490953947368421</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10998,22 +10968,22 @@
         <v>40.43377921558155</v>
       </c>
       <c r="Y94" t="n">
-        <v>3.907820229181724</v>
+        <v>2.670581863033861</v>
       </c>
       <c r="Z94" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AA94" t="n">
-        <v>25</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB94" t="n">
-        <v>17.4269499551429</v>
+        <v>11.76855544142956</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>2.1772633067625</v>
+        <v>3.420772671507033</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -11156,7 +11126,7 @@
         <v>46280</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1262335526315789</v>
+        <v>0.125</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11255,7 +11225,7 @@
         <v>46280</v>
       </c>
       <c r="C97" t="n">
-        <v>1.856496710526316</v>
+        <v>1.834909539473684</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11283,22 +11253,22 @@
         <v>12.87370897365936</v>
       </c>
       <c r="K97" t="n">
-        <v>1.478503016947874</v>
+        <v>0.2985204237275774</v>
       </c>
       <c r="L97" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M97" t="n">
-        <v>53.33333333333334</v>
+        <v>64.40677966101696</v>
       </c>
       <c r="N97" t="n">
-        <v>13.3315532081546</v>
+        <v>13.22134882184171</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>2.484759735400321</v>
+        <v>3.690462791110893</v>
       </c>
       <c r="Q97" t="n">
         <v>50</v>
@@ -11325,16 +11295,16 @@
         <v>16.31583297271808</v>
       </c>
       <c r="Y97" t="n">
-        <v>11.58554413228012</v>
+        <v>12.61361920050942</v>
       </c>
       <c r="Z97" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AA97" t="n">
-        <v>27.27272727272727</v>
+        <v>25</v>
       </c>
       <c r="AB97" t="n">
-        <v>12.78373293291585</v>
+        <v>10.94377446737897</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
@@ -11374,7 +11344,7 @@
         <v>46280</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7125822368421052</v>
+        <v>0.6994243421052632</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11383,7 +11353,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -11398,17 +11368,27 @@
       <c r="I98" t="n">
         <v>10</v>
       </c>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
+      <c r="J98" t="n">
+        <v>10.74975128742972</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
       <c r="L98" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="M98" t="n">
+        <v>47.54098360655738</v>
+      </c>
+      <c r="N98" t="n">
+        <v>14.63776826571144</v>
+      </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
-      <c r="P98" t="inlineStr"/>
+      <c r="P98" t="n">
+        <v>10.00000000000001</v>
+      </c>
       <c r="Q98" t="n">
         <v>49</v>
       </c>
@@ -11434,7 +11414,7 @@
         <v>30.85778357900837</v>
       </c>
       <c r="Y98" t="n">
-        <v>9.070734262854629</v>
+        <v>10.74975128742972</v>
       </c>
       <c r="Z98" t="n">
         <v>4</v>
@@ -11443,7 +11423,7 @@
         <v>50</v>
       </c>
       <c r="AB98" t="n">
-        <v>9.12047942398932</v>
+        <v>7.373728834792908</v>
       </c>
       <c r="AC98" t="n">
         <v>8</v>
@@ -11483,7 +11463,7 @@
         <v>46280</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5604440789473685</v>
+        <v>0.5427631578947368</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11500,11 +11480,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>5</v>
       </c>
@@ -11515,16 +11491,16 @@
         <v>12.51634982914205</v>
       </c>
       <c r="K99" t="n">
-        <v>9.31965449752974</v>
+        <v>5.870831941848298</v>
       </c>
       <c r="L99" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="M99" t="n">
-        <v>76</v>
+        <v>54.71698113207547</v>
       </c>
       <c r="N99" t="n">
-        <v>13.44442617194759</v>
+        <v>15.86138284247839</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
@@ -11557,22 +11533,22 @@
         <v>33.04241514445872</v>
       </c>
       <c r="Y99" t="n">
-        <v>4.363175891390503</v>
+        <v>7.380331751016489</v>
       </c>
       <c r="Z99" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AA99" t="n">
-        <v>27.27272727272727</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB99" t="n">
-        <v>15.93679849313842</v>
+        <v>12.01251736130811</v>
       </c>
       <c r="AC99" t="n">
         <v>10</v>
       </c>
       <c r="AD99" t="n">
-        <v>5.893989225539387</v>
+        <v>2.828414632128917</v>
       </c>
       <c r="AE99" t="n">
         <v>38</v>
@@ -11715,7 +11691,7 @@
         <v>46280</v>
       </c>
       <c r="C101" t="n">
-        <v>343.6484375</v>
+        <v>342.887541118421</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11775,22 +11751,22 @@
         <v>12.90626814318425</v>
       </c>
       <c r="Y101" t="n">
-        <v>4.920221335938313</v>
+        <v>5.130744218198801</v>
       </c>
       <c r="Z101" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AA101" t="n">
-        <v>35.48387096774194</v>
+        <v>50</v>
       </c>
       <c r="AB101" t="n">
-        <v>13.3985840727138</v>
+        <v>12.00209105524237</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>1.13565542456382</v>
+        <v>0.9162671032230785</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11923,11 +11899,11 @@
         <v>46280</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7277960526315789</v>
+        <v>0.7179276315789473</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -11937,7 +11913,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -11983,22 +11959,22 @@
         <v>14.28440963201156</v>
       </c>
       <c r="Y103" t="n">
-        <v>7.90432356768248</v>
+        <v>9.153078502357959</v>
       </c>
       <c r="Z103" t="n">
         <v>24</v>
       </c>
       <c r="AA103" t="n">
-        <v>45.83333333333334</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB103" t="n">
-        <v>9.823858635767134</v>
+        <v>9.067180759022456</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>0.103888082507142</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
         <v>33</v>
@@ -12032,7 +12008,7 @@
         <v>46280</v>
       </c>
       <c r="C104" t="n">
-        <v>0.05448190789473684</v>
+        <v>0.05324835526315789</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12092,22 +12068,22 @@
         <v>17.05083756364998</v>
       </c>
       <c r="Y104" t="n">
-        <v>3.773584777988503e-06</v>
+        <v>2.264154631541349</v>
       </c>
       <c r="Z104" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AA104" t="n">
-        <v>47.61904761904762</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="AB104" t="n">
-        <v>11.29611233976692</v>
+        <v>11.92479434760016</v>
       </c>
       <c r="AC104" t="n">
         <v>5</v>
       </c>
       <c r="AD104" t="n">
-        <v>4.999996415094332</v>
+        <v>2.799224131274125</v>
       </c>
       <c r="AE104" t="n">
         <v>42</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -438,13 +438,13 @@
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -670,7 +670,7 @@
         <v>46280</v>
       </c>
       <c r="C2" t="n">
-        <v>0.393297697368421</v>
+        <v>0.390249895942988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,22 +698,22 @@
         <v>21.42119502374098</v>
       </c>
       <c r="K2" t="n">
-        <v>7.041486757729642</v>
+        <v>6.21198483563965</v>
       </c>
       <c r="L2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M2" t="n">
-        <v>55.55555555555556</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="N2" t="n">
-        <v>15.02926611302887</v>
+        <v>14.87705714843537</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>2.763894011456003</v>
+        <v>3.566466788302858</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -740,22 +740,22 @@
         <v>11.79582706077868</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.252699253670988</v>
+        <v>4.994678577853662</v>
       </c>
       <c r="Z2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA2" t="n">
-        <v>50</v>
+        <v>43.24324324324324</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.28945017419879</v>
+        <v>9.41027054599596</v>
       </c>
       <c r="AC2" t="n">
         <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.002572084570613</v>
+        <v>5.268464278864659</v>
       </c>
       <c r="AE2" t="n">
         <v>46</v>
@@ -789,7 +789,7 @@
         <v>46280</v>
       </c>
       <c r="C3" t="n">
-        <v>0.692434216899671</v>
+        <v>0.6933207210869315</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>16.83732632822199</v>
       </c>
       <c r="K3" t="n">
-        <v>10.14051818017179</v>
+        <v>10.28152800922233</v>
       </c>
       <c r="L3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M3" t="n">
-        <v>54.16666666666666</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="N3" t="n">
-        <v>13.22808084587165</v>
+        <v>13.85448427853721</v>
       </c>
       <c r="O3" t="n">
         <v>10</v>
@@ -859,22 +859,22 @@
         <v>17.17248092970491</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.001377365861005</v>
+        <v>5.881033554812798</v>
       </c>
       <c r="Z3" t="n">
         <v>29</v>
       </c>
       <c r="AA3" t="n">
-        <v>37.93103448275862</v>
+        <v>41.37931034482759</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.97793792370923</v>
+        <v>11.43477117522758</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.253916198009</v>
+        <v>4.376340498369147</v>
       </c>
       <c r="AE3" t="n">
         <v>35</v>
@@ -908,7 +908,7 @@
         <v>46280</v>
       </c>
       <c r="C4" t="n">
-        <v>1.43811677631579</v>
+        <v>1.430025400996243</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -968,22 +968,22 @@
         <v>16.66966699739723</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.65583882744032</v>
+        <v>9.169774763289585</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA4" t="n">
-        <v>57.14285714285715</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.76431425412891</v>
+        <v>12.21826983405953</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.471534858172707</v>
+        <v>0.9140407111694171</v>
       </c>
       <c r="AE4" t="n">
         <v>40</v>
@@ -1017,7 +1017,7 @@
         <v>46280</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2253289473684211</v>
+        <v>0.2245273444783983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,16 +1045,16 @@
         <v>19.13427219952423</v>
       </c>
       <c r="K5" t="n">
-        <v>3.513883233796533</v>
+        <v>3.14563481775072</v>
       </c>
       <c r="L5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M5" t="n">
-        <v>51.61290322580645</v>
+        <v>56.25</v>
       </c>
       <c r="N5" t="n">
-        <v>12.40479182691615</v>
+        <v>11.58387228227014</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -1087,22 +1087,22 @@
         <v>10.55954734904581</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.372732418128946</v>
+        <v>6.705809411365204</v>
       </c>
       <c r="Z5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA5" t="n">
-        <v>31.57894736842105</v>
+        <v>25</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.929312891751019</v>
+        <v>10.09581628013362</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.874157257338773</v>
+        <v>3.530970758039997</v>
       </c>
       <c r="AE5" t="n">
         <v>45</v>
@@ -1136,16 +1136,16 @@
         <v>46280</v>
       </c>
       <c r="C6" t="n">
-        <v>1.51110197368421</v>
+        <v>1.530774724280803</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %90.91: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1165,25 +1165,25 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>28.20804212939517</v>
+        <v>29.57085786530786</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1362397820163341</v>
+        <v>3.40277354166667</v>
       </c>
       <c r="L6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M6" t="n">
-        <v>90.90909090909091</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N6" t="n">
-        <v>13.70526345225087</v>
+        <v>10.7351556932087</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.861224489795932</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>35</v>
@@ -1249,7 +1249,7 @@
         <v>46280</v>
       </c>
       <c r="C7" t="n">
-        <v>2.255345394736842</v>
+        <v>2.241161205938875</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,16 +1309,16 @@
         <v>18.9234494530097</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.839842389725483</v>
+        <v>9.413161620302768</v>
       </c>
       <c r="Z7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>12.56450013246144</v>
+        <v>13.12838423287637</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1358,7 +1358,7 @@
         <v>46280</v>
       </c>
       <c r="C8" t="n">
-        <v>0.34375</v>
+        <v>0.3417256983970598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>20.70550141590351</v>
       </c>
       <c r="K8" t="n">
-        <v>5.566125709548642</v>
+        <v>4.94445973866855</v>
       </c>
       <c r="L8" t="n">
         <v>5</v>
@@ -1395,13 +1395,13 @@
         <v>60</v>
       </c>
       <c r="N8" t="n">
-        <v>17.38979657077811</v>
+        <v>17.75833754694722</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.305544770249357</v>
+        <v>2.911578437718698</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1428,7 +1428,7 @@
         <v>26.93179943319606</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.29186994395644</v>
+        <v>16.78481685843375</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1473,7 +1473,7 @@
         <v>46280</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5555098684210527</v>
+        <v>0.5506265930407735</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,16 +1501,16 @@
         <v>14.50739888386581</v>
       </c>
       <c r="K9" t="n">
-        <v>4.479196003827668</v>
+        <v>3.560759240414257</v>
       </c>
       <c r="L9" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M9" t="n">
-        <v>51.16279069767442</v>
+        <v>50</v>
       </c>
       <c r="N9" t="n">
-        <v>13.70637024885155</v>
+        <v>14.79931305816791</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1582,7 +1582,7 @@
         <v>46280</v>
       </c>
       <c r="C10" t="n">
-        <v>1.881167763157895</v>
+        <v>1.875173349964071</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,22 +1610,22 @@
         <v>13.50421550203786</v>
       </c>
       <c r="K10" t="n">
-        <v>2.595456791336681</v>
+        <v>2.268532435167647</v>
       </c>
       <c r="L10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M10" t="n">
-        <v>55.31914893617022</v>
+        <v>54.16666666666666</v>
       </c>
       <c r="N10" t="n">
-        <v>10.09697779894922</v>
+        <v>10.37055776876159</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>7.217223296469188</v>
+        <v>7.559967255552102</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1691,7 +1691,7 @@
         <v>46280</v>
       </c>
       <c r="C11" t="n">
-        <v>7.725123355263158</v>
+        <v>7.751539216871155</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,10 +1716,10 @@
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>11.81477122148857</v>
+        <v>11.80661525537724</v>
       </c>
       <c r="K11" t="n">
-        <v>2.036659877800395</v>
+        <v>2.376103190767132</v>
       </c>
       <c r="L11" t="n">
         <v>58</v>
@@ -1728,13 +1728,13 @@
         <v>56.89655172413793</v>
       </c>
       <c r="N11" t="n">
-        <v>13.03197690775713</v>
+        <v>12.94286804690456</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9441117764471096</v>
+        <v>0.6094164456233564</v>
       </c>
       <c r="Q11" t="n">
         <v>49</v>
@@ -1761,16 +1761,16 @@
         <v>19.5857262818246</v>
       </c>
       <c r="Y11" t="n">
-        <v>10.01873804881014</v>
+        <v>9.71104942641472</v>
       </c>
       <c r="Z11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA11" t="n">
-        <v>53.33333333333334</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.208098680161603</v>
+        <v>11.07010377658062</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
@@ -1810,7 +1810,7 @@
         <v>46280</v>
       </c>
       <c r="C12" t="n">
-        <v>5.597245065789473</v>
+        <v>5.597762736851915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>25.10845701569052</v>
+        <v>25.10153053951003</v>
       </c>
       <c r="K12" t="n">
         <v>0.5540166204986097</v>
@@ -1923,7 +1923,7 @@
         <v>46280</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1659128289473684</v>
+        <v>0.1667506111758667</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,10 +1951,10 @@
         <v>47.07727092024744</v>
       </c>
       <c r="K13" t="n">
-        <v>2.736888039453733</v>
+        <v>3.255661298620893</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1962,7 +1962,7 @@
         <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>3.176183377574326</v>
+        <v>2.657809428426727</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1987,7 +1987,7 @@
         <v>20.61663781635479</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.82361811819354</v>
+        <v>14.39351720628036</v>
       </c>
       <c r="Z13" t="n">
         <v>2</v>
@@ -2022,7 +2022,7 @@
         <v>46280</v>
       </c>
       <c r="C14" t="n">
-        <v>8.562911184210526</v>
+        <v>8.548282306138416</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,16 +2082,16 @@
         <v>16.11612055393703</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.893755089473695</v>
+        <v>5.056234604998478</v>
       </c>
       <c r="Z14" t="n">
         <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>33.33333333333334</v>
+        <v>37.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>13.56861547631727</v>
+        <v>12.48704530520519</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2131,7 +2131,7 @@
         <v>46280</v>
       </c>
       <c r="C15" t="n">
-        <v>13.37376644736842</v>
+        <v>13.31332000775616</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,25 +2156,25 @@
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>15.72365931533905</v>
+        <v>15.78089892450823</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3858024691357986</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="M15" t="n">
-        <v>64.0625</v>
+        <v>62.90322580645162</v>
       </c>
       <c r="N15" t="n">
-        <v>17.3128965068103</v>
+        <v>17.20761445256585</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>7.584934665641829</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2201,7 +2201,7 @@
         <v>36.34743205418309</v>
       </c>
       <c r="Y15" t="n">
-        <v>15.39851911208032</v>
+        <v>15.78089892450823</v>
       </c>
       <c r="Z15" t="n">
         <v>1</v>
@@ -2246,7 +2246,7 @@
         <v>46280</v>
       </c>
       <c r="C16" t="n">
-        <v>34.08717105263158</v>
+        <v>34.15200700059148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,22 +2274,22 @@
         <v>16.99349200873118</v>
       </c>
       <c r="K16" t="n">
-        <v>1.475804705234363</v>
+        <v>1.668818082111545</v>
       </c>
       <c r="L16" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M16" t="n">
-        <v>69.73684210526316</v>
+        <v>71.7948717948718</v>
       </c>
       <c r="N16" t="n">
-        <v>17.73594465531578</v>
+        <v>17.52899811987269</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>8.400224387997346</v>
+        <v>8.194431758968502</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2355,7 +2355,7 @@
         <v>46280</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3881578947368421</v>
+        <v>0.3906611276407214</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,10 +2380,10 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>51.08056225103426</v>
+        <v>51.07603542299748</v>
       </c>
       <c r="K17" t="n">
-        <v>1.833872707659134</v>
+        <v>2.481116813234752</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2394,7 +2394,7 @@
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>6.055084745762707</v>
+        <v>5.385268387368436</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2460,7 +2460,7 @@
         <v>46280</v>
       </c>
       <c r="C18" t="n">
-        <v>0.07298519736842105</v>
+        <v>0.0719638919338171</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,25 +2485,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>33.00210927005214</v>
+        <v>34.12837610820287</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.2865326639354349</v>
       </c>
       <c r="L18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M18" t="n">
-        <v>62.5</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N18" t="n">
-        <v>9.509462556470817</v>
+        <v>10.50046967635557</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>10.00000000000001</v>
+        <v>9.685714600000006</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2569,7 +2569,7 @@
         <v>46280</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02652138157894737</v>
+        <v>0.02611261180476282</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,25 +2594,25 @@
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>11.21291804020141</v>
+        <v>11.89842102923254</v>
       </c>
       <c r="K19" t="n">
-        <v>0.78125</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M19" t="n">
-        <v>52.63157894736842</v>
+        <v>64.1025641025641</v>
       </c>
       <c r="N19" t="n">
-        <v>20.70961954883646</v>
+        <v>18.55195987404595</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>9.147286821705425</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q19" t="n">
         <v>14</v>
@@ -2639,16 +2639,16 @@
         <v>20.26411217973316</v>
       </c>
       <c r="Y19" t="n">
-        <v>10.51926896239048</v>
+        <v>11.89842102923254</v>
       </c>
       <c r="Z19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>15.15125969989996</v>
+        <v>16.74028578011673</v>
       </c>
       <c r="AC19" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
         <v>46280</v>
       </c>
       <c r="C20" t="n">
-        <v>1.593338815789474</v>
+        <v>1.603766734525067</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,22 +2716,22 @@
         <v>18.49305897009618</v>
       </c>
       <c r="K20" t="n">
-        <v>2.225611008493211</v>
+        <v>2.894646591966832</v>
       </c>
       <c r="L20" t="n">
         <v>32</v>
       </c>
       <c r="M20" t="n">
-        <v>43.75</v>
+        <v>50</v>
       </c>
       <c r="N20" t="n">
-        <v>16.46570377238519</v>
+        <v>13.64855649154946</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>7.605128416264373</v>
+        <v>6.905464611982937</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
@@ -2797,7 +2797,7 @@
         <v>46280</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8898026315789473</v>
+        <v>0.884539046884629</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2822,25 +2822,25 @@
         <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>10.08775786440359</v>
+        <v>10.37112050264447</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2780352177942591</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M21" t="n">
-        <v>54</v>
+        <v>51.92307692307692</v>
       </c>
       <c r="N21" t="n">
-        <v>12.53959404921769</v>
+        <v>13.76434079846411</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>7.700554528650638</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2906,7 +2906,7 @@
         <v>46280</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2915296052631579</v>
+        <v>0.2919677862248752</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %82.35: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2935,25 +2935,25 @@
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>20.82771333123346</v>
+        <v>20.87642808379643</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3538570417551457</v>
+        <v>0.5665716758018968</v>
       </c>
       <c r="L22" t="n">
         <v>17</v>
       </c>
       <c r="M22" t="n">
-        <v>76.47058823529412</v>
+        <v>82.35294117647059</v>
       </c>
       <c r="N22" t="n">
-        <v>12.47389722984058</v>
+        <v>11.83226844871437</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>9.612129760225653</v>
+        <v>9.380282301567178</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -3011,7 +3011,7 @@
         <v>46280</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5916940789473685</v>
+        <v>0.5942161284402957</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,10 +3036,10 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>41.91054586591394</v>
+        <v>41.90517182209699</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2787456445993097</v>
+        <v>0.6968601209193848</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -3050,7 +3050,7 @@
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.708130646282127</v>
+        <v>4.273360533698178</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3116,7 +3116,7 @@
         <v>46280</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1548108552631579</v>
+        <v>0.1562644490001774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %83.33: SAT yönü değerlendirmeye alınabilir.</t>
+          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3148,22 +3148,22 @@
         <v>23.31817459365587</v>
       </c>
       <c r="K24" t="n">
-        <v>2.360726647026845</v>
+        <v>3.321840846143909</v>
       </c>
       <c r="L24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M24" t="n">
         <v>50</v>
       </c>
       <c r="N24" t="n">
-        <v>11.72987778538172</v>
+        <v>11.15287235946911</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>7.463090194070099</v>
+        <v>6.463453514925765</v>
       </c>
       <c r="Q24" t="n">
         <v>4</v>
@@ -3190,16 +3190,16 @@
         <v>17.82705440547527</v>
       </c>
       <c r="Y24" t="n">
-        <v>13.12629585496091</v>
+        <v>12.31059677467193</v>
       </c>
       <c r="Z24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>83.33333333333333</v>
+        <v>75</v>
       </c>
       <c r="AB24" t="n">
-        <v>13.54560099901865</v>
+        <v>13.3342061142625</v>
       </c>
       <c r="AC24" t="n">
         <v>2</v>
@@ -3239,7 +3239,7 @@
         <v>46280</v>
       </c>
       <c r="C25" t="n">
-        <v>3.295641447368421</v>
+        <v>3.295946313280214</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>20.95143919294578</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3190341317191869</v>
+        <v>0.3283142231063074</v>
       </c>
       <c r="L25" t="n">
         <v>35</v>
@@ -3282,7 +3282,7 @@
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>7.656538895894571</v>
+        <v>7.646580964007521</v>
       </c>
       <c r="Q25" t="n">
         <v>44</v>
@@ -3348,7 +3348,7 @@
         <v>46280</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4370888157894737</v>
+        <v>0.4387741327606402</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3408,22 +3408,22 @@
         <v>11.40992936035117</v>
       </c>
       <c r="Y26" t="n">
-        <v>8.234106787355122</v>
+        <v>7.880277973579187</v>
       </c>
       <c r="Z26" t="n">
         <v>22</v>
       </c>
       <c r="AA26" t="n">
-        <v>45.45454545454545</v>
+        <v>50</v>
       </c>
       <c r="AB26" t="n">
-        <v>10.68664353651355</v>
+        <v>10.44719082438257</v>
       </c>
       <c r="AC26" t="n">
         <v>10</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.924345909817338</v>
+        <v>2.301051262196441</v>
       </c>
       <c r="AE26" t="n">
         <v>36</v>
@@ -3457,7 +3457,7 @@
         <v>46280</v>
       </c>
       <c r="C27" t="n">
-        <v>55.40707236842105</v>
+        <v>55.92622458856643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>68.86729662338568</v>
+        <v>69.66261412600872</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.4616805170821747</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
         <v>3</v>
@@ -3522,7 +3522,7 @@
         <v>6</v>
       </c>
       <c r="AD27" t="n">
-        <v>5.564007421150285</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>46280</v>
       </c>
       <c r="C28" t="n">
-        <v>1.38671875</v>
+        <v>1.378622621043516</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3571,25 +3571,25 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>17.9842555915977</v>
+        <v>17.97667209838105</v>
       </c>
       <c r="K28" t="n">
-        <v>0.8975317875841604</v>
+        <v>0.2991841205348011</v>
       </c>
       <c r="L28" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M28" t="n">
-        <v>69.76744186046511</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N28" t="n">
-        <v>15.37615913867865</v>
+        <v>15.98024047712831</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>1.092661230541125</v>
+        <v>1.695742487218288</v>
       </c>
       <c r="Q28" t="n">
         <v>39</v>
@@ -3655,7 +3655,7 @@
         <v>46280</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4157072368421053</v>
+        <v>0.4110166237729453</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3672,7 +3672,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %100.00: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>5</v>
       </c>
@@ -3683,7 +3687,7 @@
         <v>27.65210909859499</v>
       </c>
       <c r="K29" t="n">
-        <v>25.53293017038445</v>
+        <v>24.116485252706</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3721,22 +3725,22 @@
         <v>31.20488584758381</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.322975962791709</v>
+        <v>5.402543166808704</v>
       </c>
       <c r="Z29" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AA29" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="AB29" t="n">
-        <v>12.69230558699323</v>
+        <v>16.19254517444829</v>
       </c>
       <c r="AC29" t="n">
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>5.933529072769361</v>
+        <v>4.860021597936015</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3770,7 +3774,7 @@
         <v>46280</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4089226973684211</v>
+        <v>0.4071100015991487</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3795,25 +3799,25 @@
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>12.46365070502794</v>
+        <v>12.45555475167782</v>
       </c>
       <c r="K30" t="n">
-        <v>0.7088607594936791</v>
+        <v>0.2531607088607446</v>
       </c>
       <c r="L30" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="M30" t="n">
-        <v>42.85714285714285</v>
+        <v>44.06779661016949</v>
       </c>
       <c r="N30" t="n">
-        <v>13.93181964189898</v>
+        <v>13.85493445963043</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>4.260935143288069</v>
+        <v>4.734852504974163</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3840,16 +3844,16 @@
         <v>26.71344279693404</v>
       </c>
       <c r="Y30" t="n">
-        <v>11.84313987458255</v>
+        <v>12.23392661351896</v>
       </c>
       <c r="Z30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA30" t="n">
-        <v>55.55555555555556</v>
+        <v>50</v>
       </c>
       <c r="AB30" t="n">
-        <v>15.13668580481328</v>
+        <v>11.98915066855684</v>
       </c>
       <c r="AC30" t="n">
         <v>8</v>
@@ -3889,7 +3893,7 @@
         <v>46280</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2606907894736842</v>
+        <v>0.2611261182532393</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3946,10 +3950,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="X31" t="n">
-        <v>50.77283913219171</v>
+        <v>50.78678362361622</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.7047803974785549</v>
+        <v>0.5481648197215527</v>
       </c>
       <c r="Z31" t="n">
         <v>4</v>
@@ -3964,7 +3968,7 @@
         <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>9.361195473186113</v>
+        <v>9.503932394153313</v>
       </c>
       <c r="AE31" t="n">
         <v>10</v>
@@ -3998,7 +4002,7 @@
         <v>46280</v>
       </c>
       <c r="C32" t="n">
-        <v>2.312911184210526</v>
+        <v>2.319293494178411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4058,22 +4062,22 @@
         <v>13.38656892008534</v>
       </c>
       <c r="Y32" t="n">
-        <v>6.402960371962796</v>
+        <v>6.144686157604474</v>
       </c>
       <c r="Z32" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AA32" t="n">
-        <v>35.48387096774194</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB32" t="n">
-        <v>10.48364730798535</v>
+        <v>10.89590835038585</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.706292885313443</v>
+        <v>1.976780819795687</v>
       </c>
       <c r="AE32" t="n">
         <v>26</v>
@@ -4107,7 +4111,7 @@
         <v>46280</v>
       </c>
       <c r="C33" t="n">
-        <v>1.769120065789474</v>
+        <v>1.764143470688965</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4167,13 +4171,13 @@
         <v>15.09663082780621</v>
       </c>
       <c r="Y33" t="n">
-        <v>6.202668194109995</v>
+        <v>6.46652328847731</v>
       </c>
       <c r="Z33" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA33" t="n">
-        <v>25.71428571428572</v>
+        <v>26.47058823529412</v>
       </c>
       <c r="AB33" t="n">
         <v>11.22884089524853</v>
@@ -4182,7 +4186,7 @@
         <v>8</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.916186496231587</v>
+        <v>1.639495040104466</v>
       </c>
       <c r="AE33" t="n">
         <v>29</v>
@@ -4216,7 +4220,7 @@
         <v>46280</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7907072368421053</v>
+        <v>0.7866681098538582</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4244,16 +4248,16 @@
         <v>15.41713612942789</v>
       </c>
       <c r="K34" t="n">
-        <v>5.186484693941673</v>
+        <v>4.649166266424887</v>
       </c>
       <c r="L34" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M34" t="n">
-        <v>64.70588235294117</v>
+        <v>59.45945945945946</v>
       </c>
       <c r="N34" t="n">
-        <v>13.27608657086676</v>
+        <v>12.81533291737637</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4286,16 +4290,16 @@
         <v>10.81830054752258</v>
       </c>
       <c r="Y34" t="n">
-        <v>5.082026908692572</v>
+        <v>5.56689125407781</v>
       </c>
       <c r="Z34" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA34" t="n">
-        <v>32</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="AB34" t="n">
-        <v>10.55285401940977</v>
+        <v>9.7453229777544</v>
       </c>
       <c r="AC34" t="n">
         <v>2</v>
@@ -4335,7 +4339,7 @@
         <v>46280</v>
       </c>
       <c r="C35" t="n">
-        <v>1.4453125</v>
+        <v>1.437221758936734</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4363,7 +4367,7 @@
         <v>38.83766461406507</v>
       </c>
       <c r="K35" t="n">
-        <v>4.310235657911776</v>
+        <v>3.726315497423016</v>
       </c>
       <c r="L35" t="n">
         <v>2</v>
@@ -4374,7 +4378,7 @@
         <v>6</v>
       </c>
       <c r="P35" t="n">
-        <v>1.619941064681174</v>
+        <v>2.192003535142906</v>
       </c>
       <c r="Q35" t="n">
         <v>7</v>
@@ -4401,16 +4405,16 @@
         <v>13.94161507705984</v>
       </c>
       <c r="Y35" t="n">
-        <v>8.452907581338277</v>
+        <v>8.965380710750958</v>
       </c>
       <c r="Z35" t="n">
         <v>12</v>
       </c>
       <c r="AA35" t="n">
-        <v>66.66666666666667</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="AB35" t="n">
-        <v>11.84409368984752</v>
+        <v>12.53765928712615</v>
       </c>
       <c r="AC35" t="n">
         <v>2</v>
@@ -4450,7 +4454,7 @@
         <v>46280</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07750822368421052</v>
+        <v>0.07710416992908974</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4475,25 +4479,25 @@
         <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>11.49958181785439</v>
+        <v>11.87370670137952</v>
       </c>
       <c r="K36" t="n">
-        <v>0.3667272453605541</v>
+        <v>0.2673794110497729</v>
       </c>
       <c r="L36" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M36" t="n">
-        <v>60</v>
+        <v>67.56756756756756</v>
       </c>
       <c r="N36" t="n">
-        <v>16.84443346837099</v>
+        <v>15.78000569861148</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>1.627304983898381</v>
+        <v>1.728000272000019</v>
       </c>
       <c r="Q36" t="n">
         <v>10</v>
@@ -4559,7 +4563,7 @@
         <v>46280</v>
       </c>
       <c r="C37" t="n">
-        <v>0.05633223684210527</v>
+        <v>0.05592622520539978</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4584,19 +4588,19 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>22.97142611607663</v>
+        <v>23.52660551439098</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M37" t="n">
-        <v>68.57142857142857</v>
+        <v>71.875</v>
       </c>
       <c r="N37" t="n">
-        <v>15.40609297681062</v>
+        <v>14.06513758430328</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
@@ -4668,7 +4672,7 @@
         <v>46280</v>
       </c>
       <c r="C38" t="n">
-        <v>1.624177631578947</v>
+        <v>1.611991210776004</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4728,22 +4732,22 @@
         <v>12.11239445105858</v>
       </c>
       <c r="Y38" t="n">
-        <v>7.233134832406485</v>
+        <v>7.92917696075619</v>
       </c>
       <c r="Z38" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA38" t="n">
-        <v>56.25</v>
+        <v>60</v>
       </c>
       <c r="AB38" t="n">
-        <v>9.174291248616079</v>
+        <v>9.168989995399087</v>
       </c>
       <c r="AC38" t="n">
         <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.982600697560345</v>
+        <v>2.249163166882029</v>
       </c>
       <c r="AE38" t="n">
         <v>30</v>
@@ -4777,7 +4781,7 @@
         <v>46280</v>
       </c>
       <c r="C39" t="n">
-        <v>2.645970394736842</v>
+        <v>2.62771017389477</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4837,16 +4841,16 @@
         <v>10.27889366548247</v>
       </c>
       <c r="Y39" t="n">
-        <v>7.283698760045809</v>
+        <v>7.923547240463147</v>
       </c>
       <c r="Z39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA39" t="n">
-        <v>50</v>
+        <v>52.38095238095238</v>
       </c>
       <c r="AB39" t="n">
-        <v>10.57423961341057</v>
+        <v>10.46527149923836</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
@@ -4886,7 +4890,7 @@
         <v>46280</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2284128289473684</v>
+        <v>0.2282283508033282</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4914,7 +4918,7 @@
         <v>15.29580504962521</v>
       </c>
       <c r="K40" t="n">
-        <v>2.331270033942578</v>
+        <v>2.248621949506435</v>
       </c>
       <c r="L40" t="n">
         <v>37</v>
@@ -4929,7 +4933,7 @@
         <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>0.6534952276421535</v>
+        <v>0.7348539629850714</v>
       </c>
       <c r="Q40" t="n">
         <v>29</v>
@@ -4956,10 +4960,10 @@
         <v>37.29449902814472</v>
       </c>
       <c r="Y40" t="n">
-        <v>13.32112153525483</v>
+        <v>13.39112792981837</v>
       </c>
       <c r="Z40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr"/>
@@ -5001,7 +5005,7 @@
         <v>46280</v>
       </c>
       <c r="C41" t="n">
-        <v>1.224300986842105</v>
+        <v>1.219273924852227</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5033,7 +5037,7 @@
         <v>40.38073481248902</v>
       </c>
       <c r="K41" t="n">
-        <v>1.688736469347552</v>
+        <v>1.271195695144378</v>
       </c>
       <c r="L41" t="n">
         <v>4</v>
@@ -5042,13 +5046,13 @@
         <v>100</v>
       </c>
       <c r="N41" t="n">
-        <v>19.55681544402417</v>
+        <v>19.30180353043365</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>8.173239061887404</v>
+        <v>8.619236935971264</v>
       </c>
       <c r="Q41" t="n">
         <v>11</v>
@@ -5075,7 +5079,7 @@
         <v>14.15095011586145</v>
       </c>
       <c r="Y41" t="n">
-        <v>10.91731048569018</v>
+        <v>11.28308998536091</v>
       </c>
       <c r="Z41" t="n">
         <v>17</v>
@@ -5124,7 +5128,7 @@
         <v>46280</v>
       </c>
       <c r="C42" t="n">
-        <v>3.392269736842105</v>
+        <v>3.376134524583685</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5156,16 +5160,16 @@
         <v>17.9384880883827</v>
       </c>
       <c r="K42" t="n">
-        <v>6.88828314100467</v>
+        <v>6.379872763820527</v>
       </c>
       <c r="L42" t="n">
         <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>50</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N42" t="n">
-        <v>9.903369075310865</v>
+        <v>11.6708708659834</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
@@ -5196,7 +5200,7 @@
         <v>23.05415424937474</v>
       </c>
       <c r="Y42" t="n">
-        <v>12.28585879812122</v>
+        <v>12.70306804035408</v>
       </c>
       <c r="Z42" t="n">
         <v>4</v>
@@ -5243,7 +5247,7 @@
         <v>46280</v>
       </c>
       <c r="C43" t="n">
-        <v>6.064967105263158</v>
+        <v>6.024405810459545</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5262,7 +5266,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %88.24: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -5275,22 +5279,22 @@
         <v>20.13868121382601</v>
       </c>
       <c r="K43" t="n">
-        <v>1.23703584517012</v>
+        <v>0.5599826666959462</v>
       </c>
       <c r="L43" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M43" t="n">
-        <v>83.33333333333333</v>
+        <v>88.23529411764706</v>
       </c>
       <c r="N43" t="n">
-        <v>17.32461006185299</v>
+        <v>17.13412538541539</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>2.729202936221387</v>
+        <v>3.420861104069517</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5356,7 +5360,7 @@
         <v>46280</v>
       </c>
       <c r="C44" t="n">
-        <v>4.681332236842105</v>
+        <v>4.52961303214565</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5384,7 +5388,7 @@
         <v>25.31049029846984</v>
       </c>
       <c r="K44" t="n">
-        <v>21.89056846243633</v>
+        <v>17.94016734337485</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5422,22 +5426,22 @@
         <v>28.18267712431886</v>
       </c>
       <c r="Y44" t="n">
-        <v>4.908704360870919</v>
+        <v>7.99055692292201</v>
       </c>
       <c r="Z44" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA44" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="AB44" t="n">
-        <v>22.38906282491685</v>
+        <v>15.53705409348409</v>
       </c>
       <c r="AC44" t="n">
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>5.354113228670809</v>
+        <v>2.183953092069735</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5463,7 +5467,7 @@
         <v>46280</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02076480263157895</v>
+        <v>0.0205611119810906</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5488,25 +5492,25 @@
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>15.42186418347916</v>
+        <v>15.41404182570979</v>
       </c>
       <c r="K45" t="n">
-        <v>1.000000000000001</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="M45" t="n">
-        <v>57.53424657534246</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="N45" t="n">
-        <v>14.41603372498879</v>
+        <v>13.18395349585476</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>8.910891089108919</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q45" t="n">
         <v>38</v>
@@ -5533,16 +5537,16 @@
         <v>19.20467487893223</v>
       </c>
       <c r="Y45" t="n">
-        <v>14.57608282531396</v>
+        <v>15.41404182570979</v>
       </c>
       <c r="Z45" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA45" t="n">
-        <v>44.44444444444444</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB45" t="n">
-        <v>12.33518822913915</v>
+        <v>13.68813816694538</v>
       </c>
       <c r="AC45" t="n">
         <v>5</v>
@@ -5582,7 +5586,7 @@
         <v>46280</v>
       </c>
       <c r="C46" t="n">
-        <v>9.498355263157894</v>
+        <v>9.478672623282765</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5607,25 +5611,25 @@
         <v>10</v>
       </c>
       <c r="J46" t="n">
-        <v>12.45458057056798</v>
+        <v>12.68362764677318</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1083423618634782</v>
+        <v>0.1629549158066235</v>
       </c>
       <c r="L46" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M46" t="n">
-        <v>54.54545454545455</v>
+        <v>55.22388059701493</v>
       </c>
       <c r="N46" t="n">
-        <v>15.08343420142066</v>
+        <v>15.47338783323688</v>
       </c>
       <c r="O46" t="n">
         <v>8</v>
       </c>
       <c r="P46" t="n">
-        <v>7.883116883116892</v>
+        <v>7.824295010846005</v>
       </c>
       <c r="Q46" t="n">
         <v>51</v>
@@ -5652,16 +5656,16 @@
         <v>26.79655122306823</v>
       </c>
       <c r="Y46" t="n">
-        <v>12.35973179545484</v>
+        <v>12.54134132571958</v>
       </c>
       <c r="Z46" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA46" t="n">
-        <v>44.44444444444444</v>
+        <v>37.5</v>
       </c>
       <c r="AB46" t="n">
-        <v>14.79451359380145</v>
+        <v>10.37598329500288</v>
       </c>
       <c r="AC46" t="n">
         <v>3</v>
@@ -5701,7 +5705,7 @@
         <v>46280</v>
       </c>
       <c r="C47" t="n">
-        <v>0.947779605263158</v>
+        <v>0.9474560777154897</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5726,25 +5730,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>16.58327705889968</v>
+        <v>16.57556043110229</v>
       </c>
       <c r="K47" t="n">
-        <v>1.229688186209943</v>
+        <v>1.185772725276446</v>
       </c>
       <c r="L47" t="n">
         <v>56</v>
       </c>
       <c r="M47" t="n">
-        <v>62.5</v>
+        <v>60.71428571428572</v>
       </c>
       <c r="N47" t="n">
-        <v>16.5910468481701</v>
+        <v>16.77237180782337</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>8.663774403470704</v>
+        <v>8.710935378884299</v>
       </c>
       <c r="Q47" t="n">
         <v>51</v>
@@ -5771,7 +5775,7 @@
         <v>66.65983471422588</v>
       </c>
       <c r="Y47" t="n">
-        <v>15.5575114715695</v>
+        <v>15.58633618047956</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -5816,7 +5820,7 @@
         <v>46280</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05571546052631579</v>
+        <v>0.05489817063440085</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5833,7 +5837,11 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %80.00: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H48" t="n">
         <v>5</v>
       </c>
@@ -5841,25 +5849,25 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>12.37197428387045</v>
+        <v>13.33760203446502</v>
       </c>
       <c r="K48" t="n">
-        <v>0.3703703703703765</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="M48" t="n">
-        <v>60</v>
+        <v>57.57575757575758</v>
       </c>
       <c r="N48" t="n">
-        <v>14.21858183766153</v>
+        <v>13.56240322866279</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>9.594095940959413</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5886,16 +5894,16 @@
         <v>19.37342145735985</v>
       </c>
       <c r="Y48" t="n">
-        <v>12.04742604047738</v>
+        <v>13.33760203446502</v>
       </c>
       <c r="Z48" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AA48" t="n">
-        <v>72.72727272727273</v>
+        <v>80</v>
       </c>
       <c r="AB48" t="n">
-        <v>11.05787043682041</v>
+        <v>15.35060929822096</v>
       </c>
       <c r="AC48" t="n">
         <v>6</v>
@@ -5935,7 +5943,7 @@
         <v>46280</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2754934210526316</v>
+        <v>0.2746964490765923</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5995,22 +6003,22 @@
         <v>22.46912765663718</v>
       </c>
       <c r="Y49" t="n">
-        <v>9.48294689981044</v>
+        <v>9.7448027161812</v>
       </c>
       <c r="Z49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA49" t="n">
-        <v>46.15384615384615</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB49" t="n">
-        <v>11.24788808776712</v>
+        <v>11.33486752390138</v>
       </c>
       <c r="AC49" t="n">
         <v>10</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.571221755990281</v>
+        <v>0.2827507905348581</v>
       </c>
       <c r="AE49" t="n">
         <v>44</v>
@@ -6044,7 +6052,7 @@
         <v>46280</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6949013157894737</v>
+        <v>0.6900309462541239</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6069,10 +6077,10 @@
         <v>10</v>
       </c>
       <c r="J50" t="n">
-        <v>10.17272609298356</v>
+        <v>10.53761880451027</v>
       </c>
       <c r="K50" t="n">
-        <v>0.2967359050445095</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>47</v>
@@ -6081,13 +6089,13 @@
         <v>42.5531914893617</v>
       </c>
       <c r="N50" t="n">
-        <v>13.51691102693656</v>
+        <v>13.85650259454351</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>3.692307692307706</v>
+        <v>4.000000000000004</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6114,16 +6122,16 @@
         <v>15.51990994893744</v>
       </c>
       <c r="Y50" t="n">
-        <v>9.906176318778769</v>
+        <v>10.53761880451027</v>
       </c>
       <c r="Z50" t="n">
         <v>23</v>
       </c>
       <c r="AA50" t="n">
-        <v>60.8695652173913</v>
+        <v>73.91304347826087</v>
       </c>
       <c r="AB50" t="n">
-        <v>11.36764529003039</v>
+        <v>11.08711829665501</v>
       </c>
       <c r="AC50" t="n">
         <v>5</v>
@@ -6163,7 +6171,7 @@
         <v>46280</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1332236842105263</v>
+        <v>0.1357033370190867</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6188,25 +6196,25 @@
         <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>31.71331988759807</v>
+        <v>32.23477001147905</v>
       </c>
       <c r="K51" t="n">
-        <v>0.1545595054095905</v>
+        <v>2.803735479081171</v>
       </c>
       <c r="L51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M51" t="n">
-        <v>66.66666666666667</v>
+        <v>40</v>
       </c>
       <c r="N51" t="n">
-        <v>13.94407786065021</v>
+        <v>15.99466623099526</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>3.839506172839502</v>
+        <v>1.163639157024843</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6272,7 +6280,7 @@
         <v>46280</v>
       </c>
       <c r="C52" t="n">
-        <v>4.498355263157895</v>
+        <v>4.498771364174014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6332,7 +6340,7 @@
         <v>16.62696858241317</v>
       </c>
       <c r="Y52" t="n">
-        <v>6.234734241617168</v>
+        <v>6.226060888785668</v>
       </c>
       <c r="Z52" t="n">
         <v>19</v>
@@ -6347,7 +6355,7 @@
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.88264358246647</v>
+        <v>1.891718667283948</v>
       </c>
       <c r="AE52" t="n">
         <v>37</v>
@@ -6381,7 +6389,7 @@
         <v>46280</v>
       </c>
       <c r="C53" t="n">
-        <v>1.143092105263158</v>
+        <v>1.133945357215648</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6410,7 +6418,7 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>33.48885718675011</v>
+        <v>34.02106335182087</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -6422,7 +6430,7 @@
         <v>83.33333333333333</v>
       </c>
       <c r="N53" t="n">
-        <v>20.66638207787801</v>
+        <v>20.70738015029972</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
@@ -6486,16 +6494,16 @@
         <v>46280</v>
       </c>
       <c r="C54" t="n">
-        <v>0.06969572574013158</v>
+        <v>0.0688797230805423</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6514,22 +6522,22 @@
         <v>29.5817777621179</v>
       </c>
       <c r="K54" t="n">
-        <v>11.03808549480698</v>
+        <v>9.738043460417313</v>
       </c>
       <c r="L54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M54" t="n">
-        <v>42.85714285714285</v>
+        <v>62.5</v>
       </c>
       <c r="N54" t="n">
-        <v>13.33340404686651</v>
+        <v>21.17993563330084</v>
       </c>
       <c r="O54" t="n">
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>0.2387107800743582</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6556,16 +6564,16 @@
         <v>14.75410024187049</v>
       </c>
       <c r="Y54" t="n">
-        <v>3.238241369355122</v>
+        <v>4.371135123608372</v>
       </c>
       <c r="Z54" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AA54" t="n">
-        <v>44.11764705882353</v>
+        <v>45.71428571428572</v>
       </c>
       <c r="AB54" t="n">
-        <v>14.91104764783718</v>
+        <v>14.64885266050554</v>
       </c>
       <c r="AC54" t="n">
         <v>2</v>
@@ -6605,7 +6613,7 @@
         <v>46280</v>
       </c>
       <c r="C55" t="n">
-        <v>0.907483552631579</v>
+        <v>0.9046889271679863</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6665,16 +6673,16 @@
         <v>23.0932342837701</v>
       </c>
       <c r="Y55" t="n">
-        <v>9.208365413701912</v>
+        <v>9.487961240161013</v>
       </c>
       <c r="Z55" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AA55" t="n">
-        <v>47.05882352941177</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="AB55" t="n">
-        <v>8.623281246978431</v>
+        <v>9.513128641038493</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6714,7 +6722,7 @@
         <v>46280</v>
       </c>
       <c r="C56" t="n">
-        <v>0.6270559210526315</v>
+        <v>0.6271139154232632</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6739,7 +6747,7 @@
         <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>56.38408153574323</v>
+        <v>56.38004764074929</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -6803,11 +6811,11 @@
         <v>46280</v>
       </c>
       <c r="C57" t="n">
-        <v>1.448396381578947</v>
+        <v>1.432081480941461</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6817,7 +6825,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -6863,22 +6871,22 @@
         <v>20.62560129901716</v>
       </c>
       <c r="Y57" t="n">
-        <v>4.891055048453063</v>
+        <v>5.962372960010565</v>
       </c>
       <c r="Z57" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="AA57" t="n">
-        <v>51.11111111111111</v>
+        <v>45.23809523809524</v>
       </c>
       <c r="AB57" t="n">
-        <v>13.25929480822831</v>
+        <v>12.04617014951667</v>
       </c>
       <c r="AC57" t="n">
         <v>5</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.1145475345168068</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
         <v>44</v>
@@ -6912,7 +6920,7 @@
         <v>46280</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6977796052631579</v>
+        <v>0.6896197147620016</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6929,11 +6937,7 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6944,22 +6948,22 @@
         <v>18.04392839464337</v>
       </c>
       <c r="K58" t="n">
-        <v>6.952774846621756</v>
+        <v>5.702060545199705</v>
       </c>
       <c r="L58" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M58" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="N58" t="n">
-        <v>20.38572926033141</v>
+        <v>17.77087948887664</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>0.979147249690393</v>
+        <v>2.173977917694114</v>
       </c>
       <c r="Q58" t="n">
         <v>25</v>
@@ -6986,16 +6990,16 @@
         <v>20.50322102897642</v>
       </c>
       <c r="Y58" t="n">
-        <v>11.24488297212928</v>
+        <v>12.28279240786235</v>
       </c>
       <c r="Z58" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AA58" t="n">
-        <v>41.66666666666666</v>
+        <v>60</v>
       </c>
       <c r="AB58" t="n">
-        <v>7.686577986255374</v>
+        <v>14.24828351986104</v>
       </c>
       <c r="AC58" t="n">
         <v>6</v>
@@ -7035,7 +7039,7 @@
         <v>46280</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7417763157894737</v>
+        <v>0.7389663364316726</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7063,22 +7067,22 @@
         <v>11.95882015364728</v>
       </c>
       <c r="K59" t="n">
-        <v>1.257688446337202</v>
+        <v>0.8741064846375712</v>
       </c>
       <c r="L59" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="M59" t="n">
-        <v>60.31746031746032</v>
+        <v>60</v>
       </c>
       <c r="N59" t="n">
-        <v>14.14795892831695</v>
+        <v>13.64284710714925</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>6.658567519281244</v>
+        <v>7.064145362663177</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7144,7 +7148,7 @@
         <v>46280</v>
       </c>
       <c r="C60" t="n">
-        <v>10.6188322368421</v>
+        <v>10.54785044629948</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7163,7 +7167,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -7173,25 +7177,25 @@
         <v>10</v>
       </c>
       <c r="J60" t="n">
-        <v>24.5994329337105</v>
+        <v>25.03087531338165</v>
       </c>
       <c r="K60" t="n">
-        <v>0.09689922480620172</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M60" t="n">
-        <v>76.47058823529412</v>
+        <v>81.25</v>
       </c>
       <c r="N60" t="n">
-        <v>14.08422267691191</v>
+        <v>15.26238110577849</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>7.895450145208138</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q60" t="n">
         <v>46</v>
@@ -7257,7 +7261,7 @@
         <v>46280</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7129934210526315</v>
+        <v>0.7130593698781665</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7282,19 +7286,19 @@
         <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>14.17319122629571</v>
+        <v>14.16525261554432</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M61" t="n">
-        <v>69.76744186046511</v>
+        <v>70.45454545454545</v>
       </c>
       <c r="N61" t="n">
-        <v>19.03584639174238</v>
+        <v>18.65065625275459</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
@@ -7327,7 +7331,7 @@
         <v>49.99145178651283</v>
       </c>
       <c r="Y61" t="n">
-        <v>14.17319122629571</v>
+        <v>14.16525261554432</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -7372,7 +7376,7 @@
         <v>46280</v>
       </c>
       <c r="C62" t="n">
-        <v>8.825041118421053</v>
+        <v>8.784735093920958</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7432,16 +7436,16 @@
         <v>11.69351808836483</v>
       </c>
       <c r="Y62" t="n">
-        <v>5.567300407154785</v>
+        <v>5.998596607628515</v>
       </c>
       <c r="Z62" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="AA62" t="n">
-        <v>40.54054054054054</v>
+        <v>40</v>
       </c>
       <c r="AB62" t="n">
-        <v>18.54763979228057</v>
+        <v>21.91742148575884</v>
       </c>
       <c r="AC62" t="n">
         <v>5</v>
@@ -7481,7 +7485,7 @@
         <v>46280</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1071134868421053</v>
+        <v>0.1067121724155269</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7509,22 +7513,22 @@
         <v>14.68172212919103</v>
       </c>
       <c r="K63" t="n">
-        <v>2.317463559011634</v>
+        <v>1.934118049237843</v>
       </c>
       <c r="L63" t="n">
         <v>18</v>
       </c>
       <c r="M63" t="n">
-        <v>55.55555555555556</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N63" t="n">
-        <v>16.20841068106916</v>
+        <v>15.2462149963301</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>2.621777698233507</v>
+        <v>3.007709302278183</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7551,7 +7555,7 @@
         <v>24.85614965143601</v>
       </c>
       <c r="Y63" t="n">
-        <v>12.70450213035874</v>
+        <v>13.0315659175928</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -7596,7 +7600,7 @@
         <v>46280</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1441200657894737</v>
+        <v>0.1437221680187675</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7621,25 +7625,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>13.14393740971537</v>
+        <v>13.50818167534201</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1428571428571335</v>
+        <v>0.2869437676123798</v>
       </c>
       <c r="L64" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M64" t="n">
-        <v>63.41463414634146</v>
+        <v>62.5</v>
       </c>
       <c r="N64" t="n">
-        <v>15.97763719216314</v>
+        <v>17.41415728199853</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.850213980028539</v>
+        <v>4.69957110599446</v>
       </c>
       <c r="Q64" t="n">
         <v>55</v>
@@ -7705,7 +7709,7 @@
         <v>46280</v>
       </c>
       <c r="C65" t="n">
-        <v>6.275699013157895</v>
+        <v>6.250578042251542</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7730,25 +7734,25 @@
         <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>11.51147888476662</v>
+        <v>11.50329486812964</v>
       </c>
       <c r="K65" t="n">
-        <v>0.5766062602965416</v>
+        <v>0.1647446457990087</v>
       </c>
       <c r="L65" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M65" t="n">
-        <v>53.33333333333334</v>
+        <v>53.44827586206897</v>
       </c>
       <c r="N65" t="n">
-        <v>12.68036029155311</v>
+        <v>12.73252334824025</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>9.369369369369384</v>
+        <v>9.819078947368443</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7775,13 +7779,13 @@
         <v>24.47056390537039</v>
       </c>
       <c r="Y65" t="n">
-        <v>11.00124853237235</v>
+        <v>11.35750128471635</v>
       </c>
       <c r="Z65" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AA65" t="n">
-        <v>23.07692307692308</v>
+        <v>30</v>
       </c>
       <c r="AB65" t="n">
         <v>16.35606305772624</v>
@@ -7824,7 +7828,7 @@
         <v>46280</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4342105263157895</v>
+        <v>0.4309608882074359</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7849,25 +7853,25 @@
         <v>10</v>
       </c>
       <c r="J66" t="n">
-        <v>10.41390434728438</v>
+        <v>11.00008781442038</v>
       </c>
       <c r="K66" t="n">
-        <v>0.09478672985783199</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M66" t="n">
-        <v>56.36363636363637</v>
+        <v>58.92857142857143</v>
       </c>
       <c r="N66" t="n">
-        <v>13.79370518048586</v>
+        <v>13.55629084880372</v>
       </c>
       <c r="O66" t="n">
         <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>5.899621212121198</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="Q66" t="n">
         <v>35</v>
@@ -7894,16 +7898,16 @@
         <v>14.59585890675015</v>
       </c>
       <c r="Y66" t="n">
-        <v>10.32898861680787</v>
+        <v>11.00008781442038</v>
       </c>
       <c r="Z66" t="n">
         <v>23</v>
       </c>
       <c r="AA66" t="n">
-        <v>43.47826086956522</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="AB66" t="n">
-        <v>8.938200137593423</v>
+        <v>9.008984565776595</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
@@ -7943,7 +7947,7 @@
         <v>46280</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02672697368421053</v>
+        <v>0.02652383363316239</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7971,22 +7975,22 @@
         <v>11.46300958938384</v>
       </c>
       <c r="K67" t="n">
-        <v>1.12380649221091</v>
+        <v>0.3552086159334111</v>
       </c>
       <c r="L67" t="n">
         <v>5</v>
       </c>
       <c r="M67" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N67" t="n">
-        <v>7.356482034271883</v>
+        <v>6.688022667323312</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>2.844229867880443</v>
+        <v>3.631890595749221</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -8032,7 +8036,7 @@
         <v>46280</v>
       </c>
       <c r="C68" t="n">
-        <v>1.561472039473684</v>
+        <v>1.561616392252439</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8057,10 +8061,10 @@
         <v>10</v>
       </c>
       <c r="J68" t="n">
-        <v>72.03677607916677</v>
+        <v>72.03418985118029</v>
       </c>
       <c r="K68" t="n">
-        <v>4.015800048051688e-06</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -8071,7 +8075,7 @@
         <v>2</v>
       </c>
       <c r="P68" t="n">
-        <v>1.999995903884111</v>
+        <v>2.000000000000002</v>
       </c>
       <c r="Q68" t="n">
         <v>5</v>
@@ -8137,7 +8141,7 @@
         <v>46280</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5172697368421053</v>
+        <v>0.5173175743600726</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8162,10 +8166,10 @@
         <v>10</v>
       </c>
       <c r="J69" t="n">
-        <v>22.28047342576105</v>
+        <v>22.27328735462569</v>
       </c>
       <c r="K69" t="n">
-        <v>19.46818613485281</v>
+        <v>19.46818842916143</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -8195,7 +8199,7 @@
         <v>45.36848923911108</v>
       </c>
       <c r="Y69" t="n">
-        <v>7.149891329161806</v>
+        <v>7.141304477031374</v>
       </c>
       <c r="Z69" t="n">
         <v>1</v>
@@ -8232,7 +8236,7 @@
         <v>46280</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4666940789473684</v>
+        <v>0.4663260261050794</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8257,25 +8261,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>15.78759245299801</v>
+        <v>16.07740375784346</v>
       </c>
       <c r="K70" t="n">
-        <v>0.2650176678445249</v>
+        <v>0.5319186295175804</v>
       </c>
       <c r="L70" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M70" t="n">
-        <v>50</v>
+        <v>45.23809523809524</v>
       </c>
       <c r="N70" t="n">
-        <v>12.5088238905108</v>
+        <v>12.74002158184292</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>7.714537444933933</v>
+        <v>7.428567436382028</v>
       </c>
       <c r="Q70" t="n">
         <v>31</v>
@@ -8302,7 +8306,7 @@
         <v>44.93251946562029</v>
       </c>
       <c r="Y70" t="n">
-        <v>15.56441469448122</v>
+        <v>15.6310038340566</v>
       </c>
       <c r="Z70" t="n">
         <v>2</v>
@@ -8347,7 +8351,7 @@
         <v>46280</v>
       </c>
       <c r="C71" t="n">
-        <v>3.090049342105263</v>
+        <v>3.08416679716359</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8446,7 +8450,7 @@
         <v>46280</v>
       </c>
       <c r="C72" t="n">
-        <v>0.05962171052631578</v>
+        <v>0.0590103891240077</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8471,25 +8475,25 @@
         <v>10</v>
       </c>
       <c r="J72" t="n">
-        <v>29.83805545001131</v>
+        <v>31.04136939799487</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>0.7017540597106686</v>
       </c>
       <c r="L72" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M72" t="n">
-        <v>73.33333333333333</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N72" t="n">
-        <v>24.04684220636248</v>
+        <v>29.26676915318224</v>
       </c>
       <c r="O72" t="n">
         <v>10</v>
       </c>
       <c r="P72" t="n">
-        <v>10.00000000000001</v>
+        <v>9.23344983124721</v>
       </c>
       <c r="Q72" t="n">
         <v>15</v>
@@ -8555,7 +8559,7 @@
         <v>46280</v>
       </c>
       <c r="C73" t="n">
-        <v>0.05941611842105263</v>
+        <v>0.05818794526159744</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8580,25 +8584,25 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>21.73901626025376</v>
+        <v>23.62755013046467</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>0.354609583270471</v>
       </c>
       <c r="L73" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="M73" t="n">
-        <v>66.66666666666667</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N73" t="n">
-        <v>15.80723394580061</v>
+        <v>15.31709316854396</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>10.00000000000001</v>
+        <v>9.611307798199498</v>
       </c>
       <c r="Q73" t="n">
         <v>14</v>
@@ -8664,7 +8668,7 @@
         <v>46280</v>
       </c>
       <c r="C74" t="n">
-        <v>5.473889802631579</v>
+        <v>5.448694674989008</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8689,25 +8693,25 @@
         <v>10</v>
       </c>
       <c r="J74" t="n">
-        <v>10.76052373623427</v>
+        <v>10.75227026618852</v>
       </c>
       <c r="K74" t="n">
-        <v>3.398058252427183</v>
+        <v>2.9126213592233</v>
       </c>
       <c r="L74" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M74" t="n">
-        <v>71.1864406779661</v>
+        <v>72.1311475409836</v>
       </c>
       <c r="N74" t="n">
-        <v>15.62851530762487</v>
+        <v>15.21060899058343</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>4.45070422535212</v>
+        <v>4.943396226415109</v>
       </c>
       <c r="Q74" t="n">
         <v>28</v>
@@ -8734,7 +8738,7 @@
         <v>24.51464461150628</v>
       </c>
       <c r="Y74" t="n">
-        <v>7.728114348630588</v>
+        <v>8.15282182733965</v>
       </c>
       <c r="Z74" t="n">
         <v>17</v>
@@ -8743,13 +8747,13 @@
         <v>47.05882352941177</v>
       </c>
       <c r="AB74" t="n">
-        <v>16.67758587258489</v>
+        <v>17.30403255000777</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>2.462164542679091</v>
+        <v>2.011143085079758</v>
       </c>
       <c r="AE74" t="n">
         <v>37</v>
@@ -8783,7 +8787,7 @@
         <v>46280</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1151315789473684</v>
+        <v>0.1100019470427235</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8811,22 +8815,22 @@
         <v>26.70952832272112</v>
       </c>
       <c r="K75" t="n">
-        <v>5.992351060013146</v>
+        <v>1.269913040689907</v>
       </c>
       <c r="L75" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M75" t="n">
-        <v>25</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N75" t="n">
-        <v>13.26881515701794</v>
+        <v>21.98601318710739</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>0.007216501861084801</v>
+        <v>4.670772213865293</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8892,7 +8896,7 @@
         <v>46280</v>
       </c>
       <c r="C76" t="n">
-        <v>1.868832236842105</v>
+        <v>1.856668474603872</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8952,16 +8956,16 @@
         <v>12.60650925728801</v>
       </c>
       <c r="Y76" t="n">
-        <v>7.95792380827568</v>
+        <v>8.557002692210858</v>
       </c>
       <c r="Z76" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA76" t="n">
-        <v>44.44444444444444</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB76" t="n">
-        <v>10.20955438135788</v>
+        <v>8.760967594621983</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
@@ -9001,7 +9005,7 @@
         <v>46280</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4621710526315789</v>
+        <v>0.4597464764394641</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9026,25 +9030,25 @@
         <v>10</v>
       </c>
       <c r="J77" t="n">
-        <v>19.35990842897727</v>
+        <v>19.56827561321563</v>
       </c>
       <c r="K77" t="n">
-        <v>0.2676181980374448</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M77" t="n">
-        <v>63.33333333333334</v>
+        <v>61.29032258064516</v>
       </c>
       <c r="N77" t="n">
-        <v>10.85781526974314</v>
+        <v>11.36657707028799</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>7.711743772242019</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q77" t="n">
         <v>27</v>
@@ -9110,7 +9114,7 @@
         <v>46280</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05797697368421052</v>
+        <v>0.05757111251899807</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9167,25 +9171,25 @@
         <v>64.1025641025641</v>
       </c>
       <c r="X78" t="n">
-        <v>36.6270136023539</v>
+        <v>36.63964711299532</v>
       </c>
       <c r="Y78" t="n">
-        <v>7.843137254901967</v>
+        <v>8.496731865948991</v>
       </c>
       <c r="Z78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA78" t="n">
-        <v>60</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB78" t="n">
-        <v>15.45343681464298</v>
+        <v>15.16176426931412</v>
       </c>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>2.34042553191488</v>
+        <v>1.642857315051016</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9219,7 +9223,7 @@
         <v>46280</v>
       </c>
       <c r="C79" t="n">
-        <v>0.873766447368421</v>
+        <v>0.8717911794567426</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9244,25 +9248,25 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>12.33325414452273</v>
+        <v>12.53153482177238</v>
       </c>
       <c r="K79" t="n">
-        <v>0.04708097928436406</v>
+        <v>0.04719315595806961</v>
       </c>
       <c r="L79" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M79" t="n">
-        <v>57.4074074074074</v>
+        <v>61.81818181818182</v>
       </c>
       <c r="N79" t="n">
-        <v>11.22714428107698</v>
+        <v>11.49206354608452</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>4.950588235294129</v>
+        <v>4.950470560749531</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9289,7 +9293,7 @@
         <v>25.65117214954458</v>
       </c>
       <c r="Y79" t="n">
-        <v>12.29197978206723</v>
+        <v>12.49025569258669</v>
       </c>
       <c r="Z79" t="n">
         <v>4</v>
@@ -9338,7 +9342,7 @@
         <v>46280</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1307565789473684</v>
+        <v>0.1299462312158816</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9366,22 +9370,22 @@
         <v>10.48668504530712</v>
       </c>
       <c r="K80" t="n">
-        <v>2.288332013519701</v>
+        <v>1.654412722635756</v>
       </c>
       <c r="L80" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="M80" t="n">
-        <v>45.90163934426229</v>
+        <v>44.77611940298507</v>
       </c>
       <c r="N80" t="n">
-        <v>16.33556957547754</v>
+        <v>16.55039854440819</v>
       </c>
       <c r="O80" t="n">
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>7.53914726604501</v>
+        <v>8.209763898922118</v>
       </c>
       <c r="Q80" t="n">
         <v>39</v>
@@ -9408,16 +9412,16 @@
         <v>16.92042739318289</v>
       </c>
       <c r="Y80" t="n">
-        <v>8.438323202836173</v>
+        <v>9.005765374243669</v>
       </c>
       <c r="Z80" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA80" t="n">
-        <v>57.14285714285715</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB80" t="n">
-        <v>12.13601999736521</v>
+        <v>12.67571770684304</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
@@ -9457,7 +9461,7 @@
         <v>46280</v>
       </c>
       <c r="C81" t="n">
-        <v>1.195518092105263</v>
+        <v>1.198712812871137</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9517,22 +9521,22 @@
         <v>23.79225853623819</v>
       </c>
       <c r="Y81" t="n">
-        <v>6.118612910778253</v>
+        <v>5.867738566974056</v>
       </c>
       <c r="Z81" t="n">
         <v>11</v>
       </c>
       <c r="AA81" t="n">
-        <v>45.45454545454545</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AB81" t="n">
-        <v>9.995501637126122</v>
+        <v>10.57225322578887</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>4.134352089976046</v>
+        <v>4.389846127266361</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9566,7 +9570,7 @@
         <v>46280</v>
       </c>
       <c r="C82" t="n">
-        <v>4.710115256990131</v>
+        <v>4.626250195745384</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9591,25 +9595,25 @@
         <v>10</v>
       </c>
       <c r="J82" t="n">
-        <v>16.59648495929817</v>
+        <v>17.25076623026857</v>
       </c>
       <c r="K82" t="n">
-        <v>1.014110678602131</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M82" t="n">
-        <v>44.44444444444444</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="N82" t="n">
-        <v>8.08000535343627</v>
+        <v>8.812299547508161</v>
       </c>
       <c r="O82" t="n">
         <v>4</v>
       </c>
       <c r="P82" t="n">
-        <v>2.955913091090911</v>
+        <v>4.000000000000004</v>
       </c>
       <c r="Q82" t="n">
         <v>8</v>
@@ -9675,7 +9679,7 @@
         <v>46280</v>
       </c>
       <c r="C83" t="n">
-        <v>5.293996710526316</v>
+        <v>5.23794327718283</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9700,25 +9704,25 @@
         <v>10</v>
       </c>
       <c r="J83" t="n">
-        <v>13.24118714424848</v>
+        <v>13.99279494326494</v>
       </c>
       <c r="K83" t="n">
-        <v>0.1945525291828787</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M83" t="n">
-        <v>63.63636363636363</v>
+        <v>64.0625</v>
       </c>
       <c r="N83" t="n">
-        <v>12.21524903691012</v>
+        <v>12.43521313256074</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>9.78640776699029</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q83" t="n">
         <v>41</v>
@@ -9784,7 +9788,7 @@
         <v>46280</v>
       </c>
       <c r="C84" t="n">
-        <v>2.047697368421053</v>
+        <v>2.043774562378907</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9812,16 +9816,16 @@
         <v>14.20091622675307</v>
       </c>
       <c r="K84" t="n">
-        <v>5.606674697037572</v>
+        <v>5.404362329994816</v>
       </c>
       <c r="L84" t="n">
         <v>39</v>
       </c>
       <c r="M84" t="n">
-        <v>64.1025641025641</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N84" t="n">
-        <v>10.36085951392524</v>
+        <v>10.55881180753439</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9854,16 +9858,16 @@
         <v>11.86663135768809</v>
       </c>
       <c r="Y84" t="n">
-        <v>5.595910580908258</v>
+        <v>5.776761979209399</v>
       </c>
       <c r="Z84" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA84" t="n">
-        <v>39.47368421052632</v>
+        <v>40.54054054054054</v>
       </c>
       <c r="AB84" t="n">
-        <v>11.35542624868099</v>
+        <v>9.908696585285828</v>
       </c>
       <c r="AC84" t="n">
         <v>2</v>
@@ -9903,7 +9907,7 @@
         <v>46280</v>
       </c>
       <c r="C85" t="n">
-        <v>5.915912828947368</v>
+        <v>5.865057192606093</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9928,25 +9932,25 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>11.72218885232484</v>
+        <v>12.40495804625523</v>
       </c>
       <c r="K85" t="n">
-        <v>0.08695652173913437</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="M85" t="n">
-        <v>65.625</v>
+        <v>62.90322580645162</v>
       </c>
       <c r="N85" t="n">
-        <v>12.4522586403547</v>
+        <v>12.59505726590093</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>7.906168549087744</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q85" t="n">
         <v>32</v>
@@ -10012,7 +10016,7 @@
         <v>46280</v>
       </c>
       <c r="C86" t="n">
-        <v>4.745065789473684</v>
+        <v>4.729055755650838</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10044,16 +10048,16 @@
         <v>18.73514495170452</v>
       </c>
       <c r="K86" t="n">
-        <v>13.82024464345724</v>
+        <v>13.4362107760009</v>
       </c>
       <c r="L86" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M86" t="n">
         <v>100</v>
       </c>
       <c r="N86" t="n">
-        <v>11.59313326334698</v>
+        <v>16.42415905518173</v>
       </c>
       <c r="O86" t="n">
         <v>8</v>
@@ -10086,7 +10090,7 @@
         <v>44.99483923332605</v>
       </c>
       <c r="Y86" t="n">
-        <v>7.504143174879174</v>
+        <v>7.816227740603932</v>
       </c>
       <c r="Z86" t="n">
         <v>6</v>
@@ -10095,7 +10099,7 @@
         <v>50</v>
       </c>
       <c r="AB86" t="n">
-        <v>15.39519764941737</v>
+        <v>15.39823644341957</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
@@ -10135,7 +10139,7 @@
         <v>46280</v>
       </c>
       <c r="C87" t="n">
-        <v>5.869654605263158</v>
+        <v>5.844496080625002</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10195,16 +10199,16 @@
         <v>15.88967756874082</v>
       </c>
       <c r="Y87" t="n">
-        <v>4.847762063781225</v>
+        <v>5.255603765462869</v>
       </c>
       <c r="Z87" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="AA87" t="n">
-        <v>45.94594594594594</v>
+        <v>45.71428571428572</v>
       </c>
       <c r="AB87" t="n">
-        <v>12.72306316839886</v>
+        <v>12.87424470283853</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
@@ -10244,7 +10248,7 @@
         <v>46280</v>
       </c>
       <c r="C88" t="n">
-        <v>1.036184210526316</v>
+        <v>1.037308115072466</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10272,16 +10276,16 @@
         <v>16.8583060727446</v>
       </c>
       <c r="K88" t="n">
-        <v>4.226960166529592</v>
+        <v>4.340010677406481</v>
       </c>
       <c r="L88" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M88" t="n">
-        <v>62.7906976744186</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N88" t="n">
-        <v>16.59722997270471</v>
+        <v>15.20170034249627</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
@@ -10314,13 +10318,13 @@
         <v>22.33299319731812</v>
       </c>
       <c r="Y88" t="n">
-        <v>13.34393978866156</v>
+        <v>13.24994767892509</v>
       </c>
       <c r="Z88" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA88" t="n">
-        <v>41.66666666666666</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB88" t="n">
         <v>13.4099918685533</v>
@@ -10363,7 +10367,7 @@
         <v>46280</v>
       </c>
       <c r="C89" t="n">
-        <v>2.131990131578947</v>
+        <v>2.130131169782485</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10423,22 +10427,22 @@
         <v>21.41032003314154</v>
       </c>
       <c r="Y89" t="n">
-        <v>8.949009138888897</v>
+        <v>9.028399897332772</v>
       </c>
       <c r="Z89" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA89" t="n">
-        <v>29.62962962962963</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="AB89" t="n">
-        <v>15.33714453561096</v>
+        <v>15.1641247567547</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>1.154288219349831</v>
+        <v>1.06802573723086</v>
       </c>
       <c r="AE89" t="n">
         <v>22</v>
@@ -10472,7 +10476,7 @@
         <v>46280</v>
       </c>
       <c r="C90" t="n">
-        <v>2.730263157894737</v>
+        <v>2.716123018124851</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10497,25 +10501,25 @@
         <v>10</v>
       </c>
       <c r="J90" t="n">
-        <v>12.8208334231333</v>
+        <v>13.32304178579999</v>
       </c>
       <c r="K90" t="n">
-        <v>0.2450864393636287</v>
+        <v>0.3037275317112176</v>
       </c>
       <c r="L90" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M90" t="n">
-        <v>65.11627906976744</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N90" t="n">
-        <v>14.40993195910616</v>
+        <v>15.08047556655999</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>7.735953786949135</v>
+        <v>7.672967553330068</v>
       </c>
       <c r="Q90" t="n">
         <v>43</v>
@@ -10542,16 +10546,16 @@
         <v>20.63086277737274</v>
       </c>
       <c r="Y90" t="n">
-        <v>12.60716910790318</v>
+        <v>13.05978000005364</v>
       </c>
       <c r="Z90" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA90" t="n">
-        <v>33.33333333333334</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="AB90" t="n">
-        <v>10.84558309221278</v>
+        <v>12.23365874636309</v>
       </c>
       <c r="AC90" t="n">
         <v>2</v>
@@ -10591,7 +10595,7 @@
         <v>46280</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2302631578947368</v>
+        <v>0.2309012780895359</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10690,7 +10694,7 @@
         <v>46280</v>
       </c>
       <c r="C92" t="n">
-        <v>1.131784539473684</v>
+        <v>1.127776960704318</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10750,13 +10754,13 @@
         <v>21.60407460332612</v>
       </c>
       <c r="Y92" t="n">
-        <v>9.620728165289627</v>
+        <v>9.940755554216485</v>
       </c>
       <c r="Z92" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA92" t="n">
-        <v>63.63636363636363</v>
+        <v>70</v>
       </c>
       <c r="AB92" t="n">
         <v>12.84590382592824</v>
@@ -10799,7 +10803,7 @@
         <v>46280</v>
       </c>
       <c r="C93" t="n">
-        <v>0.04111842105263158</v>
+        <v>0.0411222239621812</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10859,13 +10863,13 @@
         <v>11.4419372600254</v>
       </c>
       <c r="Y93" t="n">
-        <v>6.444785629766447</v>
+        <v>6.436133011085177</v>
       </c>
       <c r="Z93" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AA93" t="n">
-        <v>46.875</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="AB93" t="n">
         <v>13.0285354938626</v>
@@ -10908,7 +10912,7 @@
         <v>46280</v>
       </c>
       <c r="C94" t="n">
-        <v>8.490953947368421</v>
+        <v>8.481458692199871</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10968,7 +10972,7 @@
         <v>40.43377921558155</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.670581863033861</v>
+        <v>2.779423303741879</v>
       </c>
       <c r="Z94" t="n">
         <v>12</v>
@@ -10983,7 +10987,7 @@
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>3.420772671507033</v>
+        <v>3.312649241240395</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -11017,7 +11021,7 @@
         <v>46280</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1215049311266447</v>
+        <v>0.1192544533969368</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11042,25 +11046,25 @@
         <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>19.52215329413863</v>
+        <v>20.47777775450879</v>
       </c>
       <c r="K95" t="n">
-        <v>1.025640188472488</v>
+        <v>0.3460204026532576</v>
       </c>
       <c r="L95" t="n">
         <v>25</v>
       </c>
       <c r="M95" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="N95" t="n">
-        <v>17.7408548510624</v>
+        <v>19.7967444898251</v>
       </c>
       <c r="O95" t="n">
         <v>10</v>
       </c>
       <c r="P95" t="n">
-        <v>8.883249633246603</v>
+        <v>9.62069004690842</v>
       </c>
       <c r="Q95" t="n">
         <v>21</v>
@@ -11126,7 +11130,7 @@
         <v>46280</v>
       </c>
       <c r="C96" t="n">
-        <v>0.125</v>
+        <v>0.1246003373717423</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11225,7 +11229,7 @@
         <v>46280</v>
       </c>
       <c r="C97" t="n">
-        <v>1.834909539473684</v>
+        <v>1.833023164572728</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11253,7 +11257,7 @@
         <v>12.87370897365936</v>
       </c>
       <c r="K97" t="n">
-        <v>0.2985204237275774</v>
+        <v>0.1954087403120308</v>
       </c>
       <c r="L97" t="n">
         <v>59</v>
@@ -11262,13 +11266,13 @@
         <v>64.40677966101696</v>
       </c>
       <c r="N97" t="n">
-        <v>13.22134882184171</v>
+        <v>13.34630568285463</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>3.690462791110893</v>
+        <v>3.797171255170761</v>
       </c>
       <c r="Q97" t="n">
         <v>50</v>
@@ -11295,16 +11299,16 @@
         <v>16.31583297271808</v>
       </c>
       <c r="Y97" t="n">
-        <v>12.61361920050942</v>
+        <v>12.70345658588421</v>
       </c>
       <c r="Z97" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA97" t="n">
-        <v>25</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB97" t="n">
-        <v>10.94377446737897</v>
+        <v>10.28208228437988</v>
       </c>
       <c r="AC97" t="n">
         <v>6</v>
@@ -11344,7 +11348,7 @@
         <v>46280</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6994243421052632</v>
+        <v>0.6966104959197392</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11369,19 +11373,19 @@
         <v>10</v>
       </c>
       <c r="J98" t="n">
-        <v>10.74975128742972</v>
+        <v>11.10881295683203</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M98" t="n">
-        <v>47.54098360655738</v>
+        <v>43.54838709677419</v>
       </c>
       <c r="N98" t="n">
-        <v>14.63776826571144</v>
+        <v>15.56156652968006</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
@@ -11414,7 +11418,7 @@
         <v>30.85778357900837</v>
       </c>
       <c r="Y98" t="n">
-        <v>10.74975128742972</v>
+        <v>11.10881295683203</v>
       </c>
       <c r="Z98" t="n">
         <v>4</v>
@@ -11463,21 +11467,21 @@
         <v>46280</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5427631578947368</v>
+        <v>0.5271868986528846</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -11491,22 +11495,22 @@
         <v>12.51634982914205</v>
       </c>
       <c r="K99" t="n">
-        <v>5.870831941848298</v>
+        <v>2.832542587660747</v>
       </c>
       <c r="L99" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="M99" t="n">
-        <v>54.71698113207547</v>
+        <v>50.66666666666666</v>
       </c>
       <c r="N99" t="n">
-        <v>15.86138284247839</v>
+        <v>16.512046349427</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>1.135299568562198</v>
       </c>
       <c r="Q99" t="n">
         <v>34</v>
@@ -11533,22 +11537,22 @@
         <v>33.04241514445872</v>
       </c>
       <c r="Y99" t="n">
-        <v>7.380331751016489</v>
+        <v>10.03833818081236</v>
       </c>
       <c r="Z99" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AA99" t="n">
-        <v>57.14285714285715</v>
+        <v>25</v>
       </c>
       <c r="AB99" t="n">
-        <v>12.01251736130811</v>
+        <v>5.33028826325086</v>
       </c>
       <c r="AC99" t="n">
         <v>10</v>
       </c>
       <c r="AD99" t="n">
-        <v>2.828414632128917</v>
+        <v>0</v>
       </c>
       <c r="AE99" t="n">
         <v>38</v>
@@ -11582,11 +11586,11 @@
         <v>46280</v>
       </c>
       <c r="C100" t="n">
-        <v>337.8016020123355</v>
+        <v>332.7182675828155</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -11596,7 +11600,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -11642,22 +11646,22 @@
         <v>16.86980163304483</v>
       </c>
       <c r="Y100" t="n">
-        <v>7.27951831018302</v>
+        <v>8.674802447640461</v>
       </c>
       <c r="Z100" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AA100" t="n">
-        <v>38.46153846153846</v>
+        <v>47.61904761904762</v>
       </c>
       <c r="AB100" t="n">
-        <v>12.00550094398526</v>
+        <v>9.536647754051197</v>
       </c>
       <c r="AC100" t="n">
         <v>8</v>
       </c>
       <c r="AD100" t="n">
-        <v>0.7770469659845403</v>
+        <v>0</v>
       </c>
       <c r="AE100" t="n">
         <v>39</v>
@@ -11691,7 +11695,7 @@
         <v>46280</v>
       </c>
       <c r="C101" t="n">
-        <v>342.887541118421</v>
+        <v>342.2413554204456</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11751,22 +11755,22 @@
         <v>12.90626814318425</v>
       </c>
       <c r="Y101" t="n">
-        <v>5.130744218198801</v>
+        <v>5.309529239269606</v>
       </c>
       <c r="Z101" t="n">
         <v>30</v>
       </c>
       <c r="AA101" t="n">
-        <v>50</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="AB101" t="n">
-        <v>12.00209105524237</v>
+        <v>12.09939166269356</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>0.9162671032230785</v>
+        <v>0.7291871665472294</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11800,7 +11804,7 @@
         <v>46280</v>
       </c>
       <c r="C102" t="n">
-        <v>404.2588484913651</v>
+        <v>399.9646292279465</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11899,7 +11903,7 @@
         <v>46280</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7179276315789473</v>
+        <v>0.7130593698781665</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11959,16 +11963,16 @@
         <v>14.28440963201156</v>
       </c>
       <c r="Y103" t="n">
-        <v>9.153078502357959</v>
+        <v>9.769110772334988</v>
       </c>
       <c r="Z103" t="n">
         <v>24</v>
       </c>
       <c r="AA103" t="n">
-        <v>33.33333333333334</v>
+        <v>37.5</v>
       </c>
       <c r="AB103" t="n">
-        <v>9.067180759022456</v>
+        <v>8.759393545287127</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
@@ -12008,7 +12012,7 @@
         <v>46280</v>
       </c>
       <c r="C104" t="n">
-        <v>0.05324835526315789</v>
+        <v>0.05181400178112607</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12065,25 +12069,25 @@
         <v>63.23529411764706</v>
       </c>
       <c r="X104" t="n">
-        <v>17.05083756364998</v>
+        <v>17.06166321640041</v>
       </c>
       <c r="Y104" t="n">
-        <v>2.264154631541349</v>
+        <v>4.905664720540948</v>
       </c>
       <c r="Z104" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="AA104" t="n">
-        <v>52.17391304347826</v>
+        <v>51.51515151515152</v>
       </c>
       <c r="AB104" t="n">
-        <v>11.92479434760016</v>
+        <v>13.47460625950747</v>
       </c>
       <c r="AC104" t="n">
         <v>5</v>
       </c>
       <c r="AD104" t="n">
-        <v>2.799224131274125</v>
+        <v>0.0992017865016126</v>
       </c>
       <c r="AE104" t="n">
         <v>42</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -436,15 +436,15 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C2" t="n">
-        <v>0.390249895942988</v>
+        <v>0.3793904268656104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,22 +698,22 @@
         <v>21.42119502374098</v>
       </c>
       <c r="K2" t="n">
-        <v>6.21198483563965</v>
+        <v>3.256427955393781</v>
       </c>
       <c r="L2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M2" t="n">
-        <v>57.89473684210526</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N2" t="n">
-        <v>14.87705714843537</v>
+        <v>12.4604140391455</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>3.566466788302858</v>
+        <v>6.530898054617396</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -740,22 +740,22 @@
         <v>11.79582706077868</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.994678577853662</v>
+        <v>7.638388059638757</v>
       </c>
       <c r="Z2" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>43.24324324324324</v>
+        <v>44</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.41027054599596</v>
+        <v>10.79335241570344</v>
       </c>
       <c r="AC2" t="n">
         <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.268464278864659</v>
+        <v>2.556919363735399</v>
       </c>
       <c r="AE2" t="n">
         <v>46</v>
@@ -764,10 +764,10 @@
         <v>52.17391304347826</v>
       </c>
       <c r="AG2" t="n">
-        <v>36.43599742569995</v>
+        <v>36.38659031107544</v>
       </c>
       <c r="AH2" t="n">
-        <v>15.73791561777831</v>
+        <v>15.78732273240281</v>
       </c>
       <c r="AI2" t="n">
         <v>38.13741307280403</v>
@@ -789,7 +789,7 @@
         <v>46280</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6933207210869315</v>
+        <v>0.6933463895361193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>16.83732632822199</v>
       </c>
       <c r="K3" t="n">
-        <v>10.28152800922233</v>
+        <v>10.28561090435578</v>
       </c>
       <c r="L3" t="n">
         <v>23</v>
@@ -859,7 +859,7 @@
         <v>17.17248092970491</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.881033554812798</v>
+        <v>5.877549037713681</v>
       </c>
       <c r="Z3" t="n">
         <v>29</v>
@@ -874,7 +874,7 @@
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.376340498369147</v>
+        <v>4.379880591866581</v>
       </c>
       <c r="AE3" t="n">
         <v>35</v>
@@ -905,44 +905,58 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C4" t="n">
-        <v>1.430025400996243</v>
+        <v>1.363627021805701</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %83.33: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>13.38716819771938</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
       <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="M4" t="n">
+        <v>56.06060606060606</v>
+      </c>
+      <c r="N4" t="n">
+        <v>13.41787111993552</v>
+      </c>
       <c r="O4" t="n">
         <v>5</v>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>5.000000000000004</v>
+      </c>
       <c r="Q4" t="n">
         <v>53</v>
       </c>
@@ -968,22 +982,22 @@
         <v>16.66966699739723</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.169774763289585</v>
+        <v>13.38716819771938</v>
       </c>
       <c r="Z4" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AA4" t="n">
-        <v>55</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.21826983405953</v>
+        <v>13.82559167632864</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.9140407111694171</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
         <v>40</v>
@@ -992,10 +1006,10 @@
         <v>60</v>
       </c>
       <c r="AG4" t="n">
-        <v>39.23594521098629</v>
+        <v>38.95309468037216</v>
       </c>
       <c r="AH4" t="n">
-        <v>20.76405478901371</v>
+        <v>21.04690531962784</v>
       </c>
       <c r="AI4" t="n">
         <v>44.59589366034619</v>
@@ -1014,27 +1028,31 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2245273444783983</v>
+        <v>0.2168238896767166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>BAND</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.76: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>5</v>
       </c>
@@ -1042,25 +1060,25 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>19.13427219952423</v>
+        <v>19.52862999556227</v>
       </c>
       <c r="K5" t="n">
-        <v>3.14563481775072</v>
+        <v>0.09487666034158071</v>
       </c>
       <c r="L5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M5" t="n">
-        <v>56.25</v>
+        <v>75.75757575757575</v>
       </c>
       <c r="N5" t="n">
-        <v>11.58387228227014</v>
+        <v>12.51951311963504</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.902369668246418</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1083,27 +1101,17 @@
       <c r="W5" t="n">
         <v>58.73015873015873</v>
       </c>
-      <c r="X5" t="n">
-        <v>10.55954734904581</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>6.705809411365204</v>
-      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>10.09581628013362</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
-      <c r="AD5" t="n">
-        <v>3.530970758039997</v>
-      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
         <v>45</v>
       </c>
@@ -1133,19 +1141,19 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C6" t="n">
-        <v>1.530774724280803</v>
+        <v>1.450973138500113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1155,7 +1163,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1165,25 +1173,25 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>29.57085786530786</v>
+        <v>30.97082607325095</v>
       </c>
       <c r="K6" t="n">
-        <v>3.40277354166667</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>88.88888888888889</v>
+        <v>80</v>
       </c>
       <c r="N6" t="n">
-        <v>10.7351556932087</v>
+        <v>9.721465223321935</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.000000000000002</v>
       </c>
       <c r="Q6" t="n">
         <v>35</v>
@@ -1224,10 +1232,10 @@
         <v>46.93877551020408</v>
       </c>
       <c r="AG6" t="n">
-        <v>39.03634327378123</v>
+        <v>38.69119903261306</v>
       </c>
       <c r="AH6" t="n">
-        <v>7.902432236422854</v>
+        <v>8.247576477591025</v>
       </c>
       <c r="AI6" t="n">
         <v>33.70350369317515</v>
@@ -1246,10 +1254,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C7" t="n">
-        <v>2.241161205938875</v>
+        <v>2.143576463818156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,7 +1266,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1273,17 +1281,27 @@
       <c r="I7" t="n">
         <v>10</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>13.35749781503482</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="M7" t="n">
+        <v>69.84126984126983</v>
+      </c>
+      <c r="N7" t="n">
+        <v>13.24469505007974</v>
+      </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>8.000000000000007</v>
+      </c>
       <c r="Q7" t="n">
         <v>51</v>
       </c>
@@ -1309,16 +1327,16 @@
         <v>18.9234494530097</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.413161620302768</v>
+        <v>13.35749781503482</v>
       </c>
       <c r="Z7" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AA7" t="n">
-        <v>60</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB7" t="n">
-        <v>13.12838423287637</v>
+        <v>9.880102520564243</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1355,10 +1373,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3417256983970598</v>
+        <v>0.3273937973981134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,22 +1404,22 @@
         <v>20.70550141590351</v>
       </c>
       <c r="K8" t="n">
-        <v>4.94445973866855</v>
+        <v>0.5431120659075805</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M8" t="n">
-        <v>60</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N8" t="n">
-        <v>17.75833754694722</v>
+        <v>16.69895675356172</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.911578437718698</v>
+        <v>7.416607444182066</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1428,7 +1446,7 @@
         <v>26.93179943319606</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.78481685843375</v>
+        <v>20.27484342649236</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1470,10 +1488,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5506265930407735</v>
+        <v>0.5355858355426762</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,19 +1516,19 @@
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>14.50739888386581</v>
+        <v>16.06270635736976</v>
       </c>
       <c r="K9" t="n">
-        <v>3.560759240414257</v>
+        <v>2.598425196850385</v>
       </c>
       <c r="L9" t="n">
         <v>40</v>
       </c>
       <c r="M9" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="N9" t="n">
-        <v>14.79931305816791</v>
+        <v>13.04469594544534</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1579,10 +1597,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C10" t="n">
-        <v>1.875173349964071</v>
+        <v>1.800357605277761</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,25 +1625,25 @@
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>13.50421550203786</v>
+        <v>15.6530335535529</v>
       </c>
       <c r="K10" t="n">
-        <v>2.268532435167647</v>
+        <v>0.6896551724137945</v>
       </c>
       <c r="L10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="M10" t="n">
-        <v>54.16666666666666</v>
+        <v>62.22222222222222</v>
       </c>
       <c r="N10" t="n">
-        <v>10.37055776876159</v>
+        <v>13.14065766444598</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>7.559967255552102</v>
+        <v>9.246575342465757</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1688,10 +1706,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C11" t="n">
-        <v>7.751539216871155</v>
+        <v>7.552870090634442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,25 +1734,25 @@
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>11.80661525537724</v>
+        <v>12.26450975949309</v>
       </c>
       <c r="K11" t="n">
-        <v>2.376103190767132</v>
+        <v>0.2728512960436635</v>
       </c>
       <c r="L11" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M11" t="n">
-        <v>56.89655172413793</v>
+        <v>58.92857142857143</v>
       </c>
       <c r="N11" t="n">
-        <v>12.94286804690456</v>
+        <v>13.05241126211816</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6094164456233564</v>
+        <v>2.719727891156465</v>
       </c>
       <c r="Q11" t="n">
         <v>49</v>
@@ -1743,10 +1761,10 @@
         <v>61.22448979591837</v>
       </c>
       <c r="S11" t="n">
-        <v>51.82512290948034</v>
+        <v>51.68597634176234</v>
       </c>
       <c r="T11" t="n">
-        <v>9.399366886438024</v>
+        <v>9.538513454156025</v>
       </c>
       <c r="U11" t="n">
         <v>47.24599944352045</v>
@@ -1758,19 +1776,19 @@
         <v>61.19402985074627</v>
       </c>
       <c r="X11" t="n">
-        <v>19.5857262818246</v>
+        <v>18.41457411414329</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.71104942641472</v>
+        <v>12.02512233728161</v>
       </c>
       <c r="Z11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AA11" t="n">
-        <v>52.94117647058823</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.07010377658062</v>
+        <v>8.086116495739128</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
@@ -1807,10 +1825,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C12" t="n">
-        <v>5.597762736851915</v>
+        <v>5.281871056579732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,11 +1845,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %90.91: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>5</v>
       </c>
@@ -1839,25 +1853,25 @@
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>25.10153053951003</v>
+        <v>28.93665041580083</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5540166204986097</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M12" t="n">
-        <v>90.90909090909091</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N12" t="n">
-        <v>12.16767143682461</v>
+        <v>17.53376341251548</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>4.421487603305785</v>
+        <v>5.000000000000004</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1920,10 +1934,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1667506111758667</v>
+        <v>0.1584561316973919</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1951,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1948,10 +1962,10 @@
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>47.07727092024744</v>
+        <v>48.07246356960044</v>
       </c>
       <c r="K13" t="n">
-        <v>3.255661298620893</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1962,7 +1976,7 @@
         <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>2.657809428426727</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1983,23 +1997,17 @@
         <v>0</v>
       </c>
       <c r="W13" t="inlineStr"/>
-      <c r="X13" t="n">
-        <v>20.61663781635479</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>14.39351720628036</v>
-      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
         <v>10</v>
       </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="n">
         <v>0</v>
       </c>
@@ -2019,10 +2027,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C14" t="n">
-        <v>8.548282306138416</v>
+        <v>8.359537168341658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,16 +2090,16 @@
         <v>16.11612055393703</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.056234604998478</v>
+        <v>7.152582554288167</v>
       </c>
       <c r="Z14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA14" t="n">
-        <v>37.5</v>
+        <v>31.81818181818182</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.48704530520519</v>
+        <v>11.55046017766063</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2100,19 +2108,19 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AF14" t="n">
-        <v>54.05405405405406</v>
+        <v>52.77777777777778</v>
       </c>
       <c r="AG14" t="n">
-        <v>27.02641559546062</v>
+        <v>25.4351606341429</v>
       </c>
       <c r="AH14" t="n">
-        <v>27.02763845859343</v>
+        <v>27.34261714363488</v>
       </c>
       <c r="AI14" t="n">
-        <v>38.38404689217949</v>
+        <v>37.00593802298759</v>
       </c>
       <c r="AJ14" t="n">
         <v>43</v>
@@ -2128,10 +2136,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C15" t="n">
-        <v>13.31332000775616</v>
+        <v>12.72170499619788</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,25 +2164,25 @@
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>15.78089892450823</v>
+        <v>19.84843937415058</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.4055150040551458</v>
       </c>
       <c r="L15" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="M15" t="n">
-        <v>62.90322580645162</v>
+        <v>60</v>
       </c>
       <c r="N15" t="n">
-        <v>17.20761445256585</v>
+        <v>15.31727702763958</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>8.000000000000007</v>
+        <v>7.563812600969322</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2198,13 +2206,13 @@
         <v>80.43478260869566</v>
       </c>
       <c r="X15" t="n">
-        <v>36.34743205418309</v>
+        <v>33.58229315482664</v>
       </c>
       <c r="Y15" t="n">
-        <v>15.78089892450823</v>
+        <v>19.52341276982841</v>
       </c>
       <c r="Z15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
@@ -2243,10 +2251,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C16" t="n">
-        <v>34.15200700059148</v>
+        <v>32.98600406930144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2271,25 +2279,25 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>16.99349200873118</v>
+        <v>18.74345692981887</v>
       </c>
       <c r="K16" t="n">
-        <v>1.668818082111545</v>
+        <v>0.3124999999999822</v>
       </c>
       <c r="L16" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="M16" t="n">
-        <v>71.7948717948718</v>
+        <v>67.79661016949153</v>
       </c>
       <c r="N16" t="n">
-        <v>17.52899811987269</v>
+        <v>17.58563857375307</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>8.194431758968502</v>
+        <v>9.657320872274177</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2352,10 +2360,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3906611276407214</v>
+        <v>0.3664426495673798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,10 +2388,10 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>51.07603542299748</v>
+        <v>52.97039750800809</v>
       </c>
       <c r="K17" t="n">
-        <v>2.481116813234752</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2394,7 +2402,7 @@
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>5.385268387368436</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2429,25 +2437,25 @@
       </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AF17" t="n">
-        <v>55.81395348837209</v>
+        <v>56.81818181818182</v>
       </c>
       <c r="AG17" t="n">
-        <v>39.16582607612455</v>
+        <v>39.0143300289399</v>
       </c>
       <c r="AH17" t="n">
-        <v>16.64812741224755</v>
+        <v>17.80385178924193</v>
       </c>
       <c r="AI17" t="n">
-        <v>41.1076144528241</v>
+        <v>42.22414699362943</v>
       </c>
       <c r="AJ17" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AK17" t="n">
-        <v>51.72413793103448</v>
+        <v>52.27272727272727</v>
       </c>
     </row>
     <row r="18">
@@ -2457,10 +2465,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0719638919338171</v>
+        <v>0.06720512978605341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,25 +2493,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>34.12837610820287</v>
+        <v>39.43997479113801</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2865326639354349</v>
+        <v>1.869158878504673</v>
       </c>
       <c r="L18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>57.14285714285715</v>
+        <v>25</v>
       </c>
       <c r="N18" t="n">
-        <v>10.50046967635557</v>
+        <v>16.62570916182737</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>9.685714600000006</v>
+        <v>7.981651376146792</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2553,10 +2561,10 @@
         <v>47.57507548555804</v>
       </c>
       <c r="AJ18" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AK18" t="n">
-        <v>51.16279069767442</v>
+        <v>51.76470588235294</v>
       </c>
     </row>
     <row r="19">
@@ -2566,14 +2574,14 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02611261180476282</v>
+        <v>0.02692315596933638</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2583,7 +2591,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2594,25 +2602,25 @@
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>11.89842102923254</v>
+        <v>16.09778596067288</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>8.264462809917351</v>
       </c>
       <c r="L19" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="M19" t="n">
-        <v>64.1025641025641</v>
+        <v>72.22222222222223</v>
       </c>
       <c r="N19" t="n">
-        <v>18.55195987404595</v>
+        <v>20.75148384367104</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>10.00000000000001</v>
+        <v>1.60305343511451</v>
       </c>
       <c r="Q19" t="n">
         <v>14</v>
@@ -2639,22 +2647,22 @@
         <v>20.26411217973316</v>
       </c>
       <c r="Y19" t="n">
-        <v>11.89842102923254</v>
+        <v>9.163718684695432</v>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AA19" t="n">
-        <v>62.5</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="AB19" t="n">
-        <v>16.74028578011673</v>
+        <v>12.33289022678148</v>
       </c>
       <c r="AC19" t="n">
         <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>0.9206467979481991</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -2685,10 +2693,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C20" t="n">
-        <v>1.603766734525067</v>
+        <v>1.587644121092546</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2724,7 @@
         <v>18.49305897009618</v>
       </c>
       <c r="K20" t="n">
-        <v>2.894646591966832</v>
+        <v>1.860250145422881</v>
       </c>
       <c r="L20" t="n">
         <v>32</v>
@@ -2725,13 +2733,13 @@
         <v>50</v>
       </c>
       <c r="N20" t="n">
-        <v>13.64855649154946</v>
+        <v>16.75491869608562</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>6.905464611982937</v>
+        <v>7.991095489119893</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
@@ -2794,10 +2802,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C21" t="n">
-        <v>0.884539046884629</v>
+        <v>0.8549643422323613</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2822,25 +2830,25 @@
         <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>10.37112050264447</v>
+        <v>13.40952649813111</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.04810004810005264</v>
       </c>
       <c r="L21" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M21" t="n">
-        <v>51.92307692307692</v>
+        <v>59.01639344262295</v>
       </c>
       <c r="N21" t="n">
-        <v>13.76434079846411</v>
+        <v>16.51602481853923</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>8.000000000000007</v>
+        <v>7.94807692307693</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2881,10 +2889,10 @@
         <v>62.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>36.12413792090061</v>
+        <v>36.06163792090061</v>
       </c>
       <c r="AH21" t="n">
-        <v>26.37586207909939</v>
+        <v>26.43836207909939</v>
       </c>
       <c r="AI21" t="n">
         <v>47.0324391373011</v>
@@ -2903,10 +2911,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2919677862248752</v>
+        <v>0.2776578909509423</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2933,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %82.35: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %90.91: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2935,25 +2943,25 @@
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>20.87642808379643</v>
+        <v>24.38411614496318</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5665716758018968</v>
+        <v>0.07407407407407085</v>
       </c>
       <c r="L22" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="M22" t="n">
-        <v>82.35294117647059</v>
+        <v>90.90909090909091</v>
       </c>
       <c r="N22" t="n">
-        <v>11.83226844871437</v>
+        <v>15.06277595817252</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>9.380282301567178</v>
+        <v>9.918578830495939</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -3008,10 +3016,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5942161284402957</v>
+        <v>0.5643586739831885</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,10 +3044,10 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>41.90517182209699</v>
+        <v>44.4397528000775</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6968601209193848</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -3050,7 +3058,7 @@
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.273360533698178</v>
+        <v>5.000000000000004</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3113,10 +3121,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1562644490001774</v>
+        <v>0.1483856382432127</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3130,14 +3138,10 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>BAND</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>5</v>
       </c>
@@ -3145,68 +3149,58 @@
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>23.31817459365587</v>
+        <v>24.76563460590212</v>
       </c>
       <c r="K24" t="n">
-        <v>3.321840846143909</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>14</v>
       </c>
       <c r="M24" t="n">
-        <v>50</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N24" t="n">
-        <v>11.15287235946911</v>
+        <v>15.88001405187546</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>6.463453514925765</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
         <v>100</v>
       </c>
       <c r="S24" t="n">
-        <v>89.24242424242424</v>
+        <v>89.72727272727272</v>
       </c>
       <c r="T24" t="n">
-        <v>10.75757575757576</v>
+        <v>10.27272727272728</v>
       </c>
       <c r="U24" t="n">
-        <v>51.01091635454027</v>
+        <v>56.55175352168251</v>
       </c>
       <c r="V24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W24" t="n">
-        <v>75</v>
-      </c>
-      <c r="X24" t="n">
-        <v>17.82705440547527</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>12.31059677467193</v>
-      </c>
+        <v>75.86206896551724</v>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>13.3342061142625</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
         <v>2</v>
       </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="n">
         <v>4</v>
       </c>
@@ -3236,10 +3230,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C25" t="n">
-        <v>3.295946313280214</v>
+        <v>3.224613108083113</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3264,25 +3258,25 @@
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>20.95143919294578</v>
+        <v>22.50725922230536</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3283142231063074</v>
+        <v>0.1276324186343381</v>
       </c>
       <c r="L25" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="M25" t="n">
-        <v>57.14285714285715</v>
+        <v>61.29032258064516</v>
       </c>
       <c r="N25" t="n">
-        <v>16.56288562475776</v>
+        <v>18.62626097258521</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>7.646580964007521</v>
+        <v>7.862332695984708</v>
       </c>
       <c r="Q25" t="n">
         <v>44</v>
@@ -3345,24 +3339,24 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4387741327606402</v>
+        <v>0.421316562878928</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>AL_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>BAND</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3372,17 +3366,27 @@
       <c r="I26" t="n">
         <v>10</v>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>11.71805290443946</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.1955034213098727</v>
+      </c>
       <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="M26" t="n">
+        <v>51.72413793103448</v>
+      </c>
+      <c r="N26" t="n">
+        <v>12.76750693175828</v>
+      </c>
       <c r="O26" t="n">
         <v>6</v>
       </c>
-      <c r="P26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>5.793170731707331</v>
+      </c>
       <c r="Q26" t="n">
         <v>32</v>
       </c>
@@ -3404,27 +3408,17 @@
       <c r="W26" t="n">
         <v>67.24137931034483</v>
       </c>
-      <c r="X26" t="n">
-        <v>11.40992936035117</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>7.880277973579187</v>
-      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>10.44719082438257</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
         <v>10</v>
       </c>
-      <c r="AD26" t="n">
-        <v>2.301051262196441</v>
-      </c>
+      <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="n">
         <v>36</v>
       </c>
@@ -3454,14 +3448,14 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C27" t="n">
-        <v>55.92622458856643</v>
+        <v>50.31136321598126</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3471,7 +3465,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3504,25 +3498,21 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>69.66261412600872</v>
+        <v>67.77922038036249</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>12.41502683363148</v>
       </c>
       <c r="Z27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>5.328374938728119</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
         <v>6</v>
       </c>
       <c r="AD27" t="n">
-        <v>6.000000000000005</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3543,10 +3533,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C28" t="n">
-        <v>1.378622621043516</v>
+        <v>1.320467764144933</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3571,25 +3561,25 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>17.97667209838105</v>
+        <v>21.20163810401038</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2991841205348011</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="M28" t="n">
-        <v>64.28571428571429</v>
+        <v>65.625</v>
       </c>
       <c r="N28" t="n">
-        <v>15.98024047712831</v>
+        <v>14.52939308169286</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>1.695742487218288</v>
+        <v>2.000000000000002</v>
       </c>
       <c r="Q28" t="n">
         <v>39</v>
@@ -3652,14 +3642,14 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4110166237729453</v>
+        <v>0.390488521692665</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3669,14 +3659,10 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %100.00: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>VERİ_YETERSİZ</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>5</v>
       </c>
@@ -3687,7 +3673,7 @@
         <v>27.65210909859499</v>
       </c>
       <c r="K29" t="n">
-        <v>24.116485252706</v>
+        <v>17.91752459820786</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3725,22 +3711,18 @@
         <v>31.20488584758381</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.402543166808704</v>
+        <v>10.12718479463592</v>
       </c>
       <c r="Z29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>16.19254517444829</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.860021597936015</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3771,10 +3753,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4071100015991487</v>
+        <v>0.3869946770248885</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3799,25 +3781,25 @@
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>12.45555475167782</v>
+        <v>16.57045248083407</v>
       </c>
       <c r="K30" t="n">
-        <v>0.2531607088607446</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="M30" t="n">
-        <v>44.06779661016949</v>
+        <v>57.4468085106383</v>
       </c>
       <c r="N30" t="n">
-        <v>13.85493445963043</v>
+        <v>13.53057890927115</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>4.734852504974163</v>
+        <v>5.000000000000004</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3844,17 +3826,13 @@
         <v>26.71344279693404</v>
       </c>
       <c r="Y30" t="n">
-        <v>12.23392661351896</v>
+        <v>16.57045248083407</v>
       </c>
       <c r="Z30" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>11.98915066855684</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
         <v>8</v>
       </c>
@@ -3868,10 +3846,10 @@
         <v>58.53658536585366</v>
       </c>
       <c r="AG30" t="n">
-        <v>40.08867490531909</v>
+        <v>39.87848699958872</v>
       </c>
       <c r="AH30" t="n">
-        <v>18.44791046053457</v>
+        <v>18.65809836626494</v>
       </c>
       <c r="AI30" t="n">
         <v>43.36710313403013</v>
@@ -3890,10 +3868,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2611261182532393</v>
+        <v>0.2585445054154593</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3950,25 +3928,21 @@
         <v>88.88888888888889</v>
       </c>
       <c r="X31" t="n">
-        <v>50.78678362361622</v>
+        <v>56.50346662163857</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.5481648197215527</v>
+        <v>5.128205128205121</v>
       </c>
       <c r="Z31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>10.17739856018577</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
         <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>9.503932394153313</v>
+        <v>5.135135135135139</v>
       </c>
       <c r="AE31" t="n">
         <v>10</v>
@@ -3999,24 +3973,24 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C32" t="n">
-        <v>2.319293494178411</v>
+        <v>2.217563762665187</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -4026,17 +4000,27 @@
       <c r="I32" t="n">
         <v>10</v>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="J32" t="n">
+        <v>10.3445718561754</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.09276437847867136</v>
+      </c>
       <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="M32" t="n">
+        <v>59.52380952380953</v>
+      </c>
+      <c r="N32" t="n">
+        <v>9.844195670989331</v>
+      </c>
       <c r="O32" t="n">
         <v>3</v>
       </c>
-      <c r="P32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>2.904541241890635</v>
+      </c>
       <c r="Q32" t="n">
         <v>34</v>
       </c>
@@ -4062,22 +4046,22 @@
         <v>13.38656892008534</v>
       </c>
       <c r="Y32" t="n">
-        <v>6.144686157604474</v>
+        <v>10.26140355548538</v>
       </c>
       <c r="Z32" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="AA32" t="n">
-        <v>36.36363636363637</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="AB32" t="n">
-        <v>10.89590835038585</v>
+        <v>12.42255677564395</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.976780819795687</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>26</v>
@@ -4108,14 +4092,14 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C33" t="n">
-        <v>1.764143470688965</v>
+        <v>1.708901083091847</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4125,7 +4109,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -4171,22 +4155,22 @@
         <v>15.09663082780621</v>
       </c>
       <c r="Y33" t="n">
-        <v>6.46652328847731</v>
+        <v>9.395430522867954</v>
       </c>
       <c r="Z33" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="AA33" t="n">
-        <v>26.47058823529412</v>
+        <v>36.8421052631579</v>
       </c>
       <c r="AB33" t="n">
-        <v>11.22884089524853</v>
+        <v>13.12165164905662</v>
       </c>
       <c r="AC33" t="n">
         <v>8</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.639495040104466</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>29</v>
@@ -4217,24 +4201,24 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7866681098538582</v>
+        <v>0.7505600427482172</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4245,25 +4229,25 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>15.41713612942789</v>
+        <v>15.64008867377167</v>
       </c>
       <c r="K34" t="n">
-        <v>4.649166266424887</v>
+        <v>0.1096491228070207</v>
       </c>
       <c r="L34" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="M34" t="n">
-        <v>59.45945945945946</v>
+        <v>60.41666666666666</v>
       </c>
       <c r="N34" t="n">
-        <v>12.81533291737637</v>
+        <v>12.46911694790377</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>3.886089813800653</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4286,27 +4270,17 @@
       <c r="W34" t="n">
         <v>49.12280701754386</v>
       </c>
-      <c r="X34" t="n">
-        <v>10.81830054752258</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>5.56689125407781</v>
-      </c>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>43.47826086956522</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>9.7453229777544</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
         <v>2</v>
       </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="n">
         <v>33</v>
       </c>
@@ -4314,10 +4288,10 @@
         <v>57.57575757575758</v>
       </c>
       <c r="AG34" t="n">
-        <v>22.73879956671873</v>
+        <v>22.84478538126069</v>
       </c>
       <c r="AH34" t="n">
-        <v>34.83695800903885</v>
+        <v>34.73097219449689</v>
       </c>
       <c r="AI34" t="n">
         <v>40.80726333731245</v>
@@ -4336,10 +4310,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C35" t="n">
-        <v>1.437221758936734</v>
+        <v>1.293750128450172</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4353,7 +4327,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4364,10 +4338,10 @@
         <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>38.83766461406507</v>
+        <v>42.89164722419473</v>
       </c>
       <c r="K35" t="n">
-        <v>3.726315497423016</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>2</v>
@@ -4378,7 +4352,7 @@
         <v>6</v>
       </c>
       <c r="P35" t="n">
-        <v>2.192003535142906</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="Q35" t="n">
         <v>7</v>
@@ -4401,27 +4375,17 @@
       <c r="W35" t="n">
         <v>88.23529411764706</v>
       </c>
-      <c r="X35" t="n">
-        <v>13.94161507705984</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>8.965380710750958</v>
-      </c>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>58.33333333333334</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>12.53765928712615</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="n">
         <v>2</v>
       </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="n">
         <v>7</v>
       </c>
@@ -4451,10 +4415,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07710416992908974</v>
+        <v>0.07439833939618144</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4479,25 +4443,25 @@
         <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>11.87370670137952</v>
+        <v>14.73897609331452</v>
       </c>
       <c r="K36" t="n">
-        <v>0.2673794110497729</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="M36" t="n">
-        <v>67.56756756756756</v>
+        <v>57.57575757575758</v>
       </c>
       <c r="N36" t="n">
-        <v>15.78000569861148</v>
+        <v>19.03482611313982</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>1.728000272000019</v>
+        <v>2.000000000000002</v>
       </c>
       <c r="Q36" t="n">
         <v>10</v>
@@ -4560,10 +4524,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C37" t="n">
-        <v>0.05592622520539978</v>
+        <v>0.05322975111494749</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4588,19 +4552,19 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>23.52660551439098</v>
+        <v>27.2137581173432</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="M37" t="n">
-        <v>71.875</v>
+        <v>65.21739130434783</v>
       </c>
       <c r="N37" t="n">
-        <v>14.06513758430328</v>
+        <v>15.26345636643157</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
@@ -4609,19 +4573,19 @@
         <v>10.00000000000001</v>
       </c>
       <c r="Q37" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R37" t="n">
-        <v>53.33333333333334</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="S37" t="n">
-        <v>33.87164517839575</v>
+        <v>34.25292714815337</v>
       </c>
       <c r="T37" t="n">
-        <v>19.46168815493758</v>
+        <v>21.30262840740219</v>
       </c>
       <c r="U37" t="n">
-        <v>36.1422996198733</v>
+        <v>37.31302451322448</v>
       </c>
       <c r="V37" t="n">
         <v>102</v>
@@ -4669,24 +4633,24 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C38" t="n">
-        <v>1.611991210776004</v>
+        <v>1.569147296380788</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -4696,17 +4660,27 @@
       <c r="I38" t="n">
         <v>10</v>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>10.434951519417</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.0655307994757548</v>
+      </c>
       <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="M38" t="n">
+        <v>50</v>
+      </c>
+      <c r="N38" t="n">
+        <v>13.08051447380508</v>
+      </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>9.92796332678456</v>
+      </c>
       <c r="Q38" t="n">
         <v>42</v>
       </c>
@@ -4732,22 +4706,22 @@
         <v>12.11239445105858</v>
       </c>
       <c r="Y38" t="n">
-        <v>7.92917696075619</v>
+        <v>10.37625882709683</v>
       </c>
       <c r="Z38" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AA38" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="AB38" t="n">
-        <v>9.168989995399087</v>
+        <v>9.664004665137515</v>
       </c>
       <c r="AC38" t="n">
         <v>10</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.249163166882029</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>30</v>
@@ -4756,19 +4730,19 @@
         <v>56.66666666666666</v>
       </c>
       <c r="AG38" t="n">
-        <v>15.76102938302744</v>
+        <v>15.61483055261808</v>
       </c>
       <c r="AH38" t="n">
-        <v>40.90563728363922</v>
+        <v>41.05183611404858</v>
       </c>
       <c r="AI38" t="n">
         <v>39.19730700081361</v>
       </c>
       <c r="AJ38" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AK38" t="n">
-        <v>49.25373134328358</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39">
@@ -4778,24 +4752,24 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C39" t="n">
-        <v>2.62771017389477</v>
+        <v>2.50940255256181</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>AL_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>BAND</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4805,17 +4779,27 @@
       <c r="I39" t="n">
         <v>10</v>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>12.14112876653433</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.08196721311475308</v>
+      </c>
       <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="M39" t="n">
+        <v>57.37704918032787</v>
+      </c>
+      <c r="N39" t="n">
+        <v>15.00145829369855</v>
+      </c>
       <c r="O39" t="n">
         <v>5</v>
       </c>
-      <c r="P39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>4.91400491400491</v>
+      </c>
       <c r="Q39" t="n">
         <v>42</v>
       </c>
@@ -4837,27 +4821,17 @@
       <c r="W39" t="n">
         <v>67.69230769230769</v>
       </c>
-      <c r="X39" t="n">
-        <v>10.27889366548247</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>7.923547240463147</v>
-      </c>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>52.38095238095238</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>10.46527149923836</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="n">
         <v>40</v>
       </c>
@@ -4865,10 +4839,10 @@
         <v>60</v>
       </c>
       <c r="AG39" t="n">
-        <v>40.3540954710737</v>
+        <v>40.13132335827601</v>
       </c>
       <c r="AH39" t="n">
-        <v>19.6459045289263</v>
+        <v>19.86867664172399</v>
       </c>
       <c r="AI39" t="n">
         <v>44.59589366034619</v>
@@ -4887,10 +4861,10 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2282283508033282</v>
+        <v>0.2172349302258668</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4915,25 +4889,25 @@
         <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>15.29580504962521</v>
+        <v>17.64094015586989</v>
       </c>
       <c r="K40" t="n">
-        <v>2.248621949506435</v>
+        <v>0.09469696969697239</v>
       </c>
       <c r="L40" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="M40" t="n">
-        <v>67.56756756756756</v>
+        <v>69.56521739130434</v>
       </c>
       <c r="N40" t="n">
-        <v>14.07086531497261</v>
+        <v>12.63184100263632</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>0.7348539629850714</v>
+        <v>2.90255439924314</v>
       </c>
       <c r="Q40" t="n">
         <v>29</v>
@@ -4957,13 +4931,13 @@
         <v>77.77777777777777</v>
       </c>
       <c r="X40" t="n">
-        <v>37.29449902814472</v>
+        <v>33.58584893257701</v>
       </c>
       <c r="Y40" t="n">
-        <v>13.39112792981837</v>
+        <v>17.56294862192659</v>
       </c>
       <c r="Z40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr"/>
@@ -5002,10 +4976,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C41" t="n">
-        <v>1.219273924852227</v>
+        <v>1.097478266230964</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5019,14 +4993,10 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>BAND</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>5</v>
       </c>
@@ -5034,25 +5004,25 @@
         <v>10</v>
       </c>
       <c r="J41" t="n">
-        <v>40.38073481248902</v>
+        <v>45.65404823168654</v>
       </c>
       <c r="K41" t="n">
-        <v>1.271195695144378</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>100</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N41" t="n">
-        <v>19.30180353043365</v>
+        <v>24.12996021615659</v>
       </c>
       <c r="O41" t="n">
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>8.619236935971264</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q41" t="n">
         <v>11</v>
@@ -5075,27 +5045,17 @@
       <c r="W41" t="n">
         <v>81.81818181818181</v>
       </c>
-      <c r="X41" t="n">
-        <v>14.15095011586145</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>11.28308998536091</v>
-      </c>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>41.1764705882353</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>16.78789596480024</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
         <v>3</v>
       </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="n">
         <v>11</v>
       </c>
@@ -5125,31 +5085,27 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C42" t="n">
-        <v>3.376134524583685</v>
+        <v>3.206116283371355</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>AL_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>VERİ_YETERSİZ</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>5</v>
       </c>
@@ -5160,22 +5116,22 @@
         <v>17.9384880883827</v>
       </c>
       <c r="K42" t="n">
-        <v>6.379872763820527</v>
+        <v>1.022705051456807</v>
       </c>
       <c r="L42" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M42" t="n">
-        <v>33.33333333333334</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N42" t="n">
-        <v>11.6708708659834</v>
+        <v>9.114480682038684</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>0.9674012867160853</v>
       </c>
       <c r="Q42" t="n">
         <v>2</v>
@@ -5197,19 +5153,19 @@
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="n">
-        <v>23.05415424937474</v>
+        <v>16.97972319726071</v>
       </c>
       <c r="Y42" t="n">
-        <v>12.70306804035408</v>
+        <v>13.64084108738733</v>
       </c>
       <c r="Z42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA42" t="n">
-        <v>75</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB42" t="n">
-        <v>11.85948658534362</v>
+        <v>10.9831920577776</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
@@ -5244,10 +5200,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C43" t="n">
-        <v>6.024405810459545</v>
+        <v>5.857327825389975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5264,11 +5220,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %88.24: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>5</v>
       </c>
@@ -5276,46 +5228,46 @@
         <v>10</v>
       </c>
       <c r="J43" t="n">
-        <v>20.13868121382601</v>
+        <v>21.98720228799464</v>
       </c>
       <c r="K43" t="n">
-        <v>0.5599826666959462</v>
+        <v>0.08779631255486642</v>
       </c>
       <c r="L43" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M43" t="n">
-        <v>88.23529411764706</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N43" t="n">
-        <v>17.13412538541539</v>
+        <v>20.75042084683509</v>
       </c>
       <c r="O43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P43" t="n">
-        <v>3.420861104069517</v>
+        <v>9.903508771929847</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
       </c>
       <c r="R43" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="S43" t="n">
-        <v>41.00341098517301</v>
+        <v>53.21875624375624</v>
       </c>
       <c r="T43" t="n">
-        <v>8.996589014826988</v>
+        <v>6.781243756243761</v>
       </c>
       <c r="U43" t="n">
-        <v>23.6593090512564</v>
+        <v>31.26737697336582</v>
       </c>
       <c r="V43" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W43" t="n">
-        <v>65.21739130434783</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
@@ -5357,27 +5309,31 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C44" t="n">
-        <v>4.52961303214565</v>
+        <v>4.186447993094519</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>AL_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H44" t="n">
         <v>5</v>
       </c>
@@ -5385,21 +5341,25 @@
         <v>10</v>
       </c>
       <c r="J44" t="n">
-        <v>25.31049029846984</v>
+        <v>25.16666033456245</v>
       </c>
       <c r="K44" t="n">
-        <v>17.94016734337485</v>
+        <v>9.004979757844067</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M44" t="n">
+        <v>75</v>
+      </c>
+      <c r="N44" t="n">
+        <v>11.53225155181918</v>
+      </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>0.9128209044819702</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5426,22 +5386,18 @@
         <v>28.18267712431886</v>
       </c>
       <c r="Y44" t="n">
-        <v>7.99055692292201</v>
+        <v>14.96122393190085</v>
       </c>
       <c r="Z44" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>15.53705409348409</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
         <v>10</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.183953092069735</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5464,14 +5420,14 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0205611119810906</v>
+        <v>0.02014098690835851</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5481,7 +5437,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5492,25 +5448,25 @@
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>15.41404182570979</v>
+        <v>17.98787203625159</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1.030927835051543</v>
       </c>
       <c r="L45" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M45" t="n">
-        <v>59.09090909090909</v>
+        <v>63.76811594202898</v>
       </c>
       <c r="N45" t="n">
-        <v>13.18395349585476</v>
+        <v>15.08347746403951</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>10.00000000000001</v>
+        <v>8.87755102040817</v>
       </c>
       <c r="Q45" t="n">
         <v>38</v>
@@ -5533,27 +5489,17 @@
       <c r="W45" t="n">
         <v>61.85567010309278</v>
       </c>
-      <c r="X45" t="n">
-        <v>19.20467487893223</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>15.41404182570979</v>
-      </c>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>13.68813816694538</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
         <v>5</v>
       </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="n">
         <v>19</v>
       </c>
@@ -5583,14 +5529,14 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C46" t="n">
-        <v>9.478672623282765</v>
+        <v>8.529091394866104</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5600,7 +5546,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -5611,25 +5557,25 @@
         <v>10</v>
       </c>
       <c r="J46" t="n">
-        <v>12.68362764677318</v>
+        <v>21.30302176772584</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1629549158066235</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="M46" t="n">
-        <v>55.22388059701493</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N46" t="n">
-        <v>15.47338783323688</v>
+        <v>14.76602170324743</v>
       </c>
       <c r="O46" t="n">
         <v>8</v>
       </c>
       <c r="P46" t="n">
-        <v>7.824295010846005</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q46" t="n">
         <v>51</v>
@@ -5652,41 +5598,31 @@
       <c r="W46" t="n">
         <v>65.06024096385542</v>
       </c>
-      <c r="X46" t="n">
-        <v>26.79655122306823</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>12.54134132571958</v>
-      </c>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>10.37598329500288</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
         <v>3</v>
       </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AF46" t="n">
-        <v>58.97435897435897</v>
+        <v>60</v>
       </c>
       <c r="AG46" t="n">
-        <v>18.55492620092749</v>
+        <v>18.89764882663802</v>
       </c>
       <c r="AH46" t="n">
-        <v>40.41943277343148</v>
+        <v>41.10235117336198</v>
       </c>
       <c r="AI46" t="n">
-        <v>43.41862288289698</v>
+        <v>44.59589366034619</v>
       </c>
       <c r="AJ46" t="n">
         <v>81</v>
@@ -5702,10 +5638,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9474560777154897</v>
+        <v>0.9162093840557372</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5730,25 +5666,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>16.57556043110229</v>
+        <v>18.51674922473283</v>
       </c>
       <c r="K47" t="n">
-        <v>1.185772725276446</v>
+        <v>0.1797752808988751</v>
       </c>
       <c r="L47" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="M47" t="n">
-        <v>60.71428571428572</v>
+        <v>53.48837209302326</v>
       </c>
       <c r="N47" t="n">
-        <v>16.77237180782337</v>
+        <v>15.51365073068472</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>8.710935378884299</v>
+        <v>9.802602063705713</v>
       </c>
       <c r="Q47" t="n">
         <v>51</v>
@@ -5766,16 +5702,16 @@
         <v>61.13171816155626</v>
       </c>
       <c r="V47" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="W47" t="n">
-        <v>72.46376811594203</v>
+        <v>72.85714285714286</v>
       </c>
       <c r="X47" t="n">
         <v>66.65983471422588</v>
       </c>
       <c r="Y47" t="n">
-        <v>15.58633618047956</v>
+        <v>18.37026248176607</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -5795,10 +5731,10 @@
         <v>53.65853658536585</v>
       </c>
       <c r="AG47" t="n">
-        <v>31.00855848715134</v>
+        <v>30.66455361169589</v>
       </c>
       <c r="AH47" t="n">
-        <v>22.64997809821451</v>
+        <v>22.99398297366996</v>
       </c>
       <c r="AI47" t="n">
         <v>38.74647126766948</v>
@@ -5817,14 +5753,14 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05489817063440085</v>
+        <v>0.05179110919292189</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5834,14 +5770,10 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %80.00: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>BAND</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>5</v>
       </c>
@@ -5849,19 +5781,19 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>13.33760203446502</v>
+        <v>18.24241747791605</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="M48" t="n">
-        <v>57.57575757575758</v>
+        <v>53.65853658536585</v>
       </c>
       <c r="N48" t="n">
-        <v>13.56240322866279</v>
+        <v>13.9571117606342</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
@@ -5876,10 +5808,10 @@
         <v>63.82978723404256</v>
       </c>
       <c r="S48" t="n">
-        <v>48.36559371376292</v>
+        <v>48.3802672280696</v>
       </c>
       <c r="T48" t="n">
-        <v>15.46419352027964</v>
+        <v>15.44952000597296</v>
       </c>
       <c r="U48" t="n">
         <v>49.53589653479511</v>
@@ -5890,27 +5822,17 @@
       <c r="W48" t="n">
         <v>72.5</v>
       </c>
-      <c r="X48" t="n">
-        <v>19.37342145735985</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>13.33760203446502</v>
-      </c>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>15.35060929822096</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
         <v>6</v>
       </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="n">
         <v>51</v>
       </c>
@@ -5940,24 +5862,24 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2746964490765923</v>
+        <v>0.2616273095340856</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -5967,17 +5889,27 @@
       <c r="I49" t="n">
         <v>10</v>
       </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="J49" t="n">
+        <v>14.10636998322745</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.07861635220125507</v>
+      </c>
       <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="M49" t="n">
+        <v>51.72413793103448</v>
+      </c>
+      <c r="N49" t="n">
+        <v>16.40172216933395</v>
+      </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
-      <c r="P49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>4.917517674783989</v>
+      </c>
       <c r="Q49" t="n">
         <v>54</v>
       </c>
@@ -6003,22 +5935,22 @@
         <v>22.46912765663718</v>
       </c>
       <c r="Y49" t="n">
-        <v>9.7448027161812</v>
+        <v>14.03884354453501</v>
       </c>
       <c r="Z49" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AA49" t="n">
-        <v>42.85714285714285</v>
+        <v>40</v>
       </c>
       <c r="AB49" t="n">
-        <v>11.33486752390138</v>
+        <v>14.58639676596025</v>
       </c>
       <c r="AC49" t="n">
         <v>10</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.2827507905348581</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
         <v>44</v>
@@ -6027,10 +5959,10 @@
         <v>61.36363636363637</v>
       </c>
       <c r="AG49" t="n">
-        <v>34.894538479918</v>
+        <v>34.66318078532502</v>
       </c>
       <c r="AH49" t="n">
-        <v>26.46909788371836</v>
+        <v>26.70045557831135</v>
       </c>
       <c r="AI49" t="n">
         <v>46.62357539237828</v>
@@ -6049,10 +5981,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6900309462541239</v>
+        <v>0.6728733789588344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6077,25 +6009,25 @@
         <v>10</v>
       </c>
       <c r="J50" t="n">
-        <v>10.53761880451027</v>
+        <v>12.8686768057203</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>0.122324159021403</v>
       </c>
       <c r="L50" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M50" t="n">
-        <v>42.5531914893617</v>
+        <v>43.13725490196079</v>
       </c>
       <c r="N50" t="n">
-        <v>13.85650259454351</v>
+        <v>15.83755344260452</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>4.000000000000004</v>
+        <v>3.872938301771534</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6122,16 +6054,16 @@
         <v>15.51990994893744</v>
       </c>
       <c r="Y50" t="n">
-        <v>10.53761880451027</v>
+        <v>12.76209414737869</v>
       </c>
       <c r="Z50" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AA50" t="n">
-        <v>73.91304347826087</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="AB50" t="n">
-        <v>11.08711829665501</v>
+        <v>10.07845826280632</v>
       </c>
       <c r="AC50" t="n">
         <v>5</v>
@@ -6168,10 +6100,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1357033370190867</v>
+        <v>0.1272170499619788</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6196,25 +6128,25 @@
         <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>32.23477001147905</v>
+        <v>34.6913652262994</v>
       </c>
       <c r="K51" t="n">
-        <v>2.803735479081171</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M51" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N51" t="n">
-        <v>15.99466623099526</v>
+        <v>11.3137049812576</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>1.163639157024843</v>
+        <v>4.000000000000004</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6277,24 +6209,24 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C52" t="n">
-        <v>4.498771364174014</v>
+        <v>4.289208130382062</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -6304,17 +6236,27 @@
       <c r="I52" t="n">
         <v>10</v>
       </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="J52" t="n">
+        <v>10.59426908048242</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
       <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="M52" t="n">
+        <v>51.92307692307692</v>
+      </c>
+      <c r="N52" t="n">
+        <v>12.51408749990823</v>
+      </c>
       <c r="O52" t="n">
         <v>10</v>
       </c>
-      <c r="P52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>10.00000000000001</v>
+      </c>
       <c r="Q52" t="n">
         <v>37</v>
       </c>
@@ -6340,22 +6282,22 @@
         <v>16.62696858241317</v>
       </c>
       <c r="Y52" t="n">
-        <v>6.226060888785668</v>
+        <v>10.59426908048242</v>
       </c>
       <c r="Z52" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA52" t="n">
-        <v>63.1578947368421</v>
+        <v>60</v>
       </c>
       <c r="AB52" t="n">
-        <v>12.77300814854131</v>
+        <v>10.6073227052388</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.891718667283948</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
         <v>37</v>
@@ -6364,10 +6306,10 @@
         <v>67.56756756756756</v>
       </c>
       <c r="AG52" t="n">
-        <v>39.84536943155656</v>
+        <v>39.54049929077311</v>
       </c>
       <c r="AH52" t="n">
-        <v>27.722198136011</v>
+        <v>28.02706827679445</v>
       </c>
       <c r="AI52" t="n">
         <v>51.4636672419722</v>
@@ -6386,10 +6328,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C53" t="n">
-        <v>1.133945357215648</v>
+        <v>1.08925745524796</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6408,7 +6350,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -6418,19 +6360,19 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>34.02106335182087</v>
+        <v>36.62124177673712</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M53" t="n">
-        <v>83.33333333333333</v>
+        <v>75</v>
       </c>
       <c r="N53" t="n">
-        <v>20.70738015029972</v>
+        <v>17.89336423299012</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
@@ -6494,7 +6436,7 @@
         <v>46280</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0688797230805423</v>
+        <v>0.0688822731783804</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6522,7 +6464,7 @@
         <v>29.5817777621179</v>
       </c>
       <c r="K54" t="n">
-        <v>9.738043460417313</v>
+        <v>9.742106234407544</v>
       </c>
       <c r="L54" t="n">
         <v>8</v>
@@ -6537,7 +6479,7 @@
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>0.2387107800743582</v>
+        <v>0.2349998322809688</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6564,7 +6506,7 @@
         <v>14.75410024187049</v>
       </c>
       <c r="Y54" t="n">
-        <v>4.371135123608372</v>
+        <v>4.367594706332067</v>
       </c>
       <c r="Z54" t="n">
         <v>35</v>
@@ -6610,10 +6552,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9046889271679863</v>
+        <v>0.8590747477238629</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6622,7 +6564,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6637,17 +6579,27 @@
       <c r="I55" t="n">
         <v>10</v>
       </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+      <c r="J55" t="n">
+        <v>14.05155459679566</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
       <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="M55" t="n">
+        <v>69.6969696969697</v>
+      </c>
+      <c r="N55" t="n">
+        <v>13.86156641913514</v>
+      </c>
       <c r="O55" t="n">
         <v>6</v>
       </c>
-      <c r="P55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>6.000000000000005</v>
+      </c>
       <c r="Q55" t="n">
         <v>45</v>
       </c>
@@ -6673,16 +6625,16 @@
         <v>23.0932342837701</v>
       </c>
       <c r="Y55" t="n">
-        <v>9.487961240161013</v>
+        <v>14.05155459679566</v>
       </c>
       <c r="Z55" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AA55" t="n">
-        <v>35.71428571428572</v>
+        <v>20</v>
       </c>
       <c r="AB55" t="n">
-        <v>9.513128641038493</v>
+        <v>33.66794265572751</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6697,10 +6649,10 @@
         <v>59.09090909090909</v>
       </c>
       <c r="AG55" t="n">
-        <v>39.06110949838082</v>
+        <v>38.96262464989598</v>
       </c>
       <c r="AH55" t="n">
-        <v>20.02979959252827</v>
+        <v>20.12828444101311</v>
       </c>
       <c r="AI55" t="n">
         <v>44.4097537410319</v>
@@ -6719,10 +6671,10 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C56" t="n">
-        <v>0.6271139154232632</v>
+        <v>0.5643586739831885</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6747,7 +6699,7 @@
         <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>56.38004764074929</v>
+        <v>60.74509292931025</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -6808,10 +6760,10 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C57" t="n">
-        <v>1.432081480941461</v>
+        <v>1.301970939433175</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6820,7 +6772,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6828,59 +6780,73 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.32: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>5</v>
       </c>
       <c r="I57" t="n">
         <v>10</v>
       </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="J57" t="n">
+        <v>15.383288100876</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1.036682615629969</v>
+      </c>
       <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="M57" t="n">
+        <v>76.31578947368421</v>
+      </c>
+      <c r="N57" t="n">
+        <v>18.45964007932752</v>
+      </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
-      <c r="P57" t="inlineStr"/>
+      <c r="P57" t="n">
+        <v>8.871349644830339</v>
+      </c>
       <c r="Q57" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R57" t="n">
-        <v>86.20689655172414</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="S57" t="n">
-        <v>57.72012345877791</v>
+        <v>57.62945267681865</v>
       </c>
       <c r="T57" t="n">
-        <v>28.48677309294623</v>
+        <v>29.03721398984802</v>
       </c>
       <c r="U57" t="n">
-        <v>69.44100627964798</v>
+        <v>70.3186733179637</v>
       </c>
       <c r="V57" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="W57" t="n">
-        <v>78.94736842105263</v>
+        <v>79.1304347826087</v>
       </c>
       <c r="X57" t="n">
         <v>20.62560129901716</v>
       </c>
       <c r="Y57" t="n">
-        <v>5.962372960010565</v>
+        <v>14.50608135870008</v>
       </c>
       <c r="Z57" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="AA57" t="n">
-        <v>45.23809523809524</v>
+        <v>50</v>
       </c>
       <c r="AB57" t="n">
-        <v>12.04617014951667</v>
+        <v>8.197595571501115</v>
       </c>
       <c r="AC57" t="n">
         <v>5</v>
@@ -6917,10 +6883,10 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6896197147620016</v>
+        <v>0.6588980002877285</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6937,7 +6903,11 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %86.67: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6948,22 +6918,22 @@
         <v>18.04392839464337</v>
       </c>
       <c r="K58" t="n">
-        <v>5.702060545199705</v>
+        <v>0.9931630849050022</v>
       </c>
       <c r="L58" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M58" t="n">
-        <v>70</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="N58" t="n">
-        <v>17.77087948887664</v>
+        <v>18.10016703499304</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>2.173977917694114</v>
+        <v>6.937931936248343</v>
       </c>
       <c r="Q58" t="n">
         <v>25</v>
@@ -6990,17 +6960,13 @@
         <v>20.50322102897642</v>
       </c>
       <c r="Y58" t="n">
-        <v>12.28279240786235</v>
+        <v>16.19048667535616</v>
       </c>
       <c r="Z58" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>14.24828351986104</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
         <v>6</v>
       </c>
@@ -7036,10 +7002,10 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7389663364316726</v>
+        <v>0.7020572579484966</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7064,25 +7030,25 @@
         <v>10</v>
       </c>
       <c r="J59" t="n">
-        <v>11.95882015364728</v>
+        <v>15.57699197827031</v>
       </c>
       <c r="K59" t="n">
-        <v>0.8741064846375712</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="M59" t="n">
-        <v>60</v>
+        <v>64.86486486486487</v>
       </c>
       <c r="N59" t="n">
-        <v>13.64284710714925</v>
+        <v>15.09409045457231</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>7.064145362663177</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7145,10 +7111,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C60" t="n">
-        <v>10.54785044629948</v>
+        <v>10.37877386604189</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7167,7 +7133,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.25: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -7177,25 +7143,25 @@
         <v>10</v>
       </c>
       <c r="J60" t="n">
-        <v>25.03087531338165</v>
+        <v>26.45170267216481</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>0.2979145978152964</v>
       </c>
       <c r="L60" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M60" t="n">
-        <v>81.25</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N60" t="n">
-        <v>15.26238110577849</v>
+        <v>15.16915044561204</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>8.000000000000007</v>
+        <v>7.679207920792086</v>
       </c>
       <c r="Q60" t="n">
         <v>46</v>
@@ -7230,19 +7196,19 @@
       </c>
       <c r="AD60" t="inlineStr"/>
       <c r="AE60" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AF60" t="n">
-        <v>62.5</v>
+        <v>61.29032258064516</v>
       </c>
       <c r="AG60" t="n">
-        <v>23.09901146722748</v>
+        <v>22.73645585990844</v>
       </c>
       <c r="AH60" t="n">
-        <v>39.40098853277252</v>
+        <v>38.55386672073672</v>
       </c>
       <c r="AI60" t="n">
-        <v>45.25440735307745</v>
+        <v>43.82410861966073</v>
       </c>
       <c r="AJ60" t="n">
         <v>55</v>
@@ -7258,10 +7224,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7130593698781665</v>
+        <v>0.6416342972234211</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7278,7 +7244,11 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H61" t="n">
         <v>5</v>
       </c>
@@ -7286,19 +7256,19 @@
         <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>14.16525261554432</v>
+        <v>22.76306834761157</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="M61" t="n">
-        <v>70.45454545454545</v>
+        <v>80</v>
       </c>
       <c r="N61" t="n">
-        <v>18.65065625275459</v>
+        <v>25.02831523904753</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
@@ -7331,7 +7301,7 @@
         <v>49.99145178651283</v>
       </c>
       <c r="Y61" t="n">
-        <v>14.16525261554432</v>
+        <v>22.76306834761157</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -7373,10 +7343,10 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C62" t="n">
-        <v>8.784735093920958</v>
+        <v>8.606161497831762</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7433,19 +7403,19 @@
         <v>72.05882352941177</v>
       </c>
       <c r="X62" t="n">
-        <v>11.69351808836483</v>
+        <v>11.23299668900593</v>
       </c>
       <c r="Y62" t="n">
-        <v>5.998596607628515</v>
+        <v>7.909430396210581</v>
       </c>
       <c r="Z62" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="AA62" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AB62" t="n">
-        <v>21.91742148575884</v>
+        <v>15.74253410400235</v>
       </c>
       <c r="AC62" t="n">
         <v>5</v>
@@ -7482,10 +7452,10 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1067121724155269</v>
+        <v>0.1027601372875434</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7510,25 +7480,25 @@
         <v>10</v>
       </c>
       <c r="J63" t="n">
-        <v>14.68172212919103</v>
+        <v>16.41989617820666</v>
       </c>
       <c r="K63" t="n">
-        <v>1.934118049237843</v>
+        <v>0.2004008016031955</v>
       </c>
       <c r="L63" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M63" t="n">
-        <v>61.11111111111111</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="N63" t="n">
-        <v>15.2462149963301</v>
+        <v>14.62524216558815</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>3.007709302278183</v>
+        <v>4.790000000000005</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7555,10 +7525,10 @@
         <v>24.85614965143601</v>
       </c>
       <c r="Y63" t="n">
-        <v>13.0315659175928</v>
+        <v>16.25240098016699</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA63" t="inlineStr"/>
       <c r="AB63" t="inlineStr"/>
@@ -7597,10 +7567,10 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1437221680187675</v>
+        <v>0.1368765028670078</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7625,25 +7595,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>13.50818167534201</v>
+        <v>17.51556939038839</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2869437676123798</v>
+        <v>0.1503759398496118</v>
       </c>
       <c r="L64" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="M64" t="n">
-        <v>62.5</v>
+        <v>62</v>
       </c>
       <c r="N64" t="n">
-        <v>17.41415728199853</v>
+        <v>15.0347270041972</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.69957110599446</v>
+        <v>4.842342342342354</v>
       </c>
       <c r="Q64" t="n">
         <v>55</v>
@@ -7684,10 +7654,10 @@
         <v>65.21739130434783</v>
       </c>
       <c r="AG64" t="n">
-        <v>35.02591540028634</v>
+        <v>34.92101092896311</v>
       </c>
       <c r="AH64" t="n">
-        <v>30.19147590406148</v>
+        <v>30.29638037538471</v>
       </c>
       <c r="AI64" t="n">
         <v>50.77005884206276</v>
@@ -7706,10 +7676,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C65" t="n">
-        <v>6.250578042251542</v>
+        <v>6.129642189201965</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7734,25 +7704,25 @@
         <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>11.50329486812964</v>
+        <v>13.4368745754897</v>
       </c>
       <c r="K65" t="n">
-        <v>0.1647446457990087</v>
+        <v>0.4208754208754106</v>
       </c>
       <c r="L65" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M65" t="n">
-        <v>53.44827586206897</v>
+        <v>61.01694915254237</v>
       </c>
       <c r="N65" t="n">
-        <v>12.73252334824025</v>
+        <v>12.31614180669804</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>9.819078947368443</v>
+        <v>9.538977367979907</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7779,16 +7749,16 @@
         <v>24.47056390537039</v>
       </c>
       <c r="Y65" t="n">
-        <v>11.35750128471635</v>
+        <v>13.07255165703637</v>
       </c>
       <c r="Z65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AA65" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AB65" t="n">
-        <v>16.35606305772624</v>
+        <v>15.0813486974636</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
@@ -7825,10 +7795,10 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4309608882074359</v>
+        <v>0.4135067924450748</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7842,7 +7812,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -7853,25 +7823,25 @@
         <v>10</v>
       </c>
       <c r="J66" t="n">
-        <v>11.00008781442038</v>
+        <v>14.6895074495094</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>0.09950248756218638</v>
       </c>
       <c r="L66" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M66" t="n">
-        <v>58.92857142857143</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="N66" t="n">
-        <v>13.55629084880372</v>
+        <v>16.70958532438158</v>
       </c>
       <c r="O66" t="n">
         <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>6.000000000000005</v>
+        <v>5.894632206759454</v>
       </c>
       <c r="Q66" t="n">
         <v>35</v>
@@ -7894,27 +7864,17 @@
       <c r="W66" t="n">
         <v>65.21739130434783</v>
       </c>
-      <c r="X66" t="n">
-        <v>14.59585890675015</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>11.00008781442038</v>
-      </c>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>39.1304347826087</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>9.008984565776595</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
-      <c r="AD66" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD66" t="inlineStr"/>
       <c r="AE66" t="n">
         <v>41</v>
       </c>
@@ -7944,10 +7904,10 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02652383363316239</v>
+        <v>0.02548451404731077</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7972,25 +7932,25 @@
         <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>11.46300958938384</v>
+        <v>13.6175442619109</v>
       </c>
       <c r="K67" t="n">
-        <v>0.3552086159334111</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
         <v>5</v>
       </c>
       <c r="M67" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N67" t="n">
-        <v>6.688022667323312</v>
+        <v>7.039793197149025</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>3.631890595749221</v>
+        <v>4.000000000000004</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -8033,10 +7993,10 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C68" t="n">
-        <v>1.561616392252439</v>
+        <v>1.405758678093594</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8061,7 +8021,7 @@
         <v>10</v>
       </c>
       <c r="J68" t="n">
-        <v>72.03418985118029</v>
+        <v>74.82532810127793</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -8138,10 +8098,10 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5173175743600726</v>
+        <v>0.4809174425057032</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8166,16 +8126,20 @@
         <v>10</v>
       </c>
       <c r="J69" t="n">
-        <v>22.27328735462569</v>
+        <v>22.270409719336</v>
       </c>
       <c r="K69" t="n">
-        <v>19.46818842916143</v>
+        <v>11.05791000478424</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="M69" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="N69" t="n">
+        <v>26.02810049796746</v>
+      </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
@@ -8199,10 +8163,10 @@
         <v>45.36848923911108</v>
       </c>
       <c r="Y69" t="n">
-        <v>7.141304477031374</v>
+        <v>13.67514157901266</v>
       </c>
       <c r="Z69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA69" t="inlineStr"/>
       <c r="AB69" t="inlineStr"/>
@@ -8233,10 +8197,10 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4663260261050794</v>
+        <v>0.4431017119838872</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8261,25 +8225,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>16.07740375784346</v>
+        <v>19.83281106624829</v>
       </c>
       <c r="K70" t="n">
-        <v>0.5319186295175804</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="M70" t="n">
-        <v>45.23809523809524</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="N70" t="n">
-        <v>12.74002158184292</v>
+        <v>14.07573250524651</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>7.428567436382028</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q70" t="n">
         <v>31</v>
@@ -8306,10 +8270,10 @@
         <v>44.93251946562029</v>
       </c>
       <c r="Y70" t="n">
-        <v>15.6310038340566</v>
+        <v>19.83281106624829</v>
       </c>
       <c r="Z70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="inlineStr"/>
       <c r="AB70" t="inlineStr"/>
@@ -8326,10 +8290,10 @@
         <v>52.38095238095238</v>
       </c>
       <c r="AG70" t="n">
-        <v>32.38479655485045</v>
+        <v>32.32527274532664</v>
       </c>
       <c r="AH70" t="n">
-        <v>19.99615582610193</v>
+        <v>20.05567963562574</v>
       </c>
       <c r="AI70" t="n">
         <v>37.72246413134498</v>
@@ -8348,10 +8312,10 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C71" t="n">
-        <v>3.08416679716359</v>
+        <v>2.986209589576012</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8447,10 +8411,10 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0590103891240077</v>
+        <v>0.05590151468442363</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8475,25 +8439,25 @@
         <v>10</v>
       </c>
       <c r="J72" t="n">
-        <v>31.04136939799487</v>
+        <v>34.21592673330382</v>
       </c>
       <c r="K72" t="n">
-        <v>0.7017540597106686</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="M72" t="n">
-        <v>61.53846153846154</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N72" t="n">
-        <v>29.26676915318224</v>
+        <v>11.70093578531563</v>
       </c>
       <c r="O72" t="n">
         <v>10</v>
       </c>
       <c r="P72" t="n">
-        <v>9.23344983124721</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q72" t="n">
         <v>15</v>
@@ -8556,10 +8520,10 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C73" t="n">
-        <v>0.05818794526159744</v>
+        <v>0.05610703495899871</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8584,25 +8548,25 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>23.62755013046467</v>
+        <v>26.36833828924908</v>
       </c>
       <c r="K73" t="n">
-        <v>0.354609583270471</v>
+        <v>0.3676470588235059</v>
       </c>
       <c r="L73" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M73" t="n">
-        <v>64.28571428571429</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N73" t="n">
-        <v>15.31709316854396</v>
+        <v>12.93022551610349</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>9.611307798199498</v>
+        <v>9.59706959706963</v>
       </c>
       <c r="Q73" t="n">
         <v>14</v>
@@ -8665,14 +8629,14 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C74" t="n">
-        <v>5.448694674989008</v>
+        <v>5.163696898699057</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -8682,7 +8646,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -8693,40 +8657,40 @@
         <v>10</v>
       </c>
       <c r="J74" t="n">
-        <v>10.75227026618852</v>
+        <v>12.95695255939758</v>
       </c>
       <c r="K74" t="n">
-        <v>2.9126213592233</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="M74" t="n">
-        <v>72.1311475409836</v>
+        <v>72.61904761904762</v>
       </c>
       <c r="N74" t="n">
-        <v>15.21060899058343</v>
+        <v>18.22953638222469</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>4.943396226415109</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q74" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R74" t="n">
-        <v>75</v>
+        <v>74.07407407407408</v>
       </c>
       <c r="S74" t="n">
-        <v>69.79093646861928</v>
+        <v>71.81972470052359</v>
       </c>
       <c r="T74" t="n">
-        <v>5.209063531380721</v>
+        <v>2.254349373550482</v>
       </c>
       <c r="U74" t="n">
-        <v>56.64432968100104</v>
+        <v>55.32142868544692</v>
       </c>
       <c r="V74" t="n">
         <v>115</v>
@@ -8738,22 +8702,22 @@
         <v>24.51464461150628</v>
       </c>
       <c r="Y74" t="n">
-        <v>8.15282182733965</v>
+        <v>12.95695255939758</v>
       </c>
       <c r="Z74" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AA74" t="n">
-        <v>47.05882352941177</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB74" t="n">
-        <v>17.30403255000777</v>
+        <v>14.07296724520217</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>2.011143085079758</v>
+        <v>0</v>
       </c>
       <c r="AE74" t="n">
         <v>37</v>
@@ -8762,19 +8726,19 @@
         <v>51.35135135135135</v>
       </c>
       <c r="AG74" t="n">
-        <v>29.14297368845935</v>
+        <v>28.92392069717405</v>
       </c>
       <c r="AH74" t="n">
-        <v>22.20837766289201</v>
+        <v>22.4274306541773</v>
       </c>
       <c r="AI74" t="n">
         <v>35.89489666561879</v>
       </c>
       <c r="AJ74" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AK74" t="n">
-        <v>44.44444444444444</v>
+        <v>43.82022471910113</v>
       </c>
     </row>
     <row r="75">
@@ -8784,10 +8748,10 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1100019470427235</v>
+        <v>0.1066650225044701</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8812,25 +8776,25 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>26.70952832272112</v>
+        <v>22.00260697397675</v>
       </c>
       <c r="K75" t="n">
-        <v>1.269913040689907</v>
+        <v>1.764705882352935</v>
       </c>
       <c r="L75" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M75" t="n">
-        <v>66.66666666666667</v>
+        <v>62.5</v>
       </c>
       <c r="N75" t="n">
-        <v>21.98601318710739</v>
+        <v>14.09467689902224</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>4.670772213865293</v>
+        <v>4.161849710982679</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8893,24 +8857,24 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C76" t="n">
-        <v>1.856668474603872</v>
+        <v>1.770557165464373</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>AL_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>BAND</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -8920,17 +8884,27 @@
       <c r="I76" t="n">
         <v>10</v>
       </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="J76" t="n">
+        <v>12.84869141767749</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.05807200929153211</v>
+      </c>
       <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="M76" t="n">
+        <v>53.57142857142857</v>
+      </c>
+      <c r="N76" t="n">
+        <v>14.15038331550346</v>
+      </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
-      <c r="P76" t="inlineStr"/>
+      <c r="P76" t="n">
+        <v>9.936157864190353</v>
+      </c>
       <c r="Q76" t="n">
         <v>41</v>
       </c>
@@ -8952,47 +8926,37 @@
       <c r="W76" t="n">
         <v>60</v>
       </c>
-      <c r="X76" t="n">
-        <v>12.60650925728801</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>8.557002692210858</v>
-      </c>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA76" t="n">
-        <v>41.66666666666666</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>8.760967594621983</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
-      <c r="AD76" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD76" t="inlineStr"/>
       <c r="AE76" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AF76" t="n">
-        <v>56.25</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="AG76" t="n">
-        <v>26.85420686478476</v>
+        <v>26.45137047677935</v>
       </c>
       <c r="AH76" t="n">
-        <v>29.39579313521524</v>
+        <v>28.0940840686752</v>
       </c>
       <c r="AI76" t="n">
-        <v>39.32559113685198</v>
+        <v>37.98593853621745</v>
       </c>
       <c r="AJ76" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AK76" t="n">
-        <v>56.60377358490566</v>
+        <v>55.55555555555556</v>
       </c>
     </row>
     <row r="77">
@@ -9002,10 +8966,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4597464764394641</v>
+        <v>0.4398133875906858</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9030,25 +8994,25 @@
         <v>10</v>
       </c>
       <c r="J77" t="n">
-        <v>19.56827561321563</v>
+        <v>23.12744026695216</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>0.093545369504211</v>
       </c>
       <c r="L77" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="M77" t="n">
-        <v>61.29032258064516</v>
+        <v>60</v>
       </c>
       <c r="N77" t="n">
-        <v>11.36657707028799</v>
+        <v>14.52933807299241</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>8.000000000000007</v>
+        <v>7.899065420560758</v>
       </c>
       <c r="Q77" t="n">
         <v>27</v>
@@ -9057,10 +9021,10 @@
         <v>59.25925925925926</v>
       </c>
       <c r="S77" t="n">
-        <v>37.69335518757989</v>
+        <v>37.88194542688007</v>
       </c>
       <c r="T77" t="n">
-        <v>21.56590407167937</v>
+        <v>21.37731383237919</v>
       </c>
       <c r="U77" t="n">
         <v>40.72670096806468</v>
@@ -9111,24 +9075,24 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05757111251899807</v>
+        <v>0.05179110919292189</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -9138,17 +9102,27 @@
       <c r="I78" t="n">
         <v>10</v>
       </c>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+      <c r="J78" t="n">
+        <v>17.68649068927533</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
       <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="M78" t="n">
+        <v>72.22222222222223</v>
+      </c>
+      <c r="N78" t="n">
+        <v>16.56338320758569</v>
+      </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
-      <c r="P78" t="inlineStr"/>
+      <c r="P78" t="n">
+        <v>4.000000000000004</v>
+      </c>
       <c r="Q78" t="n">
         <v>46</v>
       </c>
@@ -9171,25 +9145,21 @@
         <v>64.1025641025641</v>
       </c>
       <c r="X78" t="n">
-        <v>36.63964711299532</v>
+        <v>36.64470585093908</v>
       </c>
       <c r="Y78" t="n">
-        <v>8.496731865948991</v>
+        <v>17.68649068927533</v>
       </c>
       <c r="Z78" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA78" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="AB78" t="n">
-        <v>15.16176426931412</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
         <v>10</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.642857315051016</v>
+        <v>0</v>
       </c>
       <c r="AE78" t="n">
         <v>32</v>
@@ -9220,10 +9190,10 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8717911794567426</v>
+        <v>0.8290687876359004</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9248,25 +9218,25 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>12.53153482177238</v>
+        <v>16.77869732005618</v>
       </c>
       <c r="K79" t="n">
-        <v>0.04719315595806961</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="M79" t="n">
-        <v>61.81818181818182</v>
+        <v>60</v>
       </c>
       <c r="N79" t="n">
-        <v>11.49206354608452</v>
+        <v>14.12293353427527</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>4.950470560749531</v>
+        <v>5.000000000000004</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9293,17 +9263,13 @@
         <v>25.65117214954458</v>
       </c>
       <c r="Y79" t="n">
-        <v>12.49025569258669</v>
+        <v>16.77869732005618</v>
       </c>
       <c r="Z79" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>9.291824236449653</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
         <v>8</v>
       </c>
@@ -9317,10 +9283,10 @@
         <v>52.77777777777778</v>
       </c>
       <c r="AG79" t="n">
-        <v>26.34016065895714</v>
+        <v>26.25121703553076</v>
       </c>
       <c r="AH79" t="n">
-        <v>26.43761711882064</v>
+        <v>26.52656074224702</v>
       </c>
       <c r="AI79" t="n">
         <v>37.00593802298759</v>
@@ -9339,10 +9305,10 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1299462312158816</v>
+        <v>0.1272170499619788</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9367,25 +9333,25 @@
         <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>10.48668504530712</v>
+        <v>11.20469085942543</v>
       </c>
       <c r="K80" t="n">
-        <v>1.654412722635756</v>
+        <v>0.3241491085899773</v>
       </c>
       <c r="L80" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M80" t="n">
-        <v>44.77611940298507</v>
+        <v>49.27536231884058</v>
       </c>
       <c r="N80" t="n">
-        <v>16.55039854440819</v>
+        <v>14.88465411080209</v>
       </c>
       <c r="O80" t="n">
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>8.209763898922118</v>
+        <v>9.644588045234226</v>
       </c>
       <c r="Q80" t="n">
         <v>39</v>
@@ -9409,19 +9375,19 @@
         <v>74.35897435897436</v>
       </c>
       <c r="X80" t="n">
-        <v>16.92042739318289</v>
+        <v>16.30078916022812</v>
       </c>
       <c r="Y80" t="n">
-        <v>9.005765374243669</v>
+        <v>10.91686165637654</v>
       </c>
       <c r="Z80" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA80" t="n">
-        <v>45.45454545454545</v>
+        <v>50</v>
       </c>
       <c r="AB80" t="n">
-        <v>12.67571770684304</v>
+        <v>17.01162787358019</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
@@ -9458,10 +9424,10 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C81" t="n">
-        <v>1.198712812871137</v>
+        <v>1.163244754094992</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9521,22 +9487,22 @@
         <v>23.79225853623819</v>
       </c>
       <c r="Y81" t="n">
-        <v>5.867738566974056</v>
+        <v>8.652966642780857</v>
       </c>
       <c r="Z81" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AA81" t="n">
-        <v>54.54545454545455</v>
+        <v>50</v>
       </c>
       <c r="AB81" t="n">
-        <v>10.57225322578887</v>
+        <v>10.5869564825963</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>4.389846127266361</v>
+        <v>1.474632845438417</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9570,7 +9536,7 @@
         <v>46280</v>
       </c>
       <c r="C82" t="n">
-        <v>4.626250195745384</v>
+        <v>4.62642147097843</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9595,19 +9561,19 @@
         <v>10</v>
       </c>
       <c r="J82" t="n">
-        <v>17.25076623026857</v>
+        <v>17.2477026488152</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M82" t="n">
-        <v>28.57142857142857</v>
+        <v>37.5</v>
       </c>
       <c r="N82" t="n">
-        <v>8.812299547508161</v>
+        <v>7.805083733293841</v>
       </c>
       <c r="O82" t="n">
         <v>4</v>
@@ -9676,10 +9642,10 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C83" t="n">
-        <v>5.23794327718283</v>
+        <v>5.11128922868241</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9704,25 +9670,25 @@
         <v>10</v>
       </c>
       <c r="J83" t="n">
-        <v>13.99279494326494</v>
+        <v>16.3424306726454</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>0.3227107704719678</v>
       </c>
       <c r="L83" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="M83" t="n">
-        <v>64.0625</v>
+        <v>66</v>
       </c>
       <c r="N83" t="n">
-        <v>12.43521313256074</v>
+        <v>10.61586557916401</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>10.00000000000001</v>
+        <v>9.646160032167273</v>
       </c>
       <c r="Q83" t="n">
         <v>41</v>
@@ -9763,10 +9729,10 @@
         <v>58.53658536585366</v>
       </c>
       <c r="AG83" t="n">
-        <v>28.12792354245498</v>
+        <v>27.52049734251406</v>
       </c>
       <c r="AH83" t="n">
-        <v>30.40866182339868</v>
+        <v>31.0160880233396</v>
       </c>
       <c r="AI83" t="n">
         <v>43.36710313403013</v>
@@ -9785,24 +9751,24 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C84" t="n">
-        <v>2.043774562378907</v>
+        <v>1.945249398853197</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -9813,25 +9779,25 @@
         <v>10</v>
       </c>
       <c r="J84" t="n">
-        <v>14.20091622675307</v>
+        <v>13.26443414678632</v>
       </c>
       <c r="K84" t="n">
-        <v>5.404362329994816</v>
+        <v>0.3230866227573292</v>
       </c>
       <c r="L84" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="M84" t="n">
-        <v>66.66666666666667</v>
+        <v>57.4074074074074</v>
       </c>
       <c r="N84" t="n">
-        <v>10.55881180753439</v>
+        <v>10.98984806102496</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>4.661851558484398</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9858,16 +9824,16 @@
         <v>11.86663135768809</v>
       </c>
       <c r="Y84" t="n">
-        <v>5.776761979209399</v>
+        <v>10.31902417622717</v>
       </c>
       <c r="Z84" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="AA84" t="n">
-        <v>40.54054054054054</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="AB84" t="n">
-        <v>9.908696585285828</v>
+        <v>10.28587696493542</v>
       </c>
       <c r="AC84" t="n">
         <v>2</v>
@@ -9876,19 +9842,19 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AF84" t="n">
-        <v>43.58974358974359</v>
+        <v>44.73684210526316</v>
       </c>
       <c r="AG84" t="n">
-        <v>28.72591724014846</v>
+        <v>28.56199550464609</v>
       </c>
       <c r="AH84" t="n">
-        <v>14.86382634959513</v>
+        <v>16.17484660061707</v>
       </c>
       <c r="AI84" t="n">
-        <v>29.30475387568963</v>
+        <v>30.14640099805125</v>
       </c>
       <c r="AJ84" t="n">
         <v>56</v>
@@ -9904,10 +9870,10 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C85" t="n">
-        <v>5.865057192606093</v>
+        <v>5.70318761945866</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9932,25 +9898,25 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>12.40495804625523</v>
+        <v>15.0174071214567</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>0.2710027100270906</v>
       </c>
       <c r="L85" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="M85" t="n">
-        <v>62.90322580645162</v>
+        <v>65.45454545454545</v>
       </c>
       <c r="N85" t="n">
-        <v>12.59505726590093</v>
+        <v>13.72552366474792</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>8.000000000000007</v>
+        <v>7.708108108108136</v>
       </c>
       <c r="Q85" t="n">
         <v>32</v>
@@ -9991,10 +9957,10 @@
         <v>42.42424242424242</v>
       </c>
       <c r="AG85" t="n">
-        <v>26.91759214820712</v>
+        <v>26.87175563178237</v>
       </c>
       <c r="AH85" t="n">
-        <v>15.5066502760353</v>
+        <v>15.55248679246005</v>
       </c>
       <c r="AI85" t="n">
         <v>27.23559663341021</v>
@@ -10013,31 +9979,27 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C86" t="n">
-        <v>4.729055755650838</v>
+        <v>4.500894013194402</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>5</v>
       </c>
@@ -10048,22 +10010,22 @@
         <v>18.73514495170452</v>
       </c>
       <c r="K86" t="n">
-        <v>13.4362107760009</v>
+        <v>7.963278155703235</v>
       </c>
       <c r="L86" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="M86" t="n">
-        <v>100</v>
+        <v>52.38095238095238</v>
       </c>
       <c r="N86" t="n">
-        <v>16.42415905518173</v>
+        <v>15.60302359565044</v>
       </c>
       <c r="O86" t="n">
         <v>8</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>0.03401327277576804</v>
       </c>
       <c r="Q86" t="n">
         <v>52</v>
@@ -10087,19 +10049,19 @@
         <v>70.12987012987013</v>
       </c>
       <c r="X86" t="n">
-        <v>44.99483923332605</v>
+        <v>32.57395859734095</v>
       </c>
       <c r="Y86" t="n">
-        <v>7.816227740603932</v>
+        <v>12.26379850137972</v>
       </c>
       <c r="Z86" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA86" t="n">
-        <v>50</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB86" t="n">
-        <v>15.39823644341957</v>
+        <v>9.293216334513348</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
@@ -10136,10 +10098,10 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C87" t="n">
-        <v>5.844496080625002</v>
+        <v>5.620979509628626</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10199,16 +10161,16 @@
         <v>15.88967756874082</v>
       </c>
       <c r="Y87" t="n">
-        <v>5.255603765462869</v>
+        <v>8.87900299019142</v>
       </c>
       <c r="Z87" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="AA87" t="n">
-        <v>45.71428571428572</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="AB87" t="n">
-        <v>12.87424470283853</v>
+        <v>10.70588891383947</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
@@ -10223,10 +10185,10 @@
         <v>46.51162790697674</v>
       </c>
       <c r="AG87" t="n">
-        <v>44.84596168511808</v>
+        <v>44.70540456781678</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.665666221858665</v>
+        <v>1.806223339159963</v>
       </c>
       <c r="AI87" t="n">
         <v>32.51105770412182</v>
@@ -10245,19 +10207,19 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C88" t="n">
-        <v>1.037308115072466</v>
+        <v>0.996362291140021</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -10276,59 +10238,55 @@
         <v>16.8583060727446</v>
       </c>
       <c r="K88" t="n">
-        <v>4.340010677406481</v>
+        <v>0.2213812709373597</v>
       </c>
       <c r="L88" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="M88" t="n">
-        <v>61.90476190476191</v>
+        <v>73.07692307692308</v>
       </c>
       <c r="N88" t="n">
-        <v>15.20170034249627</v>
+        <v>13.87616080882865</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.772480975442715</v>
       </c>
       <c r="Q88" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R88" t="n">
-        <v>72.72727272727273</v>
+        <v>73.52941176470588</v>
       </c>
       <c r="S88" t="n">
-        <v>48.02255550006358</v>
+        <v>49.25718622064995</v>
       </c>
       <c r="T88" t="n">
-        <v>24.70471722720915</v>
+        <v>24.27222554405594</v>
       </c>
       <c r="U88" t="n">
-        <v>55.78244099712737</v>
+        <v>56.88285871705534</v>
       </c>
       <c r="V88" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W88" t="n">
-        <v>61.53846153846154</v>
+        <v>62.0253164556962</v>
       </c>
       <c r="X88" t="n">
         <v>22.33299319731812</v>
       </c>
       <c r="Y88" t="n">
-        <v>13.24994767892509</v>
+        <v>16.67424593404958</v>
       </c>
       <c r="Z88" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA88" t="n">
-        <v>45.45454545454545</v>
-      </c>
-      <c r="AB88" t="n">
-        <v>13.4099918685533</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
@@ -10342,10 +10300,10 @@
         <v>51.51515151515152</v>
       </c>
       <c r="AG88" t="n">
-        <v>52.44979361570975</v>
+        <v>52.16480083071696</v>
       </c>
       <c r="AH88" t="n">
-        <v>-0.9346421005582357</v>
+        <v>-0.6496493155654477</v>
       </c>
       <c r="AI88" t="n">
         <v>35.21837544891414</v>
@@ -10364,24 +10322,24 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C89" t="n">
-        <v>2.130131169782485</v>
+        <v>2.057257948496619</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -10391,17 +10349,27 @@
       <c r="I89" t="n">
         <v>10</v>
       </c>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="J89" t="n">
+        <v>12.22837120615282</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.09999999999998899</v>
+      </c>
       <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="M89" t="n">
+        <v>61.1764705882353</v>
+      </c>
+      <c r="N89" t="n">
+        <v>15.99587879436045</v>
+      </c>
       <c r="O89" t="n">
         <v>4</v>
       </c>
-      <c r="P89" t="inlineStr"/>
+      <c r="P89" t="n">
+        <v>3.896103896103909</v>
+      </c>
       <c r="Q89" t="n">
         <v>45</v>
       </c>
@@ -10427,22 +10395,22 @@
         <v>21.41032003314154</v>
       </c>
       <c r="Y89" t="n">
-        <v>9.028399897332772</v>
+        <v>12.14059957735898</v>
       </c>
       <c r="Z89" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AA89" t="n">
-        <v>34.61538461538461</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB89" t="n">
-        <v>15.1641247567547</v>
+        <v>15.99545050654658</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>1.06802573723086</v>
+        <v>0</v>
       </c>
       <c r="AE89" t="n">
         <v>22</v>
@@ -10473,10 +10441,10 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C90" t="n">
-        <v>2.716123018124851</v>
+        <v>2.605997081612101</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10501,25 +10469,25 @@
         <v>10</v>
       </c>
       <c r="J90" t="n">
-        <v>13.32304178579999</v>
+        <v>16.91371885796505</v>
       </c>
       <c r="K90" t="n">
-        <v>0.3037275317112176</v>
+        <v>0.3958828186856778</v>
       </c>
       <c r="L90" t="n">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="M90" t="n">
-        <v>63.63636363636363</v>
+        <v>63.9344262295082</v>
       </c>
       <c r="N90" t="n">
-        <v>15.08047556655999</v>
+        <v>15.06571248022794</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>7.672967553330068</v>
+        <v>7.574132492113561</v>
       </c>
       <c r="Q90" t="n">
         <v>43</v>
@@ -10546,16 +10514,16 @@
         <v>20.63086277737274</v>
       </c>
       <c r="Y90" t="n">
-        <v>13.05978000005364</v>
+        <v>16.58479454623887</v>
       </c>
       <c r="Z90" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AA90" t="n">
-        <v>30.76923076923077</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB90" t="n">
-        <v>12.23365874636309</v>
+        <v>32.38665509377456</v>
       </c>
       <c r="AC90" t="n">
         <v>2</v>
@@ -10592,10 +10560,10 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2309012780895359</v>
+        <v>0.2192901329716177</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10678,10 +10646,10 @@
         <v>27.07931000072518</v>
       </c>
       <c r="AJ91" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AK91" t="n">
-        <v>43.05555555555556</v>
+        <v>43.66197183098591</v>
       </c>
     </row>
     <row r="92">
@@ -10691,10 +10659,10 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C92" t="n">
-        <v>1.127776960704318</v>
+        <v>1.085147049756459</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10703,7 +10671,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -10718,17 +10686,27 @@
       <c r="I92" t="n">
         <v>10</v>
       </c>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="J92" t="n">
+        <v>13.59116935401785</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.2849002849002913</v>
+      </c>
       <c r="L92" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+        <v>64</v>
+      </c>
+      <c r="M92" t="n">
+        <v>57.8125</v>
+      </c>
+      <c r="N92" t="n">
+        <v>12.34465699974668</v>
+      </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
-      <c r="P92" t="inlineStr"/>
+      <c r="P92" t="n">
+        <v>7.693181818181816</v>
+      </c>
       <c r="Q92" t="n">
         <v>44</v>
       </c>
@@ -10754,16 +10732,16 @@
         <v>21.60407460332612</v>
       </c>
       <c r="Y92" t="n">
-        <v>9.940755554216485</v>
+        <v>13.34499034932844</v>
       </c>
       <c r="Z92" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AA92" t="n">
-        <v>70</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB92" t="n">
-        <v>12.84590382592824</v>
+        <v>22.24427307110499</v>
       </c>
       <c r="AC92" t="n">
         <v>4</v>
@@ -10778,10 +10756,10 @@
         <v>51.92307692307692</v>
       </c>
       <c r="AG92" t="n">
-        <v>40.32778030649548</v>
+        <v>40.08078371334503</v>
       </c>
       <c r="AH92" t="n">
-        <v>11.59529661658144</v>
+        <v>11.84229320973188</v>
       </c>
       <c r="AI92" t="n">
         <v>38.68568276805605</v>
@@ -10800,10 +10778,10 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0411222239621812</v>
+        <v>0.03945989271841667</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10812,7 +10790,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -10827,17 +10805,27 @@
       <c r="I93" t="n">
         <v>10</v>
       </c>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="J93" t="n">
+        <v>10.21837347371534</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
       <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="M93" t="n">
+        <v>57.14285714285715</v>
+      </c>
+      <c r="N93" t="n">
+        <v>18.9078285838319</v>
+      </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
-      <c r="P93" t="inlineStr"/>
+      <c r="P93" t="n">
+        <v>6.000000000000005</v>
+      </c>
       <c r="Q93" t="n">
         <v>31</v>
       </c>
@@ -10863,16 +10851,16 @@
         <v>11.4419372600254</v>
       </c>
       <c r="Y93" t="n">
-        <v>6.436133011085177</v>
+        <v>10.21837347371534</v>
       </c>
       <c r="Z93" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="AA93" t="n">
-        <v>45.45454545454545</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="AB93" t="n">
-        <v>13.0285354938626</v>
+        <v>13.42669115594144</v>
       </c>
       <c r="AC93" t="n">
         <v>2</v>
@@ -10887,10 +10875,10 @@
         <v>58.33333333333334</v>
       </c>
       <c r="AG93" t="n">
-        <v>24.71494548232858</v>
+        <v>24.28680322228977</v>
       </c>
       <c r="AH93" t="n">
-        <v>33.61838785100475</v>
+        <v>34.04653011104357</v>
       </c>
       <c r="AI93" t="n">
         <v>38.83466586522876</v>
@@ -10909,10 +10897,10 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C94" t="n">
-        <v>8.481458692199871</v>
+        <v>8.282467065376</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10948,19 +10936,19 @@
       </c>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R94" t="n">
-        <v>61.90476190476191</v>
+        <v>63.41463414634146</v>
       </c>
       <c r="S94" t="n">
-        <v>40.27276838599167</v>
+        <v>41.35906589169578</v>
       </c>
       <c r="T94" t="n">
-        <v>21.63199351877024</v>
+        <v>22.05556825464569</v>
       </c>
       <c r="U94" t="n">
-        <v>46.81404026715268</v>
+        <v>48.12070108791201</v>
       </c>
       <c r="V94" t="n">
         <v>55</v>
@@ -10969,25 +10957,25 @@
         <v>70.90909090909091</v>
       </c>
       <c r="X94" t="n">
-        <v>40.43377921558155</v>
+        <v>36.6815048892442</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.779423303741879</v>
+        <v>5.060408381855297</v>
       </c>
       <c r="Z94" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA94" t="n">
-        <v>41.66666666666666</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AB94" t="n">
-        <v>11.76855544142956</v>
+        <v>13.56192792270044</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>3.312649241240395</v>
+        <v>0.9896731196441522</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -11021,7 +11009,7 @@
         <v>46280</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1192544533969368</v>
+        <v>0.1192588684919777</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11046,10 +11034,10 @@
         <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>20.47777775450879</v>
+        <v>20.4748336450095</v>
       </c>
       <c r="K95" t="n">
-        <v>0.3460204026532576</v>
+        <v>0.3460204026532354</v>
       </c>
       <c r="L95" t="n">
         <v>25</v>
@@ -11064,7 +11052,7 @@
         <v>10</v>
       </c>
       <c r="P95" t="n">
-        <v>9.62069004690842</v>
+        <v>9.620690046908443</v>
       </c>
       <c r="Q95" t="n">
         <v>21</v>
@@ -11127,10 +11115,10 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1246003373717423</v>
+        <v>0.1229011241959019</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11226,10 +11214,10 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C97" t="n">
-        <v>1.833023164572728</v>
+        <v>1.761308753108494</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11243,7 +11231,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -11254,25 +11242,25 @@
         <v>10</v>
       </c>
       <c r="J97" t="n">
-        <v>12.87370897365936</v>
+        <v>16.16774792949364</v>
       </c>
       <c r="K97" t="n">
-        <v>0.1954087403120308</v>
+        <v>0.05837711617044938</v>
       </c>
       <c r="L97" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="M97" t="n">
-        <v>64.40677966101696</v>
+        <v>63.04347826086956</v>
       </c>
       <c r="N97" t="n">
-        <v>13.34630568285463</v>
+        <v>13.25261425923628</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>3.797171255170761</v>
+        <v>3.939323220536761</v>
       </c>
       <c r="Q97" t="n">
         <v>50</v>
@@ -11295,27 +11283,17 @@
       <c r="W97" t="n">
         <v>62.29508196721311</v>
       </c>
-      <c r="X97" t="n">
-        <v>16.31583297271808</v>
-      </c>
-      <c r="Y97" t="n">
-        <v>12.70345658588421</v>
-      </c>
+      <c r="X97" t="inlineStr"/>
+      <c r="Y97" t="inlineStr"/>
       <c r="Z97" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA97" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="AB97" t="n">
-        <v>10.28208228437988</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA97" t="inlineStr"/>
+      <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="n">
         <v>6</v>
       </c>
-      <c r="AD97" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD97" t="inlineStr"/>
       <c r="AE97" t="n">
         <v>39</v>
       </c>
@@ -11332,10 +11310,10 @@
         <v>38.56944827051576</v>
       </c>
       <c r="AJ97" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AK97" t="n">
-        <v>52.38095238095238</v>
+        <v>51.61290322580645</v>
       </c>
     </row>
     <row r="98">
@@ -11345,10 +11323,10 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6966104959197392</v>
+        <v>0.6642415274266807</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11373,25 +11351,25 @@
         <v>10</v>
       </c>
       <c r="J98" t="n">
-        <v>11.10881295683203</v>
+        <v>15.29171564364919</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>0.06191950464398133</v>
       </c>
       <c r="L98" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M98" t="n">
-        <v>43.54838709677419</v>
+        <v>50.79365079365079</v>
       </c>
       <c r="N98" t="n">
-        <v>15.56156652968006</v>
+        <v>15.64263700001116</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>10.00000000000001</v>
+        <v>9.931930693069301</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11418,17 +11396,13 @@
         <v>30.85778357900837</v>
       </c>
       <c r="Y98" t="n">
-        <v>11.10881295683203</v>
+        <v>15.23926469358333</v>
       </c>
       <c r="Z98" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA98" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB98" t="n">
-        <v>7.373728834792908</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="n">
         <v>8</v>
       </c>
@@ -11442,10 +11416,10 @@
         <v>56.86274509803921</v>
       </c>
       <c r="AG98" t="n">
-        <v>37.46666034773386</v>
+        <v>37.20855910924046</v>
       </c>
       <c r="AH98" t="n">
-        <v>19.39608475030535</v>
+        <v>19.65418598879875</v>
       </c>
       <c r="AI98" t="n">
         <v>43.26530210930225</v>
@@ -11464,10 +11438,10 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5271868986528846</v>
+        <v>0.5076350782004645</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11492,25 +11466,25 @@
         <v>10</v>
       </c>
       <c r="J99" t="n">
-        <v>12.51634982914205</v>
+        <v>13.51503694917485</v>
       </c>
       <c r="K99" t="n">
-        <v>2.832542587660747</v>
+        <v>0.162206001622045</v>
       </c>
       <c r="L99" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M99" t="n">
-        <v>50.66666666666666</v>
+        <v>54.28571428571428</v>
       </c>
       <c r="N99" t="n">
-        <v>16.512046349427</v>
+        <v>17.07530218036992</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>1.135299568562198</v>
+        <v>3.83157894736843</v>
       </c>
       <c r="Q99" t="n">
         <v>34</v>
@@ -11537,17 +11511,13 @@
         <v>33.04241514445872</v>
       </c>
       <c r="Y99" t="n">
-        <v>10.03833818081236</v>
+        <v>13.3747531486058</v>
       </c>
       <c r="Z99" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA99" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB99" t="n">
-        <v>5.33028826325086</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="n">
         <v>10</v>
       </c>
@@ -11561,10 +11531,10 @@
         <v>50</v>
       </c>
       <c r="AG99" t="n">
-        <v>36.14854763279278</v>
+        <v>35.90154855615382</v>
       </c>
       <c r="AH99" t="n">
-        <v>13.85145236720722</v>
+        <v>14.09845144384618</v>
       </c>
       <c r="AI99" t="n">
         <v>34.8499283643951</v>
@@ -11586,7 +11556,7 @@
         <v>46280</v>
       </c>
       <c r="C100" t="n">
-        <v>332.7182675828155</v>
+        <v>332.7305856366188</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11628,10 +11598,10 @@
         <v>60.41666666666666</v>
       </c>
       <c r="S100" t="n">
-        <v>36.6138185892986</v>
+        <v>36.6940103882404</v>
       </c>
       <c r="T100" t="n">
-        <v>23.80284807736807</v>
+        <v>23.72265627842626</v>
       </c>
       <c r="U100" t="n">
         <v>46.31040849254725</v>
@@ -11646,7 +11616,7 @@
         <v>16.86980163304483</v>
       </c>
       <c r="Y100" t="n">
-        <v>8.674802447640461</v>
+        <v>8.67142136278083</v>
       </c>
       <c r="Z100" t="n">
         <v>21</v>
@@ -11692,14 +11662,14 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C101" t="n">
-        <v>342.2413554204456</v>
+        <v>328.1320262243871</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -11709,7 +11679,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -11755,22 +11725,22 @@
         <v>12.90626814318425</v>
       </c>
       <c r="Y101" t="n">
-        <v>5.309529239269606</v>
+        <v>9.213262679232148</v>
       </c>
       <c r="Z101" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AA101" t="n">
-        <v>43.33333333333334</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="AB101" t="n">
-        <v>12.09939166269356</v>
+        <v>11.96512718006614</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
       <c r="AD101" t="n">
-        <v>0.7291871665472294</v>
+        <v>0</v>
       </c>
       <c r="AE101" t="n">
         <v>28</v>
@@ -11804,7 +11774,7 @@
         <v>46280</v>
       </c>
       <c r="C102" t="n">
-        <v>399.9646292279465</v>
+        <v>399.9794369085047</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11846,10 +11816,10 @@
         <v>48.27586206896552</v>
       </c>
       <c r="S102" t="n">
-        <v>26.00931549500995</v>
+        <v>26.09552239156168</v>
       </c>
       <c r="T102" t="n">
-        <v>22.26654657395557</v>
+        <v>22.18033967740384</v>
       </c>
       <c r="U102" t="n">
         <v>31.38609015268349</v>
@@ -11900,24 +11870,24 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7130593698781665</v>
+        <v>0.6778058655486363</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>AL_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t>BAND</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -11927,17 +11897,27 @@
       <c r="I103" t="n">
         <v>10</v>
       </c>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
+      <c r="J103" t="n">
+        <v>14.23010683860694</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
       <c r="L103" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="M103" t="n">
+        <v>52.45901639344262</v>
+      </c>
+      <c r="N103" t="n">
+        <v>14.16461546768283</v>
+      </c>
       <c r="O103" t="n">
         <v>10</v>
       </c>
-      <c r="P103" t="inlineStr"/>
+      <c r="P103" t="n">
+        <v>10.00000000000001</v>
+      </c>
       <c r="Q103" t="n">
         <v>43</v>
       </c>
@@ -11959,41 +11939,31 @@
       <c r="W103" t="n">
         <v>67.69230769230769</v>
       </c>
-      <c r="X103" t="n">
-        <v>14.28440963201156</v>
-      </c>
-      <c r="Y103" t="n">
-        <v>9.769110772334988</v>
-      </c>
+      <c r="X103" t="inlineStr"/>
+      <c r="Y103" t="inlineStr"/>
       <c r="Z103" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA103" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="AB103" t="n">
-        <v>8.759393545287127</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA103" t="inlineStr"/>
+      <c r="AB103" t="inlineStr"/>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
-      <c r="AD103" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD103" t="inlineStr"/>
       <c r="AE103" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AF103" t="n">
-        <v>60.60606060606061</v>
+        <v>59.375</v>
       </c>
       <c r="AG103" t="n">
-        <v>34.5730577450251</v>
+        <v>34.23085106690951</v>
       </c>
       <c r="AH103" t="n">
-        <v>26.03300286103551</v>
+        <v>25.14414893309049</v>
       </c>
       <c r="AI103" t="n">
-        <v>43.68344081994023</v>
+        <v>42.26002487538288</v>
       </c>
       <c r="AJ103" t="n">
         <v>60</v>
@@ -12009,14 +11979,14 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C104" t="n">
-        <v>0.05181400178112607</v>
+        <v>0.05014694699632119</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -12026,7 +11996,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -12069,25 +12039,25 @@
         <v>63.23529411764706</v>
       </c>
       <c r="X104" t="n">
-        <v>17.06166321640041</v>
+        <v>17.0659971289213</v>
       </c>
       <c r="Y104" t="n">
-        <v>4.905664720540948</v>
+        <v>7.968620743487675</v>
       </c>
       <c r="Z104" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="AA104" t="n">
-        <v>51.51515151515152</v>
+        <v>60.71428571428572</v>
       </c>
       <c r="AB104" t="n">
-        <v>13.47460625950747</v>
+        <v>13.84827315128828</v>
       </c>
       <c r="AC104" t="n">
         <v>5</v>
       </c>
       <c r="AD104" t="n">
-        <v>0.0992017865016126</v>
+        <v>0</v>
       </c>
       <c r="AE104" t="n">
         <v>42</v>
@@ -12096,10 +12066,10 @@
         <v>57.14285714285715</v>
       </c>
       <c r="AG104" t="n">
-        <v>30.16212875485753</v>
+        <v>30.00568606082085</v>
       </c>
       <c r="AH104" t="n">
-        <v>26.98072838799961</v>
+        <v>27.13717108203629</v>
       </c>
       <c r="AI104" t="n">
         <v>42.20623987810458</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -436,15 +436,15 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -670,7 +670,7 @@
         <v>46281</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3793904268656104</v>
+        <v>0.381034589062211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,22 +698,22 @@
         <v>21.42119502374098</v>
       </c>
       <c r="K2" t="n">
-        <v>3.256427955393781</v>
+        <v>3.703909766684732</v>
       </c>
       <c r="L2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M2" t="n">
-        <v>66.66666666666667</v>
+        <v>65</v>
       </c>
       <c r="N2" t="n">
-        <v>12.4604140391455</v>
+        <v>12.93135588622005</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>6.530898054617396</v>
+        <v>6.071217804112061</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -740,22 +740,22 @@
         <v>11.79582706077868</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.638388059638757</v>
+        <v>7.238121052313263</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.79335241570344</v>
+        <v>11.853829196456</v>
       </c>
       <c r="AC2" t="n">
         <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.556919363735399</v>
+        <v>2.977385731097903</v>
       </c>
       <c r="AE2" t="n">
         <v>46</v>
@@ -786,19 +786,19 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6933463895361193</v>
+        <v>0.6835603987093327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -814,25 +814,25 @@
         <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>16.83732632822199</v>
+        <v>16.52890779617068</v>
       </c>
       <c r="K3" t="n">
-        <v>10.28561090435578</v>
+        <v>8.729023904085054</v>
       </c>
       <c r="L3" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M3" t="n">
-        <v>52.17391304347826</v>
+        <v>65.51724137931035</v>
       </c>
       <c r="N3" t="n">
-        <v>13.85448427853721</v>
+        <v>12.05054107876322</v>
       </c>
       <c r="O3" t="n">
         <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.168939120649282</v>
       </c>
       <c r="Q3" t="n">
         <v>35</v>
@@ -859,37 +859,37 @@
         <v>17.17248092970491</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.877549037713681</v>
+        <v>7.206006870064763</v>
       </c>
       <c r="Z3" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA3" t="n">
-        <v>41.37931034482759</v>
+        <v>36</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.43477117522758</v>
+        <v>12.71633189378402</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.379880591866581</v>
+        <v>3.010963356241103</v>
       </c>
       <c r="AE3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AF3" t="n">
-        <v>60</v>
+        <v>61.76470588235294</v>
       </c>
       <c r="AG3" t="n">
-        <v>33.02274640211751</v>
+        <v>32.10001528466201</v>
       </c>
       <c r="AH3" t="n">
-        <v>26.97725359788249</v>
+        <v>29.66469059769094</v>
       </c>
       <c r="AI3" t="n">
-        <v>43.5727090128925</v>
+        <v>45.0410173444307</v>
       </c>
       <c r="AJ3" t="n">
         <v>67</v>
@@ -908,11 +908,11 @@
         <v>46281</v>
       </c>
       <c r="C4" t="n">
-        <v>1.363627021805701</v>
+        <v>1.357461413568449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -922,14 +922,10 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %83.33: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>BAND</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>5</v>
       </c>
@@ -937,25 +933,25 @@
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>13.38716819771938</v>
+        <v>15.14944887493233</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1.615384615384619</v>
       </c>
       <c r="L4" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="M4" t="n">
-        <v>56.06060606060606</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="N4" t="n">
-        <v>13.41787111993552</v>
+        <v>14.47718684331674</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>5.000000000000004</v>
+        <v>3.330809992429984</v>
       </c>
       <c r="Q4" t="n">
         <v>53</v>
@@ -978,27 +974,17 @@
       <c r="W4" t="n">
         <v>62.5</v>
       </c>
-      <c r="X4" t="n">
-        <v>16.66966699739723</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>13.38716819771938</v>
-      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>83.33333333333333</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>13.82559167632864</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
         <v>40</v>
       </c>
@@ -1031,7 +1017,7 @@
         <v>46281</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2168238896767166</v>
+        <v>0.2164128491275664</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,10 +1046,10 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>19.52862999556227</v>
+        <v>20.21576838170645</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09487666034158071</v>
+        <v>0.7655520713353958</v>
       </c>
       <c r="L5" t="n">
         <v>33</v>
@@ -1072,13 +1058,13 @@
         <v>75.75757575757575</v>
       </c>
       <c r="N5" t="n">
-        <v>12.51951311963504</v>
+        <v>11.96651226738573</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.902369668246418</v>
+        <v>2.217472025641021</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1144,16 +1130,16 @@
         <v>46281</v>
       </c>
       <c r="C6" t="n">
-        <v>1.450973138500113</v>
+        <v>1.448917935754362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1161,11 +1147,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>5</v>
       </c>
@@ -1173,25 +1155,21 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>30.97082607325095</v>
+        <v>34.44183977636651</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5.145413870246096</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>80</v>
-      </c>
-      <c r="N6" t="n">
-        <v>9.721465223321935</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.000000000000002</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>35</v>
@@ -1257,7 +1235,7 @@
         <v>46281</v>
       </c>
       <c r="C7" t="n">
-        <v>2.143576463818156</v>
+        <v>2.186735721478924</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,25 +1260,25 @@
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>13.35749781503482</v>
+        <v>14.18820253397024</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.00096805421104</v>
       </c>
       <c r="L7" t="n">
         <v>63</v>
       </c>
       <c r="M7" t="n">
-        <v>69.84126984126983</v>
+        <v>65.07936507936508</v>
       </c>
       <c r="N7" t="n">
-        <v>13.24469505007974</v>
+        <v>12.8957664259746</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>8.000000000000007</v>
+        <v>4.85338345864661</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1327,16 +1305,16 @@
         <v>18.9234494530097</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.35749781503482</v>
+        <v>11.61301790527041</v>
       </c>
       <c r="Z7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>66.66666666666667</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.880102520564243</v>
+        <v>11.48364838038053</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1376,7 +1354,7 @@
         <v>46281</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3273937973981134</v>
+        <v>0.307663851038905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1368,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1401,25 +1379,25 @@
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>20.70550141590351</v>
+        <v>25.12941981546301</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5431120659075805</v>
+        <v>0.06684491978610207</v>
       </c>
       <c r="L8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>61.53846153846154</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N8" t="n">
-        <v>16.69895675356172</v>
+        <v>20.50481622935367</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>7.416607444182066</v>
+        <v>7.927855711422849</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1442,12 +1420,8 @@
       <c r="W8" t="n">
         <v>50</v>
       </c>
-      <c r="X8" t="n">
-        <v>26.93179943319606</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>20.27484342649236</v>
-      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
@@ -1456,9 +1430,7 @@
       <c r="AC8" t="n">
         <v>8</v>
       </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
         <v>6</v>
       </c>
@@ -1491,16 +1463,16 @@
         <v>46281</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5355858355426762</v>
+        <v>0.5322975111494749</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1516,25 +1488,25 @@
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>16.06270635736976</v>
+        <v>16.06270761312454</v>
       </c>
       <c r="K9" t="n">
-        <v>2.598425196850385</v>
+        <v>1.968505462520942</v>
       </c>
       <c r="L9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M9" t="n">
-        <v>65</v>
+        <v>69.04761904761905</v>
       </c>
       <c r="N9" t="n">
-        <v>13.04469594544534</v>
+        <v>12.09690303846299</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.03088653436293942</v>
       </c>
       <c r="Q9" t="n">
         <v>35</v>
@@ -1600,7 +1572,7 @@
         <v>46281</v>
       </c>
       <c r="C10" t="n">
-        <v>1.800357605277761</v>
+        <v>1.812688821752266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,25 +1597,25 @@
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>15.6530335535529</v>
+        <v>15.84693462584358</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6896551724137945</v>
+        <v>1.612903225806472</v>
       </c>
       <c r="L10" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M10" t="n">
-        <v>62.22222222222222</v>
+        <v>59.57446808510638</v>
       </c>
       <c r="N10" t="n">
-        <v>13.14065766444598</v>
+        <v>14.35749834603612</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>9.246575342465757</v>
+        <v>8.253968253968246</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1709,21 +1681,21 @@
         <v>46281</v>
       </c>
       <c r="C11" t="n">
-        <v>7.552870090634442</v>
+        <v>7.629940193600099</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1734,25 +1706,25 @@
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>12.26450975949309</v>
+        <v>14.00006857052631</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2728512960436635</v>
+        <v>3.340292275574108</v>
       </c>
       <c r="L11" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M11" t="n">
-        <v>58.92857142857143</v>
+        <v>67.27272727272727</v>
       </c>
       <c r="N11" t="n">
-        <v>13.05241126211816</v>
+        <v>11.73934299894956</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.719727891156465</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>49</v>
@@ -1779,7 +1751,7 @@
         <v>18.41457411414329</v>
       </c>
       <c r="Y11" t="n">
-        <v>12.02512233728161</v>
+        <v>11.12741950398858</v>
       </c>
       <c r="Z11" t="n">
         <v>9</v>
@@ -1828,7 +1800,7 @@
         <v>46281</v>
       </c>
       <c r="C12" t="n">
-        <v>5.281871056579732</v>
+        <v>5.235628994800337</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1845,7 +1817,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>5</v>
       </c>
@@ -1853,25 +1829,25 @@
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>28.93665041580083</v>
+        <v>32.14418072188311</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3.810108529917122</v>
       </c>
       <c r="L12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>66.66666666666667</v>
+        <v>75</v>
       </c>
       <c r="N12" t="n">
-        <v>17.53376341251548</v>
+        <v>10.70734390704826</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>5.000000000000004</v>
+        <v>1.146219271835136</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1937,7 +1913,7 @@
         <v>46281</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1584561316973919</v>
+        <v>0.1557843681279158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,10 +1938,10 @@
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>48.07246356960044</v>
+        <v>50.16034116926631</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2.432432432432408</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1976,7 +1952,7 @@
         <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>6.000000000000005</v>
+        <v>3.482849604221672</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -2030,7 +2006,7 @@
         <v>46281</v>
       </c>
       <c r="C14" t="n">
-        <v>8.359537168341658</v>
+        <v>8.487987339951086</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2090,16 +2066,16 @@
         <v>16.11612055393703</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.152582554288167</v>
+        <v>5.725916643936124</v>
       </c>
       <c r="Z14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>31.81818181818182</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.55046017766063</v>
+        <v>10.32150836367819</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2139,7 +2115,7 @@
         <v>46281</v>
       </c>
       <c r="C15" t="n">
-        <v>12.72170499619788</v>
+        <v>12.96832932568798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,25 +2140,25 @@
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>19.84843937415058</v>
+        <v>20.43348726193051</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4055150040551458</v>
+        <v>3.104575163398704</v>
       </c>
       <c r="L15" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>59.45945945945946</v>
       </c>
       <c r="N15" t="n">
-        <v>15.31727702763958</v>
+        <v>15.72689211894256</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>7.563812600969322</v>
+        <v>4.748019017432648</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2209,7 +2185,7 @@
         <v>33.58229315482664</v>
       </c>
       <c r="Y15" t="n">
-        <v>19.52341276982841</v>
+        <v>17.96328506908193</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2254,7 +2230,7 @@
         <v>46281</v>
       </c>
       <c r="C16" t="n">
-        <v>32.98600406930144</v>
+        <v>33.21207637133404</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2279,25 +2255,25 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>18.74345692981887</v>
+        <v>19.50523702110182</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3124999999999822</v>
+        <v>1.955835962145125</v>
       </c>
       <c r="L16" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="M16" t="n">
-        <v>67.79661016949153</v>
+        <v>69.84126984126983</v>
       </c>
       <c r="N16" t="n">
-        <v>17.58563857375307</v>
+        <v>18.57141401860952</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>9.657320872274177</v>
+        <v>7.889851485148514</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2363,7 +2339,7 @@
         <v>46281</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3664426495673798</v>
+        <v>0.3740468997266581</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2388,13 +2364,13 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>52.97039750800809</v>
+        <v>54.89589441317657</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>6.432748538011679</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2402,7 +2378,7 @@
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>8.000000000000007</v>
+        <v>1.472527472527485</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2468,7 +2444,7 @@
         <v>46281</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06720512978605341</v>
+        <v>0.068643771708079</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2493,25 +2469,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>39.43997479113801</v>
+        <v>40.57193787915413</v>
       </c>
       <c r="K18" t="n">
-        <v>1.869158878504673</v>
+        <v>6.031746031746033</v>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>25</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N18" t="n">
-        <v>16.62570916182737</v>
+        <v>16.73203077467618</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>7.981651376146792</v>
+        <v>3.742514970059885</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2577,16 +2553,16 @@
         <v>46281</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02692315596933638</v>
+        <v>0.0281562776167869</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2594,7 +2570,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>5</v>
       </c>
@@ -2605,22 +2585,22 @@
         <v>16.09778596067288</v>
       </c>
       <c r="K19" t="n">
-        <v>8.264462809917351</v>
+        <v>13.22314049586777</v>
       </c>
       <c r="L19" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
-        <v>72.22222222222223</v>
+        <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>20.75148384367104</v>
+        <v>21.20569232422457</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>1.60305343511451</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>14</v>
@@ -2647,22 +2627,22 @@
         <v>20.26411217973316</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.163718684695432</v>
+        <v>5.003278319108961</v>
       </c>
       <c r="Z19" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AA19" t="n">
-        <v>61.53846153846154</v>
+        <v>43.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>12.33289022678148</v>
+        <v>15.85883430635453</v>
       </c>
       <c r="AC19" t="n">
         <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.9206467979481991</v>
+        <v>5.259888544023461</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -2696,7 +2676,7 @@
         <v>46281</v>
       </c>
       <c r="C20" t="n">
-        <v>1.587644121092546</v>
+        <v>1.59586493207555</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2724,22 +2704,22 @@
         <v>18.49305897009618</v>
       </c>
       <c r="K20" t="n">
-        <v>1.860250145422881</v>
+        <v>2.38768186138627</v>
       </c>
       <c r="L20" t="n">
         <v>32</v>
       </c>
       <c r="M20" t="n">
-        <v>50</v>
+        <v>43.75</v>
       </c>
       <c r="N20" t="n">
-        <v>16.75491869608562</v>
+        <v>16.24437067632598</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>7.991095489119893</v>
+        <v>7.434798796323361</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
@@ -2805,7 +2785,7 @@
         <v>46281</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8549643422323613</v>
+        <v>0.8496208150934091</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2830,25 +2810,25 @@
         <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>13.40952649813111</v>
+        <v>15.40873157782327</v>
       </c>
       <c r="K21" t="n">
-        <v>0.04810004810005264</v>
+        <v>1.772528530197093</v>
       </c>
       <c r="L21" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="M21" t="n">
-        <v>59.01639344262295</v>
+        <v>50</v>
       </c>
       <c r="N21" t="n">
-        <v>16.51602481853923</v>
+        <v>20.47016217413191</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>7.94807692307693</v>
+        <v>6.119010267053704</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2914,7 +2894,7 @@
         <v>46281</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2776578909509423</v>
+        <v>0.2758082084797666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2933,7 +2913,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %90.91: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %90.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2943,25 +2923,25 @@
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>24.38411614496318</v>
+        <v>26.8486338409792</v>
       </c>
       <c r="K22" t="n">
-        <v>0.07407407407407085</v>
+        <v>2.756508422664639</v>
       </c>
       <c r="L22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>90.90909090909091</v>
+        <v>90</v>
       </c>
       <c r="N22" t="n">
-        <v>15.06277595817252</v>
+        <v>19.55279061767296</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>9.918578830495939</v>
+        <v>7.049180327868854</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -3019,7 +2999,7 @@
         <v>46281</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5643586739831885</v>
+        <v>0.5528495386069836</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3044,13 +3024,13 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>44.4397528000775</v>
+        <v>46.2607379394388</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1.28012250295424</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3058,7 +3038,7 @@
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>5.000000000000004</v>
+        <v>3.672860384758381</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3124,7 +3104,7 @@
         <v>46281</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1483856382432127</v>
+        <v>0.1418089894568099</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3149,25 +3129,25 @@
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>24.76563460590212</v>
+        <v>28.72533804769673</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.8771929824561431</v>
       </c>
       <c r="L24" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M24" t="n">
-        <v>71.42857142857143</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N24" t="n">
-        <v>15.88001405187546</v>
+        <v>19.52502691695604</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>10.00000000000001</v>
+        <v>9.043478260869575</v>
       </c>
       <c r="Q24" t="n">
         <v>5</v>
@@ -3233,7 +3213,7 @@
         <v>46281</v>
       </c>
       <c r="C25" t="n">
-        <v>3.224613108083113</v>
+        <v>3.210226688862856</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3258,10 +3238,10 @@
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>22.50725922230536</v>
+        <v>23.0512414485687</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1276324186343381</v>
+        <v>0.385604113110527</v>
       </c>
       <c r="L25" t="n">
         <v>31</v>
@@ -3270,13 +3250,13 @@
         <v>61.29032258064516</v>
       </c>
       <c r="N25" t="n">
-        <v>18.62626097258521</v>
+        <v>19.36314826082585</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>7.862332695984708</v>
+        <v>7.585147247119095</v>
       </c>
       <c r="Q25" t="n">
         <v>44</v>
@@ -3342,7 +3322,7 @@
         <v>46281</v>
       </c>
       <c r="C26" t="n">
-        <v>0.421316562878928</v>
+        <v>0.4258380089195799</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,25 +3347,25 @@
         <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>11.71805290443946</v>
+        <v>12.75362124351463</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1955034213098727</v>
+        <v>2.472802705550636</v>
       </c>
       <c r="L26" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="M26" t="n">
-        <v>51.72413793103448</v>
+        <v>47.69230769230769</v>
       </c>
       <c r="N26" t="n">
-        <v>12.76750693175828</v>
+        <v>14.71710548002947</v>
       </c>
       <c r="O26" t="n">
         <v>6</v>
       </c>
       <c r="P26" t="n">
-        <v>5.793170731707331</v>
+        <v>3.442081412162157</v>
       </c>
       <c r="Q26" t="n">
         <v>32</v>
@@ -3536,16 +3516,16 @@
         <v>46281</v>
       </c>
       <c r="C28" t="n">
-        <v>1.320467764144933</v>
+        <v>1.299915736687424</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3561,25 +3541,25 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>21.20163810401038</v>
+        <v>24.20640147415714</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>2.346279575779486</v>
       </c>
       <c r="L28" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="M28" t="n">
-        <v>65.625</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N28" t="n">
-        <v>14.52939308169286</v>
+        <v>11.2644668141695</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.000000000000002</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>39</v>
@@ -3645,7 +3625,7 @@
         <v>46281</v>
       </c>
       <c r="C29" t="n">
-        <v>0.390488521692665</v>
+        <v>0.3869946770248885</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3673,10 +3653,10 @@
         <v>27.65210909859499</v>
       </c>
       <c r="K29" t="n">
-        <v>17.91752459820786</v>
+        <v>16.86247306232915</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3711,7 +3691,7 @@
         <v>31.20488584758381</v>
       </c>
       <c r="Y29" t="n">
-        <v>10.12718479463592</v>
+        <v>10.93130998331551</v>
       </c>
       <c r="Z29" t="n">
         <v>2</v>
@@ -3756,7 +3736,7 @@
         <v>46281</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3869946770248885</v>
+        <v>0.3839118729062622</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,25 +3761,25 @@
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>16.57045248083407</v>
+        <v>18.38702786494759</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1.411509229098784</v>
       </c>
       <c r="L30" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M30" t="n">
-        <v>57.4468085106383</v>
+        <v>51.11111111111111</v>
       </c>
       <c r="N30" t="n">
-        <v>13.53057890927115</v>
+        <v>15.16909149395723</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>5.000000000000004</v>
+        <v>3.538543897216306</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3826,10 +3806,10 @@
         <v>26.71344279693404</v>
       </c>
       <c r="Y30" t="n">
-        <v>16.57045248083407</v>
+        <v>17.23505323111951</v>
       </c>
       <c r="Z30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
@@ -3871,11 +3851,11 @@
         <v>46281</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2585445054154593</v>
+        <v>0.2388145590562509</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3885,7 +3865,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3928,10 +3908,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="X31" t="n">
-        <v>56.50346662163857</v>
+        <v>56.50346933625374</v>
       </c>
       <c r="Y31" t="n">
-        <v>5.128205128205121</v>
+        <v>12.36802565274163</v>
       </c>
       <c r="Z31" t="n">
         <v>1</v>
@@ -3942,7 +3922,7 @@
         <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>5.135135135135139</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>10</v>
@@ -3976,7 +3956,7 @@
         <v>46281</v>
       </c>
       <c r="C32" t="n">
-        <v>2.217563762665187</v>
+        <v>2.213453357173685</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4001,25 +3981,25 @@
         <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>10.3445718561754</v>
+        <v>10.92675123348043</v>
       </c>
       <c r="K32" t="n">
-        <v>0.09276437847867136</v>
+        <v>0.5602255262104894</v>
       </c>
       <c r="L32" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="M32" t="n">
-        <v>59.52380952380953</v>
+        <v>60.41666666666666</v>
       </c>
       <c r="N32" t="n">
-        <v>9.844195670989331</v>
+        <v>10.74540716100651</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>2.904541241890635</v>
+        <v>2.426182380779962</v>
       </c>
       <c r="Q32" t="n">
         <v>34</v>
@@ -4046,16 +4026,16 @@
         <v>13.38656892008534</v>
       </c>
       <c r="Y32" t="n">
-        <v>10.26140355548538</v>
+        <v>10.42774015686541</v>
       </c>
       <c r="Z32" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA32" t="n">
-        <v>47.36842105263158</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="AB32" t="n">
-        <v>12.42255677564395</v>
+        <v>12.53034342436907</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
@@ -4095,7 +4075,7 @@
         <v>46281</v>
       </c>
       <c r="C33" t="n">
-        <v>1.708901083091847</v>
+        <v>1.730480711922231</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4104,7 +4084,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4119,17 +4099,27 @@
       <c r="I33" t="n">
         <v>10</v>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>10.21266957407478</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.184466019417486</v>
+      </c>
       <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="M33" t="n">
+        <v>45.83333333333334</v>
+      </c>
+      <c r="N33" t="n">
+        <v>11.67431254712018</v>
+      </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>1.776722090261273</v>
+      </c>
       <c r="Q33" t="n">
         <v>39</v>
       </c>
@@ -4155,16 +4145,16 @@
         <v>15.09663082780621</v>
       </c>
       <c r="Y33" t="n">
-        <v>9.395430522867954</v>
+        <v>8.251295851178364</v>
       </c>
       <c r="Z33" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AA33" t="n">
-        <v>36.8421052631579</v>
+        <v>31.81818181818182</v>
       </c>
       <c r="AB33" t="n">
-        <v>13.12165164905662</v>
+        <v>13.6135716205669</v>
       </c>
       <c r="AC33" t="n">
         <v>8</v>
@@ -4204,7 +4194,7 @@
         <v>46281</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7505600427482172</v>
+        <v>0.7448054750601147</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4229,25 +4219,25 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>15.64008867377167</v>
+        <v>17.90633629163635</v>
       </c>
       <c r="K34" t="n">
-        <v>0.1096491228070207</v>
+        <v>2.084507042253536</v>
       </c>
       <c r="L34" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="M34" t="n">
-        <v>60.41666666666666</v>
+        <v>60.52631578947368</v>
       </c>
       <c r="N34" t="n">
-        <v>12.46911694790377</v>
+        <v>12.10887200520458</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>3.886089813800653</v>
+        <v>1.876379690949226</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4418,7 +4408,7 @@
         <v>46281</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07439833939618144</v>
+        <v>0.07419281912160634</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4443,25 +4433,25 @@
         <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>14.73897609331452</v>
+        <v>16.15214364858043</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1.404496091086993</v>
       </c>
       <c r="L36" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M36" t="n">
-        <v>57.57575757575758</v>
+        <v>62.5</v>
       </c>
       <c r="N36" t="n">
-        <v>19.03482611313982</v>
+        <v>16.8750525091739</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>2.000000000000002</v>
+        <v>0.5872559224376905</v>
       </c>
       <c r="Q36" t="n">
         <v>10</v>
@@ -4527,7 +4517,7 @@
         <v>46281</v>
       </c>
       <c r="C37" t="n">
-        <v>0.05322975111494749</v>
+        <v>0.05405183221324784</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4552,25 +4542,25 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>27.2137581173432</v>
+        <v>28.05684368632165</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>2.734377407836974</v>
       </c>
       <c r="L37" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M37" t="n">
-        <v>65.21739130434783</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N37" t="n">
-        <v>15.26345636643157</v>
+        <v>16.09802536859771</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>10.00000000000001</v>
+        <v>7.072240836501908</v>
       </c>
       <c r="Q37" t="n">
         <v>27</v>
@@ -4636,11 +4626,11 @@
         <v>46281</v>
       </c>
       <c r="C38" t="n">
-        <v>1.569147296380788</v>
+        <v>1.570174897753664</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4650,7 +4640,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -4661,25 +4651,25 @@
         <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>10.434951519417</v>
+        <v>11.25665100789579</v>
       </c>
       <c r="K38" t="n">
-        <v>0.0655307994757548</v>
+        <v>1.058203103426592</v>
       </c>
       <c r="L38" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="M38" t="n">
-        <v>50</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N38" t="n">
-        <v>13.08051447380508</v>
+        <v>12.82041562218495</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>9.92796332678456</v>
+        <v>8.84816533638746</v>
       </c>
       <c r="Q38" t="n">
         <v>42</v>
@@ -4702,27 +4692,17 @@
       <c r="W38" t="n">
         <v>57.57575757575758</v>
       </c>
-      <c r="X38" t="n">
-        <v>12.11239445105858</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>10.37625882709683</v>
-      </c>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>56</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>9.664004665137515</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
         <v>10</v>
       </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="n">
         <v>30</v>
       </c>
@@ -4755,7 +4735,7 @@
         <v>46281</v>
       </c>
       <c r="C39" t="n">
-        <v>2.50940255256181</v>
+        <v>2.521733769036316</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4780,25 +4760,25 @@
         <v>10</v>
       </c>
       <c r="J39" t="n">
-        <v>12.14112876653433</v>
+        <v>12.93329891699999</v>
       </c>
       <c r="K39" t="n">
-        <v>0.08196721311475308</v>
+        <v>1.488833746898255</v>
       </c>
       <c r="L39" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M39" t="n">
-        <v>57.37704918032787</v>
+        <v>55.88235294117647</v>
       </c>
       <c r="N39" t="n">
-        <v>15.00145829369855</v>
+        <v>16.01350623743097</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
       </c>
       <c r="P39" t="n">
-        <v>4.91400491400491</v>
+        <v>3.459657701711505</v>
       </c>
       <c r="Q39" t="n">
         <v>42</v>
@@ -4864,7 +4844,7 @@
         <v>46281</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2172349302258668</v>
+        <v>0.2063423556733872</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4889,25 +4869,25 @@
         <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>17.64094015586989</v>
+        <v>22.08645938444355</v>
       </c>
       <c r="K40" t="n">
-        <v>0.09469696969697239</v>
+        <v>0.5005028143258761</v>
       </c>
       <c r="L40" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M40" t="n">
-        <v>69.56521739130434</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N40" t="n">
-        <v>12.63184100263632</v>
+        <v>17.989535017136</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>2.90255439924314</v>
+        <v>2.487049433266941</v>
       </c>
       <c r="Q40" t="n">
         <v>29</v>
@@ -4934,7 +4914,7 @@
         <v>33.58584893257701</v>
       </c>
       <c r="Y40" t="n">
-        <v>17.56294862192659</v>
+        <v>21.69649992092175</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -5088,7 +5068,7 @@
         <v>46281</v>
       </c>
       <c r="C42" t="n">
-        <v>3.206116283371355</v>
+        <v>3.210226688862856</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5102,7 +5082,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -5113,25 +5093,25 @@
         <v>10</v>
       </c>
       <c r="J42" t="n">
-        <v>17.9384880883827</v>
+        <v>18.42777866747934</v>
       </c>
       <c r="K42" t="n">
-        <v>1.022705051456807</v>
+        <v>1.758957654723114</v>
       </c>
       <c r="L42" t="n">
         <v>9</v>
       </c>
       <c r="M42" t="n">
-        <v>55.55555555555556</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="N42" t="n">
-        <v>9.114480682038684</v>
+        <v>9.043407489538058</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
       </c>
       <c r="P42" t="n">
-        <v>0.9674012867160853</v>
+        <v>0.2368758002560867</v>
       </c>
       <c r="Q42" t="n">
         <v>2</v>
@@ -5152,27 +5132,17 @@
         <v>0</v>
       </c>
       <c r="W42" t="inlineStr"/>
-      <c r="X42" t="n">
-        <v>16.97972319726071</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>13.64084108738733</v>
-      </c>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>10.9831920577776</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="n">
         <v>1</v>
       </c>
@@ -5203,7 +5173,7 @@
         <v>46281</v>
       </c>
       <c r="C43" t="n">
-        <v>5.857327825389975</v>
+        <v>5.852189818525598</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5220,7 +5190,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H43" t="n">
         <v>5</v>
       </c>
@@ -5228,25 +5202,25 @@
         <v>10</v>
       </c>
       <c r="J43" t="n">
-        <v>21.98720228799464</v>
+        <v>26.64468274841287</v>
       </c>
       <c r="K43" t="n">
-        <v>0.08779631255486642</v>
+        <v>6.349206349206349</v>
       </c>
       <c r="L43" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M43" t="n">
-        <v>73.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="N43" t="n">
-        <v>20.75042084683509</v>
+        <v>13.55676570531921</v>
       </c>
       <c r="O43" t="n">
         <v>10</v>
       </c>
       <c r="P43" t="n">
-        <v>9.903508771929847</v>
+        <v>3.43283582089553</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5312,7 +5286,7 @@
         <v>46281</v>
       </c>
       <c r="C44" t="n">
-        <v>4.186447993094519</v>
+        <v>4.075467044823973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5329,11 +5303,7 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>5</v>
       </c>
@@ -5344,22 +5314,22 @@
         <v>25.16666033456245</v>
       </c>
       <c r="K44" t="n">
-        <v>9.004979757844067</v>
+        <v>6.115304300346014</v>
       </c>
       <c r="L44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M44" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="N44" t="n">
-        <v>11.53225155181918</v>
+        <v>13.63613675790799</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>0.9128209044819702</v>
+        <v>3.660825104603993</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5386,10 +5356,10 @@
         <v>28.18267712431886</v>
       </c>
       <c r="Y44" t="n">
-        <v>14.96122393190085</v>
+        <v>17.2155655655176</v>
       </c>
       <c r="Z44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr"/>
@@ -5448,25 +5418,25 @@
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>17.98787203625159</v>
+        <v>19.6788445923302</v>
       </c>
       <c r="K45" t="n">
-        <v>1.030927835051543</v>
+        <v>3.157895822714685</v>
       </c>
       <c r="L45" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="M45" t="n">
-        <v>63.76811594202898</v>
+        <v>56</v>
       </c>
       <c r="N45" t="n">
-        <v>15.08347746403951</v>
+        <v>15.35542289931829</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>8.87755102040817</v>
+        <v>6.632651938775536</v>
       </c>
       <c r="Q45" t="n">
         <v>38</v>
@@ -5641,7 +5611,7 @@
         <v>46281</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9162093840557372</v>
+        <v>0.9408718170047476</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5666,25 +5636,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>18.51674922473283</v>
+        <v>18.95621252985475</v>
       </c>
       <c r="K47" t="n">
-        <v>0.1797752808988751</v>
+        <v>3.434256072515818</v>
       </c>
       <c r="L47" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="M47" t="n">
-        <v>53.48837209302326</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N47" t="n">
-        <v>15.51365073068472</v>
+        <v>14.42991978913006</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>9.802602063705713</v>
+        <v>6.347746072520755</v>
       </c>
       <c r="Q47" t="n">
         <v>51</v>
@@ -5711,7 +5681,7 @@
         <v>66.65983471422588</v>
       </c>
       <c r="Y47" t="n">
-        <v>18.37026248176607</v>
+        <v>16.17296133726447</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -5756,7 +5726,7 @@
         <v>46281</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05179110919292189</v>
+        <v>0.05096902809462154</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5781,25 +5751,25 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>18.24241747791605</v>
+        <v>21.81120084197526</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>2.904564315352687</v>
       </c>
       <c r="L48" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M48" t="n">
-        <v>53.65853658536585</v>
+        <v>60.52631578947368</v>
       </c>
       <c r="N48" t="n">
-        <v>13.9571117606342</v>
+        <v>16.8766366077258</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>10.00000000000001</v>
+        <v>6.895161290322593</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5865,7 +5835,7 @@
         <v>46281</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2616273095340856</v>
+        <v>0.2612162689849354</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5890,25 +5860,25 @@
         <v>10</v>
       </c>
       <c r="J49" t="n">
-        <v>14.10636998322745</v>
+        <v>16.33474246007769</v>
       </c>
       <c r="K49" t="n">
-        <v>0.07861635220125507</v>
+        <v>2.582728006456825</v>
       </c>
       <c r="L49" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="M49" t="n">
-        <v>51.72413793103448</v>
+        <v>52.38095238095238</v>
       </c>
       <c r="N49" t="n">
-        <v>16.40172216933395</v>
+        <v>18.5149054643229</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>4.917517674783989</v>
+        <v>2.356412273800168</v>
       </c>
       <c r="Q49" t="n">
         <v>54</v>
@@ -5935,7 +5905,7 @@
         <v>22.46912765663718</v>
       </c>
       <c r="Y49" t="n">
-        <v>14.03884354453501</v>
+        <v>14.17389642191988</v>
       </c>
       <c r="Z49" t="n">
         <v>5</v>
@@ -5984,11 +5954,11 @@
         <v>46281</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6728733789588344</v>
+        <v>0.6835604332367388</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5998,7 +5968,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -6009,25 +5979,25 @@
         <v>10</v>
       </c>
       <c r="J50" t="n">
-        <v>12.8686768057203</v>
+        <v>13.72133807245333</v>
       </c>
       <c r="K50" t="n">
-        <v>0.122324159021403</v>
+        <v>2.717726991970326</v>
       </c>
       <c r="L50" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M50" t="n">
-        <v>43.13725490196079</v>
+        <v>56.36363636363637</v>
       </c>
       <c r="N50" t="n">
-        <v>15.83755344260452</v>
+        <v>15.29437605280425</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>3.872938301771534</v>
+        <v>1.248346361996422</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6050,27 +6020,17 @@
       <c r="W50" t="n">
         <v>70</v>
       </c>
-      <c r="X50" t="n">
-        <v>15.51990994893744</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>12.76209414737869</v>
-      </c>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>61.11111111111111</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>10.07845826280632</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
         <v>5</v>
       </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="n">
         <v>42</v>
       </c>
@@ -6103,7 +6063,7 @@
         <v>46281</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1272170499619788</v>
+        <v>0.1229011241959019</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6120,7 +6080,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H51" t="n">
         <v>5</v>
       </c>
@@ -6128,25 +6092,25 @@
         <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>34.6913652262994</v>
+        <v>37.32903222039072</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>0.6734006734006703</v>
       </c>
       <c r="L51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M51" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N51" t="n">
-        <v>11.3137049812576</v>
+        <v>10.69605849893178</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>4.000000000000004</v>
+        <v>3.304347826086973</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6212,7 +6176,7 @@
         <v>46281</v>
       </c>
       <c r="C52" t="n">
-        <v>4.289208130382062</v>
+        <v>4.328256982551329</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6237,25 +6201,25 @@
         <v>10</v>
       </c>
       <c r="J52" t="n">
-        <v>10.59426908048242</v>
+        <v>11.87945099445477</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>2.382111386803287</v>
       </c>
       <c r="L52" t="n">
         <v>52</v>
       </c>
       <c r="M52" t="n">
-        <v>51.92307692307692</v>
+        <v>55.76923076923077</v>
       </c>
       <c r="N52" t="n">
-        <v>12.51408749990823</v>
+        <v>11.51371376542996</v>
       </c>
       <c r="O52" t="n">
         <v>10</v>
       </c>
       <c r="P52" t="n">
-        <v>10.00000000000001</v>
+        <v>7.440644180911704</v>
       </c>
       <c r="Q52" t="n">
         <v>37</v>
@@ -6282,16 +6246,16 @@
         <v>16.62696858241317</v>
       </c>
       <c r="Y52" t="n">
-        <v>10.59426908048242</v>
+        <v>9.780321362480093</v>
       </c>
       <c r="Z52" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA52" t="n">
-        <v>60</v>
+        <v>68.75</v>
       </c>
       <c r="AB52" t="n">
-        <v>10.6073227052388</v>
+        <v>11.61629564000714</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
@@ -6331,7 +6295,7 @@
         <v>46281</v>
       </c>
       <c r="C53" t="n">
-        <v>1.08925745524796</v>
+        <v>1.069733029163327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6348,11 +6312,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>5</v>
       </c>
@@ -6360,25 +6320,25 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>36.62124177673712</v>
+        <v>39.61080584387218</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>3.06930693069305</v>
       </c>
       <c r="L53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M53" t="n">
-        <v>75</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N53" t="n">
-        <v>17.89336423299012</v>
+        <v>28.71403390950369</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>8.000000000000007</v>
+        <v>4.783861671469758</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6433,10 +6393,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0688822731783804</v>
+        <v>0.06782168958217728</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6461,25 +6421,25 @@
         <v>10</v>
       </c>
       <c r="J54" t="n">
-        <v>29.5817777621179</v>
+        <v>28.93741561274367</v>
       </c>
       <c r="K54" t="n">
-        <v>9.742106234407544</v>
+        <v>8.052401869053893</v>
       </c>
       <c r="L54" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M54" t="n">
-        <v>62.5</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N54" t="n">
-        <v>21.17993563330084</v>
+        <v>21.66831939456864</v>
       </c>
       <c r="O54" t="n">
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>0.2349998322809688</v>
+        <v>1.802457046078776</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6506,16 +6466,16 @@
         <v>14.75410024187049</v>
       </c>
       <c r="Y54" t="n">
-        <v>4.367594706332067</v>
+        <v>5.840051343430197</v>
       </c>
       <c r="Z54" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="AA54" t="n">
-        <v>45.71428571428572</v>
+        <v>41.37931034482759</v>
       </c>
       <c r="AB54" t="n">
-        <v>14.64885266050554</v>
+        <v>14.56659153746906</v>
       </c>
       <c r="AC54" t="n">
         <v>2</v>
@@ -6555,7 +6515,7 @@
         <v>46281</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8590747477238629</v>
+        <v>0.8475656123476581</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6580,25 +6540,25 @@
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>14.05155459679566</v>
+        <v>18.57516013239783</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>4.14141816505984</v>
       </c>
       <c r="L55" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="M55" t="n">
-        <v>69.6969696969697</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N55" t="n">
-        <v>13.86156641913514</v>
+        <v>13.26859523904215</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>6.000000000000005</v>
+        <v>1.784671140155192</v>
       </c>
       <c r="Q55" t="n">
         <v>45</v>
@@ -6625,13 +6585,13 @@
         <v>23.0932342837701</v>
       </c>
       <c r="Y55" t="n">
-        <v>14.05155459679566</v>
+        <v>15.20301702325007</v>
       </c>
       <c r="Z55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA55" t="n">
-        <v>20</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB55" t="n">
         <v>33.66794265572751</v>
@@ -6699,10 +6659,10 @@
         <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>60.74509292931025</v>
+        <v>60.7450942444783</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>3.350327859585889e-06</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
@@ -6713,7 +6673,7 @@
         <v>4</v>
       </c>
       <c r="P56" t="n">
-        <v>4.000000000000004</v>
+        <v>3.999996515659143</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -6763,7 +6723,7 @@
         <v>46281</v>
       </c>
       <c r="C57" t="n">
-        <v>1.301970939433175</v>
+        <v>1.288612121585795</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6782,7 +6742,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.32: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.88: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -6795,22 +6755,22 @@
         <v>15.383288100876</v>
       </c>
       <c r="K57" t="n">
-        <v>1.036682615629969</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="M57" t="n">
-        <v>76.31578947368421</v>
+        <v>80.88235294117646</v>
       </c>
       <c r="N57" t="n">
-        <v>18.45964007932752</v>
+        <v>17.1163048611607</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>8.871349644830339</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q57" t="n">
         <v>30</v>
@@ -6837,17 +6797,13 @@
         <v>20.62560129901716</v>
       </c>
       <c r="Y57" t="n">
-        <v>14.50608135870008</v>
+        <v>15.383288100876</v>
       </c>
       <c r="Z57" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>8.197595571501115</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
         <v>5</v>
       </c>
@@ -6886,16 +6842,16 @@
         <v>46281</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6588980002877285</v>
+        <v>0.7061676634399984</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6903,11 +6859,7 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %86.67: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6918,22 +6870,22 @@
         <v>18.04392839464337</v>
       </c>
       <c r="K58" t="n">
-        <v>0.9931630849050022</v>
+        <v>8.238461746641779</v>
       </c>
       <c r="L58" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="M58" t="n">
-        <v>86.66666666666667</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N58" t="n">
-        <v>18.10016703499304</v>
+        <v>26.9204158835382</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>6.937931936248343</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>25</v>
@@ -6960,13 +6912,17 @@
         <v>20.50322102897642</v>
       </c>
       <c r="Y58" t="n">
-        <v>16.19048667535616</v>
+        <v>10.17795140877224</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA58" t="inlineStr"/>
-      <c r="AB58" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>7.890987522049663</v>
+      </c>
       <c r="AC58" t="n">
         <v>6</v>
       </c>
@@ -7005,7 +6961,7 @@
         <v>46281</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7020572579484966</v>
+        <v>0.7090449472840497</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7030,25 +6986,25 @@
         <v>10</v>
       </c>
       <c r="J59" t="n">
-        <v>15.57699197827031</v>
+        <v>17.60353959471696</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>3.479304139172146</v>
       </c>
       <c r="L59" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M59" t="n">
-        <v>64.86486486486487</v>
+        <v>65.71428571428571</v>
       </c>
       <c r="N59" t="n">
-        <v>15.09409045457231</v>
+        <v>14.80449329782947</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>8.000000000000007</v>
+        <v>4.368695652173948</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7114,7 +7070,7 @@
         <v>46281</v>
       </c>
       <c r="C60" t="n">
-        <v>10.37877386604189</v>
+        <v>10.44042994841441</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7133,7 +7089,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %91.67: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -7143,25 +7099,25 @@
         <v>10</v>
       </c>
       <c r="J60" t="n">
-        <v>26.45170267216481</v>
+        <v>27.03599897665605</v>
       </c>
       <c r="K60" t="n">
-        <v>0.2979145978152964</v>
+        <v>1.701701701701697</v>
       </c>
       <c r="L60" t="n">
         <v>12</v>
       </c>
       <c r="M60" t="n">
-        <v>83.33333333333333</v>
+        <v>91.66666666666667</v>
       </c>
       <c r="N60" t="n">
-        <v>15.16915044561204</v>
+        <v>13.35433234994239</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>7.679207920792086</v>
+        <v>6.192913385826793</v>
       </c>
       <c r="Q60" t="n">
         <v>46</v>
@@ -7256,10 +7212,10 @@
         <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>22.76306834761157</v>
+        <v>22.76307005464179</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>2.210121774481877e-06</v>
       </c>
       <c r="L61" t="n">
         <v>25</v>
@@ -7274,7 +7230,7 @@
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>10.00000000000001</v>
+        <v>9.999997568866114</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
@@ -7346,7 +7302,7 @@
         <v>46281</v>
       </c>
       <c r="C62" t="n">
-        <v>8.606161497831762</v>
+        <v>8.601023490967384</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7406,13 +7362,13 @@
         <v>11.23299668900593</v>
       </c>
       <c r="Y62" t="n">
-        <v>7.909430396210581</v>
+        <v>7.964409840750175</v>
       </c>
       <c r="Z62" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA62" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB62" t="n">
         <v>15.74253410400235</v>
@@ -7455,7 +7411,7 @@
         <v>46281</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1027601372875434</v>
+        <v>0.1019380561892431</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7480,25 +7436,25 @@
         <v>10</v>
       </c>
       <c r="J63" t="n">
-        <v>16.41989617820666</v>
+        <v>17.75986027495195</v>
       </c>
       <c r="K63" t="n">
-        <v>0.2004008016031955</v>
+        <v>1.018333024999984</v>
       </c>
       <c r="L63" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M63" t="n">
-        <v>70.58823529411765</v>
+        <v>68.75</v>
       </c>
       <c r="N63" t="n">
-        <v>14.62524216558815</v>
+        <v>17.27832568856377</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>4.790000000000005</v>
+        <v>3.941529082661299</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7525,7 +7481,7 @@
         <v>24.85614965143601</v>
       </c>
       <c r="Y63" t="n">
-        <v>16.25240098016699</v>
+        <v>16.92238177232566</v>
       </c>
       <c r="Z63" t="n">
         <v>1</v>
@@ -7570,16 +7526,16 @@
         <v>46281</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1368765028670078</v>
+        <v>0.1494132396160881</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7595,25 +7551,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>17.51556939038839</v>
+        <v>18.13575431954985</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1503759398496118</v>
+        <v>10.15151682047753</v>
       </c>
       <c r="L64" t="n">
+        <v>22</v>
+      </c>
+      <c r="M64" t="n">
         <v>50</v>
       </c>
-      <c r="M64" t="n">
-        <v>62</v>
-      </c>
       <c r="N64" t="n">
-        <v>15.0347270041972</v>
+        <v>18.82919173036433</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>4.842342342342354</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>55</v>
@@ -7679,7 +7635,7 @@
         <v>46281</v>
       </c>
       <c r="C65" t="n">
-        <v>6.129642189201965</v>
+        <v>6.170746244116983</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7704,25 +7660,25 @@
         <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>13.4368745754897</v>
+        <v>14.82130166561233</v>
       </c>
       <c r="K65" t="n">
-        <v>0.4208754208754106</v>
+        <v>2.73738237810095</v>
       </c>
       <c r="L65" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="M65" t="n">
-        <v>61.01694915254237</v>
+        <v>60.78431372549019</v>
       </c>
       <c r="N65" t="n">
-        <v>12.31614180669804</v>
+        <v>11.98322223955101</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>9.538977367979907</v>
+        <v>7.069109075770186</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7749,13 +7705,13 @@
         <v>24.47056390537039</v>
       </c>
       <c r="Y65" t="n">
-        <v>13.07255165703637</v>
+        <v>12.48963498751103</v>
       </c>
       <c r="Z65" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA65" t="n">
-        <v>60</v>
+        <v>37.5</v>
       </c>
       <c r="AB65" t="n">
         <v>15.0813486974636</v>
@@ -7798,7 +7754,7 @@
         <v>46281</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4135067924450748</v>
+        <v>0.4089853464044228</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7823,25 +7779,25 @@
         <v>10</v>
       </c>
       <c r="J66" t="n">
-        <v>14.6895074495094</v>
+        <v>16.7692159743721</v>
       </c>
       <c r="K66" t="n">
-        <v>0.09950248756218638</v>
+        <v>1.478837327893934</v>
       </c>
       <c r="L66" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="M66" t="n">
-        <v>58.62068965517241</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N66" t="n">
-        <v>16.70958532438158</v>
+        <v>17.4651299818803</v>
       </c>
       <c r="O66" t="n">
         <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>5.894632206759454</v>
+        <v>4.455276381909545</v>
       </c>
       <c r="Q66" t="n">
         <v>35</v>
@@ -7907,7 +7863,7 @@
         <v>46281</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02548451404731077</v>
+        <v>0.0250734734981606</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7932,25 +7888,25 @@
         <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>13.6175442619109</v>
+        <v>16.40407509217184</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1.666666666666661</v>
       </c>
       <c r="L67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M67" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N67" t="n">
-        <v>7.039793197149025</v>
+        <v>8.929437427954834</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>4.000000000000004</v>
+        <v>2.295081967213131</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -8101,7 +8057,7 @@
         <v>46281</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4809174425057032</v>
+        <v>0.4747518342684506</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8118,7 +8074,11 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H69" t="n">
         <v>5</v>
       </c>
@@ -8126,19 +8086,19 @@
         <v>10</v>
       </c>
       <c r="J69" t="n">
-        <v>22.270409719336</v>
+        <v>22.2553779663549</v>
       </c>
       <c r="K69" t="n">
-        <v>11.05791000478424</v>
+        <v>9.612893133614753</v>
       </c>
       <c r="L69" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M69" t="n">
-        <v>66.66666666666667</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N69" t="n">
-        <v>26.02810049796746</v>
+        <v>32.4160653623916</v>
       </c>
       <c r="O69" t="n">
         <v>8</v>
@@ -8163,10 +8123,10 @@
         <v>45.36848923911108</v>
       </c>
       <c r="Y69" t="n">
-        <v>13.67514157901266</v>
+        <v>14.78187053312787</v>
       </c>
       <c r="Z69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA69" t="inlineStr"/>
       <c r="AB69" t="inlineStr"/>
@@ -8200,7 +8160,7 @@
         <v>46281</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4431017119838872</v>
+        <v>0.4344698604517336</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8225,25 +8185,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>19.83281106624829</v>
+        <v>24.07170695606632</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>3.525954946131238</v>
       </c>
       <c r="L70" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="M70" t="n">
-        <v>56.66666666666666</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="N70" t="n">
-        <v>14.07573250524651</v>
+        <v>13.27357779797516</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>8.000000000000007</v>
+        <v>4.321665089877014</v>
       </c>
       <c r="Q70" t="n">
         <v>31</v>
@@ -8270,7 +8230,7 @@
         <v>44.93251946562029</v>
       </c>
       <c r="Y70" t="n">
-        <v>19.83281106624829</v>
+        <v>21.39450955197072</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -8315,16 +8275,16 @@
         <v>46281</v>
       </c>
       <c r="C71" t="n">
-        <v>2.986209589576012</v>
+        <v>3.000596008796268</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8339,17 +8299,27 @@
       <c r="I71" t="n">
         <v>10</v>
       </c>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="J71" t="n">
+        <v>10.66103530061523</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1.5299026425591</v>
+      </c>
       <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+        <v>73</v>
+      </c>
+      <c r="M71" t="n">
+        <v>49.31506849315068</v>
+      </c>
+      <c r="N71" t="n">
+        <v>17.35900256785373</v>
+      </c>
       <c r="O71" t="n">
         <v>2</v>
       </c>
-      <c r="P71" t="inlineStr"/>
+      <c r="P71" t="n">
+        <v>0.4630136986301547</v>
+      </c>
       <c r="Q71" t="n">
         <v>40</v>
       </c>
@@ -8414,7 +8384,7 @@
         <v>46281</v>
       </c>
       <c r="C72" t="n">
-        <v>0.05590151468442363</v>
+        <v>0.05343527138952258</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8431,7 +8401,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H72" t="n">
         <v>5</v>
       </c>
@@ -8439,25 +8413,25 @@
         <v>10</v>
       </c>
       <c r="J72" t="n">
-        <v>34.21592673330382</v>
+        <v>37.36002064699394</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>0.3861038744205958</v>
       </c>
       <c r="L72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M72" t="n">
-        <v>66.66666666666667</v>
+        <v>75</v>
       </c>
       <c r="N72" t="n">
-        <v>11.70093578531563</v>
+        <v>19.90671805482509</v>
       </c>
       <c r="O72" t="n">
         <v>10</v>
       </c>
       <c r="P72" t="n">
-        <v>10.00000000000001</v>
+        <v>9.576919269230789</v>
       </c>
       <c r="Q72" t="n">
         <v>15</v>
@@ -8523,7 +8497,7 @@
         <v>46281</v>
       </c>
       <c r="C73" t="n">
-        <v>0.05610703495899871</v>
+        <v>0.05528495386069836</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8548,10 +8522,10 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>26.36833828924908</v>
+        <v>28.53397539838882</v>
       </c>
       <c r="K73" t="n">
-        <v>0.3676470588235059</v>
+        <v>1.893939393939381</v>
       </c>
       <c r="L73" t="n">
         <v>12</v>
@@ -8560,13 +8534,13 @@
         <v>58.33333333333334</v>
       </c>
       <c r="N73" t="n">
-        <v>12.93022551610349</v>
+        <v>20.11481107078213</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>9.59706959706963</v>
+        <v>7.95539033457251</v>
       </c>
       <c r="Q73" t="n">
         <v>14</v>
@@ -8632,7 +8606,7 @@
         <v>46281</v>
       </c>
       <c r="C74" t="n">
-        <v>5.163696898699057</v>
+        <v>4.901658548615822</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8657,19 +8631,19 @@
         <v>10</v>
       </c>
       <c r="J74" t="n">
-        <v>12.95695255939758</v>
+        <v>17.37406242951771</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="M74" t="n">
-        <v>72.61904761904762</v>
+        <v>74.54545454545455</v>
       </c>
       <c r="N74" t="n">
-        <v>18.22953638222469</v>
+        <v>20.47113481513891</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
@@ -8702,16 +8676,16 @@
         <v>24.51464461150628</v>
       </c>
       <c r="Y74" t="n">
-        <v>12.95695255939758</v>
+        <v>17.37406242951771</v>
       </c>
       <c r="Z74" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AA74" t="n">
-        <v>55.55555555555556</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB74" t="n">
-        <v>14.07296724520217</v>
+        <v>30.81122903952395</v>
       </c>
       <c r="AC74" t="n">
         <v>10</v>
@@ -8751,7 +8725,7 @@
         <v>46281</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1066650225044701</v>
+        <v>0.1072815833281953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8768,7 +8742,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>5</v>
       </c>
@@ -8776,25 +8754,25 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>22.00260697397675</v>
+        <v>22.00260850333738</v>
       </c>
       <c r="K75" t="n">
-        <v>1.764705882352935</v>
+        <v>2.352943183391032</v>
       </c>
       <c r="L75" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M75" t="n">
-        <v>62.5</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N75" t="n">
-        <v>14.09467689902224</v>
+        <v>13.65710407480026</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>4.161849710982679</v>
+        <v>3.563216360153265</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8860,7 +8838,7 @@
         <v>46281</v>
       </c>
       <c r="C76" t="n">
-        <v>1.770557165464373</v>
+        <v>1.789053990176131</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8885,25 +8863,25 @@
         <v>10</v>
       </c>
       <c r="J76" t="n">
-        <v>12.84869141767749</v>
+        <v>14.36700844688754</v>
       </c>
       <c r="K76" t="n">
-        <v>0.05807200929153211</v>
+        <v>2.895982948355247</v>
       </c>
       <c r="L76" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M76" t="n">
-        <v>53.57142857142857</v>
+        <v>41.30434782608695</v>
       </c>
       <c r="N76" t="n">
-        <v>14.15038331550346</v>
+        <v>11.86997620926326</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>9.936157864190353</v>
+        <v>6.904076182653651</v>
       </c>
       <c r="Q76" t="n">
         <v>41</v>
@@ -8969,7 +8947,7 @@
         <v>46281</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4398133875906858</v>
+        <v>0.4488562796719897</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8994,25 +8972,25 @@
         <v>10</v>
       </c>
       <c r="J77" t="n">
-        <v>23.12744026695216</v>
+        <v>24.13419034764688</v>
       </c>
       <c r="K77" t="n">
-        <v>0.093545369504211</v>
+        <v>3.507109004739317</v>
       </c>
       <c r="L77" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="M77" t="n">
-        <v>60</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N77" t="n">
-        <v>14.52933807299241</v>
+        <v>13.06574358588145</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>7.899065420560758</v>
+        <v>4.34065934065937</v>
       </c>
       <c r="Q77" t="n">
         <v>27</v>
@@ -9103,10 +9081,10 @@
         <v>10</v>
       </c>
       <c r="J78" t="n">
-        <v>17.68649068927533</v>
+        <v>17.7024064797947</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>7.936507895323075e-07</v>
       </c>
       <c r="L78" t="n">
         <v>54</v>
@@ -9115,13 +9093,13 @@
         <v>72.22222222222223</v>
       </c>
       <c r="N78" t="n">
-        <v>16.56338320758569</v>
+        <v>16.65865179315538</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>4.000000000000004</v>
+        <v>3.999999174603186</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9145,10 +9123,10 @@
         <v>64.1025641025641</v>
       </c>
       <c r="X78" t="n">
-        <v>36.64470585093908</v>
+        <v>36.67113091579677</v>
       </c>
       <c r="Y78" t="n">
-        <v>17.68649068927533</v>
+        <v>17.70240582663919</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -9193,7 +9171,7 @@
         <v>46281</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8290687876359004</v>
+        <v>0.8286577470867502</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9218,25 +9196,25 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>16.77869732005618</v>
+        <v>18.8004344699408</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>2.439024390243905</v>
       </c>
       <c r="L79" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="M79" t="n">
-        <v>60</v>
+        <v>65.51724137931035</v>
       </c>
       <c r="N79" t="n">
-        <v>14.12293353427527</v>
+        <v>10.32872810805917</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>5.000000000000004</v>
+        <v>2.499999999999991</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9263,7 +9241,7 @@
         <v>25.65117214954458</v>
       </c>
       <c r="Y79" t="n">
-        <v>16.77869732005618</v>
+        <v>16.81995726189056</v>
       </c>
       <c r="Z79" t="n">
         <v>0</v>
@@ -9308,7 +9286,7 @@
         <v>46281</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1272170499619788</v>
+        <v>0.1266004891382535</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9333,25 +9311,25 @@
         <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>11.20469085942543</v>
+        <v>13.07558125490144</v>
       </c>
       <c r="K80" t="n">
-        <v>0.3241491085899773</v>
+        <v>1.986755642296401</v>
       </c>
       <c r="L80" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="M80" t="n">
-        <v>49.27536231884058</v>
+        <v>52.38095238095238</v>
       </c>
       <c r="N80" t="n">
-        <v>14.88465411080209</v>
+        <v>15.04851229569683</v>
       </c>
       <c r="O80" t="n">
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>9.644588045234226</v>
+        <v>7.857142142857154</v>
       </c>
       <c r="Q80" t="n">
         <v>39</v>
@@ -9378,16 +9356,16 @@
         <v>16.30078916022812</v>
       </c>
       <c r="Y80" t="n">
-        <v>10.91686165637654</v>
+        <v>11.34860546094984</v>
       </c>
       <c r="Z80" t="n">
         <v>24</v>
       </c>
       <c r="AA80" t="n">
-        <v>50</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="AB80" t="n">
-        <v>17.01162787358019</v>
+        <v>18.0934003197824</v>
       </c>
       <c r="AC80" t="n">
         <v>8</v>
@@ -9427,16 +9405,16 @@
         <v>46281</v>
       </c>
       <c r="C81" t="n">
-        <v>1.163244754094992</v>
+        <v>1.17043796370512</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9451,17 +9429,27 @@
       <c r="I81" t="n">
         <v>10</v>
       </c>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+      <c r="J81" t="n">
+        <v>10.34756831148802</v>
+      </c>
+      <c r="K81" t="n">
+        <v>2.520253427819852</v>
+      </c>
       <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="M81" t="n">
+        <v>53.65853658536585</v>
+      </c>
+      <c r="N81" t="n">
+        <v>13.12025342493991</v>
+      </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
-      <c r="P81" t="inlineStr"/>
+      <c r="P81" t="n">
+        <v>7.295872105355583</v>
+      </c>
       <c r="Q81" t="n">
         <v>32</v>
       </c>
@@ -9487,7 +9475,7 @@
         <v>23.79225853623819</v>
       </c>
       <c r="Y81" t="n">
-        <v>8.652966642780857</v>
+        <v>8.08809982873443</v>
       </c>
       <c r="Z81" t="n">
         <v>8</v>
@@ -9502,7 +9490,7 @@
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.474632845438417</v>
+        <v>2.08014432048842</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9533,10 +9521,10 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C82" t="n">
-        <v>4.62642147097843</v>
+        <v>4.675586246583226</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9561,25 +9549,25 @@
         <v>10</v>
       </c>
       <c r="J82" t="n">
-        <v>17.2477026488152</v>
+        <v>19.38271394011772</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>3.739168643846513</v>
       </c>
       <c r="L82" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M82" t="n">
-        <v>37.5</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N82" t="n">
-        <v>7.805083733293841</v>
+        <v>8.579489435939424</v>
       </c>
       <c r="O82" t="n">
         <v>4</v>
       </c>
       <c r="P82" t="n">
-        <v>4.000000000000004</v>
+        <v>0.2514299657142782</v>
       </c>
       <c r="Q82" t="n">
         <v>8</v>
@@ -9645,7 +9633,7 @@
         <v>46281</v>
       </c>
       <c r="C83" t="n">
-        <v>5.11128922868241</v>
+        <v>5.199662946749697</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9670,25 +9658,25 @@
         <v>10</v>
       </c>
       <c r="J83" t="n">
-        <v>16.3424306726454</v>
+        <v>16.91612217329925</v>
       </c>
       <c r="K83" t="n">
-        <v>0.3227107704719678</v>
+        <v>2.761983401397439</v>
       </c>
       <c r="L83" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="M83" t="n">
-        <v>66</v>
+        <v>58.69565217391305</v>
       </c>
       <c r="N83" t="n">
-        <v>10.61586557916401</v>
+        <v>11.89650719797397</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>9.646160032167273</v>
+        <v>7.043476934782622</v>
       </c>
       <c r="Q83" t="n">
         <v>41</v>
@@ -9754,11 +9742,11 @@
         <v>46281</v>
       </c>
       <c r="C84" t="n">
-        <v>1.945249398853197</v>
+        <v>1.994574264751218</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -9768,7 +9756,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -9779,25 +9767,25 @@
         <v>10</v>
       </c>
       <c r="J84" t="n">
-        <v>13.26443414678632</v>
+        <v>13.58177596213546</v>
       </c>
       <c r="K84" t="n">
-        <v>0.3230866227573292</v>
+        <v>3.244680851063819</v>
       </c>
       <c r="L84" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M84" t="n">
-        <v>57.4074074074074</v>
+        <v>48.07692307692308</v>
       </c>
       <c r="N84" t="n">
-        <v>10.98984806102496</v>
+        <v>11.58387831822891</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>4.661851558484398</v>
+        <v>1.700154559505429</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9820,27 +9808,17 @@
       <c r="W84" t="n">
         <v>56.89655172413793</v>
       </c>
-      <c r="X84" t="n">
-        <v>11.86663135768809</v>
-      </c>
-      <c r="Y84" t="n">
-        <v>10.31902417622717</v>
-      </c>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA84" t="n">
-        <v>43.47826086956522</v>
-      </c>
-      <c r="AB84" t="n">
-        <v>10.28587696493542</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
         <v>2</v>
       </c>
-      <c r="AD84" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD84" t="inlineStr"/>
       <c r="AE84" t="n">
         <v>38</v>
       </c>
@@ -9873,7 +9851,7 @@
         <v>46281</v>
       </c>
       <c r="C85" t="n">
-        <v>5.70318761945866</v>
+        <v>5.728877653780546</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9898,25 +9876,25 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>15.0174071214567</v>
+        <v>15.86185926388125</v>
       </c>
       <c r="K85" t="n">
-        <v>0.2710027100270906</v>
+        <v>1.733576642335755</v>
       </c>
       <c r="L85" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M85" t="n">
-        <v>65.45454545454545</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="N85" t="n">
-        <v>13.72552366474792</v>
+        <v>15.72056805328279</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>7.708108108108136</v>
+        <v>6.159641255605397</v>
       </c>
       <c r="Q85" t="n">
         <v>32</v>
@@ -9982,24 +9960,28 @@
         <v>46281</v>
       </c>
       <c r="C86" t="n">
-        <v>4.500894013194402</v>
+        <v>4.75573915366751</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
+          <t>ÇELİŞKİLİ_BEKLE</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H86" t="n">
         <v>5</v>
       </c>
@@ -10010,22 +9992,22 @@
         <v>18.73514495170452</v>
       </c>
       <c r="K86" t="n">
-        <v>7.963278155703235</v>
+        <v>14.07626742114032</v>
       </c>
       <c r="L86" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="M86" t="n">
-        <v>52.38095238095238</v>
+        <v>100</v>
       </c>
       <c r="N86" t="n">
-        <v>15.60302359565044</v>
+        <v>11.59313326334698</v>
       </c>
       <c r="O86" t="n">
         <v>8</v>
       </c>
       <c r="P86" t="n">
-        <v>0.03401327277576804</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>52</v>
@@ -10052,16 +10034,16 @@
         <v>32.57395859734095</v>
       </c>
       <c r="Y86" t="n">
-        <v>12.26379850137972</v>
+        <v>7.296086635704402</v>
       </c>
       <c r="Z86" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA86" t="n">
-        <v>42.85714285714285</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB86" t="n">
-        <v>9.293216334513348</v>
+        <v>5.489735975290166</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
@@ -10101,7 +10083,7 @@
         <v>46281</v>
       </c>
       <c r="C87" t="n">
-        <v>5.620979509628626</v>
+        <v>5.677497585136774</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10161,16 +10143,16 @@
         <v>15.88967756874082</v>
       </c>
       <c r="Y87" t="n">
-        <v>8.87900299019142</v>
+        <v>7.962795524827715</v>
       </c>
       <c r="Z87" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA87" t="n">
-        <v>43.47826086956522</v>
+        <v>68</v>
       </c>
       <c r="AB87" t="n">
-        <v>10.70588891383947</v>
+        <v>11.57148063067813</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
@@ -10210,7 +10192,7 @@
         <v>46281</v>
       </c>
       <c r="C88" t="n">
-        <v>0.996362291140021</v>
+        <v>0.9922518856485193</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10224,7 +10206,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -10235,25 +10217,25 @@
         <v>10</v>
       </c>
       <c r="J88" t="n">
-        <v>16.8583060727446</v>
+        <v>19.38989550963131</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2213812709373597</v>
+        <v>2.942430703624743</v>
       </c>
       <c r="L88" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M88" t="n">
-        <v>73.07692307692308</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N88" t="n">
-        <v>13.87616080882865</v>
+        <v>16.68482307006266</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
       </c>
       <c r="P88" t="n">
-        <v>2.772480975442715</v>
+        <v>0.05592377796188597</v>
       </c>
       <c r="Q88" t="n">
         <v>34</v>
@@ -10276,23 +10258,17 @@
       <c r="W88" t="n">
         <v>62.0253164556962</v>
       </c>
-      <c r="X88" t="n">
-        <v>22.33299319731812</v>
-      </c>
-      <c r="Y88" t="n">
-        <v>16.67424593404958</v>
-      </c>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="inlineStr"/>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
-      <c r="AD88" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD88" t="inlineStr"/>
       <c r="AE88" t="n">
         <v>33</v>
       </c>
@@ -10325,7 +10301,7 @@
         <v>46281</v>
       </c>
       <c r="C89" t="n">
-        <v>2.057257948496619</v>
+        <v>2.032595515547609</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10350,25 +10326,25 @@
         <v>10</v>
       </c>
       <c r="J89" t="n">
-        <v>12.22837120615282</v>
+        <v>14.11546256812646</v>
       </c>
       <c r="K89" t="n">
-        <v>0.09999999999998899</v>
+        <v>1.07307260747882</v>
       </c>
       <c r="L89" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M89" t="n">
-        <v>61.1764705882353</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N89" t="n">
-        <v>15.99587879436045</v>
+        <v>14.23551475598784</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>3.896103896103909</v>
+        <v>2.895852789484321</v>
       </c>
       <c r="Q89" t="n">
         <v>45</v>
@@ -10395,16 +10371,16 @@
         <v>21.41032003314154</v>
       </c>
       <c r="Y89" t="n">
-        <v>12.14059957735898</v>
+        <v>13.19385912288513</v>
       </c>
       <c r="Z89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AA89" t="n">
-        <v>33.33333333333334</v>
+        <v>40</v>
       </c>
       <c r="AB89" t="n">
-        <v>15.99545050654658</v>
+        <v>20.63598439723828</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
@@ -10444,11 +10420,11 @@
         <v>46281</v>
       </c>
       <c r="C90" t="n">
-        <v>2.605997081612101</v>
+        <v>2.597776270629098</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -10458,7 +10434,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -10469,25 +10445,25 @@
         <v>10</v>
       </c>
       <c r="J90" t="n">
-        <v>16.91371885796505</v>
+        <v>18.7556950036317</v>
       </c>
       <c r="K90" t="n">
-        <v>0.3958828186856778</v>
+        <v>2.348178137651824</v>
       </c>
       <c r="L90" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="M90" t="n">
-        <v>63.9344262295082</v>
+        <v>61.22448979591837</v>
       </c>
       <c r="N90" t="n">
-        <v>15.06571248022794</v>
+        <v>15.50086276685579</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>7.574132492113561</v>
+        <v>5.522151898734173</v>
       </c>
       <c r="Q90" t="n">
         <v>43</v>
@@ -10510,27 +10486,17 @@
       <c r="W90" t="n">
         <v>70.45454545454545</v>
       </c>
-      <c r="X90" t="n">
-        <v>20.63086277737274</v>
-      </c>
-      <c r="Y90" t="n">
-        <v>16.58479454623887</v>
-      </c>
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA90" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="AB90" t="n">
-        <v>32.38665509377456</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
         <v>2</v>
       </c>
-      <c r="AD90" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD90" t="inlineStr"/>
       <c r="AE90" t="n">
         <v>25</v>
       </c>
@@ -10563,16 +10529,16 @@
         <v>46281</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2192901329716177</v>
+        <v>0.2194956532461927</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10587,17 +10553,27 @@
       <c r="I91" t="n">
         <v>10</v>
       </c>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="J91" t="n">
+        <v>10.17169207219154</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1.040684136481751</v>
+      </c>
       <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="M91" t="n">
+        <v>51.61290322580645</v>
+      </c>
+      <c r="N91" t="n">
+        <v>15.39510502908388</v>
+      </c>
       <c r="O91" t="n">
         <v>6</v>
       </c>
-      <c r="P91" t="inlineStr"/>
+      <c r="P91" t="n">
+        <v>4.908236623595519</v>
+      </c>
       <c r="Q91" t="n">
         <v>44</v>
       </c>
@@ -10662,7 +10638,7 @@
         <v>46281</v>
       </c>
       <c r="C92" t="n">
-        <v>1.085147049756459</v>
+        <v>1.078981441519206</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10687,25 +10663,25 @@
         <v>10</v>
       </c>
       <c r="J92" t="n">
-        <v>13.59116935401785</v>
+        <v>15.80678164352948</v>
       </c>
       <c r="K92" t="n">
-        <v>0.2849002849002913</v>
+        <v>2.339182802685746</v>
       </c>
       <c r="L92" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="M92" t="n">
-        <v>57.8125</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="N92" t="n">
-        <v>12.34465699974668</v>
+        <v>13.00975297690628</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>7.693181818181816</v>
+        <v>5.531427008000001</v>
       </c>
       <c r="Q92" t="n">
         <v>44</v>
@@ -10732,17 +10708,13 @@
         <v>21.60407460332612</v>
       </c>
       <c r="Y92" t="n">
-        <v>13.34499034932844</v>
+        <v>13.83734835870725</v>
       </c>
       <c r="Z92" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA92" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="AB92" t="n">
-        <v>22.24427307110499</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA92" t="inlineStr"/>
+      <c r="AB92" t="inlineStr"/>
       <c r="AC92" t="n">
         <v>4</v>
       </c>
@@ -10781,11 +10753,11 @@
         <v>46281</v>
       </c>
       <c r="C93" t="n">
-        <v>0.03945989271841667</v>
+        <v>0.03987093326756685</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -10795,7 +10767,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -10806,25 +10778,25 @@
         <v>10</v>
       </c>
       <c r="J93" t="n">
-        <v>10.21837347371534</v>
+        <v>11.15359968525608</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>2.105264232686999</v>
       </c>
       <c r="L93" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M93" t="n">
-        <v>57.14285714285715</v>
+        <v>57.35294117647059</v>
       </c>
       <c r="N93" t="n">
-        <v>18.9078285838319</v>
+        <v>18.41153557119262</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>6.000000000000005</v>
+        <v>3.814431896907222</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10847,27 +10819,17 @@
       <c r="W93" t="n">
         <v>78.31325301204819</v>
       </c>
-      <c r="X93" t="n">
-        <v>11.4419372600254</v>
-      </c>
-      <c r="Y93" t="n">
-        <v>10.21837347371534</v>
-      </c>
+      <c r="X93" t="inlineStr"/>
+      <c r="Y93" t="inlineStr"/>
       <c r="Z93" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA93" t="n">
-        <v>58.33333333333334</v>
-      </c>
-      <c r="AB93" t="n">
-        <v>13.42669115594144</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA93" t="inlineStr"/>
+      <c r="AB93" t="inlineStr"/>
       <c r="AC93" t="n">
         <v>2</v>
       </c>
-      <c r="AD93" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD93" t="inlineStr"/>
       <c r="AE93" t="n">
         <v>24</v>
       </c>
@@ -10900,7 +10862,7 @@
         <v>46281</v>
       </c>
       <c r="C94" t="n">
-        <v>8.282467065376</v>
+        <v>8.333847134019772</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10960,22 +10922,22 @@
         <v>36.6815048892442</v>
       </c>
       <c r="Y94" t="n">
-        <v>5.060408381855297</v>
+        <v>4.47145309886433</v>
       </c>
       <c r="Z94" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA94" t="n">
-        <v>46.15384615384615</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB94" t="n">
-        <v>13.56192792270044</v>
+        <v>12.58922709873709</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>0.9896731196441522</v>
+        <v>1.600094370447813</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -11006,10 +10968,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1192588684919777</v>
+        <v>0.1140637562940584</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11034,25 +10996,25 @@
         <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>20.4748336450095</v>
+        <v>24.77606696791015</v>
       </c>
       <c r="K95" t="n">
-        <v>0.3460204026532354</v>
+        <v>1.462530220682168</v>
       </c>
       <c r="L95" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="M95" t="n">
-        <v>56</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N95" t="n">
-        <v>19.7967444898251</v>
+        <v>16.35774984253148</v>
       </c>
       <c r="O95" t="n">
         <v>10</v>
       </c>
       <c r="P95" t="n">
-        <v>9.620690046908443</v>
+        <v>8.414406540768059</v>
       </c>
       <c r="Q95" t="n">
         <v>21</v>
@@ -11122,12 +11084,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -11142,17 +11104,27 @@
       <c r="I96" t="n">
         <v>10</v>
       </c>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+      <c r="J96" t="n">
+        <v>10.99197108330091</v>
+      </c>
+      <c r="K96" t="n">
+        <v>2.572900206832274</v>
+      </c>
       <c r="L96" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="M96" t="n">
+        <v>49.20634920634921</v>
+      </c>
+      <c r="N96" t="n">
+        <v>12.8448817714815</v>
+      </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
-      <c r="P96" t="inlineStr"/>
+      <c r="P96" t="n">
+        <v>7.240801204013358</v>
+      </c>
       <c r="Q96" t="n">
         <v>48</v>
       </c>
@@ -11217,7 +11189,7 @@
         <v>46281</v>
       </c>
       <c r="C97" t="n">
-        <v>1.761308753108494</v>
+        <v>1.773639969582999</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11242,25 +11214,25 @@
         <v>10</v>
       </c>
       <c r="J97" t="n">
-        <v>16.16774792949364</v>
+        <v>17.34228334307187</v>
       </c>
       <c r="K97" t="n">
-        <v>0.05837711617044938</v>
+        <v>2.190649043001525</v>
       </c>
       <c r="L97" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M97" t="n">
-        <v>63.04347826086956</v>
+        <v>48.83720930232558</v>
       </c>
       <c r="N97" t="n">
-        <v>13.25261425923628</v>
+        <v>13.4775711360814</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>3.939323220536761</v>
+        <v>1.770564111239881</v>
       </c>
       <c r="Q97" t="n">
         <v>50</v>
@@ -11326,7 +11298,7 @@
         <v>46281</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6642415274266807</v>
+        <v>0.6593090408368786</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11351,25 +11323,25 @@
         <v>10</v>
       </c>
       <c r="J98" t="n">
-        <v>15.29171564364919</v>
+        <v>17.65200939318058</v>
       </c>
       <c r="K98" t="n">
-        <v>0.06191950464398133</v>
+        <v>2.165606331940473</v>
       </c>
       <c r="L98" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="M98" t="n">
-        <v>50.79365079365079</v>
+        <v>51.06382978723404</v>
       </c>
       <c r="N98" t="n">
-        <v>15.64263700001116</v>
+        <v>13.85503513301794</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>9.931930693069301</v>
+        <v>7.66832787406484</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11396,7 +11368,7 @@
         <v>30.85778357900837</v>
       </c>
       <c r="Y98" t="n">
-        <v>15.23926469358333</v>
+        <v>15.86867609437357</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
@@ -11441,7 +11413,7 @@
         <v>46281</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5076350782004645</v>
+        <v>0.5101013214953656</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11466,25 +11438,25 @@
         <v>10</v>
       </c>
       <c r="J99" t="n">
-        <v>13.51503694917485</v>
+        <v>14.07617215145111</v>
       </c>
       <c r="K99" t="n">
-        <v>0.162206001622045</v>
+        <v>1.306122448979607</v>
       </c>
       <c r="L99" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M99" t="n">
-        <v>54.28571428571428</v>
+        <v>52.77777777777778</v>
       </c>
       <c r="N99" t="n">
-        <v>17.07530218036992</v>
+        <v>17.18388695119406</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>3.83157894736843</v>
+        <v>2.659145850120859</v>
       </c>
       <c r="Q99" t="n">
         <v>34</v>
@@ -11511,7 +11483,7 @@
         <v>33.04241514445872</v>
       </c>
       <c r="Y99" t="n">
-        <v>13.3747531486058</v>
+        <v>12.95390174689862</v>
       </c>
       <c r="Z99" t="n">
         <v>0</v>
@@ -11553,24 +11525,24 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C100" t="n">
-        <v>332.7305856366188</v>
+        <v>316.3602287120045</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
+          <t>AL_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t>BAND</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -11580,17 +11552,27 @@
       <c r="I100" t="n">
         <v>10</v>
       </c>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
+      <c r="J100" t="n">
+        <v>14.5380172928869</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1.606827379056286</v>
+      </c>
       <c r="L100" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="M100" t="n">
+        <v>48.07692307692308</v>
+      </c>
+      <c r="N100" t="n">
+        <v>13.92213299672397</v>
+      </c>
       <c r="O100" t="n">
         <v>5</v>
       </c>
-      <c r="P100" t="inlineStr"/>
+      <c r="P100" t="n">
+        <v>3.33951242103554</v>
+      </c>
       <c r="Q100" t="n">
         <v>48</v>
       </c>
@@ -11612,27 +11594,17 @@
       <c r="W100" t="n">
         <v>64.91228070175438</v>
       </c>
-      <c r="X100" t="n">
-        <v>16.86980163304483</v>
-      </c>
-      <c r="Y100" t="n">
-        <v>8.67142136278083</v>
-      </c>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr"/>
       <c r="Z100" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA100" t="n">
-        <v>47.61904761904762</v>
-      </c>
-      <c r="AB100" t="n">
-        <v>9.536647754051197</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr"/>
       <c r="AC100" t="n">
         <v>8</v>
       </c>
-      <c r="AD100" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD100" t="inlineStr"/>
       <c r="AE100" t="n">
         <v>39</v>
       </c>
@@ -11665,7 +11637,7 @@
         <v>46281</v>
       </c>
       <c r="C101" t="n">
-        <v>328.1320262243871</v>
+        <v>329.082968534846</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11674,7 +11646,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -11689,17 +11661,27 @@
       <c r="I101" t="n">
         <v>10</v>
       </c>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
+      <c r="J101" t="n">
+        <v>10.63471966983749</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1.885028830601287</v>
+      </c>
       <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="M101" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="N101" t="n">
+        <v>8.611050456197843</v>
+      </c>
       <c r="O101" t="n">
         <v>2</v>
       </c>
-      <c r="P101" t="inlineStr"/>
+      <c r="P101" t="n">
+        <v>0.1128440269569708</v>
+      </c>
       <c r="Q101" t="n">
         <v>30</v>
       </c>
@@ -11725,16 +11707,16 @@
         <v>12.90626814318425</v>
       </c>
       <c r="Y101" t="n">
-        <v>9.213262679232148</v>
+        <v>8.950158371066264</v>
       </c>
       <c r="Z101" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA101" t="n">
-        <v>61.90476190476191</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="AB101" t="n">
-        <v>11.96512718006614</v>
+        <v>11.64547042777423</v>
       </c>
       <c r="AC101" t="n">
         <v>6</v>
@@ -11771,19 +11753,19 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C102" t="n">
-        <v>399.9794369085047</v>
+        <v>382.3542540127834</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -11798,17 +11780,27 @@
       <c r="I102" t="n">
         <v>10</v>
       </c>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+      <c r="J102" t="n">
+        <v>11.9059086841427</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1.818425143219216</v>
+      </c>
       <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="M102" t="n">
+        <v>50</v>
+      </c>
+      <c r="N102" t="n">
+        <v>9.386884136526934</v>
+      </c>
       <c r="O102" t="n">
         <v>4</v>
       </c>
-      <c r="P102" t="inlineStr"/>
+      <c r="P102" t="n">
+        <v>2.14261304249419</v>
+      </c>
       <c r="Q102" t="n">
         <v>29</v>
       </c>
@@ -11873,7 +11865,7 @@
         <v>46281</v>
       </c>
       <c r="C103" t="n">
-        <v>0.6778058655486363</v>
+        <v>0.6695850545656329</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11898,25 +11890,25 @@
         <v>10</v>
       </c>
       <c r="J103" t="n">
-        <v>14.23010683860694</v>
+        <v>16.98681049994946</v>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>2.067669172932329</v>
       </c>
       <c r="L103" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="M103" t="n">
-        <v>52.45901639344262</v>
+        <v>53.19148936170212</v>
       </c>
       <c r="N103" t="n">
-        <v>14.16461546768283</v>
+        <v>14.70566983010254</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
       </c>
       <c r="P103" t="n">
-        <v>10.00000000000001</v>
+        <v>7.771639042357292</v>
       </c>
       <c r="Q103" t="n">
         <v>43</v>
@@ -11982,21 +11974,21 @@
         <v>46281</v>
       </c>
       <c r="C104" t="n">
-        <v>0.05014694699632119</v>
+        <v>0.05261319029122223</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -12006,17 +11998,27 @@
       <c r="I104" t="n">
         <v>10</v>
       </c>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
+      <c r="J104" t="n">
+        <v>11.00325743953869</v>
+      </c>
+      <c r="K104" t="n">
+        <v>8.474580867566983</v>
+      </c>
       <c r="L104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="M104" t="n">
+        <v>63.63636363636363</v>
+      </c>
+      <c r="N104" t="n">
+        <v>10.25362128503169</v>
+      </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
-      <c r="P104" t="inlineStr"/>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
       <c r="Q104" t="n">
         <v>32</v>
       </c>
@@ -12039,25 +12041,25 @@
         <v>63.23529411764706</v>
       </c>
       <c r="X104" t="n">
-        <v>17.0659971289213</v>
+        <v>17.08863596112118</v>
       </c>
       <c r="Y104" t="n">
-        <v>7.968620743487675</v>
+        <v>3.461156521752007</v>
       </c>
       <c r="Z104" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="AA104" t="n">
-        <v>60.71428571428572</v>
+        <v>51.16279069767442</v>
       </c>
       <c r="AB104" t="n">
-        <v>13.84827315128828</v>
+        <v>13.4459439464976</v>
       </c>
       <c r="AC104" t="n">
         <v>5</v>
       </c>
       <c r="AD104" t="n">
-        <v>0</v>
+        <v>1.594014826368551</v>
       </c>
       <c r="AE104" t="n">
         <v>42</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -670,7 +670,7 @@
         <v>46281</v>
       </c>
       <c r="C2" t="n">
-        <v>0.381034589062211</v>
+        <v>0.3711619877512433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -695,25 +695,25 @@
         <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>21.42119502374098</v>
+        <v>22.33623436483442</v>
       </c>
       <c r="K2" t="n">
-        <v>3.703909766684732</v>
+        <v>2.207130730050921</v>
       </c>
       <c r="L2" t="n">
         <v>20</v>
       </c>
       <c r="M2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="N2" t="n">
-        <v>12.93135588622005</v>
+        <v>12.87005792266073</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>6.071217804112061</v>
+        <v>7.624584717607985</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -736,27 +736,17 @@
       <c r="W2" t="n">
         <v>64.91228070175438</v>
       </c>
-      <c r="X2" t="n">
-        <v>11.79582706077868</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>7.238121052313263</v>
-      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>11.853829196456</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
         <v>10</v>
       </c>
-      <c r="AD2" t="n">
-        <v>2.977385731097903</v>
-      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
         <v>46</v>
       </c>
@@ -789,7 +779,7 @@
         <v>46281</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6835603987093327</v>
+        <v>0.6835463504459698</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,7 +807,7 @@
         <v>16.52890779617068</v>
       </c>
       <c r="K3" t="n">
-        <v>8.729023904085054</v>
+        <v>8.726789348124985</v>
       </c>
       <c r="L3" t="n">
         <v>29</v>
@@ -832,7 +822,7 @@
         <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>1.168939120649282</v>
+        <v>1.171018347463959</v>
       </c>
       <c r="Q3" t="n">
         <v>35</v>
@@ -859,7 +849,7 @@
         <v>17.17248092970491</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.206006870064763</v>
+        <v>7.207913935565402</v>
       </c>
       <c r="Z3" t="n">
         <v>25</v>
@@ -874,7 +864,7 @@
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.010963356241103</v>
+        <v>3.008970034896918</v>
       </c>
       <c r="AE3" t="n">
         <v>34</v>
@@ -908,7 +898,7 @@
         <v>46281</v>
       </c>
       <c r="C4" t="n">
-        <v>1.357461413568449</v>
+        <v>1.324550947428994</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,25 +923,25 @@
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>15.14944887493233</v>
+        <v>18.02299847582851</v>
       </c>
       <c r="K4" t="n">
-        <v>1.615384615384619</v>
+        <v>2.62738853503186</v>
       </c>
       <c r="L4" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="M4" t="n">
-        <v>57.89473684210526</v>
+        <v>50</v>
       </c>
       <c r="N4" t="n">
-        <v>14.47718684331674</v>
+        <v>16.04678991337</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>3.330809992429984</v>
+        <v>2.311869666408062</v>
       </c>
       <c r="Q4" t="n">
         <v>53</v>
@@ -1017,16 +1007,16 @@
         <v>46281</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2164128491275664</v>
+        <v>0.2164084014961568</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1034,11 +1024,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.76: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>5</v>
       </c>
@@ -1046,25 +1032,25 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>20.21576838170645</v>
+        <v>22.20242808709211</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7655520713353958</v>
+        <v>3.336604514229635</v>
       </c>
       <c r="L5" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="M5" t="n">
-        <v>75.75757575757575</v>
+        <v>73.07692307692308</v>
       </c>
       <c r="N5" t="n">
-        <v>11.96651226738573</v>
+        <v>13.19275446866066</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.217472025641021</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>41</v>
@@ -1130,16 +1116,16 @@
         <v>46281</v>
       </c>
       <c r="C6" t="n">
-        <v>1.448917935754362</v>
+        <v>1.377985120637922</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1155,10 +1141,10 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>34.44183977636651</v>
+        <v>34.44318710178523</v>
       </c>
       <c r="K6" t="n">
-        <v>5.145413870246096</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1169,7 +1155,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.000000000000002</v>
       </c>
       <c r="Q6" t="n">
         <v>35</v>
@@ -1235,7 +1221,7 @@
         <v>46281</v>
       </c>
       <c r="C7" t="n">
-        <v>2.186735721478924</v>
+        <v>2.141477249373176</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,7 +1238,11 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>5</v>
       </c>
@@ -1260,25 +1250,25 @@
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>14.18820253397024</v>
+        <v>15.68520386805919</v>
       </c>
       <c r="K7" t="n">
-        <v>3.00096805421104</v>
+        <v>2.660098522167487</v>
       </c>
       <c r="L7" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="M7" t="n">
-        <v>65.07936507936508</v>
+        <v>64.58333333333333</v>
       </c>
       <c r="N7" t="n">
-        <v>12.8957664259746</v>
+        <v>12.83984986580655</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>4.85338345864661</v>
+        <v>5.201535508637245</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1305,16 +1295,16 @@
         <v>18.9234494530097</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.61301790527041</v>
+        <v>13.44234722218491</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AA7" t="n">
-        <v>64.28571428571429</v>
+        <v>75</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.48364838038053</v>
+        <v>9.880102520564243</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1354,7 +1344,7 @@
         <v>46281</v>
       </c>
       <c r="C8" t="n">
-        <v>0.307663851038905</v>
+        <v>0.3074520120021374</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,10 +1369,10 @@
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>25.12941981546301</v>
+        <v>25.1309585260591</v>
       </c>
       <c r="K8" t="n">
-        <v>0.06684491978610207</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>9</v>
@@ -1397,7 +1387,7 @@
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>7.927855711422849</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1463,16 +1453,16 @@
         <v>46281</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5322975111494749</v>
+        <v>0.5232438653458835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1488,25 +1478,25 @@
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>16.06270761312454</v>
+        <v>17.65061537695776</v>
       </c>
       <c r="K9" t="n">
-        <v>1.968505462520942</v>
+        <v>2.1669341894061</v>
       </c>
       <c r="L9" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="M9" t="n">
-        <v>69.04761904761905</v>
+        <v>67.85714285714286</v>
       </c>
       <c r="N9" t="n">
-        <v>12.09690303846299</v>
+        <v>11.67091914406717</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03088653436293942</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>35</v>
@@ -1572,7 +1562,7 @@
         <v>46281</v>
       </c>
       <c r="C10" t="n">
-        <v>1.812688821752266</v>
+        <v>1.774631098688807</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,25 +1587,25 @@
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>15.84693462584358</v>
+        <v>17.73916070770556</v>
       </c>
       <c r="K10" t="n">
-        <v>1.612903225806472</v>
+        <v>1.767825574543314</v>
       </c>
       <c r="L10" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="M10" t="n">
-        <v>59.57446808510638</v>
+        <v>56.09756097560975</v>
       </c>
       <c r="N10" t="n">
-        <v>14.35749834603612</v>
+        <v>17.49959131359964</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>8.253968253968246</v>
+        <v>8.089171974522301</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1681,21 +1671,21 @@
         <v>46281</v>
       </c>
       <c r="C11" t="n">
-        <v>7.629940193600099</v>
+        <v>7.280406099716387</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1706,25 +1696,25 @@
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>14.00006857052631</v>
+        <v>16.81458041053866</v>
       </c>
       <c r="K11" t="n">
-        <v>3.340292275574108</v>
+        <v>1.942446043165469</v>
       </c>
       <c r="L11" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M11" t="n">
-        <v>67.27272727272727</v>
+        <v>72.91666666666667</v>
       </c>
       <c r="N11" t="n">
-        <v>11.73934299894956</v>
+        <v>13.93046486797963</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.037402964008471</v>
       </c>
       <c r="Q11" t="n">
         <v>49</v>
@@ -1747,27 +1737,17 @@
       <c r="W11" t="n">
         <v>61.19402985074627</v>
       </c>
-      <c r="X11" t="n">
-        <v>18.41457411414329</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>11.12741950398858</v>
-      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>44.44444444444444</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>8.086116495739128</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
         <v>2</v>
       </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="n">
         <v>48</v>
       </c>
@@ -1800,7 +1780,7 @@
         <v>46281</v>
       </c>
       <c r="C12" t="n">
-        <v>5.235628994800337</v>
+        <v>5.051584528751696</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1799,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1829,25 +1809,25 @@
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>32.14418072188311</v>
+        <v>32.22852520273922</v>
       </c>
       <c r="K12" t="n">
-        <v>3.810108529917122</v>
+        <v>0.2855977152182998</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
-        <v>75</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N12" t="n">
-        <v>10.70734390704826</v>
+        <v>15.92439245875134</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>1.146219271835136</v>
+        <v>4.700976403580137</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1913,7 +1893,7 @@
         <v>46281</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1557843681279158</v>
+        <v>0.1500267170866044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,10 +1918,10 @@
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>50.16034116926631</v>
+        <v>50.83486051568098</v>
       </c>
       <c r="K13" t="n">
-        <v>2.432432432432408</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1952,7 +1932,7 @@
         <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>3.482849604221672</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -2006,21 +1986,21 @@
         <v>46281</v>
       </c>
       <c r="C14" t="n">
-        <v>8.487987339951086</v>
+        <v>8.318262156274406</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -2030,17 +2010,27 @@
       <c r="I14" t="n">
         <v>10</v>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>10.97787677915245</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.782051282051291</v>
+      </c>
       <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="M14" t="n">
+        <v>56.41025641025641</v>
+      </c>
+      <c r="N14" t="n">
+        <v>10.43669730398746</v>
+      </c>
       <c r="O14" t="n">
         <v>2</v>
       </c>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
       <c r="Q14" t="n">
         <v>41</v>
       </c>
@@ -2066,16 +2056,16 @@
         <v>16.11612055393703</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.725916643936124</v>
+        <v>7.611014426569107</v>
       </c>
       <c r="Z14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA14" t="n">
-        <v>33.33333333333334</v>
+        <v>31.81818181818182</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.32150836367819</v>
+        <v>11.06099760120646</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2115,7 +2105,7 @@
         <v>46281</v>
       </c>
       <c r="C15" t="n">
-        <v>12.96832932568798</v>
+        <v>12.9783386082453</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2140,25 +2130,25 @@
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>20.43348726193051</v>
+        <v>20.43512248147792</v>
       </c>
       <c r="K15" t="n">
-        <v>3.104575163398704</v>
+        <v>3.186274509803932</v>
       </c>
       <c r="L15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M15" t="n">
-        <v>59.45945945945946</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N15" t="n">
-        <v>15.72689211894256</v>
+        <v>16.22817479799679</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>4.748019017432648</v>
+        <v>4.665083135391912</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2185,7 +2175,7 @@
         <v>33.58229315482664</v>
       </c>
       <c r="Y15" t="n">
-        <v>17.96328506908193</v>
+        <v>17.89996707034854</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2230,7 +2220,7 @@
         <v>46281</v>
       </c>
       <c r="C16" t="n">
-        <v>33.21207637133404</v>
+        <v>32.71815528792798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2255,25 +2245,25 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>19.50523702110182</v>
+        <v>20.72571441444857</v>
       </c>
       <c r="K16" t="n">
-        <v>1.955835962145125</v>
+        <v>1.985906470211396</v>
       </c>
       <c r="L16" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="M16" t="n">
-        <v>69.84126984126983</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N16" t="n">
-        <v>18.57141401860952</v>
+        <v>17.28873974926752</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>7.889851485148514</v>
+        <v>7.858040201005045</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2339,7 +2329,7 @@
         <v>46281</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3740468997266581</v>
+        <v>0.3617082494142793</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,13 +2354,13 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>54.89589441317657</v>
+        <v>54.89682137494209</v>
       </c>
       <c r="K17" t="n">
-        <v>6.432748538011679</v>
+        <v>2.923976608187129</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2378,7 +2368,7 @@
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>1.472527472527485</v>
+        <v>4.931818181818204</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2444,7 +2434,7 @@
         <v>46281</v>
       </c>
       <c r="C18" t="n">
-        <v>0.068643771708079</v>
+        <v>0.06740926466357022</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2469,16 +2459,16 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>40.57193787915413</v>
+        <v>40.57315922121754</v>
       </c>
       <c r="K18" t="n">
-        <v>6.031746031746033</v>
+        <v>4.126984126984135</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>33.33333333333334</v>
+        <v>25</v>
       </c>
       <c r="N18" t="n">
         <v>16.73203077467618</v>
@@ -2487,7 +2477,7 @@
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>3.742514970059885</v>
+        <v>5.640243902439024</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2553,7 +2543,7 @@
         <v>46281</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0281562776167869</v>
+        <v>0.02815569896008879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,7 +2572,7 @@
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>16.09778596067288</v>
+        <v>16.09951028584119</v>
       </c>
       <c r="K19" t="n">
         <v>13.22314049586777</v>
@@ -2627,7 +2617,7 @@
         <v>20.26411217973316</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.003278319108961</v>
+        <v>5.005230654216875</v>
       </c>
       <c r="Z19" t="n">
         <v>16</v>
@@ -2642,7 +2632,7 @@
         <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.259888544023461</v>
+        <v>5.257941442651493</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -2676,7 +2666,7 @@
         <v>46281</v>
       </c>
       <c r="C20" t="n">
-        <v>1.59586493207555</v>
+        <v>1.561921986107115</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,25 +2691,25 @@
         <v>10</v>
       </c>
       <c r="J20" t="n">
-        <v>18.49305897009618</v>
+        <v>19.82651786594795</v>
       </c>
       <c r="K20" t="n">
-        <v>2.38768186138627</v>
+        <v>1.876675603217159</v>
       </c>
       <c r="L20" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M20" t="n">
-        <v>43.75</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N20" t="n">
-        <v>16.24437067632598</v>
+        <v>16.04253316628892</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>7.434798796323361</v>
+        <v>7.973684210526333</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
@@ -2785,7 +2775,7 @@
         <v>46281</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8496208150934091</v>
+        <v>0.8294627810431995</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2810,25 +2800,25 @@
         <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>15.40873157782327</v>
+        <v>17.90942004166591</v>
       </c>
       <c r="K21" t="n">
-        <v>1.772528530197093</v>
+        <v>2.38457635717908</v>
       </c>
       <c r="L21" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="M21" t="n">
-        <v>50</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N21" t="n">
-        <v>20.47016217413191</v>
+        <v>15.02069085561023</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>6.119010267053704</v>
+        <v>5.484638255698737</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2894,7 +2884,7 @@
         <v>46281</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2758082084797666</v>
+        <v>0.27765218463562</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,7 +2903,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %90.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2923,25 +2913,25 @@
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>26.8486338409792</v>
+        <v>26.85013721896759</v>
       </c>
       <c r="K22" t="n">
-        <v>2.756508422664639</v>
+        <v>3.44563552833077</v>
       </c>
       <c r="L22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
-        <v>90</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N22" t="n">
-        <v>19.55279061767296</v>
+        <v>23.0527243397274</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>7.049180327868854</v>
+        <v>6.336047372316811</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -2999,7 +2989,7 @@
         <v>46281</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5528495386069836</v>
+        <v>0.5454395988326688</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3024,10 +3014,10 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>46.2607379394388</v>
+        <v>46.54509966186163</v>
       </c>
       <c r="K23" t="n">
-        <v>1.28012250295424</v>
+        <v>0.4542013626040786</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3038,7 +3028,7 @@
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>3.672860384758381</v>
+        <v>4.525244913338367</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3104,7 +3094,7 @@
         <v>46281</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1418089894568099</v>
+        <v>0.1405729787496403</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,25 +3119,25 @@
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>28.72533804769673</v>
+        <v>28.72680285640142</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8771929824561431</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M24" t="n">
-        <v>54.54545454545455</v>
+        <v>70</v>
       </c>
       <c r="N24" t="n">
-        <v>19.52502691695604</v>
+        <v>17.43156237718561</v>
       </c>
       <c r="O24" t="n">
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>9.043478260869575</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>5</v>
@@ -3213,7 +3203,7 @@
         <v>46281</v>
       </c>
       <c r="C25" t="n">
-        <v>3.210226688862856</v>
+        <v>3.144395577294587</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3238,25 +3228,25 @@
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>23.0512414485687</v>
+        <v>26.01993766845922</v>
       </c>
       <c r="K25" t="n">
-        <v>0.385604113110527</v>
+        <v>2.272727272727271</v>
       </c>
       <c r="L25" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="M25" t="n">
-        <v>61.29032258064516</v>
+        <v>73.07692307692308</v>
       </c>
       <c r="N25" t="n">
-        <v>19.36314826082585</v>
+        <v>12.89590990493771</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>7.585147247119095</v>
+        <v>5.600000000000005</v>
       </c>
       <c r="Q25" t="n">
         <v>44</v>
@@ -3322,7 +3312,7 @@
         <v>46281</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4258380089195799</v>
+        <v>0.4208968720457067</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3347,25 +3337,25 @@
         <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>12.75362124351463</v>
+        <v>13.96354607862311</v>
       </c>
       <c r="K26" t="n">
-        <v>2.472802705550636</v>
+        <v>2.708124373119358</v>
       </c>
       <c r="L26" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="M26" t="n">
-        <v>47.69230769230769</v>
+        <v>40.35087719298246</v>
       </c>
       <c r="N26" t="n">
-        <v>14.71710548002947</v>
+        <v>15.23538622738405</v>
       </c>
       <c r="O26" t="n">
         <v>6</v>
       </c>
       <c r="P26" t="n">
-        <v>3.442081412162157</v>
+        <v>3.205078125000016</v>
       </c>
       <c r="Q26" t="n">
         <v>32</v>
@@ -3431,7 +3421,7 @@
         <v>46281</v>
       </c>
       <c r="C27" t="n">
-        <v>50.31136321598126</v>
+        <v>50.31032923671339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3478,7 +3468,7 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>67.77922038036249</v>
+        <v>67.77577224808454</v>
       </c>
       <c r="Y27" t="n">
         <v>12.41502683363148</v>
@@ -3516,16 +3506,16 @@
         <v>46281</v>
       </c>
       <c r="C28" t="n">
-        <v>1.299915736687424</v>
+        <v>1.262896132187924</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3541,25 +3531,25 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>24.20640147415714</v>
+        <v>25.98625046455084</v>
       </c>
       <c r="K28" t="n">
-        <v>2.346279575779486</v>
+        <v>1.822700911350461</v>
       </c>
       <c r="L28" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M28" t="n">
         <v>66.66666666666667</v>
       </c>
       <c r="N28" t="n">
-        <v>11.2644668141695</v>
+        <v>16.70707419789855</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>0.1741253051261049</v>
       </c>
       <c r="Q28" t="n">
         <v>39</v>
@@ -3625,11 +3615,11 @@
         <v>46281</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3869946770248885</v>
+        <v>0.3962349459492787</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3639,10 +3629,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SAT_Güncel_Benzer_Başarı_% %100.00: SAT yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>5</v>
       </c>
@@ -3653,10 +3647,10 @@
         <v>27.65210909859499</v>
       </c>
       <c r="K29" t="n">
-        <v>16.86247306232915</v>
+        <v>19.65279743207695</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3691,18 +3685,22 @@
         <v>31.20488584758381</v>
       </c>
       <c r="Y29" t="n">
-        <v>10.93130998331551</v>
+        <v>8.804617557402949</v>
       </c>
       <c r="Z29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>14.1224438478875</v>
+      </c>
       <c r="AC29" t="n">
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.310792729390087</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3736,7 +3734,7 @@
         <v>46281</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3839118729062622</v>
+        <v>0.3695178593448148</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3761,25 +3759,25 @@
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>18.38702786494759</v>
+        <v>21.04705350921352</v>
       </c>
       <c r="K30" t="n">
-        <v>1.411509229098784</v>
+        <v>0.8978675645342271</v>
       </c>
       <c r="L30" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="M30" t="n">
-        <v>51.11111111111111</v>
+        <v>55.88235294117647</v>
       </c>
       <c r="N30" t="n">
-        <v>15.16909149395723</v>
+        <v>14.51899735127237</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>3.538543897216306</v>
+        <v>4.065628476084537</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3806,10 +3804,10 @@
         <v>26.71344279693404</v>
       </c>
       <c r="Y30" t="n">
-        <v>17.23505323111951</v>
+        <v>20.33816061142867</v>
       </c>
       <c r="Z30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
@@ -3851,7 +3849,7 @@
         <v>46281</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2388145590562509</v>
+        <v>0.2437420362530313</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3908,10 +3906,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="X31" t="n">
-        <v>56.50346933625374</v>
+        <v>56.50025293875822</v>
       </c>
       <c r="Y31" t="n">
-        <v>12.36802565274163</v>
+        <v>10.55807093300479</v>
       </c>
       <c r="Z31" t="n">
         <v>1</v>
@@ -3956,21 +3954,21 @@
         <v>46281</v>
       </c>
       <c r="C32" t="n">
-        <v>2.213453357173685</v>
+        <v>2.180525299025854</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3981,25 +3979,25 @@
         <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>10.92675123348043</v>
+        <v>14.67107717442044</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5602255262104894</v>
+        <v>3.411306042884976</v>
       </c>
       <c r="L32" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="M32" t="n">
-        <v>60.41666666666666</v>
+        <v>59.52380952380953</v>
       </c>
       <c r="N32" t="n">
-        <v>10.74540716100651</v>
+        <v>10.96319618056995</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>2.426182380779962</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>34</v>
@@ -4022,27 +4020,17 @@
       <c r="W32" t="n">
         <v>56.60377358490566</v>
       </c>
-      <c r="X32" t="n">
-        <v>13.38656892008534</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>10.42774015686541</v>
-      </c>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>38.88888888888889</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>12.53034342436907</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="n">
         <v>26</v>
       </c>
@@ -4075,11 +4063,11 @@
         <v>46281</v>
       </c>
       <c r="C33" t="n">
-        <v>1.730480711922231</v>
+        <v>1.666735172016934</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4089,7 +4077,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -4100,25 +4088,25 @@
         <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>10.21266957407478</v>
+        <v>13.64684832148788</v>
       </c>
       <c r="K33" t="n">
-        <v>2.184466019417486</v>
+        <v>2.334384858044158</v>
       </c>
       <c r="L33" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M33" t="n">
-        <v>45.83333333333334</v>
+        <v>50.98039215686274</v>
       </c>
       <c r="N33" t="n">
-        <v>11.67431254712018</v>
+        <v>11.43361381568396</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>1.776722090261273</v>
+        <v>1.627620221948223</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4141,27 +4129,17 @@
       <c r="W33" t="n">
         <v>62.06896551724138</v>
       </c>
-      <c r="X33" t="n">
-        <v>15.09663082780621</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>8.251295851178364</v>
-      </c>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>31.81818181818182</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>13.6135716205669</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
         <v>8</v>
       </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="n">
         <v>29</v>
       </c>
@@ -4194,7 +4172,7 @@
         <v>46281</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7448054750601147</v>
+        <v>0.712729664186773</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4219,25 +4197,25 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>17.90633629163635</v>
+        <v>20.35922049452815</v>
       </c>
       <c r="K34" t="n">
-        <v>2.084507042253536</v>
+        <v>0.6968641114982521</v>
       </c>
       <c r="L34" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="M34" t="n">
-        <v>60.52631578947368</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N34" t="n">
-        <v>12.10887200520458</v>
+        <v>11.39877164871466</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>1.876379690949226</v>
+        <v>3.280276816609007</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4303,7 +4281,7 @@
         <v>46281</v>
       </c>
       <c r="C35" t="n">
-        <v>1.293750128450172</v>
+        <v>1.293723539808459</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4328,7 +4306,7 @@
         <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>42.89164722419473</v>
+        <v>42.89282089250778</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -4408,16 +4386,16 @@
         <v>46281</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07419281912160634</v>
+        <v>0.07193061778124871</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4433,25 +4411,25 @@
         <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>16.15214364858043</v>
+        <v>19.92223104152002</v>
       </c>
       <c r="K36" t="n">
-        <v>1.404496091086993</v>
+        <v>2.941176470588225</v>
       </c>
       <c r="L36" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="M36" t="n">
-        <v>62.5</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="N36" t="n">
-        <v>16.8750525091739</v>
+        <v>15.58751127859284</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>0.5872559224376905</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>10</v>
@@ -4517,7 +4495,7 @@
         <v>46281</v>
       </c>
       <c r="C37" t="n">
-        <v>0.05405183221324784</v>
+        <v>0.05281762505651691</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4542,25 +4520,25 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>28.05684368632165</v>
+        <v>28.90138710360903</v>
       </c>
       <c r="K37" t="n">
-        <v>2.734377407836974</v>
+        <v>1.581027667984181</v>
       </c>
       <c r="L37" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M37" t="n">
         <v>66.66666666666667</v>
       </c>
       <c r="N37" t="n">
-        <v>16.09802536859771</v>
+        <v>16.97343841729532</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>7.072240836501908</v>
+        <v>8.287937743190676</v>
       </c>
       <c r="Q37" t="n">
         <v>27</v>
@@ -4626,7 +4604,7 @@
         <v>46281</v>
       </c>
       <c r="C38" t="n">
-        <v>1.570174897753664</v>
+        <v>1.525956677216491</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4651,25 +4629,25 @@
         <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>11.25665100789579</v>
+        <v>15.42556854266918</v>
       </c>
       <c r="K38" t="n">
-        <v>1.058203103426592</v>
+        <v>3.053435114503822</v>
       </c>
       <c r="L38" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M38" t="n">
-        <v>54.54545454545455</v>
+        <v>56.25</v>
       </c>
       <c r="N38" t="n">
-        <v>12.82041562218495</v>
+        <v>13.19453677931492</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>8.84816533638746</v>
+        <v>6.740740740740736</v>
       </c>
       <c r="Q38" t="n">
         <v>42</v>
@@ -4735,7 +4713,7 @@
         <v>46281</v>
       </c>
       <c r="C39" t="n">
-        <v>2.521733769036316</v>
+        <v>2.474413251674956</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4760,25 +4738,25 @@
         <v>10</v>
       </c>
       <c r="J39" t="n">
-        <v>12.93329891699999</v>
+        <v>15.16752191136769</v>
       </c>
       <c r="K39" t="n">
-        <v>1.488833746898255</v>
+        <v>2.207130730050944</v>
       </c>
       <c r="L39" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="M39" t="n">
-        <v>55.88235294117647</v>
+        <v>65.38461538461539</v>
       </c>
       <c r="N39" t="n">
-        <v>16.01350623743097</v>
+        <v>16.03608256009219</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
       </c>
       <c r="P39" t="n">
-        <v>3.459657701711505</v>
+        <v>2.73255813953488</v>
       </c>
       <c r="Q39" t="n">
         <v>42</v>
@@ -4844,7 +4822,7 @@
         <v>46281</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2063423556733872</v>
+        <v>0.2053105347527642</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4869,25 +4847,25 @@
         <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>22.08645938444355</v>
+        <v>22.0880606327607</v>
       </c>
       <c r="K40" t="n">
-        <v>0.5005028143258761</v>
+        <v>2.302302348766716e-06</v>
       </c>
       <c r="L40" t="n">
         <v>18</v>
       </c>
       <c r="M40" t="n">
-        <v>55.55555555555556</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N40" t="n">
-        <v>17.989535017136</v>
+        <v>17.07297762827142</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>2.487049433266941</v>
+        <v>2.999997628628637</v>
       </c>
       <c r="Q40" t="n">
         <v>29</v>
@@ -4914,7 +4892,7 @@
         <v>33.58584893257701</v>
       </c>
       <c r="Y40" t="n">
-        <v>21.69649992092175</v>
+        <v>22.08805883899229</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -4959,7 +4937,7 @@
         <v>46281</v>
       </c>
       <c r="C41" t="n">
-        <v>1.097478266230964</v>
+        <v>1.097455711291052</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4984,7 +4962,7 @@
         <v>10</v>
       </c>
       <c r="J41" t="n">
-        <v>45.65404823168654</v>
+        <v>45.65516512822501</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -5068,16 +5046,16 @@
         <v>46281</v>
       </c>
       <c r="C42" t="n">
-        <v>3.210226688862856</v>
+        <v>3.136174935262444</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5085,7 +5063,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H42" t="n">
         <v>5</v>
       </c>
@@ -5093,25 +5075,25 @@
         <v>10</v>
       </c>
       <c r="J42" t="n">
-        <v>18.42777866747934</v>
+        <v>21.03333569370082</v>
       </c>
       <c r="K42" t="n">
-        <v>1.758957654723114</v>
+        <v>2.691790040376851</v>
       </c>
       <c r="L42" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M42" t="n">
-        <v>44.44444444444444</v>
+        <v>80</v>
       </c>
       <c r="N42" t="n">
-        <v>9.043407489538058</v>
+        <v>18.35389376095361</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
       </c>
       <c r="P42" t="n">
-        <v>0.2368758002560867</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>2</v>
@@ -5173,7 +5155,7 @@
         <v>46281</v>
       </c>
       <c r="C43" t="n">
-        <v>5.852189818525598</v>
+        <v>5.8006905339307</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5192,7 +5174,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -5202,25 +5184,25 @@
         <v>10</v>
       </c>
       <c r="J43" t="n">
-        <v>26.64468274841287</v>
+        <v>26.64619031792358</v>
       </c>
       <c r="K43" t="n">
-        <v>6.349206349206349</v>
+        <v>5.415499533146595</v>
       </c>
       <c r="L43" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M43" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N43" t="n">
-        <v>13.55676570531921</v>
+        <v>13.79399724434061</v>
       </c>
       <c r="O43" t="n">
         <v>10</v>
       </c>
       <c r="P43" t="n">
-        <v>3.43283582089553</v>
+        <v>4.348981399468554</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5286,7 +5268,7 @@
         <v>46281</v>
       </c>
       <c r="C44" t="n">
-        <v>4.075467044823973</v>
+        <v>4.075383287434748</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5314,7 +5296,7 @@
         <v>25.16666033456245</v>
       </c>
       <c r="K44" t="n">
-        <v>6.115304300346014</v>
+        <v>6.113123460519021</v>
       </c>
       <c r="L44" t="n">
         <v>5</v>
@@ -5329,7 +5311,7 @@
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>3.660825104603993</v>
+        <v>3.662955544727842</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5356,7 +5338,7 @@
         <v>28.18267712431886</v>
       </c>
       <c r="Y44" t="n">
-        <v>17.2155655655176</v>
+        <v>17.21726691852092</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -5393,7 +5375,7 @@
         <v>46281</v>
       </c>
       <c r="C45" t="n">
-        <v>0.02014098690835851</v>
+        <v>0.0197295408771425</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5418,25 +5400,25 @@
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>19.6788445923302</v>
+        <v>19.68049532099574</v>
       </c>
       <c r="K45" t="n">
-        <v>3.157895822714685</v>
+        <v>1.05263264265929</v>
       </c>
       <c r="L45" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="M45" t="n">
-        <v>56</v>
+        <v>68.96551724137932</v>
       </c>
       <c r="N45" t="n">
-        <v>15.35542289931829</v>
+        <v>15.55413213175814</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>6.632651938775536</v>
+        <v>8.854165520833334</v>
       </c>
       <c r="Q45" t="n">
         <v>38</v>
@@ -5502,7 +5484,7 @@
         <v>46281</v>
       </c>
       <c r="C46" t="n">
-        <v>8.529091394866104</v>
+        <v>8.528916108348062</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5527,7 +5509,7 @@
         <v>10</v>
       </c>
       <c r="J46" t="n">
-        <v>21.30302176772584</v>
+        <v>21.30463911694348</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -5611,7 +5593,7 @@
         <v>46281</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9408718170047476</v>
+        <v>0.9540055078301616</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5636,25 +5618,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>18.95621252985475</v>
+        <v>18.95787810976907</v>
       </c>
       <c r="K47" t="n">
-        <v>3.434256072515818</v>
+        <v>4.880257031153001</v>
       </c>
       <c r="L47" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="M47" t="n">
-        <v>55.17241379310344</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="N47" t="n">
-        <v>14.42991978913006</v>
+        <v>14.25725341281695</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>6.347746072520755</v>
+        <v>4.881512606635074</v>
       </c>
       <c r="Q47" t="n">
         <v>51</v>
@@ -5681,7 +5663,7 @@
         <v>66.65983471422588</v>
       </c>
       <c r="Y47" t="n">
-        <v>16.17296133726447</v>
+        <v>15.00281425802548</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -5726,7 +5708,7 @@
         <v>46281</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05096902809462154</v>
+        <v>0.04952936824365983</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5751,25 +5733,25 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>21.81120084197526</v>
+        <v>21.81280774729728</v>
       </c>
       <c r="K48" t="n">
-        <v>2.904564315352687</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M48" t="n">
-        <v>60.52631578947368</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N48" t="n">
-        <v>16.8766366077258</v>
+        <v>15.66116427323397</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>6.895161290322593</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5835,11 +5817,11 @@
         <v>46281</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2612162689849354</v>
+        <v>0.2505240659295491</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5849,7 +5831,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -5860,25 +5842,25 @@
         <v>10</v>
       </c>
       <c r="J49" t="n">
-        <v>16.33474246007769</v>
+        <v>18.76736374837591</v>
       </c>
       <c r="K49" t="n">
-        <v>2.582728006456825</v>
+        <v>1.330008312551945</v>
       </c>
       <c r="L49" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M49" t="n">
-        <v>52.38095238095238</v>
+        <v>56.81818181818182</v>
       </c>
       <c r="N49" t="n">
-        <v>18.5149054643229</v>
+        <v>17.33023260021261</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>2.356412273800168</v>
+        <v>3.621821164889272</v>
       </c>
       <c r="Q49" t="n">
         <v>54</v>
@@ -5901,27 +5883,17 @@
       <c r="W49" t="n">
         <v>67.14285714285714</v>
       </c>
-      <c r="X49" t="n">
-        <v>22.46912765663718</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>14.17389642191988</v>
-      </c>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>14.58639676596025</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
         <v>10</v>
       </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="n">
         <v>44</v>
       </c>
@@ -5954,16 +5926,16 @@
         <v>46281</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6835604332367388</v>
+        <v>0.6695712935180237</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5979,25 +5951,25 @@
         <v>10</v>
       </c>
       <c r="J50" t="n">
-        <v>13.72133807245333</v>
+        <v>16.76065457250247</v>
       </c>
       <c r="K50" t="n">
-        <v>2.717726991970326</v>
+        <v>4.289372599231767</v>
       </c>
       <c r="L50" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="M50" t="n">
-        <v>56.36363636363637</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N50" t="n">
-        <v>15.29437605280425</v>
+        <v>17.21690808685419</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>1.248346361996422</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>40</v>
@@ -6063,7 +6035,7 @@
         <v>46281</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1229011241959019</v>
+        <v>0.1220765341773193</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6092,10 +6064,10 @@
         <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>37.32903222039072</v>
+        <v>37.33032020937051</v>
       </c>
       <c r="K51" t="n">
-        <v>0.6734006734006703</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
         <v>3</v>
@@ -6104,13 +6076,13 @@
         <v>100</v>
       </c>
       <c r="N51" t="n">
-        <v>10.69605849893178</v>
+        <v>10.96169884631585</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>3.304347826086973</v>
+        <v>4.000000000000004</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6176,7 +6148,7 @@
         <v>46281</v>
       </c>
       <c r="C52" t="n">
-        <v>4.328256982551329</v>
+        <v>4.229520325537425</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6201,25 +6173,25 @@
         <v>10</v>
       </c>
       <c r="J52" t="n">
-        <v>11.87945099445477</v>
+        <v>14.10886131100679</v>
       </c>
       <c r="K52" t="n">
-        <v>2.382111386803287</v>
+        <v>2.643391521197014</v>
       </c>
       <c r="L52" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M52" t="n">
-        <v>55.76923076923077</v>
+        <v>50</v>
       </c>
       <c r="N52" t="n">
-        <v>11.51371376542996</v>
+        <v>11.98968400717528</v>
       </c>
       <c r="O52" t="n">
         <v>10</v>
       </c>
       <c r="P52" t="n">
-        <v>7.440644180911704</v>
+        <v>7.167152575315838</v>
       </c>
       <c r="Q52" t="n">
         <v>37</v>
@@ -6246,16 +6218,16 @@
         <v>16.62696858241317</v>
       </c>
       <c r="Y52" t="n">
-        <v>9.780321362480093</v>
+        <v>11.83842223344238</v>
       </c>
       <c r="Z52" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA52" t="n">
-        <v>68.75</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="AB52" t="n">
-        <v>11.61629564000714</v>
+        <v>11.14714845297855</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
@@ -6295,7 +6267,7 @@
         <v>46281</v>
       </c>
       <c r="C53" t="n">
-        <v>1.069733029163327</v>
+        <v>1.05532492087632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6320,10 +6292,10 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>39.61080584387218</v>
+        <v>40.15015741156469</v>
       </c>
       <c r="K53" t="n">
-        <v>3.06930693069305</v>
+        <v>2.597402597402598</v>
       </c>
       <c r="L53" t="n">
         <v>3</v>
@@ -6338,7 +6310,7 @@
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>4.783861671469758</v>
+        <v>5.265822784810137</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6396,7 +6368,7 @@
         <v>46281</v>
       </c>
       <c r="C54" t="n">
-        <v>0.06782168958217728</v>
+        <v>0.06782029573759711</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6424,7 +6396,7 @@
         <v>28.93741561274367</v>
       </c>
       <c r="K54" t="n">
-        <v>8.052401869053893</v>
+        <v>8.05018121876271</v>
       </c>
       <c r="L54" t="n">
         <v>11</v>
@@ -6439,7 +6411,7 @@
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>1.802457046078776</v>
+        <v>1.804549292971225</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6466,7 +6438,7 @@
         <v>14.75410024187049</v>
       </c>
       <c r="Y54" t="n">
-        <v>5.840051343430197</v>
+        <v>5.841986481509364</v>
       </c>
       <c r="Z54" t="n">
         <v>29</v>
@@ -6515,7 +6487,7 @@
         <v>46281</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8475656123476581</v>
+        <v>0.8368613588721279</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6540,25 +6512,25 @@
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>18.57516013239783</v>
+        <v>18.57683354355052</v>
       </c>
       <c r="K55" t="n">
-        <v>4.14141816505984</v>
+        <v>2.828286801193913</v>
       </c>
       <c r="L55" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M55" t="n">
-        <v>55.55555555555556</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N55" t="n">
-        <v>13.26859523904215</v>
+        <v>14.35723484369811</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>1.784671140155192</v>
+        <v>3.084475388506869</v>
       </c>
       <c r="Q55" t="n">
         <v>45</v>
@@ -6585,17 +6557,13 @@
         <v>23.0932342837701</v>
       </c>
       <c r="Y55" t="n">
-        <v>15.20301702325007</v>
+        <v>16.27395287354861</v>
       </c>
       <c r="Z55" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>33.66794265572751</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
         <v>3</v>
       </c>
@@ -6634,7 +6602,7 @@
         <v>46281</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5643586739831885</v>
+        <v>0.564347075506597</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6659,7 +6627,7 @@
         <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>60.7450942444783</v>
+        <v>60.74590099579886</v>
       </c>
       <c r="K56" t="n">
         <v>3.350327859585889e-06</v>
@@ -6723,7 +6691,7 @@
         <v>46281</v>
       </c>
       <c r="C57" t="n">
-        <v>1.288612121585795</v>
+        <v>1.28858563853837</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6752,7 +6720,7 @@
         <v>10</v>
       </c>
       <c r="J57" t="n">
-        <v>15.383288100876</v>
+        <v>15.38502711012216</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -6797,7 +6765,7 @@
         <v>20.62560129901716</v>
       </c>
       <c r="Y57" t="n">
-        <v>15.383288100876</v>
+        <v>15.38502711012216</v>
       </c>
       <c r="Z57" t="n">
         <v>2</v>
@@ -6842,16 +6810,16 @@
         <v>46281</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7061676634399984</v>
+        <v>0.6691602614164166</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6859,7 +6827,11 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %82.61: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6870,22 +6842,22 @@
         <v>18.04392839464337</v>
       </c>
       <c r="K58" t="n">
-        <v>8.238461746641779</v>
+        <v>2.566120069653621</v>
       </c>
       <c r="L58" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="M58" t="n">
-        <v>72.72727272727273</v>
+        <v>82.60869565217391</v>
       </c>
       <c r="N58" t="n">
-        <v>26.9204158835382</v>
+        <v>18.56118354850544</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>5.297928718231892</v>
       </c>
       <c r="Q58" t="n">
         <v>25</v>
@@ -6912,17 +6884,13 @@
         <v>20.50322102897642</v>
       </c>
       <c r="Y58" t="n">
-        <v>10.17795140877224</v>
+        <v>14.88516307378175</v>
       </c>
       <c r="Z58" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>7.890987522049663</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
         <v>6</v>
       </c>
@@ -6961,7 +6929,7 @@
         <v>46281</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7090449472840497</v>
+        <v>0.7012207653417731</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6986,25 +6954,25 @@
         <v>10</v>
       </c>
       <c r="J59" t="n">
-        <v>17.60353959471696</v>
+        <v>17.70408692387225</v>
       </c>
       <c r="K59" t="n">
-        <v>3.479304139172146</v>
+        <v>2.462462462462467</v>
       </c>
       <c r="L59" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M59" t="n">
-        <v>65.71428571428571</v>
+        <v>63.88888888888889</v>
       </c>
       <c r="N59" t="n">
-        <v>14.80449329782947</v>
+        <v>15.95336001625915</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>4.368695652173948</v>
+        <v>5.404454865181707</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7070,7 +7038,7 @@
         <v>46281</v>
       </c>
       <c r="C60" t="n">
-        <v>10.44042994841441</v>
+        <v>10.1730445147766</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7087,11 +7055,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %91.67: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>5</v>
       </c>
@@ -7099,25 +7063,25 @@
         <v>10</v>
       </c>
       <c r="J60" t="n">
-        <v>27.03599897665605</v>
+        <v>29.37463568904754</v>
       </c>
       <c r="K60" t="n">
-        <v>1.701701701701697</v>
+        <v>2.378490175801451</v>
       </c>
       <c r="L60" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M60" t="n">
-        <v>91.66666666666667</v>
+        <v>60</v>
       </c>
       <c r="N60" t="n">
-        <v>13.35433234994239</v>
+        <v>11.81922306253522</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>6.192913385826793</v>
+        <v>5.490909090909102</v>
       </c>
       <c r="Q60" t="n">
         <v>46</v>
@@ -7183,7 +7147,7 @@
         <v>46281</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6416342972234211</v>
+        <v>0.6416211106087385</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7212,10 +7176,10 @@
         <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>22.76307005464179</v>
+        <v>22.76465739752364</v>
       </c>
       <c r="K61" t="n">
-        <v>2.210121774481877e-06</v>
+        <v>2.210121752277416e-06</v>
       </c>
       <c r="L61" t="n">
         <v>25</v>
@@ -7230,7 +7194,7 @@
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>9.999997568866114</v>
+        <v>9.999997568866137</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
@@ -7257,7 +7221,7 @@
         <v>49.99145178651283</v>
       </c>
       <c r="Y61" t="n">
-        <v>22.76306834761157</v>
+        <v>22.76465569052852</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -7302,21 +7266,21 @@
         <v>46281</v>
       </c>
       <c r="C62" t="n">
-        <v>8.601023490967384</v>
+        <v>8.492950799457438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>AL_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>BAND</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -7326,17 +7290,27 @@
       <c r="I62" t="n">
         <v>10</v>
       </c>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="J62" t="n">
+        <v>11.10006525340588</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2.226345083487957</v>
+      </c>
       <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="M62" t="n">
+        <v>52.30769230769231</v>
+      </c>
+      <c r="N62" t="n">
+        <v>13.41078457700024</v>
+      </c>
       <c r="O62" t="n">
         <v>6</v>
       </c>
-      <c r="P62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>3.691470054446455</v>
+      </c>
       <c r="Q62" t="n">
         <v>30</v>
       </c>
@@ -7358,27 +7332,17 @@
       <c r="W62" t="n">
         <v>72.05882352941177</v>
       </c>
-      <c r="X62" t="n">
-        <v>11.23299668900593</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>7.964409840750175</v>
-      </c>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>15.74253410400235</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
         <v>5</v>
       </c>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="n">
         <v>27</v>
       </c>
@@ -7411,7 +7375,7 @@
         <v>46281</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1019380561892431</v>
+        <v>0.09885322043651608</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7425,7 +7389,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -7436,25 +7400,25 @@
         <v>10</v>
       </c>
       <c r="J63" t="n">
-        <v>17.75986027495195</v>
+        <v>21.61385831157259</v>
       </c>
       <c r="K63" t="n">
-        <v>1.018333024999984</v>
+        <v>2.777777777777768</v>
       </c>
       <c r="L63" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="M63" t="n">
-        <v>68.75</v>
+        <v>62.5</v>
       </c>
       <c r="N63" t="n">
-        <v>17.27832568856377</v>
+        <v>13.0731539657678</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>3.941529082661299</v>
+        <v>2.162162162162184</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7477,23 +7441,17 @@
       <c r="W63" t="n">
         <v>66.66666666666667</v>
       </c>
-      <c r="X63" t="n">
-        <v>24.85614965143601</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>16.92238177232566</v>
-      </c>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="inlineStr"/>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
         <v>10</v>
       </c>
-      <c r="AD63" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD63" t="inlineStr"/>
       <c r="AE63" t="n">
         <v>1</v>
       </c>
@@ -7526,16 +7484,16 @@
         <v>46281</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1494132396160881</v>
+        <v>0.1409840108512475</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7551,25 +7509,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>18.13575431954985</v>
+        <v>18.13743676119727</v>
       </c>
       <c r="K64" t="n">
-        <v>10.15151682047753</v>
+        <v>3.939395514233257</v>
       </c>
       <c r="L64" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="M64" t="n">
-        <v>50</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N64" t="n">
-        <v>18.82919173036433</v>
+        <v>12.50629597748074</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.020406632653081</v>
       </c>
       <c r="Q64" t="n">
         <v>55</v>
@@ -7635,7 +7593,7 @@
         <v>46281</v>
       </c>
       <c r="C65" t="n">
-        <v>6.170746244116983</v>
+        <v>6.067861399975338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7660,25 +7618,25 @@
         <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>14.82130166561233</v>
+        <v>15.62454617285346</v>
       </c>
       <c r="K65" t="n">
-        <v>2.73738237810095</v>
+        <v>1.98618307426599</v>
       </c>
       <c r="L65" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M65" t="n">
-        <v>60.78431372549019</v>
+        <v>62.96296296296296</v>
       </c>
       <c r="N65" t="n">
-        <v>11.98322223955101</v>
+        <v>12.38469844409487</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>7.069109075770186</v>
+        <v>7.857747671464854</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7705,16 +7663,16 @@
         <v>24.47056390537039</v>
       </c>
       <c r="Y65" t="n">
-        <v>12.48963498751103</v>
+        <v>13.94869519010357</v>
       </c>
       <c r="Z65" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AA65" t="n">
-        <v>37.5</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB65" t="n">
-        <v>15.0813486974636</v>
+        <v>16.71963460649922</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
@@ -7754,7 +7712,7 @@
         <v>46281</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4089853464044228</v>
+        <v>0.3962349459492787</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7779,25 +7737,25 @@
         <v>10</v>
       </c>
       <c r="J66" t="n">
-        <v>16.7692159743721</v>
+        <v>19.91164625527118</v>
       </c>
       <c r="K66" t="n">
-        <v>1.478837327893934</v>
+        <v>2.172760996290402</v>
       </c>
       <c r="L66" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="M66" t="n">
-        <v>58.8235294117647</v>
+        <v>45.71428571428572</v>
       </c>
       <c r="N66" t="n">
-        <v>17.4651299818803</v>
+        <v>14.07833946977136</v>
       </c>
       <c r="O66" t="n">
         <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>4.455276381909545</v>
+        <v>3.745850622406643</v>
       </c>
       <c r="Q66" t="n">
         <v>35</v>
@@ -7863,7 +7821,7 @@
         <v>46281</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0250734734981606</v>
+        <v>0.02425089399482099</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7888,25 +7846,25 @@
         <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>16.40407509217184</v>
+        <v>18.49564829454171</v>
       </c>
       <c r="K67" t="n">
-        <v>1.666666666666661</v>
+        <v>0.8547008547008517</v>
       </c>
       <c r="L67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M67" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N67" t="n">
-        <v>8.929437427954834</v>
+        <v>11.81759600692333</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>2.295081967213131</v>
+        <v>3.118644067796628</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7952,7 +7910,7 @@
         <v>46281</v>
       </c>
       <c r="C68" t="n">
-        <v>1.405758678093594</v>
+        <v>1.405729787496404</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7977,7 +7935,7 @@
         <v>10</v>
       </c>
       <c r="J68" t="n">
-        <v>74.82532810127793</v>
+        <v>74.82584548119281</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -8057,28 +8015,24 @@
         <v>46281</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4747518342684506</v>
+        <v>0.4656993711208846</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>AL_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>VERİ_YETERSİZ</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>5</v>
       </c>
@@ -8089,22 +8043,22 @@
         <v>22.2553779663549</v>
       </c>
       <c r="K69" t="n">
-        <v>9.612893133614753</v>
+        <v>7.52281869057625</v>
       </c>
       <c r="L69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M69" t="n">
-        <v>85.71428571428571</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N69" t="n">
-        <v>32.4160653623916</v>
+        <v>27.26484434775983</v>
       </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>0.4437953870954248</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8123,7 +8077,7 @@
         <v>45.36848923911108</v>
       </c>
       <c r="Y69" t="n">
-        <v>14.78187053312787</v>
+        <v>16.40679100908998</v>
       </c>
       <c r="Z69" t="n">
         <v>1</v>
@@ -8160,7 +8114,7 @@
         <v>46281</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4344698604517336</v>
+        <v>0.4266513214682067</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8185,25 +8139,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>24.07170695606632</v>
+        <v>24.07326740435939</v>
       </c>
       <c r="K70" t="n">
-        <v>3.525954946131238</v>
+        <v>1.665034280117528</v>
       </c>
       <c r="L70" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M70" t="n">
-        <v>60.8695652173913</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N70" t="n">
-        <v>13.27357779797516</v>
+        <v>14.52954830714423</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>4.321665089877014</v>
+        <v>6.231213872832386</v>
       </c>
       <c r="Q70" t="n">
         <v>31</v>
@@ -8230,7 +8184,7 @@
         <v>44.93251946562029</v>
       </c>
       <c r="Y70" t="n">
-        <v>21.39450955197072</v>
+        <v>22.8090612788688</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -8275,16 +8229,16 @@
         <v>46281</v>
       </c>
       <c r="C71" t="n">
-        <v>3.000596008796268</v>
+        <v>2.951210489539233</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8300,25 +8254,25 @@
         <v>10</v>
       </c>
       <c r="J71" t="n">
-        <v>10.66103530061523</v>
+        <v>12.71302799751677</v>
       </c>
       <c r="K71" t="n">
-        <v>1.5299026425591</v>
+        <v>2.206405693950164</v>
       </c>
       <c r="L71" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M71" t="n">
-        <v>49.31506849315068</v>
+        <v>54.66666666666666</v>
       </c>
       <c r="N71" t="n">
-        <v>17.35900256785373</v>
+        <v>17.0847915617772</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
       </c>
       <c r="P71" t="n">
-        <v>0.4630136986301547</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>40</v>
@@ -8384,7 +8338,7 @@
         <v>46281</v>
       </c>
       <c r="C72" t="n">
-        <v>0.05343527138952258</v>
+        <v>0.05322865715812405</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8413,10 +8367,10 @@
         <v>10</v>
       </c>
       <c r="J72" t="n">
-        <v>37.36002064699394</v>
+        <v>37.36130799911185</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3861038744205958</v>
+        <v>3.474903587097344e-06</v>
       </c>
       <c r="L72" t="n">
         <v>4</v>
@@ -8431,7 +8385,7 @@
         <v>10</v>
       </c>
       <c r="P72" t="n">
-        <v>9.576919269230789</v>
+        <v>9.999996177606185</v>
       </c>
       <c r="Q72" t="n">
         <v>15</v>
@@ -8497,7 +8451,7 @@
         <v>46281</v>
       </c>
       <c r="C73" t="n">
-        <v>0.05528495386069836</v>
+        <v>0.05507830161535616</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8522,10 +8476,10 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>28.53397539838882</v>
+        <v>28.80614321513075</v>
       </c>
       <c r="K73" t="n">
-        <v>1.893939393939381</v>
+        <v>1.901140684410652</v>
       </c>
       <c r="L73" t="n">
         <v>12</v>
@@ -8540,7 +8494,7 @@
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>7.95539033457251</v>
+        <v>7.947761194029845</v>
       </c>
       <c r="Q73" t="n">
         <v>14</v>
@@ -8606,7 +8560,7 @@
         <v>46281</v>
       </c>
       <c r="C74" t="n">
-        <v>4.901658548615822</v>
+        <v>4.901557811665091</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8631,7 +8585,7 @@
         <v>10</v>
       </c>
       <c r="J74" t="n">
-        <v>17.37406242951771</v>
+        <v>17.37576052515606</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -8676,7 +8630,7 @@
         <v>24.51464461150628</v>
       </c>
       <c r="Y74" t="n">
-        <v>17.37406242951771</v>
+        <v>17.37576052515606</v>
       </c>
       <c r="Z74" t="n">
         <v>3</v>
@@ -8725,7 +8679,7 @@
         <v>46281</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1072815833281953</v>
+        <v>0.1058407661638374</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8742,11 +8696,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>5</v>
       </c>
@@ -8754,25 +8704,25 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>22.00260850333738</v>
+        <v>22.61594163229673</v>
       </c>
       <c r="K75" t="n">
-        <v>2.352943183391032</v>
+        <v>1.778656126482225</v>
       </c>
       <c r="L75" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M75" t="n">
-        <v>83.33333333333333</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N75" t="n">
-        <v>13.65710407480026</v>
+        <v>13.79231513665973</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>3.563216360153265</v>
+        <v>4.147572815533973</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8838,7 +8788,7 @@
         <v>46281</v>
       </c>
       <c r="C76" t="n">
-        <v>1.789053990176131</v>
+        <v>1.733527888528094</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8863,25 +8813,25 @@
         <v>10</v>
       </c>
       <c r="J76" t="n">
-        <v>14.36700844688754</v>
+        <v>16.6968026846143</v>
       </c>
       <c r="K76" t="n">
-        <v>2.895982948355247</v>
+        <v>2.490886998784925</v>
       </c>
       <c r="L76" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="M76" t="n">
-        <v>41.30434782608695</v>
+        <v>50</v>
       </c>
       <c r="N76" t="n">
-        <v>11.86997620926326</v>
+        <v>12.58967301356177</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>6.904076182653651</v>
+        <v>7.326615293420291</v>
       </c>
       <c r="Q76" t="n">
         <v>41</v>
@@ -8947,7 +8897,7 @@
         <v>46281</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4488562796719897</v>
+        <v>0.4418595092276706</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8972,25 +8922,25 @@
         <v>10</v>
       </c>
       <c r="J77" t="n">
-        <v>24.13419034764688</v>
+        <v>24.27956799614378</v>
       </c>
       <c r="K77" t="n">
-        <v>3.507109004739317</v>
+        <v>2.089268755935425</v>
       </c>
       <c r="L77" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M77" t="n">
-        <v>71.42857142857143</v>
+        <v>62.5</v>
       </c>
       <c r="N77" t="n">
-        <v>13.06574358588145</v>
+        <v>15.58240736748492</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>4.34065934065937</v>
+        <v>5.789767441860461</v>
       </c>
       <c r="Q77" t="n">
         <v>27</v>
@@ -9056,7 +9006,7 @@
         <v>46281</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05179110919292189</v>
+        <v>0.05179004480249907</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9081,7 +9031,7 @@
         <v>10</v>
       </c>
       <c r="J78" t="n">
-        <v>17.7024064797947</v>
+        <v>17.7040978274358</v>
       </c>
       <c r="K78" t="n">
         <v>7.936507895323075e-07</v>
@@ -9126,7 +9076,7 @@
         <v>36.67113091579677</v>
       </c>
       <c r="Y78" t="n">
-        <v>17.70240582663919</v>
+        <v>17.70409717429371</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -9171,11 +9121,11 @@
         <v>46281</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8286577470867502</v>
+        <v>0.7863044103744502</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -9185,10 +9135,14 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
+          <t>BAND</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.95: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H79" t="n">
         <v>5</v>
       </c>
@@ -9196,25 +9150,25 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>18.8004344699408</v>
+        <v>21.27764888392525</v>
       </c>
       <c r="K79" t="n">
-        <v>2.439024390243905</v>
+        <v>0.2620545073375391</v>
       </c>
       <c r="L79" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M79" t="n">
-        <v>65.51724137931035</v>
+        <v>80.95238095238095</v>
       </c>
       <c r="N79" t="n">
-        <v>10.32872810805917</v>
+        <v>10.96162233878875</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>2.499999999999991</v>
+        <v>4.72556194458964</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9237,12 +9191,8 @@
       <c r="W79" t="n">
         <v>57.89473684210526</v>
       </c>
-      <c r="X79" t="n">
-        <v>25.65117214954458</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>16.81995726189056</v>
-      </c>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="n">
         <v>0</v>
       </c>
@@ -9251,9 +9201,7 @@
       <c r="AC79" t="n">
         <v>8</v>
       </c>
-      <c r="AD79" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD79" t="inlineStr"/>
       <c r="AE79" t="n">
         <v>36</v>
       </c>
@@ -9286,11 +9234,11 @@
         <v>46281</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1266004891382535</v>
+        <v>0.1255703070409799</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -9300,7 +9248,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -9311,25 +9259,25 @@
         <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>13.07558125490144</v>
+        <v>14.37257191021615</v>
       </c>
       <c r="K80" t="n">
-        <v>1.986755642296401</v>
+        <v>2.689075630252113</v>
       </c>
       <c r="L80" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="M80" t="n">
-        <v>52.38095238095238</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="N80" t="n">
-        <v>15.04851229569683</v>
+        <v>14.08548448314545</v>
       </c>
       <c r="O80" t="n">
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>7.857142142857154</v>
+        <v>7.119476268412428</v>
       </c>
       <c r="Q80" t="n">
         <v>39</v>
@@ -9352,27 +9300,17 @@
       <c r="W80" t="n">
         <v>74.35897435897436</v>
       </c>
-      <c r="X80" t="n">
-        <v>16.30078916022812</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>11.34860546094984</v>
-      </c>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA80" t="n">
-        <v>45.83333333333334</v>
-      </c>
-      <c r="AB80" t="n">
-        <v>18.0934003197824</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
         <v>8</v>
       </c>
-      <c r="AD80" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD80" t="inlineStr"/>
       <c r="AE80" t="n">
         <v>24</v>
       </c>
@@ -9405,11 +9343,11 @@
         <v>46281</v>
       </c>
       <c r="C81" t="n">
-        <v>1.17043796370512</v>
+        <v>1.155000205516051</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9430,25 +9368,25 @@
         <v>10</v>
       </c>
       <c r="J81" t="n">
-        <v>10.34756831148802</v>
+        <v>11.64050719803407</v>
       </c>
       <c r="K81" t="n">
-        <v>2.520253427819852</v>
+        <v>2.648401826484026</v>
       </c>
       <c r="L81" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M81" t="n">
-        <v>53.65853658536585</v>
+        <v>51.02040816326531</v>
       </c>
       <c r="N81" t="n">
-        <v>13.12025342493991</v>
+        <v>13.2556313833504</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>7.295872105355583</v>
+        <v>7.161921708185059</v>
       </c>
       <c r="Q81" t="n">
         <v>32</v>
@@ -9475,22 +9413,22 @@
         <v>23.79225853623819</v>
       </c>
       <c r="Y81" t="n">
-        <v>8.08809982873443</v>
+        <v>9.300392776794785</v>
       </c>
       <c r="Z81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA81" t="n">
-        <v>50</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB81" t="n">
-        <v>10.5869564825963</v>
+        <v>9.102176101498813</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>2.08014432048842</v>
+        <v>0.771345372514709</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9524,7 +9462,7 @@
         <v>46281</v>
       </c>
       <c r="C82" t="n">
-        <v>4.675586246583226</v>
+        <v>4.675490155781167</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9549,10 +9487,10 @@
         <v>10</v>
       </c>
       <c r="J82" t="n">
-        <v>19.38271394011772</v>
+        <v>19.38437075474348</v>
       </c>
       <c r="K82" t="n">
-        <v>3.739168643846513</v>
+        <v>3.739168643846491</v>
       </c>
       <c r="L82" t="n">
         <v>7</v>
@@ -9567,7 +9505,7 @@
         <v>4</v>
       </c>
       <c r="P82" t="n">
-        <v>0.2514299657142782</v>
+        <v>0.2514299657143004</v>
       </c>
       <c r="Q82" t="n">
         <v>8</v>
@@ -9633,7 +9571,7 @@
         <v>46281</v>
       </c>
       <c r="C83" t="n">
-        <v>5.199662946749697</v>
+        <v>5.137901270089194</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9658,25 +9596,25 @@
         <v>10</v>
       </c>
       <c r="J83" t="n">
-        <v>16.91612217329925</v>
+        <v>17.93020279426077</v>
       </c>
       <c r="K83" t="n">
-        <v>2.761983401397439</v>
+        <v>2.79605263157896</v>
       </c>
       <c r="L83" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="M83" t="n">
-        <v>58.69565217391305</v>
+        <v>51.35135135135135</v>
       </c>
       <c r="N83" t="n">
-        <v>11.89650719797397</v>
+        <v>12.36250608798611</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>7.043476934782622</v>
+        <v>7.007999999999992</v>
       </c>
       <c r="Q83" t="n">
         <v>41</v>
@@ -9742,7 +9680,7 @@
         <v>46281</v>
       </c>
       <c r="C84" t="n">
-        <v>1.994574264751218</v>
+        <v>1.960623124666036</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9767,25 +9705,25 @@
         <v>10</v>
       </c>
       <c r="J84" t="n">
-        <v>13.58177596213546</v>
+        <v>15.19236884649807</v>
       </c>
       <c r="K84" t="n">
-        <v>3.244680851063819</v>
+        <v>3.414634146341466</v>
       </c>
       <c r="L84" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="M84" t="n">
-        <v>48.07692307692308</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="N84" t="n">
-        <v>11.58387831822891</v>
+        <v>12.78563173092211</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>1.700154559505429</v>
+        <v>1.53301886792454</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9851,7 +9789,7 @@
         <v>46281</v>
       </c>
       <c r="C85" t="n">
-        <v>5.728877653780546</v>
+        <v>5.54379547042624</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9876,25 +9814,25 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>15.86185926388125</v>
+        <v>20.69989676657544</v>
       </c>
       <c r="K85" t="n">
-        <v>1.733576642335755</v>
+        <v>4.453049370764761</v>
       </c>
       <c r="L85" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="M85" t="n">
-        <v>57.69230769230769</v>
+        <v>60</v>
       </c>
       <c r="N85" t="n">
-        <v>15.72056805328279</v>
+        <v>12.3216736571236</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>6.159641255605397</v>
+        <v>3.395736793327164</v>
       </c>
       <c r="Q85" t="n">
         <v>32</v>
@@ -9960,7 +9898,7 @@
         <v>46281</v>
       </c>
       <c r="C86" t="n">
-        <v>4.75573915366751</v>
+        <v>4.747420773562415</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9992,7 +9930,7 @@
         <v>18.73514495170452</v>
       </c>
       <c r="K86" t="n">
-        <v>14.07626742114032</v>
+        <v>13.87673382126915</v>
       </c>
       <c r="L86" t="n">
         <v>4</v>
@@ -10034,16 +9972,16 @@
         <v>32.57395859734095</v>
       </c>
       <c r="Y86" t="n">
-        <v>7.296086635704402</v>
+        <v>7.458237326412343</v>
       </c>
       <c r="Z86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA86" t="n">
-        <v>33.33333333333334</v>
+        <v>25</v>
       </c>
       <c r="AB86" t="n">
-        <v>5.489735975290166</v>
+        <v>5.266319656673107</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
@@ -10083,16 +10021,16 @@
         <v>46281</v>
       </c>
       <c r="C87" t="n">
-        <v>5.677497585136774</v>
+        <v>5.564347075506597</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -10107,17 +10045,27 @@
       <c r="I87" t="n">
         <v>10</v>
       </c>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
+      <c r="J87" t="n">
+        <v>13.37852897610052</v>
+      </c>
+      <c r="K87" t="n">
+        <v>4.134615384615392</v>
+      </c>
       <c r="L87" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="M87" t="n">
+        <v>62.96296296296296</v>
+      </c>
+      <c r="N87" t="n">
+        <v>12.51943425223574</v>
+      </c>
       <c r="O87" t="n">
         <v>5</v>
       </c>
-      <c r="P87" t="inlineStr"/>
+      <c r="P87" t="n">
+        <v>0.8310249307479145</v>
+      </c>
       <c r="Q87" t="n">
         <v>47</v>
       </c>
@@ -10143,16 +10091,16 @@
         <v>15.88967756874082</v>
       </c>
       <c r="Y87" t="n">
-        <v>7.962795524827715</v>
+        <v>9.797064308766213</v>
       </c>
       <c r="Z87" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AA87" t="n">
-        <v>68</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="AB87" t="n">
-        <v>11.57148063067813</v>
+        <v>9.982420860260039</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
@@ -10192,16 +10140,16 @@
         <v>46281</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9922518856485193</v>
+        <v>0.9704467918944469</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -10217,25 +10165,25 @@
         <v>10</v>
       </c>
       <c r="J88" t="n">
-        <v>19.38989550963131</v>
+        <v>21.41965384897848</v>
       </c>
       <c r="K88" t="n">
-        <v>2.942430703624743</v>
+        <v>3.280839895013132</v>
       </c>
       <c r="L88" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M88" t="n">
-        <v>66.66666666666667</v>
+        <v>70.27027027027027</v>
       </c>
       <c r="N88" t="n">
-        <v>16.68482307006266</v>
+        <v>15.09663045550047</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
       </c>
       <c r="P88" t="n">
-        <v>0.05592377796188597</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
         <v>34</v>
@@ -10301,7 +10249,7 @@
         <v>46281</v>
       </c>
       <c r="C89" t="n">
-        <v>2.032595515547609</v>
+        <v>2.023305520161125</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10326,25 +10274,25 @@
         <v>10</v>
       </c>
       <c r="J89" t="n">
-        <v>14.11546256812646</v>
+        <v>15.60931331442587</v>
       </c>
       <c r="K89" t="n">
-        <v>1.07307260747882</v>
+        <v>2.392095683827344</v>
       </c>
       <c r="L89" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="M89" t="n">
-        <v>64.28571428571429</v>
+        <v>59.72222222222222</v>
       </c>
       <c r="N89" t="n">
-        <v>14.23551475598784</v>
+        <v>14.82350100418043</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>2.895852789484321</v>
+        <v>1.570340274250892</v>
       </c>
       <c r="Q89" t="n">
         <v>45</v>
@@ -10371,16 +10319,16 @@
         <v>21.41032003314154</v>
       </c>
       <c r="Y89" t="n">
-        <v>13.19385912288513</v>
+        <v>13.59060734066798</v>
       </c>
       <c r="Z89" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA89" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="AB89" t="n">
-        <v>20.63598439723828</v>
+        <v>15.88199252440822</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
@@ -10420,7 +10368,7 @@
         <v>46281</v>
       </c>
       <c r="C90" t="n">
-        <v>2.597776270629098</v>
+        <v>2.560729993012454</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10445,25 +10393,25 @@
         <v>10</v>
       </c>
       <c r="J90" t="n">
-        <v>18.7556950036317</v>
+        <v>19.80990087027463</v>
       </c>
       <c r="K90" t="n">
-        <v>2.348178137651824</v>
+        <v>2.214930270713689</v>
       </c>
       <c r="L90" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="M90" t="n">
-        <v>61.22448979591837</v>
+        <v>63.04347826086956</v>
       </c>
       <c r="N90" t="n">
-        <v>15.50086276685579</v>
+        <v>17.25633212126395</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>5.522151898734173</v>
+        <v>5.659711075441431</v>
       </c>
       <c r="Q90" t="n">
         <v>43</v>
@@ -10529,7 +10477,7 @@
         <v>46281</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2194956532461927</v>
+        <v>0.2135311767849069</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10554,25 +10502,25 @@
         <v>10</v>
       </c>
       <c r="J91" t="n">
-        <v>10.17169207219154</v>
+        <v>13.48785164958405</v>
       </c>
       <c r="K91" t="n">
-        <v>1.040684136481751</v>
+        <v>2.062868369351678</v>
       </c>
       <c r="L91" t="n">
         <v>62</v>
       </c>
       <c r="M91" t="n">
-        <v>51.61290322580645</v>
+        <v>64.51612903225806</v>
       </c>
       <c r="N91" t="n">
-        <v>15.39510502908388</v>
+        <v>15.63083422701726</v>
       </c>
       <c r="O91" t="n">
         <v>6</v>
       </c>
       <c r="P91" t="n">
-        <v>4.908236623595519</v>
+        <v>3.85755534167469</v>
       </c>
       <c r="Q91" t="n">
         <v>44</v>
@@ -10638,11 +10586,11 @@
         <v>46281</v>
       </c>
       <c r="C92" t="n">
-        <v>1.078981441519206</v>
+        <v>1.023880965103374</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -10652,7 +10600,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -10663,25 +10611,25 @@
         <v>10</v>
       </c>
       <c r="J92" t="n">
-        <v>15.80678164352948</v>
+        <v>18.95953720206354</v>
       </c>
       <c r="K92" t="n">
-        <v>2.339182802685746</v>
+        <v>0.8910490076954103</v>
       </c>
       <c r="L92" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="M92" t="n">
-        <v>47.05882352941177</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N92" t="n">
-        <v>13.00975297690628</v>
+        <v>14.14877382778777</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>5.531427008000001</v>
+        <v>7.046166198313952</v>
       </c>
       <c r="Q92" t="n">
         <v>44</v>
@@ -10704,23 +10652,17 @@
       <c r="W92" t="n">
         <v>67.14285714285714</v>
       </c>
-      <c r="X92" t="n">
-        <v>21.60407460332612</v>
-      </c>
-      <c r="Y92" t="n">
-        <v>13.83734835870725</v>
-      </c>
+      <c r="X92" t="inlineStr"/>
+      <c r="Y92" t="inlineStr"/>
       <c r="Z92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="inlineStr"/>
       <c r="AB92" t="inlineStr"/>
       <c r="AC92" t="n">
         <v>4</v>
       </c>
-      <c r="AD92" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD92" t="inlineStr"/>
       <c r="AE92" t="n">
         <v>52</v>
       </c>
@@ -10753,7 +10695,7 @@
         <v>46281</v>
       </c>
       <c r="C93" t="n">
-        <v>0.03987093326756685</v>
+        <v>0.03925356570348144</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10778,25 +10720,25 @@
         <v>10</v>
       </c>
       <c r="J93" t="n">
-        <v>11.15359968525608</v>
+        <v>13.4934398260194</v>
       </c>
       <c r="K93" t="n">
-        <v>2.105264232686999</v>
+        <v>3.243243243243232</v>
       </c>
       <c r="L93" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="M93" t="n">
-        <v>57.35294117647059</v>
+        <v>56.45161290322581</v>
       </c>
       <c r="N93" t="n">
-        <v>18.41153557119262</v>
+        <v>19.44900800053373</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>3.814431896907222</v>
+        <v>2.670157068062839</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10862,16 +10804,16 @@
         <v>46281</v>
       </c>
       <c r="C94" t="n">
-        <v>8.333847134019772</v>
+        <v>8.251469439763245</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -10886,17 +10828,27 @@
       <c r="I94" t="n">
         <v>10</v>
       </c>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
+      <c r="J94" t="n">
+        <v>10.48063678978293</v>
+      </c>
+      <c r="K94" t="n">
+        <v>5.657894736842084</v>
+      </c>
       <c r="L94" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="M94" t="n">
+        <v>46.42857142857143</v>
+      </c>
+      <c r="N94" t="n">
+        <v>15.50282251833736</v>
+      </c>
       <c r="O94" t="n">
         <v>8</v>
       </c>
-      <c r="P94" t="inlineStr"/>
+      <c r="P94" t="n">
+        <v>2.216687422166896</v>
+      </c>
       <c r="Q94" t="n">
         <v>41</v>
       </c>
@@ -10922,22 +10874,22 @@
         <v>36.6815048892442</v>
       </c>
       <c r="Y94" t="n">
-        <v>4.47145309886433</v>
+        <v>5.415725450257503</v>
       </c>
       <c r="Z94" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA94" t="n">
-        <v>41.66666666666666</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AB94" t="n">
-        <v>12.58922709873709</v>
+        <v>13.56192792270044</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>1.600094370447813</v>
+        <v>0.617729059639005</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -10971,7 +10923,7 @@
         <v>46281</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1140637562940584</v>
+        <v>0.1140614121007851</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10996,10 +10948,10 @@
         <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>24.77606696791015</v>
+        <v>24.77761294047443</v>
       </c>
       <c r="K95" t="n">
-        <v>1.462530220682168</v>
+        <v>1.462530220682146</v>
       </c>
       <c r="L95" t="n">
         <v>21</v>
@@ -11014,7 +10966,7 @@
         <v>10</v>
       </c>
       <c r="P95" t="n">
-        <v>8.414406540768059</v>
+        <v>8.414406540768082</v>
       </c>
       <c r="Q95" t="n">
         <v>21</v>
@@ -11080,7 +11032,7 @@
         <v>46281</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1229011241959019</v>
+        <v>0.1214599860249085</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11105,25 +11057,25 @@
         <v>10</v>
       </c>
       <c r="J96" t="n">
-        <v>10.99197108330091</v>
+        <v>11.75714561105962</v>
       </c>
       <c r="K96" t="n">
-        <v>2.572900206832274</v>
+        <v>2.249134948096887</v>
       </c>
       <c r="L96" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="M96" t="n">
-        <v>49.20634920634921</v>
+        <v>49.27536231884058</v>
       </c>
       <c r="N96" t="n">
-        <v>12.8448817714815</v>
+        <v>13.74821700210951</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>7.240801204013358</v>
+        <v>7.580372250423029</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11189,7 +11141,7 @@
         <v>46281</v>
       </c>
       <c r="C97" t="n">
-        <v>1.773639969582999</v>
+        <v>1.732500308274076</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11214,25 +11166,25 @@
         <v>10</v>
       </c>
       <c r="J97" t="n">
-        <v>17.34228334307187</v>
+        <v>19.39936861373087</v>
       </c>
       <c r="K97" t="n">
-        <v>2.190649043001525</v>
+        <v>2.367941712204003</v>
       </c>
       <c r="L97" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="M97" t="n">
-        <v>48.83720930232558</v>
+        <v>51.72413793103448</v>
       </c>
       <c r="N97" t="n">
-        <v>13.4775711360814</v>
+        <v>13.16306078720314</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>1.770564111239881</v>
+        <v>1.59430604982207</v>
       </c>
       <c r="Q97" t="n">
         <v>50</v>
@@ -11298,7 +11250,7 @@
         <v>46281</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6593090408368786</v>
+        <v>0.6268239549508816</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11323,25 +11275,25 @@
         <v>10</v>
       </c>
       <c r="J98" t="n">
-        <v>17.65200939318058</v>
+        <v>20.01394502517393</v>
       </c>
       <c r="K98" t="n">
-        <v>2.165606331940473</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M98" t="n">
-        <v>51.06382978723404</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N98" t="n">
-        <v>13.85503513301794</v>
+        <v>17.96328743253116</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>7.66832787406484</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11368,7 +11320,7 @@
         <v>30.85778357900837</v>
       </c>
       <c r="Y98" t="n">
-        <v>15.86867609437357</v>
+        <v>20.01394502517393</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
@@ -11413,7 +11365,7 @@
         <v>46281</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5101013214953656</v>
+        <v>0.4911833614205269</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11438,25 +11390,25 @@
         <v>10</v>
       </c>
       <c r="J99" t="n">
-        <v>14.07617215145111</v>
+        <v>18.77734876067304</v>
       </c>
       <c r="K99" t="n">
-        <v>1.306122448979607</v>
+        <v>3.195164075993073</v>
       </c>
       <c r="L99" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="M99" t="n">
-        <v>52.77777777777778</v>
+        <v>47.91666666666666</v>
       </c>
       <c r="N99" t="n">
-        <v>17.18388695119406</v>
+        <v>17.00887407976602</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>2.659145850120859</v>
+        <v>0.7799163179916579</v>
       </c>
       <c r="Q99" t="n">
         <v>34</v>
@@ -11483,7 +11435,7 @@
         <v>33.04241514445872</v>
       </c>
       <c r="Y99" t="n">
-        <v>12.95390174689862</v>
+        <v>16.18215178670491</v>
       </c>
       <c r="Z99" t="n">
         <v>0</v>
@@ -11528,7 +11480,7 @@
         <v>46281</v>
       </c>
       <c r="C100" t="n">
-        <v>316.3602287120045</v>
+        <v>316.3537270015208</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11553,7 +11505,7 @@
         <v>10</v>
       </c>
       <c r="J100" t="n">
-        <v>14.5380172928869</v>
+        <v>14.53977367380488</v>
       </c>
       <c r="K100" t="n">
         <v>1.606827379056286</v>
@@ -11637,11 +11589,11 @@
         <v>46281</v>
       </c>
       <c r="C101" t="n">
-        <v>329.082968534846</v>
+        <v>320.7994574376258</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -11651,7 +11603,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -11662,25 +11614,25 @@
         <v>10</v>
       </c>
       <c r="J101" t="n">
-        <v>10.63471966983749</v>
+        <v>12.87519982509333</v>
       </c>
       <c r="K101" t="n">
-        <v>1.885028830601287</v>
+        <v>1.874530094816418</v>
       </c>
       <c r="L101" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M101" t="n">
-        <v>42.5</v>
+        <v>51.16279069767442</v>
       </c>
       <c r="N101" t="n">
-        <v>8.611050456197843</v>
+        <v>10.70929923463633</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
       </c>
       <c r="P101" t="n">
-        <v>0.1128440269569708</v>
+        <v>0.1231612112142288</v>
       </c>
       <c r="Q101" t="n">
         <v>30</v>
@@ -11703,27 +11655,17 @@
       <c r="W101" t="n">
         <v>52.63157894736842</v>
       </c>
-      <c r="X101" t="n">
-        <v>12.90626814318425</v>
-      </c>
-      <c r="Y101" t="n">
-        <v>8.950158371066264</v>
-      </c>
+      <c r="X101" t="inlineStr"/>
+      <c r="Y101" t="inlineStr"/>
       <c r="Z101" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA101" t="n">
-        <v>63.63636363636363</v>
-      </c>
-      <c r="AB101" t="n">
-        <v>11.64547042777423</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA101" t="inlineStr"/>
+      <c r="AB101" t="inlineStr"/>
       <c r="AC101" t="n">
         <v>6</v>
       </c>
-      <c r="AD101" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD101" t="inlineStr"/>
       <c r="AE101" t="n">
         <v>28</v>
       </c>
@@ -11756,7 +11698,7 @@
         <v>46281</v>
       </c>
       <c r="C102" t="n">
-        <v>382.3542540127834</v>
+        <v>382.3463960191541</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11781,10 +11723,10 @@
         <v>10</v>
       </c>
       <c r="J102" t="n">
-        <v>11.9059086841427</v>
+        <v>11.90771915911735</v>
       </c>
       <c r="K102" t="n">
-        <v>1.818425143219216</v>
+        <v>1.818425143219238</v>
       </c>
       <c r="L102" t="n">
         <v>36</v>
@@ -11799,7 +11741,7 @@
         <v>4</v>
       </c>
       <c r="P102" t="n">
-        <v>2.14261304249419</v>
+        <v>2.142613042494168</v>
       </c>
       <c r="Q102" t="n">
         <v>29</v>
@@ -11865,7 +11807,7 @@
         <v>46281</v>
       </c>
       <c r="C103" t="n">
-        <v>0.6695850545656329</v>
+        <v>0.6535410415553454</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11890,25 +11832,25 @@
         <v>10</v>
       </c>
       <c r="J103" t="n">
-        <v>16.98681049994946</v>
+        <v>18.80894382278397</v>
       </c>
       <c r="K103" t="n">
-        <v>2.067669172932329</v>
+        <v>1.857783472133256</v>
       </c>
       <c r="L103" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M103" t="n">
-        <v>53.19148936170212</v>
+        <v>52.27272727272727</v>
       </c>
       <c r="N103" t="n">
-        <v>14.70566983010254</v>
+        <v>19.06584845343957</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
       </c>
       <c r="P103" t="n">
-        <v>7.771639042357292</v>
+        <v>7.993710691823908</v>
       </c>
       <c r="Q103" t="n">
         <v>43</v>
@@ -11974,16 +11916,16 @@
         <v>46281</v>
       </c>
       <c r="C104" t="n">
-        <v>0.05261319029122223</v>
+        <v>0.05261210900571334</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -11998,27 +11940,17 @@
       <c r="I104" t="n">
         <v>10</v>
       </c>
-      <c r="J104" t="n">
-        <v>11.00325743953869</v>
-      </c>
-      <c r="K104" t="n">
-        <v>8.474580867566983</v>
-      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="n">
-        <v>11</v>
-      </c>
-      <c r="M104" t="n">
-        <v>63.63636363636363</v>
-      </c>
-      <c r="N104" t="n">
-        <v>10.25362128503169</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="O104" t="n">
         <v>4</v>
       </c>
-      <c r="P104" t="n">
-        <v>0</v>
-      </c>
+      <c r="P104" t="inlineStr"/>
       <c r="Q104" t="n">
         <v>32</v>
       </c>
@@ -12041,25 +11973,25 @@
         <v>63.23529411764706</v>
       </c>
       <c r="X104" t="n">
-        <v>17.08863596112118</v>
+        <v>17.89060837989</v>
       </c>
       <c r="Y104" t="n">
-        <v>3.461156521752007</v>
+        <v>4.119850187265916</v>
       </c>
       <c r="Z104" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="AA104" t="n">
-        <v>51.16279069767442</v>
+        <v>47.22222222222222</v>
       </c>
       <c r="AB104" t="n">
-        <v>13.4459439464976</v>
+        <v>13.61814568788858</v>
       </c>
       <c r="AC104" t="n">
         <v>5</v>
       </c>
       <c r="AD104" t="n">
-        <v>1.594014826368551</v>
+        <v>0.9179687500000089</v>
       </c>
       <c r="AE104" t="n">
         <v>42</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -444,7 +444,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -670,7 +670,7 @@
         <v>46281</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3711619877512433</v>
+        <v>0.372834449015693</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,25 +695,25 @@
         <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>22.33623436483442</v>
+        <v>22.33032903992303</v>
       </c>
       <c r="K2" t="n">
-        <v>2.207130730050921</v>
+        <v>2.659871578223538</v>
       </c>
       <c r="L2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M2" t="n">
-        <v>60</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="N2" t="n">
-        <v>12.87005792266073</v>
+        <v>13.30650164128567</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>7.624584717607985</v>
+        <v>7.149948961492258</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -779,7 +779,7 @@
         <v>46281</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6835463504459698</v>
+        <v>0.6827762551076552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,22 +807,22 @@
         <v>16.52890779617068</v>
       </c>
       <c r="K3" t="n">
-        <v>8.726789348124985</v>
+        <v>8.604295835326203</v>
       </c>
       <c r="L3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M3" t="n">
-        <v>65.51724137931035</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N3" t="n">
-        <v>12.05054107876322</v>
+        <v>11.99220577121672</v>
       </c>
       <c r="O3" t="n">
         <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>1.171018347463959</v>
+        <v>1.285127953676968</v>
       </c>
       <c r="Q3" t="n">
         <v>35</v>
@@ -849,7 +849,7 @@
         <v>17.17248092970491</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.207913935565402</v>
+        <v>7.312455131439089</v>
       </c>
       <c r="Z3" t="n">
         <v>25</v>
@@ -864,7 +864,7 @@
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.008970034896918</v>
+        <v>2.899574988605091</v>
       </c>
       <c r="AE3" t="n">
         <v>34</v>
@@ -898,7 +898,7 @@
         <v>46281</v>
       </c>
       <c r="C4" t="n">
-        <v>1.324550947428994</v>
+        <v>1.340066469466299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,25 +923,25 @@
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>18.02299847582851</v>
+        <v>18.01676654844163</v>
       </c>
       <c r="K4" t="n">
-        <v>2.62738853503186</v>
+        <v>3.821652450707891</v>
       </c>
       <c r="L4" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="M4" t="n">
-        <v>50</v>
+        <v>52.77777777777778</v>
       </c>
       <c r="N4" t="n">
-        <v>16.04678991337</v>
+        <v>15.53719206193585</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>2.311869666408062</v>
+        <v>1.13497283223416</v>
       </c>
       <c r="Q4" t="n">
         <v>53</v>
@@ -1007,7 +1007,7 @@
         <v>46281</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2164084014961568</v>
+        <v>0.2180691020019262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,7 +1024,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %79.17: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>5</v>
       </c>
@@ -1032,19 +1036,19 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>22.20242808709211</v>
+        <v>22.19651614701201</v>
       </c>
       <c r="K5" t="n">
-        <v>3.336604514229635</v>
+        <v>4.12168888430906</v>
       </c>
       <c r="L5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M5" t="n">
-        <v>73.07692307692308</v>
+        <v>79.16666666666667</v>
       </c>
       <c r="N5" t="n">
-        <v>13.19275446866066</v>
+        <v>10.73688545398247</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -1116,7 +1120,7 @@
         <v>46281</v>
       </c>
       <c r="C6" t="n">
-        <v>1.377985120637922</v>
+        <v>1.378089955032092</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,7 +1145,7 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>34.44318710178523</v>
+        <v>34.43819966856769</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1221,7 +1225,7 @@
         <v>46281</v>
       </c>
       <c r="C7" t="n">
-        <v>2.141477249373176</v>
+        <v>2.149861306947088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1238,11 +1242,7 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %75.00: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>5</v>
       </c>
@@ -1250,25 +1250,25 @@
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>15.68520386805919</v>
+        <v>15.67879320005955</v>
       </c>
       <c r="K7" t="n">
-        <v>2.660098522167487</v>
+        <v>3.05418568472906</v>
       </c>
       <c r="L7" t="n">
         <v>48</v>
       </c>
       <c r="M7" t="n">
-        <v>64.58333333333333</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N7" t="n">
-        <v>12.83984986580655</v>
+        <v>13.0925230763544</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>5.201535508637245</v>
+        <v>4.799236714558641</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1295,13 +1295,13 @@
         <v>18.9234494530097</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.44234722218491</v>
+        <v>13.10346697278498</v>
       </c>
       <c r="Z7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA7" t="n">
-        <v>75</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB7" t="n">
         <v>9.880102520564243</v>
@@ -1344,7 +1344,7 @@
         <v>46281</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3074520120021374</v>
+        <v>0.3074753891812642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>25.1309585260591</v>
+        <v>25.12526584256618</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1453,7 +1453,7 @@
         <v>46281</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5232438653458835</v>
+        <v>0.5319159620625101</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,19 +1478,19 @@
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>17.65061537695776</v>
+        <v>17.64435387980061</v>
       </c>
       <c r="K9" t="n">
-        <v>2.1669341894061</v>
+        <v>3.852323743652231</v>
       </c>
       <c r="L9" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="M9" t="n">
-        <v>67.85714285714286</v>
+        <v>60</v>
       </c>
       <c r="N9" t="n">
-        <v>11.67091914406717</v>
+        <v>13.55634135822285</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1562,7 +1562,7 @@
         <v>46281</v>
       </c>
       <c r="C10" t="n">
-        <v>1.774631098688807</v>
+        <v>1.785042580785678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,25 +1587,25 @@
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>17.73916070770556</v>
+        <v>17.7329076906843</v>
       </c>
       <c r="K10" t="n">
-        <v>1.767825574543314</v>
+        <v>2.357100808560575</v>
       </c>
       <c r="L10" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M10" t="n">
-        <v>56.09756097560975</v>
+        <v>52.77777777777778</v>
       </c>
       <c r="N10" t="n">
-        <v>17.49959131359964</v>
+        <v>13.08747965179568</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>8.089171974522301</v>
+        <v>7.466896904137621</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1671,16 +1671,16 @@
         <v>46281</v>
       </c>
       <c r="C11" t="n">
-        <v>7.280406099716387</v>
+        <v>7.399140361583522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1696,25 +1696,25 @@
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>16.81458041053866</v>
+        <v>16.80825561190469</v>
       </c>
       <c r="K11" t="n">
-        <v>1.942446043165469</v>
+        <v>3.597122302158273</v>
       </c>
       <c r="L11" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M11" t="n">
-        <v>72.91666666666667</v>
+        <v>70.73170731707317</v>
       </c>
       <c r="N11" t="n">
-        <v>13.93046486797963</v>
+        <v>11.88658417633129</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.037402964008471</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>49</v>
@@ -1780,7 +1780,7 @@
         <v>46281</v>
       </c>
       <c r="C12" t="n">
-        <v>5.051584528751696</v>
+        <v>5.04580266324654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,10 +1809,10 @@
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>32.22852520273922</v>
+        <v>32.22337067864791</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2855977152182998</v>
+        <v>0.1631962015687716</v>
       </c>
       <c r="L12" t="n">
         <v>6</v>
@@ -1827,7 +1827,7 @@
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>4.700976403580137</v>
+        <v>4.828923179226052</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1893,7 +1893,7 @@
         <v>46281</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1500267170866044</v>
+        <v>0.1500381279038789</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>50.83486051568098</v>
+        <v>50.83112108557266</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1986,7 +1986,7 @@
         <v>46281</v>
       </c>
       <c r="C14" t="n">
-        <v>8.318262156274406</v>
+        <v>8.334309490616995</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2011,19 +2011,19 @@
         <v>10</v>
       </c>
       <c r="J14" t="n">
-        <v>10.97787677915245</v>
+        <v>10.97110820112375</v>
       </c>
       <c r="K14" t="n">
-        <v>3.782051282051291</v>
+        <v>3.974358974358982</v>
       </c>
       <c r="L14" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M14" t="n">
-        <v>56.41025641025641</v>
+        <v>64.86486486486487</v>
       </c>
       <c r="N14" t="n">
-        <v>10.43669730398746</v>
+        <v>9.996147253704111</v>
       </c>
       <c r="O14" t="n">
         <v>2</v>
@@ -2056,7 +2056,7 @@
         <v>16.11612055393703</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.611014426569107</v>
+        <v>7.432780450142773</v>
       </c>
       <c r="Z14" t="n">
         <v>22</v>
@@ -2105,7 +2105,7 @@
         <v>46281</v>
       </c>
       <c r="C15" t="n">
-        <v>12.9783386082453</v>
+        <v>13.10264439030415</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,25 +2130,25 @@
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>20.43512248147792</v>
+        <v>20.42907296184905</v>
       </c>
       <c r="K15" t="n">
-        <v>3.186274509803932</v>
+        <v>4.166666666666652</v>
       </c>
       <c r="L15" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M15" t="n">
-        <v>58.33333333333334</v>
+        <v>65.625</v>
       </c>
       <c r="N15" t="n">
-        <v>16.22817479799679</v>
+        <v>15.23151380759086</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>4.665083135391912</v>
+        <v>3.680000000000017</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2175,7 +2175,7 @@
         <v>33.58229315482664</v>
       </c>
       <c r="Y15" t="n">
-        <v>17.89996707034854</v>
+        <v>17.11361766859276</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2220,7 +2220,7 @@
         <v>46281</v>
       </c>
       <c r="C16" t="n">
-        <v>32.71815528792798</v>
+        <v>32.88506827370454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,25 +2245,25 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>20.72571441444857</v>
+        <v>20.7196869892621</v>
       </c>
       <c r="K16" t="n">
-        <v>1.985906470211396</v>
+        <v>2.498398462524021</v>
       </c>
       <c r="L16" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M16" t="n">
-        <v>66.66666666666667</v>
+        <v>67.39130434782609</v>
       </c>
       <c r="N16" t="n">
-        <v>17.28873974926752</v>
+        <v>16.16966178998889</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>7.858040201005045</v>
+        <v>7.318750000000018</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2329,7 +2329,7 @@
         <v>46281</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3617082494142793</v>
+        <v>0.3629689379880387</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>54.89682137494209</v>
+        <v>54.89339106339885</v>
       </c>
       <c r="K17" t="n">
-        <v>2.923976608187129</v>
+        <v>3.27485062897992</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2368,7 +2368,7 @@
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>4.931818181818204</v>
+        <v>4.575314650413209</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2434,7 +2434,7 @@
         <v>46281</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06740926466357022</v>
+        <v>0.06905864131946277</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2459,16 +2459,16 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>40.57315922121754</v>
+        <v>40.56863896093654</v>
       </c>
       <c r="K18" t="n">
-        <v>4.126984126984135</v>
+        <v>6.66666010582031</v>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>25</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N18" t="n">
         <v>16.73203077467618</v>
@@ -2477,7 +2477,7 @@
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>5.640243902439024</v>
+        <v>3.125006343006143</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2543,7 +2543,7 @@
         <v>46281</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02815569896008879</v>
+        <v>0.02774677676700156</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %90.91: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2572,19 +2572,19 @@
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>16.09951028584119</v>
+        <v>16.0931283448295</v>
       </c>
       <c r="K19" t="n">
-        <v>13.22314049586777</v>
+        <v>11.57024589850426</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="M19" t="n">
-        <v>100</v>
+        <v>90.90909090909091</v>
       </c>
       <c r="N19" t="n">
-        <v>21.20569232422457</v>
+        <v>22.14238667462718</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
@@ -2617,22 +2617,22 @@
         <v>20.26411217973316</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.005230654216875</v>
+        <v>6.384896968583886</v>
       </c>
       <c r="Z19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA19" t="n">
-        <v>43.75</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="AB19" t="n">
-        <v>15.85883430635453</v>
+        <v>15.22852344795927</v>
       </c>
       <c r="AC19" t="n">
         <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.257941442651493</v>
+        <v>3.861666455895396</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -2666,7 +2666,7 @@
         <v>46281</v>
       </c>
       <c r="C20" t="n">
-        <v>1.561921986107115</v>
+        <v>1.572317326836498</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2691,25 +2691,25 @@
         <v>10</v>
       </c>
       <c r="J20" t="n">
-        <v>19.82651786594795</v>
+        <v>19.82042371699879</v>
       </c>
       <c r="K20" t="n">
-        <v>1.876675603217159</v>
+        <v>2.546918993254521</v>
       </c>
       <c r="L20" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="M20" t="n">
-        <v>55.17241379310344</v>
+        <v>42.30769230769231</v>
       </c>
       <c r="N20" t="n">
-        <v>16.04253316628892</v>
+        <v>17.32442696279431</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>7.973684210526333</v>
+        <v>7.267971656209138</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
@@ -2775,7 +2775,7 @@
         <v>46281</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8294627810431995</v>
+        <v>0.8340475817041283</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2800,25 +2800,25 @@
         <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>17.90942004166591</v>
+        <v>17.90318229766043</v>
       </c>
       <c r="K21" t="n">
-        <v>2.38457635717908</v>
+        <v>2.942678117328779</v>
       </c>
       <c r="L21" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M21" t="n">
-        <v>54.54545454545455</v>
+        <v>52.38095238095238</v>
       </c>
       <c r="N21" t="n">
-        <v>15.02069085561023</v>
+        <v>15.41321588006652</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>5.484638255698737</v>
+        <v>4.91275530728581</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2884,7 +2884,7 @@
         <v>46281</v>
       </c>
       <c r="C22" t="n">
-        <v>0.27765218463562</v>
+        <v>0.2789064789248746</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %90.91: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2913,25 +2913,25 @@
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>26.85013721896759</v>
+        <v>26.84457309657031</v>
       </c>
       <c r="K22" t="n">
-        <v>3.44563552833077</v>
+        <v>3.905047883604884</v>
       </c>
       <c r="L22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M22" t="n">
-        <v>88.88888888888889</v>
+        <v>90.90909090909091</v>
       </c>
       <c r="N22" t="n">
-        <v>23.0527243397274</v>
+        <v>20.17357471518222</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>6.336047372316811</v>
+        <v>5.865886442035739</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -2989,7 +2989,7 @@
         <v>46281</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5454395988326688</v>
+        <v>0.5483585198355052</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3014,10 +3014,10 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>46.54509966186163</v>
+        <v>46.98618794638018</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4542013626040786</v>
+        <v>1.832059298001343</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.525244913338367</v>
+        <v>3.110946320674901</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3094,7 +3094,7 @@
         <v>46281</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1405729787496403</v>
+        <v>0.1405836699530621</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>28.72680285640142</v>
+        <v>28.72138221115397</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3203,7 +3203,7 @@
         <v>46281</v>
       </c>
       <c r="C25" t="n">
-        <v>3.144395577294587</v>
+        <v>3.185740989015128</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3220,7 +3220,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>5</v>
       </c>
@@ -3228,25 +3232,25 @@
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>26.01993766845922</v>
+        <v>26.01430975971111</v>
       </c>
       <c r="K25" t="n">
-        <v>2.272727272727271</v>
+        <v>3.609621443725319</v>
       </c>
       <c r="L25" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M25" t="n">
-        <v>73.07692307692308</v>
+        <v>75</v>
       </c>
       <c r="N25" t="n">
-        <v>12.89590990493771</v>
+        <v>12.66996064697004</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>5.600000000000005</v>
+        <v>4.237423605161306</v>
       </c>
       <c r="Q25" t="n">
         <v>44</v>
@@ -3312,7 +3316,7 @@
         <v>46281</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4208968720457067</v>
+        <v>0.4217510100647179</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3337,25 +3341,25 @@
         <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>13.96354607862311</v>
+        <v>13.95700222161058</v>
       </c>
       <c r="K26" t="n">
-        <v>2.708124373119358</v>
+        <v>2.908725750169272</v>
       </c>
       <c r="L26" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M26" t="n">
-        <v>40.35087719298246</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N26" t="n">
-        <v>15.23538622738405</v>
+        <v>14.69871934269606</v>
       </c>
       <c r="O26" t="n">
         <v>6</v>
       </c>
       <c r="P26" t="n">
-        <v>3.205078125000016</v>
+        <v>3.003899064240079</v>
       </c>
       <c r="Q26" t="n">
         <v>32</v>
@@ -3421,7 +3425,7 @@
         <v>46281</v>
       </c>
       <c r="C27" t="n">
-        <v>50.31032923671339</v>
+        <v>50.31415445876795</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3468,7 +3472,7 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>67.77577224808454</v>
+        <v>67.78852866598044</v>
       </c>
       <c r="Y27" t="n">
         <v>12.41502683363148</v>
@@ -3506,7 +3510,7 @@
         <v>46281</v>
       </c>
       <c r="C28" t="n">
-        <v>1.262896132187924</v>
+        <v>1.240383637502447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3531,25 +3535,25 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>25.98625046455084</v>
+        <v>25.98062488782275</v>
       </c>
       <c r="K28" t="n">
-        <v>1.822700911350461</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M28" t="n">
-        <v>66.66666666666667</v>
+        <v>65</v>
       </c>
       <c r="N28" t="n">
-        <v>16.70707419789855</v>
+        <v>15.78282104681022</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>0.1741253051261049</v>
+        <v>2.000000000000002</v>
       </c>
       <c r="Q28" t="n">
         <v>39</v>
@@ -3615,7 +3619,7 @@
         <v>46281</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3962349459492787</v>
+        <v>0.4090080288439965</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3647,7 +3651,7 @@
         <v>27.65210909859499</v>
       </c>
       <c r="K29" t="n">
-        <v>19.65279743207695</v>
+        <v>23.50994106821762</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3685,7 +3689,7 @@
         <v>31.20488584758381</v>
       </c>
       <c r="Y29" t="n">
-        <v>8.804617557402949</v>
+        <v>5.864830970018254</v>
       </c>
       <c r="Z29" t="n">
         <v>3</v>
@@ -3694,13 +3698,13 @@
         <v>100</v>
       </c>
       <c r="AB29" t="n">
-        <v>14.1224438478875</v>
+        <v>16.19254517444829</v>
       </c>
       <c r="AC29" t="n">
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.310792729390087</v>
+        <v>4.392799282768278</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3734,7 +3738,7 @@
         <v>46281</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3695178593448148</v>
+        <v>0.3740676672337966</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3759,25 +3763,25 @@
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>21.04705350921352</v>
+        <v>21.0410518898386</v>
       </c>
       <c r="K30" t="n">
-        <v>0.8978675645342271</v>
+        <v>2.132441507354499</v>
       </c>
       <c r="L30" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="M30" t="n">
-        <v>55.88235294117647</v>
+        <v>51.61290322580645</v>
       </c>
       <c r="N30" t="n">
-        <v>14.51899735127237</v>
+        <v>11.17699640764965</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>4.065628476084537</v>
+        <v>2.807686226162542</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3804,7 +3808,7 @@
         <v>26.71344279693404</v>
       </c>
       <c r="Y30" t="n">
-        <v>20.33816061142867</v>
+        <v>19.35729850656703</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -3849,11 +3853,11 @@
         <v>46281</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2437420362530313</v>
+        <v>0.2454048133601897</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3863,7 +3867,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3906,10 +3910,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="X31" t="n">
-        <v>56.50025293875822</v>
+        <v>56.51215205029592</v>
       </c>
       <c r="Y31" t="n">
-        <v>10.55807093300479</v>
+        <v>9.954755860513265</v>
       </c>
       <c r="Z31" t="n">
         <v>1</v>
@@ -3920,7 +3924,7 @@
         <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>0.05024600679259805</v>
       </c>
       <c r="AE31" t="n">
         <v>10</v>
@@ -3954,7 +3958,7 @@
         <v>46281</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180525299025854</v>
+        <v>2.205354953792472</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3979,19 +3983,19 @@
         <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>14.67107717442044</v>
+        <v>14.66459067233932</v>
       </c>
       <c r="K32" t="n">
-        <v>3.411306042884976</v>
+        <v>4.58090121840915</v>
       </c>
       <c r="L32" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="M32" t="n">
-        <v>59.52380952380953</v>
+        <v>62.85714285714285</v>
       </c>
       <c r="N32" t="n">
-        <v>10.96319618056995</v>
+        <v>10.7525626358017</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4063,7 +4067,7 @@
         <v>46281</v>
       </c>
       <c r="C33" t="n">
-        <v>1.666735172016934</v>
+        <v>1.684332027956643</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4088,25 +4092,25 @@
         <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>13.64684832148788</v>
+        <v>13.64028267214126</v>
       </c>
       <c r="K33" t="n">
-        <v>2.334384858044158</v>
+        <v>3.406936214511047</v>
       </c>
       <c r="L33" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M33" t="n">
-        <v>50.98039215686274</v>
+        <v>54</v>
       </c>
       <c r="N33" t="n">
-        <v>11.43361381568396</v>
+        <v>11.55849982952366</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>1.627620221948223</v>
+        <v>0.5735241824191384</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4172,7 +4176,7 @@
         <v>46281</v>
       </c>
       <c r="C34" t="n">
-        <v>0.712729664186773</v>
+        <v>0.714839146524788</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4197,25 +4201,25 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>20.35922049452815</v>
+        <v>20.35316837217597</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6968641114982521</v>
+        <v>0.9872246327670808</v>
       </c>
       <c r="L34" t="n">
         <v>26</v>
       </c>
       <c r="M34" t="n">
-        <v>69.23076923076923</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N34" t="n">
-        <v>11.39877164871466</v>
+        <v>10.96936711775501</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>3.280276816609007</v>
+        <v>2.983323265084925</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4281,7 +4285,7 @@
         <v>46281</v>
       </c>
       <c r="C35" t="n">
-        <v>1.293723539808459</v>
+        <v>1.29382192051397</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4306,7 +4310,7 @@
         <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>42.89282089250778</v>
+        <v>42.88847819919079</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -4386,7 +4390,7 @@
         <v>46281</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07193061778124871</v>
+        <v>0.07255268126226562</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4411,19 +4415,19 @@
         <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>19.92223104152002</v>
+        <v>19.91614017004532</v>
       </c>
       <c r="K36" t="n">
-        <v>2.941176470588225</v>
+        <v>3.823525475778666</v>
       </c>
       <c r="L36" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M36" t="n">
-        <v>47.36842105263158</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N36" t="n">
-        <v>15.58751127859284</v>
+        <v>13.44413963731622</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4495,7 +4499,7 @@
         <v>46281</v>
       </c>
       <c r="C37" t="n">
-        <v>0.05281762505651691</v>
+        <v>0.05302717094709516</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4520,25 +4524,25 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>28.90138710360903</v>
+        <v>28.89598213870331</v>
       </c>
       <c r="K37" t="n">
-        <v>1.581027667984181</v>
+        <v>1.976282632129833</v>
       </c>
       <c r="L37" t="n">
         <v>24</v>
       </c>
       <c r="M37" t="n">
-        <v>66.66666666666667</v>
+        <v>70.83333333333333</v>
       </c>
       <c r="N37" t="n">
-        <v>16.97343841729532</v>
+        <v>16.36949645570671</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>8.287937743190676</v>
+        <v>7.868219119944797</v>
       </c>
       <c r="Q37" t="n">
         <v>27</v>
@@ -4604,7 +4608,7 @@
         <v>46281</v>
       </c>
       <c r="C38" t="n">
-        <v>1.525956677216491</v>
+        <v>1.534293998091374</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4629,25 +4633,25 @@
         <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>15.42556854266918</v>
+        <v>15.41913455348373</v>
       </c>
       <c r="K38" t="n">
-        <v>3.053435114503822</v>
+        <v>3.608602872918265</v>
       </c>
       <c r="L38" t="n">
         <v>48</v>
       </c>
       <c r="M38" t="n">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="N38" t="n">
-        <v>13.19453677931492</v>
+        <v>12.58692404747017</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>6.740740740740736</v>
+        <v>6.168789994129309</v>
       </c>
       <c r="Q38" t="n">
         <v>42</v>
@@ -4713,7 +4717,7 @@
         <v>46281</v>
       </c>
       <c r="C39" t="n">
-        <v>2.474413251674956</v>
+        <v>2.484878002878146</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4738,25 +4742,25 @@
         <v>10</v>
       </c>
       <c r="J39" t="n">
-        <v>15.16752191136769</v>
+        <v>15.16106968610098</v>
       </c>
       <c r="K39" t="n">
-        <v>2.207130730050944</v>
+        <v>2.63157758891075</v>
       </c>
       <c r="L39" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M39" t="n">
-        <v>65.38461538461539</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="N39" t="n">
-        <v>16.03608256009219</v>
+        <v>15.98166047721427</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
       </c>
       <c r="P39" t="n">
-        <v>2.73255813953488</v>
+        <v>2.307693661862964</v>
       </c>
       <c r="Q39" t="n">
         <v>42</v>
@@ -4822,7 +4826,7 @@
         <v>46281</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2053105347527642</v>
+        <v>0.2053261403067142</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4847,10 +4851,10 @@
         <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>22.0880606327607</v>
+        <v>22.08213679021579</v>
       </c>
       <c r="K40" t="n">
-        <v>2.302302348766716e-06</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>18</v>
@@ -4865,7 +4869,7 @@
         <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>2.999997628628637</v>
+        <v>3.000000000000003</v>
       </c>
       <c r="Q40" t="n">
         <v>29</v>
@@ -4892,7 +4896,7 @@
         <v>33.58584893257701</v>
       </c>
       <c r="Y40" t="n">
-        <v>22.08805883899229</v>
+        <v>22.08213679021579</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -4937,7 +4941,7 @@
         <v>46281</v>
       </c>
       <c r="C41" t="n">
-        <v>1.097455711291052</v>
+        <v>1.097539185081235</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4962,7 +4966,7 @@
         <v>10</v>
       </c>
       <c r="J41" t="n">
-        <v>45.65516512822501</v>
+        <v>45.65103159527513</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -5046,7 +5050,7 @@
         <v>46281</v>
       </c>
       <c r="C42" t="n">
-        <v>3.136174935262444</v>
+        <v>3.144634653672997</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5065,7 +5069,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -5075,19 +5079,19 @@
         <v>10</v>
       </c>
       <c r="J42" t="n">
-        <v>21.03333569370082</v>
+        <v>21.02732841592907</v>
       </c>
       <c r="K42" t="n">
-        <v>2.691790040376851</v>
+        <v>2.960964817887723</v>
       </c>
       <c r="L42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M42" t="n">
-        <v>80</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N42" t="n">
-        <v>18.35389376095361</v>
+        <v>14.12854066520737</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
@@ -5155,7 +5159,7 @@
         <v>46281</v>
       </c>
       <c r="C43" t="n">
-        <v>5.8006905339307</v>
+        <v>5.837099618582556</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5174,7 +5178,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -5184,25 +5188,25 @@
         <v>10</v>
       </c>
       <c r="J43" t="n">
-        <v>26.64619031792358</v>
+        <v>26.64061304155033</v>
       </c>
       <c r="K43" t="n">
-        <v>5.415499533146595</v>
+        <v>6.069094304388423</v>
       </c>
       <c r="L43" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M43" t="n">
-        <v>88.88888888888889</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N43" t="n">
-        <v>13.79399724434061</v>
+        <v>14.53783433294402</v>
       </c>
       <c r="O43" t="n">
         <v>10</v>
       </c>
       <c r="P43" t="n">
-        <v>4.348981399468554</v>
+        <v>3.70598591549296</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5268,7 +5272,7 @@
         <v>46281</v>
       </c>
       <c r="C44" t="n">
-        <v>4.075383287434748</v>
+        <v>4.075693211859418</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5296,7 +5300,7 @@
         <v>25.16666033456245</v>
       </c>
       <c r="K44" t="n">
-        <v>6.113123460519021</v>
+        <v>6.121193142906889</v>
       </c>
       <c r="L44" t="n">
         <v>5</v>
@@ -5311,7 +5315,7 @@
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>3.662955544727842</v>
+        <v>3.65507279198205</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5338,7 +5342,7 @@
         <v>28.18267712431886</v>
       </c>
       <c r="Y44" t="n">
-        <v>17.21726691852092</v>
+        <v>17.21097146380824</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -5375,7 +5379,7 @@
         <v>46281</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0197295408771425</v>
+        <v>0.01993657325752841</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5400,25 +5404,25 @@
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>19.68049532099574</v>
+        <v>19.67438842514809</v>
       </c>
       <c r="K45" t="n">
-        <v>1.05263264265929</v>
+        <v>2.105267390581766</v>
       </c>
       <c r="L45" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M45" t="n">
-        <v>68.96551724137932</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N45" t="n">
-        <v>15.55413213175814</v>
+        <v>17.81786928956835</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>8.854165520833334</v>
+        <v>7.731954296949861</v>
       </c>
       <c r="Q45" t="n">
         <v>38</v>
@@ -5484,7 +5488,7 @@
         <v>46281</v>
       </c>
       <c r="C46" t="n">
-        <v>8.528916108348062</v>
+        <v>8.529564583492116</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5509,7 +5513,7 @@
         <v>10</v>
       </c>
       <c r="J46" t="n">
-        <v>21.30463911694348</v>
+        <v>21.29865570887185</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -5593,7 +5597,7 @@
         <v>46281</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9540055078301616</v>
+        <v>0.961477158577572</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5618,25 +5622,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>18.95787810976907</v>
+        <v>18.95171627150033</v>
       </c>
       <c r="K47" t="n">
-        <v>4.880257031153001</v>
+        <v>5.693629813947099</v>
       </c>
       <c r="L47" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M47" t="n">
-        <v>57.69230769230769</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="N47" t="n">
-        <v>14.25725341281695</v>
+        <v>15.12768264263546</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>4.881512606635074</v>
+        <v>4.074389529088385</v>
       </c>
       <c r="Q47" t="n">
         <v>51</v>
@@ -5663,10 +5667,10 @@
         <v>66.65983471422588</v>
       </c>
       <c r="Y47" t="n">
-        <v>15.00281425802548</v>
+        <v>14.33712702544205</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr"/>
@@ -5708,7 +5712,7 @@
         <v>46281</v>
       </c>
       <c r="C48" t="n">
-        <v>0.04952936824365983</v>
+        <v>0.04953313593705256</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5733,7 +5737,7 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>21.81280774729728</v>
+        <v>21.80686005650104</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -5817,7 +5821,7 @@
         <v>46281</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2505240659295491</v>
+        <v>0.2511597144897737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5842,10 +5846,10 @@
         <v>10</v>
       </c>
       <c r="J49" t="n">
-        <v>18.76736374837591</v>
+        <v>18.76118924813161</v>
       </c>
       <c r="K49" t="n">
-        <v>1.330008312551945</v>
+        <v>1.579389395381137</v>
       </c>
       <c r="L49" t="n">
         <v>44</v>
@@ -5854,13 +5858,13 @@
         <v>56.81818181818182</v>
       </c>
       <c r="N49" t="n">
-        <v>17.33023260021261</v>
+        <v>17.27015430670839</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>3.621821164889272</v>
+        <v>3.367425838035598</v>
       </c>
       <c r="Q49" t="n">
         <v>54</v>
@@ -5926,7 +5930,7 @@
         <v>46281</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6695712935180237</v>
+        <v>0.6753771022086393</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5951,19 +5955,19 @@
         <v>10</v>
       </c>
       <c r="J50" t="n">
-        <v>16.76065457250247</v>
+        <v>16.75432628663439</v>
       </c>
       <c r="K50" t="n">
-        <v>4.289372599231767</v>
+        <v>5.185662138050651</v>
       </c>
       <c r="L50" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M50" t="n">
-        <v>64.28571428571429</v>
+        <v>56.09756097560975</v>
       </c>
       <c r="N50" t="n">
-        <v>17.21690808685419</v>
+        <v>18.31155651433684</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
@@ -6035,7 +6039,7 @@
         <v>46281</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1220765341773193</v>
+        <v>0.1220858171993182</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6064,7 +6068,7 @@
         <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>37.33032020937051</v>
+        <v>37.32555464144151</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -6148,7 +6152,7 @@
         <v>46281</v>
       </c>
       <c r="C52" t="n">
-        <v>4.229520325537425</v>
+        <v>4.244229124074993</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6173,25 +6177,25 @@
         <v>10</v>
       </c>
       <c r="J52" t="n">
-        <v>14.10886131100679</v>
+        <v>14.10233078968066</v>
       </c>
       <c r="K52" t="n">
-        <v>2.643391521197014</v>
+        <v>2.992518703241909</v>
       </c>
       <c r="L52" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M52" t="n">
-        <v>50</v>
+        <v>48.83720930232558</v>
       </c>
       <c r="N52" t="n">
-        <v>11.98968400717528</v>
+        <v>12.57201847202214</v>
       </c>
       <c r="O52" t="n">
         <v>10</v>
       </c>
       <c r="P52" t="n">
-        <v>7.167152575315838</v>
+        <v>6.803874092009687</v>
       </c>
       <c r="Q52" t="n">
         <v>37</v>
@@ -6218,7 +6222,7 @@
         <v>16.62696858241317</v>
       </c>
       <c r="Y52" t="n">
-        <v>11.83842223344238</v>
+        <v>11.531826972913</v>
       </c>
       <c r="Z52" t="n">
         <v>15</v>
@@ -6267,7 +6271,7 @@
         <v>46281</v>
       </c>
       <c r="C53" t="n">
-        <v>1.05532492087632</v>
+        <v>1.073903010813164</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6292,25 +6296,21 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>40.15015741156469</v>
+        <v>40.14560778496996</v>
       </c>
       <c r="K53" t="n">
-        <v>2.597402597402598</v>
+        <v>4.395605980832373</v>
       </c>
       <c r="L53" t="n">
-        <v>3</v>
-      </c>
-      <c r="M53" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N53" t="n">
-        <v>28.71403390950369</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>5.265822784810137</v>
+        <v>3.452630008038282</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6368,7 +6368,7 @@
         <v>46281</v>
       </c>
       <c r="C54" t="n">
-        <v>0.06782029573759711</v>
+        <v>0.06474248021917259</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6396,22 +6396,22 @@
         <v>28.93741561274367</v>
       </c>
       <c r="K54" t="n">
-        <v>8.05018121876271</v>
+        <v>3.146656088020294</v>
       </c>
       <c r="L54" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="M54" t="n">
-        <v>54.54545454545455</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N54" t="n">
-        <v>21.66831939456864</v>
+        <v>20.38177089078518</v>
       </c>
       <c r="O54" t="n">
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>1.804549292971225</v>
+        <v>6.644271537151347</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6438,16 +6438,16 @@
         <v>14.75410024187049</v>
       </c>
       <c r="Y54" t="n">
-        <v>5.841986481509364</v>
+        <v>10.11505831110596</v>
       </c>
       <c r="Z54" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AA54" t="n">
-        <v>41.37931034482759</v>
+        <v>52.38095238095238</v>
       </c>
       <c r="AB54" t="n">
-        <v>14.56659153746906</v>
+        <v>19.20175943300067</v>
       </c>
       <c r="AC54" t="n">
         <v>2</v>
@@ -6487,7 +6487,7 @@
         <v>46281</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8368613588721279</v>
+        <v>0.8541896765673153</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6512,25 +6512,25 @@
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>18.57683354355052</v>
+        <v>18.57064273349606</v>
       </c>
       <c r="K55" t="n">
-        <v>2.828286801193913</v>
+        <v>4.949502463958044</v>
       </c>
       <c r="L55" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M55" t="n">
-        <v>53.84615384615385</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="N55" t="n">
-        <v>14.35723484369811</v>
+        <v>13.01006777547481</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>3.084475388506869</v>
+        <v>1.000955232162948</v>
       </c>
       <c r="Q55" t="n">
         <v>45</v>
@@ -6557,13 +6557,17 @@
         <v>23.0932342837701</v>
       </c>
       <c r="Y55" t="n">
-        <v>16.27395287354861</v>
+        <v>14.54029468920525</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="inlineStr"/>
-      <c r="AB55" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>33.66794265572751</v>
+      </c>
       <c r="AC55" t="n">
         <v>3</v>
       </c>
@@ -6602,7 +6606,7 @@
         <v>46281</v>
       </c>
       <c r="C56" t="n">
-        <v>0.564347075506597</v>
+        <v>0.5643899653385399</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6627,10 +6631,10 @@
         <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>60.74590099579886</v>
+        <v>60.7429164069973</v>
       </c>
       <c r="K56" t="n">
-        <v>3.350327859585889e-06</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
@@ -6641,7 +6645,7 @@
         <v>4</v>
       </c>
       <c r="P56" t="n">
-        <v>3.999996515659143</v>
+        <v>4.000000000000004</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -6691,7 +6695,7 @@
         <v>46281</v>
       </c>
       <c r="C57" t="n">
-        <v>1.28858563853837</v>
+        <v>1.288683628596204</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6720,7 +6724,7 @@
         <v>10</v>
       </c>
       <c r="J57" t="n">
-        <v>15.38502711012216</v>
+        <v>15.37859259320753</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -6765,7 +6769,7 @@
         <v>20.62560129901716</v>
       </c>
       <c r="Y57" t="n">
-        <v>15.38502711012216</v>
+        <v>15.37859259320753</v>
       </c>
       <c r="Z57" t="n">
         <v>2</v>
@@ -6810,7 +6814,7 @@
         <v>46281</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6691602614164166</v>
+        <v>0.6909974751093273</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6827,11 +6831,7 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %82.61: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6842,22 +6842,22 @@
         <v>18.04392839464337</v>
       </c>
       <c r="K58" t="n">
-        <v>2.566120069653621</v>
+        <v>5.913237958681949</v>
       </c>
       <c r="L58" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M58" t="n">
-        <v>82.60869565217391</v>
+        <v>73.68421052631579</v>
       </c>
       <c r="N58" t="n">
-        <v>18.56118354850544</v>
+        <v>17.77087948887664</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>5.297928718231892</v>
+        <v>1.970256109186397</v>
       </c>
       <c r="Q58" t="n">
         <v>25</v>
@@ -6884,13 +6884,17 @@
         <v>20.50322102897642</v>
       </c>
       <c r="Y58" t="n">
-        <v>14.88516307378175</v>
+        <v>12.10754612674306</v>
       </c>
       <c r="Z58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA58" t="inlineStr"/>
-      <c r="AB58" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>54.54545454545455</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>14.24828351986104</v>
+      </c>
       <c r="AC58" t="n">
         <v>6</v>
       </c>
@@ -6929,7 +6933,7 @@
         <v>46281</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7012207653417731</v>
+        <v>0.7049736354971337</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6954,10 +6958,10 @@
         <v>10</v>
       </c>
       <c r="J59" t="n">
-        <v>17.70408692387225</v>
+        <v>17.6978316350445</v>
       </c>
       <c r="K59" t="n">
-        <v>2.462462462462467</v>
+        <v>3.00300307154</v>
       </c>
       <c r="L59" t="n">
         <v>36</v>
@@ -6966,13 +6970,13 @@
         <v>63.88888888888889</v>
       </c>
       <c r="N59" t="n">
-        <v>15.95336001625915</v>
+        <v>15.22130524936779</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>5.404454865181707</v>
+        <v>4.85131188358594</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7038,7 +7042,7 @@
         <v>46281</v>
       </c>
       <c r="C60" t="n">
-        <v>10.1730445147766</v>
+        <v>10.23547750019054</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7063,10 +7067,10 @@
         <v>10</v>
       </c>
       <c r="J60" t="n">
-        <v>29.37463568904754</v>
+        <v>29.36926586330257</v>
       </c>
       <c r="K60" t="n">
-        <v>2.378490175801451</v>
+        <v>2.998965873836612</v>
       </c>
       <c r="L60" t="n">
         <v>5</v>
@@ -7075,13 +7079,13 @@
         <v>60</v>
       </c>
       <c r="N60" t="n">
-        <v>11.81922306253522</v>
+        <v>10.89704054938486</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>5.490909090909102</v>
+        <v>4.855421686746997</v>
       </c>
       <c r="Q60" t="n">
         <v>46</v>
@@ -7147,7 +7151,7 @@
         <v>46281</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6416211106087385</v>
+        <v>0.6416698805089741</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7176,10 +7180,10 @@
         <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>22.76465739752364</v>
+        <v>22.75878499834842</v>
       </c>
       <c r="K61" t="n">
-        <v>2.210121752277416e-06</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
         <v>25</v>
@@ -7194,7 +7198,7 @@
         <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>9.999997568866137</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
@@ -7221,7 +7225,7 @@
         <v>49.99145178651283</v>
       </c>
       <c r="Y61" t="n">
-        <v>22.76465569052852</v>
+        <v>22.75878499834842</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -7266,7 +7270,7 @@
         <v>46281</v>
       </c>
       <c r="C62" t="n">
-        <v>8.492950799457438</v>
+        <v>8.519287999656584</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7291,25 +7295,25 @@
         <v>10</v>
       </c>
       <c r="J62" t="n">
-        <v>11.10006525340588</v>
+        <v>11.09330596567706</v>
       </c>
       <c r="K62" t="n">
-        <v>2.226345083487957</v>
+        <v>2.53555967841681</v>
       </c>
       <c r="L62" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="M62" t="n">
-        <v>52.30769230769231</v>
+        <v>56.45161290322581</v>
       </c>
       <c r="N62" t="n">
-        <v>13.41078457700024</v>
+        <v>13.2947046315765</v>
       </c>
       <c r="O62" t="n">
         <v>6</v>
       </c>
       <c r="P62" t="n">
-        <v>3.691470054446455</v>
+        <v>3.378769601930043</v>
       </c>
       <c r="Q62" t="n">
         <v>30</v>
@@ -7375,7 +7379,7 @@
         <v>46281</v>
       </c>
       <c r="C63" t="n">
-        <v>0.09885322043651608</v>
+        <v>0.0986552087262155</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7400,10 +7404,10 @@
         <v>10</v>
       </c>
       <c r="J63" t="n">
-        <v>21.61385831157259</v>
+        <v>21.60790126179767</v>
       </c>
       <c r="K63" t="n">
-        <v>2.777777777777768</v>
+        <v>2.564110349551041</v>
       </c>
       <c r="L63" t="n">
         <v>8</v>
@@ -7412,13 +7416,13 @@
         <v>62.5</v>
       </c>
       <c r="N63" t="n">
-        <v>13.0731539657678</v>
+        <v>13.13794972801555</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>2.162162162162184</v>
+        <v>2.374992228906536</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7484,7 +7488,7 @@
         <v>46281</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1409840108512475</v>
+        <v>0.141405795837778</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7509,25 +7513,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>18.13743676119727</v>
+        <v>18.13121254268995</v>
       </c>
       <c r="K64" t="n">
-        <v>3.939395514233257</v>
+        <v>4.242427488521638</v>
       </c>
       <c r="L64" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M64" t="n">
-        <v>54.54545454545455</v>
+        <v>58.53658536585366</v>
       </c>
       <c r="N64" t="n">
-        <v>12.50629597748074</v>
+        <v>12.93871554408919</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>1.020406632653081</v>
+        <v>0.7267410494270932</v>
       </c>
       <c r="Q64" t="n">
         <v>55</v>
@@ -7593,7 +7597,7 @@
         <v>46281</v>
       </c>
       <c r="C65" t="n">
-        <v>6.067861399975338</v>
+        <v>6.181365177072901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7618,25 +7622,25 @@
         <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>15.62454617285346</v>
+        <v>15.61813089289524</v>
       </c>
       <c r="K65" t="n">
-        <v>1.98618307426599</v>
+        <v>3.886010362694314</v>
       </c>
       <c r="L65" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="M65" t="n">
-        <v>62.96296296296296</v>
+        <v>51.16279069767442</v>
       </c>
       <c r="N65" t="n">
-        <v>12.38469844409487</v>
+        <v>11.97402330287637</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>7.857747671464854</v>
+        <v>5.885286783042387</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7663,16 +7667,16 @@
         <v>24.47056390537039</v>
       </c>
       <c r="Y65" t="n">
-        <v>13.94869519010357</v>
+        <v>12.33904271515801</v>
       </c>
       <c r="Z65" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AA65" t="n">
-        <v>66.66666666666667</v>
+        <v>37.5</v>
       </c>
       <c r="AB65" t="n">
-        <v>16.71963460649922</v>
+        <v>15.0813486974636</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
@@ -7712,7 +7716,7 @@
         <v>46281</v>
       </c>
       <c r="C66" t="n">
-        <v>0.3962349459492787</v>
+        <v>0.3987314450084639</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7737,25 +7741,25 @@
         <v>10</v>
       </c>
       <c r="J66" t="n">
-        <v>19.91164625527118</v>
+        <v>19.90555336900347</v>
       </c>
       <c r="K66" t="n">
-        <v>2.172760996290402</v>
+        <v>2.808684453667465</v>
       </c>
       <c r="L66" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M66" t="n">
-        <v>45.71428571428572</v>
+        <v>51.35135135135135</v>
       </c>
       <c r="N66" t="n">
-        <v>14.07833946977136</v>
+        <v>15.65496524017184</v>
       </c>
       <c r="O66" t="n">
         <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>3.745850622406643</v>
+        <v>3.104130320596377</v>
       </c>
       <c r="Q66" t="n">
         <v>35</v>
@@ -7821,7 +7825,7 @@
         <v>46281</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02425089399482099</v>
+        <v>0.02425273682419872</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7846,10 +7850,10 @@
         <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>18.49564829454171</v>
+        <v>18.4894540984521</v>
       </c>
       <c r="K67" t="n">
-        <v>0.8547008547008517</v>
+        <v>0.8547000292205231</v>
       </c>
       <c r="L67" t="n">
         <v>5</v>
@@ -7864,7 +7868,7 @@
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>3.118644067796628</v>
+        <v>3.118644911806978</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7910,7 +7914,7 @@
         <v>46281</v>
       </c>
       <c r="C68" t="n">
-        <v>1.405729787496404</v>
+        <v>1.405836700147216</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7935,7 +7939,7 @@
         <v>10</v>
       </c>
       <c r="J68" t="n">
-        <v>74.82584548119281</v>
+        <v>74.8239308631663</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -8015,16 +8019,16 @@
         <v>46281</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4656993711208846</v>
+        <v>0.4682011737285541</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -8032,7 +8036,11 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H69" t="n">
         <v>5</v>
       </c>
@@ -8043,22 +8051,22 @@
         <v>22.2553779663549</v>
       </c>
       <c r="K69" t="n">
-        <v>7.52281869057625</v>
+        <v>8.100446415382079</v>
       </c>
       <c r="L69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M69" t="n">
-        <v>66.66666666666667</v>
+        <v>80</v>
       </c>
       <c r="N69" t="n">
-        <v>27.26484434775983</v>
+        <v>35.69382644421589</v>
       </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>0.4437953870954248</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8077,7 +8085,7 @@
         <v>45.36848923911108</v>
       </c>
       <c r="Y69" t="n">
-        <v>16.40679100908998</v>
+        <v>15.95771651767813</v>
       </c>
       <c r="Z69" t="n">
         <v>1</v>
@@ -8114,7 +8122,7 @@
         <v>46281</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4266513214682067</v>
+        <v>0.4312054482844937</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8139,25 +8147,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>24.07326740435939</v>
+        <v>24.06749420464227</v>
       </c>
       <c r="K70" t="n">
-        <v>1.665034280117528</v>
+        <v>2.742406747336301</v>
       </c>
       <c r="L70" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M70" t="n">
-        <v>66.66666666666667</v>
+        <v>68</v>
       </c>
       <c r="N70" t="n">
-        <v>14.52954830714423</v>
+        <v>14.3189803914637</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>6.231213872832386</v>
+        <v>5.11725724470633</v>
       </c>
       <c r="Q70" t="n">
         <v>31</v>
@@ -8184,7 +8192,7 @@
         <v>44.93251946562029</v>
       </c>
       <c r="Y70" t="n">
-        <v>22.8090612788688</v>
+        <v>21.98511604228885</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -8229,7 +8237,7 @@
         <v>46281</v>
       </c>
       <c r="C71" t="n">
-        <v>2.951210489539233</v>
+        <v>2.984319883151526</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8254,19 +8262,19 @@
         <v>10</v>
       </c>
       <c r="J71" t="n">
-        <v>12.71302799751677</v>
+        <v>12.70639134744024</v>
       </c>
       <c r="K71" t="n">
-        <v>2.206405693950164</v>
+        <v>3.345193558718873</v>
       </c>
       <c r="L71" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="M71" t="n">
-        <v>54.66666666666666</v>
+        <v>54.41176470588236</v>
       </c>
       <c r="N71" t="n">
-        <v>17.0847915617772</v>
+        <v>17.10351843160066</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
@@ -8338,7 +8346,7 @@
         <v>46281</v>
       </c>
       <c r="C72" t="n">
-        <v>0.05322865715812405</v>
+        <v>0.05323270241827414</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8367,10 +8375,10 @@
         <v>10</v>
       </c>
       <c r="J72" t="n">
-        <v>37.36130799911185</v>
+        <v>37.35654542033834</v>
       </c>
       <c r="K72" t="n">
-        <v>3.474903587097344e-06</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
         <v>4</v>
@@ -8385,7 +8393,7 @@
         <v>10</v>
       </c>
       <c r="P72" t="n">
-        <v>9.999996177606185</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q72" t="n">
         <v>15</v>
@@ -8451,7 +8459,7 @@
         <v>46281</v>
       </c>
       <c r="C73" t="n">
-        <v>0.05507830161535616</v>
+        <v>0.0554935537395348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8476,25 +8484,25 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>28.80614321513075</v>
+        <v>28.80072718754351</v>
       </c>
       <c r="K73" t="n">
-        <v>1.901140684410652</v>
+        <v>2.661594565484626</v>
       </c>
       <c r="L73" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M73" t="n">
-        <v>58.33333333333334</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N73" t="n">
-        <v>20.11481107078213</v>
+        <v>20.00269978225033</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>7.947761194029845</v>
+        <v>7.148150645404638</v>
       </c>
       <c r="Q73" t="n">
         <v>14</v>
@@ -8560,7 +8568,7 @@
         <v>46281</v>
       </c>
       <c r="C74" t="n">
-        <v>4.901557811665091</v>
+        <v>4.901930489549083</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8585,7 +8593,7 @@
         <v>10</v>
       </c>
       <c r="J74" t="n">
-        <v>17.37576052515606</v>
+        <v>17.36947839447086</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -8630,7 +8638,7 @@
         <v>24.51464461150628</v>
       </c>
       <c r="Y74" t="n">
-        <v>17.37576052515606</v>
+        <v>17.36947839447086</v>
       </c>
       <c r="Z74" t="n">
         <v>3</v>
@@ -8679,7 +8687,7 @@
         <v>46281</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1058407661638374</v>
+        <v>0.1066709414460192</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8696,7 +8704,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %81.82: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>5</v>
       </c>
@@ -8704,25 +8716,25 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>22.61594163229673</v>
+        <v>22.61005884355163</v>
       </c>
       <c r="K75" t="n">
-        <v>1.778656126482225</v>
+        <v>2.56917236248031</v>
       </c>
       <c r="L75" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M75" t="n">
-        <v>66.66666666666667</v>
+        <v>81.81818181818181</v>
       </c>
       <c r="N75" t="n">
-        <v>13.79231513665973</v>
+        <v>16.95980103928093</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>4.147572815533973</v>
+        <v>3.344891606802802</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8788,7 +8800,7 @@
         <v>46281</v>
       </c>
       <c r="C76" t="n">
-        <v>1.733527888528094</v>
+        <v>1.732632097357969</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8813,25 +8825,25 @@
         <v>10</v>
       </c>
       <c r="J76" t="n">
-        <v>16.6968026846143</v>
+        <v>16.69046584362804</v>
       </c>
       <c r="K76" t="n">
-        <v>2.490886998784925</v>
+        <v>2.430133567291515</v>
       </c>
       <c r="L76" t="n">
         <v>40</v>
       </c>
       <c r="M76" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="N76" t="n">
-        <v>12.58967301356177</v>
+        <v>12.09379352040093</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>7.326615293420291</v>
+        <v>7.390272929533448</v>
       </c>
       <c r="Q76" t="n">
         <v>41</v>
@@ -8897,7 +8909,7 @@
         <v>46281</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4418595092276706</v>
+        <v>0.4468258604417319</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8922,25 +8934,25 @@
         <v>10</v>
       </c>
       <c r="J77" t="n">
-        <v>24.27956799614378</v>
+        <v>24.27381268520708</v>
       </c>
       <c r="K77" t="n">
-        <v>2.089268755935425</v>
+        <v>3.228871401296374</v>
       </c>
       <c r="L77" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M77" t="n">
-        <v>62.5</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N77" t="n">
-        <v>15.58240736748492</v>
+        <v>14.93209402914525</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>5.789767441860461</v>
+        <v>4.621893598115734</v>
       </c>
       <c r="Q77" t="n">
         <v>27</v>
@@ -9006,7 +9018,7 @@
         <v>46281</v>
       </c>
       <c r="C78" t="n">
-        <v>0.05179004480249907</v>
+        <v>0.0517939821200213</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9031,10 +9043,10 @@
         <v>10</v>
       </c>
       <c r="J78" t="n">
-        <v>17.7040978274358</v>
+        <v>17.69784066106923</v>
       </c>
       <c r="K78" t="n">
-        <v>7.936507895323075e-07</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
         <v>54</v>
@@ -9049,7 +9061,7 @@
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>3.999999174603186</v>
+        <v>4.000000000000004</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9076,7 +9088,7 @@
         <v>36.67113091579677</v>
       </c>
       <c r="Y78" t="n">
-        <v>17.70409717429371</v>
+        <v>17.69784066106923</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -9121,7 +9133,7 @@
         <v>46281</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7863044103744502</v>
+        <v>0.7855420934629819</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9140,7 +9152,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.95: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %76.19: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H79" t="n">
@@ -9150,25 +9162,25 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>21.27764888392525</v>
+        <v>21.2716637331844</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2620545073375391</v>
+        <v>0.1572362951673512</v>
       </c>
       <c r="L79" t="n">
         <v>21</v>
       </c>
       <c r="M79" t="n">
-        <v>80.95238095238095</v>
+        <v>76.19047619047619</v>
       </c>
       <c r="N79" t="n">
-        <v>10.96162233878875</v>
+        <v>11.16947312028342</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>4.72556194458964</v>
+        <v>4.835161076690286</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9234,7 +9246,7 @@
         <v>46281</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1255703070409799</v>
+        <v>0.1253743207381818</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9259,25 +9271,25 @@
         <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>14.37257191021615</v>
+        <v>14.3660641740055</v>
       </c>
       <c r="K80" t="n">
-        <v>2.689075630252113</v>
+        <v>2.521009996469248</v>
       </c>
       <c r="L80" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M80" t="n">
-        <v>56.52173913043478</v>
+        <v>53.52112676056338</v>
       </c>
       <c r="N80" t="n">
-        <v>14.08548448314545</v>
+        <v>14.10895329588439</v>
       </c>
       <c r="O80" t="n">
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>7.119476268412428</v>
+        <v>7.295080299919343</v>
       </c>
       <c r="Q80" t="n">
         <v>39</v>
@@ -9343,7 +9355,7 @@
         <v>46281</v>
       </c>
       <c r="C81" t="n">
-        <v>1.155000205516051</v>
+        <v>1.156115681497425</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9368,25 +9380,25 @@
         <v>10</v>
       </c>
       <c r="J81" t="n">
-        <v>11.64050719803407</v>
+        <v>11.63378900147833</v>
       </c>
       <c r="K81" t="n">
-        <v>2.648401826484026</v>
+        <v>2.739726027397271</v>
       </c>
       <c r="L81" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M81" t="n">
-        <v>51.02040816326531</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="N81" t="n">
-        <v>13.2556313833504</v>
+        <v>13.27513906931236</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>7.161921708185059</v>
+        <v>7.066666666666666</v>
       </c>
       <c r="Q81" t="n">
         <v>32</v>
@@ -9413,22 +9425,22 @@
         <v>23.79225853623819</v>
       </c>
       <c r="Y81" t="n">
-        <v>9.300392776794785</v>
+        <v>9.212796919327049</v>
       </c>
       <c r="Z81" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA81" t="n">
-        <v>57.14285714285715</v>
+        <v>62.5</v>
       </c>
       <c r="AB81" t="n">
-        <v>9.102176101498813</v>
+        <v>9.59631867771729</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.771345372514709</v>
+        <v>0.8670859481963</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9462,16 +9474,16 @@
         <v>46281</v>
       </c>
       <c r="C82" t="n">
-        <v>4.675490155781167</v>
+        <v>4.663513619190403</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9487,25 +9499,25 @@
         <v>10</v>
       </c>
       <c r="J82" t="n">
-        <v>19.38437075474348</v>
+        <v>20.03998055701367</v>
       </c>
       <c r="K82" t="n">
-        <v>3.739168643846491</v>
+        <v>4.321836275862068</v>
       </c>
       <c r="L82" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M82" t="n">
-        <v>42.85714285714285</v>
+        <v>40</v>
       </c>
       <c r="N82" t="n">
-        <v>8.579489435939424</v>
+        <v>10.05840616638602</v>
       </c>
       <c r="O82" t="n">
         <v>4</v>
       </c>
       <c r="P82" t="n">
-        <v>0.2514299657143004</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
         <v>8</v>
@@ -9571,7 +9583,7 @@
         <v>46281</v>
       </c>
       <c r="C83" t="n">
-        <v>5.137901270089194</v>
+        <v>5.189674836943998</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9596,25 +9608,25 @@
         <v>10</v>
       </c>
       <c r="J83" t="n">
-        <v>17.93020279426077</v>
+        <v>17.92396384855412</v>
       </c>
       <c r="K83" t="n">
-        <v>2.79605263157896</v>
+        <v>3.824014459963987</v>
       </c>
       <c r="L83" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M83" t="n">
-        <v>51.35135135135135</v>
+        <v>61.76470588235294</v>
       </c>
       <c r="N83" t="n">
-        <v>12.36250608798611</v>
+        <v>11.78231284439357</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>7.007999999999992</v>
+        <v>5.948513522772303</v>
       </c>
       <c r="Q83" t="n">
         <v>41</v>
@@ -9680,7 +9692,7 @@
         <v>46281</v>
       </c>
       <c r="C84" t="n">
-        <v>1.960623124666036</v>
+        <v>1.967965804504506</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9705,25 +9717,25 @@
         <v>10</v>
       </c>
       <c r="J84" t="n">
-        <v>15.19236884649807</v>
+        <v>15.18592070700058</v>
       </c>
       <c r="K84" t="n">
-        <v>3.414634146341466</v>
+        <v>3.794037940379402</v>
       </c>
       <c r="L84" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M84" t="n">
-        <v>59.09090909090909</v>
+        <v>59.52380952380953</v>
       </c>
       <c r="N84" t="n">
-        <v>12.78563173092211</v>
+        <v>12.80301434137708</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>1.53301886792454</v>
+        <v>1.161879895561357</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9789,7 +9801,7 @@
         <v>46281</v>
       </c>
       <c r="C85" t="n">
-        <v>5.54379547042624</v>
+        <v>5.611014774200838</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9814,10 +9826,10 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>20.69989676657544</v>
+        <v>20.69386737840766</v>
       </c>
       <c r="K85" t="n">
-        <v>4.453049370764761</v>
+        <v>5.711519845111335</v>
       </c>
       <c r="L85" t="n">
         <v>25</v>
@@ -9826,13 +9838,13 @@
         <v>60</v>
       </c>
       <c r="N85" t="n">
-        <v>12.3216736571236</v>
+        <v>12.47903562685071</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>3.395736793327164</v>
+        <v>2.164835164835166</v>
       </c>
       <c r="Q85" t="n">
         <v>32</v>
@@ -9898,21 +9910,21 @@
         <v>46281</v>
       </c>
       <c r="C86" t="n">
-        <v>4.747420773562415</v>
+        <v>4.823828389711874</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -9930,7 +9942,7 @@
         <v>18.73514495170452</v>
       </c>
       <c r="K86" t="n">
-        <v>13.87673382126915</v>
+        <v>15.70952897071627</v>
       </c>
       <c r="L86" t="n">
         <v>4</v>
@@ -9939,7 +9951,7 @@
         <v>100</v>
       </c>
       <c r="N86" t="n">
-        <v>11.59313326334698</v>
+        <v>9.572507806866966</v>
       </c>
       <c r="O86" t="n">
         <v>8</v>
@@ -9972,22 +9984,22 @@
         <v>32.57395859734095</v>
       </c>
       <c r="Y86" t="n">
-        <v>7.458237326412343</v>
+        <v>5.968819004881953</v>
       </c>
       <c r="Z86" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AA86" t="n">
-        <v>25</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AB86" t="n">
-        <v>5.266319656673107</v>
+        <v>11.53839637208252</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>0.03316027171845759</v>
       </c>
       <c r="AE86" t="n">
         <v>52</v>
@@ -10021,7 +10033,7 @@
         <v>46281</v>
       </c>
       <c r="C87" t="n">
-        <v>5.564347075506597</v>
+        <v>5.595599898447539</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10046,25 +10058,25 @@
         <v>10</v>
       </c>
       <c r="J87" t="n">
-        <v>13.37852897610052</v>
+        <v>13.37194292575289</v>
       </c>
       <c r="K87" t="n">
-        <v>4.134615384615392</v>
+        <v>4.711538461538467</v>
       </c>
       <c r="L87" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M87" t="n">
-        <v>62.96296296296296</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N87" t="n">
-        <v>12.51943425223574</v>
+        <v>12.46335282189862</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>0.8310249307479145</v>
+        <v>0.2754820936639035</v>
       </c>
       <c r="Q87" t="n">
         <v>47</v>
@@ -10091,16 +10103,16 @@
         <v>15.88967756874082</v>
       </c>
       <c r="Y87" t="n">
-        <v>9.797064308766213</v>
+        <v>9.290428698216235</v>
       </c>
       <c r="Z87" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA87" t="n">
-        <v>38.09523809523809</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="AB87" t="n">
-        <v>9.982420860260039</v>
+        <v>9.81984764394735</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
@@ -10140,7 +10152,7 @@
         <v>46281</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9704467918944469</v>
+        <v>0.9729869606312084</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10165,19 +10177,19 @@
         <v>10</v>
       </c>
       <c r="J88" t="n">
-        <v>21.41965384897848</v>
+        <v>21.4136770887586</v>
       </c>
       <c r="K88" t="n">
-        <v>3.280839895013132</v>
+        <v>3.543304651731605</v>
       </c>
       <c r="L88" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M88" t="n">
-        <v>70.27027027027027</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N88" t="n">
-        <v>15.09663045550047</v>
+        <v>15.7982644002163</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
@@ -10249,7 +10261,7 @@
         <v>46281</v>
       </c>
       <c r="C89" t="n">
-        <v>2.023305520161125</v>
+        <v>2.035791320506183</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10274,25 +10286,25 @@
         <v>10</v>
       </c>
       <c r="J89" t="n">
-        <v>15.60931331442587</v>
+        <v>15.60289553329434</v>
       </c>
       <c r="K89" t="n">
-        <v>2.392095683827344</v>
+        <v>3.016122177694558</v>
       </c>
       <c r="L89" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="M89" t="n">
-        <v>59.72222222222222</v>
+        <v>60.9375</v>
       </c>
       <c r="N89" t="n">
-        <v>14.82350100418043</v>
+        <v>15.49811169581316</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>1.570340274250892</v>
+        <v>0.9550716931552961</v>
       </c>
       <c r="Q89" t="n">
         <v>45</v>
@@ -10319,16 +10331,16 @@
         <v>21.41032003314154</v>
       </c>
       <c r="Y89" t="n">
-        <v>13.59060734066798</v>
+        <v>13.05737574814198</v>
       </c>
       <c r="Z89" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA89" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="AB89" t="n">
-        <v>15.88199252440822</v>
+        <v>20.63598439723828</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
@@ -10368,7 +10380,7 @@
         <v>46281</v>
       </c>
       <c r="C90" t="n">
-        <v>2.560729993012454</v>
+        <v>2.571201244203928</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10393,25 +10405,25 @@
         <v>10</v>
       </c>
       <c r="J90" t="n">
-        <v>19.80990087027463</v>
+        <v>19.80380280689519</v>
       </c>
       <c r="K90" t="n">
-        <v>2.214930270713689</v>
+        <v>2.625099999865443</v>
       </c>
       <c r="L90" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M90" t="n">
-        <v>63.04347826086956</v>
+        <v>67.44186046511628</v>
       </c>
       <c r="N90" t="n">
-        <v>17.25633212126395</v>
+        <v>16.22175178846877</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>5.659711075441431</v>
+        <v>5.237412679882025</v>
       </c>
       <c r="Q90" t="n">
         <v>43</v>
@@ -10477,7 +10489,7 @@
         <v>46281</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2135311767849069</v>
+        <v>0.2147805982575309</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10502,25 +10514,25 @@
         <v>10</v>
       </c>
       <c r="J91" t="n">
-        <v>13.48785164958405</v>
+        <v>13.48127127666011</v>
       </c>
       <c r="K91" t="n">
-        <v>2.062868369351678</v>
+        <v>2.652254339666116</v>
       </c>
       <c r="L91" t="n">
         <v>62</v>
       </c>
       <c r="M91" t="n">
-        <v>64.51612903225806</v>
+        <v>61.29032258064516</v>
       </c>
       <c r="N91" t="n">
-        <v>15.63083422701726</v>
+        <v>14.02094716097644</v>
       </c>
       <c r="O91" t="n">
         <v>6</v>
       </c>
       <c r="P91" t="n">
-        <v>3.85755534167469</v>
+        <v>3.261249041113623</v>
       </c>
       <c r="Q91" t="n">
         <v>44</v>
@@ -10586,7 +10598,7 @@
         <v>46281</v>
       </c>
       <c r="C92" t="n">
-        <v>1.023880965103374</v>
+        <v>1.024369879808872</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10611,25 +10623,25 @@
         <v>10</v>
       </c>
       <c r="J92" t="n">
-        <v>18.95953720206354</v>
+        <v>18.9533737337655</v>
       </c>
       <c r="K92" t="n">
-        <v>0.8910490076954103</v>
+        <v>0.9315493520300144</v>
       </c>
       <c r="L92" t="n">
         <v>39</v>
       </c>
       <c r="M92" t="n">
-        <v>69.23076923076923</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N92" t="n">
-        <v>14.14877382778777</v>
+        <v>14.27412854503239</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>7.046166198313952</v>
+        <v>7.003212269452619</v>
       </c>
       <c r="Q92" t="n">
         <v>44</v>
@@ -10695,7 +10707,7 @@
         <v>46281</v>
       </c>
       <c r="C93" t="n">
-        <v>0.03925356570348144</v>
+        <v>0.03925654963513977</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10720,10 +10732,10 @@
         <v>10</v>
       </c>
       <c r="J93" t="n">
-        <v>13.4934398260194</v>
+        <v>13.48686157735825</v>
       </c>
       <c r="K93" t="n">
-        <v>3.243243243243232</v>
+        <v>3.243240505478484</v>
       </c>
       <c r="L93" t="n">
         <v>62</v>
@@ -10738,7 +10750,7 @@
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>2.670157068062839</v>
+        <v>2.670159790630788</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10804,11 +10816,11 @@
         <v>46281</v>
       </c>
       <c r="C94" t="n">
-        <v>8.251469439763245</v>
+        <v>8.2572351118505</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -10829,25 +10841,25 @@
         <v>10</v>
       </c>
       <c r="J94" t="n">
-        <v>10.48063678978293</v>
+        <v>10.47383040533549</v>
       </c>
       <c r="K94" t="n">
-        <v>5.657894736842084</v>
+        <v>5.723684210526314</v>
       </c>
       <c r="L94" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M94" t="n">
-        <v>46.42857142857143</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="N94" t="n">
-        <v>15.50282251833736</v>
+        <v>15.97263423873417</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>2.216687422166896</v>
+        <v>2.153080273802122</v>
       </c>
       <c r="Q94" t="n">
         <v>41</v>
@@ -10874,7 +10886,7 @@
         <v>36.6815048892442</v>
       </c>
       <c r="Y94" t="n">
-        <v>5.415725450257503</v>
+        <v>5.349635171956669</v>
       </c>
       <c r="Z94" t="n">
         <v>13</v>
@@ -10889,7 +10901,7 @@
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>0.617729059639005</v>
+        <v>0.6871234244314794</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -10923,7 +10935,7 @@
         <v>46281</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1140614121007851</v>
+        <v>0.11057604433118</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10948,25 +10960,25 @@
         <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>24.77761294047443</v>
+        <v>27.10987320553127</v>
       </c>
       <c r="K95" t="n">
-        <v>1.462530220682146</v>
+        <v>1.509432398718458</v>
       </c>
       <c r="L95" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="M95" t="n">
-        <v>61.90476190476191</v>
+        <v>40</v>
       </c>
       <c r="N95" t="n">
-        <v>16.35774984253148</v>
+        <v>13.50348863394128</v>
       </c>
       <c r="O95" t="n">
         <v>10</v>
       </c>
       <c r="P95" t="n">
-        <v>8.414406540768082</v>
+        <v>8.364313936789136</v>
       </c>
       <c r="Q95" t="n">
         <v>21</v>
@@ -11032,7 +11044,7 @@
         <v>46281</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1214599860249085</v>
+        <v>0.1229079430840341</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11057,25 +11069,25 @@
         <v>10</v>
       </c>
       <c r="J96" t="n">
-        <v>11.75714561105962</v>
+        <v>11.75043307651951</v>
       </c>
       <c r="K96" t="n">
-        <v>2.249134948096887</v>
+        <v>3.46020419954276</v>
       </c>
       <c r="L96" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="M96" t="n">
-        <v>49.27536231884058</v>
+        <v>49.12280701754386</v>
       </c>
       <c r="N96" t="n">
-        <v>13.74821700210951</v>
+        <v>13.78833771514818</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>7.580372250423029</v>
+        <v>6.321073741401095</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11141,7 +11153,7 @@
         <v>46281</v>
       </c>
       <c r="C97" t="n">
-        <v>1.732500308274076</v>
+        <v>1.75215754395832</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11166,25 +11178,25 @@
         <v>10</v>
       </c>
       <c r="J97" t="n">
-        <v>19.39936861373087</v>
+        <v>19.39324184071789</v>
       </c>
       <c r="K97" t="n">
-        <v>2.367941712204003</v>
+        <v>3.521556264577774</v>
       </c>
       <c r="L97" t="n">
         <v>29</v>
       </c>
       <c r="M97" t="n">
-        <v>51.72413793103448</v>
+        <v>48.27586206896552</v>
       </c>
       <c r="N97" t="n">
-        <v>13.16306078720314</v>
+        <v>12.52044075672272</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>1.59430604982207</v>
+        <v>0.462168221466297</v>
       </c>
       <c r="Q97" t="n">
         <v>50</v>
@@ -11250,7 +11262,7 @@
         <v>46281</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6268239549508816</v>
+        <v>0.6342707668665086</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11275,25 +11287,25 @@
         <v>10</v>
       </c>
       <c r="J98" t="n">
-        <v>20.01394502517393</v>
+        <v>20.00786348235382</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>1.180329868852459</v>
       </c>
       <c r="L98" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M98" t="n">
-        <v>57.14285714285715</v>
+        <v>55.31914893617022</v>
       </c>
       <c r="N98" t="n">
-        <v>17.96328743253116</v>
+        <v>17.88226239073032</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>10.00000000000001</v>
+        <v>8.716783333854906</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11320,7 +11332,7 @@
         <v>30.85778357900837</v>
       </c>
       <c r="Y98" t="n">
-        <v>20.01394502517393</v>
+        <v>19.0636924023028</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
@@ -11365,7 +11377,7 @@
         <v>46281</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4911833614205269</v>
+        <v>0.4899875203611729</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11390,25 +11402,25 @@
         <v>10</v>
       </c>
       <c r="J99" t="n">
-        <v>18.77734876067304</v>
+        <v>18.77117372239303</v>
       </c>
       <c r="K99" t="n">
-        <v>3.195164075993073</v>
+        <v>2.936098032833123</v>
       </c>
       <c r="L99" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M99" t="n">
-        <v>47.91666666666666</v>
+        <v>49.01960784313726</v>
       </c>
       <c r="N99" t="n">
-        <v>17.00887407976602</v>
+        <v>17.45280326453614</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>0.7799163179916579</v>
+        <v>1.033555756919724</v>
       </c>
       <c r="Q99" t="n">
         <v>34</v>
@@ -11435,7 +11447,7 @@
         <v>33.04241514445872</v>
       </c>
       <c r="Y99" t="n">
-        <v>16.18215178670491</v>
+        <v>16.38621575196278</v>
       </c>
       <c r="Z99" t="n">
         <v>0</v>
@@ -11480,7 +11492,7 @@
         <v>46281</v>
       </c>
       <c r="C100" t="n">
-        <v>316.3537270015208</v>
+        <v>311.378643642982</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11505,25 +11517,25 @@
         <v>10</v>
       </c>
       <c r="J100" t="n">
-        <v>14.53977367380488</v>
+        <v>16.74174295537163</v>
       </c>
       <c r="K100" t="n">
-        <v>1.606827379056286</v>
+        <v>2.653906669425177</v>
       </c>
       <c r="L100" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M100" t="n">
-        <v>48.07692307692308</v>
+        <v>43.58974358974359</v>
       </c>
       <c r="N100" t="n">
-        <v>13.92213299672397</v>
+        <v>12.95131148290171</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
       </c>
       <c r="P100" t="n">
-        <v>3.33951242103554</v>
+        <v>2.285439888936636</v>
       </c>
       <c r="Q100" t="n">
         <v>48</v>
@@ -11589,16 +11601,16 @@
         <v>46281</v>
       </c>
       <c r="C101" t="n">
-        <v>320.7994574376258</v>
+        <v>323.0144060479765</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -11614,25 +11626,25 @@
         <v>10</v>
       </c>
       <c r="J101" t="n">
-        <v>12.87519982509333</v>
+        <v>12.8685741725276</v>
       </c>
       <c r="K101" t="n">
-        <v>1.874530094816418</v>
+        <v>2.57011898166426</v>
       </c>
       <c r="L101" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M101" t="n">
-        <v>51.16279069767442</v>
+        <v>43.58974358974359</v>
       </c>
       <c r="N101" t="n">
-        <v>10.70929923463633</v>
+        <v>10.26074329556575</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
       </c>
       <c r="P101" t="n">
-        <v>0.1231612112142288</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
         <v>30</v>
@@ -11698,7 +11710,7 @@
         <v>46281</v>
       </c>
       <c r="C102" t="n">
-        <v>382.3463960191541</v>
+        <v>376.6443845813294</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11723,25 +11735,25 @@
         <v>10</v>
       </c>
       <c r="J102" t="n">
-        <v>11.90771915911735</v>
+        <v>13.67983142705997</v>
       </c>
       <c r="K102" t="n">
-        <v>1.818425143219238</v>
+        <v>2.359097070931426</v>
       </c>
       <c r="L102" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="M102" t="n">
-        <v>50</v>
+        <v>53.125</v>
       </c>
       <c r="N102" t="n">
-        <v>9.386884136526934</v>
+        <v>10.62899496630217</v>
       </c>
       <c r="O102" t="n">
         <v>4</v>
       </c>
       <c r="P102" t="n">
-        <v>2.142613042494168</v>
+        <v>1.603084607058891</v>
       </c>
       <c r="Q102" t="n">
         <v>29</v>
@@ -11807,7 +11819,7 @@
         <v>46281</v>
       </c>
       <c r="C103" t="n">
-        <v>0.6535410415553454</v>
+        <v>0.6601677236027294</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11832,25 +11844,25 @@
         <v>10</v>
       </c>
       <c r="J103" t="n">
-        <v>18.80894382278397</v>
+        <v>18.80277245522091</v>
       </c>
       <c r="K103" t="n">
-        <v>1.857783472133256</v>
+        <v>2.882766303302664</v>
       </c>
       <c r="L103" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="M103" t="n">
-        <v>52.27272727272727</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="N103" t="n">
-        <v>19.06584845343957</v>
+        <v>18.45620348177728</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
       </c>
       <c r="P103" t="n">
-        <v>7.993710691823908</v>
+        <v>6.917809417872234</v>
       </c>
       <c r="Q103" t="n">
         <v>43</v>
@@ -11916,7 +11928,7 @@
         <v>46281</v>
       </c>
       <c r="C104" t="n">
-        <v>0.05261210900571334</v>
+        <v>0.05241057653355823</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11973,25 +11985,25 @@
         <v>63.23529411764706</v>
       </c>
       <c r="X104" t="n">
-        <v>17.89060837989</v>
+        <v>17.89957543470515</v>
       </c>
       <c r="Y104" t="n">
-        <v>4.119850187265916</v>
+        <v>4.494386756722479</v>
       </c>
       <c r="Z104" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA104" t="n">
-        <v>47.22222222222222</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="AB104" t="n">
-        <v>13.61814568788858</v>
+        <v>13.85961485882081</v>
       </c>
       <c r="AC104" t="n">
         <v>5</v>
       </c>
       <c r="AD104" t="n">
-        <v>0.9179687500000089</v>
+        <v>0.5294068339099622</v>
       </c>
       <c r="AE104" t="n">
         <v>42</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -444,7 +444,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C2" t="n">
-        <v>0.372834449015693</v>
+        <v>0.3872624550590653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,25 +695,25 @@
         <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>22.33032903992303</v>
+        <v>22.31899460285077</v>
       </c>
       <c r="K2" t="n">
-        <v>2.659871578223538</v>
+        <v>6.617060638595862</v>
       </c>
       <c r="L2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M2" t="n">
-        <v>57.89473684210526</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N2" t="n">
-        <v>13.30650164128567</v>
+        <v>12.44788564839658</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>7.149948961492258</v>
+        <v>3.172981266920716</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -754,10 +754,10 @@
         <v>52.17391304347826</v>
       </c>
       <c r="AG2" t="n">
-        <v>36.38659031107544</v>
+        <v>36.22766409236662</v>
       </c>
       <c r="AH2" t="n">
-        <v>15.78732273240281</v>
+        <v>15.94624895111164</v>
       </c>
       <c r="AI2" t="n">
         <v>38.13741307280403</v>
@@ -779,7 +779,7 @@
         <v>46281</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6827762551076552</v>
+        <v>0.6828758935431253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,22 +807,22 @@
         <v>16.52890779617068</v>
       </c>
       <c r="K3" t="n">
-        <v>8.604295835326203</v>
+        <v>8.620144602827162</v>
       </c>
       <c r="L3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M3" t="n">
-        <v>66.66666666666667</v>
+        <v>65.51724137931035</v>
       </c>
       <c r="N3" t="n">
-        <v>11.99220577121672</v>
+        <v>12.05054107876322</v>
       </c>
       <c r="O3" t="n">
         <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>1.285127953676968</v>
+        <v>1.270349438603979</v>
       </c>
       <c r="Q3" t="n">
         <v>35</v>
@@ -849,7 +849,7 @@
         <v>17.17248092970491</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.312455131439089</v>
+        <v>7.298929116307217</v>
       </c>
       <c r="Z3" t="n">
         <v>25</v>
@@ -864,7 +864,7 @@
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.899574988605091</v>
+        <v>2.913742913586914</v>
       </c>
       <c r="AE3" t="n">
         <v>34</v>
@@ -895,24 +895,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C4" t="n">
-        <v>1.340066469466299</v>
+        <v>1.43502824858757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -923,25 +923,25 @@
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>18.01676654844163</v>
+        <v>18.0048026275308</v>
       </c>
       <c r="K4" t="n">
-        <v>3.821652450707891</v>
+        <v>11.16259437813452</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="M4" t="n">
-        <v>52.77777777777778</v>
+        <v>50</v>
       </c>
       <c r="N4" t="n">
-        <v>15.53719206193585</v>
+        <v>16.66999385576534</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>1.13497283223416</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>53</v>
@@ -964,31 +964,41 @@
       <c r="W4" t="n">
         <v>62.5</v>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>11.56045620482793</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.3566333808844635</v>
+      </c>
       <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>39.6551724137931</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>11.61340489271349</v>
+      </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AD4" t="n">
+        <v>9.677881173944147</v>
+      </c>
       <c r="AE4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF4" t="n">
-        <v>60</v>
+        <v>58.97435897435897</v>
       </c>
       <c r="AG4" t="n">
-        <v>38.95309468037216</v>
+        <v>38.98149428237421</v>
       </c>
       <c r="AH4" t="n">
-        <v>21.04690531962784</v>
+        <v>19.99286469198476</v>
       </c>
       <c r="AI4" t="n">
-        <v>44.59589366034619</v>
+        <v>43.41862288289698</v>
       </c>
       <c r="AJ4" t="n">
         <v>64</v>
@@ -1004,10 +1014,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2180691020019262</v>
+        <v>0.2233179250128403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,11 +1034,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %79.17: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>5</v>
       </c>
@@ -1036,19 +1042,19 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>22.19651614701201</v>
+        <v>21.70061550970117</v>
       </c>
       <c r="K5" t="n">
-        <v>4.12168888430906</v>
+        <v>6.612291985926122</v>
       </c>
       <c r="L5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M5" t="n">
-        <v>79.16666666666667</v>
+        <v>69.56521739130434</v>
       </c>
       <c r="N5" t="n">
-        <v>10.73688545398247</v>
+        <v>12.20014732543721</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -1089,19 +1095,19 @@
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF5" t="n">
-        <v>51.11111111111111</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="AG5" t="n">
-        <v>27.05164642728918</v>
+        <v>28.62807286251545</v>
       </c>
       <c r="AH5" t="n">
-        <v>24.05946468382194</v>
+        <v>23.54584018096281</v>
       </c>
       <c r="AI5" t="n">
-        <v>37.00446464458318</v>
+        <v>38.13741307280403</v>
       </c>
       <c r="AJ5" t="n">
         <v>64</v>
@@ -1117,19 +1123,19 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C6" t="n">
-        <v>1.378089955032092</v>
+        <v>1.386748844375963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1145,10 +1151,10 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>34.43819966856769</v>
+        <v>38.01799643637762</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>10.38430089942763</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1159,7 +1165,7 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.000000000000002</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>35</v>
@@ -1200,19 +1206,19 @@
         <v>46.93877551020408</v>
       </c>
       <c r="AG6" t="n">
-        <v>38.69119903261306</v>
+        <v>38.34885643649939</v>
       </c>
       <c r="AH6" t="n">
-        <v>8.247576477591025</v>
+        <v>8.589919073704692</v>
       </c>
       <c r="AI6" t="n">
         <v>33.70350369317515</v>
       </c>
       <c r="AJ6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AK6" t="n">
-        <v>40</v>
+        <v>40.50632911392405</v>
       </c>
     </row>
     <row r="7">
@@ -1222,10 +1228,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C7" t="n">
-        <v>2.149861306947088</v>
+        <v>2.218798151001541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,25 +1256,25 @@
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>15.67879320005955</v>
+        <v>15.66648809562797</v>
       </c>
       <c r="K7" t="n">
-        <v>3.05418568472906</v>
+        <v>6.343173229902788</v>
       </c>
       <c r="L7" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="M7" t="n">
-        <v>66.66666666666667</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N7" t="n">
-        <v>13.0925230763544</v>
+        <v>13.49804390284456</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>4.799236714558641</v>
+        <v>1.558000123350967</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1295,16 +1301,16 @@
         <v>18.9234494530097</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.10346697278498</v>
+        <v>10.31706734467297</v>
       </c>
       <c r="Z7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AA7" t="n">
-        <v>66.66666666666667</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.880102520564243</v>
+        <v>13.52821329026354</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1341,10 +1347,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3074753891812642</v>
+        <v>0.3042629686697483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,25 +1375,25 @@
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>25.12526584256618</v>
+        <v>30.96043286594978</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>7.318840579710151</v>
       </c>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
         <v>66.66666666666667</v>
       </c>
       <c r="N8" t="n">
-        <v>20.50481622935367</v>
+        <v>10.50913721135396</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>8.000000000000007</v>
+        <v>0.6347062795408531</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1450,10 +1456,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5319159620625101</v>
+        <v>0.5403184386235235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,19 +1484,19 @@
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>17.64435387980061</v>
+        <v>17.63233561222002</v>
       </c>
       <c r="K9" t="n">
-        <v>3.852323743652231</v>
+        <v>5.477447412177794</v>
       </c>
       <c r="L9" t="n">
         <v>25</v>
       </c>
       <c r="M9" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="N9" t="n">
-        <v>13.55634135822285</v>
+        <v>10.13518226827468</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1546,10 +1552,10 @@
         <v>28.88348224624216</v>
       </c>
       <c r="AJ9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AK9" t="n">
-        <v>45.45454545454545</v>
+        <v>46.2962962962963</v>
       </c>
     </row>
     <row r="10">
@@ -1559,10 +1565,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C10" t="n">
-        <v>1.785042580785678</v>
+        <v>1.839753466872111</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,25 +1593,25 @@
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>17.7329076906843</v>
+        <v>15.97669139496675</v>
       </c>
       <c r="K10" t="n">
-        <v>2.357100808560575</v>
+        <v>5.478914909450427</v>
       </c>
       <c r="L10" t="n">
         <v>36</v>
       </c>
       <c r="M10" t="n">
-        <v>52.77777777777778</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N10" t="n">
-        <v>13.08747965179568</v>
+        <v>10.53826025924606</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>7.466896904137621</v>
+        <v>4.286245354752416</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1636,29 +1642,29 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF10" t="n">
-        <v>55.17241379310344</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="AG10" t="n">
-        <v>40.36338157708393</v>
+        <v>31.75890669599265</v>
       </c>
       <c r="AH10" t="n">
-        <v>14.80903221601952</v>
+        <v>14.90775997067401</v>
       </c>
       <c r="AI10" t="n">
-        <v>37.54796321097091</v>
+        <v>30.23238890769975</v>
       </c>
       <c r="AJ10" t="n">
         <v>54</v>
       </c>
       <c r="AK10" t="n">
-        <v>51.85185185185185</v>
+        <v>48.14814814814815</v>
       </c>
     </row>
     <row r="11">
@@ -1668,10 +1674,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C11" t="n">
-        <v>7.399140361583522</v>
+        <v>7.719568567026195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,19 +1702,19 @@
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>16.80825561190469</v>
+        <v>16.79611533140597</v>
       </c>
       <c r="K11" t="n">
-        <v>3.597122302158273</v>
+        <v>8.067743275387706</v>
       </c>
       <c r="L11" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="M11" t="n">
-        <v>70.73170731707317</v>
+        <v>68.96551724137932</v>
       </c>
       <c r="N11" t="n">
-        <v>11.88658417633129</v>
+        <v>12.06591450785958</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1723,10 +1729,10 @@
         <v>61.22448979591837</v>
       </c>
       <c r="S11" t="n">
-        <v>51.68597634176234</v>
+        <v>51.51900046050075</v>
       </c>
       <c r="T11" t="n">
-        <v>9.538513454156025</v>
+        <v>9.705489335417617</v>
       </c>
       <c r="U11" t="n">
         <v>47.24599944352045</v>
@@ -1777,19 +1783,19 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C12" t="n">
-        <v>5.04580266324654</v>
+        <v>5.279917822290704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1799,7 +1805,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1809,25 +1815,25 @@
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>32.22337067864791</v>
+        <v>33.96592951889502</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1631962015687716</v>
+        <v>7.576391795730442</v>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>83.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>15.92439245875134</v>
+        <v>10.57818638012683</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>4.828923179226052</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1890,10 +1896,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1500381279038789</v>
+        <v>0.1452491011813046</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,10 +1924,10 @@
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>50.83112108557266</v>
+        <v>52.87493091246841</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1.726618705035965</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1932,7 +1938,7 @@
         <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>6.000000000000005</v>
+        <v>4.20084865629422</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1983,10 +1989,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C14" t="n">
-        <v>8.334309490616995</v>
+        <v>8.659476117103237</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2011,19 +2017,19 @@
         <v>10</v>
       </c>
       <c r="J14" t="n">
-        <v>10.97110820112375</v>
+        <v>10.95811609803855</v>
       </c>
       <c r="K14" t="n">
-        <v>3.974358974358982</v>
+        <v>8.015199974240449</v>
       </c>
       <c r="L14" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="M14" t="n">
-        <v>64.86486486486487</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="N14" t="n">
-        <v>9.996147253704111</v>
+        <v>11.25156720707579</v>
       </c>
       <c r="O14" t="n">
         <v>2</v>
@@ -2056,16 +2062,16 @@
         <v>16.11612055393703</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.432780450142773</v>
+        <v>3.821231042465323</v>
       </c>
       <c r="Z14" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AA14" t="n">
-        <v>31.81818181818182</v>
+        <v>39.28571428571428</v>
       </c>
       <c r="AB14" t="n">
-        <v>11.06099760120646</v>
+        <v>12.73191461813376</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2080,10 +2086,10 @@
         <v>52.77777777777778</v>
       </c>
       <c r="AG14" t="n">
-        <v>25.4351606341429</v>
+        <v>25.38026384011567</v>
       </c>
       <c r="AH14" t="n">
-        <v>27.34261714363488</v>
+        <v>27.39751393766211</v>
       </c>
       <c r="AI14" t="n">
         <v>37.00593802298759</v>
@@ -2102,10 +2108,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C15" t="n">
-        <v>13.10264439030415</v>
+        <v>13.28197226502311</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,25 +2136,25 @@
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>20.42907296184905</v>
+        <v>20.41746107198076</v>
       </c>
       <c r="K15" t="n">
-        <v>4.166666666666652</v>
+        <v>5.576925102168229</v>
       </c>
       <c r="L15" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="M15" t="n">
-        <v>65.625</v>
+        <v>69.56521739130434</v>
       </c>
       <c r="N15" t="n">
-        <v>15.23151380759086</v>
+        <v>17.25561569455263</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>3.680000000000017</v>
+        <v>2.295080004922423</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2175,7 +2181,7 @@
         <v>33.58229315482664</v>
       </c>
       <c r="Y15" t="n">
-        <v>17.11361766859276</v>
+        <v>15.97920248156125</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2217,10 +2223,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C16" t="n">
-        <v>32.88506827370454</v>
+        <v>33.24088341037493</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,25 +2251,25 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>20.7196869892621</v>
+        <v>20.70811750908044</v>
       </c>
       <c r="K16" t="n">
-        <v>2.498398462524021</v>
+        <v>3.592309713782971</v>
       </c>
       <c r="L16" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="M16" t="n">
-        <v>67.39130434782609</v>
+        <v>60.97560975609756</v>
       </c>
       <c r="N16" t="n">
-        <v>16.16966178998889</v>
+        <v>15.60041637170563</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>7.318750000000018</v>
+        <v>6.185488386078997</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2304,19 +2310,19 @@
         <v>51.61290322580645</v>
       </c>
       <c r="AG16" t="n">
-        <v>35.43931098083497</v>
+        <v>35.37314059208394</v>
       </c>
       <c r="AH16" t="n">
-        <v>16.17359224497147</v>
+        <v>16.23976263372251</v>
       </c>
       <c r="AI16" t="n">
         <v>34.8403954480288</v>
       </c>
       <c r="AJ16" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AK16" t="n">
-        <v>53.04347826086956</v>
+        <v>53.50877192982456</v>
       </c>
     </row>
     <row r="17">
@@ -2326,10 +2332,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3629689379880387</v>
+        <v>0.3494607087827427</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2354,10 +2360,10 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>54.89339106339885</v>
+        <v>55.14987614016763</v>
       </c>
       <c r="K17" t="n">
-        <v>3.27485062897992</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2368,7 +2374,7 @@
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>4.575314650413209</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2377,10 +2383,10 @@
         <v>65.21739130434783</v>
       </c>
       <c r="S17" t="n">
-        <v>47.44785591160005</v>
+        <v>47.47414077770186</v>
       </c>
       <c r="T17" t="n">
-        <v>17.76953539274778</v>
+        <v>17.74325052664597</v>
       </c>
       <c r="U17" t="n">
         <v>50.77005884206276</v>
@@ -2431,24 +2437,24 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06905864131946277</v>
+        <v>0.0682074987159733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AL_BEKLE_EŞİK</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2459,25 +2465,21 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>40.56863896093654</v>
+        <v>39.60735883121092</v>
       </c>
       <c r="K18" t="n">
-        <v>6.66666010582031</v>
+        <v>5.336629563130613</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
-      </c>
-      <c r="M18" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="N18" t="n">
-        <v>16.73203077467618</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>3.125006343006143</v>
+        <v>4.427111875717005</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2500,17 +2502,27 @@
       <c r="W18" t="n">
         <v>75.28089887640449</v>
       </c>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
+      <c r="X18" t="n">
+        <v>12.69840753338387</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>6.532282160306957</v>
+      </c>
       <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>13.79385170587001</v>
+      </c>
       <c r="AC18" t="n">
         <v>8</v>
       </c>
-      <c r="AD18" t="inlineStr"/>
+      <c r="AD18" t="n">
+        <v>1.570293865749806</v>
+      </c>
       <c r="AE18" t="n">
         <v>36</v>
       </c>
@@ -2540,10 +2552,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02774677676700156</v>
+        <v>0.02773497688751926</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2562,7 +2574,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %90.91: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %81.82: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2572,19 +2584,19 @@
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>16.0931283448295</v>
+        <v>16.08088370486966</v>
       </c>
       <c r="K19" t="n">
-        <v>11.57024589850426</v>
+        <v>11.50652609518852</v>
       </c>
       <c r="L19" t="n">
         <v>11</v>
       </c>
       <c r="M19" t="n">
-        <v>90.90909090909091</v>
+        <v>81.81818181818181</v>
       </c>
       <c r="N19" t="n">
-        <v>22.14238667462718</v>
+        <v>23.83833040774617</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
@@ -2617,7 +2629,7 @@
         <v>20.26411217973316</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.384896968583886</v>
+        <v>6.424708689518887</v>
       </c>
       <c r="Z19" t="n">
         <v>15</v>
@@ -2626,13 +2638,13 @@
         <v>53.33333333333334</v>
       </c>
       <c r="AB19" t="n">
-        <v>15.22852344795927</v>
+        <v>15.30321733399655</v>
       </c>
       <c r="AC19" t="n">
         <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.861666455895396</v>
+        <v>3.820764285540246</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -2663,10 +2675,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C20" t="n">
-        <v>1.572317326836498</v>
+        <v>1.605546995377504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2691,25 +2703,25 @@
         <v>10</v>
       </c>
       <c r="J20" t="n">
-        <v>19.82042371699879</v>
+        <v>19.80872300614697</v>
       </c>
       <c r="K20" t="n">
-        <v>2.546918993254521</v>
+        <v>4.69888722247167</v>
       </c>
       <c r="L20" t="n">
         <v>26</v>
       </c>
       <c r="M20" t="n">
-        <v>42.30769230769231</v>
+        <v>50</v>
       </c>
       <c r="N20" t="n">
-        <v>17.32442696279431</v>
+        <v>12.48330859736214</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>7.267971656209138</v>
+        <v>5.06319877714092</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
@@ -2772,24 +2784,24 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8340475817041283</v>
+        <v>0.8534155110426297</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AL_BEKLE_EŞİK</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2800,25 +2812,25 @@
         <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>17.90318229766043</v>
+        <v>17.89120180125073</v>
       </c>
       <c r="K21" t="n">
-        <v>2.942678117328779</v>
+        <v>5.317803882213878</v>
       </c>
       <c r="L21" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="M21" t="n">
-        <v>52.38095238095238</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N21" t="n">
-        <v>15.41321588006652</v>
+        <v>15.39536796977263</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>4.91275530728581</v>
+        <v>2.54676419267712</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2841,17 +2853,27 @@
       <c r="W21" t="n">
         <v>72.05882352941177</v>
       </c>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
+      <c r="X21" t="n">
+        <v>11.00964066838261</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>5.127335564639712</v>
+      </c>
       <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>10.17115125108776</v>
+      </c>
       <c r="AC21" t="n">
         <v>4</v>
       </c>
-      <c r="AD21" t="inlineStr"/>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
       <c r="AE21" t="n">
         <v>40</v>
       </c>
@@ -2881,10 +2903,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2789064789248746</v>
+        <v>0.2884437596302003</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,12 +2920,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %90.91: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2913,25 +2935,25 @@
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>26.84457309657031</v>
+        <v>26.83389742906096</v>
       </c>
       <c r="K22" t="n">
-        <v>3.905047883604884</v>
+        <v>7.442429222262392</v>
       </c>
       <c r="L22" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M22" t="n">
-        <v>90.90909090909091</v>
+        <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>20.17357471518222</v>
+        <v>13.79180858874516</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>5.865886442035739</v>
+        <v>2.380410417235512</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -2954,17 +2976,27 @@
       <c r="W22" t="n">
         <v>75</v>
       </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
+      <c r="X22" t="n">
+        <v>10.71975172264201</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.960016121233233</v>
+      </c>
       <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>34.61538461538461</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>13.86583964828695</v>
+      </c>
       <c r="AC22" t="n">
         <v>5</v>
       </c>
-      <c r="AD22" t="inlineStr"/>
+      <c r="AD22" t="n">
+        <v>2.102209622494733</v>
+      </c>
       <c r="AE22" t="n">
         <v>0</v>
       </c>
@@ -2986,10 +3018,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5483585198355052</v>
+        <v>0.5448382126348228</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3014,10 +3046,10 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>46.98618794638018</v>
+        <v>47.94737415629003</v>
       </c>
       <c r="K23" t="n">
-        <v>1.832059298001343</v>
+        <v>3.755868544600927</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3028,7 +3060,7 @@
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>3.110946320674901</v>
+        <v>1.199095022624452</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3091,10 +3123,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1405836699530621</v>
+        <v>0.1265536723163842</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3119,20 +3151,16 @@
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>28.72138221115397</v>
+        <v>35.83486018094283</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>10</v>
-      </c>
-      <c r="M24" t="n">
-        <v>70</v>
-      </c>
-      <c r="N24" t="n">
-        <v>17.43156237718561</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
         <v>10</v>
       </c>
@@ -3187,10 +3215,10 @@
         <v>4.558726080970055</v>
       </c>
       <c r="AJ24" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AK24" t="n">
-        <v>50</v>
+        <v>48.48484848484848</v>
       </c>
     </row>
     <row r="25">
@@ -3200,10 +3228,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C25" t="n">
-        <v>3.185740989015128</v>
+        <v>3.241910631741141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3220,11 +3248,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>5</v>
       </c>
@@ -3232,25 +3256,25 @@
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>26.01430975971111</v>
+        <v>26.00351293078278</v>
       </c>
       <c r="K25" t="n">
-        <v>3.609621443725319</v>
+        <v>5.421038399930911</v>
       </c>
       <c r="L25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M25" t="n">
-        <v>75</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N25" t="n">
-        <v>12.66996064697004</v>
+        <v>12.86359735303449</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>4.237423605161306</v>
+        <v>2.446344334311523</v>
       </c>
       <c r="Q25" t="n">
         <v>44</v>
@@ -3300,10 +3324,10 @@
         <v>38.56944827051576</v>
       </c>
       <c r="AJ25" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK25" t="n">
-        <v>48.19277108433735</v>
+        <v>48.78048780487805</v>
       </c>
     </row>
     <row r="26">
@@ -3313,10 +3337,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4217510100647179</v>
+        <v>0.431843862352337</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,25 +3365,25 @@
         <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>13.95700222161058</v>
+        <v>13.94444585396061</v>
       </c>
       <c r="K26" t="n">
-        <v>2.908725750169272</v>
+        <v>5.356042363486102</v>
       </c>
       <c r="L26" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="M26" t="n">
-        <v>42.85714285714285</v>
+        <v>51.11111111111111</v>
       </c>
       <c r="N26" t="n">
-        <v>14.69871934269606</v>
+        <v>13.79984498519905</v>
       </c>
       <c r="O26" t="n">
         <v>6</v>
       </c>
       <c r="P26" t="n">
-        <v>3.003899064240079</v>
+        <v>0.6112204122969978</v>
       </c>
       <c r="Q26" t="n">
         <v>32</v>
@@ -3422,19 +3446,19 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C27" t="n">
-        <v>50.31415445876795</v>
+        <v>45.27991782229071</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3442,24 +3466,38 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H27" t="n">
         <v>5</v>
       </c>
       <c r="I27" t="n">
         <v>10</v>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>21.1899360280639</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
       <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="M27" t="n">
+        <v>77.77777777777777</v>
+      </c>
+      <c r="N27" t="n">
+        <v>27.55321188300974</v>
+      </c>
       <c r="O27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>8.000000000000007</v>
+      </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
@@ -3472,10 +3510,10 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>67.78852866598044</v>
+        <v>59.38704518397979</v>
       </c>
       <c r="Y27" t="n">
-        <v>12.41502683363148</v>
+        <v>21.1899360280639</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -3507,19 +3545,19 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C28" t="n">
-        <v>1.240383637502447</v>
+        <v>1.288135593220339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3535,25 +3573,25 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>25.98062488782275</v>
+        <v>26.56379120725283</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>4.674457429048418</v>
       </c>
       <c r="L28" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M28" t="n">
-        <v>65</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="N28" t="n">
-        <v>15.78282104681022</v>
+        <v>15.46735764916599</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.000000000000002</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>39</v>
@@ -3616,10 +3654,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4090080288439965</v>
+        <v>0.408834103749358</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3651,7 +3689,7 @@
         <v>27.65210909859499</v>
       </c>
       <c r="K29" t="n">
-        <v>23.50994106821762</v>
+        <v>23.45742014766305</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3689,7 +3727,7 @@
         <v>31.20488584758381</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.864830970018254</v>
+        <v>5.904860668771672</v>
       </c>
       <c r="Z29" t="n">
         <v>3</v>
@@ -3704,7 +3742,7 @@
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.392799282768278</v>
+        <v>4.352126326964512</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3735,24 +3773,24 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3740676672337966</v>
+        <v>0.3932203389830509</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3763,25 +3801,25 @@
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>21.0410518898386</v>
+        <v>21.02952930685888</v>
       </c>
       <c r="K30" t="n">
-        <v>2.132441507354499</v>
+        <v>7.346068534839545</v>
       </c>
       <c r="L30" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="M30" t="n">
-        <v>51.61290322580645</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="N30" t="n">
-        <v>11.17699640764965</v>
+        <v>12.57899308142685</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>2.807686226162542</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>48</v>
@@ -3808,13 +3846,17 @@
         <v>26.71344279693404</v>
       </c>
       <c r="Y30" t="n">
-        <v>19.35729850656703</v>
+        <v>15.22830440745536</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>22.32041901315758</v>
+      </c>
       <c r="AC30" t="n">
         <v>8</v>
       </c>
@@ -3822,19 +3864,19 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AF30" t="n">
-        <v>58.53658536585366</v>
+        <v>57.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>39.87848699958872</v>
+        <v>39.50945405858332</v>
       </c>
       <c r="AH30" t="n">
-        <v>18.65809836626494</v>
+        <v>17.99054594141668</v>
       </c>
       <c r="AI30" t="n">
-        <v>43.36710313403013</v>
+        <v>42.19506854199106</v>
       </c>
       <c r="AJ30" t="n">
         <v>63</v>
@@ -3850,24 +3892,24 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2454048133601897</v>
+        <v>0.2263995891114535</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3877,17 +3919,27 @@
       <c r="I31" t="n">
         <v>10</v>
       </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>17.09111861646706</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.1818181818181719</v>
+      </c>
       <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="M31" t="n">
+        <v>58.8235294117647</v>
+      </c>
+      <c r="N31" t="n">
+        <v>16.71235064055969</v>
+      </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
-      <c r="P31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>9.800362976406563</v>
+      </c>
       <c r="Q31" t="n">
         <v>6</v>
       </c>
@@ -3910,13 +3962,13 @@
         <v>88.88888888888889</v>
       </c>
       <c r="X31" t="n">
-        <v>56.51215205029592</v>
+        <v>56.43630133425017</v>
       </c>
       <c r="Y31" t="n">
-        <v>9.954755860513265</v>
+        <v>16.94037519576973</v>
       </c>
       <c r="Z31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
@@ -3924,7 +3976,7 @@
         <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.05024600679259805</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>10</v>
@@ -3955,10 +4007,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C32" t="n">
-        <v>2.205354953792472</v>
+        <v>2.235233692860811</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3972,7 +4024,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3983,19 +4035,19 @@
         <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>14.66459067233932</v>
+        <v>14.6521375640011</v>
       </c>
       <c r="K32" t="n">
-        <v>4.58090121840915</v>
+        <v>5.98232511415977</v>
       </c>
       <c r="L32" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M32" t="n">
-        <v>62.85714285714285</v>
+        <v>53.125</v>
       </c>
       <c r="N32" t="n">
-        <v>10.7525626358017</v>
+        <v>10.93289225040109</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4024,17 +4076,27 @@
       <c r="W32" t="n">
         <v>56.60377358490566</v>
       </c>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
+      <c r="X32" t="n">
+        <v>11.59844220999626</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>5.032433235285295</v>
+      </c>
       <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>36.36363636363637</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>8.974670206958006</v>
+      </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
-      <c r="AD32" t="inlineStr"/>
+      <c r="AD32" t="n">
+        <v>3.124821310908121</v>
+      </c>
       <c r="AE32" t="n">
         <v>26</v>
       </c>
@@ -4064,19 +4126,19 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C33" t="n">
-        <v>1.684332027956643</v>
+        <v>1.737031330251669</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4092,25 +4154,25 @@
         <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>13.64028267214126</v>
+        <v>13.62768008519154</v>
       </c>
       <c r="K33" t="n">
-        <v>3.406936214511047</v>
+        <v>6.626767449901894</v>
       </c>
       <c r="L33" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="M33" t="n">
-        <v>54</v>
+        <v>69.6969696969697</v>
       </c>
       <c r="N33" t="n">
-        <v>11.55849982952366</v>
+        <v>11.31155109327979</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>0.5735241824191384</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>39</v>
@@ -4173,24 +4235,24 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C34" t="n">
-        <v>0.714839146524788</v>
+        <v>0.7548022598870058</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4201,25 +4263,25 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>20.35316837217597</v>
+        <v>17.9051929331112</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9872246327670808</v>
+        <v>6.617360976273146</v>
       </c>
       <c r="L34" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M34" t="n">
-        <v>61.53846153846154</v>
+        <v>70.83333333333333</v>
       </c>
       <c r="N34" t="n">
-        <v>10.96936711775501</v>
+        <v>11.63714603350821</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>2.983323265084925</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>35</v>
@@ -4242,17 +4304,27 @@
       <c r="W34" t="n">
         <v>49.12280701754386</v>
       </c>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
+      <c r="X34" t="n">
+        <v>11.67247563853926</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>4.526732870710659</v>
+      </c>
       <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>10.34830267484583</v>
+      </c>
       <c r="AC34" t="n">
         <v>2</v>
       </c>
-      <c r="AD34" t="inlineStr"/>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
       <c r="AE34" t="n">
         <v>33</v>
       </c>
@@ -4260,10 +4332,10 @@
         <v>57.57575757575758</v>
       </c>
       <c r="AG34" t="n">
-        <v>22.84478538126069</v>
+        <v>22.95497821872625</v>
       </c>
       <c r="AH34" t="n">
-        <v>34.73097219449689</v>
+        <v>34.62077935703132</v>
       </c>
       <c r="AI34" t="n">
         <v>40.80726333731245</v>
@@ -4282,10 +4354,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C35" t="n">
-        <v>1.29382192051397</v>
+        <v>1.226502311248074</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4310,13 +4382,13 @@
         <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>42.88847819919079</v>
+        <v>48.58068030402142</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>5.291005291005302</v>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4324,7 +4396,7 @@
         <v>6</v>
       </c>
       <c r="P35" t="n">
-        <v>6.000000000000005</v>
+        <v>0.6733668341708521</v>
       </c>
       <c r="Q35" t="n">
         <v>7</v>
@@ -4387,10 +4459,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07255268126226562</v>
+        <v>0.0731381612737545</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4404,7 +4476,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -4415,19 +4487,19 @@
         <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>19.91614017004532</v>
+        <v>19.90445342722118</v>
       </c>
       <c r="K36" t="n">
-        <v>3.823525475778666</v>
+        <v>4.646081385390488</v>
       </c>
       <c r="L36" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M36" t="n">
-        <v>52.94117647058823</v>
+        <v>60</v>
       </c>
       <c r="N36" t="n">
-        <v>13.44413963731622</v>
+        <v>12.53972468366134</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -4456,17 +4528,27 @@
       <c r="W36" t="n">
         <v>44.44444444444444</v>
       </c>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
+      <c r="X36" t="n">
+        <v>10.58823174740495</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>5.373221244360749</v>
+      </c>
       <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>37.03703703703704</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>11.79597455712513</v>
+      </c>
       <c r="AC36" t="n">
         <v>4</v>
       </c>
-      <c r="AD36" t="inlineStr"/>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
       <c r="AE36" t="n">
         <v>6</v>
       </c>
@@ -4496,10 +4578,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C37" t="n">
-        <v>0.05302717094709516</v>
+        <v>0.05403184386235234</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,25 +4606,25 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>28.89598213870331</v>
+        <v>28.88560583600921</v>
       </c>
       <c r="K37" t="n">
-        <v>1.976282632129833</v>
+        <v>3.893202731922019</v>
       </c>
       <c r="L37" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="M37" t="n">
-        <v>70.83333333333333</v>
+        <v>68.75</v>
       </c>
       <c r="N37" t="n">
-        <v>16.36949645570671</v>
+        <v>16.92641827120465</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>7.868219119944797</v>
+        <v>5.87795650484999</v>
       </c>
       <c r="Q37" t="n">
         <v>27</v>
@@ -4605,10 +4687,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C38" t="n">
-        <v>1.534293998091374</v>
+        <v>1.583975346687211</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4633,25 +4715,25 @@
         <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>15.41913455348373</v>
+        <v>15.40679155672489</v>
       </c>
       <c r="K38" t="n">
-        <v>3.608602872918265</v>
+        <v>6.947903765125685</v>
       </c>
       <c r="L38" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="M38" t="n">
-        <v>62.5</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N38" t="n">
-        <v>12.58692404747017</v>
+        <v>11.18861704017208</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>6.168789994129309</v>
+        <v>2.853815855593766</v>
       </c>
       <c r="Q38" t="n">
         <v>42</v>
@@ -4692,10 +4774,10 @@
         <v>56.66666666666666</v>
       </c>
       <c r="AG38" t="n">
-        <v>15.61483055261808</v>
+        <v>15.45143185980763</v>
       </c>
       <c r="AH38" t="n">
-        <v>41.05183611404858</v>
+        <v>41.21523480685904</v>
       </c>
       <c r="AI38" t="n">
         <v>39.19730700081361</v>
@@ -4714,19 +4796,19 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C39" t="n">
-        <v>2.484878002878146</v>
+        <v>2.656394453004623</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4742,25 +4824,25 @@
         <v>10</v>
       </c>
       <c r="J39" t="n">
-        <v>15.16106968610098</v>
+        <v>15.14868902959718</v>
       </c>
       <c r="K39" t="n">
-        <v>2.63157758891075</v>
+        <v>9.699620525649832</v>
       </c>
       <c r="L39" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="M39" t="n">
-        <v>60.8695652173913</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="N39" t="n">
-        <v>15.98166047721427</v>
+        <v>15.56291847452139</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
       </c>
       <c r="P39" t="n">
-        <v>2.307693661862964</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>42</v>
@@ -4801,10 +4883,10 @@
         <v>60</v>
       </c>
       <c r="AG39" t="n">
-        <v>40.13132335827601</v>
+        <v>39.89436953524482</v>
       </c>
       <c r="AH39" t="n">
-        <v>19.86867664172399</v>
+        <v>20.10563046475518</v>
       </c>
       <c r="AI39" t="n">
         <v>44.59589366034619</v>
@@ -4823,24 +4905,24 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2053261403067142</v>
+        <v>0.195582948125321</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4851,25 +4933,25 @@
         <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>22.08213679021579</v>
+        <v>29.83357657172154</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>5.777777777777771</v>
       </c>
       <c r="L40" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="M40" t="n">
-        <v>61.11111111111111</v>
+        <v>70</v>
       </c>
       <c r="N40" t="n">
-        <v>17.07297762827142</v>
+        <v>14.5131890624577</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>3.000000000000003</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>29</v>
@@ -4892,12 +4974,8 @@
       <c r="W40" t="n">
         <v>77.77777777777777</v>
       </c>
-      <c r="X40" t="n">
-        <v>33.58584893257701</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>22.08213679021579</v>
-      </c>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="n">
         <v>0</v>
       </c>
@@ -4906,9 +4984,7 @@
       <c r="AC40" t="n">
         <v>5</v>
       </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="n">
         <v>14</v>
       </c>
@@ -4938,10 +5014,10 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C41" t="n">
-        <v>1.097539185081235</v>
+        <v>0.9873651771956857</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4966,20 +5042,16 @@
         <v>10</v>
       </c>
       <c r="J41" t="n">
-        <v>45.65103159527513</v>
+        <v>51.10673081311258</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>3</v>
-      </c>
-      <c r="M41" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N41" t="n">
-        <v>24.12996021615659</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
         <v>10</v>
       </c>
@@ -5047,14 +5119,14 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C42" t="n">
-        <v>3.144634653672997</v>
+        <v>3.204930662557782</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5064,7 +5136,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5079,10 +5151,10 @@
         <v>10</v>
       </c>
       <c r="J42" t="n">
-        <v>21.02732841592907</v>
+        <v>21.01580383026476</v>
       </c>
       <c r="K42" t="n">
-        <v>2.960964817887723</v>
+        <v>4.919852936112434</v>
       </c>
       <c r="L42" t="n">
         <v>7</v>
@@ -5091,7 +5163,7 @@
         <v>85.71428571428571</v>
       </c>
       <c r="N42" t="n">
-        <v>14.12854066520737</v>
+        <v>13.76422757864045</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
@@ -5118,17 +5190,27 @@
         <v>0</v>
       </c>
       <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
+      <c r="X42" t="n">
+        <v>11.70928208999582</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>6.077766347485458</v>
+      </c>
       <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>9.725617469520763</v>
+      </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
-      <c r="AD42" t="inlineStr"/>
+      <c r="AD42" t="n">
+        <v>4.176043839657484</v>
+      </c>
       <c r="AE42" t="n">
         <v>1</v>
       </c>
@@ -5156,10 +5238,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C43" t="n">
-        <v>5.837099618582556</v>
+        <v>5.880842321520288</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5173,14 +5255,10 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>BAND</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SATMA_BEKLE</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>5</v>
       </c>
@@ -5188,25 +5266,25 @@
         <v>10</v>
       </c>
       <c r="J43" t="n">
-        <v>26.64061304155033</v>
+        <v>26.62990760988233</v>
       </c>
       <c r="K43" t="n">
-        <v>6.069094304388423</v>
+        <v>6.848374095222765</v>
       </c>
       <c r="L43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M43" t="n">
-        <v>85.71428571428571</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N43" t="n">
-        <v>14.53783433294402</v>
+        <v>16.84208748274783</v>
       </c>
       <c r="O43" t="n">
         <v>10</v>
       </c>
       <c r="P43" t="n">
-        <v>3.70598591549296</v>
+        <v>2.949624579189702</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5229,17 +5307,27 @@
       <c r="W43" t="n">
         <v>66.66666666666667</v>
       </c>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
+      <c r="X43" t="n">
+        <v>10.08403361344539</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>2.93926322647704</v>
+      </c>
       <c r="Z43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>34.78260869565217</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>10.84202005888328</v>
+      </c>
       <c r="AC43" t="n">
         <v>2</v>
       </c>
-      <c r="AD43" t="inlineStr"/>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
       <c r="AE43" t="n">
         <v>10</v>
       </c>
@@ -5269,10 +5357,10 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C44" t="n">
-        <v>4.075693211859418</v>
+        <v>3.667180277349769</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5286,7 +5374,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5297,25 +5385,25 @@
         <v>10</v>
       </c>
       <c r="J44" t="n">
-        <v>25.16666033456245</v>
+        <v>28.54575647949613</v>
       </c>
       <c r="K44" t="n">
-        <v>6.121193142906889</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M44" t="n">
-        <v>40</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N44" t="n">
-        <v>13.63613675790799</v>
+        <v>19.20931872006684</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
       </c>
       <c r="P44" t="n">
-        <v>3.65507279198205</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q44" t="n">
         <v>2</v>
@@ -5338,12 +5426,8 @@
       <c r="W44" t="n">
         <v>50</v>
       </c>
-      <c r="X44" t="n">
-        <v>28.18267712431886</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>17.21097146380824</v>
-      </c>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
         <v>0</v>
       </c>
@@ -5352,9 +5436,7 @@
       <c r="AC44" t="n">
         <v>10</v>
       </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="n">
         <v>0</v>
       </c>
@@ -5376,10 +5458,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C45" t="n">
-        <v>0.01993657325752841</v>
+        <v>0.01992809450436569</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5404,10 +5486,10 @@
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>19.67438842514809</v>
+        <v>19.70854648567448</v>
       </c>
       <c r="K45" t="n">
-        <v>2.105267390581766</v>
+        <v>2.105263157894743</v>
       </c>
       <c r="L45" t="n">
         <v>54</v>
@@ -5422,7 +5504,7 @@
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>7.731954296949861</v>
+        <v>7.731958762886593</v>
       </c>
       <c r="Q45" t="n">
         <v>38</v>
@@ -5485,10 +5567,10 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C46" t="n">
-        <v>8.529564583492116</v>
+        <v>8.346173600410889</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5513,25 +5595,25 @@
         <v>10</v>
       </c>
       <c r="J46" t="n">
-        <v>21.29865570887185</v>
+        <v>28.15632518747767</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>7.189973614775735</v>
       </c>
       <c r="L46" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="M46" t="n">
-        <v>55.17241379310344</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N46" t="n">
-        <v>14.76602170324743</v>
+        <v>15.98944669041125</v>
       </c>
       <c r="O46" t="n">
         <v>8</v>
       </c>
       <c r="P46" t="n">
-        <v>8.000000000000007</v>
+        <v>0.7556923076923017</v>
       </c>
       <c r="Q46" t="n">
         <v>51</v>
@@ -5572,19 +5654,19 @@
         <v>60</v>
       </c>
       <c r="AG46" t="n">
-        <v>18.89764882663802</v>
+        <v>18.63060337209256</v>
       </c>
       <c r="AH46" t="n">
-        <v>41.10235117336198</v>
+        <v>41.36939662790743</v>
       </c>
       <c r="AI46" t="n">
         <v>44.59589366034619</v>
       </c>
       <c r="AJ46" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK46" t="n">
-        <v>55.55555555555556</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="47">
@@ -5594,27 +5676,31 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C47" t="n">
-        <v>0.961477158577572</v>
+        <v>1.01160760143811</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>ÇELİŞKİLİ_BEKLE</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H47" t="n">
         <v>5</v>
       </c>
@@ -5622,25 +5708,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>18.95171627150033</v>
+        <v>18.93988878903028</v>
       </c>
       <c r="K47" t="n">
-        <v>5.693629813947099</v>
+        <v>11.1881625271506</v>
       </c>
       <c r="L47" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="M47" t="n">
-        <v>60.8695652173913</v>
+        <v>80</v>
       </c>
       <c r="N47" t="n">
-        <v>15.12768264263546</v>
+        <v>13.04145845344455</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>4.074389529088385</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>51</v>
@@ -5667,10 +5753,10 @@
         <v>66.65983471422588</v>
       </c>
       <c r="Y47" t="n">
-        <v>14.33712702544205</v>
+        <v>9.870751802057963</v>
       </c>
       <c r="Z47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr"/>
@@ -5687,10 +5773,10 @@
         <v>53.65853658536585</v>
       </c>
       <c r="AG47" t="n">
-        <v>30.66455361169589</v>
+        <v>30.36663735610388</v>
       </c>
       <c r="AH47" t="n">
-        <v>22.99398297366996</v>
+        <v>23.29189922926197</v>
       </c>
       <c r="AI47" t="n">
         <v>38.74647126766948</v>
@@ -5709,10 +5795,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C48" t="n">
-        <v>0.04953313593705256</v>
+        <v>0.04951206985105291</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5737,25 +5823,25 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>21.80686005650104</v>
+        <v>27.02915304173016</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>7.111111111111112</v>
       </c>
       <c r="L48" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="M48" t="n">
-        <v>61.11111111111111</v>
+        <v>60</v>
       </c>
       <c r="N48" t="n">
-        <v>15.66116427323397</v>
+        <v>13.14248535050986</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>10.00000000000001</v>
+        <v>2.69709543568466</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5818,24 +5904,24 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2511597144897737</v>
+        <v>0.2670775552131485</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -5846,25 +5932,25 @@
         <v>10</v>
       </c>
       <c r="J49" t="n">
-        <v>18.76118924813161</v>
+        <v>18.74933396180286</v>
       </c>
       <c r="K49" t="n">
-        <v>1.579389395381137</v>
+        <v>8.001462567485129</v>
       </c>
       <c r="L49" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="M49" t="n">
-        <v>56.81818181818182</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N49" t="n">
-        <v>17.27015430670839</v>
+        <v>18.09600846902872</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
       </c>
       <c r="P49" t="n">
-        <v>3.367425838035598</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>54</v>
@@ -5887,17 +5973,27 @@
       <c r="W49" t="n">
         <v>67.14285714285714</v>
       </c>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
+      <c r="X49" t="n">
+        <v>11.47132295072795</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>3.112782993323371</v>
+      </c>
       <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="inlineStr"/>
-      <c r="AB49" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>37.25490196078432</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>12.00064654298627</v>
+      </c>
       <c r="AC49" t="n">
         <v>10</v>
       </c>
-      <c r="AD49" t="inlineStr"/>
+      <c r="AD49" t="n">
+        <v>7.108488838318083</v>
+      </c>
       <c r="AE49" t="n">
         <v>44</v>
       </c>
@@ -5905,19 +6001,19 @@
         <v>61.36363636363637</v>
       </c>
       <c r="AG49" t="n">
-        <v>34.66318078532502</v>
+        <v>34.41304081092033</v>
       </c>
       <c r="AH49" t="n">
-        <v>26.70045557831135</v>
+        <v>26.95059555271604</v>
       </c>
       <c r="AI49" t="n">
         <v>46.62357539237828</v>
       </c>
       <c r="AJ49" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AK49" t="n">
-        <v>56.92307692307692</v>
+        <v>57.8125</v>
       </c>
     </row>
     <row r="50">
@@ -5927,10 +6023,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6753771022086393</v>
+        <v>0.6980996404725218</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5955,19 +6051,19 @@
         <v>10</v>
       </c>
       <c r="J50" t="n">
-        <v>16.75432628663439</v>
+        <v>16.74217813615844</v>
       </c>
       <c r="K50" t="n">
-        <v>5.185662138050651</v>
+        <v>8.708688076499005</v>
       </c>
       <c r="L50" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="M50" t="n">
-        <v>56.09756097560975</v>
+        <v>73.68421052631579</v>
       </c>
       <c r="N50" t="n">
-        <v>18.31155651433684</v>
+        <v>15.9882991805839</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
@@ -6023,10 +6119,10 @@
         <v>44.49431275003934</v>
       </c>
       <c r="AJ50" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AK50" t="n">
-        <v>54.23728813559322</v>
+        <v>55.17241379310344</v>
       </c>
     </row>
     <row r="51">
@@ -6036,19 +6132,19 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1220858171993182</v>
+        <v>0.11628145865434</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6056,11 +6152,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>5</v>
       </c>
@@ -6068,25 +6160,21 @@
         <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>37.32555464144151</v>
+        <v>42.62559109626197</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>4.044117647058809</v>
       </c>
       <c r="L51" t="n">
-        <v>3</v>
-      </c>
-      <c r="M51" t="n">
-        <v>100</v>
-      </c>
-      <c r="N51" t="n">
-        <v>10.96169884631585</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>4.000000000000004</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6121,25 +6209,25 @@
       </c>
       <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF51" t="n">
-        <v>58.33333333333334</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="AG51" t="n">
-        <v>70.99849224849225</v>
+        <v>69.70373643450567</v>
       </c>
       <c r="AH51" t="n">
-        <v>-12.66515891515892</v>
+        <v>-15.85758258835182</v>
       </c>
       <c r="AI51" t="n">
-        <v>31.95113125495497</v>
+        <v>29.14379571450601</v>
       </c>
       <c r="AJ51" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK51" t="n">
-        <v>43.75</v>
+        <v>41.1764705882353</v>
       </c>
     </row>
     <row r="52">
@@ -6149,14 +6237,14 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C52" t="n">
-        <v>4.244229124074993</v>
+        <v>4.417051874678994</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6166,7 +6254,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -6177,25 +6265,25 @@
         <v>10</v>
       </c>
       <c r="J52" t="n">
-        <v>14.10233078968066</v>
+        <v>14.08979563001946</v>
       </c>
       <c r="K52" t="n">
-        <v>2.992518703241909</v>
+        <v>7.170679680869729</v>
       </c>
       <c r="L52" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="M52" t="n">
-        <v>48.83720930232558</v>
+        <v>54.83870967741935</v>
       </c>
       <c r="N52" t="n">
-        <v>12.57201847202214</v>
+        <v>13.07754061473337</v>
       </c>
       <c r="O52" t="n">
         <v>10</v>
       </c>
       <c r="P52" t="n">
-        <v>6.803874092009687</v>
+        <v>2.640013413701725</v>
       </c>
       <c r="Q52" t="n">
         <v>37</v>
@@ -6219,25 +6307,25 @@
         <v>67.9245283018868</v>
       </c>
       <c r="X52" t="n">
-        <v>16.62696858241317</v>
+        <v>16.53731163255363</v>
       </c>
       <c r="Y52" t="n">
-        <v>11.531826972913</v>
+        <v>7.929450061467602</v>
       </c>
       <c r="Z52" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA52" t="n">
-        <v>53.33333333333334</v>
+        <v>62.5</v>
       </c>
       <c r="AB52" t="n">
-        <v>11.14714845297855</v>
+        <v>12.9570496400252</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>0.07662595539995598</v>
       </c>
       <c r="AE52" t="n">
         <v>37</v>
@@ -6246,10 +6334,10 @@
         <v>67.56756756756756</v>
       </c>
       <c r="AG52" t="n">
-        <v>39.54049929077311</v>
+        <v>39.1150650126505</v>
       </c>
       <c r="AH52" t="n">
-        <v>28.02706827679445</v>
+        <v>28.45250255491706</v>
       </c>
       <c r="AI52" t="n">
         <v>51.4636672419722</v>
@@ -6268,10 +6356,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C53" t="n">
-        <v>1.073903010813164</v>
+        <v>1.065228556753981</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6296,10 +6384,10 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>40.14560778496996</v>
+        <v>40.58944447798576</v>
       </c>
       <c r="K53" t="n">
-        <v>4.395605980832373</v>
+        <v>4.325955734406417</v>
       </c>
       <c r="L53" t="n">
         <v>2</v>
@@ -6310,7 +6398,7 @@
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>3.452630008038282</v>
+        <v>3.521697203471574</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6368,7 +6456,7 @@
         <v>46281</v>
       </c>
       <c r="C54" t="n">
-        <v>0.06474248021917259</v>
+        <v>0.06475192817432517</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6396,7 +6484,7 @@
         <v>28.93741561274367</v>
       </c>
       <c r="K54" t="n">
-        <v>3.146656088020294</v>
+        <v>3.161708414986442</v>
       </c>
       <c r="L54" t="n">
         <v>19</v>
@@ -6411,7 +6499,7 @@
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>6.644271537151347</v>
+        <v>6.628711069329452</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6438,7 +6526,7 @@
         <v>14.75410024187049</v>
       </c>
       <c r="Y54" t="n">
-        <v>10.11505831110596</v>
+        <v>10.10194128353622</v>
       </c>
       <c r="Z54" t="n">
         <v>21</v>
@@ -6484,24 +6572,24 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8541896765673153</v>
+        <v>0.8982023626091423</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6512,25 +6600,25 @@
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>18.57064273349606</v>
+        <v>18.55875964046422</v>
       </c>
       <c r="K55" t="n">
-        <v>4.949502463958044</v>
+        <v>10.34099253981891</v>
       </c>
       <c r="L55" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="M55" t="n">
-        <v>57.89473684210526</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N55" t="n">
-        <v>13.01006777547481</v>
+        <v>11.59043445810737</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>1.000955232162948</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>45</v>
@@ -6557,16 +6645,16 @@
         <v>23.0932342837701</v>
       </c>
       <c r="Y55" t="n">
-        <v>14.54029468920525</v>
+        <v>10.13692705054864</v>
       </c>
       <c r="Z55" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AA55" t="n">
-        <v>25</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB55" t="n">
-        <v>33.66794265572751</v>
+        <v>8.653238977710041</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6581,10 +6669,10 @@
         <v>59.09090909090909</v>
       </c>
       <c r="AG55" t="n">
-        <v>38.96262464989598</v>
+        <v>38.91733479482351</v>
       </c>
       <c r="AH55" t="n">
-        <v>20.12828444101311</v>
+        <v>20.17357429608558</v>
       </c>
       <c r="AI55" t="n">
         <v>44.4097537410319</v>
@@ -6603,10 +6691,10 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5643899653385399</v>
+        <v>0.5078582434514638</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6631,7 +6719,7 @@
         <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>60.7429164069973</v>
+        <v>64.67507443260313</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -6692,14 +6780,14 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C57" t="n">
-        <v>1.288683628596204</v>
+        <v>1.159732922444787</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6709,12 +6797,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.88: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %82.76: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -6724,19 +6812,19 @@
         <v>10</v>
       </c>
       <c r="J57" t="n">
-        <v>15.37859259320753</v>
+        <v>23.84614040594677</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="M57" t="n">
-        <v>80.88235294117646</v>
+        <v>82.75862068965517</v>
       </c>
       <c r="N57" t="n">
-        <v>17.1163048611607</v>
+        <v>22.23894895011225</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
@@ -6765,23 +6853,17 @@
       <c r="W57" t="n">
         <v>79.1304347826087</v>
       </c>
-      <c r="X57" t="n">
-        <v>20.62560129901716</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>15.37859259320753</v>
-      </c>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
         <v>5</v>
       </c>
-      <c r="AD57" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD57" t="inlineStr"/>
       <c r="AE57" t="n">
         <v>44</v>
       </c>
@@ -6811,10 +6893,10 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6909974751093273</v>
+        <v>0.6927580893682589</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6831,7 +6913,11 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6842,22 +6928,22 @@
         <v>18.04392839464337</v>
       </c>
       <c r="K58" t="n">
-        <v>5.913237958681949</v>
+        <v>6.183097637880008</v>
       </c>
       <c r="L58" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M58" t="n">
-        <v>73.68421052631579</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="N58" t="n">
-        <v>17.77087948887664</v>
+        <v>17.97095866556823</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>1.970256109186397</v>
+        <v>1.711103181709994</v>
       </c>
       <c r="Q58" t="n">
         <v>25</v>
@@ -6884,13 +6970,13 @@
         <v>20.50322102897642</v>
       </c>
       <c r="Y58" t="n">
-        <v>12.10754612674306</v>
+        <v>11.88360217164068</v>
       </c>
       <c r="Z58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA58" t="n">
-        <v>54.54545454545455</v>
+        <v>50</v>
       </c>
       <c r="AB58" t="n">
         <v>14.24828351986104</v>
@@ -6930,19 +7016,19 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7049736354971337</v>
+        <v>0.7498715973292245</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6958,25 +7044,25 @@
         <v>10</v>
       </c>
       <c r="J59" t="n">
-        <v>17.6978316350445</v>
+        <v>17.68582117154297</v>
       </c>
       <c r="K59" t="n">
-        <v>3.00300307154</v>
+        <v>9.547013684545981</v>
       </c>
       <c r="L59" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="M59" t="n">
-        <v>63.88888888888889</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="N59" t="n">
-        <v>15.22130524936779</v>
+        <v>12.358607259554</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>4.85131188358594</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7039,10 +7125,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C60" t="n">
-        <v>10.23547750019054</v>
+        <v>10.55983564458141</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7059,7 +7145,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H60" t="n">
         <v>5</v>
       </c>
@@ -7067,25 +7157,25 @@
         <v>10</v>
       </c>
       <c r="J60" t="n">
-        <v>29.36926586330257</v>
+        <v>29.35895862752387</v>
       </c>
       <c r="K60" t="n">
-        <v>2.998965873836612</v>
+        <v>6.24745663520736</v>
       </c>
       <c r="L60" t="n">
         <v>5</v>
       </c>
       <c r="M60" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="N60" t="n">
-        <v>10.89704054938486</v>
+        <v>10.04048277585515</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>4.855421686746997</v>
+        <v>1.649492063428748</v>
       </c>
       <c r="Q60" t="n">
         <v>46</v>
@@ -7126,10 +7216,10 @@
         <v>61.29032258064516</v>
       </c>
       <c r="AG60" t="n">
-        <v>22.73645585990844</v>
+        <v>22.37213780671093</v>
       </c>
       <c r="AH60" t="n">
-        <v>38.55386672073672</v>
+        <v>38.91818477393423</v>
       </c>
       <c r="AI60" t="n">
         <v>43.82410861966073</v>
@@ -7148,10 +7238,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6416698805089741</v>
+        <v>0.5772984078068825</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7168,11 +7258,7 @@
           <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>5</v>
       </c>
@@ -7180,19 +7266,19 @@
         <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>22.75878499834842</v>
+        <v>30.50752140313542</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="M61" t="n">
-        <v>80</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N61" t="n">
-        <v>25.02831523904753</v>
+        <v>13.94629772108441</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
@@ -7225,7 +7311,7 @@
         <v>49.99145178651283</v>
       </c>
       <c r="Y61" t="n">
-        <v>22.75878499834842</v>
+        <v>30.50752140313542</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -7267,10 +7353,10 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C62" t="n">
-        <v>8.519287999656584</v>
+        <v>8.757062146892656</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7295,25 +7381,25 @@
         <v>10</v>
       </c>
       <c r="J62" t="n">
-        <v>11.09330596567706</v>
+        <v>11.08033169507211</v>
       </c>
       <c r="K62" t="n">
-        <v>2.53555967841681</v>
+        <v>5.381958480690674</v>
       </c>
       <c r="L62" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="M62" t="n">
-        <v>56.45161290322581</v>
+        <v>65.95744680851064</v>
       </c>
       <c r="N62" t="n">
-        <v>13.2947046315765</v>
+        <v>13.37005229730381</v>
       </c>
       <c r="O62" t="n">
         <v>6</v>
       </c>
       <c r="P62" t="n">
-        <v>3.378769601930043</v>
+        <v>0.5864775415258316</v>
       </c>
       <c r="Q62" t="n">
         <v>30</v>
@@ -7376,19 +7462,19 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0986552087262155</v>
+        <v>0.1006676938880329</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7396,7 +7482,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H63" t="n">
         <v>5</v>
       </c>
@@ -7404,25 +7494,25 @@
         <v>10</v>
       </c>
       <c r="J63" t="n">
-        <v>21.60790126179767</v>
+        <v>22.98070115115823</v>
       </c>
       <c r="K63" t="n">
-        <v>2.564110349551041</v>
+        <v>6.521739130434812</v>
       </c>
       <c r="L63" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M63" t="n">
-        <v>62.5</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="N63" t="n">
-        <v>13.13794972801555</v>
+        <v>11.21872105224002</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>2.374992228906536</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7457,25 +7547,25 @@
       </c>
       <c r="AD63" t="inlineStr"/>
       <c r="AE63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF63" t="n">
         <v>100</v>
       </c>
       <c r="AG63" t="n">
-        <v>20</v>
+        <v>25.38461538461539</v>
       </c>
       <c r="AH63" t="n">
-        <v>80</v>
+        <v>74.61538461538461</v>
       </c>
       <c r="AI63" t="n">
-        <v>20.65493143772375</v>
+        <v>34.2380227506653</v>
       </c>
       <c r="AJ63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK63" t="n">
-        <v>66.66666666666667</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64">
@@ -7485,24 +7575,24 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C64" t="n">
-        <v>0.141405795837778</v>
+        <v>0.1448382126348228</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -7513,25 +7603,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>18.13121254268995</v>
+        <v>18.11926532303334</v>
       </c>
       <c r="K64" t="n">
-        <v>4.242427488521638</v>
+        <v>6.757179204496633</v>
       </c>
       <c r="L64" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="M64" t="n">
-        <v>58.53658536585366</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="N64" t="n">
-        <v>12.93871554408919</v>
+        <v>13.25722701435867</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>0.7267410494270932</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>55</v>
@@ -7554,17 +7644,27 @@
       <c r="W64" t="n">
         <v>72.27722772277228</v>
       </c>
-      <c r="X64" t="inlineStr"/>
-      <c r="Y64" t="inlineStr"/>
+      <c r="X64" t="n">
+        <v>11.36363653581267</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>4.136410658460033</v>
+      </c>
       <c r="Z64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" t="inlineStr"/>
-      <c r="AB64" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>58.92857142857143</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>13.96461539681414</v>
+      </c>
       <c r="AC64" t="n">
         <v>2</v>
       </c>
-      <c r="AD64" t="inlineStr"/>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
       <c r="AE64" t="n">
         <v>46</v>
       </c>
@@ -7572,10 +7672,10 @@
         <v>65.21739130434783</v>
       </c>
       <c r="AG64" t="n">
-        <v>34.92101092896311</v>
+        <v>34.80250198692476</v>
       </c>
       <c r="AH64" t="n">
-        <v>30.29638037538471</v>
+        <v>30.41488931742307</v>
       </c>
       <c r="AI64" t="n">
         <v>50.77005884206276</v>
@@ -7594,10 +7694,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C65" t="n">
-        <v>6.181365177072901</v>
+        <v>6.276322547508989</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7622,25 +7722,25 @@
         <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>15.61813089289524</v>
+        <v>15.60581693593351</v>
       </c>
       <c r="K65" t="n">
-        <v>3.886010362694314</v>
+        <v>5.46650359195715</v>
       </c>
       <c r="L65" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="M65" t="n">
-        <v>51.16279069767442</v>
+        <v>55.88235294117647</v>
       </c>
       <c r="N65" t="n">
-        <v>11.97402330287637</v>
+        <v>13.04152662096548</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>5.885286783042387</v>
+        <v>4.298517779239797</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7658,25 +7758,25 @@
         <v>54.18970269185592</v>
       </c>
       <c r="V65" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="W65" t="n">
-        <v>64.17910447761194</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="X65" t="n">
         <v>24.47056390537039</v>
       </c>
       <c r="Y65" t="n">
-        <v>12.33904271515801</v>
+        <v>10.99240588733341</v>
       </c>
       <c r="Z65" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AA65" t="n">
-        <v>37.5</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB65" t="n">
-        <v>15.0813486974636</v>
+        <v>14.01224876090615</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
@@ -7713,10 +7813,10 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C66" t="n">
-        <v>0.3987314450084639</v>
+        <v>0.4071905495634309</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7730,7 +7830,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -7741,25 +7841,25 @@
         <v>10</v>
       </c>
       <c r="J66" t="n">
-        <v>19.90555336900347</v>
+        <v>19.89386508123355</v>
       </c>
       <c r="K66" t="n">
-        <v>2.808684453667465</v>
+        <v>4.974456004293337</v>
       </c>
       <c r="L66" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="M66" t="n">
-        <v>51.35135135135135</v>
+        <v>55.17241379310344</v>
       </c>
       <c r="N66" t="n">
-        <v>15.65496524017184</v>
+        <v>15.10222239306331</v>
       </c>
       <c r="O66" t="n">
         <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>3.104130320596377</v>
+        <v>0.9769462350581071</v>
       </c>
       <c r="Q66" t="n">
         <v>35</v>
@@ -7782,17 +7882,27 @@
       <c r="W66" t="n">
         <v>65.21739130434783</v>
       </c>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
+      <c r="X66" t="n">
+        <v>11.49973494118825</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>5.852282016936416</v>
+      </c>
       <c r="Z66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" t="inlineStr"/>
-      <c r="AB66" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>45.94594594594594</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>10.79089929087324</v>
+      </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
-      <c r="AD66" t="inlineStr"/>
+      <c r="AD66" t="n">
+        <v>0.156900226822454</v>
+      </c>
       <c r="AE66" t="n">
         <v>41</v>
       </c>
@@ -7822,10 +7932,10 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02425273682419872</v>
+        <v>0.02465331278890601</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7850,25 +7960,25 @@
         <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>18.4894540984521</v>
+        <v>18.52411411845527</v>
       </c>
       <c r="K67" t="n">
-        <v>0.8547000292205231</v>
+        <v>2.564102564102577</v>
       </c>
       <c r="L67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M67" t="n">
-        <v>60</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N67" t="n">
-        <v>11.81759600692333</v>
+        <v>14.00245556282399</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>3.118644911806978</v>
+        <v>1.400000000000001</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -7911,10 +8021,10 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C68" t="n">
-        <v>1.405836700147216</v>
+        <v>1.265536723163842</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7939,7 +8049,7 @@
         <v>10</v>
       </c>
       <c r="J68" t="n">
-        <v>74.8239308631663</v>
+        <v>77.33645733232144</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -8016,31 +8126,27 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4682011737285541</v>
+        <v>0.4334874165382641</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>AL_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>VERİ_YETERSİZ</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>5</v>
       </c>
@@ -8048,25 +8154,25 @@
         <v>10</v>
       </c>
       <c r="J69" t="n">
-        <v>22.2553779663549</v>
+        <v>24.03271488855209</v>
       </c>
       <c r="K69" t="n">
-        <v>8.100446415382079</v>
+        <v>2.427184466019416</v>
       </c>
       <c r="L69" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M69" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="N69" t="n">
-        <v>35.69382644421589</v>
+        <v>24.40139995090738</v>
       </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>5.440758293838877</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8085,10 +8191,10 @@
         <v>45.36848923911108</v>
       </c>
       <c r="Y69" t="n">
-        <v>15.95771651767813</v>
+        <v>22.18884874507033</v>
       </c>
       <c r="Z69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="inlineStr"/>
       <c r="AB69" t="inlineStr"/>
@@ -8119,10 +8225,10 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4312054482844937</v>
+        <v>0.438828967642527</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8147,25 +8253,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>24.06749420464227</v>
+        <v>24.99185434120895</v>
       </c>
       <c r="K70" t="n">
-        <v>2.742406747336301</v>
+        <v>5.847373637264619</v>
       </c>
       <c r="L70" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M70" t="n">
-        <v>68</v>
+        <v>69.56521739130434</v>
       </c>
       <c r="N70" t="n">
-        <v>14.3189803914637</v>
+        <v>12.31109841844929</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>5.11725724470633</v>
+        <v>2.033707865168544</v>
       </c>
       <c r="Q70" t="n">
         <v>31</v>
@@ -8192,7 +8298,7 @@
         <v>44.93251946562029</v>
       </c>
       <c r="Y70" t="n">
-        <v>21.98511604228885</v>
+        <v>20.60584780615577</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -8212,10 +8318,10 @@
         <v>52.38095238095238</v>
       </c>
       <c r="AG70" t="n">
-        <v>32.32527274532664</v>
+        <v>32.16267740415987</v>
       </c>
       <c r="AH70" t="n">
-        <v>20.05567963562574</v>
+        <v>20.21827497679251</v>
       </c>
       <c r="AI70" t="n">
         <v>37.72246413134498</v>
@@ -8234,10 +8340,10 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C71" t="n">
-        <v>2.984319883151526</v>
+        <v>3.050847457627119</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8262,19 +8368,19 @@
         <v>10</v>
       </c>
       <c r="J71" t="n">
-        <v>12.70639134744024</v>
+        <v>12.25699904489306</v>
       </c>
       <c r="K71" t="n">
-        <v>3.345193558718873</v>
+        <v>5.633587999276202</v>
       </c>
       <c r="L71" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="M71" t="n">
-        <v>54.41176470588236</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N71" t="n">
-        <v>17.10351843160066</v>
+        <v>15.32047770277594</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
@@ -8343,10 +8449,10 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C72" t="n">
-        <v>0.05323270241827414</v>
+        <v>0.04807395993836672</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8363,11 +8469,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>5</v>
       </c>
@@ -8375,19 +8477,19 @@
         <v>10</v>
       </c>
       <c r="J72" t="n">
-        <v>37.35654542033834</v>
+        <v>43.42727704859612</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M72" t="n">
-        <v>75</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N72" t="n">
-        <v>19.90671805482509</v>
+        <v>42.84896195445003</v>
       </c>
       <c r="O72" t="n">
         <v>10</v>
@@ -8456,10 +8558,10 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0554935537395348</v>
+        <v>0.05485362095531587</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8484,25 +8586,25 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>28.80072718754351</v>
+        <v>31.26644883376827</v>
       </c>
       <c r="K73" t="n">
-        <v>2.661594565484626</v>
+        <v>5.118110236220486</v>
       </c>
       <c r="L73" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M73" t="n">
-        <v>63.63636363636363</v>
+        <v>60</v>
       </c>
       <c r="N73" t="n">
-        <v>20.00269978225033</v>
+        <v>17.85869494881592</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>7.148150645404638</v>
+        <v>4.64419475655431</v>
       </c>
       <c r="Q73" t="n">
         <v>14</v>
@@ -8565,14 +8667,14 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C74" t="n">
-        <v>4.901930489549083</v>
+        <v>4.410888546481766</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -8582,7 +8684,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -8593,19 +8695,19 @@
         <v>10</v>
       </c>
       <c r="J74" t="n">
-        <v>17.36947839447086</v>
+        <v>25.64684013437128</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="M74" t="n">
-        <v>74.54545454545455</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N74" t="n">
-        <v>20.47113481513891</v>
+        <v>22.76378277075152</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
@@ -8620,10 +8722,10 @@
         <v>74.07407407407408</v>
       </c>
       <c r="S74" t="n">
-        <v>71.81972470052359</v>
+        <v>72.01788139931887</v>
       </c>
       <c r="T74" t="n">
-        <v>2.254349373550482</v>
+        <v>2.056192674755209</v>
       </c>
       <c r="U74" t="n">
         <v>55.32142868544692</v>
@@ -8634,27 +8736,17 @@
       <c r="W74" t="n">
         <v>77.39130434782609</v>
       </c>
-      <c r="X74" t="n">
-        <v>24.51464461150628</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>17.36947839447086</v>
-      </c>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>30.81122903952395</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
         <v>10</v>
       </c>
-      <c r="AD74" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD74" t="inlineStr"/>
       <c r="AE74" t="n">
         <v>37</v>
       </c>
@@ -8662,10 +8754,10 @@
         <v>51.35135135135135</v>
       </c>
       <c r="AG74" t="n">
-        <v>28.92392069717405</v>
+        <v>28.58533621905718</v>
       </c>
       <c r="AH74" t="n">
-        <v>22.4274306541773</v>
+        <v>22.76601513229418</v>
       </c>
       <c r="AI74" t="n">
         <v>35.89489666561879</v>
@@ -8684,10 +8776,10 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1066709414460192</v>
+        <v>0.1064201335387776</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8701,12 +8793,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.82: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H75" t="n">
@@ -8716,25 +8808,25 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>22.61005884355163</v>
+        <v>20.63050282149162</v>
       </c>
       <c r="K75" t="n">
-        <v>2.56917236248031</v>
+        <v>2.313077975542965</v>
       </c>
       <c r="L75" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M75" t="n">
-        <v>81.81818181818181</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="N75" t="n">
-        <v>16.95980103928093</v>
+        <v>13.29337292582021</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>3.344891606802802</v>
+        <v>3.603568671190183</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8757,17 +8849,27 @@
       <c r="W75" t="n">
         <v>100</v>
       </c>
-      <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr"/>
+      <c r="X75" t="n">
+        <v>11.06719281897857</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>7.881818763262871</v>
+      </c>
       <c r="Z75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA75" t="inlineStr"/>
-      <c r="AB75" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>10.40453534313213</v>
+      </c>
       <c r="AC75" t="n">
         <v>10</v>
       </c>
-      <c r="AD75" t="inlineStr"/>
+      <c r="AD75" t="n">
+        <v>2.299417127324255</v>
+      </c>
       <c r="AE75" t="n">
         <v>4</v>
       </c>
@@ -8797,10 +8899,10 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C76" t="n">
-        <v>1.732632097357969</v>
+        <v>1.822290703646636</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8814,7 +8916,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -8825,25 +8927,25 @@
         <v>10</v>
       </c>
       <c r="J76" t="n">
-        <v>16.69046584362804</v>
+        <v>16.67830837391378</v>
       </c>
       <c r="K76" t="n">
-        <v>2.430133567291515</v>
+        <v>7.714872222919444</v>
       </c>
       <c r="L76" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="M76" t="n">
-        <v>52.5</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N76" t="n">
-        <v>12.09379352040093</v>
+        <v>13.015290494646</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>7.390272929533448</v>
+        <v>2.121459859648178</v>
       </c>
       <c r="Q76" t="n">
         <v>41</v>
@@ -8866,37 +8968,47 @@
       <c r="W76" t="n">
         <v>60</v>
       </c>
-      <c r="X76" t="inlineStr"/>
-      <c r="Y76" t="inlineStr"/>
+      <c r="X76" t="n">
+        <v>10.81408696253991</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>2.796769638744701</v>
+      </c>
       <c r="Z76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA76" t="inlineStr"/>
-      <c r="AB76" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>36.95652173913044</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>10.29901372834726</v>
+      </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
-      <c r="AD76" t="inlineStr"/>
+      <c r="AD76" t="n">
+        <v>1.237850179241473</v>
+      </c>
       <c r="AE76" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AF76" t="n">
-        <v>54.54545454545455</v>
+        <v>53.125</v>
       </c>
       <c r="AG76" t="n">
-        <v>26.45137047677935</v>
+        <v>26.4186008041787</v>
       </c>
       <c r="AH76" t="n">
-        <v>28.0940840686752</v>
+        <v>26.7063991958213</v>
       </c>
       <c r="AI76" t="n">
-        <v>37.98593853621745</v>
+        <v>36.44951711897464</v>
       </c>
       <c r="AJ76" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AK76" t="n">
-        <v>55.55555555555556</v>
+        <v>56.60377358490566</v>
       </c>
     </row>
     <row r="77">
@@ -8906,10 +9018,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4468258604417319</v>
+        <v>0.4552645095017976</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8934,40 +9046,40 @@
         <v>10</v>
       </c>
       <c r="J77" t="n">
-        <v>24.27381268520708</v>
+        <v>24.26276186325519</v>
       </c>
       <c r="K77" t="n">
-        <v>3.228871401296374</v>
+        <v>5.163081220833443</v>
       </c>
       <c r="L77" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M77" t="n">
-        <v>61.90476190476191</v>
+        <v>50</v>
       </c>
       <c r="N77" t="n">
-        <v>14.93209402914525</v>
+        <v>14.52266323959448</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>4.621893598115734</v>
+        <v>2.697637560855859</v>
       </c>
       <c r="Q77" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R77" t="n">
-        <v>59.25925925925926</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="S77" t="n">
-        <v>37.88194542688007</v>
+        <v>39.12629649762003</v>
       </c>
       <c r="T77" t="n">
-        <v>21.37731383237919</v>
+        <v>18.56601119468766</v>
       </c>
       <c r="U77" t="n">
-        <v>40.72670096806468</v>
+        <v>38.94861374659171</v>
       </c>
       <c r="V77" t="n">
         <v>74</v>
@@ -9015,24 +9127,24 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0517939821200213</v>
+        <v>0.04971751412429379</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -9043,25 +9155,25 @@
         <v>10</v>
       </c>
       <c r="J78" t="n">
-        <v>17.69784066106923</v>
+        <v>25.8942641091822</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>6.607929515418487</v>
       </c>
       <c r="L78" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="M78" t="n">
-        <v>72.22222222222223</v>
+        <v>50</v>
       </c>
       <c r="N78" t="n">
-        <v>16.65865179315538</v>
+        <v>17.26382553739754</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>4.000000000000004</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9088,7 +9200,7 @@
         <v>36.67113091579677</v>
       </c>
       <c r="Y78" t="n">
-        <v>17.69784066106923</v>
+        <v>20.99740931463477</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -9130,19 +9242,19 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7855420934629819</v>
+        <v>0.8152028762198255</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -9150,11 +9262,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.19: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>5</v>
       </c>
@@ -9162,25 +9270,25 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>21.2716637331844</v>
+        <v>22.50123891318462</v>
       </c>
       <c r="K79" t="n">
-        <v>0.1572362951673512</v>
+        <v>5.588078765300719</v>
       </c>
       <c r="L79" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M79" t="n">
-        <v>76.19047619047619</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N79" t="n">
-        <v>11.16947312028342</v>
+        <v>9.851354600863276</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>4.835161076690286</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9221,10 +9329,10 @@
         <v>52.77777777777778</v>
       </c>
       <c r="AG79" t="n">
-        <v>26.25121703553076</v>
+        <v>26.07940132552061</v>
       </c>
       <c r="AH79" t="n">
-        <v>26.52656074224702</v>
+        <v>26.69837645225717</v>
       </c>
       <c r="AI79" t="n">
         <v>37.00593802298759</v>
@@ -9243,10 +9351,10 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1253743207381818</v>
+        <v>0.1273754494093477</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9271,25 +9379,25 @@
         <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>14.3660641740055</v>
+        <v>14.35356750130339</v>
       </c>
       <c r="K80" t="n">
-        <v>2.521009996469248</v>
+        <v>4.142174059407444</v>
       </c>
       <c r="L80" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="M80" t="n">
-        <v>53.52112676056338</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N80" t="n">
-        <v>14.10895329588439</v>
+        <v>15.97764254988657</v>
       </c>
       <c r="O80" t="n">
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>7.295080299919343</v>
+        <v>5.62483546507393</v>
       </c>
       <c r="Q80" t="n">
         <v>39</v>
@@ -9352,10 +9460,10 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C81" t="n">
-        <v>1.156115681497425</v>
+        <v>1.18130457113508</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9380,25 +9488,25 @@
         <v>10</v>
       </c>
       <c r="J81" t="n">
-        <v>11.63378900147833</v>
+        <v>11.6208936042725</v>
       </c>
       <c r="K81" t="n">
-        <v>2.739726027397271</v>
+        <v>4.962852150011821</v>
       </c>
       <c r="L81" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="M81" t="n">
-        <v>45.83333333333334</v>
+        <v>54.28571428571428</v>
       </c>
       <c r="N81" t="n">
-        <v>13.27513906931236</v>
+        <v>14.61042500973081</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>7.066666666666666</v>
+        <v>4.79898149374709</v>
       </c>
       <c r="Q81" t="n">
         <v>32</v>
@@ -9425,22 +9533,22 @@
         <v>23.79225853623819</v>
       </c>
       <c r="Y81" t="n">
-        <v>9.212796919327049</v>
+        <v>7.23476922235089</v>
       </c>
       <c r="Z81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA81" t="n">
-        <v>62.5</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB81" t="n">
-        <v>9.59631867771729</v>
+        <v>10.31224629251335</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.8670859481963</v>
+        <v>2.980891390522322</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9474,7 +9582,7 @@
         <v>46281</v>
       </c>
       <c r="C82" t="n">
-        <v>4.663513619190403</v>
+        <v>4.664194171856571</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9499,7 +9607,7 @@
         <v>10</v>
       </c>
       <c r="J82" t="n">
-        <v>20.03998055701367</v>
+        <v>20.02831188637983</v>
       </c>
       <c r="K82" t="n">
         <v>4.321836275862068</v>
@@ -9580,10 +9688,10 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C83" t="n">
-        <v>5.189674836943998</v>
+        <v>5.423728813559323</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9608,25 +9716,25 @@
         <v>10</v>
       </c>
       <c r="J83" t="n">
-        <v>17.92396384855412</v>
+        <v>17.91198638482344</v>
       </c>
       <c r="K83" t="n">
-        <v>3.824014459963987</v>
+        <v>8.490638158096164</v>
       </c>
       <c r="L83" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="M83" t="n">
-        <v>61.76470588235294</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N83" t="n">
-        <v>11.78231284439357</v>
+        <v>10.11104878975791</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>5.948513522772303</v>
+        <v>1.391236946827012</v>
       </c>
       <c r="Q83" t="n">
         <v>41</v>
@@ -9667,10 +9775,10 @@
         <v>58.53658536585366</v>
       </c>
       <c r="AG83" t="n">
-        <v>27.52049734251406</v>
+        <v>26.94157983411617</v>
       </c>
       <c r="AH83" t="n">
-        <v>31.0160880233396</v>
+        <v>31.59500553173749</v>
       </c>
       <c r="AI83" t="n">
         <v>43.36710313403013</v>
@@ -9689,24 +9797,24 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C84" t="n">
-        <v>1.967965804504506</v>
+        <v>2.04417051874679</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -9717,25 +9825,25 @@
         <v>10</v>
       </c>
       <c r="J84" t="n">
-        <v>15.18592070700058</v>
+        <v>15.16163094199509</v>
       </c>
       <c r="K84" t="n">
-        <v>3.794037940379402</v>
+        <v>7.797479899838966</v>
       </c>
       <c r="L84" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="M84" t="n">
-        <v>59.52380952380953</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="N84" t="n">
-        <v>12.80301434137708</v>
+        <v>9.320724527744272</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
       </c>
       <c r="P84" t="n">
-        <v>1.161879895561357</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
         <v>41</v>
@@ -9758,17 +9866,27 @@
       <c r="W84" t="n">
         <v>56.89655172413793</v>
       </c>
-      <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr"/>
+      <c r="X84" t="n">
+        <v>10.78590455284554</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>2.697477323553432</v>
+      </c>
       <c r="Z84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA84" t="inlineStr"/>
-      <c r="AB84" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>33.9622641509434</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>11.1452999859144</v>
+      </c>
       <c r="AC84" t="n">
         <v>2</v>
       </c>
-      <c r="AD84" t="inlineStr"/>
+      <c r="AD84" t="n">
+        <v>0</v>
+      </c>
       <c r="AE84" t="n">
         <v>38</v>
       </c>
@@ -9776,10 +9894,10 @@
         <v>44.73684210526316</v>
       </c>
       <c r="AG84" t="n">
-        <v>28.56199550464609</v>
+        <v>28.42345692786126</v>
       </c>
       <c r="AH84" t="n">
-        <v>16.17484660061707</v>
+        <v>16.31338517740189</v>
       </c>
       <c r="AI84" t="n">
         <v>30.14640099805125</v>
@@ -9798,24 +9916,24 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C85" t="n">
-        <v>5.611014774200838</v>
+        <v>5.834617360041089</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -9826,25 +9944,25 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>20.69386737840766</v>
+        <v>18.97253537621143</v>
       </c>
       <c r="K85" t="n">
-        <v>5.711519845111335</v>
+        <v>9.908153580910595</v>
       </c>
       <c r="L85" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="M85" t="n">
-        <v>60</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N85" t="n">
-        <v>12.47903562685071</v>
+        <v>13.06681422181477</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>2.164835164835166</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
         <v>32</v>
@@ -9867,17 +9985,27 @@
       <c r="W85" t="n">
         <v>57.89473684210526</v>
       </c>
-      <c r="X85" t="inlineStr"/>
-      <c r="Y85" t="inlineStr"/>
+      <c r="X85" t="n">
+        <v>11.51984511132624</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>1.445206033784174</v>
+      </c>
       <c r="Z85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA85" t="inlineStr"/>
-      <c r="AB85" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>32.14285714285715</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>10.80937071531154</v>
+      </c>
       <c r="AC85" t="n">
         <v>6</v>
       </c>
-      <c r="AD85" t="inlineStr"/>
+      <c r="AD85" t="n">
+        <v>4.62158539723313</v>
+      </c>
       <c r="AE85" t="n">
         <v>33</v>
       </c>
@@ -9885,10 +10013,10 @@
         <v>42.42424242424242</v>
       </c>
       <c r="AG85" t="n">
-        <v>26.87175563178237</v>
+        <v>26.82314114466521</v>
       </c>
       <c r="AH85" t="n">
-        <v>15.55248679246005</v>
+        <v>15.60110127957721</v>
       </c>
       <c r="AI85" t="n">
         <v>27.23559663341021</v>
@@ -9907,10 +10035,10 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C86" t="n">
-        <v>4.823828389711874</v>
+        <v>5.049820236260914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9927,11 +10055,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>5</v>
       </c>
@@ -9942,17 +10066,13 @@
         <v>18.73514495170452</v>
       </c>
       <c r="K86" t="n">
-        <v>15.70952897071627</v>
+        <v>21.13041213712048</v>
       </c>
       <c r="L86" t="n">
-        <v>4</v>
-      </c>
-      <c r="M86" t="n">
-        <v>100</v>
-      </c>
-      <c r="N86" t="n">
-        <v>9.572507806866966</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="O86" t="n">
         <v>8</v>
       </c>
@@ -9981,25 +10101,25 @@
         <v>70.12987012987013</v>
       </c>
       <c r="X86" t="n">
-        <v>32.57395859734095</v>
+        <v>25.31841820362353</v>
       </c>
       <c r="Y86" t="n">
-        <v>5.968819004881953</v>
+        <v>1.563546157366125</v>
       </c>
       <c r="Z86" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="AA86" t="n">
-        <v>46.15384615384615</v>
+        <v>39.39393939393939</v>
       </c>
       <c r="AB86" t="n">
-        <v>11.53839637208252</v>
+        <v>14.37428716199456</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.03316027171845759</v>
+        <v>4.506921642795314</v>
       </c>
       <c r="AE86" t="n">
         <v>52</v>
@@ -10030,19 +10150,19 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C87" t="n">
-        <v>5.595599898447539</v>
+        <v>5.819209039548023</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -10058,25 +10178,25 @@
         <v>10</v>
       </c>
       <c r="J87" t="n">
-        <v>13.37194292575289</v>
+        <v>13.35930117963161</v>
       </c>
       <c r="K87" t="n">
-        <v>4.711538461538467</v>
+        <v>8.880090365493265</v>
       </c>
       <c r="L87" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="M87" t="n">
-        <v>66.66666666666667</v>
+        <v>56.25</v>
       </c>
       <c r="N87" t="n">
-        <v>12.46335282189862</v>
+        <v>10.66774603943682</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>0.2754820936639035</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
         <v>47</v>
@@ -10103,16 +10223,16 @@
         <v>15.88967756874082</v>
       </c>
       <c r="Y87" t="n">
-        <v>9.290428698216235</v>
+        <v>5.66552883108804</v>
       </c>
       <c r="Z87" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="AA87" t="n">
-        <v>43.47826086956522</v>
+        <v>48.57142857142857</v>
       </c>
       <c r="AB87" t="n">
-        <v>9.81984764394735</v>
+        <v>12.87565806722536</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
@@ -10127,10 +10247,10 @@
         <v>46.51162790697674</v>
       </c>
       <c r="AG87" t="n">
-        <v>44.70540456781678</v>
+        <v>44.54142126429858</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.806223339159963</v>
+        <v>1.970206642678157</v>
       </c>
       <c r="AI87" t="n">
         <v>32.51105770412182</v>
@@ -10149,10 +10269,10 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9729869606312084</v>
+        <v>1.015305598356446</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10166,7 +10286,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -10177,19 +10297,19 @@
         <v>10</v>
       </c>
       <c r="J88" t="n">
-        <v>21.4136770887586</v>
+        <v>21.40220888346344</v>
       </c>
       <c r="K88" t="n">
-        <v>3.543304651731605</v>
+        <v>8.031003390109515</v>
       </c>
       <c r="L88" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="M88" t="n">
-        <v>66.66666666666667</v>
+        <v>65.38461538461539</v>
       </c>
       <c r="N88" t="n">
-        <v>15.7982644002163</v>
+        <v>12.82925226559228</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
@@ -10218,17 +10338,27 @@
       <c r="W88" t="n">
         <v>62.0253164556962</v>
       </c>
-      <c r="X88" t="inlineStr"/>
-      <c r="Y88" t="inlineStr"/>
+      <c r="X88" t="n">
+        <v>12.09536008844403</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>3.625802794270616</v>
+      </c>
       <c r="Z88" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA88" t="inlineStr"/>
-      <c r="AB88" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>37.70491803278689</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>12.03512072489898</v>
+      </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
-      <c r="AD88" t="inlineStr"/>
+      <c r="AD88" t="n">
+        <v>2.463519567028094</v>
+      </c>
       <c r="AE88" t="n">
         <v>33</v>
       </c>
@@ -10236,10 +10366,10 @@
         <v>51.51515151515152</v>
       </c>
       <c r="AG88" t="n">
-        <v>52.16480083071696</v>
+        <v>51.79797467441712</v>
       </c>
       <c r="AH88" t="n">
-        <v>-0.6496493155654477</v>
+        <v>-0.2828231592656039</v>
       </c>
       <c r="AI88" t="n">
         <v>35.21837544891414</v>
@@ -10258,19 +10388,19 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C89" t="n">
-        <v>2.035791320506183</v>
+        <v>2.103749357986646</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -10286,25 +10416,25 @@
         <v>10</v>
       </c>
       <c r="J89" t="n">
-        <v>15.60289553329434</v>
+        <v>15.59057935301659</v>
       </c>
       <c r="K89" t="n">
-        <v>3.016122177694558</v>
+        <v>6.43943565168863</v>
       </c>
       <c r="L89" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="M89" t="n">
-        <v>60.9375</v>
+        <v>71.05263157894737</v>
       </c>
       <c r="N89" t="n">
-        <v>15.49811169581316</v>
+        <v>18.27058283257839</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>0.9550716931552961</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
         <v>45</v>
@@ -10331,16 +10461,16 @@
         <v>21.41032003314154</v>
       </c>
       <c r="Y89" t="n">
-        <v>13.05737574814198</v>
+        <v>10.1550890264909</v>
       </c>
       <c r="Z89" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AA89" t="n">
-        <v>40</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="AB89" t="n">
-        <v>20.63598439723828</v>
+        <v>17.94417613395044</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
@@ -10377,10 +10507,10 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C90" t="n">
-        <v>2.571201244203928</v>
+        <v>2.66050333846944</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10405,25 +10535,25 @@
         <v>10</v>
       </c>
       <c r="J90" t="n">
-        <v>19.80380280689519</v>
+        <v>19.79209967053214</v>
       </c>
       <c r="K90" t="n">
-        <v>2.625099999865443</v>
+        <v>6.173946250946938</v>
       </c>
       <c r="L90" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="M90" t="n">
-        <v>67.44186046511628</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N90" t="n">
-        <v>16.22175178846877</v>
+        <v>17.26814489631478</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>5.237412679882025</v>
+        <v>1.719869905501215</v>
       </c>
       <c r="Q90" t="n">
         <v>43</v>
@@ -10486,24 +10616,24 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2147805982575309</v>
+        <v>0.2245505906522856</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -10514,25 +10644,25 @@
         <v>10</v>
       </c>
       <c r="J91" t="n">
-        <v>13.48127127666011</v>
+        <v>13.46864548496864</v>
       </c>
       <c r="K91" t="n">
-        <v>2.652254339666116</v>
+        <v>7.306065881522317</v>
       </c>
       <c r="L91" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="M91" t="n">
-        <v>61.29032258064516</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N91" t="n">
-        <v>14.02094716097644</v>
+        <v>13.74271301446917</v>
       </c>
       <c r="O91" t="n">
         <v>6</v>
       </c>
       <c r="P91" t="n">
-        <v>3.261249041113623</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>44</v>
@@ -10555,17 +10685,27 @@
       <c r="W91" t="n">
         <v>66.25</v>
       </c>
-      <c r="X91" t="inlineStr"/>
-      <c r="Y91" t="inlineStr"/>
+      <c r="X91" t="n">
+        <v>10.31433396881691</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>2.726996555266314</v>
+      </c>
       <c r="Z91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA91" t="inlineStr"/>
-      <c r="AB91" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>31.11111111111111</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>12.47955093451849</v>
+      </c>
       <c r="AC91" t="n">
         <v>5</v>
       </c>
-      <c r="AD91" t="inlineStr"/>
+      <c r="AD91" t="n">
+        <v>2.336725878958912</v>
+      </c>
       <c r="AE91" t="n">
         <v>39</v>
       </c>
@@ -10595,10 +10735,10 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C92" t="n">
-        <v>1.024369879808872</v>
+        <v>1.080636877247047</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10623,25 +10763,25 @@
         <v>10</v>
       </c>
       <c r="J92" t="n">
-        <v>18.9533737337655</v>
+        <v>19.02065273936991</v>
       </c>
       <c r="K92" t="n">
-        <v>0.9315493520300144</v>
+        <v>6.564019448946534</v>
       </c>
       <c r="L92" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="M92" t="n">
-        <v>66.66666666666667</v>
+        <v>65</v>
       </c>
       <c r="N92" t="n">
-        <v>14.27412854503239</v>
+        <v>14.49553492530685</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>7.003212269452619</v>
+        <v>1.347528517110264</v>
       </c>
       <c r="Q92" t="n">
         <v>44</v>
@@ -10682,10 +10822,10 @@
         <v>51.92307692307692</v>
       </c>
       <c r="AG92" t="n">
-        <v>40.08078371334503</v>
+        <v>39.80652524576674</v>
       </c>
       <c r="AH92" t="n">
-        <v>11.84229320973188</v>
+        <v>12.11655167731018</v>
       </c>
       <c r="AI92" t="n">
         <v>38.68568276805605</v>
@@ -10704,10 +10844,10 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C93" t="n">
-        <v>0.03925654963513977</v>
+        <v>0.0396507447354905</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10732,25 +10872,25 @@
         <v>10</v>
       </c>
       <c r="J93" t="n">
-        <v>13.48686157735825</v>
+        <v>13.47423660146673</v>
       </c>
       <c r="K93" t="n">
-        <v>3.243240505478484</v>
+        <v>4.264743216516309</v>
       </c>
       <c r="L93" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="M93" t="n">
-        <v>56.45161290322581</v>
+        <v>64.15094339622641</v>
       </c>
       <c r="N93" t="n">
-        <v>19.44900800053373</v>
+        <v>18.74669448162565</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>2.670159790630788</v>
+        <v>1.664279534914548</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10785,19 +10925,19 @@
       </c>
       <c r="AD93" t="inlineStr"/>
       <c r="AE93" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF93" t="n">
-        <v>58.33333333333334</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="AG93" t="n">
-        <v>24.28680322228977</v>
+        <v>24.81020000375118</v>
       </c>
       <c r="AH93" t="n">
-        <v>34.04653011104357</v>
+        <v>36.05936521364012</v>
       </c>
       <c r="AI93" t="n">
-        <v>38.83466586522876</v>
+        <v>40.78552239138171</v>
       </c>
       <c r="AJ93" t="n">
         <v>89</v>
@@ -10813,19 +10953,19 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C94" t="n">
-        <v>8.2572351118505</v>
+        <v>8.479712378017464</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -10841,25 +10981,25 @@
         <v>10</v>
       </c>
       <c r="J94" t="n">
-        <v>10.47383040533549</v>
+        <v>10.46076573384858</v>
       </c>
       <c r="K94" t="n">
-        <v>5.723684210526314</v>
+        <v>8.556388698591633</v>
       </c>
       <c r="L94" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M94" t="n">
-        <v>44.44444444444444</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N94" t="n">
-        <v>15.97263423873417</v>
+        <v>13.67467251595421</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>2.153080273802122</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>41</v>
@@ -10868,10 +11008,10 @@
         <v>63.41463414634146</v>
       </c>
       <c r="S94" t="n">
-        <v>41.35906589169578</v>
+        <v>41.4511736037438</v>
       </c>
       <c r="T94" t="n">
-        <v>22.05556825464569</v>
+        <v>21.96346054259767</v>
       </c>
       <c r="U94" t="n">
         <v>48.12070108791201</v>
@@ -10883,25 +11023,25 @@
         <v>70.90909090909091</v>
       </c>
       <c r="X94" t="n">
-        <v>36.6815048892442</v>
+        <v>30.64601732980787</v>
       </c>
       <c r="Y94" t="n">
-        <v>5.349635171956669</v>
+        <v>2.799440812294107</v>
       </c>
       <c r="Z94" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA94" t="n">
-        <v>46.15384615384615</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB94" t="n">
-        <v>13.56192792270044</v>
+        <v>12.16646182899771</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>0.6871234244314794</v>
+        <v>3.292737422966097</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -10919,10 +11059,10 @@
         <v>37.25897138449667</v>
       </c>
       <c r="AJ94" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AK94" t="n">
-        <v>53.57142857142857</v>
+        <v>54.54545454545455</v>
       </c>
     </row>
     <row r="95">
@@ -10935,7 +11075,7 @@
         <v>46281</v>
       </c>
       <c r="C95" t="n">
-        <v>0.11057604433118</v>
+        <v>0.1105921808385281</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10960,7 +11100,7 @@
         <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>27.10987320553127</v>
+        <v>27.09923625361518</v>
       </c>
       <c r="K95" t="n">
         <v>1.509432398718458</v>
@@ -11041,10 +11181,10 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1229079430840341</v>
+        <v>0.125115562403698</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11069,25 +11209,25 @@
         <v>10</v>
       </c>
       <c r="J96" t="n">
-        <v>11.75043307651951</v>
+        <v>11.73755470133672</v>
       </c>
       <c r="K96" t="n">
-        <v>3.46020419954276</v>
+        <v>5.303144617760203</v>
       </c>
       <c r="L96" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M96" t="n">
-        <v>49.12280701754386</v>
+        <v>60</v>
       </c>
       <c r="N96" t="n">
-        <v>13.78833771514818</v>
+        <v>14.83656468726668</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>6.321073741401095</v>
+        <v>4.460318254776641</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11150,19 +11290,19 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C97" t="n">
-        <v>1.75215754395832</v>
+        <v>1.798664612223934</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -11178,25 +11318,25 @@
         <v>10</v>
       </c>
       <c r="J97" t="n">
-        <v>19.39324184071789</v>
+        <v>19.38147879065393</v>
       </c>
       <c r="K97" t="n">
-        <v>3.521556264577774</v>
+        <v>6.253796623444763</v>
       </c>
       <c r="L97" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M97" t="n">
-        <v>48.27586206896552</v>
+        <v>47.61904761904762</v>
       </c>
       <c r="N97" t="n">
-        <v>12.52044075672272</v>
+        <v>10.2405732777383</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>0.462168221466297</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>50</v>
@@ -11259,10 +11399,10 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6342707668665086</v>
+        <v>0.6722136620441705</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11287,25 +11427,25 @@
         <v>10</v>
       </c>
       <c r="J98" t="n">
-        <v>20.00786348235382</v>
+        <v>19.99619012483309</v>
       </c>
       <c r="K98" t="n">
-        <v>1.180329868852459</v>
+        <v>7.217421296407256</v>
       </c>
       <c r="L98" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="M98" t="n">
-        <v>55.31914893617022</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N98" t="n">
-        <v>17.88226239073032</v>
+        <v>17.72021339555821</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>8.716783333854906</v>
+        <v>2.595267326846251</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11332,10 +11472,10 @@
         <v>30.85778357900837</v>
       </c>
       <c r="Y98" t="n">
-        <v>19.0636924023028</v>
+        <v>14.22197811296562</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA98" t="inlineStr"/>
       <c r="AB98" t="inlineStr"/>
@@ -11352,10 +11492,10 @@
         <v>56.86274509803921</v>
       </c>
       <c r="AG98" t="n">
-        <v>37.20855910924046</v>
+        <v>36.83192412476235</v>
       </c>
       <c r="AH98" t="n">
-        <v>19.65418598879875</v>
+        <v>20.03082097327687</v>
       </c>
       <c r="AI98" t="n">
         <v>43.26530210930225</v>
@@ -11374,24 +11514,24 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4899875203611729</v>
+        <v>0.4955315870570108</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -11402,25 +11542,25 @@
         <v>10</v>
       </c>
       <c r="J99" t="n">
-        <v>18.77117372239303</v>
+        <v>18.75931989311172</v>
       </c>
       <c r="K99" t="n">
-        <v>2.936098032833123</v>
+        <v>4.085600782067633</v>
       </c>
       <c r="L99" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="M99" t="n">
-        <v>49.01960784313726</v>
+        <v>57.5</v>
       </c>
       <c r="N99" t="n">
-        <v>17.45280326453614</v>
+        <v>16.56472255328778</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>1.033555756919724</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>34</v>
@@ -11447,7 +11587,7 @@
         <v>33.04241514445872</v>
       </c>
       <c r="Y99" t="n">
-        <v>16.38621575196278</v>
+        <v>15.44015003130763</v>
       </c>
       <c r="Z99" t="n">
         <v>0</v>
@@ -11455,31 +11595,31 @@
       <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="AF99" t="n">
-        <v>50</v>
+        <v>43.90243902439025</v>
       </c>
       <c r="AG99" t="n">
-        <v>35.90154855615382</v>
+        <v>28.98051503528407</v>
       </c>
       <c r="AH99" t="n">
-        <v>14.09845144384618</v>
+        <v>14.92192398910617</v>
       </c>
       <c r="AI99" t="n">
-        <v>34.8499283643951</v>
+        <v>29.89013173655036</v>
       </c>
       <c r="AJ99" t="n">
         <v>78</v>
       </c>
       <c r="AK99" t="n">
-        <v>48.71794871794872</v>
+        <v>46.15384615384615</v>
       </c>
     </row>
     <row r="100">
@@ -11492,7 +11632,7 @@
         <v>46281</v>
       </c>
       <c r="C100" t="n">
-        <v>311.378643642982</v>
+        <v>311.4240835373241</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11517,10 +11657,10 @@
         <v>10</v>
       </c>
       <c r="J100" t="n">
-        <v>16.74174295537163</v>
+        <v>16.72959296859361</v>
       </c>
       <c r="K100" t="n">
-        <v>2.653906669425177</v>
+        <v>2.653906669425155</v>
       </c>
       <c r="L100" t="n">
         <v>39</v>
@@ -11535,7 +11675,7 @@
         <v>5</v>
       </c>
       <c r="P100" t="n">
-        <v>2.285439888936636</v>
+        <v>2.285439888936658</v>
       </c>
       <c r="Q100" t="n">
         <v>48</v>
@@ -11544,10 +11684,10 @@
         <v>60.41666666666666</v>
       </c>
       <c r="S100" t="n">
-        <v>36.6940103882404</v>
+        <v>36.43012149935151</v>
       </c>
       <c r="T100" t="n">
-        <v>23.72265627842626</v>
+        <v>23.98654516731516</v>
       </c>
       <c r="U100" t="n">
         <v>46.31040849254725</v>
@@ -11598,10 +11738,10 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C101" t="n">
-        <v>323.0144060479765</v>
+        <v>333.628145865434</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11626,19 +11766,19 @@
         <v>10</v>
       </c>
       <c r="J101" t="n">
-        <v>12.8685741725276</v>
+        <v>12.85585896914321</v>
       </c>
       <c r="K101" t="n">
-        <v>2.57011898166426</v>
+        <v>5.924952246312443</v>
       </c>
       <c r="L101" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="M101" t="n">
-        <v>43.58974358974359</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N101" t="n">
-        <v>10.26074329556575</v>
+        <v>8.711895906939038</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11653,10 +11793,10 @@
         <v>46.66666666666666</v>
       </c>
       <c r="S101" t="n">
-        <v>18.6844317051725</v>
+        <v>18.76776503850583</v>
       </c>
       <c r="T101" t="n">
-        <v>27.98223496149417</v>
+        <v>27.89890162816083</v>
       </c>
       <c r="U101" t="n">
         <v>30.23238890769975</v>
@@ -11710,7 +11850,7 @@
         <v>46281</v>
       </c>
       <c r="C102" t="n">
-        <v>376.6443845813294</v>
+        <v>376.699348790948</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11735,7 +11875,7 @@
         <v>10</v>
       </c>
       <c r="J102" t="n">
-        <v>13.67983142705997</v>
+        <v>13.66723461151199</v>
       </c>
       <c r="K102" t="n">
         <v>2.359097070931426</v>
@@ -11816,24 +11956,24 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C103" t="n">
-        <v>0.6601677236027294</v>
+        <v>0.7116589625064201</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -11844,25 +11984,25 @@
         <v>10</v>
       </c>
       <c r="J103" t="n">
-        <v>18.80277245522091</v>
+        <v>18.79092323718417</v>
       </c>
       <c r="K103" t="n">
-        <v>2.882766303302664</v>
+        <v>10.89115228041664</v>
       </c>
       <c r="L103" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="M103" t="n">
-        <v>47.05882352941177</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="N103" t="n">
-        <v>18.45620348177728</v>
+        <v>18.86051193733509</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
       </c>
       <c r="P103" t="n">
-        <v>6.917809417872234</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
         <v>43</v>
@@ -11885,17 +12025,27 @@
       <c r="W103" t="n">
         <v>67.69230769230769</v>
       </c>
-      <c r="X103" t="inlineStr"/>
-      <c r="Y103" t="inlineStr"/>
+      <c r="X103" t="n">
+        <v>11.33888240947563</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>0.4021327674301189</v>
+      </c>
       <c r="Z103" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA103" t="inlineStr"/>
-      <c r="AB103" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>38.18181818181818</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>11.17863579793928</v>
+      </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
-      <c r="AD103" t="inlineStr"/>
+      <c r="AD103" t="n">
+        <v>7.628544108106428</v>
+      </c>
       <c r="AE103" t="n">
         <v>32</v>
       </c>
@@ -11903,19 +12053,19 @@
         <v>59.375</v>
       </c>
       <c r="AG103" t="n">
-        <v>34.23085106690951</v>
+        <v>34.05307872219637</v>
       </c>
       <c r="AH103" t="n">
-        <v>25.14414893309049</v>
+        <v>25.32192127780363</v>
       </c>
       <c r="AI103" t="n">
         <v>42.26002487538288</v>
       </c>
       <c r="AJ103" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AK103" t="n">
-        <v>50</v>
+        <v>50.84745762711864</v>
       </c>
     </row>
     <row r="104">
@@ -11925,24 +12075,24 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C104" t="n">
-        <v>0.05241057653355823</v>
+        <v>0.0519774011299435</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -11952,17 +12102,27 @@
       <c r="I104" t="n">
         <v>10</v>
       </c>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
+      <c r="J104" t="n">
+        <v>11.61049328507885</v>
+      </c>
+      <c r="K104" t="n">
+        <v>7.142170145591331</v>
+      </c>
       <c r="L104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="M104" t="n">
+        <v>57.14285714285715</v>
+      </c>
+      <c r="N104" t="n">
+        <v>13.23547020137772</v>
+      </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
-      <c r="P104" t="inlineStr"/>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
       <c r="Q104" t="n">
         <v>32</v>
       </c>
@@ -11985,46 +12145,46 @@
         <v>63.23529411764706</v>
       </c>
       <c r="X104" t="n">
-        <v>17.89957543470515</v>
+        <v>17.91678067456379</v>
       </c>
       <c r="Y104" t="n">
-        <v>4.494386756722479</v>
+        <v>5.297564324650317</v>
       </c>
       <c r="Z104" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="AA104" t="n">
-        <v>44.11764705882353</v>
+        <v>45.16129032258065</v>
       </c>
       <c r="AB104" t="n">
-        <v>13.85961485882081</v>
+        <v>15.04730035498116</v>
       </c>
       <c r="AC104" t="n">
         <v>5</v>
       </c>
       <c r="AD104" t="n">
-        <v>0.5294068339099622</v>
+        <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AF104" t="n">
-        <v>57.14285714285715</v>
+        <v>55.81395348837209</v>
       </c>
       <c r="AG104" t="n">
-        <v>30.00568606082085</v>
+        <v>30.00683953084836</v>
       </c>
       <c r="AH104" t="n">
-        <v>27.13717108203629</v>
+        <v>25.80711395752374</v>
       </c>
       <c r="AI104" t="n">
-        <v>42.20623987810458</v>
+        <v>41.1076144528241</v>
       </c>
       <c r="AJ104" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK104" t="n">
-        <v>62.33766233766234</v>
+        <v>61.53846153846154</v>
       </c>
     </row>
   </sheetData>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -444,7 +444,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -670,7 +670,7 @@
         <v>46282</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3872624550590653</v>
+        <v>0.3802773497688752</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,25 +695,25 @@
         <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>22.31899460285077</v>
+        <v>22.3316078451137</v>
       </c>
       <c r="K2" t="n">
-        <v>6.617060638595862</v>
+        <v>4.710996456505301</v>
       </c>
       <c r="L2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M2" t="n">
-        <v>58.8235294117647</v>
+        <v>62.5</v>
       </c>
       <c r="N2" t="n">
-        <v>12.44788564839658</v>
+        <v>12.34147749132199</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>3.172981266920716</v>
+        <v>5.051048812902525</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6828758935431253</v>
+        <v>0.697688733025167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -807,64 +807,64 @@
         <v>16.52890779617068</v>
       </c>
       <c r="K3" t="n">
-        <v>8.620144602827162</v>
+        <v>10.97631617328578</v>
       </c>
       <c r="L3" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M3" t="n">
-        <v>65.51724137931035</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="N3" t="n">
-        <v>12.05054107876322</v>
+        <v>13.61056402226099</v>
       </c>
       <c r="O3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P3" t="n">
-        <v>1.270349438603979</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>35</v>
       </c>
       <c r="R3" t="n">
-        <v>60</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="S3" t="n">
-        <v>57.77439736053181</v>
+        <v>54.34091527482774</v>
       </c>
       <c r="T3" t="n">
-        <v>2.225602639468192</v>
+        <v>2.801941868029409</v>
       </c>
       <c r="U3" t="n">
-        <v>43.5727090128925</v>
+        <v>40.85741114397492</v>
       </c>
       <c r="V3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W3" t="n">
-        <v>66.19718309859155</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="X3" t="n">
         <v>17.17248092970491</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.298929116307217</v>
+        <v>5.288071659194782</v>
       </c>
       <c r="Z3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AA3" t="n">
-        <v>36</v>
+        <v>37.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.71633189378402</v>
+        <v>11.72478051794883</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.913742913586914</v>
+        <v>4.975010458925643</v>
       </c>
       <c r="AE3" t="n">
         <v>34</v>
@@ -873,10 +873,10 @@
         <v>61.76470588235294</v>
       </c>
       <c r="AG3" t="n">
-        <v>32.10001528466201</v>
+        <v>31.87565631030304</v>
       </c>
       <c r="AH3" t="n">
-        <v>29.66469059769094</v>
+        <v>29.88904957204991</v>
       </c>
       <c r="AI3" t="n">
         <v>45.0410173444307</v>
@@ -898,7 +898,7 @@
         <v>46282</v>
       </c>
       <c r="C4" t="n">
-        <v>1.43502824858757</v>
+        <v>1.420647149460709</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,19 +923,19 @@
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>18.0048026275308</v>
+        <v>18.01811637499802</v>
       </c>
       <c r="K4" t="n">
-        <v>11.16259437813452</v>
+        <v>10.06645300474955</v>
       </c>
       <c r="L4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M4" t="n">
-        <v>50</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N4" t="n">
-        <v>16.66999385576534</v>
+        <v>12.11791814276196</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -965,25 +965,25 @@
         <v>62.5</v>
       </c>
       <c r="X4" t="n">
-        <v>11.56045620482793</v>
+        <v>11.57857347263838</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3566333808844635</v>
+        <v>1.355206847360912</v>
       </c>
       <c r="Z4" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AA4" t="n">
-        <v>39.6551724137931</v>
+        <v>44.26229508196721</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.61340489271349</v>
+        <v>10.80972660017727</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>9.677881173944147</v>
+        <v>8.763557483731022</v>
       </c>
       <c r="AE4" t="n">
         <v>39</v>
@@ -1017,7 +1017,7 @@
         <v>46282</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2233179250128403</v>
+        <v>0.2214689265536723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,7 +1034,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>5</v>
       </c>
@@ -1042,19 +1046,19 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>21.70061550970117</v>
+        <v>21.7133291595898</v>
       </c>
       <c r="K5" t="n">
-        <v>6.612291985926122</v>
+        <v>5.746747857827406</v>
       </c>
       <c r="L5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M5" t="n">
-        <v>69.56521739130434</v>
+        <v>75</v>
       </c>
       <c r="N5" t="n">
-        <v>12.20014732543721</v>
+        <v>10.94964894035436</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -1126,7 +1130,7 @@
         <v>46282</v>
       </c>
       <c r="C6" t="n">
-        <v>1.386748844375963</v>
+        <v>1.388803287108372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,7 +1158,7 @@
         <v>38.01799643637762</v>
       </c>
       <c r="K6" t="n">
-        <v>10.38430089942763</v>
+        <v>10.54783319705641</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1231,7 +1235,7 @@
         <v>46282</v>
       </c>
       <c r="C7" t="n">
-        <v>2.218798151001541</v>
+        <v>2.192090395480226</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,25 +1260,25 @@
         <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>15.66648809562797</v>
+        <v>15.68018152056624</v>
       </c>
       <c r="K7" t="n">
-        <v>6.343173229902788</v>
+        <v>5.080178623695453</v>
       </c>
       <c r="L7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M7" t="n">
-        <v>64.70588235294117</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N7" t="n">
-        <v>13.49804390284456</v>
+        <v>13.3800083599176</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>1.558000123350967</v>
+        <v>2.778660461513649</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1301,16 +1305,16 @@
         <v>18.9234494530097</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.31706734467297</v>
+        <v>11.39658412663525</v>
       </c>
       <c r="Z7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>53.84615384615385</v>
+        <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>13.52821329026354</v>
+        <v>11.48364838038053</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1350,7 +1354,7 @@
         <v>46282</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3042629686697483</v>
+        <v>0.2997431946584489</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1378,22 +1382,22 @@
         <v>30.96043286594978</v>
       </c>
       <c r="K8" t="n">
-        <v>7.318840579710151</v>
+        <v>5.724637681159406</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>66.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="N8" t="n">
-        <v>10.50913721135396</v>
+        <v>11.3421540561739</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6347062795408531</v>
+        <v>2.152159013022636</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1459,7 +1463,7 @@
         <v>46282</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5403184386235235</v>
+        <v>0.5325115562403698</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,19 +1488,19 @@
         <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>17.63233561222002</v>
+        <v>17.6457098380072</v>
       </c>
       <c r="K9" t="n">
-        <v>5.477447412177794</v>
+        <v>3.970320564707586</v>
       </c>
       <c r="L9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M9" t="n">
-        <v>56</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N9" t="n">
-        <v>10.13518226827468</v>
+        <v>14.08200345625803</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1568,7 +1572,7 @@
         <v>46282</v>
       </c>
       <c r="C10" t="n">
-        <v>1.839753466872111</v>
+        <v>1.803800719054956</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,25 +1597,25 @@
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>15.97669139496675</v>
+        <v>15.9903344514868</v>
       </c>
       <c r="K10" t="n">
-        <v>5.478914909450427</v>
+        <v>3.434424465530683</v>
       </c>
       <c r="L10" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M10" t="n">
-        <v>55.55555555555556</v>
+        <v>56.09756097560975</v>
       </c>
       <c r="N10" t="n">
-        <v>10.53826025924606</v>
+        <v>10.69370433130505</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>4.286245354752416</v>
+        <v>6.347572936568424</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1677,7 +1681,7 @@
         <v>46282</v>
       </c>
       <c r="C11" t="n">
-        <v>7.719568567026195</v>
+        <v>7.591165896250643</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,19 +1706,19 @@
         <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>16.79611533140597</v>
+        <v>16.80962533618998</v>
       </c>
       <c r="K11" t="n">
-        <v>8.067743275387706</v>
+        <v>6.287467427608617</v>
       </c>
       <c r="L11" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="M11" t="n">
-        <v>68.96551724137932</v>
+        <v>71.05263157894737</v>
       </c>
       <c r="N11" t="n">
-        <v>12.06591450785958</v>
+        <v>12.55504624302741</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1786,7 +1790,7 @@
         <v>46282</v>
       </c>
       <c r="C12" t="n">
-        <v>5.279917822290704</v>
+        <v>5.192604006163329</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,19 +1819,19 @@
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>33.96592951889502</v>
+        <v>33.96593120498892</v>
       </c>
       <c r="K12" t="n">
-        <v>7.576391795730442</v>
+        <v>5.797407473269933</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>10.57818638012683</v>
+        <v>11.3182983278354</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
@@ -1899,7 +1903,7 @@
         <v>46282</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1452491011813046</v>
+        <v>0.1397021058038007</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1924,10 +1928,10 @@
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>52.87493091246841</v>
+        <v>54.16324215371029</v>
       </c>
       <c r="K13" t="n">
-        <v>1.726618705035965</v>
+        <v>0.5917159763313418</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1938,7 +1942,7 @@
         <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>4.20084865629422</v>
+        <v>5.376470588235316</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1992,7 +1996,7 @@
         <v>46282</v>
       </c>
       <c r="C14" t="n">
-        <v>8.659476117103237</v>
+        <v>8.551617873651772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,19 +2021,19 @@
         <v>10</v>
       </c>
       <c r="J14" t="n">
-        <v>10.95811609803855</v>
+        <v>10.97257403209156</v>
       </c>
       <c r="K14" t="n">
-        <v>8.015199974240449</v>
+        <v>6.687137955434386</v>
       </c>
       <c r="L14" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M14" t="n">
-        <v>45.45454545454545</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N14" t="n">
-        <v>11.25156720707579</v>
+        <v>9.921811465743719</v>
       </c>
       <c r="O14" t="n">
         <v>2</v>
@@ -2062,16 +2066,16 @@
         <v>16.11612055393703</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.821231042465323</v>
+        <v>5.01918723944531</v>
       </c>
       <c r="Z14" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>39.28571428571428</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.73191461813376</v>
+        <v>13.3466841859654</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2111,7 +2115,7 @@
         <v>46282</v>
       </c>
       <c r="C15" t="n">
-        <v>13.28197226502311</v>
+        <v>12.9532614278377</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2136,25 +2140,25 @@
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>20.41746107198076</v>
+        <v>20.43038307058605</v>
       </c>
       <c r="K15" t="n">
-        <v>5.576925102168229</v>
+        <v>2.980760319344999</v>
       </c>
       <c r="L15" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="M15" t="n">
-        <v>69.56521739130434</v>
+        <v>60.52631578947368</v>
       </c>
       <c r="N15" t="n">
-        <v>17.25561569455263</v>
+        <v>15.35380440396754</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>2.295080004922423</v>
+        <v>4.873958655083022</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2181,7 +2185,7 @@
         <v>33.58229315482664</v>
       </c>
       <c r="Y15" t="n">
-        <v>15.97920248156125</v>
+        <v>18.05860350289925</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2226,7 +2230,7 @@
         <v>46282</v>
       </c>
       <c r="C16" t="n">
-        <v>33.24088341037493</v>
+        <v>32.23420647149461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2243,7 +2247,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %78.26: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>5</v>
       </c>
@@ -2251,25 +2259,25 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>20.70811750908044</v>
+        <v>20.72099231313619</v>
       </c>
       <c r="K16" t="n">
-        <v>3.592309713782971</v>
+        <v>0.4714027333827753</v>
       </c>
       <c r="L16" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="M16" t="n">
-        <v>60.97560975609756</v>
+        <v>78.26086956521739</v>
       </c>
       <c r="N16" t="n">
-        <v>15.60041637170563</v>
+        <v>15.39875477097618</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>6.185488386078997</v>
+        <v>9.483889950161162</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2335,7 +2343,7 @@
         <v>46282</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3494607087827427</v>
+        <v>0.3266563944530047</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2360,10 +2368,10 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>55.14987614016763</v>
+        <v>58.07660480139403</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2.389937181490609e-06</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2374,7 +2382,7 @@
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>8.000000000000007</v>
+        <v>7.999997418867921</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2440,11 +2448,11 @@
         <v>46282</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0682074987159733</v>
+        <v>0.06368772470467386</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2454,7 +2462,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2465,21 +2473,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>39.60735883121092</v>
+        <v>41.94120981718441</v>
       </c>
       <c r="K18" t="n">
-        <v>5.336629563130613</v>
+        <v>2.3102320360749</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="N18" t="n">
+        <v>12.28395657351243</v>
+      </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>4.427111875717005</v>
+        <v>7.516127967741948</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2502,27 +2514,17 @@
       <c r="W18" t="n">
         <v>75.28089887640449</v>
       </c>
-      <c r="X18" t="n">
-        <v>12.69840753338387</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>6.532282160306957</v>
-      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>35</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>42.85714285714285</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>13.79385170587001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
         <v>8</v>
       </c>
-      <c r="AD18" t="n">
-        <v>1.570293865749806</v>
-      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="n">
         <v>36</v>
       </c>
@@ -2555,28 +2557,24 @@
         <v>46282</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02773497688751926</v>
+        <v>0.02629686697483308</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.82: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>5</v>
       </c>
@@ -2584,25 +2582,25 @@
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>16.08088370486966</v>
+        <v>16.0945098434464</v>
       </c>
       <c r="K19" t="n">
-        <v>11.50652609518852</v>
+        <v>5.741875773460658</v>
       </c>
       <c r="L19" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="M19" t="n">
-        <v>81.81818181818181</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="N19" t="n">
-        <v>23.83833040774617</v>
+        <v>20.50431033269351</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4.026904379549578</v>
       </c>
       <c r="Q19" t="n">
         <v>14</v>
@@ -2629,22 +2627,22 @@
         <v>20.26411217973316</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.424708689518887</v>
+        <v>11.27676083154384</v>
       </c>
       <c r="Z19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AA19" t="n">
-        <v>53.33333333333334</v>
+        <v>50</v>
       </c>
       <c r="AB19" t="n">
-        <v>15.30321733399655</v>
+        <v>16.74028578011673</v>
       </c>
       <c r="AC19" t="n">
         <v>10</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.820764285540246</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -2678,7 +2676,7 @@
         <v>46282</v>
       </c>
       <c r="C20" t="n">
-        <v>1.605546995377504</v>
+        <v>1.581920903954802</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2703,25 +2701,25 @@
         <v>10</v>
       </c>
       <c r="J20" t="n">
-        <v>19.80872300614697</v>
+        <v>19.82174384694231</v>
       </c>
       <c r="K20" t="n">
-        <v>4.69888722247167</v>
+        <v>3.174965373200389</v>
       </c>
       <c r="L20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M20" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N20" t="n">
-        <v>12.48330859736214</v>
+        <v>14.50842908359004</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>5.06319877714092</v>
+        <v>6.615010339099592</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
@@ -2787,7 +2785,7 @@
         <v>46282</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8534155110426297</v>
+        <v>0.8386235233692861</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2812,25 +2810,25 @@
         <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>17.89120180125073</v>
+        <v>17.90453399434356</v>
       </c>
       <c r="K21" t="n">
-        <v>5.317803882213878</v>
+        <v>3.509169910838761</v>
       </c>
       <c r="L21" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M21" t="n">
-        <v>42.85714285714285</v>
+        <v>58.53658536585366</v>
       </c>
       <c r="N21" t="n">
-        <v>15.39536796977263</v>
+        <v>15.24784620041386</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>2.54676419267712</v>
+        <v>4.3385818792959</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2857,16 +2855,16 @@
         <v>11.00964066838261</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.127335564639712</v>
+        <v>6.756594033080332</v>
       </c>
       <c r="Z21" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AA21" t="n">
-        <v>50</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="AB21" t="n">
-        <v>10.17115125108776</v>
+        <v>11.9748699679329</v>
       </c>
       <c r="AC21" t="n">
         <v>4</v>
@@ -2906,7 +2904,7 @@
         <v>46282</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2884437596302003</v>
+        <v>0.289060092449923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,10 +2933,10 @@
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>26.83389742906096</v>
+        <v>26.84577757624037</v>
       </c>
       <c r="K22" t="n">
-        <v>7.442429222262392</v>
+        <v>7.689492851388535</v>
       </c>
       <c r="L22" t="n">
         <v>7</v>
@@ -2947,13 +2945,13 @@
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>13.79180858874516</v>
+        <v>12.26786550530817</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>2.380410417235512</v>
+        <v>2.145527003084657</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -2977,10 +2975,10 @@
         <v>75</v>
       </c>
       <c r="X22" t="n">
-        <v>10.71975172264201</v>
+        <v>10.71975172264199</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.960016121233233</v>
+        <v>2.736872892240927</v>
       </c>
       <c r="Z22" t="n">
         <v>26</v>
@@ -2995,7 +2993,7 @@
         <v>5</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.102209622494733</v>
+        <v>2.326808910073119</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3021,7 +3019,7 @@
         <v>46282</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5448382126348228</v>
+        <v>0.5111453518233179</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3046,10 +3044,10 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>47.94737415629003</v>
+        <v>49.65802523708145</v>
       </c>
       <c r="K23" t="n">
-        <v>3.755868544600927</v>
+        <v>0.64725200026714</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3060,7 +3058,7 @@
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>1.199095022624452</v>
+        <v>4.32475593046624</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3151,10 +3149,10 @@
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>35.83486018094283</v>
+        <v>35.83486174340565</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2.435065016292981e-06</v>
       </c>
       <c r="L24" t="n">
         <v>2</v>
@@ -3165,7 +3163,7 @@
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>10.00000000000001</v>
+        <v>9.999997321428555</v>
       </c>
       <c r="Q24" t="n">
         <v>5</v>
@@ -3231,7 +3229,7 @@
         <v>46282</v>
       </c>
       <c r="C25" t="n">
-        <v>3.241910631741141</v>
+        <v>3.192604006163328</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3248,7 +3246,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>5</v>
       </c>
@@ -3256,25 +3258,25 @@
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>26.00351293078278</v>
+        <v>26.01552790938969</v>
       </c>
       <c r="K25" t="n">
-        <v>5.421038399930911</v>
+        <v>3.834536450003867</v>
       </c>
       <c r="L25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M25" t="n">
-        <v>68.42105263157895</v>
+        <v>80</v>
       </c>
       <c r="N25" t="n">
-        <v>12.86359735303449</v>
+        <v>12.75293965107267</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>2.446344334311523</v>
+        <v>4.01163590883058</v>
       </c>
       <c r="Q25" t="n">
         <v>44</v>
@@ -3340,7 +3342,7 @@
         <v>46282</v>
       </c>
       <c r="C26" t="n">
-        <v>0.431843862352337</v>
+        <v>0.4219825372367745</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3365,25 +3367,25 @@
         <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>13.94444585396061</v>
+        <v>13.95841889083065</v>
       </c>
       <c r="K26" t="n">
-        <v>5.356042363486102</v>
+        <v>2.966914508090568</v>
       </c>
       <c r="L26" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="M26" t="n">
-        <v>51.11111111111111</v>
+        <v>44.64285714285715</v>
       </c>
       <c r="N26" t="n">
-        <v>13.79984498519905</v>
+        <v>14.45547397671901</v>
       </c>
       <c r="O26" t="n">
         <v>6</v>
       </c>
       <c r="P26" t="n">
-        <v>0.6112204122969978</v>
+        <v>2.945689405572227</v>
       </c>
       <c r="Q26" t="n">
         <v>32</v>
@@ -3478,7 +3480,7 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>21.1899360280639</v>
+        <v>21.17713737983576</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3510,10 +3512,10 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>59.38704518397979</v>
+        <v>59.36116514542724</v>
       </c>
       <c r="Y27" t="n">
-        <v>21.1899360280639</v>
+        <v>21.17713737983576</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -3548,7 +3550,7 @@
         <v>46282</v>
       </c>
       <c r="C28" t="n">
-        <v>1.288135593220339</v>
+        <v>1.284026707755521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3576,7 +3578,7 @@
         <v>26.56379120725283</v>
       </c>
       <c r="K28" t="n">
-        <v>4.674457429048418</v>
+        <v>4.340567612687818</v>
       </c>
       <c r="L28" t="n">
         <v>17</v>
@@ -3585,7 +3587,7 @@
         <v>70.58823529411765</v>
       </c>
       <c r="N28" t="n">
-        <v>15.46735764916599</v>
+        <v>15.51067522962931</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
@@ -3657,7 +3659,7 @@
         <v>46282</v>
       </c>
       <c r="C29" t="n">
-        <v>0.408834103749358</v>
+        <v>0.3960965588084233</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,7 +3691,7 @@
         <v>27.65210909859499</v>
       </c>
       <c r="K29" t="n">
-        <v>23.45742014766305</v>
+        <v>19.61100806266052</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3727,7 +3729,7 @@
         <v>31.20488584758381</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.904860668771672</v>
+        <v>8.836468024819977</v>
       </c>
       <c r="Z29" t="n">
         <v>3</v>
@@ -3736,13 +3738,13 @@
         <v>100</v>
       </c>
       <c r="AB29" t="n">
-        <v>16.19254517444829</v>
+        <v>14.1224438478875</v>
       </c>
       <c r="AC29" t="n">
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.352126326964512</v>
+        <v>1.276312961960269</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3776,7 +3778,7 @@
         <v>46282</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3932203389830509</v>
+        <v>0.3876733436055471</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3801,19 +3803,19 @@
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>21.02952930685888</v>
+        <v>21.04235192254695</v>
       </c>
       <c r="K30" t="n">
-        <v>7.346068534839545</v>
+        <v>5.848969240474799</v>
       </c>
       <c r="L30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M30" t="n">
-        <v>47.36842105263158</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N30" t="n">
-        <v>12.57899308142685</v>
+        <v>10.69789263517809</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
@@ -3846,17 +3848,13 @@
         <v>26.71344279693404</v>
       </c>
       <c r="Y30" t="n">
-        <v>15.22830440745536</v>
+        <v>16.42414337349438</v>
       </c>
       <c r="Z30" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>22.32041901315758</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
         <v>8</v>
       </c>
@@ -3895,7 +3893,7 @@
         <v>46282</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2263995891114535</v>
+        <v>0.2313302516692347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3920,25 +3918,25 @@
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>17.09111861646706</v>
+        <v>17.90687778255445</v>
       </c>
       <c r="K31" t="n">
-        <v>0.1818181818181719</v>
+        <v>3.397612488521573</v>
       </c>
       <c r="L31" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M31" t="n">
-        <v>58.8235294117647</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N31" t="n">
-        <v>16.71235064055969</v>
+        <v>16.69870611185395</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>9.800362976406563</v>
+        <v>6.385435168738907</v>
       </c>
       <c r="Q31" t="n">
         <v>6</v>
@@ -3962,10 +3960,10 @@
         <v>88.88888888888889</v>
       </c>
       <c r="X31" t="n">
-        <v>56.43630133425017</v>
+        <v>56.41090041471573</v>
       </c>
       <c r="Y31" t="n">
-        <v>16.94037519576973</v>
+        <v>15.11767160987724</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -4010,7 +4008,7 @@
         <v>46282</v>
       </c>
       <c r="C32" t="n">
-        <v>2.235233692860811</v>
+        <v>2.192090395480226</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4035,19 +4033,19 @@
         <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>14.6521375640011</v>
+        <v>14.66599569135187</v>
       </c>
       <c r="K32" t="n">
-        <v>5.98232511415977</v>
+        <v>3.953589564854565</v>
       </c>
       <c r="L32" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="M32" t="n">
-        <v>53.125</v>
+        <v>59.45945945945946</v>
       </c>
       <c r="N32" t="n">
-        <v>10.93289225040109</v>
+        <v>12.05557824792131</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4077,25 +4075,25 @@
         <v>56.60377358490566</v>
       </c>
       <c r="X32" t="n">
-        <v>11.59844220999626</v>
+        <v>11.59844220999629</v>
       </c>
       <c r="Y32" t="n">
-        <v>5.032433235285295</v>
+        <v>6.850322006069121</v>
       </c>
       <c r="Z32" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="AA32" t="n">
-        <v>36.36363636363637</v>
+        <v>47.82608695652174</v>
       </c>
       <c r="AB32" t="n">
-        <v>8.974670206958006</v>
+        <v>8.332568517950866</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.124821310908121</v>
+        <v>1.234226482249123</v>
       </c>
       <c r="AE32" t="n">
         <v>26</v>
@@ -4129,7 +4127,7 @@
         <v>46282</v>
       </c>
       <c r="C33" t="n">
-        <v>1.737031330251669</v>
+        <v>1.726759116589625</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4154,19 +4152,19 @@
         <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>13.62768008519154</v>
+        <v>13.64170455604291</v>
       </c>
       <c r="K33" t="n">
-        <v>6.626767449901894</v>
+        <v>6.013426583231674</v>
       </c>
       <c r="L33" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M33" t="n">
-        <v>69.6969696969697</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N33" t="n">
-        <v>11.31155109327979</v>
+        <v>11.51903483928009</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
@@ -4238,7 +4236,7 @@
         <v>46282</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7548022598870058</v>
+        <v>0.7428864920390343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,19 +4261,19 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>17.9051929331112</v>
+        <v>17.91852285443199</v>
       </c>
       <c r="K34" t="n">
-        <v>6.617360976273146</v>
+        <v>4.951275606791095</v>
       </c>
       <c r="L34" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M34" t="n">
-        <v>70.83333333333333</v>
+        <v>60.71428571428572</v>
       </c>
       <c r="N34" t="n">
-        <v>11.63714603350821</v>
+        <v>11.86464976481211</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4308,16 +4306,16 @@
         <v>11.67247563853926</v>
       </c>
       <c r="Y34" t="n">
-        <v>4.526732870710659</v>
+        <v>6.018672007866376</v>
       </c>
       <c r="Z34" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AA34" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="AB34" t="n">
-        <v>10.34830267484583</v>
+        <v>10.82707370702024</v>
       </c>
       <c r="AC34" t="n">
         <v>2</v>
@@ -4357,7 +4355,7 @@
         <v>46282</v>
       </c>
       <c r="C35" t="n">
-        <v>1.226502311248074</v>
+        <v>1.164869029275809</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4385,7 +4383,7 @@
         <v>48.58068030402142</v>
       </c>
       <c r="K35" t="n">
-        <v>5.291005291005302</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -4396,7 +4394,7 @@
         <v>6</v>
       </c>
       <c r="P35" t="n">
-        <v>0.6733668341708521</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="Q35" t="n">
         <v>7</v>
@@ -4462,16 +4460,16 @@
         <v>46282</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0731381612737545</v>
+        <v>0.07046738572162302</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4487,25 +4485,25 @@
         <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>19.90445342722118</v>
+        <v>19.9174587240494</v>
       </c>
       <c r="K36" t="n">
-        <v>4.646081385390488</v>
+        <v>0.8411095180875572</v>
       </c>
       <c r="L36" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="M36" t="n">
-        <v>60</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N36" t="n">
-        <v>12.53972468366134</v>
+        <v>13.92140376410561</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.149224247383529</v>
       </c>
       <c r="Q36" t="n">
         <v>10</v>
@@ -4529,19 +4527,19 @@
         <v>44.44444444444444</v>
       </c>
       <c r="X36" t="n">
-        <v>10.58823174740495</v>
+        <v>10.58823174740493</v>
       </c>
       <c r="Y36" t="n">
-        <v>5.373221244360749</v>
+        <v>8.813887404928234</v>
       </c>
       <c r="Z36" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="AA36" t="n">
-        <v>37.03703703703704</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="AB36" t="n">
-        <v>11.79597455712513</v>
+        <v>13.39736841960425</v>
       </c>
       <c r="AC36" t="n">
         <v>4</v>
@@ -4581,7 +4579,7 @@
         <v>46282</v>
       </c>
       <c r="C37" t="n">
-        <v>0.05403184386235234</v>
+        <v>0.0532100667693888</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4606,25 +4604,25 @@
         <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>28.88560583600921</v>
+        <v>28.89715284260867</v>
       </c>
       <c r="K37" t="n">
-        <v>3.893202731922019</v>
+        <v>2.329693481585626</v>
       </c>
       <c r="L37" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="M37" t="n">
-        <v>68.75</v>
+        <v>68.18181818181819</v>
       </c>
       <c r="N37" t="n">
-        <v>16.92641827120465</v>
+        <v>17.00923921307097</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>5.87795650484999</v>
+        <v>7.495680146637662</v>
       </c>
       <c r="Q37" t="n">
         <v>27</v>
@@ -4690,7 +4688,7 @@
         <v>46282</v>
       </c>
       <c r="C38" t="n">
-        <v>1.583975346687211</v>
+        <v>1.563430919363123</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4715,25 +4713,25 @@
         <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>15.40679155672489</v>
+        <v>15.42052714918329</v>
       </c>
       <c r="K38" t="n">
-        <v>6.947903765125685</v>
+        <v>5.577914347654844</v>
       </c>
       <c r="L38" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M38" t="n">
-        <v>54.54545454545455</v>
+        <v>70.27027027027027</v>
       </c>
       <c r="N38" t="n">
-        <v>11.18861704017208</v>
+        <v>10.99826113622809</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>2.853815855593766</v>
+        <v>4.188457102669974</v>
       </c>
       <c r="Q38" t="n">
         <v>42</v>
@@ -4799,7 +4797,7 @@
         <v>46282</v>
       </c>
       <c r="C39" t="n">
-        <v>2.656394453004623</v>
+        <v>2.652285567539805</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4813,7 +4811,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4824,16 +4822,16 @@
         <v>10</v>
       </c>
       <c r="J39" t="n">
-        <v>15.14868902959718</v>
+        <v>15.16246653075239</v>
       </c>
       <c r="K39" t="n">
-        <v>9.699620525649832</v>
+        <v>9.54772571907354</v>
       </c>
       <c r="L39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M39" t="n">
-        <v>45.45454545454545</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="N39" t="n">
         <v>15.56291847452139</v>
@@ -4865,17 +4863,27 @@
       <c r="W39" t="n">
         <v>67.69230769230769</v>
       </c>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
+      <c r="X39" t="n">
+        <v>10.14171287727583</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.5392935543540367</v>
+      </c>
       <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>46.80851063829788</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>11.50558243321231</v>
+      </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
-      <c r="AD39" t="inlineStr"/>
+      <c r="AD39" t="n">
+        <v>5.490315362509691</v>
+      </c>
       <c r="AE39" t="n">
         <v>40</v>
       </c>
@@ -4908,16 +4916,16 @@
         <v>46282</v>
       </c>
       <c r="C40" t="n">
-        <v>0.195582948125321</v>
+        <v>0.1873651771956857</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4936,22 +4944,22 @@
         <v>29.83357657172154</v>
       </c>
       <c r="K40" t="n">
-        <v>5.777777777777771</v>
+        <v>1.33333333333332</v>
       </c>
       <c r="L40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M40" t="n">
-        <v>70</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N40" t="n">
-        <v>14.5131890624577</v>
+        <v>11.97496631083943</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.644736842105288</v>
       </c>
       <c r="Q40" t="n">
         <v>29</v>
@@ -5122,7 +5130,7 @@
         <v>46282</v>
       </c>
       <c r="C42" t="n">
-        <v>3.204930662557782</v>
+        <v>3.157678479712378</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5151,10 +5159,10 @@
         <v>10</v>
       </c>
       <c r="J42" t="n">
-        <v>21.01580383026476</v>
+        <v>21.02862867458981</v>
       </c>
       <c r="K42" t="n">
-        <v>4.919852936112434</v>
+        <v>3.38974529754168</v>
       </c>
       <c r="L42" t="n">
         <v>7</v>
@@ -5163,7 +5171,7 @@
         <v>85.71428571428571</v>
       </c>
       <c r="N42" t="n">
-        <v>13.76422757864045</v>
+        <v>15.00085957256051</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
@@ -5194,22 +5202,22 @@
         <v>11.70928208999582</v>
       </c>
       <c r="Y42" t="n">
-        <v>6.077766347485458</v>
+        <v>7.447489265709983</v>
       </c>
       <c r="Z42" t="n">
         <v>6</v>
       </c>
       <c r="AA42" t="n">
-        <v>16.66666666666667</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB42" t="n">
-        <v>9.725617469520763</v>
+        <v>10.28383030711321</v>
       </c>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.176043839657484</v>
+        <v>2.757905446366593</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -5241,7 +5249,7 @@
         <v>46282</v>
       </c>
       <c r="C43" t="n">
-        <v>5.880842321520288</v>
+        <v>5.752439650744736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5258,7 +5266,11 @@
           <t>SATMA_BEKLE</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %90.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H43" t="n">
         <v>5</v>
       </c>
@@ -5266,25 +5278,25 @@
         <v>10</v>
       </c>
       <c r="J43" t="n">
-        <v>26.62990760988233</v>
+        <v>26.64182087935456</v>
       </c>
       <c r="K43" t="n">
-        <v>6.848374095222765</v>
+        <v>4.532413329707863</v>
       </c>
       <c r="L43" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M43" t="n">
-        <v>66.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="N43" t="n">
-        <v>16.84208748274783</v>
+        <v>13.64758851004747</v>
       </c>
       <c r="O43" t="n">
         <v>10</v>
       </c>
       <c r="P43" t="n">
-        <v>2.949624579189702</v>
+        <v>5.230517976320614</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5308,19 +5320,19 @@
         <v>66.66666666666667</v>
       </c>
       <c r="X43" t="n">
-        <v>10.08403361344539</v>
+        <v>10.08403361344536</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.93926322647704</v>
+        <v>5.043074914234847</v>
       </c>
       <c r="Z43" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AA43" t="n">
-        <v>34.78260869565217</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB43" t="n">
-        <v>10.84202005888328</v>
+        <v>12.22193855346982</v>
       </c>
       <c r="AC43" t="n">
         <v>2</v>
@@ -5486,10 +5498,10 @@
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>19.70854648567448</v>
+        <v>19.70854733084767</v>
       </c>
       <c r="K45" t="n">
-        <v>2.105263157894743</v>
+        <v>2.105264232686999</v>
       </c>
       <c r="L45" t="n">
         <v>54</v>
@@ -5504,7 +5516,7 @@
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>7.731958762886593</v>
+        <v>7.731957628865982</v>
       </c>
       <c r="Q45" t="n">
         <v>38</v>
@@ -5570,7 +5582,7 @@
         <v>46282</v>
       </c>
       <c r="C46" t="n">
-        <v>8.346173600410889</v>
+        <v>8.243451463790448</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5598,22 +5610,22 @@
         <v>28.15632518747767</v>
       </c>
       <c r="K46" t="n">
-        <v>7.189973614775735</v>
+        <v>5.870712401055411</v>
       </c>
       <c r="L46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M46" t="n">
-        <v>54.54545454545455</v>
+        <v>50</v>
       </c>
       <c r="N46" t="n">
-        <v>15.98944669041125</v>
+        <v>19.97556224910608</v>
       </c>
       <c r="O46" t="n">
         <v>8</v>
       </c>
       <c r="P46" t="n">
-        <v>0.7556923076923017</v>
+        <v>2.011214953271034</v>
       </c>
       <c r="Q46" t="n">
         <v>51</v>
@@ -5679,28 +5691,24 @@
         <v>46282</v>
       </c>
       <c r="C47" t="n">
-        <v>1.01160760143811</v>
+        <v>0.9746276322547509</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>5</v>
       </c>
@@ -5708,25 +5716,25 @@
         <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>18.93988878903028</v>
+        <v>18.95305070442179</v>
       </c>
       <c r="K47" t="n">
-        <v>11.1881625271506</v>
+        <v>7.141004168378196</v>
       </c>
       <c r="L47" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M47" t="n">
-        <v>80</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N47" t="n">
-        <v>13.04145845344455</v>
+        <v>17.22084568422099</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.668442258697468</v>
       </c>
       <c r="Q47" t="n">
         <v>51</v>
@@ -5753,7 +5761,7 @@
         <v>66.65983471422588</v>
       </c>
       <c r="Y47" t="n">
-        <v>9.870751802057963</v>
+        <v>13.16548467688119</v>
       </c>
       <c r="Z47" t="n">
         <v>2</v>
@@ -5798,7 +5806,7 @@
         <v>46282</v>
       </c>
       <c r="C48" t="n">
-        <v>0.04951206985105291</v>
+        <v>0.0482794042116076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5826,22 +5834,22 @@
         <v>27.02915304173016</v>
       </c>
       <c r="K48" t="n">
-        <v>7.111111111111112</v>
+        <v>4.444444444444429</v>
       </c>
       <c r="L48" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M48" t="n">
-        <v>60</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="N48" t="n">
-        <v>13.14248535050986</v>
+        <v>13.15490657936633</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>2.69709543568466</v>
+        <v>5.319148936170248</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5907,7 +5915,7 @@
         <v>46282</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2670775552131485</v>
+        <v>0.2658448895737031</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5932,19 +5940,19 @@
         <v>10</v>
       </c>
       <c r="J49" t="n">
-        <v>18.74933396180286</v>
+        <v>18.76252681801688</v>
       </c>
       <c r="K49" t="n">
-        <v>8.001462567485129</v>
+        <v>7.520452620171314</v>
       </c>
       <c r="L49" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M49" t="n">
-        <v>57.14285714285715</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N49" t="n">
-        <v>18.09600846902872</v>
+        <v>15.07354813377234</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
@@ -5977,22 +5985,22 @@
         <v>11.47132295072795</v>
       </c>
       <c r="Y49" t="n">
-        <v>3.112782993323371</v>
+        <v>3.544293030686452</v>
       </c>
       <c r="Z49" t="n">
         <v>51</v>
       </c>
       <c r="AA49" t="n">
-        <v>37.25490196078432</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB49" t="n">
-        <v>12.00064654298627</v>
+        <v>10.40275928582287</v>
       </c>
       <c r="AC49" t="n">
         <v>10</v>
       </c>
       <c r="AD49" t="n">
-        <v>7.108488838318083</v>
+        <v>6.692923801146744</v>
       </c>
       <c r="AE49" t="n">
         <v>44</v>
@@ -6026,7 +6034,7 @@
         <v>46282</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6980996404725218</v>
+        <v>0.6808423215202877</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6051,19 +6059,19 @@
         <v>10</v>
       </c>
       <c r="J50" t="n">
-        <v>16.74217813615844</v>
+        <v>16.75569689884803</v>
       </c>
       <c r="K50" t="n">
-        <v>8.708688076499005</v>
+        <v>6.038580965396334</v>
       </c>
       <c r="L50" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="M50" t="n">
-        <v>73.68421052631579</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="N50" t="n">
-        <v>15.9882991805839</v>
+        <v>18.0425855074497</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
@@ -6135,16 +6143,16 @@
         <v>46282</v>
       </c>
       <c r="C51" t="n">
-        <v>0.11628145865434</v>
+        <v>0.1099126861838726</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6160,13 +6168,13 @@
         <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>42.62559109626197</v>
+        <v>43.5748011217725</v>
       </c>
       <c r="K51" t="n">
-        <v>4.044117647058809</v>
+        <v>1.869158894329814e-06</v>
       </c>
       <c r="L51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -6174,7 +6182,7 @@
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3.999998056074783</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6240,11 +6248,11 @@
         <v>46282</v>
       </c>
       <c r="C52" t="n">
-        <v>4.417051874678994</v>
+        <v>4.341037493579867</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6254,7 +6262,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -6265,25 +6273,25 @@
         <v>10</v>
       </c>
       <c r="J52" t="n">
-        <v>14.08979563001946</v>
+        <v>14.1037450661144</v>
       </c>
       <c r="K52" t="n">
-        <v>7.170679680869729</v>
+        <v>5.343451910685548</v>
       </c>
       <c r="L52" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M52" t="n">
-        <v>54.83870967741935</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="N52" t="n">
-        <v>13.07754061473337</v>
+        <v>13.89573997051477</v>
       </c>
       <c r="O52" t="n">
         <v>10</v>
       </c>
       <c r="P52" t="n">
-        <v>2.640013413701725</v>
+        <v>4.420348873001112</v>
       </c>
       <c r="Q52" t="n">
         <v>37</v>
@@ -6310,22 +6318,22 @@
         <v>16.53731163255363</v>
       </c>
       <c r="Y52" t="n">
-        <v>7.929450061467602</v>
+        <v>9.51391999064235</v>
       </c>
       <c r="Z52" t="n">
         <v>16</v>
       </c>
       <c r="AA52" t="n">
-        <v>62.5</v>
+        <v>68.75</v>
       </c>
       <c r="AB52" t="n">
-        <v>12.9570496400252</v>
+        <v>11.77801037928238</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.07662595539995598</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
         <v>37</v>
@@ -6359,7 +6367,7 @@
         <v>46282</v>
       </c>
       <c r="C53" t="n">
-        <v>1.065228556753981</v>
+        <v>1.009964047252183</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6384,21 +6392,25 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>40.58944447798576</v>
+        <v>42.07172100726159</v>
       </c>
       <c r="K53" t="n">
-        <v>4.325955734406417</v>
+        <v>1.444492227175664</v>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
-      </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M53" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="N53" t="n">
+        <v>28.71403390950369</v>
+      </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>3.521697203471574</v>
+        <v>6.462162340113919</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6453,10 +6465,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C54" t="n">
-        <v>0.06475192817432517</v>
+        <v>0.06471494812532101</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6481,10 +6493,10 @@
         <v>10</v>
       </c>
       <c r="J54" t="n">
-        <v>28.93741561274367</v>
+        <v>28.78472294046982</v>
       </c>
       <c r="K54" t="n">
-        <v>3.161708414986442</v>
+        <v>3.102792408311417</v>
       </c>
       <c r="L54" t="n">
         <v>19</v>
@@ -6493,13 +6505,13 @@
         <v>68.42105263157895</v>
       </c>
       <c r="N54" t="n">
-        <v>20.38177089078518</v>
+        <v>20.28852740144532</v>
       </c>
       <c r="O54" t="n">
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>6.628711069329452</v>
+        <v>6.689641890952891</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6526,7 +6538,7 @@
         <v>14.75410024187049</v>
       </c>
       <c r="Y54" t="n">
-        <v>10.10194128353622</v>
+        <v>10.15328237422565</v>
       </c>
       <c r="Z54" t="n">
         <v>21</v>
@@ -6575,7 +6587,7 @@
         <v>46282</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8982023626091423</v>
+        <v>0.8682074987159732</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6600,19 +6612,19 @@
         <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>18.55875964046422</v>
+        <v>18.57198344066605</v>
       </c>
       <c r="K55" t="n">
-        <v>10.34099253981891</v>
+        <v>6.673550121944993</v>
       </c>
       <c r="L55" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="M55" t="n">
-        <v>66.66666666666667</v>
+        <v>61.29032258064516</v>
       </c>
       <c r="N55" t="n">
-        <v>11.59043445810737</v>
+        <v>12.61308200475298</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
@@ -6645,16 +6657,16 @@
         <v>23.0932342837701</v>
       </c>
       <c r="Y55" t="n">
-        <v>10.13692705054864</v>
+        <v>13.13784394227323</v>
       </c>
       <c r="Z55" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AA55" t="n">
-        <v>42.85714285714285</v>
+        <v>14.28571428571429</v>
       </c>
       <c r="AB55" t="n">
-        <v>8.653238977710041</v>
+        <v>33.66794265572751</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6719,10 +6731,10 @@
         <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>64.67507443260313</v>
+        <v>64.6750754186144</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>2.791262221357727e-06</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
@@ -6733,7 +6745,7 @@
         <v>4</v>
       </c>
       <c r="P56" t="n">
-        <v>4.000000000000004</v>
+        <v>3.999997097087382</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -6896,7 +6908,7 @@
         <v>46282</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6927580893682589</v>
+        <v>0.6557781201848999</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6915,7 +6927,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %81.48: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6928,22 +6940,22 @@
         <v>18.04392839464337</v>
       </c>
       <c r="K58" t="n">
-        <v>6.183097637880008</v>
+        <v>0.5149607532956679</v>
       </c>
       <c r="L58" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="M58" t="n">
-        <v>77.77777777777777</v>
+        <v>81.48148148148148</v>
       </c>
       <c r="N58" t="n">
-        <v>17.97095866556823</v>
+        <v>18.38788453508219</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>1.711103181709994</v>
+        <v>7.446691706994391</v>
       </c>
       <c r="Q58" t="n">
         <v>25</v>
@@ -6970,17 +6982,13 @@
         <v>20.50322102897642</v>
       </c>
       <c r="Y58" t="n">
-        <v>11.88360217164068</v>
+        <v>16.58732447564563</v>
       </c>
       <c r="Z58" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>14.24828351986104</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
         <v>6</v>
       </c>
@@ -7019,7 +7027,7 @@
         <v>46282</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7498715973292245</v>
+        <v>0.7560349255264509</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7033,7 +7041,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -7044,19 +7052,19 @@
         <v>10</v>
       </c>
       <c r="J59" t="n">
-        <v>17.68582117154297</v>
+        <v>17.69918671275772</v>
       </c>
       <c r="K59" t="n">
-        <v>9.547013684545981</v>
+        <v>10.46533660738964</v>
       </c>
       <c r="L59" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M59" t="n">
-        <v>52.94117647058823</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="N59" t="n">
-        <v>12.358607259554</v>
+        <v>9.615778066966326</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
@@ -7085,17 +7093,27 @@
       <c r="W59" t="n">
         <v>65.51724137931035</v>
       </c>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
+      <c r="X59" t="n">
+        <v>11.6660490692541</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1.075270838247167</v>
+      </c>
       <c r="Z59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="inlineStr"/>
-      <c r="AB59" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>54</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>12.9774609813349</v>
+      </c>
       <c r="AC59" t="n">
         <v>6</v>
       </c>
-      <c r="AD59" t="inlineStr"/>
+      <c r="AD59" t="n">
+        <v>4.978258928260859</v>
+      </c>
       <c r="AE59" t="n">
         <v>42</v>
       </c>
@@ -7128,7 +7146,7 @@
         <v>46282</v>
       </c>
       <c r="C60" t="n">
-        <v>10.55983564458141</v>
+        <v>10.43656908063688</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7145,11 +7163,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>5</v>
       </c>
@@ -7157,25 +7171,25 @@
         <v>10</v>
       </c>
       <c r="J60" t="n">
-        <v>29.35895862752387</v>
+        <v>29.37042877474947</v>
       </c>
       <c r="K60" t="n">
-        <v>6.24745663520736</v>
+        <v>5.024266980845571</v>
       </c>
       <c r="L60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M60" t="n">
-        <v>80</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N60" t="n">
-        <v>10.04048277585515</v>
+        <v>11.22664512296512</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>1.649492063428748</v>
+        <v>2.833376613518435</v>
       </c>
       <c r="Q60" t="n">
         <v>46</v>
@@ -7356,21 +7370,21 @@
         <v>46282</v>
       </c>
       <c r="C62" t="n">
-        <v>8.757062146892656</v>
+        <v>8.690292758089369</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -7380,27 +7394,17 @@
       <c r="I62" t="n">
         <v>10</v>
       </c>
-      <c r="J62" t="n">
-        <v>11.08033169507211</v>
-      </c>
-      <c r="K62" t="n">
-        <v>5.381958480690674</v>
-      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
-        <v>47</v>
-      </c>
-      <c r="M62" t="n">
-        <v>65.95744680851064</v>
-      </c>
-      <c r="N62" t="n">
-        <v>13.37005229730381</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="n">
         <v>6</v>
       </c>
-      <c r="P62" t="n">
-        <v>0.5864775415258316</v>
-      </c>
+      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="n">
         <v>30</v>
       </c>
@@ -7422,17 +7426,27 @@
       <c r="W62" t="n">
         <v>72.05882352941177</v>
       </c>
-      <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
+      <c r="X62" t="n">
+        <v>12.69355362364248</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>7.185957213384531</v>
+      </c>
       <c r="Z62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="inlineStr"/>
-      <c r="AB62" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>20.54413063837905</v>
+      </c>
       <c r="AC62" t="n">
         <v>5</v>
       </c>
-      <c r="AD62" t="inlineStr"/>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
       <c r="AE62" t="n">
         <v>27</v>
       </c>
@@ -7465,16 +7479,16 @@
         <v>46282</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1006676938880329</v>
+        <v>0.0953261427837699</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7482,11 +7496,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %83.33: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>5</v>
       </c>
@@ -7494,25 +7504,25 @@
         <v>10</v>
       </c>
       <c r="J63" t="n">
-        <v>22.98070115115823</v>
+        <v>22.98070282549081</v>
       </c>
       <c r="K63" t="n">
-        <v>6.521739130434812</v>
+        <v>0.8695674102079609</v>
       </c>
       <c r="L63" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M63" t="n">
-        <v>83.33333333333333</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N63" t="n">
-        <v>11.21872105224002</v>
+        <v>13.66536901271402</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>4.094825323275897</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7578,7 +7588,7 @@
         <v>46282</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1448382126348228</v>
+        <v>0.1421674370826913</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7587,7 +7597,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7603,25 +7613,25 @@
         <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>18.11926532303334</v>
+        <v>18.13256048493127</v>
       </c>
       <c r="K64" t="n">
-        <v>6.757179204496633</v>
+        <v>4.805624634329075</v>
       </c>
       <c r="L64" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M64" t="n">
-        <v>56.66666666666666</v>
+        <v>52.5</v>
       </c>
       <c r="N64" t="n">
-        <v>13.25722701435867</v>
+        <v>13.7431377645763</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>0.185462723350116</v>
       </c>
       <c r="Q64" t="n">
         <v>55</v>
@@ -7648,16 +7658,16 @@
         <v>11.36363653581267</v>
       </c>
       <c r="Y64" t="n">
-        <v>4.136410658460033</v>
+        <v>5.888827004472564</v>
       </c>
       <c r="Z64" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="AA64" t="n">
-        <v>58.92857142857143</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="AB64" t="n">
-        <v>13.96461539681414</v>
+        <v>13.35187013801021</v>
       </c>
       <c r="AC64" t="n">
         <v>2</v>
@@ -7697,7 +7707,7 @@
         <v>46282</v>
       </c>
       <c r="C65" t="n">
-        <v>6.276322547508989</v>
+        <v>6.153055983564458</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7722,25 +7732,25 @@
         <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>15.60581693593351</v>
+        <v>15.61952021218654</v>
       </c>
       <c r="K65" t="n">
-        <v>5.46650359195715</v>
+        <v>3.411939598744995</v>
       </c>
       <c r="L65" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="M65" t="n">
-        <v>55.88235294117647</v>
+        <v>61.36363636363637</v>
       </c>
       <c r="N65" t="n">
-        <v>13.04152662096548</v>
+        <v>11.5165735319105</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>4.298517779239797</v>
+        <v>6.370696098359385</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7767,16 +7777,16 @@
         <v>24.47056390537039</v>
       </c>
       <c r="Y65" t="n">
-        <v>10.99240588733341</v>
+        <v>12.74050920869512</v>
       </c>
       <c r="Z65" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AA65" t="n">
-        <v>28.57142857142857</v>
+        <v>50</v>
       </c>
       <c r="AB65" t="n">
-        <v>14.01224876090615</v>
+        <v>15.0813486974636</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
@@ -7816,7 +7826,7 @@
         <v>46282</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4071905495634309</v>
+        <v>0.4041088854648177</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7830,7 +7840,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -7841,25 +7851,25 @@
         <v>10</v>
       </c>
       <c r="J66" t="n">
-        <v>19.89386508123355</v>
+        <v>19.90687209731571</v>
       </c>
       <c r="K66" t="n">
-        <v>4.974456004293337</v>
+        <v>4.196916148590235</v>
       </c>
       <c r="L66" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M66" t="n">
-        <v>55.17241379310344</v>
+        <v>51.51515151515152</v>
       </c>
       <c r="N66" t="n">
-        <v>15.10222239306331</v>
+        <v>15.83003245469546</v>
       </c>
       <c r="O66" t="n">
         <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>0.9769462350581071</v>
+        <v>1.730457980962208</v>
       </c>
       <c r="Q66" t="n">
         <v>35</v>
@@ -7883,25 +7893,25 @@
         <v>65.21739130434783</v>
       </c>
       <c r="X66" t="n">
-        <v>11.49973494118825</v>
+        <v>11.49973494118828</v>
       </c>
       <c r="Y66" t="n">
-        <v>5.852282016936416</v>
+        <v>6.549628836741195</v>
       </c>
       <c r="Z66" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="AA66" t="n">
-        <v>45.94594594594594</v>
+        <v>43.75</v>
       </c>
       <c r="AB66" t="n">
-        <v>10.79089929087324</v>
+        <v>11.69942193211742</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.156900226822454</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
         <v>41</v>
@@ -7935,7 +7945,7 @@
         <v>46282</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02465331278890601</v>
+        <v>0.02239342578325629</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7960,10 +7970,10 @@
         <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>18.52411411845527</v>
+        <v>24.79148995549716</v>
       </c>
       <c r="K67" t="n">
-        <v>2.564102564102577</v>
+        <v>0.92592592592593</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
@@ -7972,13 +7982,13 @@
         <v>66.66666666666667</v>
       </c>
       <c r="N67" t="n">
-        <v>14.00245556282399</v>
+        <v>10.57717221367301</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>1.400000000000001</v>
+        <v>3.045871559633029</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -8049,10 +8059,10 @@
         <v>10</v>
       </c>
       <c r="J68" t="n">
-        <v>77.33645733232144</v>
+        <v>77.33645789523086</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>2.483766303740254e-06</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -8063,7 +8073,7 @@
         <v>2</v>
       </c>
       <c r="P68" t="n">
-        <v>2.000000000000002</v>
+        <v>1.999997466558434</v>
       </c>
       <c r="Q68" t="n">
         <v>5</v>
@@ -8129,7 +8139,7 @@
         <v>46282</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4334874165382641</v>
+        <v>0.4215716486902928</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8146,7 +8156,11 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H69" t="n">
         <v>5</v>
       </c>
@@ -8154,25 +8168,25 @@
         <v>10</v>
       </c>
       <c r="J69" t="n">
-        <v>24.03271488855209</v>
+        <v>24.32773347150917</v>
       </c>
       <c r="K69" t="n">
-        <v>2.427184466019416</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M69" t="n">
-        <v>60</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="N69" t="n">
-        <v>24.40139995090738</v>
+        <v>20.61256174271245</v>
       </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>5.440758293838877</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8191,7 +8205,7 @@
         <v>45.36848923911108</v>
       </c>
       <c r="Y69" t="n">
-        <v>22.18884874507033</v>
+        <v>24.32773347150917</v>
       </c>
       <c r="Z69" t="n">
         <v>0</v>
@@ -8228,7 +8242,7 @@
         <v>46282</v>
       </c>
       <c r="C70" t="n">
-        <v>0.438828967642527</v>
+        <v>0.4330765279917822</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8245,7 +8259,11 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.95: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H70" t="n">
         <v>5</v>
       </c>
@@ -8256,22 +8274,22 @@
         <v>24.99185434120895</v>
       </c>
       <c r="K70" t="n">
-        <v>5.847373637264619</v>
+        <v>4.459861248761143</v>
       </c>
       <c r="L70" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M70" t="n">
-        <v>69.56521739130434</v>
+        <v>80.95238095238095</v>
       </c>
       <c r="N70" t="n">
-        <v>12.31109841844929</v>
+        <v>12.46017152627624</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>2.033707865168544</v>
+        <v>3.388994307400384</v>
       </c>
       <c r="Q70" t="n">
         <v>31</v>
@@ -8298,7 +8316,7 @@
         <v>44.93251946562029</v>
       </c>
       <c r="Y70" t="n">
-        <v>20.60584780615577</v>
+        <v>21.64659511955822</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -8343,7 +8361,7 @@
         <v>46282</v>
       </c>
       <c r="C71" t="n">
-        <v>3.050847457627119</v>
+        <v>3.003595274781715</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8368,19 +8386,19 @@
         <v>10</v>
       </c>
       <c r="J71" t="n">
-        <v>12.25699904489306</v>
+        <v>12.27124607635546</v>
       </c>
       <c r="K71" t="n">
-        <v>5.633587999276202</v>
+        <v>4.014401281445878</v>
       </c>
       <c r="L71" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="M71" t="n">
-        <v>61.53846153846154</v>
+        <v>54.6875</v>
       </c>
       <c r="N71" t="n">
-        <v>15.32047770277594</v>
+        <v>16.31050643755811</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
@@ -8477,10 +8495,10 @@
         <v>10</v>
       </c>
       <c r="J72" t="n">
-        <v>43.42727704859612</v>
+        <v>43.42727922447008</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>3.846153973086075e-06</v>
       </c>
       <c r="L72" t="n">
         <v>3</v>
@@ -8495,7 +8513,7 @@
         <v>10</v>
       </c>
       <c r="P72" t="n">
-        <v>10.00000000000001</v>
+        <v>9.999995769230807</v>
       </c>
       <c r="Q72" t="n">
         <v>15</v>
@@ -8561,7 +8579,7 @@
         <v>46282</v>
       </c>
       <c r="C73" t="n">
-        <v>0.05485362095531587</v>
+        <v>0.05279917822290704</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8586,25 +8604,25 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>31.26644883376827</v>
+        <v>31.26644991618639</v>
       </c>
       <c r="K73" t="n">
-        <v>5.118110236220486</v>
+        <v>1.181103955607932</v>
       </c>
       <c r="L73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M73" t="n">
-        <v>60</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="N73" t="n">
-        <v>17.85869494881592</v>
+        <v>21.67361112404349</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>4.64419475655431</v>
+        <v>8.715951595330761</v>
       </c>
       <c r="Q73" t="n">
         <v>14</v>
@@ -8695,10 +8713,10 @@
         <v>10</v>
       </c>
       <c r="J74" t="n">
-        <v>25.64684013437128</v>
+        <v>25.64684119062249</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>1.420586870359841e-06</v>
       </c>
       <c r="L74" t="n">
         <v>27</v>
@@ -8713,7 +8731,7 @@
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>8.000000000000007</v>
+        <v>7.9999984657662</v>
       </c>
       <c r="Q74" t="n">
         <v>27</v>
@@ -8779,7 +8797,7 @@
         <v>46282</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1064201335387776</v>
+        <v>0.1029275808936826</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8793,14 +8811,10 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.92: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>BAND</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>5</v>
       </c>
@@ -8808,25 +8822,25 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>20.63050282149162</v>
+        <v>21.92996714778428</v>
       </c>
       <c r="K75" t="n">
-        <v>2.313077975542965</v>
+        <v>0.6024096385542022</v>
       </c>
       <c r="L75" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M75" t="n">
-        <v>76.92307692307692</v>
+        <v>60</v>
       </c>
       <c r="N75" t="n">
-        <v>13.29337292582021</v>
+        <v>20.09443459697961</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>3.603568671190183</v>
+        <v>5.365269461077871</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8849,27 +8863,17 @@
       <c r="W75" t="n">
         <v>100</v>
       </c>
-      <c r="X75" t="n">
-        <v>11.06719281897857</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>7.881818763262871</v>
-      </c>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA75" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>10.40453534313213</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
         <v>10</v>
       </c>
-      <c r="AD75" t="n">
-        <v>2.299417127324255</v>
-      </c>
+      <c r="AD75" t="inlineStr"/>
       <c r="AE75" t="n">
         <v>4</v>
       </c>
@@ -8902,7 +8906,7 @@
         <v>46282</v>
       </c>
       <c r="C76" t="n">
-        <v>1.822290703646636</v>
+        <v>1.802773497688752</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8927,25 +8931,25 @@
         <v>10</v>
       </c>
       <c r="J76" t="n">
-        <v>16.67830837391378</v>
+        <v>16.69183750728255</v>
       </c>
       <c r="K76" t="n">
-        <v>7.714872222919444</v>
+        <v>6.578523409098258</v>
       </c>
       <c r="L76" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M76" t="n">
-        <v>61.90476190476191</v>
+        <v>52</v>
       </c>
       <c r="N76" t="n">
-        <v>13.015290494646</v>
+        <v>13.07079506901141</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>2.121459859648178</v>
+        <v>3.210287102372877</v>
       </c>
       <c r="Q76" t="n">
         <v>41</v>
@@ -8972,22 +8976,22 @@
         <v>10.81408696253991</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.796769638744701</v>
+        <v>3.822224835794985</v>
       </c>
       <c r="Z76" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AA76" t="n">
-        <v>36.95652173913044</v>
+        <v>36.11111111111111</v>
       </c>
       <c r="AB76" t="n">
-        <v>10.29901372834726</v>
+        <v>10.13713202632063</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.237850179241473</v>
+        <v>0.184840171132572</v>
       </c>
       <c r="AE76" t="n">
         <v>32</v>
@@ -9021,7 +9025,7 @@
         <v>46282</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4552645095017976</v>
+        <v>0.4466358500256805</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9046,25 +9050,25 @@
         <v>10</v>
       </c>
       <c r="J77" t="n">
-        <v>24.26276186325519</v>
+        <v>24.27505949158866</v>
       </c>
       <c r="K77" t="n">
-        <v>5.163081220833443</v>
+        <v>3.186672784832223</v>
       </c>
       <c r="L77" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M77" t="n">
-        <v>50</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N77" t="n">
-        <v>14.52266323959448</v>
+        <v>14.93209402914525</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>2.697637560855859</v>
+        <v>4.664679154065432</v>
       </c>
       <c r="Q77" t="n">
         <v>26</v>
@@ -9130,21 +9134,21 @@
         <v>46282</v>
       </c>
       <c r="C78" t="n">
-        <v>0.04971751412429379</v>
+        <v>0.0482794042116076</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -9155,25 +9159,25 @@
         <v>10</v>
       </c>
       <c r="J78" t="n">
-        <v>25.8942641091822</v>
+        <v>25.89426476209616</v>
       </c>
       <c r="K78" t="n">
-        <v>6.607929515418487</v>
+        <v>3.524229986997618</v>
       </c>
       <c r="L78" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="M78" t="n">
-        <v>50</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="N78" t="n">
-        <v>17.26382553739754</v>
+        <v>24.73030317669522</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>0.4595735829787229</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9200,7 +9204,7 @@
         <v>36.67113091579677</v>
       </c>
       <c r="Y78" t="n">
-        <v>20.99740931463477</v>
+        <v>23.28260821875691</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -9245,16 +9249,16 @@
         <v>46282</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8152028762198255</v>
+        <v>0.8057524396507447</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -9273,22 +9277,22 @@
         <v>22.50123891318462</v>
       </c>
       <c r="K79" t="n">
-        <v>5.588078765300719</v>
+        <v>4.364023416711027</v>
       </c>
       <c r="L79" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M79" t="n">
-        <v>63.1578947368421</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N79" t="n">
-        <v>9.851354600863276</v>
+        <v>10.56661665793823</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>0.6093829678735174</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9354,7 +9358,7 @@
         <v>46282</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1273754494093477</v>
+        <v>0.1265536723163842</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9379,25 +9383,25 @@
         <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>14.35356750130339</v>
+        <v>14.36747410815714</v>
       </c>
       <c r="K80" t="n">
-        <v>4.142174059407444</v>
+        <v>3.487092501040645</v>
       </c>
       <c r="L80" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="M80" t="n">
-        <v>63.1578947368421</v>
+        <v>55.22388059701493</v>
       </c>
       <c r="N80" t="n">
-        <v>15.97764254988657</v>
+        <v>15.53660303334201</v>
       </c>
       <c r="O80" t="n">
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>5.62483546507393</v>
+        <v>6.293449107089244</v>
       </c>
       <c r="Q80" t="n">
         <v>39</v>
@@ -9463,7 +9467,7 @@
         <v>46282</v>
       </c>
       <c r="C81" t="n">
-        <v>1.18130457113508</v>
+        <v>1.152542372881356</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9488,25 +9492,25 @@
         <v>10</v>
       </c>
       <c r="J81" t="n">
-        <v>11.6208936042725</v>
+        <v>11.75203263413206</v>
       </c>
       <c r="K81" t="n">
-        <v>4.962852150011821</v>
+        <v>2.559414990859232</v>
       </c>
       <c r="L81" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="M81" t="n">
-        <v>54.28571428571428</v>
+        <v>50</v>
       </c>
       <c r="N81" t="n">
-        <v>14.61042500973081</v>
+        <v>13.2556313833504</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>4.79898149374709</v>
+        <v>7.254901960784332</v>
       </c>
       <c r="Q81" t="n">
         <v>32</v>
@@ -9533,22 +9537,22 @@
         <v>23.79225853623819</v>
       </c>
       <c r="Y81" t="n">
-        <v>7.23476922235089</v>
+        <v>9.493400928241469</v>
       </c>
       <c r="Z81" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA81" t="n">
-        <v>66.66666666666667</v>
+        <v>62.5</v>
       </c>
       <c r="AB81" t="n">
-        <v>10.31224629251335</v>
+        <v>8.615772679614428</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>2.980891390522322</v>
+        <v>0.5597371649738725</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9579,10 +9583,10 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C82" t="n">
-        <v>4.664194171856571</v>
+        <v>4.719054893682589</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9607,19 +9611,19 @@
         <v>10</v>
       </c>
       <c r="J82" t="n">
-        <v>20.02831188637983</v>
+        <v>20.04129707202715</v>
       </c>
       <c r="K82" t="n">
-        <v>4.321836275862068</v>
+        <v>5.566021221854478</v>
       </c>
       <c r="L82" t="n">
         <v>5</v>
       </c>
       <c r="M82" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N82" t="n">
-        <v>10.05840616638602</v>
+        <v>8.014054265482534</v>
       </c>
       <c r="O82" t="n">
         <v>4</v>
@@ -9691,7 +9695,7 @@
         <v>46282</v>
       </c>
       <c r="C83" t="n">
-        <v>5.423728813559323</v>
+        <v>5.387776065742168</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9716,10 +9720,10 @@
         <v>10</v>
       </c>
       <c r="J83" t="n">
-        <v>17.91198638482344</v>
+        <v>17.92531520307596</v>
       </c>
       <c r="K83" t="n">
-        <v>8.490638158096164</v>
+        <v>7.78897867355961</v>
       </c>
       <c r="L83" t="n">
         <v>24</v>
@@ -9728,13 +9732,13 @@
         <v>58.33333333333334</v>
       </c>
       <c r="N83" t="n">
-        <v>10.11104878975791</v>
+        <v>10.70695472386624</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>1.391236946827012</v>
+        <v>2.051249908524055</v>
       </c>
       <c r="Q83" t="n">
         <v>41</v>
@@ -9800,7 +9804,7 @@
         <v>46282</v>
       </c>
       <c r="C84" t="n">
-        <v>2.04417051874679</v>
+        <v>2.006163328197227</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9825,19 +9829,19 @@
         <v>10</v>
       </c>
       <c r="J84" t="n">
-        <v>15.16163094199509</v>
+        <v>15.17540634174243</v>
       </c>
       <c r="K84" t="n">
-        <v>7.797479899838966</v>
+        <v>5.810385821939956</v>
       </c>
       <c r="L84" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="M84" t="n">
-        <v>58.62068965517241</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N84" t="n">
-        <v>9.320724527744272</v>
+        <v>9.644407476415203</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9867,19 +9871,19 @@
         <v>56.89655172413793</v>
       </c>
       <c r="X84" t="n">
-        <v>10.78590455284554</v>
+        <v>10.78590455284552</v>
       </c>
       <c r="Y84" t="n">
-        <v>2.697477323553432</v>
+        <v>4.49111170864901</v>
       </c>
       <c r="Z84" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="AA84" t="n">
-        <v>33.9622641509434</v>
+        <v>27.02702702702703</v>
       </c>
       <c r="AB84" t="n">
-        <v>11.1452999859144</v>
+        <v>10.27488055780199</v>
       </c>
       <c r="AC84" t="n">
         <v>2</v>
@@ -9919,7 +9923,7 @@
         <v>46282</v>
       </c>
       <c r="C85" t="n">
-        <v>5.834617360041089</v>
+        <v>5.767847971237802</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9944,19 +9948,19 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>18.97253537621143</v>
+        <v>18.98569199070202</v>
       </c>
       <c r="K85" t="n">
-        <v>9.908153580910595</v>
+        <v>8.668046502281413</v>
       </c>
       <c r="L85" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M85" t="n">
-        <v>57.14285714285715</v>
+        <v>68.18181818181819</v>
       </c>
       <c r="N85" t="n">
-        <v>13.06681422181477</v>
+        <v>13.90948768041349</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
@@ -9986,25 +9990,25 @@
         <v>57.89473684210526</v>
       </c>
       <c r="X85" t="n">
-        <v>11.51984511132624</v>
+        <v>11.51984511132622</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.445206033784174</v>
+        <v>2.557211773561885</v>
       </c>
       <c r="Z85" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="AA85" t="n">
-        <v>32.14285714285715</v>
+        <v>26.53061224489796</v>
       </c>
       <c r="AB85" t="n">
-        <v>10.80937071531154</v>
+        <v>11.386201848345</v>
       </c>
       <c r="AC85" t="n">
         <v>6</v>
       </c>
       <c r="AD85" t="n">
-        <v>4.62158539723313</v>
+        <v>3.533138048592932</v>
       </c>
       <c r="AE85" t="n">
         <v>33</v>
@@ -10038,16 +10042,16 @@
         <v>46282</v>
       </c>
       <c r="C86" t="n">
-        <v>5.049820236260914</v>
+        <v>5.213148433487417</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -10062,23 +10066,17 @@
       <c r="I86" t="n">
         <v>10</v>
       </c>
-      <c r="J86" t="n">
-        <v>18.73514495170452</v>
-      </c>
-      <c r="K86" t="n">
-        <v>21.13041213712048</v>
-      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="n">
         <v>8</v>
       </c>
-      <c r="P86" t="n">
-        <v>0</v>
-      </c>
+      <c r="P86" t="inlineStr"/>
       <c r="Q86" t="n">
         <v>52</v>
       </c>
@@ -10101,25 +10099,25 @@
         <v>70.12987012987013</v>
       </c>
       <c r="X86" t="n">
-        <v>25.31841820362353</v>
+        <v>28.97992177002235</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.563546157366125</v>
+        <v>1.264591439688723</v>
       </c>
       <c r="Z86" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AA86" t="n">
-        <v>39.39393939393939</v>
+        <v>40</v>
       </c>
       <c r="AB86" t="n">
-        <v>14.37428716199456</v>
+        <v>13.91846076202928</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>4.506921642795314</v>
+        <v>4.796059113300489</v>
       </c>
       <c r="AE86" t="n">
         <v>52</v>
@@ -10153,7 +10151,7 @@
         <v>46282</v>
       </c>
       <c r="C87" t="n">
-        <v>5.819209039548023</v>
+        <v>5.731895223420647</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10178,19 +10176,19 @@
         <v>10</v>
       </c>
       <c r="J87" t="n">
-        <v>13.35930117963161</v>
+        <v>13.37336922777884</v>
       </c>
       <c r="K87" t="n">
-        <v>8.880090365493265</v>
+        <v>7.263825187625939</v>
       </c>
       <c r="L87" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="M87" t="n">
-        <v>56.25</v>
+        <v>65</v>
       </c>
       <c r="N87" t="n">
-        <v>10.66774603943682</v>
+        <v>11.33733408847504</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10223,16 +10221,16 @@
         <v>15.88967756874082</v>
       </c>
       <c r="Y87" t="n">
-        <v>5.66552883108804</v>
+        <v>7.080962202554519</v>
       </c>
       <c r="Z87" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="AA87" t="n">
-        <v>48.57142857142857</v>
+        <v>53.57142857142857</v>
       </c>
       <c r="AB87" t="n">
-        <v>12.87565806722536</v>
+        <v>12.50709394467145</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
@@ -10272,7 +10270,7 @@
         <v>46282</v>
       </c>
       <c r="C88" t="n">
-        <v>1.015305598356446</v>
+        <v>0.9873651771956857</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10286,7 +10284,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SATMA_BEKLE</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -10297,19 +10295,19 @@
         <v>10</v>
       </c>
       <c r="J88" t="n">
-        <v>21.40220888346344</v>
+        <v>21.41497098631751</v>
       </c>
       <c r="K88" t="n">
-        <v>8.031003390109515</v>
+        <v>5.075135408064702</v>
       </c>
       <c r="L88" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="M88" t="n">
-        <v>65.38461538461539</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N88" t="n">
-        <v>12.82925226559228</v>
+        <v>13.97762866645933</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
@@ -10342,22 +10340,22 @@
         <v>12.09536008844403</v>
       </c>
       <c r="Y88" t="n">
-        <v>3.625802794270616</v>
+        <v>6.262725481982779</v>
       </c>
       <c r="Z88" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="AA88" t="n">
-        <v>37.70491803278689</v>
+        <v>37.5</v>
       </c>
       <c r="AB88" t="n">
-        <v>12.03512072489898</v>
+        <v>11.21667741778429</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>2.463519567028094</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
         <v>33</v>
@@ -10391,16 +10389,16 @@
         <v>46282</v>
       </c>
       <c r="C89" t="n">
-        <v>2.103749357986646</v>
+        <v>2.045197740112994</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -10416,25 +10414,25 @@
         <v>10</v>
       </c>
       <c r="J89" t="n">
-        <v>15.59057935301659</v>
+        <v>15.60428510343075</v>
       </c>
       <c r="K89" t="n">
-        <v>6.43943565168863</v>
+        <v>3.493814479426294</v>
       </c>
       <c r="L89" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="M89" t="n">
-        <v>71.05263157894737</v>
+        <v>66.10169491525424</v>
       </c>
       <c r="N89" t="n">
-        <v>18.27058283257839</v>
+        <v>15.49634425848416</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>0.4890973659825271</v>
       </c>
       <c r="Q89" t="n">
         <v>45</v>
@@ -10461,16 +10459,16 @@
         <v>21.41032003314154</v>
       </c>
       <c r="Y89" t="n">
-        <v>10.1550890264909</v>
+        <v>12.65565539635908</v>
       </c>
       <c r="Z89" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="AA89" t="n">
-        <v>39.1304347826087</v>
+        <v>40</v>
       </c>
       <c r="AB89" t="n">
-        <v>17.94417613395044</v>
+        <v>20.63598439723828</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
@@ -10510,7 +10508,7 @@
         <v>46282</v>
       </c>
       <c r="C90" t="n">
-        <v>2.66050333846944</v>
+        <v>2.578325629173087</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10535,25 +10533,25 @@
         <v>10</v>
       </c>
       <c r="J90" t="n">
-        <v>19.79209967053214</v>
+        <v>19.80512321049643</v>
       </c>
       <c r="K90" t="n">
-        <v>6.173946250946938</v>
+        <v>2.911152038440079</v>
       </c>
       <c r="L90" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="M90" t="n">
-        <v>72.72727272727273</v>
+        <v>70.73170731707317</v>
       </c>
       <c r="N90" t="n">
-        <v>17.26814489631478</v>
+        <v>15.84628685195545</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>1.719869905501215</v>
+        <v>4.944894562699198</v>
       </c>
       <c r="Q90" t="n">
         <v>43</v>
@@ -10619,16 +10617,16 @@
         <v>46282</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2245505906522856</v>
+        <v>0.220236260914227</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10644,25 +10642,25 @@
         <v>10</v>
       </c>
       <c r="J91" t="n">
-        <v>13.46864548496864</v>
+        <v>13.48269577863128</v>
       </c>
       <c r="K91" t="n">
-        <v>7.306065881522317</v>
+        <v>5.261467231019679</v>
       </c>
       <c r="L91" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M91" t="n">
-        <v>72.72727272727273</v>
+        <v>69.23076923076923</v>
       </c>
       <c r="N91" t="n">
-        <v>13.74271301446917</v>
+        <v>13.8624981041094</v>
       </c>
       <c r="O91" t="n">
         <v>6</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>0.7016173994225827</v>
       </c>
       <c r="Q91" t="n">
         <v>44</v>
@@ -10686,25 +10684,25 @@
         <v>66.25</v>
       </c>
       <c r="X91" t="n">
-        <v>10.31433396881691</v>
+        <v>10.31433396881694</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.726996555266314</v>
+        <v>4.580426274635863</v>
       </c>
       <c r="Z91" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="AA91" t="n">
-        <v>31.11111111111111</v>
+        <v>39.28571428571428</v>
       </c>
       <c r="AB91" t="n">
-        <v>12.47955093451849</v>
+        <v>14.17133284229286</v>
       </c>
       <c r="AC91" t="n">
         <v>5</v>
       </c>
       <c r="AD91" t="n">
-        <v>2.336725878958912</v>
+        <v>0.4397145250006673</v>
       </c>
       <c r="AE91" t="n">
         <v>39</v>
@@ -10738,7 +10736,7 @@
         <v>46282</v>
       </c>
       <c r="C92" t="n">
-        <v>1.080636877247047</v>
+        <v>1.062146892655367</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10766,22 +10764,22 @@
         <v>19.02065273936991</v>
       </c>
       <c r="K92" t="n">
-        <v>6.564019448946534</v>
+        <v>4.740680713128054</v>
       </c>
       <c r="L92" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M92" t="n">
-        <v>65</v>
+        <v>62.5</v>
       </c>
       <c r="N92" t="n">
-        <v>14.49553492530685</v>
+        <v>12.63039748365475</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>1.347528517110264</v>
+        <v>3.111798839458402</v>
       </c>
       <c r="Q92" t="n">
         <v>44</v>
@@ -10847,7 +10845,7 @@
         <v>46282</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0396507447354905</v>
+        <v>0.03882896764252697</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10872,25 +10870,25 @@
         <v>10</v>
       </c>
       <c r="J93" t="n">
-        <v>13.47423660146673</v>
+        <v>13.488285987287</v>
       </c>
       <c r="K93" t="n">
-        <v>4.264743216516309</v>
+        <v>2.120397418129549</v>
       </c>
       <c r="L93" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="M93" t="n">
-        <v>64.15094339622641</v>
+        <v>57.57575757575758</v>
       </c>
       <c r="N93" t="n">
-        <v>18.74669448162565</v>
+        <v>18.39462105831583</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>1.664279534914548</v>
+        <v>3.799047673096601</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10956,7 +10954,7 @@
         <v>46282</v>
       </c>
       <c r="C94" t="n">
-        <v>8.479712378017464</v>
+        <v>8.438623523369287</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10981,19 +10979,19 @@
         <v>10</v>
       </c>
       <c r="J94" t="n">
-        <v>10.46076573384858</v>
+        <v>10.47530442381612</v>
       </c>
       <c r="K94" t="n">
-        <v>8.556388698591633</v>
+        <v>8.04791747700917</v>
       </c>
       <c r="L94" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M94" t="n">
-        <v>58.8235294117647</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="N94" t="n">
-        <v>13.67467251595421</v>
+        <v>14.1134274536275</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
@@ -11026,22 +11024,22 @@
         <v>30.64601732980787</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.799440812294107</v>
+        <v>3.270430802301161</v>
       </c>
       <c r="Z94" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA94" t="n">
-        <v>33.33333333333334</v>
+        <v>31.25</v>
       </c>
       <c r="AB94" t="n">
-        <v>12.16646182899771</v>
+        <v>12.16124896923941</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>3.292737422966097</v>
+        <v>2.821856047058446</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -11072,10 +11070,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1105921808385281</v>
+        <v>0.1088854687211094</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11100,25 +11098,25 @@
         <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>27.09923625361518</v>
+        <v>27.27834334389649</v>
       </c>
       <c r="K95" t="n">
-        <v>1.509432398718458</v>
+        <v>0.1890402660797097</v>
       </c>
       <c r="L95" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M95" t="n">
-        <v>40</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="N95" t="n">
-        <v>13.50348863394128</v>
+        <v>12.09171874021741</v>
       </c>
       <c r="O95" t="n">
         <v>10</v>
       </c>
       <c r="P95" t="n">
-        <v>8.364313936789136</v>
+        <v>9.792448064044311</v>
       </c>
       <c r="Q95" t="n">
         <v>21</v>
@@ -11184,7 +11182,7 @@
         <v>46282</v>
       </c>
       <c r="C96" t="n">
-        <v>0.125115562403698</v>
+        <v>0.1210066769388803</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11209,25 +11207,25 @@
         <v>10</v>
       </c>
       <c r="J96" t="n">
-        <v>11.73755470133672</v>
+        <v>11.75188607616355</v>
       </c>
       <c r="K96" t="n">
-        <v>5.303144617760203</v>
+        <v>1.861452744147951</v>
       </c>
       <c r="L96" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="M96" t="n">
-        <v>60</v>
+        <v>54.92957746478874</v>
       </c>
       <c r="N96" t="n">
-        <v>14.83656468726668</v>
+        <v>13.14156559941216</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>4.460318254776641</v>
+        <v>7.989820522483781</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11293,7 +11291,7 @@
         <v>46282</v>
       </c>
       <c r="C97" t="n">
-        <v>1.798664612223934</v>
+        <v>1.784283513097072</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11318,19 +11316,19 @@
         <v>10</v>
       </c>
       <c r="J97" t="n">
-        <v>19.38147879065393</v>
+        <v>19.39456900406833</v>
       </c>
       <c r="K97" t="n">
-        <v>6.253796623444763</v>
+        <v>5.421369213188809</v>
       </c>
       <c r="L97" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M97" t="n">
-        <v>47.61904761904762</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="N97" t="n">
-        <v>10.2405732777383</v>
+        <v>11.70571747402433</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11402,7 +11400,7 @@
         <v>46282</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6722136620441705</v>
+        <v>0.668104776579353</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11427,25 +11425,25 @@
         <v>10</v>
       </c>
       <c r="J98" t="n">
-        <v>19.99619012483309</v>
+        <v>20.0091805261642</v>
       </c>
       <c r="K98" t="n">
-        <v>7.217421296407256</v>
+        <v>6.579363620237966</v>
       </c>
       <c r="L98" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M98" t="n">
-        <v>64.70588235294117</v>
+        <v>52.38095238095238</v>
       </c>
       <c r="N98" t="n">
-        <v>17.72021339555821</v>
+        <v>16.88825880427897</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>2.595267326846251</v>
+        <v>3.209473451117995</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11472,10 +11470,10 @@
         <v>30.85778357900837</v>
       </c>
       <c r="Y98" t="n">
-        <v>14.22197811296562</v>
+        <v>14.74629365017242</v>
       </c>
       <c r="Z98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA98" t="inlineStr"/>
       <c r="AB98" t="inlineStr"/>
@@ -11517,21 +11515,21 @@
         <v>46282</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4955315870570108</v>
+        <v>0.4897791474062661</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -11542,25 +11540,25 @@
         <v>10</v>
       </c>
       <c r="J99" t="n">
-        <v>18.75931989311172</v>
+        <v>18.77251112788727</v>
       </c>
       <c r="K99" t="n">
-        <v>4.085600782067633</v>
+        <v>2.894017362325263</v>
       </c>
       <c r="L99" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="M99" t="n">
-        <v>57.5</v>
+        <v>49.01960784313726</v>
       </c>
       <c r="N99" t="n">
-        <v>16.56472255328778</v>
+        <v>17.37652325273918</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>1.07487555256025</v>
       </c>
       <c r="Q99" t="n">
         <v>34</v>
@@ -11587,7 +11585,7 @@
         <v>33.04241514445872</v>
       </c>
       <c r="Y99" t="n">
-        <v>15.44015003130763</v>
+        <v>16.42177349694751</v>
       </c>
       <c r="Z99" t="n">
         <v>0</v>
@@ -11629,24 +11627,24 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C100" t="n">
-        <v>311.4240835373241</v>
+        <v>330.0242360041089</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -11657,25 +11655,25 @@
         <v>10</v>
       </c>
       <c r="J100" t="n">
-        <v>16.72959296859361</v>
+        <v>16.74333965049621</v>
       </c>
       <c r="K100" t="n">
-        <v>2.653906669425155</v>
+        <v>8.802988034743686</v>
       </c>
       <c r="L100" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="M100" t="n">
-        <v>43.58974358974359</v>
+        <v>50</v>
       </c>
       <c r="N100" t="n">
-        <v>12.95131148290171</v>
+        <v>11.99209827934179</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
       </c>
       <c r="P100" t="n">
-        <v>2.285439888936658</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>48</v>
@@ -11698,17 +11696,27 @@
       <c r="W100" t="n">
         <v>64.91228070175438</v>
       </c>
-      <c r="X100" t="inlineStr"/>
-      <c r="Y100" t="inlineStr"/>
+      <c r="X100" t="n">
+        <v>10.05542668049453</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>1.138007169230137</v>
+      </c>
       <c r="Z100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA100" t="inlineStr"/>
-      <c r="AB100" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>36.17021276595744</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>11.74090739478531</v>
+      </c>
       <c r="AC100" t="n">
         <v>8</v>
       </c>
-      <c r="AD100" t="inlineStr"/>
+      <c r="AD100" t="n">
+        <v>6.940981700132321</v>
+      </c>
       <c r="AE100" t="n">
         <v>39</v>
       </c>
@@ -11741,7 +11749,7 @@
         <v>46282</v>
       </c>
       <c r="C101" t="n">
-        <v>333.628145865434</v>
+        <v>329.6686183872625</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11766,19 +11774,19 @@
         <v>10</v>
       </c>
       <c r="J101" t="n">
-        <v>12.85585896914321</v>
+        <v>12.87023644471203</v>
       </c>
       <c r="K101" t="n">
-        <v>5.924952246312443</v>
+        <v>4.685097289186735</v>
       </c>
       <c r="L101" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="M101" t="n">
-        <v>58.33333333333334</v>
+        <v>48.27586206896552</v>
       </c>
       <c r="N101" t="n">
-        <v>8.711895906939038</v>
+        <v>8.71415599283568</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11847,10 +11855,10 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C102" t="n">
-        <v>376.699348790948</v>
+        <v>374.8638931689779</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11875,25 +11883,25 @@
         <v>10</v>
       </c>
       <c r="J102" t="n">
-        <v>13.66723461151199</v>
+        <v>13.70795483068423</v>
       </c>
       <c r="K102" t="n">
-        <v>2.359097070931426</v>
+        <v>1.908422343954985</v>
       </c>
       <c r="L102" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M102" t="n">
-        <v>53.125</v>
+        <v>54.28571428571428</v>
       </c>
       <c r="N102" t="n">
-        <v>10.62899496630217</v>
+        <v>11.41903029479795</v>
       </c>
       <c r="O102" t="n">
         <v>4</v>
       </c>
       <c r="P102" t="n">
-        <v>1.603084607058891</v>
+        <v>2.052409023648361</v>
       </c>
       <c r="Q102" t="n">
         <v>29</v>
@@ -11959,16 +11967,16 @@
         <v>46282</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7116589625064201</v>
+        <v>0.7042629686697484</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -11984,25 +11992,25 @@
         <v>10</v>
       </c>
       <c r="J103" t="n">
-        <v>18.79092323718417</v>
+        <v>18.80410934045254</v>
       </c>
       <c r="K103" t="n">
-        <v>10.89115228041664</v>
+        <v>9.756525233285007</v>
       </c>
       <c r="L103" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M103" t="n">
-        <v>70.58823529411765</v>
+        <v>56.25</v>
       </c>
       <c r="N103" t="n">
-        <v>18.86051193733509</v>
+        <v>20.79805992900338</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>0.2218317008464865</v>
       </c>
       <c r="Q103" t="n">
         <v>43</v>
@@ -12029,22 +12037,22 @@
         <v>11.33888240947563</v>
       </c>
       <c r="Y103" t="n">
-        <v>0.4021327674301189</v>
+        <v>1.421208064915813</v>
       </c>
       <c r="Z103" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA103" t="n">
-        <v>38.18181818181818</v>
+        <v>32.14285714285715</v>
       </c>
       <c r="AB103" t="n">
-        <v>11.17863579793928</v>
+        <v>11.39555378317706</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>7.628544108106428</v>
+        <v>6.673638219685662</v>
       </c>
       <c r="AE103" t="n">
         <v>32</v>
@@ -12078,7 +12086,7 @@
         <v>46282</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0519774011299435</v>
+        <v>0.05053929121725732</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12106,16 +12114,16 @@
         <v>11.61049328507885</v>
       </c>
       <c r="K104" t="n">
-        <v>7.142170145591331</v>
+        <v>4.194680604211687</v>
       </c>
       <c r="L104" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="M104" t="n">
-        <v>57.14285714285715</v>
+        <v>55</v>
       </c>
       <c r="N104" t="n">
-        <v>13.23547020137772</v>
+        <v>14.67097486046199</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
@@ -12145,19 +12153,19 @@
         <v>63.23529411764706</v>
       </c>
       <c r="X104" t="n">
-        <v>17.91678067456379</v>
+        <v>17.89763425757407</v>
       </c>
       <c r="Y104" t="n">
-        <v>5.297564324650317</v>
+        <v>7.902835790749663</v>
       </c>
       <c r="Z104" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="AA104" t="n">
-        <v>45.16129032258065</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="AB104" t="n">
-        <v>15.04730035498116</v>
+        <v>14.03021068267866</v>
       </c>
       <c r="AC104" t="n">
         <v>5</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -670,7 +670,7 @@
         <v>46282</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3802773497688752</v>
+        <v>0.3923985618900874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,22 +698,22 @@
         <v>22.3316078451137</v>
       </c>
       <c r="K2" t="n">
-        <v>4.710996456505301</v>
+        <v>8.048624112331249</v>
       </c>
       <c r="L2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="N2" t="n">
-        <v>12.34147749132199</v>
+        <v>13.29782535914281</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>5.051048812902525</v>
+        <v>1.806016415017031</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -898,7 +898,7 @@
         <v>46282</v>
       </c>
       <c r="C4" t="n">
-        <v>1.420647149460709</v>
+        <v>1.473035439137134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,7 +915,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>5</v>
       </c>
@@ -926,16 +930,16 @@
         <v>18.01811637499802</v>
       </c>
       <c r="K4" t="n">
-        <v>10.06645300474955</v>
+        <v>14.1253026817143</v>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>53.84615384615385</v>
+        <v>80</v>
       </c>
       <c r="N4" t="n">
-        <v>12.11791814276196</v>
+        <v>18.60812358619205</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -965,25 +969,25 @@
         <v>62.5</v>
       </c>
       <c r="X4" t="n">
-        <v>11.57857347263838</v>
+        <v>14.1253026817143</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.355206847360912</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA4" t="n">
-        <v>44.26229508196721</v>
+        <v>43.54838709677419</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.80972660017727</v>
+        <v>11.69249888820733</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>8.763557483731022</v>
+        <v>9.999999999999998</v>
       </c>
       <c r="AE4" t="n">
         <v>39</v>
@@ -1017,7 +1021,7 @@
         <v>46282</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2214689265536723</v>
+        <v>0.2278376990241397</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,11 +1038,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>5</v>
       </c>
@@ -1049,16 +1049,16 @@
         <v>21.7133291595898</v>
       </c>
       <c r="K5" t="n">
-        <v>5.746747857827406</v>
+        <v>8.78770257359054</v>
       </c>
       <c r="L5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M5" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="N5" t="n">
-        <v>10.94964894035436</v>
+        <v>12.04334207013304</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -1130,7 +1130,7 @@
         <v>46282</v>
       </c>
       <c r="C6" t="n">
-        <v>1.388803287108372</v>
+        <v>1.410374935798665</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,10 +1158,10 @@
         <v>38.01799643637762</v>
       </c>
       <c r="K6" t="n">
-        <v>10.54783319705641</v>
+        <v>12.26492232215863</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1235,7 +1235,7 @@
         <v>46282</v>
       </c>
       <c r="C7" t="n">
-        <v>2.192090395480226</v>
+        <v>2.241397021058038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,22 +1263,22 @@
         <v>15.68018152056624</v>
       </c>
       <c r="K7" t="n">
-        <v>5.080178623695453</v>
+        <v>7.443744028539578</v>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="M7" t="n">
-        <v>63.1578947368421</v>
+        <v>70.37037037037037</v>
       </c>
       <c r="N7" t="n">
-        <v>13.3800083599176</v>
+        <v>13.57832933825642</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.778660461513649</v>
+        <v>0.5177183432035548</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1305,7 +1305,7 @@
         <v>18.9234494530097</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.39658412663525</v>
+        <v>9.403630067627978</v>
       </c>
       <c r="Z7" t="n">
         <v>15</v>
@@ -1314,7 +1314,7 @@
         <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.48364838038053</v>
+        <v>13.12838423287637</v>
       </c>
       <c r="AC7" t="n">
         <v>5</v>
@@ -1354,7 +1354,7 @@
         <v>46282</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2997431946584489</v>
+        <v>0.3009758602978942</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>30.96043286594978</v>
       </c>
       <c r="K8" t="n">
-        <v>5.724637681159406</v>
+        <v>6.159420289855078</v>
       </c>
       <c r="L8" t="n">
         <v>4</v>
@@ -1397,7 +1397,7 @@
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.152159013022636</v>
+        <v>1.733788395904434</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1463,7 +1463,7 @@
         <v>46282</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5325115562403698</v>
+        <v>0.5427837699024141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,16 +1491,16 @@
         <v>17.6457098380072</v>
       </c>
       <c r="K9" t="n">
-        <v>3.970320564707586</v>
+        <v>5.975920884242858</v>
       </c>
       <c r="L9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M9" t="n">
-        <v>58.33333333333334</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N9" t="n">
-        <v>14.08200345625803</v>
+        <v>9.341279069049643</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1572,7 +1572,7 @@
         <v>46282</v>
       </c>
       <c r="C10" t="n">
-        <v>1.803800719054956</v>
+        <v>1.844889573703133</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,22 +1600,22 @@
         <v>15.9903344514868</v>
       </c>
       <c r="K10" t="n">
-        <v>3.434424465530683</v>
+        <v>5.790561697091734</v>
       </c>
       <c r="L10" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M10" t="n">
-        <v>56.09756097560975</v>
+        <v>51.51515151515152</v>
       </c>
       <c r="N10" t="n">
-        <v>10.69370433130505</v>
+        <v>9.876644813116769</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>6.347572936568424</v>
+        <v>3.979030109473358</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1681,7 +1681,7 @@
         <v>46282</v>
       </c>
       <c r="C11" t="n">
-        <v>7.591165896250643</v>
+        <v>7.80688238315357</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1709,16 +1709,16 @@
         <v>16.80962533618998</v>
       </c>
       <c r="K11" t="n">
-        <v>6.287467427608617</v>
+        <v>9.307814945849181</v>
       </c>
       <c r="L11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="M11" t="n">
-        <v>71.05263157894737</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="N11" t="n">
-        <v>12.55504624302741</v>
+        <v>11.76712508191444</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1747,17 +1747,27 @@
       <c r="W11" t="n">
         <v>61.19402985074627</v>
       </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
+      <c r="X11" t="n">
+        <v>10.2426844157808</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.8480104370515384</v>
+      </c>
       <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>45.09803921568628</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>10.75629325911953</v>
+      </c>
       <c r="AC11" t="n">
         <v>2</v>
       </c>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>1.161842105263156</v>
+      </c>
       <c r="AE11" t="n">
         <v>48</v>
       </c>
@@ -1790,7 +1800,7 @@
         <v>46282</v>
       </c>
       <c r="C12" t="n">
-        <v>5.192604006163329</v>
+        <v>5.279917822290704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,16 +1832,16 @@
         <v>33.96593120498892</v>
       </c>
       <c r="K12" t="n">
-        <v>5.797407473269933</v>
+        <v>7.576394542553411</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="n">
-        <v>11.3182983278354</v>
+        <v>10.57818638012683</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
@@ -1903,7 +1913,7 @@
         <v>46282</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1397021058038007</v>
+        <v>0.1438109912686184</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,10 +1938,10 @@
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>54.16324215371029</v>
+        <v>54.5022714277213</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5917159763313418</v>
+        <v>4.321907600596142</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1942,7 +1952,7 @@
         <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>5.376470588235316</v>
+        <v>1.608571428571426</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1996,7 +2006,7 @@
         <v>46282</v>
       </c>
       <c r="C14" t="n">
-        <v>8.551617873651772</v>
+        <v>8.618387262455059</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,16 +2034,16 @@
         <v>10.97257403209156</v>
       </c>
       <c r="K14" t="n">
-        <v>6.687137955434386</v>
+        <v>7.520130624155508</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M14" t="n">
-        <v>53.84615384615385</v>
+        <v>44</v>
       </c>
       <c r="N14" t="n">
-        <v>9.921811465743719</v>
+        <v>11.74722695280736</v>
       </c>
       <c r="O14" t="n">
         <v>2</v>
@@ -2066,16 +2076,16 @@
         <v>16.11612055393703</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.01918723944531</v>
+        <v>4.277595307981519</v>
       </c>
       <c r="Z14" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AA14" t="n">
-        <v>33.33333333333334</v>
+        <v>37.03703703703704</v>
       </c>
       <c r="AB14" t="n">
-        <v>13.3466841859654</v>
+        <v>12.83608271177326</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2115,21 +2125,21 @@
         <v>46282</v>
       </c>
       <c r="C15" t="n">
-        <v>12.9532614278377</v>
+        <v>13.60041088854648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -2143,22 +2153,22 @@
         <v>20.43038307058605</v>
       </c>
       <c r="K15" t="n">
-        <v>2.980760319344999</v>
+        <v>8.125715037916571</v>
       </c>
       <c r="L15" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="M15" t="n">
-        <v>60.52631578947368</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N15" t="n">
-        <v>15.35380440396754</v>
+        <v>17.52537808654624</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>4.873958655083022</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2185,13 +2195,17 @@
         <v>33.58229315482664</v>
       </c>
       <c r="Y15" t="n">
-        <v>18.05860350289925</v>
+        <v>13.96478274214005</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>10.69899700373172</v>
+      </c>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
@@ -2230,7 +2244,7 @@
         <v>46282</v>
       </c>
       <c r="C16" t="n">
-        <v>32.23420647149461</v>
+        <v>33.24088341037493</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,11 +2261,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.26: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>5</v>
       </c>
@@ -2259,25 +2269,25 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>20.72099231313619</v>
+        <v>20.85493449406155</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4714027333827753</v>
+        <v>3.784477228992933</v>
       </c>
       <c r="L16" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M16" t="n">
-        <v>78.26086956521739</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N16" t="n">
-        <v>15.39875477097618</v>
+        <v>14.98778431551972</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>9.483889950161162</v>
+        <v>5.988875154511764</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2448,7 +2458,7 @@
         <v>46282</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06368772470467386</v>
+        <v>0.0632768361581921</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,13 +2486,13 @@
         <v>41.94120981718441</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3102320360749</v>
+        <v>1.650166022938948</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>66.66666666666667</v>
+        <v>40</v>
       </c>
       <c r="N18" t="n">
         <v>12.28395657351243</v>
@@ -2491,7 +2501,7 @@
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>7.516127967741948</v>
+        <v>8.214284642857139</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2557,7 +2567,7 @@
         <v>46282</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02629686697483308</v>
+        <v>0.02588597842835131</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,22 +2595,22 @@
         <v>16.0945098434464</v>
       </c>
       <c r="K19" t="n">
-        <v>5.741875773460658</v>
+        <v>4.089658964500331</v>
       </c>
       <c r="L19" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M19" t="n">
-        <v>57.89473684210526</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="N19" t="n">
-        <v>20.50431033269351</v>
+        <v>22.95620354700146</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>4.026904379549578</v>
+        <v>5.678125083986862</v>
       </c>
       <c r="Q19" t="n">
         <v>14</v>
@@ -2627,16 +2637,16 @@
         <v>20.26411217973316</v>
       </c>
       <c r="Y19" t="n">
-        <v>11.27676083154384</v>
+        <v>12.66306144355097</v>
       </c>
       <c r="Z19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>16.74028578011673</v>
+        <v>17.32542942283422</v>
       </c>
       <c r="AC19" t="n">
         <v>10</v>
@@ -2676,7 +2686,7 @@
         <v>46282</v>
       </c>
       <c r="C20" t="n">
-        <v>1.581920903954802</v>
+        <v>1.652799178222907</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2704,22 +2714,22 @@
         <v>19.82174384694231</v>
       </c>
       <c r="K20" t="n">
-        <v>3.174965373200389</v>
+        <v>7.797739795765857</v>
       </c>
       <c r="L20" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="M20" t="n">
-        <v>52</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N20" t="n">
-        <v>14.50842908359004</v>
+        <v>9.77179969240437</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>6.615010339099592</v>
+        <v>2.042955824868464</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
@@ -2785,11 +2795,11 @@
         <v>46282</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8386235233692861</v>
+        <v>0.8645095017976374</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2799,7 +2809,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2813,22 +2823,22 @@
         <v>17.90453399434356</v>
       </c>
       <c r="K21" t="n">
-        <v>3.509169910838761</v>
+        <v>6.704210432339419</v>
       </c>
       <c r="L21" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M21" t="n">
-        <v>58.53658536585366</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="N21" t="n">
-        <v>15.24784620041386</v>
+        <v>21.10628509391671</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>4.3385818792959</v>
+        <v>1.214375292605951</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2855,22 +2865,22 @@
         <v>11.00964066838261</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.756594033080332</v>
+        <v>3.878429125723182</v>
       </c>
       <c r="Z21" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AA21" t="n">
-        <v>43.47826086956522</v>
+        <v>35</v>
       </c>
       <c r="AB21" t="n">
-        <v>11.9748699679329</v>
+        <v>11.57440181663743</v>
       </c>
       <c r="AC21" t="n">
         <v>4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>0.126476162604372</v>
       </c>
       <c r="AE21" t="n">
         <v>40</v>
@@ -2904,7 +2914,7 @@
         <v>46282</v>
       </c>
       <c r="C22" t="n">
-        <v>0.289060092449923</v>
+        <v>0.2886492039034412</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2936,7 +2946,7 @@
         <v>26.84577757624037</v>
       </c>
       <c r="K22" t="n">
-        <v>7.689492851388535</v>
+        <v>7.536416102488208</v>
       </c>
       <c r="L22" t="n">
         <v>7</v>
@@ -2951,7 +2961,7 @@
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>2.145527003084657</v>
+        <v>2.290929888498305</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -2978,7 +2988,7 @@
         <v>10.71975172264199</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.736872892240927</v>
+        <v>2.875128936459481</v>
       </c>
       <c r="Z22" t="n">
         <v>26</v>
@@ -2993,7 +3003,7 @@
         <v>5</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.326808910073119</v>
+        <v>2.187772339126604</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3019,7 +3029,7 @@
         <v>46282</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5111453518233179</v>
+        <v>0.5082691319979455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3044,10 +3054,10 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>49.65802523708145</v>
+        <v>49.78021309444885</v>
       </c>
       <c r="K23" t="n">
-        <v>0.64725200026714</v>
+        <v>0.3244120032441122</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3058,7 +3068,7 @@
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.32475593046624</v>
+        <v>4.660468876313684</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3229,7 +3239,7 @@
         <v>46282</v>
       </c>
       <c r="C25" t="n">
-        <v>3.192604006163328</v>
+        <v>3.235747303543914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,11 +3256,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>5</v>
       </c>
@@ -3261,22 +3267,22 @@
         <v>26.01552790938969</v>
       </c>
       <c r="K25" t="n">
-        <v>3.834536450003867</v>
+        <v>5.237705861490394</v>
       </c>
       <c r="L25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M25" t="n">
-        <v>80</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N25" t="n">
-        <v>12.75293965107267</v>
+        <v>13.45008776986097</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>4.01163590883058</v>
+        <v>2.624814096712869</v>
       </c>
       <c r="Q25" t="n">
         <v>44</v>
@@ -3342,7 +3348,7 @@
         <v>46282</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4219825372367745</v>
+        <v>0.4302003081664099</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3370,22 +3376,22 @@
         <v>13.95841889083065</v>
       </c>
       <c r="K26" t="n">
-        <v>2.966914508090568</v>
+        <v>4.972112453720401</v>
       </c>
       <c r="L26" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M26" t="n">
-        <v>44.64285714285715</v>
+        <v>45.65217391304348</v>
       </c>
       <c r="N26" t="n">
-        <v>14.45547397671901</v>
+        <v>14.09959491208586</v>
       </c>
       <c r="O26" t="n">
         <v>6</v>
       </c>
       <c r="P26" t="n">
-        <v>2.945689405572227</v>
+        <v>0.9792005917121704</v>
       </c>
       <c r="Q26" t="n">
         <v>32</v>
@@ -3550,7 +3556,7 @@
         <v>46282</v>
       </c>
       <c r="C28" t="n">
-        <v>1.284026707755521</v>
+        <v>1.31381612737545</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,16 +3584,16 @@
         <v>26.56379120725283</v>
       </c>
       <c r="K28" t="n">
-        <v>4.340567612687818</v>
+        <v>6.761268781302188</v>
       </c>
       <c r="L28" t="n">
         <v>17</v>
       </c>
       <c r="M28" t="n">
-        <v>70.58823529411765</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N28" t="n">
-        <v>15.51067522962931</v>
+        <v>15.8747128063225</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
@@ -3659,11 +3665,11 @@
         <v>46282</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3960965588084233</v>
+        <v>0.377195685670262</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3673,14 +3679,10 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>SAT_Güncel_Benzer_Başarı_% %100.00: SAT yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>VERİ_YETERSİZ</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>5</v>
       </c>
@@ -3691,10 +3693,10 @@
         <v>27.65210909859499</v>
       </c>
       <c r="K29" t="n">
-        <v>19.61100806266052</v>
+        <v>13.90342883975346</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3729,22 +3731,18 @@
         <v>31.20488584758381</v>
       </c>
       <c r="Y29" t="n">
-        <v>8.836468024819977</v>
+        <v>13.18659506927877</v>
       </c>
       <c r="Z29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>14.1224438478875</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.276312961960269</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3778,7 +3776,7 @@
         <v>46282</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3876733436055471</v>
+        <v>0.3981510015408321</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3806,16 +3804,16 @@
         <v>21.04235192254695</v>
       </c>
       <c r="K30" t="n">
-        <v>5.848969240474799</v>
+        <v>8.70975219292005</v>
       </c>
       <c r="L30" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M30" t="n">
-        <v>61.90476190476191</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N30" t="n">
-        <v>10.69789263517809</v>
+        <v>12.48817316107839</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
@@ -3848,13 +3846,17 @@
         <v>26.71344279693404</v>
       </c>
       <c r="Y30" t="n">
-        <v>16.42414337349438</v>
+        <v>14.16533643764289</v>
       </c>
       <c r="Z30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>22.32041901315758</v>
+      </c>
       <c r="AC30" t="n">
         <v>8</v>
       </c>
@@ -3893,21 +3895,21 @@
         <v>46282</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2313302516692347</v>
+        <v>0.257216230097586</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3921,22 +3923,22 @@
         <v>17.90687778255445</v>
       </c>
       <c r="K31" t="n">
-        <v>3.397612488521573</v>
+        <v>14.96786042240588</v>
       </c>
       <c r="L31" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>69.23076923076923</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N31" t="n">
-        <v>16.69870611185395</v>
+        <v>18.41492698874927</v>
       </c>
       <c r="O31" t="n">
         <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>6.385435168738907</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>6</v>
@@ -3963,10 +3965,10 @@
         <v>56.41090041471573</v>
       </c>
       <c r="Y31" t="n">
-        <v>15.11767160987724</v>
+        <v>5.619293832652139</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
@@ -3974,7 +3976,7 @@
         <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>4.641527220171849</v>
       </c>
       <c r="AE31" t="n">
         <v>10</v>
@@ -4008,7 +4010,7 @@
         <v>46282</v>
       </c>
       <c r="C32" t="n">
-        <v>2.192090395480226</v>
+        <v>2.29070364663585</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4036,16 +4038,16 @@
         <v>14.66599569135187</v>
       </c>
       <c r="K32" t="n">
-        <v>3.953589564854565</v>
+        <v>8.630039704604364</v>
       </c>
       <c r="L32" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="M32" t="n">
-        <v>59.45945945945946</v>
+        <v>51.85185185185185</v>
       </c>
       <c r="N32" t="n">
-        <v>12.05557824792131</v>
+        <v>10.64601903097006</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4078,22 +4080,22 @@
         <v>11.59844220999629</v>
       </c>
       <c r="Y32" t="n">
-        <v>6.850322006069121</v>
+        <v>2.659896004467721</v>
       </c>
       <c r="Z32" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="AA32" t="n">
-        <v>47.82608695652174</v>
+        <v>40.42553191489362</v>
       </c>
       <c r="AB32" t="n">
-        <v>8.332568517950866</v>
+        <v>11.53490202973891</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.234226482249123</v>
+        <v>5.4860265978115</v>
       </c>
       <c r="AE32" t="n">
         <v>26</v>
@@ -4127,7 +4129,7 @@
         <v>46282</v>
       </c>
       <c r="C33" t="n">
-        <v>1.726759116589625</v>
+        <v>1.77195685670262</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,16 +4157,16 @@
         <v>13.64170455604291</v>
       </c>
       <c r="K33" t="n">
-        <v>6.013426583231674</v>
+        <v>8.788316987551848</v>
       </c>
       <c r="L33" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="M33" t="n">
-        <v>66.66666666666667</v>
+        <v>48.38709677419355</v>
       </c>
       <c r="N33" t="n">
-        <v>11.51903483928009</v>
+        <v>10.92054846451217</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
@@ -4236,7 +4238,7 @@
         <v>46282</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7428864920390343</v>
+        <v>0.7498715973292245</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4264,16 +4266,16 @@
         <v>17.91852285443199</v>
       </c>
       <c r="K34" t="n">
-        <v>4.951275606791095</v>
+        <v>5.938096229200096</v>
       </c>
       <c r="L34" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="M34" t="n">
-        <v>60.71428571428572</v>
+        <v>64</v>
       </c>
       <c r="N34" t="n">
-        <v>11.86464976481211</v>
+        <v>12.81179770458309</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4306,16 +4308,16 @@
         <v>11.67247563853926</v>
       </c>
       <c r="Y34" t="n">
-        <v>6.018672007866376</v>
+        <v>5.134998016789893</v>
       </c>
       <c r="Z34" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA34" t="n">
-        <v>36</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="AB34" t="n">
-        <v>10.82707370702024</v>
+        <v>9.761702805601765</v>
       </c>
       <c r="AC34" t="n">
         <v>2</v>
@@ -4460,7 +4462,7 @@
         <v>46282</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07046738572162302</v>
+        <v>0.07005649717514124</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,7 +4476,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -4485,25 +4487,25 @@
         <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>19.9174587240494</v>
+        <v>21.12740158531219</v>
       </c>
       <c r="K36" t="n">
-        <v>0.8411095180875572</v>
+        <v>1.791044776119399</v>
       </c>
       <c r="L36" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M36" t="n">
-        <v>53.84615384615385</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="N36" t="n">
-        <v>13.92140376410561</v>
+        <v>12.70701001702191</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>1.149224247383529</v>
+        <v>0.2052785923753797</v>
       </c>
       <c r="Q36" t="n">
         <v>10</v>
@@ -4526,27 +4528,17 @@
       <c r="W36" t="n">
         <v>44.44444444444444</v>
       </c>
-      <c r="X36" t="n">
-        <v>10.58823174740493</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>8.813887404928234</v>
-      </c>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>13.39736841960425</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
         <v>4</v>
       </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="n">
         <v>6</v>
       </c>
@@ -4579,7 +4571,7 @@
         <v>46282</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0532100667693888</v>
+        <v>0.05382639958911146</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4596,7 +4588,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H37" t="n">
         <v>5</v>
       </c>
@@ -4607,22 +4603,22 @@
         <v>28.89715284260867</v>
       </c>
       <c r="K37" t="n">
-        <v>2.329693481585626</v>
+        <v>3.514979506468863</v>
       </c>
       <c r="L37" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="M37" t="n">
-        <v>68.18181818181819</v>
+        <v>75</v>
       </c>
       <c r="N37" t="n">
-        <v>17.00923921307097</v>
+        <v>16.50507586539958</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>7.495680146637662</v>
+        <v>6.264813580073092</v>
       </c>
       <c r="Q37" t="n">
         <v>27</v>
@@ -4688,7 +4684,7 @@
         <v>46282</v>
       </c>
       <c r="C38" t="n">
-        <v>1.563430919363123</v>
+        <v>1.596302003081664</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4716,22 +4712,22 @@
         <v>15.42052714918329</v>
       </c>
       <c r="K38" t="n">
-        <v>5.577914347654844</v>
+        <v>7.797686528420278</v>
       </c>
       <c r="L38" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M38" t="n">
-        <v>70.27027027027027</v>
+        <v>64.51612903225806</v>
       </c>
       <c r="N38" t="n">
-        <v>10.99826113622809</v>
+        <v>10.93042466995157</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>4.188457102669974</v>
+        <v>2.043006248560908</v>
       </c>
       <c r="Q38" t="n">
         <v>42</v>
@@ -4797,7 +4793,7 @@
         <v>46282</v>
       </c>
       <c r="C39" t="n">
-        <v>2.652285567539805</v>
+        <v>2.730354391371341</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4825,16 +4821,16 @@
         <v>15.16246653075239</v>
       </c>
       <c r="K39" t="n">
-        <v>9.54772571907354</v>
+        <v>12.77221338547541</v>
       </c>
       <c r="L39" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="M39" t="n">
-        <v>43.47826086956522</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="N39" t="n">
-        <v>15.56291847452139</v>
+        <v>13.3783564311</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4864,25 +4860,25 @@
         <v>67.69230769230769</v>
       </c>
       <c r="X39" t="n">
-        <v>10.14171287727583</v>
+        <v>12.77221338547541</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.5392935543540367</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="AA39" t="n">
-        <v>46.80851063829788</v>
+        <v>38.80597014925373</v>
       </c>
       <c r="AB39" t="n">
-        <v>11.50558243321231</v>
+        <v>11.59044072703114</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>5.490315362509691</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="AE39" t="n">
         <v>40</v>
@@ -4916,7 +4912,7 @@
         <v>46282</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1873651771956857</v>
+        <v>0.1855161787365177</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4944,22 +4940,22 @@
         <v>29.83357657172154</v>
       </c>
       <c r="K40" t="n">
-        <v>1.33333333333332</v>
+        <v>0.3333333333333188</v>
       </c>
       <c r="L40" t="n">
         <v>11</v>
       </c>
       <c r="M40" t="n">
-        <v>72.72727272727273</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="N40" t="n">
-        <v>11.97496631083943</v>
+        <v>12.83266905617622</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>1.644736842105288</v>
+        <v>2.657807308970117</v>
       </c>
       <c r="Q40" t="n">
         <v>29</v>
@@ -5130,26 +5126,26 @@
         <v>46282</v>
       </c>
       <c r="C42" t="n">
-        <v>3.157678479712378</v>
+        <v>2.828967642526965</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -5159,25 +5155,25 @@
         <v>10</v>
       </c>
       <c r="J42" t="n">
-        <v>21.02862867458981</v>
+        <v>26.85119801730374</v>
       </c>
       <c r="K42" t="n">
-        <v>3.38974529754168</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M42" t="n">
-        <v>85.71428571428571</v>
+        <v>75</v>
       </c>
       <c r="N42" t="n">
-        <v>15.00085957256051</v>
+        <v>16.10719482417057</v>
       </c>
       <c r="O42" t="n">
         <v>2</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.000000000000002</v>
       </c>
       <c r="Q42" t="n">
         <v>2</v>
@@ -5198,27 +5194,17 @@
         <v>0</v>
       </c>
       <c r="W42" t="inlineStr"/>
-      <c r="X42" t="n">
-        <v>11.70928208999582</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>7.447489265709983</v>
-      </c>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>33.33333333333334</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>10.28383030711321</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
         <v>10</v>
       </c>
-      <c r="AD42" t="n">
-        <v>2.757905446366593</v>
-      </c>
+      <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="n">
         <v>1</v>
       </c>
@@ -5249,7 +5235,7 @@
         <v>46282</v>
       </c>
       <c r="C43" t="n">
-        <v>5.752439650744736</v>
+        <v>5.675398048279405</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5268,7 +5254,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %90.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -5281,22 +5267,22 @@
         <v>26.64182087935456</v>
       </c>
       <c r="K43" t="n">
-        <v>4.532413329707863</v>
+        <v>3.132425651184989</v>
       </c>
       <c r="L43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M43" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="N43" t="n">
-        <v>13.64758851004747</v>
+        <v>15.06274995757913</v>
       </c>
       <c r="O43" t="n">
         <v>10</v>
       </c>
       <c r="P43" t="n">
-        <v>5.230517976320614</v>
+        <v>6.658986546134926</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5323,16 +5309,16 @@
         <v>10.08403361344536</v>
       </c>
       <c r="Y43" t="n">
-        <v>5.043074914234847</v>
+        <v>6.314819446633491</v>
       </c>
       <c r="Z43" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA43" t="n">
-        <v>33.33333333333334</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="AB43" t="n">
-        <v>12.22193855346982</v>
+        <v>10.80118519534348</v>
       </c>
       <c r="AC43" t="n">
         <v>2</v>
@@ -5582,16 +5568,16 @@
         <v>46282</v>
       </c>
       <c r="C46" t="n">
-        <v>8.243451463790448</v>
+        <v>8.695428864920391</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5610,22 +5596,22 @@
         <v>28.15632518747767</v>
       </c>
       <c r="K46" t="n">
-        <v>5.870712401055411</v>
+        <v>11.6754617414248</v>
       </c>
       <c r="L46" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M46" t="n">
-        <v>50</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N46" t="n">
-        <v>19.97556224910608</v>
+        <v>9.859569556306326</v>
       </c>
       <c r="O46" t="n">
         <v>8</v>
       </c>
       <c r="P46" t="n">
-        <v>2.011214953271034</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>51</v>
@@ -5691,7 +5677,7 @@
         <v>46282</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9746276322547509</v>
+        <v>0.9972265023112481</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5719,22 +5705,22 @@
         <v>18.95305070442179</v>
       </c>
       <c r="K47" t="n">
-        <v>7.141004168378196</v>
+        <v>9.625302325739415</v>
       </c>
       <c r="L47" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M47" t="n">
-        <v>61.90476190476191</v>
+        <v>56.25</v>
       </c>
       <c r="N47" t="n">
-        <v>17.22084568422099</v>
+        <v>14.77409691035926</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>2.668442258697468</v>
+        <v>0.3417985321921613</v>
       </c>
       <c r="Q47" t="n">
         <v>51</v>
@@ -5761,7 +5747,7 @@
         <v>66.65983471422588</v>
       </c>
       <c r="Y47" t="n">
-        <v>13.16548467688119</v>
+        <v>11.15203680893366</v>
       </c>
       <c r="Z47" t="n">
         <v>2</v>
@@ -5806,7 +5792,7 @@
         <v>46282</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0482794042116076</v>
+        <v>0.04992295839753468</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5834,22 +5820,22 @@
         <v>27.02915304173016</v>
       </c>
       <c r="K48" t="n">
-        <v>4.444444444444429</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="L48" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M48" t="n">
-        <v>44.44444444444444</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N48" t="n">
-        <v>13.15490657936633</v>
+        <v>11.66660468424351</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>5.319148936170248</v>
+        <v>1.85185185185186</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5915,7 +5901,7 @@
         <v>46282</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2658448895737031</v>
+        <v>0.2761171032357473</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5943,16 +5929,16 @@
         <v>18.76252681801688</v>
       </c>
       <c r="K49" t="n">
-        <v>7.520452620171314</v>
+        <v>11.67502961476834</v>
       </c>
       <c r="L49" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M49" t="n">
-        <v>63.63636363636363</v>
+        <v>47.61904761904762</v>
       </c>
       <c r="N49" t="n">
-        <v>15.07354813377234</v>
+        <v>17.29347668086765</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
@@ -5982,25 +5968,25 @@
         <v>67.14285714285714</v>
       </c>
       <c r="X49" t="n">
-        <v>11.47132295072795</v>
+        <v>11.67502961476834</v>
       </c>
       <c r="Y49" t="n">
-        <v>3.544293030686452</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AA49" t="n">
-        <v>33.33333333333334</v>
+        <v>42</v>
       </c>
       <c r="AB49" t="n">
-        <v>10.40275928582287</v>
+        <v>10.48534602744506</v>
       </c>
       <c r="AC49" t="n">
         <v>10</v>
       </c>
       <c r="AD49" t="n">
-        <v>6.692923801146744</v>
+        <v>9.999999999999998</v>
       </c>
       <c r="AE49" t="n">
         <v>44</v>
@@ -6034,7 +6020,7 @@
         <v>46282</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6808423215202877</v>
+        <v>0.7194658448895738</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6048,7 +6034,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -6062,16 +6048,16 @@
         <v>16.75569689884803</v>
       </c>
       <c r="K50" t="n">
-        <v>6.038580965396334</v>
+        <v>12.05404663271514</v>
       </c>
       <c r="L50" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="M50" t="n">
-        <v>57.89473684210526</v>
+        <v>55</v>
       </c>
       <c r="N50" t="n">
-        <v>18.0425855074497</v>
+        <v>16.58862239127276</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
@@ -6100,17 +6086,27 @@
       <c r="W50" t="n">
         <v>70</v>
       </c>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
+      <c r="X50" t="n">
+        <v>13.14194999808132</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0.9615384615384581</v>
+      </c>
       <c r="Z50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="inlineStr"/>
-      <c r="AB50" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>46.15384615384615</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>12.98504755739105</v>
+      </c>
       <c r="AC50" t="n">
         <v>5</v>
       </c>
-      <c r="AD50" t="inlineStr"/>
+      <c r="AD50" t="n">
+        <v>4.077669902912628</v>
+      </c>
       <c r="AE50" t="n">
         <v>42</v>
       </c>
@@ -6248,11 +6244,11 @@
         <v>46282</v>
       </c>
       <c r="C52" t="n">
-        <v>4.341037493579867</v>
+        <v>4.519774011299435</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6262,7 +6258,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -6276,22 +6272,22 @@
         <v>14.1037450661144</v>
       </c>
       <c r="K52" t="n">
-        <v>5.343451910685548</v>
+        <v>9.68083019569721</v>
       </c>
       <c r="L52" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="M52" t="n">
-        <v>46.15384615384615</v>
+        <v>70.83333333333333</v>
       </c>
       <c r="N52" t="n">
-        <v>13.89573997051477</v>
+        <v>11.73973172536463</v>
       </c>
       <c r="O52" t="n">
         <v>10</v>
       </c>
       <c r="P52" t="n">
-        <v>4.420348873001112</v>
+        <v>0.2909987130233382</v>
       </c>
       <c r="Q52" t="n">
         <v>37</v>
@@ -6318,22 +6314,22 @@
         <v>16.53731163255363</v>
       </c>
       <c r="Y52" t="n">
-        <v>9.51391999064235</v>
+        <v>5.788274481501743</v>
       </c>
       <c r="Z52" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA52" t="n">
-        <v>68.75</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB52" t="n">
-        <v>11.77801037928238</v>
+        <v>13.01254235891325</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>2.347611729140853</v>
       </c>
       <c r="AE52" t="n">
         <v>37</v>
@@ -6367,7 +6363,7 @@
         <v>46282</v>
       </c>
       <c r="C53" t="n">
-        <v>1.009964047252183</v>
+        <v>0.9668207498715974</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6392,25 +6388,21 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>42.07172100726159</v>
+        <v>43.76916435099497</v>
       </c>
       <c r="K53" t="n">
-        <v>1.444492227175664</v>
+        <v>0.04251700680271142</v>
       </c>
       <c r="L53" t="n">
-        <v>3</v>
-      </c>
-      <c r="M53" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N53" t="n">
-        <v>28.71403390950369</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>6.462162340113919</v>
+        <v>7.954101147471326</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6587,7 +6579,7 @@
         <v>46282</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8682074987159732</v>
+        <v>0.9064201335387776</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6615,16 +6607,16 @@
         <v>18.57198344066605</v>
       </c>
       <c r="K55" t="n">
-        <v>6.673550121944993</v>
+        <v>11.3685998906818</v>
       </c>
       <c r="L55" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="M55" t="n">
-        <v>61.29032258064516</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N55" t="n">
-        <v>12.61308200475298</v>
+        <v>10.39215044032665</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
@@ -6657,16 +6649,16 @@
         <v>23.0932342837701</v>
       </c>
       <c r="Y55" t="n">
-        <v>13.13784394227323</v>
+        <v>9.314758039117255</v>
       </c>
       <c r="Z55" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AA55" t="n">
-        <v>14.28571428571429</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="AB55" t="n">
-        <v>33.66794265572751</v>
+        <v>9.409062864639326</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6908,7 +6900,7 @@
         <v>46282</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6557781201848999</v>
+        <v>0.6216743708269132</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6922,12 +6914,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %81.48: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %78.95: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -6937,25 +6929,25 @@
         <v>10</v>
       </c>
       <c r="J58" t="n">
-        <v>18.04392839464337</v>
+        <v>21.9059616006776</v>
       </c>
       <c r="K58" t="n">
-        <v>0.5149607532956679</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="M58" t="n">
-        <v>81.48148148148148</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="N58" t="n">
-        <v>18.38788453508219</v>
+        <v>21.22911893857821</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>7.446691706994391</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q58" t="n">
         <v>25</v>
@@ -6978,12 +6970,8 @@
       <c r="W58" t="n">
         <v>80.95238095238095</v>
       </c>
-      <c r="X58" t="n">
-        <v>20.50322102897642</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>16.58732447564563</v>
-      </c>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="n">
         <v>0</v>
       </c>
@@ -6992,9 +6980,7 @@
       <c r="AC58" t="n">
         <v>6</v>
       </c>
-      <c r="AD58" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD58" t="inlineStr"/>
       <c r="AE58" t="n">
         <v>4</v>
       </c>
@@ -7027,7 +7013,7 @@
         <v>46282</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7560349255264509</v>
+        <v>0.7704160246533128</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7044,7 +7030,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H59" t="n">
         <v>5</v>
       </c>
@@ -7055,16 +7045,16 @@
         <v>17.69918671275772</v>
       </c>
       <c r="K59" t="n">
-        <v>10.46533660738964</v>
+        <v>12.56657942329109</v>
       </c>
       <c r="L59" t="n">
         <v>14</v>
       </c>
       <c r="M59" t="n">
-        <v>64.28571428571429</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="N59" t="n">
-        <v>9.615778066966326</v>
+        <v>12.69156947560585</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
@@ -7094,25 +7084,25 @@
         <v>65.51724137931035</v>
       </c>
       <c r="X59" t="n">
-        <v>11.6660490692541</v>
+        <v>12.98682798647137</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.075270838247167</v>
+        <v>0.3719447396386744</v>
       </c>
       <c r="Z59" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="AA59" t="n">
-        <v>54</v>
+        <v>48.27586206896552</v>
       </c>
       <c r="AB59" t="n">
-        <v>12.9774609813349</v>
+        <v>13.72491834223873</v>
       </c>
       <c r="AC59" t="n">
         <v>6</v>
       </c>
       <c r="AD59" t="n">
-        <v>4.978258928260859</v>
+        <v>5.64906666666668</v>
       </c>
       <c r="AE59" t="n">
         <v>42</v>
@@ -7146,16 +7136,16 @@
         <v>46282</v>
       </c>
       <c r="C60" t="n">
-        <v>10.43656908063688</v>
+        <v>10.78582434514638</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -7163,7 +7153,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H60" t="n">
         <v>5</v>
       </c>
@@ -7174,22 +7168,22 @@
         <v>29.37042877474947</v>
       </c>
       <c r="K60" t="n">
-        <v>5.024266980845571</v>
+        <v>8.538858592409305</v>
       </c>
       <c r="L60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M60" t="n">
-        <v>66.66666666666667</v>
+        <v>80</v>
       </c>
       <c r="N60" t="n">
-        <v>11.22664512296512</v>
+        <v>9.330313441253185</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>2.833376613518435</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>46</v>
@@ -7370,11 +7364,11 @@
         <v>46282</v>
       </c>
       <c r="C62" t="n">
-        <v>8.690292758089369</v>
+        <v>8.931689779147407</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7384,7 +7378,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -7430,22 +7424,22 @@
         <v>12.69355362364248</v>
       </c>
       <c r="Y62" t="n">
-        <v>7.185957213384531</v>
+        <v>4.607789358200765</v>
       </c>
       <c r="Z62" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="AA62" t="n">
-        <v>50</v>
+        <v>46.80851063829788</v>
       </c>
       <c r="AB62" t="n">
-        <v>20.54413063837905</v>
+        <v>15.91397725010352</v>
       </c>
       <c r="AC62" t="n">
         <v>5</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>0.4111558366877599</v>
       </c>
       <c r="AE62" t="n">
         <v>27</v>
@@ -7479,7 +7473,7 @@
         <v>46282</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0953261427837699</v>
+        <v>0.0967642526964561</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7507,22 +7501,22 @@
         <v>22.98070282549081</v>
       </c>
       <c r="K63" t="n">
-        <v>0.8695674102079609</v>
+        <v>2.391306573724061</v>
       </c>
       <c r="L63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M63" t="n">
-        <v>66.66666666666667</v>
+        <v>62.5</v>
       </c>
       <c r="N63" t="n">
-        <v>13.66536901271402</v>
+        <v>12.46026019189929</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>4.094825323275897</v>
+        <v>2.547768471337575</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7588,7 +7582,7 @@
         <v>46282</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1421674370826913</v>
+        <v>0.1450436569080637</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7597,7 +7591,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7616,22 +7610,22 @@
         <v>18.13256048493127</v>
       </c>
       <c r="K64" t="n">
-        <v>4.805624634329075</v>
+        <v>6.925969641381968</v>
       </c>
       <c r="L64" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M64" t="n">
-        <v>52.5</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="N64" t="n">
-        <v>13.7431377645763</v>
+        <v>13.51095418880734</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>0.185462723350116</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>55</v>
@@ -7658,16 +7652,16 @@
         <v>11.36363653581267</v>
       </c>
       <c r="Y64" t="n">
-        <v>5.888827004472564</v>
+        <v>3.984843735776922</v>
       </c>
       <c r="Z64" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="AA64" t="n">
-        <v>52.17391304347826</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="AB64" t="n">
-        <v>13.35187013801021</v>
+        <v>14.24395685401651</v>
       </c>
       <c r="AC64" t="n">
         <v>2</v>
@@ -7707,7 +7701,7 @@
         <v>46282</v>
       </c>
       <c r="C65" t="n">
-        <v>6.153055983564458</v>
+        <v>6.302003081664099</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7735,22 +7729,22 @@
         <v>15.61952021218654</v>
       </c>
       <c r="K65" t="n">
-        <v>3.411939598744995</v>
+        <v>5.915233629098582</v>
       </c>
       <c r="L65" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M65" t="n">
-        <v>61.36363636363637</v>
+        <v>58.06451612903226</v>
       </c>
       <c r="N65" t="n">
-        <v>11.5165735319105</v>
+        <v>13.42191900068244</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>6.370696098359385</v>
+        <v>3.856637266368823</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7777,16 +7771,16 @@
         <v>24.47056390537039</v>
       </c>
       <c r="Y65" t="n">
-        <v>12.74050920869512</v>
+        <v>10.62821769538307</v>
       </c>
       <c r="Z65" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AA65" t="n">
-        <v>50</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="AB65" t="n">
-        <v>15.0813486974636</v>
+        <v>15.00601971697285</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
@@ -7826,21 +7820,21 @@
         <v>46282</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4041088854648177</v>
+        <v>0.4191063174114021</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -7854,22 +7848,22 @@
         <v>19.90687209731571</v>
       </c>
       <c r="K66" t="n">
-        <v>4.196916148590235</v>
+        <v>8.063908969559751</v>
       </c>
       <c r="L66" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="M66" t="n">
-        <v>51.51515151515152</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="N66" t="n">
-        <v>15.83003245469546</v>
+        <v>14.02355017649872</v>
       </c>
       <c r="O66" t="n">
         <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>1.730457980962208</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
         <v>35</v>
@@ -7896,22 +7890,22 @@
         <v>11.49973494118828</v>
       </c>
       <c r="Y66" t="n">
-        <v>6.549628836741195</v>
+        <v>3.081465595806843</v>
       </c>
       <c r="Z66" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="AA66" t="n">
-        <v>43.75</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB66" t="n">
-        <v>11.69942193211742</v>
+        <v>11.42607909402794</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>3.011327422700782</v>
       </c>
       <c r="AE66" t="n">
         <v>41</v>
@@ -7945,7 +7939,7 @@
         <v>46282</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02239342578325629</v>
+        <v>0.02280431432973806</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7962,7 +7956,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H67" t="n">
         <v>5</v>
       </c>
@@ -7973,22 +7971,22 @@
         <v>24.79148995549716</v>
       </c>
       <c r="K67" t="n">
-        <v>0.92592592592593</v>
+        <v>2.77777777777779</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
       </c>
       <c r="M67" t="n">
-        <v>66.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="N67" t="n">
-        <v>10.57717221367301</v>
+        <v>10.56848628706042</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>3.045871559633029</v>
+        <v>1.189189189189177</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -8242,7 +8240,7 @@
         <v>46282</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4330765279917822</v>
+        <v>0.4449922958397535</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8259,11 +8257,7 @@
           <t>SAT_ADAYI</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.95: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>5</v>
       </c>
@@ -8274,22 +8268,22 @@
         <v>24.99185434120895</v>
       </c>
       <c r="K70" t="n">
-        <v>4.459861248761143</v>
+        <v>7.333994053518333</v>
       </c>
       <c r="L70" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M70" t="n">
-        <v>80.95238095238095</v>
+        <v>72.22222222222223</v>
       </c>
       <c r="N70" t="n">
-        <v>12.46017152627624</v>
+        <v>11.00256638103325</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>3.388994307400384</v>
+        <v>0.6204986149584535</v>
       </c>
       <c r="Q70" t="n">
         <v>31</v>
@@ -8316,7 +8310,7 @@
         <v>44.93251946562029</v>
       </c>
       <c r="Y70" t="n">
-        <v>21.64659511955822</v>
+        <v>19.49076139893885</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -8361,7 +8355,7 @@
         <v>46282</v>
       </c>
       <c r="C71" t="n">
-        <v>3.003595274781715</v>
+        <v>3.093990755007704</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8389,16 +8383,16 @@
         <v>12.27124607635546</v>
       </c>
       <c r="K71" t="n">
-        <v>4.014401281445878</v>
+        <v>7.144793659273252</v>
       </c>
       <c r="L71" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="M71" t="n">
-        <v>54.6875</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N71" t="n">
-        <v>16.31050643755811</v>
+        <v>14.33792192373144</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
@@ -8579,7 +8573,7 @@
         <v>46282</v>
       </c>
       <c r="C73" t="n">
-        <v>0.05279917822290704</v>
+        <v>0.05362095531587057</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8607,22 +8601,22 @@
         <v>31.26644991618639</v>
       </c>
       <c r="K73" t="n">
-        <v>1.181103955607932</v>
+        <v>2.755907130014279</v>
       </c>
       <c r="L73" t="n">
         <v>7</v>
       </c>
       <c r="M73" t="n">
-        <v>42.85714285714285</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N73" t="n">
-        <v>21.67361112404349</v>
+        <v>18.25806919375062</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>8.715951595330761</v>
+        <v>7.049806743295028</v>
       </c>
       <c r="Q73" t="n">
         <v>14</v>
@@ -8797,7 +8791,7 @@
         <v>46282</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1029275808936826</v>
+        <v>0.1033384694401644</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8822,25 +8816,25 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>21.92996714778428</v>
+        <v>22.08673428202569</v>
       </c>
       <c r="K75" t="n">
-        <v>0.6024096385542022</v>
+        <v>1.207243460764595</v>
       </c>
       <c r="L75" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M75" t="n">
-        <v>60</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N75" t="n">
-        <v>20.09443459697961</v>
+        <v>18.39790111350874</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>5.365269461077871</v>
+        <v>4.735586481113319</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8906,16 +8900,16 @@
         <v>46282</v>
       </c>
       <c r="C76" t="n">
-        <v>1.802773497688752</v>
+        <v>1.866461222393426</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8934,22 +8928,22 @@
         <v>16.69183750728255</v>
       </c>
       <c r="K76" t="n">
-        <v>6.578523409098258</v>
+        <v>10.34369061785272</v>
       </c>
       <c r="L76" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M76" t="n">
-        <v>52</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N76" t="n">
-        <v>13.07079506901141</v>
+        <v>12.05057279388566</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>3.210287102372877</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
         <v>41</v>
@@ -8973,25 +8967,25 @@
         <v>60</v>
       </c>
       <c r="X76" t="n">
-        <v>10.81408696253991</v>
+        <v>10.89024714815578</v>
       </c>
       <c r="Y76" t="n">
-        <v>3.822224835794985</v>
+        <v>0.4928806133625452</v>
       </c>
       <c r="Z76" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="AA76" t="n">
-        <v>36.11111111111111</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="AB76" t="n">
-        <v>10.13713202632063</v>
+        <v>9.89623813342066</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.184840171132572</v>
+        <v>3.524490919097412</v>
       </c>
       <c r="AE76" t="n">
         <v>32</v>
@@ -9025,7 +9019,7 @@
         <v>46282</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4466358500256805</v>
+        <v>0.4643040575243966</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9053,22 +9047,22 @@
         <v>24.27505949158866</v>
       </c>
       <c r="K77" t="n">
-        <v>3.186672784832223</v>
+        <v>7.268574284140228</v>
       </c>
       <c r="L77" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M77" t="n">
-        <v>61.90476190476191</v>
+        <v>50</v>
       </c>
       <c r="N77" t="n">
-        <v>14.93209402914525</v>
+        <v>12.78101208095246</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>4.664679154065432</v>
+        <v>0.6818639296186868</v>
       </c>
       <c r="Q77" t="n">
         <v>26</v>
@@ -9134,21 +9128,21 @@
         <v>46282</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0482794042116076</v>
+        <v>0.04992295839753468</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -9162,22 +9156,22 @@
         <v>25.89426476209616</v>
       </c>
       <c r="K78" t="n">
-        <v>3.524229986997618</v>
+        <v>7.048459092937964</v>
       </c>
       <c r="L78" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="M78" t="n">
-        <v>56.52173913043478</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N78" t="n">
-        <v>24.73030317669522</v>
+        <v>16.20453229241359</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>0.4595735829787229</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9204,7 +9198,7 @@
         <v>36.67113091579677</v>
       </c>
       <c r="Y78" t="n">
-        <v>23.28260821875691</v>
+        <v>20.67095232833161</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -9249,16 +9243,16 @@
         <v>46282</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8057524396507447</v>
+        <v>0.8275295326142784</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -9277,22 +9271,22 @@
         <v>22.50123891318462</v>
       </c>
       <c r="K79" t="n">
-        <v>4.364023416711027</v>
+        <v>7.184672698243766</v>
       </c>
       <c r="L79" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="M79" t="n">
-        <v>55.55555555555556</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N79" t="n">
-        <v>10.56661665793823</v>
+        <v>11.81136006680001</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>0.6093829678735174</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
         <v>41</v>
@@ -9358,7 +9352,7 @@
         <v>46282</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1265536723163842</v>
+        <v>0.1288135593220339</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9386,22 +9380,22 @@
         <v>14.36747410815714</v>
       </c>
       <c r="K80" t="n">
-        <v>3.487092501040645</v>
+        <v>5.335076295702068</v>
       </c>
       <c r="L80" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="M80" t="n">
-        <v>55.22388059701493</v>
+        <v>62.74509803921568</v>
       </c>
       <c r="N80" t="n">
-        <v>15.53660303334201</v>
+        <v>17.24107372390105</v>
       </c>
       <c r="O80" t="n">
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>6.293449107089244</v>
+        <v>4.428651754333313</v>
       </c>
       <c r="Q80" t="n">
         <v>39</v>
@@ -9467,7 +9461,7 @@
         <v>46282</v>
       </c>
       <c r="C81" t="n">
-        <v>1.152542372881356</v>
+        <v>1.183359013867489</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9495,22 +9489,22 @@
         <v>11.75203263413206</v>
       </c>
       <c r="K81" t="n">
-        <v>2.559414990859232</v>
+        <v>5.301645338208405</v>
       </c>
       <c r="L81" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="M81" t="n">
-        <v>50</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N81" t="n">
-        <v>13.2556313833504</v>
+        <v>15.46238709479638</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>7.254901960784332</v>
+        <v>4.461805555555576</v>
       </c>
       <c r="Q81" t="n">
         <v>32</v>
@@ -9537,22 +9531,22 @@
         <v>23.79225853623819</v>
       </c>
       <c r="Y81" t="n">
-        <v>9.493400928241469</v>
+        <v>7.073438386215836</v>
       </c>
       <c r="Z81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA81" t="n">
-        <v>62.5</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB81" t="n">
-        <v>8.615772679614428</v>
+        <v>10.78755071299194</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.5597371649738725</v>
+        <v>3.149327342969344</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9695,21 +9689,21 @@
         <v>46282</v>
       </c>
       <c r="C83" t="n">
-        <v>5.387776065742168</v>
+        <v>5.63944530046225</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ALMA_BEKLE</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -9723,22 +9717,22 @@
         <v>17.92531520307596</v>
       </c>
       <c r="K83" t="n">
-        <v>7.78897867355961</v>
+        <v>12.82392619977928</v>
       </c>
       <c r="L83" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="M83" t="n">
-        <v>58.33333333333334</v>
+        <v>60</v>
       </c>
       <c r="N83" t="n">
-        <v>10.70695472386624</v>
+        <v>9.960217924426816</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
       </c>
       <c r="P83" t="n">
-        <v>2.051249908524055</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
         <v>41</v>
@@ -9761,17 +9755,27 @@
       <c r="W83" t="n">
         <v>61.90476190476191</v>
       </c>
-      <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
+      <c r="X83" t="n">
+        <v>13.33769635551598</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>0.4533091568449721</v>
+      </c>
       <c r="Z83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA83" t="inlineStr"/>
-      <c r="AB83" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>41.53846153846154</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>13.42071945660485</v>
+      </c>
       <c r="AC83" t="n">
         <v>8</v>
       </c>
-      <c r="AD83" t="inlineStr"/>
+      <c r="AD83" t="n">
+        <v>7.581056466302361</v>
+      </c>
       <c r="AE83" t="n">
         <v>41</v>
       </c>
@@ -9804,7 +9808,7 @@
         <v>46282</v>
       </c>
       <c r="C84" t="n">
-        <v>2.006163328197227</v>
+        <v>2.03492552645095</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9832,16 +9836,16 @@
         <v>15.17540634174243</v>
       </c>
       <c r="K84" t="n">
-        <v>5.810385821939956</v>
+        <v>7.327380600749134</v>
       </c>
       <c r="L84" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="M84" t="n">
-        <v>64.70588235294117</v>
+        <v>51.61290322580645</v>
       </c>
       <c r="N84" t="n">
-        <v>9.644407476415203</v>
+        <v>9.20041578810123</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9874,16 +9878,16 @@
         <v>10.78590455284552</v>
       </c>
       <c r="Y84" t="n">
-        <v>4.49111170864901</v>
+        <v>3.121808650708502</v>
       </c>
       <c r="Z84" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AA84" t="n">
-        <v>27.02702702702703</v>
+        <v>30</v>
       </c>
       <c r="AB84" t="n">
-        <v>10.27488055780199</v>
+        <v>12.37721799199906</v>
       </c>
       <c r="AC84" t="n">
         <v>2</v>
@@ -9923,7 +9927,7 @@
         <v>46282</v>
       </c>
       <c r="C85" t="n">
-        <v>5.767847971237802</v>
+        <v>5.932203389830509</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9951,16 +9955,16 @@
         <v>18.98569199070202</v>
       </c>
       <c r="K85" t="n">
-        <v>8.668046502281413</v>
+        <v>11.76455361543636</v>
       </c>
       <c r="L85" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="M85" t="n">
-        <v>68.18181818181819</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="N85" t="n">
-        <v>13.90948768041349</v>
+        <v>11.58916989402006</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
@@ -9990,25 +9994,25 @@
         <v>57.89473684210526</v>
       </c>
       <c r="X85" t="n">
-        <v>11.51984511132622</v>
+        <v>12.24838285186682</v>
       </c>
       <c r="Y85" t="n">
-        <v>2.557211773561885</v>
+        <v>0.4310344827586299</v>
       </c>
       <c r="Z85" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="AA85" t="n">
-        <v>26.53061224489796</v>
+        <v>36.8421052631579</v>
       </c>
       <c r="AB85" t="n">
-        <v>11.386201848345</v>
+        <v>11.03764195490517</v>
       </c>
       <c r="AC85" t="n">
         <v>6</v>
       </c>
       <c r="AD85" t="n">
-        <v>3.533138048592932</v>
+        <v>5.593073593073594</v>
       </c>
       <c r="AE85" t="n">
         <v>33</v>
@@ -10042,7 +10046,7 @@
         <v>46282</v>
       </c>
       <c r="C86" t="n">
-        <v>5.213148433487417</v>
+        <v>5.300462249614792</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10099,25 +10103,25 @@
         <v>70.12987012987013</v>
       </c>
       <c r="X86" t="n">
-        <v>28.97992177002235</v>
+        <v>29.48178916990571</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.264591439688723</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AA86" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB86" t="n">
-        <v>13.91846076202928</v>
+        <v>12.51003871173557</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>4.796059113300489</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="AE86" t="n">
         <v>52</v>
@@ -10151,7 +10155,7 @@
         <v>46282</v>
       </c>
       <c r="C87" t="n">
-        <v>5.731895223420647</v>
+        <v>5.875706214689266</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10179,16 +10183,16 @@
         <v>13.37336922777884</v>
       </c>
       <c r="K87" t="n">
-        <v>7.263825187625939</v>
+        <v>9.955032271186459</v>
       </c>
       <c r="L87" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M87" t="n">
-        <v>65</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N87" t="n">
-        <v>11.33733408847504</v>
+        <v>11.08166016718459</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10221,16 +10225,16 @@
         <v>15.88967756874082</v>
       </c>
       <c r="Y87" t="n">
-        <v>7.080962202554519</v>
+        <v>4.749660178962689</v>
       </c>
       <c r="Z87" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AA87" t="n">
-        <v>53.57142857142857</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB87" t="n">
-        <v>12.50709394467145</v>
+        <v>10.95382325810438</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
@@ -10270,7 +10274,7 @@
         <v>46282</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9873651771956857</v>
+        <v>1.019414483821264</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10284,7 +10288,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -10298,16 +10302,16 @@
         <v>21.41497098631751</v>
       </c>
       <c r="K88" t="n">
-        <v>5.075135408064702</v>
+        <v>8.485813960636079</v>
       </c>
       <c r="L88" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M88" t="n">
-        <v>63.63636363636363</v>
+        <v>68</v>
       </c>
       <c r="N88" t="n">
-        <v>13.97762866645933</v>
+        <v>12.11345534804188</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
@@ -10340,22 +10344,22 @@
         <v>12.09536008844403</v>
       </c>
       <c r="Y88" t="n">
-        <v>6.262725481982779</v>
+        <v>3.22006738277123</v>
       </c>
       <c r="Z88" t="n">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="AA88" t="n">
-        <v>37.5</v>
+        <v>34.375</v>
       </c>
       <c r="AB88" t="n">
-        <v>11.21667741778429</v>
+        <v>13.29314141936841</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>2.872426692239594</v>
       </c>
       <c r="AE88" t="n">
         <v>33</v>
@@ -10389,24 +10393,28 @@
         <v>46282</v>
       </c>
       <c r="C89" t="n">
-        <v>2.045197740112994</v>
+        <v>2.128402670775552</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.32: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H89" t="n">
         <v>5</v>
       </c>
@@ -10417,22 +10425,22 @@
         <v>15.60428510343075</v>
       </c>
       <c r="K89" t="n">
-        <v>3.493814479426294</v>
+        <v>7.704260975073485</v>
       </c>
       <c r="L89" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="M89" t="n">
-        <v>66.10169491525424</v>
+        <v>76.31578947368421</v>
       </c>
       <c r="N89" t="n">
-        <v>15.49634425848416</v>
+        <v>17.14608470071638</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>0.4890973659825271</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
         <v>45</v>
@@ -10459,22 +10467,22 @@
         <v>21.41032003314154</v>
       </c>
       <c r="Y89" t="n">
-        <v>12.65565539635908</v>
+        <v>9.102218976020094</v>
       </c>
       <c r="Z89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AA89" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB89" t="n">
-        <v>20.63598439723828</v>
+        <v>15.1641247567547</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>0.9876820026476274</v>
       </c>
       <c r="AE89" t="n">
         <v>22</v>
@@ -10508,7 +10516,7 @@
         <v>46282</v>
       </c>
       <c r="C90" t="n">
-        <v>2.578325629173087</v>
+        <v>2.676938880328711</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10525,7 +10533,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H90" t="n">
         <v>5</v>
       </c>
@@ -10536,22 +10548,22 @@
         <v>19.80512321049643</v>
       </c>
       <c r="K90" t="n">
-        <v>2.911152038440079</v>
+        <v>6.847196100468067</v>
       </c>
       <c r="L90" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="M90" t="n">
-        <v>70.73170731707317</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="N90" t="n">
-        <v>15.84628685195545</v>
+        <v>16.6187541379661</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>4.944894562699198</v>
+        <v>1.078927610274372</v>
       </c>
       <c r="Q90" t="n">
         <v>43</v>
@@ -10617,16 +10629,16 @@
         <v>46282</v>
       </c>
       <c r="C91" t="n">
-        <v>0.220236260914227</v>
+        <v>0.2311248073959938</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10645,22 +10657,22 @@
         <v>13.48269577863128</v>
       </c>
       <c r="K91" t="n">
-        <v>5.261467231019679</v>
+        <v>10.46562559225479</v>
       </c>
       <c r="L91" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="M91" t="n">
-        <v>69.23076923076923</v>
+        <v>50</v>
       </c>
       <c r="N91" t="n">
-        <v>13.8624981041094</v>
+        <v>22.27250123952689</v>
       </c>
       <c r="O91" t="n">
         <v>6</v>
       </c>
       <c r="P91" t="n">
-        <v>0.7016173994225827</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>44</v>
@@ -10684,25 +10696,25 @@
         <v>66.25</v>
       </c>
       <c r="X91" t="n">
-        <v>10.31433396881694</v>
+        <v>11.05477559541348</v>
       </c>
       <c r="Y91" t="n">
-        <v>4.580426274635863</v>
+        <v>0.5305039787798504</v>
       </c>
       <c r="Z91" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AA91" t="n">
-        <v>39.28571428571428</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="AB91" t="n">
-        <v>14.17133284229286</v>
+        <v>11.39053161299989</v>
       </c>
       <c r="AC91" t="n">
         <v>5</v>
       </c>
       <c r="AD91" t="n">
-        <v>0.4397145250006673</v>
+        <v>4.493333333333327</v>
       </c>
       <c r="AE91" t="n">
         <v>39</v>
@@ -10736,7 +10748,7 @@
         <v>46282</v>
       </c>
       <c r="C92" t="n">
-        <v>1.062146892655367</v>
+        <v>1.088854648176682</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10764,22 +10776,22 @@
         <v>19.02065273936991</v>
       </c>
       <c r="K92" t="n">
-        <v>4.740680713128054</v>
+        <v>7.374392220421377</v>
       </c>
       <c r="L92" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="M92" t="n">
-        <v>62.5</v>
+        <v>64.70588235294117</v>
       </c>
       <c r="N92" t="n">
-        <v>12.63039748365475</v>
+        <v>11.91139454291524</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>3.111798839458402</v>
+        <v>0.5826415094339898</v>
       </c>
       <c r="Q92" t="n">
         <v>44</v>
@@ -10845,7 +10857,7 @@
         <v>46282</v>
       </c>
       <c r="C93" t="n">
-        <v>0.03882896764252697</v>
+        <v>0.03903441191576785</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10873,22 +10885,22 @@
         <v>13.488285987287</v>
       </c>
       <c r="K93" t="n">
-        <v>2.120397418129549</v>
+        <v>2.660716981188438</v>
       </c>
       <c r="L93" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M93" t="n">
-        <v>57.57575757575758</v>
+        <v>58.46153846153846</v>
       </c>
       <c r="N93" t="n">
-        <v>18.39462105831583</v>
+        <v>17.93657452806584</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>3.799047673096601</v>
+        <v>3.252736895869779</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10954,7 +10966,7 @@
         <v>46282</v>
       </c>
       <c r="C94" t="n">
-        <v>8.438623523369287</v>
+        <v>8.443759630200308</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10982,16 +10994,16 @@
         <v>10.47530442381612</v>
       </c>
       <c r="K94" t="n">
-        <v>8.04791747700917</v>
+        <v>8.113680056118721</v>
       </c>
       <c r="L94" t="n">
         <v>19</v>
       </c>
       <c r="M94" t="n">
-        <v>47.36842105263158</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N94" t="n">
-        <v>14.1134274536275</v>
+        <v>14.30891523166163</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
@@ -11024,7 +11036,7 @@
         <v>30.64601732980787</v>
       </c>
       <c r="Y94" t="n">
-        <v>3.270430802301161</v>
+        <v>3.211557053550296</v>
       </c>
       <c r="Z94" t="n">
         <v>16</v>
@@ -11039,7 +11051,7 @@
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>2.821856047058446</v>
+        <v>2.880966840217147</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -11182,7 +11194,7 @@
         <v>46282</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1210066769388803</v>
+        <v>0.1234720082177709</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11210,22 +11222,22 @@
         <v>11.75188607616355</v>
       </c>
       <c r="K96" t="n">
-        <v>1.861452744147951</v>
+        <v>3.93672852161786</v>
       </c>
       <c r="L96" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="M96" t="n">
-        <v>54.92957746478874</v>
+        <v>50.87719298245614</v>
       </c>
       <c r="N96" t="n">
-        <v>13.14156559941216</v>
+        <v>14.16762232896863</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>7.989820522483781</v>
+        <v>5.833617783266143</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11291,7 +11303,7 @@
         <v>46282</v>
       </c>
       <c r="C97" t="n">
-        <v>1.784283513097072</v>
+        <v>1.837699024139702</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11319,16 +11331,16 @@
         <v>19.39456900406833</v>
       </c>
       <c r="K97" t="n">
-        <v>5.421369213188809</v>
+        <v>8.57733420978397</v>
       </c>
       <c r="L97" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="M97" t="n">
-        <v>46.15384615384615</v>
+        <v>40</v>
       </c>
       <c r="N97" t="n">
-        <v>11.70571747402433</v>
+        <v>9.464468407632657</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11400,7 +11412,7 @@
         <v>46282</v>
       </c>
       <c r="C98" t="n">
-        <v>0.668104776579353</v>
+        <v>0.6833076527991783</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11428,22 +11440,22 @@
         <v>20.0091805261642</v>
       </c>
       <c r="K98" t="n">
-        <v>6.579363620237966</v>
+        <v>9.00460129179319</v>
       </c>
       <c r="L98" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="M98" t="n">
-        <v>52.38095238095238</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N98" t="n">
-        <v>16.88825880427897</v>
+        <v>17.43898315702185</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>3.209473451117995</v>
+        <v>0.9131712757172838</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11470,10 +11482,10 @@
         <v>30.85778357900837</v>
       </c>
       <c r="Y98" t="n">
-        <v>14.74629365017242</v>
+        <v>12.80632616250722</v>
       </c>
       <c r="Z98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA98" t="inlineStr"/>
       <c r="AB98" t="inlineStr"/>
@@ -11515,21 +11527,21 @@
         <v>46282</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4897791474062661</v>
+        <v>0.4971751412429379</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -11543,22 +11555,22 @@
         <v>18.77251112788727</v>
       </c>
       <c r="K99" t="n">
-        <v>2.894017362325263</v>
+        <v>4.447786080883853</v>
       </c>
       <c r="L99" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="M99" t="n">
-        <v>49.01960784313726</v>
+        <v>57.89473684210526</v>
       </c>
       <c r="N99" t="n">
-        <v>17.37652325273918</v>
+        <v>17.06738541524516</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>1.07487555256025</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>34</v>
@@ -11585,7 +11597,7 @@
         <v>33.04241514445872</v>
       </c>
       <c r="Y99" t="n">
-        <v>16.42177349694751</v>
+        <v>15.15968618398196</v>
       </c>
       <c r="Z99" t="n">
         <v>0</v>
@@ -11749,7 +11761,7 @@
         <v>46282</v>
       </c>
       <c r="C101" t="n">
-        <v>329.6686183872625</v>
+        <v>336.8864920390345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11777,16 +11789,16 @@
         <v>12.87023644471203</v>
       </c>
       <c r="K101" t="n">
-        <v>4.685097289186735</v>
+        <v>6.977107396649251</v>
       </c>
       <c r="L101" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M101" t="n">
-        <v>48.27586206896552</v>
+        <v>47.82608695652174</v>
       </c>
       <c r="N101" t="n">
-        <v>8.71415599283568</v>
+        <v>8.232394468922378</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11967,16 +11979,16 @@
         <v>46282</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7042629686697484</v>
+        <v>0.7256291730868003</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -11984,7 +11996,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H103" t="n">
         <v>5</v>
       </c>
@@ -11995,22 +12011,22 @@
         <v>18.80410934045254</v>
       </c>
       <c r="K103" t="n">
-        <v>9.756525233285007</v>
+        <v>13.08636147140103</v>
       </c>
       <c r="L103" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M103" t="n">
-        <v>56.25</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="N103" t="n">
-        <v>20.79805992900338</v>
+        <v>14.82383750962397</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
       </c>
       <c r="P103" t="n">
-        <v>0.2218317008464865</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
         <v>43</v>
@@ -12034,25 +12050,25 @@
         <v>67.69230769230769</v>
       </c>
       <c r="X103" t="n">
-        <v>11.33888240947563</v>
+        <v>13.08636147140103</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.421208064915813</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="AA103" t="n">
-        <v>32.14285714285715</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="AB103" t="n">
-        <v>11.39555378317706</v>
+        <v>10.42210671372402</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
       </c>
       <c r="AD103" t="n">
-        <v>6.673638219685662</v>
+        <v>7.999999999999996</v>
       </c>
       <c r="AE103" t="n">
         <v>32</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -444,7 +444,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -670,7 +670,7 @@
         <v>46282</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3923985618900874</v>
+        <v>0.3920335794563988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>22.3316078451137</v>
       </c>
       <c r="K2" t="n">
-        <v>8.048624112331249</v>
+        <v>7.94812463650425</v>
       </c>
       <c r="L2" t="n">
         <v>10</v>
@@ -713,7 +713,7 @@
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>1.806016415017031</v>
+        <v>1.900797601074666</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -779,7 +779,7 @@
         <v>46282</v>
       </c>
       <c r="C3" t="n">
-        <v>0.697688733025167</v>
+        <v>0.7166735706629459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,16 +807,16 @@
         <v>16.52890779617068</v>
       </c>
       <c r="K3" t="n">
-        <v>10.97631617328578</v>
+        <v>13.99609740875636</v>
       </c>
       <c r="L3" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
-        <v>56.52173913043478</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="N3" t="n">
-        <v>13.61056402226099</v>
+        <v>13.91823412431131</v>
       </c>
       <c r="O3" t="n">
         <v>8</v>
@@ -849,22 +849,22 @@
         <v>17.17248092970491</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.288071659194782</v>
+        <v>2.710861369278461</v>
       </c>
       <c r="Z3" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="AA3" t="n">
-        <v>37.5</v>
+        <v>34.88372093023256</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.72478051794883</v>
+        <v>13.25827481325848</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.975010458925643</v>
+        <v>7.492242950560779</v>
       </c>
       <c r="AE3" t="n">
         <v>34</v>
@@ -898,7 +898,7 @@
         <v>46282</v>
       </c>
       <c r="C4" t="n">
-        <v>1.473035439137134</v>
+        <v>1.470125991793388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,11 +915,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>5</v>
       </c>
@@ -930,16 +926,16 @@
         <v>18.01811637499802</v>
       </c>
       <c r="K4" t="n">
-        <v>14.1253026817143</v>
+        <v>13.89988953148073</v>
       </c>
       <c r="L4" t="n">
         <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="N4" t="n">
-        <v>18.60812358619205</v>
+        <v>21.99783982695302</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -969,25 +965,25 @@
         <v>62.5</v>
       </c>
       <c r="X4" t="n">
-        <v>14.1253026817143</v>
+        <v>14.13866364625549</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>0.2091965221485137</v>
       </c>
       <c r="Z4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA4" t="n">
-        <v>43.54838709677419</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.69249888820733</v>
+        <v>12.81285984640327</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>9.999999999999998</v>
+        <v>9.811328435715572</v>
       </c>
       <c r="AE4" t="n">
         <v>39</v>
@@ -1021,7 +1017,7 @@
         <v>46282</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2278376990241397</v>
+        <v>0.22848078504769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,7 +1045,7 @@
         <v>21.7133291595898</v>
       </c>
       <c r="K5" t="n">
-        <v>8.78770257359054</v>
+        <v>9.09476260517823</v>
       </c>
       <c r="L5" t="n">
         <v>20</v>
@@ -1058,7 +1054,7 @@
         <v>55</v>
       </c>
       <c r="N5" t="n">
-        <v>12.04334207013304</v>
+        <v>11.81190499200247</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -1130,7 +1126,7 @@
         <v>46282</v>
       </c>
       <c r="C6" t="n">
-        <v>1.410374935798665</v>
+        <v>1.407458087283017</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,10 +1151,10 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>38.01799643637762</v>
+        <v>38.01073584402899</v>
       </c>
       <c r="K6" t="n">
-        <v>12.26492232215863</v>
+        <v>12.01962107293508</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -1235,7 +1231,7 @@
         <v>46282</v>
       </c>
       <c r="C7" t="n">
-        <v>2.241397021058038</v>
+        <v>2.249878256313728</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,7 +1259,7 @@
         <v>15.68018152056624</v>
       </c>
       <c r="K7" t="n">
-        <v>7.443744028539578</v>
+        <v>7.850301037983631</v>
       </c>
       <c r="L7" t="n">
         <v>27</v>
@@ -1272,13 +1268,13 @@
         <v>70.37037037037037</v>
       </c>
       <c r="N7" t="n">
-        <v>13.57832933825642</v>
+        <v>13.65465917798175</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5177183432035548</v>
+        <v>0.1388025444302166</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1305,13 +1301,13 @@
         <v>18.9234494530097</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.403630067627978</v>
+        <v>9.060821935249319</v>
       </c>
       <c r="Z7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>60</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="AB7" t="n">
         <v>13.12838423287637</v>
@@ -1354,7 +1350,7 @@
         <v>46282</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3009758602978942</v>
+        <v>0.3016275205492949</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,10 +1375,10 @@
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>30.96043286594978</v>
+        <v>30.95234632522249</v>
       </c>
       <c r="K8" t="n">
-        <v>6.159420289855078</v>
+        <v>6.37681237597143</v>
       </c>
       <c r="L8" t="n">
         <v>4</v>
@@ -1391,13 +1387,13 @@
         <v>50</v>
       </c>
       <c r="N8" t="n">
-        <v>11.3421540561739</v>
+        <v>10.50913721135396</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>1.733788395904434</v>
+        <v>1.525884812464295</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1463,7 +1459,7 @@
         <v>46282</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5427837699024141</v>
+        <v>0.5407926484814162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,16 +1487,16 @@
         <v>17.6457098380072</v>
       </c>
       <c r="K9" t="n">
-        <v>5.975920884242858</v>
+        <v>5.587164001883371</v>
       </c>
       <c r="L9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M9" t="n">
-        <v>61.53846153846154</v>
+        <v>62.5</v>
       </c>
       <c r="N9" t="n">
-        <v>9.341279069049643</v>
+        <v>9.71639099143081</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1572,7 +1568,7 @@
         <v>46282</v>
       </c>
       <c r="C10" t="n">
-        <v>1.844889573703133</v>
+        <v>1.844078296841618</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,22 +1596,22 @@
         <v>15.9903344514868</v>
       </c>
       <c r="K10" t="n">
-        <v>5.790561697091734</v>
+        <v>5.744041061876004</v>
       </c>
       <c r="L10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M10" t="n">
-        <v>51.51515151515152</v>
+        <v>51.42857142857143</v>
       </c>
       <c r="N10" t="n">
-        <v>9.876644813116769</v>
+        <v>10.33659719937111</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>3.979030109473358</v>
+        <v>4.02477425241734</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1681,7 +1677,7 @@
         <v>46282</v>
       </c>
       <c r="C11" t="n">
-        <v>7.80688238315357</v>
+        <v>7.802659980229574</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,16 +1705,16 @@
         <v>16.80962533618998</v>
       </c>
       <c r="K11" t="n">
-        <v>9.307814945849181</v>
+        <v>9.248695105842518</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M11" t="n">
-        <v>56.66666666666666</v>
+        <v>54.83870967741935</v>
       </c>
       <c r="N11" t="n">
-        <v>11.76712508191444</v>
+        <v>11.78285485434354</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1748,10 +1744,10 @@
         <v>61.19402985074627</v>
       </c>
       <c r="X11" t="n">
-        <v>10.2426844157808</v>
+        <v>10.25559552156457</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.8480104370515384</v>
+        <v>0.9132420091324089</v>
       </c>
       <c r="Z11" t="n">
         <v>51</v>
@@ -1760,13 +1756,13 @@
         <v>45.09803921568628</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.75629325911953</v>
+        <v>10.70569028601007</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.161842105263156</v>
+        <v>1.0967741935484</v>
       </c>
       <c r="AE11" t="n">
         <v>48</v>
@@ -1800,7 +1796,7 @@
         <v>46282</v>
       </c>
       <c r="C12" t="n">
-        <v>5.279917822290704</v>
+        <v>5.2497159313987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,11 +1813,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>5</v>
       </c>
@@ -1829,20 +1821,16 @@
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>33.96593120498892</v>
+        <v>33.95819760477713</v>
       </c>
       <c r="K12" t="n">
-        <v>7.576394542553411</v>
+        <v>6.94851675339454</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M12" t="n">
-        <v>100</v>
-      </c>
-      <c r="N12" t="n">
-        <v>10.57818638012683</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
         <v>5</v>
       </c>
@@ -1913,7 +1901,7 @@
         <v>46282</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1438109912686184</v>
+        <v>0.1428004881635027</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,10 +1926,10 @@
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>54.5022714277213</v>
+        <v>54.4969426760356</v>
       </c>
       <c r="K13" t="n">
-        <v>4.321907600596142</v>
+        <v>3.576747668692981</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1952,7 +1940,7 @@
         <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>1.608571428571426</v>
+        <v>2.33957175316819</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -2006,7 +1994,7 @@
         <v>46282</v>
       </c>
       <c r="C14" t="n">
-        <v>8.618387262455059</v>
+        <v>8.588576357435054</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2034,16 +2022,16 @@
         <v>10.97257403209156</v>
       </c>
       <c r="K14" t="n">
-        <v>7.520130624155508</v>
+        <v>7.148219696488267</v>
       </c>
       <c r="L14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M14" t="n">
-        <v>44</v>
+        <v>48.14814814814815</v>
       </c>
       <c r="N14" t="n">
-        <v>11.74722695280736</v>
+        <v>10.713405803398</v>
       </c>
       <c r="O14" t="n">
         <v>2</v>
@@ -2076,16 +2064,16 @@
         <v>16.11612055393703</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.277595307981519</v>
+        <v>4.608698033777037</v>
       </c>
       <c r="Z14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA14" t="n">
-        <v>37.03703703703704</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.83608271177326</v>
+        <v>12.59720226487137</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2125,7 +2113,7 @@
         <v>46282</v>
       </c>
       <c r="C15" t="n">
-        <v>13.60041088854648</v>
+        <v>13.68419103840131</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2153,16 +2141,16 @@
         <v>20.43038307058605</v>
       </c>
       <c r="K15" t="n">
-        <v>8.125715037916571</v>
+        <v>8.791782312153519</v>
       </c>
       <c r="L15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M15" t="n">
-        <v>71.42857142857143</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N15" t="n">
-        <v>17.52537808654624</v>
+        <v>15.61607838434473</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
@@ -2195,7 +2183,7 @@
         <v>33.58229315482664</v>
       </c>
       <c r="Y15" t="n">
-        <v>13.96478274214005</v>
+        <v>13.43479556353752</v>
       </c>
       <c r="Z15" t="n">
         <v>7</v>
@@ -2244,7 +2232,7 @@
         <v>46282</v>
       </c>
       <c r="C16" t="n">
-        <v>33.24088341037493</v>
+        <v>33.20368275984461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2269,10 +2257,10 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>20.85493449406155</v>
+        <v>20.84566539545038</v>
       </c>
       <c r="K16" t="n">
-        <v>3.784477228992933</v>
+        <v>3.656189865298276</v>
       </c>
       <c r="L16" t="n">
         <v>36</v>
@@ -2281,13 +2269,13 @@
         <v>61.11111111111111</v>
       </c>
       <c r="N16" t="n">
-        <v>14.98778431551972</v>
+        <v>16.19174944747391</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>5.988875154511764</v>
+        <v>6.120049504950487</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2353,7 +2341,7 @@
         <v>46282</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3266563944530047</v>
+        <v>0.3266946431089913</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2378,10 +2366,10 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>58.07660480139403</v>
+        <v>58.07169493011239</v>
       </c>
       <c r="K17" t="n">
-        <v>2.389937181490609e-06</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2392,7 +2380,7 @@
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>7.999997418867921</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
@@ -2458,7 +2446,7 @@
         <v>46282</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0632768361581921</v>
+        <v>0.06390064979130475</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2483,16 +2471,16 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>41.94120981718441</v>
+        <v>41.93441024417237</v>
       </c>
       <c r="K18" t="n">
-        <v>1.650166022938948</v>
+        <v>2.640261742312822</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>40</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N18" t="n">
         <v>12.28395657351243</v>
@@ -2501,7 +2489,7 @@
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>8.214284642857139</v>
+        <v>7.170420391331844</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2567,7 +2555,7 @@
         <v>46282</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02588597842835131</v>
+        <v>0.02568354173874119</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,7 +2583,7 @@
         <v>16.0945098434464</v>
       </c>
       <c r="K19" t="n">
-        <v>4.089658964500331</v>
+        <v>3.275644302402747</v>
       </c>
       <c r="L19" t="n">
         <v>26</v>
@@ -2604,13 +2592,13 @@
         <v>57.69230769230769</v>
       </c>
       <c r="N19" t="n">
-        <v>22.95620354700146</v>
+        <v>24.49254697987282</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>5.678125083986862</v>
+        <v>6.511076007337779</v>
       </c>
       <c r="Q19" t="n">
         <v>14</v>
@@ -2637,16 +2625,16 @@
         <v>20.26411217973316</v>
       </c>
       <c r="Y19" t="n">
-        <v>12.66306144355097</v>
+        <v>13.34606443573016</v>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA19" t="n">
-        <v>62.5</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="AB19" t="n">
-        <v>17.32542942283422</v>
+        <v>10.82905106195671</v>
       </c>
       <c r="AC19" t="n">
         <v>10</v>
@@ -2686,7 +2674,7 @@
         <v>46282</v>
       </c>
       <c r="C20" t="n">
-        <v>1.652799178222907</v>
+        <v>1.651965436072488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2714,7 +2702,7 @@
         <v>19.82174384694231</v>
       </c>
       <c r="K20" t="n">
-        <v>7.797739795765857</v>
+        <v>7.743362034346446</v>
       </c>
       <c r="L20" t="n">
         <v>14</v>
@@ -2729,7 +2717,7 @@
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>2.042955824868464</v>
+        <v>2.094456607855055</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
@@ -2795,7 +2783,7 @@
         <v>46282</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8645095017976374</v>
+        <v>0.8650216543241483</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2811,7 @@
         <v>17.90453399434356</v>
       </c>
       <c r="K21" t="n">
-        <v>6.704210432339419</v>
+        <v>6.76742411691853</v>
       </c>
       <c r="L21" t="n">
         <v>33</v>
@@ -2838,7 +2826,7 @@
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>1.214375292605951</v>
+        <v>1.1544493962238</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2865,22 +2853,22 @@
         <v>11.00964066838261</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.878429125723182</v>
+        <v>3.821484806114095</v>
       </c>
       <c r="Z21" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AA21" t="n">
-        <v>35</v>
+        <v>34.14634146341464</v>
       </c>
       <c r="AB21" t="n">
-        <v>11.57440181663743</v>
+        <v>11.66619032230929</v>
       </c>
       <c r="AC21" t="n">
         <v>4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.126476162604372</v>
+        <v>0.1856081823742417</v>
       </c>
       <c r="AE21" t="n">
         <v>40</v>
@@ -2914,7 +2902,7 @@
         <v>46282</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2886492039034412</v>
+        <v>0.2907376846747536</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2946,22 +2934,22 @@
         <v>26.84577757624037</v>
       </c>
       <c r="K22" t="n">
-        <v>7.536416102488208</v>
+        <v>8.314480736683505</v>
       </c>
       <c r="L22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>12.26786550530817</v>
+        <v>12.48981676768944</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>2.290929888498305</v>
+        <v>1.55613474011298</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -2988,22 +2976,22 @@
         <v>10.71975172264199</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.875128936459481</v>
+        <v>2.172395573992802</v>
       </c>
       <c r="Z22" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA22" t="n">
-        <v>34.61538461538461</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="AB22" t="n">
-        <v>13.86583964828695</v>
+        <v>13.73881392598284</v>
       </c>
       <c r="AC22" t="n">
         <v>5</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.187772339126604</v>
+        <v>2.890395244366728</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3029,7 +3017,7 @@
         <v>46282</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5082691319979455</v>
+        <v>0.5017536730517946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3054,10 +3042,10 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>49.78021309444885</v>
+        <v>50.26314571687826</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3244120032441122</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3068,7 +3056,7 @@
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.660468876313684</v>
+        <v>5.000000000000004</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3134,7 +3122,7 @@
         <v>46282</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1265536723163842</v>
+        <v>0.1265684906064916</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,10 +3147,10 @@
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>35.83486174340565</v>
+        <v>35.82734702356686</v>
       </c>
       <c r="K24" t="n">
-        <v>2.435065016292981e-06</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>2</v>
@@ -3173,7 +3161,7 @@
         <v>10</v>
       </c>
       <c r="P24" t="n">
-        <v>9.999997321428555</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>5</v>
@@ -3239,7 +3227,7 @@
         <v>46282</v>
       </c>
       <c r="C25" t="n">
-        <v>3.235747303543914</v>
+        <v>3.223798033711111</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3267,7 +3255,7 @@
         <v>26.01552790938969</v>
       </c>
       <c r="K25" t="n">
-        <v>5.237705861490394</v>
+        <v>4.849074233010997</v>
       </c>
       <c r="L25" t="n">
         <v>19</v>
@@ -3276,13 +3264,13 @@
         <v>68.42105263157895</v>
       </c>
       <c r="N25" t="n">
-        <v>13.45008776986097</v>
+        <v>13.65276053951098</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>2.624814096712869</v>
+        <v>3.005201323939732</v>
       </c>
       <c r="Q25" t="n">
         <v>44</v>
@@ -3348,7 +3336,7 @@
         <v>46282</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4302003081664099</v>
+        <v>0.4286069570696814</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3376,22 +3364,22 @@
         <v>13.95841889083065</v>
       </c>
       <c r="K26" t="n">
-        <v>4.972112453720401</v>
+        <v>4.583322796137557</v>
       </c>
       <c r="L26" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M26" t="n">
-        <v>45.65217391304348</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="N26" t="n">
-        <v>14.09959491208586</v>
+        <v>13.64226975620035</v>
       </c>
       <c r="O26" t="n">
         <v>6</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9792005917121704</v>
+        <v>1.354591885193734</v>
       </c>
       <c r="Q26" t="n">
         <v>32</v>
@@ -3457,7 +3445,7 @@
         <v>46282</v>
       </c>
       <c r="C27" t="n">
-        <v>45.27991782229071</v>
+        <v>45.28522079374847</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3486,7 +3474,7 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>21.17713737983576</v>
+        <v>21.16790601611432</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3521,7 +3509,7 @@
         <v>59.36116514542724</v>
       </c>
       <c r="Y27" t="n">
-        <v>21.17713737983576</v>
+        <v>21.16790601611432</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -3556,7 +3544,7 @@
         <v>46282</v>
       </c>
       <c r="C28" t="n">
-        <v>1.31381612737545</v>
+        <v>1.321161449708689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3581,19 +3569,19 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>26.56379120725283</v>
+        <v>26.5551888271766</v>
       </c>
       <c r="K28" t="n">
-        <v>6.761268781302188</v>
+        <v>7.345578309870882</v>
       </c>
       <c r="L28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M28" t="n">
-        <v>58.8235294117647</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N28" t="n">
-        <v>15.8747128063225</v>
+        <v>15.82052131603536</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
@@ -3665,7 +3653,7 @@
         <v>46282</v>
       </c>
       <c r="C29" t="n">
-        <v>0.377195685670262</v>
+        <v>0.3737469102719835</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3693,10 +3681,10 @@
         <v>27.65210909859499</v>
       </c>
       <c r="K29" t="n">
-        <v>13.90342883975346</v>
+        <v>12.86198706805328</v>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3731,10 +3719,10 @@
         <v>31.20488584758381</v>
       </c>
       <c r="Y29" t="n">
-        <v>13.18659506927877</v>
+        <v>13.98034734837454</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
@@ -3776,7 +3764,7 @@
         <v>46282</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3981510015408321</v>
+        <v>0.3953210697169328</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3804,16 +3792,16 @@
         <v>21.04235192254695</v>
       </c>
       <c r="K30" t="n">
-        <v>8.70975219292005</v>
+        <v>7.93707753906161</v>
       </c>
       <c r="L30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M30" t="n">
-        <v>55.55555555555556</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N30" t="n">
-        <v>12.48817316107839</v>
+        <v>11.48365102803138</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
@@ -3846,7 +3834,7 @@
         <v>26.71344279693404</v>
       </c>
       <c r="Y30" t="n">
-        <v>14.16533643764289</v>
+        <v>14.77542217162011</v>
       </c>
       <c r="Z30" t="n">
         <v>4</v>
@@ -3895,7 +3883,7 @@
         <v>46282</v>
       </c>
       <c r="C31" t="n">
-        <v>0.257216230097586</v>
+        <v>0.2601229076479458</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3920,20 +3908,16 @@
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>17.90687778255445</v>
+        <v>17.8972608580232</v>
       </c>
       <c r="K31" t="n">
-        <v>14.96786042240588</v>
+        <v>16.25343851917638</v>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
-      </c>
-      <c r="M31" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="N31" t="n">
-        <v>18.41492698874927</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
         <v>10</v>
       </c>
@@ -3965,7 +3949,7 @@
         <v>56.41090041471573</v>
       </c>
       <c r="Y31" t="n">
-        <v>5.619293832652139</v>
+        <v>4.552742629022233</v>
       </c>
       <c r="Z31" t="n">
         <v>1</v>
@@ -3976,7 +3960,7 @@
         <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>4.641527220171849</v>
+        <v>5.707086322874366</v>
       </c>
       <c r="AE31" t="n">
         <v>10</v>
@@ -4010,7 +3994,7 @@
         <v>46282</v>
       </c>
       <c r="C32" t="n">
-        <v>2.29070364663585</v>
+        <v>2.290971923095714</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4038,7 +4022,7 @@
         <v>14.66599569135187</v>
       </c>
       <c r="K32" t="n">
-        <v>8.630039704604364</v>
+        <v>8.64276194500837</v>
       </c>
       <c r="L32" t="n">
         <v>27</v>
@@ -4080,13 +4064,13 @@
         <v>11.59844220999629</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.659896004467721</v>
+        <v>2.648495988345578</v>
       </c>
       <c r="Z32" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AA32" t="n">
-        <v>40.42553191489362</v>
+        <v>39.58333333333334</v>
       </c>
       <c r="AB32" t="n">
         <v>11.53490202973891</v>
@@ -4095,7 +4079,7 @@
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>5.4860265978115</v>
+        <v>5.497094334581377</v>
       </c>
       <c r="AE32" t="n">
         <v>26</v>
@@ -4129,7 +4113,7 @@
         <v>46282</v>
       </c>
       <c r="C33" t="n">
-        <v>1.77195685670262</v>
+        <v>1.761890963277646</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4157,16 +4141,16 @@
         <v>13.64170455604291</v>
       </c>
       <c r="K33" t="n">
-        <v>8.788316987551848</v>
+        <v>8.170326994998245</v>
       </c>
       <c r="L33" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M33" t="n">
-        <v>48.38709677419355</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N33" t="n">
-        <v>10.92054846451217</v>
+        <v>10.9883450025001</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
@@ -4238,7 +4222,7 @@
         <v>46282</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7498715973292245</v>
+        <v>0.742562546216917</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4266,16 +4250,16 @@
         <v>17.91852285443199</v>
       </c>
       <c r="K34" t="n">
-        <v>5.938096229200096</v>
+        <v>4.905510166682769</v>
       </c>
       <c r="L34" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M34" t="n">
-        <v>64</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N34" t="n">
-        <v>12.81179770458309</v>
+        <v>12.23954432356245</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4308,16 +4292,16 @@
         <v>11.67247563853926</v>
       </c>
       <c r="Y34" t="n">
-        <v>5.134998016789893</v>
+        <v>6.05965385218089</v>
       </c>
       <c r="Z34" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AA34" t="n">
-        <v>38.46153846153846</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="AB34" t="n">
-        <v>9.761702805601765</v>
+        <v>10.82707370702024</v>
       </c>
       <c r="AC34" t="n">
         <v>2</v>
@@ -4357,7 +4341,7 @@
         <v>46282</v>
       </c>
       <c r="C35" t="n">
-        <v>1.164869029275809</v>
+        <v>1.165005468884894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4382,7 +4366,7 @@
         <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>48.58068030402142</v>
+        <v>48.57465762533187</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -4462,7 +4446,7 @@
         <v>46282</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07005649717514124</v>
+        <v>0.06944829912170786</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4487,10 +4471,10 @@
         <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>21.12740158531219</v>
+        <v>21.1181667514496</v>
       </c>
       <c r="K36" t="n">
-        <v>1.791044776119399</v>
+        <v>0.8955286834486209</v>
       </c>
       <c r="L36" t="n">
         <v>23</v>
@@ -4499,13 +4483,13 @@
         <v>56.52173913043478</v>
       </c>
       <c r="N36" t="n">
-        <v>12.70701001702191</v>
+        <v>14.82977244487345</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>0.2052785923753797</v>
+        <v>1.094668248398367</v>
       </c>
       <c r="Q36" t="n">
         <v>10</v>
@@ -4571,7 +4555,7 @@
         <v>46282</v>
       </c>
       <c r="C37" t="n">
-        <v>0.05382639958911146</v>
+        <v>0.05403817407846314</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4588,11 +4572,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>5</v>
       </c>
@@ -4603,22 +4583,22 @@
         <v>28.89715284260867</v>
       </c>
       <c r="K37" t="n">
-        <v>3.514979506468863</v>
+        <v>3.922248654927141</v>
       </c>
       <c r="L37" t="n">
         <v>16</v>
       </c>
       <c r="M37" t="n">
-        <v>75</v>
+        <v>68.75</v>
       </c>
       <c r="N37" t="n">
-        <v>16.50507586539958</v>
+        <v>16.92641827120465</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>6.264813580073092</v>
+        <v>5.848363968002634</v>
       </c>
       <c r="Q37" t="n">
         <v>27</v>
@@ -4684,7 +4664,7 @@
         <v>46282</v>
       </c>
       <c r="C38" t="n">
-        <v>1.596302003081664</v>
+        <v>1.591352183464562</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4712,22 +4692,22 @@
         <v>15.42052714918329</v>
       </c>
       <c r="K38" t="n">
-        <v>7.797686528420278</v>
+        <v>7.463427032142955</v>
       </c>
       <c r="L38" t="n">
         <v>31</v>
       </c>
       <c r="M38" t="n">
-        <v>64.51612903225806</v>
+        <v>61.29032258064516</v>
       </c>
       <c r="N38" t="n">
-        <v>10.93042466995157</v>
+        <v>11.24487615979568</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>2.043006248560908</v>
+        <v>2.360405803081589</v>
       </c>
       <c r="Q38" t="n">
         <v>42</v>
@@ -4793,7 +4773,7 @@
         <v>46282</v>
       </c>
       <c r="C39" t="n">
-        <v>2.730354391371341</v>
+        <v>2.722455424306566</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4821,16 +4801,16 @@
         <v>15.16246653075239</v>
       </c>
       <c r="K39" t="n">
-        <v>12.77221338547541</v>
+        <v>12.44596123221329</v>
       </c>
       <c r="L39" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M39" t="n">
-        <v>70.58823529411765</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N39" t="n">
-        <v>13.3783564311</v>
+        <v>13.67042644814202</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4860,25 +4840,25 @@
         <v>67.69230769230769</v>
       </c>
       <c r="X39" t="n">
-        <v>12.77221338547541</v>
+        <v>12.7854155610625</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>0.3009736029792154</v>
       </c>
       <c r="Z39" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AA39" t="n">
-        <v>38.80597014925373</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="AB39" t="n">
-        <v>11.59044072703114</v>
+        <v>12.20529778138521</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>6.000000000000005</v>
+        <v>5.716230742641526</v>
       </c>
       <c r="AE39" t="n">
         <v>40</v>
@@ -4912,7 +4892,7 @@
         <v>46282</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1855161787365177</v>
+        <v>0.1849215005189366</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4937,10 +4917,10 @@
         <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>29.83357657172154</v>
+        <v>29.82535900952999</v>
       </c>
       <c r="K40" t="n">
-        <v>0.3333333333333188</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>11</v>
@@ -4955,7 +4935,7 @@
         <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>2.657807308970117</v>
+        <v>3.000000000000003</v>
       </c>
       <c r="Q40" t="n">
         <v>29</v>
@@ -5021,7 +5001,7 @@
         <v>46282</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9873651771956857</v>
+        <v>0.9874808409202831</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5046,7 +5026,7 @@
         <v>10</v>
       </c>
       <c r="J41" t="n">
-        <v>51.10673081311258</v>
+        <v>51.10100326898552</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -5126,7 +5106,7 @@
         <v>46282</v>
       </c>
       <c r="C42" t="n">
-        <v>2.828967642526965</v>
+        <v>2.829298895271888</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5155,7 +5135,7 @@
         <v>10</v>
       </c>
       <c r="J42" t="n">
-        <v>26.85119801730374</v>
+        <v>26.84263279333992</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -5235,7 +5215,7 @@
         <v>46282</v>
       </c>
       <c r="C43" t="n">
-        <v>5.675398048279405</v>
+        <v>5.670926015914056</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5267,7 +5247,7 @@
         <v>26.64182087935456</v>
       </c>
       <c r="K43" t="n">
-        <v>3.132425651184989</v>
+        <v>3.0511605942664</v>
       </c>
       <c r="L43" t="n">
         <v>9</v>
@@ -5282,7 +5262,7 @@
         <v>10</v>
       </c>
       <c r="P43" t="n">
-        <v>6.658986546134926</v>
+        <v>6.74309669649682</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5309,7 +5289,7 @@
         <v>10.08403361344536</v>
       </c>
       <c r="Y43" t="n">
-        <v>6.314819446633491</v>
+        <v>6.38864037620076</v>
       </c>
       <c r="Z43" t="n">
         <v>13</v>
@@ -5358,7 +5338,7 @@
         <v>46282</v>
       </c>
       <c r="C44" t="n">
-        <v>3.667180277349769</v>
+        <v>3.667609760292242</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5383,7 +5363,7 @@
         <v>10</v>
       </c>
       <c r="J44" t="n">
-        <v>28.54575647949613</v>
+        <v>28.53738809385965</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -5459,7 +5439,7 @@
         <v>46282</v>
       </c>
       <c r="C45" t="n">
-        <v>0.01992809450436569</v>
+        <v>0.01993042900566817</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5484,10 +5464,10 @@
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>19.70854733084767</v>
+        <v>19.69914397275242</v>
       </c>
       <c r="K45" t="n">
-        <v>2.105264232686999</v>
+        <v>2.105267390581766</v>
       </c>
       <c r="L45" t="n">
         <v>54</v>
@@ -5502,7 +5482,7 @@
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>7.731957628865982</v>
+        <v>7.731954296949861</v>
       </c>
       <c r="Q45" t="n">
         <v>38</v>
@@ -5568,7 +5548,7 @@
         <v>46282</v>
       </c>
       <c r="C46" t="n">
-        <v>8.695428864920391</v>
+        <v>8.819728233083724</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5585,7 +5565,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H46" t="n">
         <v>5</v>
       </c>
@@ -5593,19 +5577,19 @@
         <v>10</v>
       </c>
       <c r="J46" t="n">
-        <v>28.15632518747767</v>
+        <v>28.14791119347603</v>
       </c>
       <c r="K46" t="n">
-        <v>11.6754617414248</v>
+        <v>13.25857519788918</v>
       </c>
       <c r="L46" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M46" t="n">
-        <v>57.14285714285715</v>
+        <v>100</v>
       </c>
       <c r="N46" t="n">
-        <v>9.859569556306326</v>
+        <v>26.46943788476914</v>
       </c>
       <c r="O46" t="n">
         <v>8</v>
@@ -5677,7 +5661,7 @@
         <v>46282</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9972265023112481</v>
+        <v>0.9821386204738698</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5705,22 +5689,22 @@
         <v>18.95305070442179</v>
       </c>
       <c r="K47" t="n">
-        <v>9.625302325739415</v>
+        <v>7.96668855640601</v>
       </c>
       <c r="L47" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M47" t="n">
-        <v>56.25</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N47" t="n">
-        <v>14.77409691035926</v>
+        <v>17.05870831769058</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>0.3417985321921613</v>
+        <v>1.883276657625488</v>
       </c>
       <c r="Q47" t="n">
         <v>51</v>
@@ -5747,7 +5731,7 @@
         <v>66.65983471422588</v>
       </c>
       <c r="Y47" t="n">
-        <v>11.15203680893366</v>
+        <v>12.49629266957479</v>
       </c>
       <c r="Z47" t="n">
         <v>2</v>
@@ -5792,7 +5776,7 @@
         <v>46282</v>
       </c>
       <c r="C48" t="n">
-        <v>0.04992295839753468</v>
+        <v>0.04992880657839122</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5817,10 +5801,10 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>27.02915304173016</v>
+        <v>27.02060703861709</v>
       </c>
       <c r="K48" t="n">
-        <v>8.000000000000007</v>
+        <v>8.000003111111109</v>
       </c>
       <c r="L48" t="n">
         <v>15</v>
@@ -5835,7 +5819,7 @@
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>1.85185185185186</v>
+        <v>1.851848917847976</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5901,7 +5885,7 @@
         <v>46282</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2761171032357473</v>
+        <v>0.2747111601774241</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5929,16 +5913,16 @@
         <v>18.76252681801688</v>
       </c>
       <c r="K49" t="n">
-        <v>11.67502961476834</v>
+        <v>11.10639865770351</v>
       </c>
       <c r="L49" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M49" t="n">
-        <v>47.61904761904762</v>
+        <v>45</v>
       </c>
       <c r="N49" t="n">
-        <v>17.29347668086765</v>
+        <v>14.92483544763925</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
@@ -5968,25 +5952,25 @@
         <v>67.14285714285714</v>
       </c>
       <c r="X49" t="n">
-        <v>11.67502961476834</v>
+        <v>11.68810497984585</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>0.5208310430616758</v>
       </c>
       <c r="Z49" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AA49" t="n">
-        <v>42</v>
+        <v>39.28571428571428</v>
       </c>
       <c r="AB49" t="n">
-        <v>10.48534602744506</v>
+        <v>10.20021926404256</v>
       </c>
       <c r="AC49" t="n">
         <v>10</v>
       </c>
       <c r="AD49" t="n">
-        <v>9.999999999999998</v>
+        <v>9.528797894402985</v>
       </c>
       <c r="AE49" t="n">
         <v>44</v>
@@ -6020,7 +6004,7 @@
         <v>46282</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7194658448895738</v>
+        <v>0.7133860804024121</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6048,16 +6032,16 @@
         <v>16.75569689884803</v>
       </c>
       <c r="K50" t="n">
-        <v>12.05404663271514</v>
+        <v>11.10714662599572</v>
       </c>
       <c r="L50" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M50" t="n">
-        <v>55</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N50" t="n">
-        <v>16.58862239127276</v>
+        <v>15.92581263012463</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
@@ -6087,25 +6071,25 @@
         <v>70</v>
       </c>
       <c r="X50" t="n">
-        <v>13.14194999808132</v>
+        <v>13.15520260429783</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.9615384615384581</v>
+        <v>1.809952994794362</v>
       </c>
       <c r="Z50" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AA50" t="n">
-        <v>46.15384615384615</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="AB50" t="n">
-        <v>12.98504755739105</v>
+        <v>13.02416954739634</v>
       </c>
       <c r="AC50" t="n">
         <v>5</v>
       </c>
       <c r="AD50" t="n">
-        <v>4.077669902912628</v>
+        <v>3.248849656866459</v>
       </c>
       <c r="AE50" t="n">
         <v>42</v>
@@ -6139,7 +6123,7 @@
         <v>46282</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1099126861838726</v>
+        <v>0.109925556587129</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6164,10 +6148,10 @@
         <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>43.5748011217725</v>
+        <v>43.56819286730693</v>
       </c>
       <c r="K51" t="n">
-        <v>1.869158894329814e-06</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
         <v>1</v>
@@ -6178,7 +6162,7 @@
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>3.999998056074783</v>
+        <v>4.000000000000004</v>
       </c>
       <c r="Q51" t="n">
         <v>13</v>
@@ -6244,7 +6228,7 @@
         <v>46282</v>
       </c>
       <c r="C52" t="n">
-        <v>4.519774011299435</v>
+        <v>4.493592399942317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6272,22 +6256,22 @@
         <v>14.1037450661144</v>
       </c>
       <c r="K52" t="n">
-        <v>9.68083019569721</v>
+        <v>9.045484078318179</v>
       </c>
       <c r="L52" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M52" t="n">
-        <v>70.83333333333333</v>
+        <v>65.21739130434783</v>
       </c>
       <c r="N52" t="n">
-        <v>11.73973172536463</v>
+        <v>11.9939935339122</v>
       </c>
       <c r="O52" t="n">
         <v>10</v>
       </c>
       <c r="P52" t="n">
-        <v>0.2909987130233382</v>
+        <v>0.8753374151618143</v>
       </c>
       <c r="Q52" t="n">
         <v>37</v>
@@ -6314,22 +6298,22 @@
         <v>16.53731163255363</v>
       </c>
       <c r="Y52" t="n">
-        <v>5.788274481501743</v>
+        <v>6.334013002198191</v>
       </c>
       <c r="Z52" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AA52" t="n">
-        <v>66.66666666666667</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="AB52" t="n">
-        <v>13.01254235891325</v>
+        <v>13.01782768349203</v>
       </c>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.347611729140853</v>
+        <v>1.778646711789733</v>
       </c>
       <c r="AE52" t="n">
         <v>37</v>
@@ -6363,7 +6347,7 @@
         <v>46282</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9668207498715974</v>
+        <v>0.9665230616153951</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6388,10 +6372,10 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>43.76916435099497</v>
+        <v>43.76257775955705</v>
       </c>
       <c r="K53" t="n">
-        <v>0.04251700680271142</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
@@ -6402,7 +6386,7 @@
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>7.954101147471326</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6460,7 +6444,7 @@
         <v>46282</v>
       </c>
       <c r="C54" t="n">
-        <v>0.06471494812532101</v>
+        <v>0.06472252723631114</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6488,7 +6472,7 @@
         <v>28.78472294046982</v>
       </c>
       <c r="K54" t="n">
-        <v>3.102792408311417</v>
+        <v>3.114867323453763</v>
       </c>
       <c r="L54" t="n">
         <v>19</v>
@@ -6503,7 +6487,7 @@
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>6.689641890952891</v>
+        <v>6.67714836401696</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6530,7 +6514,7 @@
         <v>14.75410024187049</v>
       </c>
       <c r="Y54" t="n">
-        <v>10.15328237422565</v>
+        <v>10.14275994834552</v>
       </c>
       <c r="Z54" t="n">
         <v>21</v>
@@ -6579,7 +6563,7 @@
         <v>46282</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9064201335387776</v>
+        <v>0.9057044534756745</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6607,13 +6591,13 @@
         <v>18.57198344066605</v>
       </c>
       <c r="K55" t="n">
-        <v>11.3685998906818</v>
+        <v>11.28066684104148</v>
       </c>
       <c r="L55" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M55" t="n">
-        <v>66.66666666666667</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="N55" t="n">
         <v>10.39215044032665</v>
@@ -6649,16 +6633,16 @@
         <v>23.0932342837701</v>
       </c>
       <c r="Y55" t="n">
-        <v>9.314758039117255</v>
+        <v>9.386360177339515</v>
       </c>
       <c r="Z55" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA55" t="n">
-        <v>35.29411764705883</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB55" t="n">
-        <v>9.409062864639326</v>
+        <v>9.513128641038493</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
@@ -6698,7 +6682,7 @@
         <v>46282</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5078582434514638</v>
+        <v>0.5079177072480308</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6723,10 +6707,10 @@
         <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>64.6750754186144</v>
+        <v>64.67093832924205</v>
       </c>
       <c r="K56" t="n">
-        <v>2.791262221357727e-06</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
@@ -6737,7 +6721,7 @@
         <v>4</v>
       </c>
       <c r="P56" t="n">
-        <v>3.999997097087382</v>
+        <v>4.000000000000004</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -6787,7 +6771,7 @@
         <v>46282</v>
       </c>
       <c r="C57" t="n">
-        <v>1.159732922444787</v>
+        <v>1.159868760537146</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6816,7 +6800,7 @@
         <v>10</v>
       </c>
       <c r="J57" t="n">
-        <v>23.84614040594677</v>
+        <v>23.83722059793512</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -6900,7 +6884,7 @@
         <v>46282</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6216743708269132</v>
+        <v>0.6217471831372184</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6929,7 +6913,7 @@
         <v>10</v>
       </c>
       <c r="J58" t="n">
-        <v>21.9059616006776</v>
+        <v>21.8968149997821</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -7013,7 +6997,7 @@
         <v>46282</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7704160246533128</v>
+        <v>0.775026580575391</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7032,7 +7016,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %90.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -7045,16 +7029,16 @@
         <v>17.69918671275772</v>
       </c>
       <c r="K59" t="n">
-        <v>12.56657942329109</v>
+        <v>13.24023429647689</v>
       </c>
       <c r="L59" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M59" t="n">
-        <v>78.57142857142857</v>
+        <v>90</v>
       </c>
       <c r="N59" t="n">
-        <v>12.69156947560585</v>
+        <v>13.25416669446671</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
@@ -7084,25 +7068,25 @@
         <v>65.51724137931035</v>
       </c>
       <c r="X59" t="n">
-        <v>12.98682798647137</v>
+        <v>13.24023429647689</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.3719447396386744</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="AA59" t="n">
-        <v>48.27586206896552</v>
+        <v>41.50943396226415</v>
       </c>
       <c r="AB59" t="n">
-        <v>13.72491834223873</v>
+        <v>13.01623925622412</v>
       </c>
       <c r="AC59" t="n">
         <v>6</v>
       </c>
       <c r="AD59" t="n">
-        <v>5.64906666666668</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="AE59" t="n">
         <v>42</v>
@@ -7136,7 +7120,7 @@
         <v>46282</v>
       </c>
       <c r="C60" t="n">
-        <v>10.78582434514638</v>
+        <v>10.7768141135758</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7168,7 +7152,7 @@
         <v>29.37042877474947</v>
       </c>
       <c r="K60" t="n">
-        <v>8.538858592409305</v>
+        <v>8.448187706343591</v>
       </c>
       <c r="L60" t="n">
         <v>5</v>
@@ -7249,7 +7233,7 @@
         <v>46282</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5772984078068825</v>
+        <v>0.5773660260946987</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7274,7 +7258,7 @@
         <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>30.50752140313542</v>
+        <v>30.49938183033342</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -7319,7 +7303,7 @@
         <v>49.99145178651283</v>
       </c>
       <c r="Y61" t="n">
-        <v>30.50752140313542</v>
+        <v>30.49938183033342</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -7364,7 +7348,7 @@
         <v>46282</v>
       </c>
       <c r="C62" t="n">
-        <v>8.931689779147407</v>
+        <v>8.937872525081934</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7421,10 +7405,10 @@
         <v>72.05882352941177</v>
       </c>
       <c r="X62" t="n">
-        <v>12.69355362364248</v>
+        <v>12.70675176372491</v>
       </c>
       <c r="Y62" t="n">
-        <v>4.607789358200765</v>
+        <v>4.552934722984093</v>
       </c>
       <c r="Z62" t="n">
         <v>47</v>
@@ -7433,13 +7417,13 @@
         <v>46.80851063829788</v>
       </c>
       <c r="AB62" t="n">
-        <v>15.91397725010352</v>
+        <v>16.00314046821093</v>
       </c>
       <c r="AC62" t="n">
         <v>5</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.4111558366877599</v>
+        <v>0.468390804597707</v>
       </c>
       <c r="AE62" t="n">
         <v>27</v>
@@ -7473,7 +7457,7 @@
         <v>46282</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0967642526964561</v>
+        <v>0.09718652235033334</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7498,10 +7482,10 @@
         <v>10</v>
       </c>
       <c r="J63" t="n">
-        <v>22.98070282549081</v>
+        <v>22.97168268688948</v>
       </c>
       <c r="K63" t="n">
-        <v>2.391306573724061</v>
+        <v>2.826089626654116</v>
       </c>
       <c r="L63" t="n">
         <v>8</v>
@@ -7510,13 +7494,13 @@
         <v>62.5</v>
       </c>
       <c r="N63" t="n">
-        <v>12.46026019189929</v>
+        <v>13.0731539657678</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>2.547768471337575</v>
+        <v>2.114162253217078</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7582,7 +7566,7 @@
         <v>46282</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1450436569080637</v>
+        <v>0.1450606425076003</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7610,7 +7594,7 @@
         <v>18.13256048493127</v>
       </c>
       <c r="K64" t="n">
-        <v>6.925969641381968</v>
+        <v>6.938491400272384</v>
       </c>
       <c r="L64" t="n">
         <v>30</v>
@@ -7652,7 +7636,7 @@
         <v>11.36363653581267</v>
       </c>
       <c r="Y64" t="n">
-        <v>3.984843735776922</v>
+        <v>3.973599707402919</v>
       </c>
       <c r="Z64" t="n">
         <v>56</v>
@@ -7661,7 +7645,7 @@
         <v>57.14285714285715</v>
       </c>
       <c r="AB64" t="n">
-        <v>14.24395685401651</v>
+        <v>14.24438709734272</v>
       </c>
       <c r="AC64" t="n">
         <v>2</v>
@@ -7701,7 +7685,7 @@
         <v>46282</v>
       </c>
       <c r="C65" t="n">
-        <v>6.302003081664099</v>
+        <v>6.29760443433934</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7729,7 +7713,7 @@
         <v>15.61952021218654</v>
       </c>
       <c r="K65" t="n">
-        <v>5.915233629098582</v>
+        <v>5.841307330901535</v>
       </c>
       <c r="L65" t="n">
         <v>31</v>
@@ -7744,7 +7728,7 @@
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>3.856637266368823</v>
+        <v>3.929177344811863</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7771,7 +7755,7 @@
         <v>24.47056390537039</v>
       </c>
       <c r="Y65" t="n">
-        <v>10.62821769538307</v>
+        <v>10.6905970604911</v>
       </c>
       <c r="Z65" t="n">
         <v>14</v>
@@ -7820,7 +7804,7 @@
         <v>46282</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4191063174114021</v>
+        <v>0.4195663394878228</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7848,7 +7832,7 @@
         <v>19.90687209731571</v>
       </c>
       <c r="K66" t="n">
-        <v>8.063908969559751</v>
+        <v>8.182522747794717</v>
       </c>
       <c r="L66" t="n">
         <v>17</v>
@@ -7857,7 +7841,7 @@
         <v>70.58823529411765</v>
       </c>
       <c r="N66" t="n">
-        <v>14.02355017649872</v>
+        <v>13.82481913979146</v>
       </c>
       <c r="O66" t="n">
         <v>6</v>
@@ -7890,22 +7874,22 @@
         <v>11.49973494118828</v>
       </c>
       <c r="Y66" t="n">
-        <v>3.081465595806843</v>
+        <v>2.975085272752687</v>
       </c>
       <c r="Z66" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AA66" t="n">
-        <v>33.33333333333334</v>
+        <v>37.73584905660378</v>
       </c>
       <c r="AB66" t="n">
-        <v>11.42607909402794</v>
+        <v>11.36272926096687</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>3.011327422700782</v>
+        <v>3.117668009037511</v>
       </c>
       <c r="AE66" t="n">
         <v>41</v>
@@ -7939,7 +7923,7 @@
         <v>46282</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02280431432973806</v>
+        <v>0.02280698526947051</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7968,10 +7952,10 @@
         <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>24.79148995549716</v>
+        <v>24.78267910195914</v>
       </c>
       <c r="K67" t="n">
-        <v>2.77777777777779</v>
+        <v>2.777774897119456</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
@@ -7986,7 +7970,7 @@
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>1.189189189189177</v>
+        <v>1.189192025322594</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -8032,7 +8016,7 @@
         <v>46282</v>
       </c>
       <c r="C68" t="n">
-        <v>1.265536723163842</v>
+        <v>1.265684905448511</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8057,10 +8041,10 @@
         <v>10</v>
       </c>
       <c r="J68" t="n">
-        <v>77.33645789523086</v>
+        <v>77.33380364754903</v>
       </c>
       <c r="K68" t="n">
-        <v>2.483766303740254e-06</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -8071,7 +8055,7 @@
         <v>2</v>
       </c>
       <c r="P68" t="n">
-        <v>1.999997466558434</v>
+        <v>2.000000000000002</v>
       </c>
       <c r="Q68" t="n">
         <v>5</v>
@@ -8137,7 +8121,7 @@
         <v>46282</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4215716486902928</v>
+        <v>0.4216210306347187</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8166,7 +8150,7 @@
         <v>10</v>
       </c>
       <c r="J69" t="n">
-        <v>24.32773347150917</v>
+        <v>24.31886939425941</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -8203,7 +8187,7 @@
         <v>45.36848923911108</v>
       </c>
       <c r="Y69" t="n">
-        <v>24.32773347150917</v>
+        <v>24.31886939425941</v>
       </c>
       <c r="Z69" t="n">
         <v>0</v>
@@ -8240,7 +8224,7 @@
         <v>46282</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4449922958397535</v>
+        <v>0.4425788101450749</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8265,10 +8249,10 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>24.99185434120895</v>
+        <v>24.98306858684308</v>
       </c>
       <c r="K70" t="n">
-        <v>7.333994053518333</v>
+        <v>6.739348806283552</v>
       </c>
       <c r="L70" t="n">
         <v>18</v>
@@ -8277,13 +8261,13 @@
         <v>72.22222222222223</v>
       </c>
       <c r="N70" t="n">
-        <v>11.00256638103325</v>
+        <v>11.2152183575151</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>0.6204986149584535</v>
+        <v>1.181055728571434</v>
       </c>
       <c r="Q70" t="n">
         <v>31</v>
@@ -8310,7 +8294,7 @@
         <v>44.93251946562029</v>
       </c>
       <c r="Y70" t="n">
-        <v>19.49076139893885</v>
+        <v>19.92741591513995</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -8355,7 +8339,7 @@
         <v>46282</v>
       </c>
       <c r="C71" t="n">
-        <v>3.093990755007704</v>
+        <v>3.0861343126593</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8383,16 +8367,16 @@
         <v>12.27124607635546</v>
       </c>
       <c r="K71" t="n">
-        <v>7.144793659273252</v>
+        <v>6.872725330383345</v>
       </c>
       <c r="L71" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M71" t="n">
-        <v>53.84615384615385</v>
+        <v>60.97560975609756</v>
       </c>
       <c r="N71" t="n">
-        <v>14.33792192373144</v>
+        <v>14.15337200123552</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
@@ -8464,7 +8448,7 @@
         <v>46282</v>
       </c>
       <c r="C72" t="n">
-        <v>0.04807395993836672</v>
+        <v>0.0480795882857085</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8489,10 +8473,10 @@
         <v>10</v>
       </c>
       <c r="J72" t="n">
-        <v>43.42727922447008</v>
+        <v>43.42065369293228</v>
       </c>
       <c r="K72" t="n">
-        <v>3.846153973086075e-06</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
         <v>3</v>
@@ -8507,7 +8491,7 @@
         <v>10</v>
       </c>
       <c r="P72" t="n">
-        <v>9.999995769230807</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q72" t="n">
         <v>15</v>
@@ -8573,7 +8557,7 @@
         <v>46282</v>
       </c>
       <c r="C73" t="n">
-        <v>0.05362095531587057</v>
+        <v>0.05362723309580827</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8598,10 +8582,10 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>31.26644991618639</v>
+        <v>31.25840016539586</v>
       </c>
       <c r="K73" t="n">
-        <v>2.755907130014279</v>
+        <v>2.755903193006337</v>
       </c>
       <c r="L73" t="n">
         <v>7</v>
@@ -8616,7 +8600,7 @@
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>7.049806743295028</v>
+        <v>7.04981084482037</v>
       </c>
       <c r="Q73" t="n">
         <v>14</v>
@@ -8682,7 +8666,7 @@
         <v>46282</v>
       </c>
       <c r="C74" t="n">
-        <v>4.410888546481766</v>
+        <v>4.52030334601845</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8707,25 +8691,25 @@
         <v>10</v>
       </c>
       <c r="J74" t="n">
-        <v>25.64684119062249</v>
+        <v>25.63813329763319</v>
       </c>
       <c r="K74" t="n">
-        <v>1.420586870359841e-06</v>
+        <v>2.468562238142114</v>
       </c>
       <c r="L74" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="M74" t="n">
-        <v>66.66666666666667</v>
+        <v>62.5</v>
       </c>
       <c r="N74" t="n">
-        <v>22.76378277075152</v>
+        <v>13.14679252584914</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>7.9999984657662</v>
+        <v>5.398180320909107</v>
       </c>
       <c r="Q74" t="n">
         <v>27</v>
@@ -8791,7 +8775,7 @@
         <v>46282</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1033384694401644</v>
+        <v>0.1033505762715296</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8816,10 +8800,10 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>22.08673428202569</v>
+        <v>22.07761273851969</v>
       </c>
       <c r="K75" t="n">
-        <v>1.207243460764595</v>
+        <v>1.207251962479439</v>
       </c>
       <c r="L75" t="n">
         <v>14</v>
@@ -8834,7 +8818,7 @@
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>4.735586481113319</v>
+        <v>4.735577683007719</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8900,7 +8884,7 @@
         <v>46282</v>
       </c>
       <c r="C76" t="n">
-        <v>1.866461222393426</v>
+        <v>1.861543073787306</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8928,7 +8912,7 @@
         <v>16.69183750728255</v>
       </c>
       <c r="K76" t="n">
-        <v>10.34369061785272</v>
+        <v>10.05293361647748</v>
       </c>
       <c r="L76" t="n">
         <v>19</v>
@@ -8937,7 +8921,7 @@
         <v>63.1578947368421</v>
       </c>
       <c r="N76" t="n">
-        <v>12.05057279388566</v>
+        <v>11.15319882028068</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
@@ -8967,10 +8951,10 @@
         <v>60</v>
       </c>
       <c r="X76" t="n">
-        <v>10.89024714815578</v>
+        <v>10.90323779832005</v>
       </c>
       <c r="Y76" t="n">
-        <v>0.4928806133625452</v>
+        <v>0.7667081671581588</v>
       </c>
       <c r="Z76" t="n">
         <v>57</v>
@@ -8979,13 +8963,13 @@
         <v>42.10526315789474</v>
       </c>
       <c r="AB76" t="n">
-        <v>9.89623813342066</v>
+        <v>9.806989393884249</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>3.524490919097412</v>
+        <v>3.258273280189394</v>
       </c>
       <c r="AE76" t="n">
         <v>32</v>
@@ -9019,7 +9003,7 @@
         <v>46282</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4643040575243966</v>
+        <v>0.4623037512973415</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9047,22 +9031,22 @@
         <v>24.27505949158866</v>
       </c>
       <c r="K77" t="n">
-        <v>7.268574284140228</v>
+        <v>6.806441779307204</v>
       </c>
       <c r="L77" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M77" t="n">
-        <v>50</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N77" t="n">
-        <v>12.78101208095246</v>
+        <v>13.5424507755035</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>0.6818639296186868</v>
+        <v>1.11749647381667</v>
       </c>
       <c r="Q77" t="n">
         <v>26</v>
@@ -9128,7 +9112,7 @@
         <v>46282</v>
       </c>
       <c r="C78" t="n">
-        <v>0.04992295839753468</v>
+        <v>0.04972333844994962</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9153,19 +9137,19 @@
         <v>10</v>
       </c>
       <c r="J78" t="n">
-        <v>25.89426476209616</v>
+        <v>25.8855858461943</v>
       </c>
       <c r="K78" t="n">
-        <v>7.048459092937964</v>
+        <v>6.607933978924518</v>
       </c>
       <c r="L78" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M78" t="n">
-        <v>61.53846153846154</v>
+        <v>50</v>
       </c>
       <c r="N78" t="n">
-        <v>16.20453229241359</v>
+        <v>17.26382553739754</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
@@ -9198,7 +9182,7 @@
         <v>36.67113091579677</v>
       </c>
       <c r="Y78" t="n">
-        <v>20.67095232833161</v>
+        <v>20.98815429004413</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -9243,7 +9227,7 @@
         <v>46282</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8275295326142784</v>
+        <v>0.8255717720196152</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9268,19 +9252,19 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>22.50123891318462</v>
+        <v>22.49215884768965</v>
       </c>
       <c r="K79" t="n">
-        <v>7.184672698243766</v>
+        <v>6.918569327807811</v>
       </c>
       <c r="L79" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M79" t="n">
-        <v>71.42857142857143</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="N79" t="n">
-        <v>11.81136006680001</v>
+        <v>11.33059066455084</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
@@ -9352,7 +9336,7 @@
         <v>46282</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1288135593220339</v>
+        <v>0.1286231817533876</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9380,7 +9364,7 @@
         <v>14.36747410815714</v>
       </c>
       <c r="K80" t="n">
-        <v>5.335076295702068</v>
+        <v>5.179398307888561</v>
       </c>
       <c r="L80" t="n">
         <v>51</v>
@@ -9389,13 +9373,13 @@
         <v>62.74509803921568</v>
       </c>
       <c r="N80" t="n">
-        <v>17.24107372390105</v>
+        <v>16.57102549954389</v>
       </c>
       <c r="O80" t="n">
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>4.428651754333313</v>
+        <v>4.583218548180179</v>
       </c>
       <c r="Q80" t="n">
         <v>39</v>
@@ -9461,7 +9445,7 @@
         <v>46282</v>
       </c>
       <c r="C81" t="n">
-        <v>1.183359013867489</v>
+        <v>1.174251559731902</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9486,25 +9470,25 @@
         <v>10</v>
       </c>
       <c r="J81" t="n">
-        <v>11.75203263413206</v>
+        <v>11.74169622012081</v>
       </c>
       <c r="K81" t="n">
-        <v>5.301645338208405</v>
+        <v>4.478977579451127</v>
       </c>
       <c r="L81" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="M81" t="n">
-        <v>54.54545454545455</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="N81" t="n">
-        <v>15.46238709479638</v>
+        <v>15.20846825806983</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>4.461805555555576</v>
+        <v>5.284338101749153</v>
       </c>
       <c r="Q81" t="n">
         <v>32</v>
@@ -9531,22 +9515,22 @@
         <v>23.79225853623819</v>
       </c>
       <c r="Y81" t="n">
-        <v>7.073438386215836</v>
+        <v>7.78862658181616</v>
       </c>
       <c r="Z81" t="n">
         <v>9</v>
       </c>
       <c r="AA81" t="n">
-        <v>66.66666666666667</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="AB81" t="n">
-        <v>10.78755071299194</v>
+        <v>10.89853603576646</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>3.149327342969344</v>
+        <v>2.398156904306292</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9580,7 +9564,7 @@
         <v>46282</v>
       </c>
       <c r="C82" t="n">
-        <v>4.719054893682589</v>
+        <v>4.756591930014869</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9608,16 +9592,16 @@
         <v>20.04129707202715</v>
       </c>
       <c r="K82" t="n">
-        <v>5.566021221854478</v>
+        <v>6.405730795770159</v>
       </c>
       <c r="L82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M82" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N82" t="n">
-        <v>8.014054265482534</v>
+        <v>8.901881472194736</v>
       </c>
       <c r="O82" t="n">
         <v>4</v>
@@ -9689,7 +9673,7 @@
         <v>46282</v>
       </c>
       <c r="C83" t="n">
-        <v>5.63944530046225</v>
+        <v>5.624695640784321</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9717,16 +9701,16 @@
         <v>17.92531520307596</v>
       </c>
       <c r="K83" t="n">
-        <v>12.82392619977928</v>
+        <v>12.52884141283435</v>
       </c>
       <c r="L83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M83" t="n">
         <v>60</v>
       </c>
       <c r="N83" t="n">
-        <v>9.960217924426816</v>
+        <v>10.98802159309777</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
@@ -9756,25 +9740,25 @@
         <v>61.90476190476191</v>
       </c>
       <c r="X83" t="n">
-        <v>13.33769635551598</v>
+        <v>13.35096993457194</v>
       </c>
       <c r="Y83" t="n">
-        <v>0.4533091568449721</v>
+        <v>0.7252946509519576</v>
       </c>
       <c r="Z83" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AA83" t="n">
-        <v>41.53846153846154</v>
+        <v>42.42424242424242</v>
       </c>
       <c r="AB83" t="n">
-        <v>13.42071945660485</v>
+        <v>13.40005366713753</v>
       </c>
       <c r="AC83" t="n">
         <v>8</v>
       </c>
       <c r="AD83" t="n">
-        <v>7.581056466302361</v>
+        <v>7.327853881278523</v>
       </c>
       <c r="AE83" t="n">
         <v>41</v>
@@ -9808,7 +9792,7 @@
         <v>46282</v>
       </c>
       <c r="C84" t="n">
-        <v>2.03492552645095</v>
+        <v>2.037218562153607</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9836,7 +9820,7 @@
         <v>15.17540634174243</v>
       </c>
       <c r="K84" t="n">
-        <v>7.327380600749134</v>
+        <v>7.448321398036839</v>
       </c>
       <c r="L84" t="n">
         <v>31</v>
@@ -9878,16 +9862,16 @@
         <v>10.78590455284552</v>
       </c>
       <c r="Y84" t="n">
-        <v>3.121808650708502</v>
+        <v>3.012642418979061</v>
       </c>
       <c r="Z84" t="n">
         <v>50</v>
       </c>
       <c r="AA84" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AB84" t="n">
-        <v>12.37721799199906</v>
+        <v>11.53232374393195</v>
       </c>
       <c r="AC84" t="n">
         <v>2</v>
@@ -9927,7 +9911,7 @@
         <v>46282</v>
       </c>
       <c r="C85" t="n">
-        <v>5.932203389830509</v>
+        <v>5.943171558344711</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9955,7 +9939,7 @@
         <v>18.98569199070202</v>
       </c>
       <c r="K85" t="n">
-        <v>11.76455361543636</v>
+        <v>11.97119731549396</v>
       </c>
       <c r="L85" t="n">
         <v>18</v>
@@ -9994,25 +9978,25 @@
         <v>57.89473684210526</v>
       </c>
       <c r="X85" t="n">
-        <v>12.24838285186682</v>
+        <v>12.26152885563785</v>
       </c>
       <c r="Y85" t="n">
-        <v>0.4310344827586299</v>
+        <v>0.2586206896551757</v>
       </c>
       <c r="Z85" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="AA85" t="n">
-        <v>36.8421052631579</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="AB85" t="n">
-        <v>11.03764195490517</v>
+        <v>10.95647780374587</v>
       </c>
       <c r="AC85" t="n">
         <v>6</v>
       </c>
       <c r="AD85" t="n">
-        <v>5.593073593073594</v>
+        <v>5.756266205704408</v>
       </c>
       <c r="AE85" t="n">
         <v>33</v>
@@ -10046,7 +10030,7 @@
         <v>46282</v>
       </c>
       <c r="C86" t="n">
-        <v>5.300462249614792</v>
+        <v>5.301083014876182</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10103,7 +10087,7 @@
         <v>70.12987012987013</v>
       </c>
       <c r="X86" t="n">
-        <v>29.48178916990571</v>
+        <v>29.49695346934114</v>
       </c>
       <c r="Y86" t="n">
         <v>0</v>
@@ -10155,7 +10139,7 @@
         <v>46282</v>
       </c>
       <c r="C87" t="n">
-        <v>5.875706214689266</v>
+        <v>5.896941183214977</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10183,16 +10167,16 @@
         <v>13.37336922777884</v>
       </c>
       <c r="K87" t="n">
-        <v>9.955032271186459</v>
+        <v>10.35241286923014</v>
       </c>
       <c r="L87" t="n">
         <v>30</v>
       </c>
       <c r="M87" t="n">
-        <v>53.33333333333334</v>
+        <v>50</v>
       </c>
       <c r="N87" t="n">
-        <v>11.08166016718459</v>
+        <v>11.32783601422248</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10225,16 +10209,16 @@
         <v>15.88967756874082</v>
       </c>
       <c r="Y87" t="n">
-        <v>4.749660178962689</v>
+        <v>4.405422755534937</v>
       </c>
       <c r="Z87" t="n">
         <v>36</v>
       </c>
       <c r="AA87" t="n">
-        <v>44.44444444444444</v>
+        <v>47.22222222222222</v>
       </c>
       <c r="AB87" t="n">
-        <v>10.95382325810438</v>
+        <v>10.77883709639034</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
@@ -10274,7 +10258,7 @@
         <v>46282</v>
       </c>
       <c r="C88" t="n">
-        <v>1.019414483821264</v>
+        <v>1.018301091006772</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10302,16 +10286,16 @@
         <v>21.41497098631751</v>
       </c>
       <c r="K88" t="n">
-        <v>8.485813960636079</v>
+        <v>8.367326998114976</v>
       </c>
       <c r="L88" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M88" t="n">
-        <v>68</v>
+        <v>65.38461538461539</v>
       </c>
       <c r="N88" t="n">
-        <v>12.11345534804188</v>
+        <v>12.07070712396973</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
@@ -10344,22 +10328,22 @@
         <v>12.09536008844403</v>
       </c>
       <c r="Y88" t="n">
-        <v>3.22006738277123</v>
+        <v>3.325769315864269</v>
       </c>
       <c r="Z88" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AA88" t="n">
-        <v>34.375</v>
+        <v>34.92063492063492</v>
       </c>
       <c r="AB88" t="n">
-        <v>13.29314141936841</v>
+        <v>12.36969129801072</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>2.872426692239594</v>
+        <v>2.766229082156613</v>
       </c>
       <c r="AE88" t="n">
         <v>33</v>
@@ -10393,7 +10377,7 @@
         <v>46282</v>
       </c>
       <c r="C89" t="n">
-        <v>2.128402670775552</v>
+        <v>2.13276136865291</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10412,7 +10396,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.32: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -10425,16 +10409,16 @@
         <v>15.60428510343075</v>
       </c>
       <c r="K89" t="n">
-        <v>7.704260975073485</v>
+        <v>7.924825598553964</v>
       </c>
       <c r="L89" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M89" t="n">
-        <v>76.31578947368421</v>
+        <v>75</v>
       </c>
       <c r="N89" t="n">
-        <v>17.14608470071638</v>
+        <v>17.36179616620545</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10467,22 +10451,22 @@
         <v>21.41032003314154</v>
       </c>
       <c r="Y89" t="n">
-        <v>9.102218976020094</v>
+        <v>8.916071885224808</v>
       </c>
       <c r="Z89" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA89" t="n">
-        <v>36</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="AB89" t="n">
-        <v>15.1641247567547</v>
+        <v>15.33714453561096</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.9876820026476274</v>
+        <v>1.190032245215999</v>
       </c>
       <c r="AE89" t="n">
         <v>22</v>
@@ -10516,16 +10500,16 @@
         <v>46282</v>
       </c>
       <c r="C90" t="n">
-        <v>2.676938880328711</v>
+        <v>2.71218200761107</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -10535,7 +10519,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %76.47: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H90" t="n">
@@ -10548,22 +10532,22 @@
         <v>19.80512321049643</v>
       </c>
       <c r="K90" t="n">
-        <v>6.847196100468067</v>
+        <v>8.253888408463371</v>
       </c>
       <c r="L90" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M90" t="n">
-        <v>76.47058823529412</v>
+        <v>75</v>
       </c>
       <c r="N90" t="n">
-        <v>16.6187541379661</v>
+        <v>17.18741887381497</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>1.078927610274372</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>43</v>
@@ -10629,7 +10613,7 @@
         <v>46282</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2311248073959938</v>
+        <v>0.2305354761945859</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10657,16 +10641,16 @@
         <v>13.48269577863128</v>
       </c>
       <c r="K91" t="n">
-        <v>10.46562559225479</v>
+        <v>10.18395595852732</v>
       </c>
       <c r="L91" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M91" t="n">
-        <v>50</v>
+        <v>54.05405405405406</v>
       </c>
       <c r="N91" t="n">
-        <v>22.27250123952689</v>
+        <v>21.22479696508859</v>
       </c>
       <c r="O91" t="n">
         <v>6</v>
@@ -10696,25 +10680,25 @@
         <v>66.25</v>
       </c>
       <c r="X91" t="n">
-        <v>11.05477559541348</v>
+        <v>11.06778593403772</v>
       </c>
       <c r="Y91" t="n">
-        <v>0.5305039787798504</v>
+        <v>0.7957572648790379</v>
       </c>
       <c r="Z91" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="AA91" t="n">
-        <v>36.36363636363637</v>
+        <v>36.20689655172414</v>
       </c>
       <c r="AB91" t="n">
-        <v>11.39053161299989</v>
+        <v>11.67423453823978</v>
       </c>
       <c r="AC91" t="n">
         <v>5</v>
       </c>
       <c r="AD91" t="n">
-        <v>4.493333333333327</v>
+        <v>4.237966662722736</v>
       </c>
       <c r="AE91" t="n">
         <v>39</v>
@@ -10748,7 +10732,7 @@
         <v>46282</v>
       </c>
       <c r="C92" t="n">
-        <v>1.088854648176682</v>
+        <v>1.084872787428834</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10773,25 +10757,25 @@
         <v>10</v>
       </c>
       <c r="J92" t="n">
-        <v>19.02065273936991</v>
+        <v>19.01116781741373</v>
       </c>
       <c r="K92" t="n">
-        <v>7.374392220421377</v>
+        <v>6.969202973030497</v>
       </c>
       <c r="L92" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M92" t="n">
-        <v>64.70588235294117</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="N92" t="n">
-        <v>11.91139454291524</v>
+        <v>15.61979318393709</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>0.5826415094339898</v>
+        <v>0.9636390646281523</v>
       </c>
       <c r="Q92" t="n">
         <v>44</v>
@@ -10857,7 +10841,7 @@
         <v>46282</v>
       </c>
       <c r="C93" t="n">
-        <v>0.03903441191576785</v>
+        <v>0.03903898303194994</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10885,7 +10869,7 @@
         <v>13.488285987287</v>
       </c>
       <c r="K93" t="n">
-        <v>2.660716981188438</v>
+        <v>2.672739041765926</v>
       </c>
       <c r="L93" t="n">
         <v>65</v>
@@ -10900,7 +10884,7 @@
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>3.252736895869779</v>
+        <v>3.240646922724633</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10966,7 +10950,7 @@
         <v>46282</v>
       </c>
       <c r="C94" t="n">
-        <v>8.443759630200308</v>
+        <v>8.465295357089097</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10994,7 +10978,7 @@
         <v>10.47530442381612</v>
       </c>
       <c r="K94" t="n">
-        <v>8.113680056118721</v>
+        <v>8.389422946560909</v>
       </c>
       <c r="L94" t="n">
         <v>19</v>
@@ -11003,7 +10987,7 @@
         <v>52.63157894736842</v>
       </c>
       <c r="N94" t="n">
-        <v>14.30891523166163</v>
+        <v>14.06792694841168</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
@@ -11036,22 +11020,22 @@
         <v>30.64601732980787</v>
       </c>
       <c r="Y94" t="n">
-        <v>3.211557053550296</v>
+        <v>2.964699070308952</v>
       </c>
       <c r="Z94" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA94" t="n">
-        <v>31.25</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB94" t="n">
-        <v>12.16124896923941</v>
+        <v>12.16646182899771</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>2.880966840217147</v>
+        <v>3.128037838405162</v>
       </c>
       <c r="AE94" t="n">
         <v>38</v>
@@ -11085,7 +11069,7 @@
         <v>46282</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1088854687211094</v>
+        <v>0.108898220876161</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11110,25 +11094,25 @@
         <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>27.27834334389649</v>
+        <v>28.23223192098074</v>
       </c>
       <c r="K95" t="n">
-        <v>0.1890402660797097</v>
+        <v>1.532574774298978</v>
       </c>
       <c r="L95" t="n">
         <v>14</v>
       </c>
       <c r="M95" t="n">
-        <v>35.71428571428572</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="N95" t="n">
-        <v>12.09171874021741</v>
+        <v>15.6975867986275</v>
       </c>
       <c r="O95" t="n">
         <v>10</v>
       </c>
       <c r="P95" t="n">
-        <v>9.792448064044311</v>
+        <v>8.339614399145923</v>
       </c>
       <c r="Q95" t="n">
         <v>21</v>
@@ -11194,7 +11178,7 @@
         <v>46282</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1234720082177709</v>
+        <v>0.1232810003459577</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11222,22 +11206,22 @@
         <v>11.75188607616355</v>
       </c>
       <c r="K96" t="n">
-        <v>3.93672852161786</v>
+        <v>3.77594120144138</v>
       </c>
       <c r="L96" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M96" t="n">
-        <v>50.87719298245614</v>
+        <v>52.54237288135593</v>
       </c>
       <c r="N96" t="n">
-        <v>14.16762232896863</v>
+        <v>14.28546973432773</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>5.833617783266143</v>
+        <v>5.997593205613039</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11303,7 +11287,7 @@
         <v>46282</v>
       </c>
       <c r="C97" t="n">
-        <v>1.837699024139702</v>
+        <v>1.840996240396314</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11331,16 +11315,16 @@
         <v>19.39456900406833</v>
       </c>
       <c r="K97" t="n">
-        <v>8.57733420978397</v>
+        <v>8.772144647594171</v>
       </c>
       <c r="L97" t="n">
         <v>15</v>
       </c>
       <c r="M97" t="n">
-        <v>40</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="N97" t="n">
-        <v>9.464468407632657</v>
+        <v>9.30806921970809</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11412,7 +11396,7 @@
         <v>46282</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6833076527991783</v>
+        <v>0.6780455019027675</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11440,22 +11424,22 @@
         <v>20.0091805261642</v>
       </c>
       <c r="K98" t="n">
-        <v>9.00460129179319</v>
+        <v>8.165157070656836</v>
       </c>
       <c r="L98" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M98" t="n">
-        <v>73.33333333333333</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N98" t="n">
-        <v>17.43898315702185</v>
+        <v>18.48573543490522</v>
       </c>
       <c r="O98" t="n">
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>0.9131712757172838</v>
+        <v>1.696334548975509</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11482,7 +11466,7 @@
         <v>30.85778357900837</v>
       </c>
       <c r="Y98" t="n">
-        <v>12.80632616250722</v>
+        <v>13.47780447401995</v>
       </c>
       <c r="Z98" t="n">
         <v>2</v>
@@ -11527,7 +11511,7 @@
         <v>46282</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4971751412429379</v>
+        <v>0.4951786925307269</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11555,16 +11539,16 @@
         <v>18.77251112788727</v>
       </c>
       <c r="K99" t="n">
-        <v>4.447786080883853</v>
+        <v>4.028367186582016</v>
       </c>
       <c r="L99" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M99" t="n">
-        <v>57.89473684210526</v>
+        <v>58.97435897435897</v>
       </c>
       <c r="N99" t="n">
-        <v>17.06738541524516</v>
+        <v>16.62360548972542</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
@@ -11597,7 +11581,7 @@
         <v>33.04241514445872</v>
       </c>
       <c r="Y99" t="n">
-        <v>15.15968618398196</v>
+        <v>15.50036961967851</v>
       </c>
       <c r="Z99" t="n">
         <v>0</v>
@@ -11642,7 +11626,7 @@
         <v>46282</v>
       </c>
       <c r="C100" t="n">
-        <v>330.0242360041089</v>
+        <v>338.9352262569049</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11670,16 +11654,16 @@
         <v>16.74333965049621</v>
       </c>
       <c r="K100" t="n">
-        <v>8.802988034743686</v>
+        <v>11.74077944543452</v>
       </c>
       <c r="L100" t="n">
         <v>16</v>
       </c>
       <c r="M100" t="n">
-        <v>50</v>
+        <v>56.25</v>
       </c>
       <c r="N100" t="n">
-        <v>11.99209827934179</v>
+        <v>15.69115833473383</v>
       </c>
       <c r="O100" t="n">
         <v>5</v>
@@ -11709,25 +11693,25 @@
         <v>64.91228070175438</v>
       </c>
       <c r="X100" t="n">
-        <v>10.05542668049453</v>
+        <v>12.25809768500474</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.138007169230137</v>
+        <v>0.4608293301226363</v>
       </c>
       <c r="Z100" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="AA100" t="n">
-        <v>36.17021276595744</v>
+        <v>44.82758620689656</v>
       </c>
       <c r="AB100" t="n">
-        <v>11.74090739478531</v>
+        <v>11.57012987101301</v>
       </c>
       <c r="AC100" t="n">
         <v>8</v>
       </c>
       <c r="AD100" t="n">
-        <v>6.940981700132321</v>
+        <v>7.574074225393234</v>
       </c>
       <c r="AE100" t="n">
         <v>39</v>
@@ -11761,7 +11745,7 @@
         <v>46282</v>
       </c>
       <c r="C101" t="n">
-        <v>336.8864920390345</v>
+        <v>336.3473485781018</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11789,7 +11773,7 @@
         <v>12.87023644471203</v>
       </c>
       <c r="K101" t="n">
-        <v>6.977107396649251</v>
+        <v>6.805904308115474</v>
       </c>
       <c r="L101" t="n">
         <v>23</v>
@@ -11798,7 +11782,7 @@
         <v>47.82608695652174</v>
       </c>
       <c r="N101" t="n">
-        <v>8.232394468922378</v>
+        <v>7.880778017543602</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11870,7 +11854,7 @@
         <v>46282</v>
       </c>
       <c r="C102" t="n">
-        <v>374.8638931689779</v>
+        <v>379.6676781025531</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11895,25 +11879,25 @@
         <v>10</v>
       </c>
       <c r="J102" t="n">
-        <v>13.70795483068423</v>
+        <v>13.69784871135864</v>
       </c>
       <c r="K102" t="n">
-        <v>1.908422343954985</v>
+        <v>3.202266151994415</v>
       </c>
       <c r="L102" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="M102" t="n">
-        <v>54.28571428571428</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="N102" t="n">
-        <v>11.41903029479795</v>
+        <v>9.259483436088804</v>
       </c>
       <c r="O102" t="n">
         <v>4</v>
       </c>
       <c r="P102" t="n">
-        <v>2.052409023648361</v>
+        <v>0.7729809409714905</v>
       </c>
       <c r="Q102" t="n">
         <v>29</v>
@@ -11979,7 +11963,7 @@
         <v>46282</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7256291730868003</v>
+        <v>0.7257141490003528</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12011,7 +11995,7 @@
         <v>18.80410934045254</v>
       </c>
       <c r="K103" t="n">
-        <v>13.08636147140103</v>
+        <v>13.0996046226314</v>
       </c>
       <c r="L103" t="n">
         <v>9</v>
@@ -12050,7 +12034,7 @@
         <v>67.69230769230769</v>
       </c>
       <c r="X103" t="n">
-        <v>13.08636147140103</v>
+        <v>13.0996046226314</v>
       </c>
       <c r="Y103" t="n">
         <v>0</v>
@@ -12102,21 +12086,21 @@
         <v>46282</v>
       </c>
       <c r="C104" t="n">
-        <v>0.05053929121725732</v>
+        <v>0.05033974283527441</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -12130,22 +12114,22 @@
         <v>11.61049328507885</v>
       </c>
       <c r="K104" t="n">
-        <v>4.194680604211687</v>
+        <v>3.783280297143321</v>
       </c>
       <c r="L104" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="M104" t="n">
-        <v>55</v>
+        <v>51.02040816326531</v>
       </c>
       <c r="N104" t="n">
-        <v>14.67097486046199</v>
+        <v>14.22996646647806</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>0.2088194767366991</v>
       </c>
       <c r="Q104" t="n">
         <v>32</v>
@@ -12172,16 +12156,16 @@
         <v>17.89763425757407</v>
       </c>
       <c r="Y104" t="n">
-        <v>7.902835790749663</v>
+        <v>8.266470492791067</v>
       </c>
       <c r="Z104" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA104" t="n">
-        <v>60.8695652173913</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="AB104" t="n">
-        <v>14.03021068267866</v>
+        <v>14.47578631409413</v>
       </c>
       <c r="AC104" t="n">
         <v>5</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -438,13 +438,13 @@
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="27" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3920335794563988</v>
+        <v>0.3852447637827459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,22 +698,22 @@
         <v>22.3316078451137</v>
       </c>
       <c r="K2" t="n">
-        <v>7.94812463650425</v>
+        <v>6.078795173732421</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M2" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="N2" t="n">
-        <v>13.29782535914281</v>
+        <v>13.7376354826656</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>1.900797601074666</v>
+        <v>3.696502038739746</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -744,29 +744,29 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="AF2" t="n">
-        <v>52.17391304347826</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="AG2" t="n">
-        <v>36.22766409236662</v>
+        <v>38.12522537167639</v>
       </c>
       <c r="AH2" t="n">
-        <v>15.94624895111164</v>
+        <v>15.72092847447745</v>
       </c>
       <c r="AI2" t="n">
-        <v>38.13741307280403</v>
+        <v>38.56944827051576</v>
       </c>
       <c r="AJ2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AK2" t="n">
-        <v>49.0566037735849</v>
+        <v>46.15384615384615</v>
       </c>
     </row>
     <row r="3">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7166735706629459</v>
+        <v>0.6983201990298599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,16 +807,16 @@
         <v>16.52890779617068</v>
       </c>
       <c r="K3" t="n">
-        <v>13.99609740875636</v>
+        <v>11.07675891755315</v>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="M3" t="n">
-        <v>58.33333333333334</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="N3" t="n">
-        <v>13.91823412431131</v>
+        <v>14.1611498725775</v>
       </c>
       <c r="O3" t="n">
         <v>8</v>
@@ -849,22 +849,22 @@
         <v>17.17248092970491</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.710861369278461</v>
+        <v>5.202349531037709</v>
       </c>
       <c r="Z3" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="AA3" t="n">
-        <v>34.88372093023256</v>
+        <v>37.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.25827481325848</v>
+        <v>11.73299621483433</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>7.492242950560779</v>
+        <v>5.060938161682693</v>
       </c>
       <c r="AE3" t="n">
         <v>34</v>
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C4" t="n">
-        <v>1.470125991793388</v>
+        <v>1.449537109679056</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,16 +926,16 @@
         <v>18.01811637499802</v>
       </c>
       <c r="K4" t="n">
-        <v>13.89988953148073</v>
+        <v>12.30473958413618</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M4" t="n">
-        <v>60</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="N4" t="n">
-        <v>21.99783982695302</v>
+        <v>19.05893258305035</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -965,25 +965,25 @@
         <v>62.5</v>
       </c>
       <c r="X4" t="n">
-        <v>14.13866364625549</v>
+        <v>14.60802662483958</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2091965221485137</v>
+        <v>2.009708314970837</v>
       </c>
       <c r="Z4" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AA4" t="n">
-        <v>44.44444444444444</v>
+        <v>40.32258064516129</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.81285984640327</v>
+        <v>13.81477285831064</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>9.811328435715572</v>
+        <v>8.15416665021511</v>
       </c>
       <c r="AE4" t="n">
         <v>39</v>
@@ -992,10 +992,10 @@
         <v>58.97435897435897</v>
       </c>
       <c r="AG4" t="n">
-        <v>38.98149428237421</v>
+        <v>38.76889646727108</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.99286469198476</v>
+        <v>20.20546250708789</v>
       </c>
       <c r="AI4" t="n">
         <v>43.41862288289698</v>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C5" t="n">
-        <v>0.22848078504769</v>
+        <v>0.2224537322394023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,7 +1034,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>5</v>
       </c>
@@ -1042,19 +1046,19 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>21.7133291595898</v>
+        <v>21.5381778578712</v>
       </c>
       <c r="K5" t="n">
-        <v>9.09476260517823</v>
+        <v>6.216971830817153</v>
       </c>
       <c r="L5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M5" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="N5" t="n">
-        <v>11.81190499200247</v>
+        <v>12.03297387416751</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -1101,10 +1105,10 @@
         <v>52.17391304347826</v>
       </c>
       <c r="AG5" t="n">
-        <v>28.62807286251545</v>
+        <v>28.3966466800023</v>
       </c>
       <c r="AH5" t="n">
-        <v>23.54584018096281</v>
+        <v>23.77726636347596</v>
       </c>
       <c r="AI5" t="n">
         <v>38.13741307280403</v>
@@ -1123,24 +1127,24 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C6" t="n">
-        <v>1.407458087283017</v>
+        <v>1.345998834137457</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1151,16 +1155,20 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>38.01073584402899</v>
+        <v>36.85572424855874</v>
       </c>
       <c r="K6" t="n">
-        <v>12.01962107293508</v>
+        <v>7.12367785757031</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="N6" t="n">
+        <v>15.09254522848125</v>
+      </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
@@ -1188,31 +1196,41 @@
       <c r="W6" t="n">
         <v>74.68354430379746</v>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>14.14554587665273</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>6.151679388935916</v>
+      </c>
       <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>58.8235294117647</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>12.65498052944222</v>
+      </c>
       <c r="AC6" t="n">
         <v>4</v>
       </c>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
       <c r="AE6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF6" t="n">
-        <v>46.93877551020408</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="AG6" t="n">
-        <v>38.34885643649939</v>
+        <v>37.52410598857484</v>
       </c>
       <c r="AH6" t="n">
-        <v>8.589919073704692</v>
+        <v>8.309227344758497</v>
       </c>
       <c r="AI6" t="n">
-        <v>33.70350369317515</v>
+        <v>32.57524229286744</v>
       </c>
       <c r="AJ6" t="n">
         <v>79</v>
@@ -1228,14 +1246,14 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C7" t="n">
-        <v>2.249878256313728</v>
+        <v>2.210185453826818</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1245,7 +1263,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1259,22 +1277,22 @@
         <v>15.68018152056624</v>
       </c>
       <c r="K7" t="n">
-        <v>7.850301037983631</v>
+        <v>5.947584441989484</v>
       </c>
       <c r="L7" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M7" t="n">
-        <v>70.37037037037037</v>
+        <v>62.85714285714285</v>
       </c>
       <c r="N7" t="n">
-        <v>13.65465917798175</v>
+        <v>13.70711250283193</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1388025444302166</v>
+        <v>1.937199011020674</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1297,27 +1315,17 @@
       <c r="W7" t="n">
         <v>68.1159420289855</v>
       </c>
-      <c r="X7" t="n">
-        <v>18.9234494530097</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>9.060821935249319</v>
-      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>64.28571428571429</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>13.12838423287637</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
         <v>5</v>
       </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="n">
         <v>45</v>
       </c>
@@ -1347,10 +1355,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3016275205492949</v>
+        <v>0.289292348049088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1375,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>5</v>
       </c>
@@ -1375,25 +1387,25 @@
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>30.95234632522249</v>
+        <v>30.94951034805541</v>
       </c>
       <c r="K8" t="n">
-        <v>6.37681237597143</v>
+        <v>2.022301722695485</v>
       </c>
       <c r="L8" t="n">
         <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>10.50913721135396</v>
+        <v>13.22118055964986</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>1.525884812464295</v>
+        <v>5.859207424620116</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1456,10 +1468,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5407926484814162</v>
+        <v>0.5556217527266317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,16 +1499,16 @@
         <v>17.6457098380072</v>
       </c>
       <c r="K9" t="n">
-        <v>5.587164001883371</v>
+        <v>8.482475294182489</v>
       </c>
       <c r="L9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M9" t="n">
-        <v>62.5</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="N9" t="n">
-        <v>9.71639099143081</v>
+        <v>8.398768760569258</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1565,10 +1577,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C10" t="n">
-        <v>1.844078296841618</v>
+        <v>1.78680575355133</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,22 +1608,22 @@
         <v>15.9903344514868</v>
       </c>
       <c r="K10" t="n">
-        <v>5.744041061876004</v>
+        <v>2.459890828245004</v>
       </c>
       <c r="L10" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="M10" t="n">
-        <v>51.42857142857143</v>
+        <v>57.77777777777778</v>
       </c>
       <c r="N10" t="n">
-        <v>10.33659719937111</v>
+        <v>12.20322904279378</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>4.02477425241734</v>
+        <v>7.359083745652817</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1652,10 +1664,10 @@
         <v>46.66666666666666</v>
       </c>
       <c r="AG10" t="n">
-        <v>31.75890669599265</v>
+        <v>31.5381911370418</v>
       </c>
       <c r="AH10" t="n">
-        <v>14.90775997067401</v>
+        <v>15.12847552962487</v>
       </c>
       <c r="AI10" t="n">
         <v>30.23238890769975</v>
@@ -1674,24 +1686,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C11" t="n">
-        <v>7.802659980229574</v>
+        <v>7.642361823791678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1705,16 +1717,16 @@
         <v>16.80962533618998</v>
       </c>
       <c r="K11" t="n">
-        <v>9.248695105842518</v>
+        <v>7.004285575876401</v>
       </c>
       <c r="L11" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M11" t="n">
-        <v>54.83870967741935</v>
+        <v>72.97297297297297</v>
       </c>
       <c r="N11" t="n">
-        <v>11.78285485434354</v>
+        <v>11.7104971159868</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1723,46 +1735,46 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R11" t="n">
-        <v>61.22448979591837</v>
+        <v>60</v>
       </c>
       <c r="S11" t="n">
-        <v>51.51900046050075</v>
+        <v>51.68862045129074</v>
       </c>
       <c r="T11" t="n">
-        <v>9.705489335417617</v>
+        <v>8.311379548709262</v>
       </c>
       <c r="U11" t="n">
-        <v>47.24599944352045</v>
+        <v>46.18143774758936</v>
       </c>
       <c r="V11" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="W11" t="n">
-        <v>61.19402985074627</v>
+        <v>60.29411764705883</v>
       </c>
       <c r="X11" t="n">
-        <v>10.25559552156457</v>
+        <v>10.26012402231442</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.9132420091324089</v>
+        <v>2.952870292236476</v>
       </c>
       <c r="Z11" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="AA11" t="n">
-        <v>45.09803921568628</v>
+        <v>45.65217391304348</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.70569028601007</v>
+        <v>11.09169529249605</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.0967741935484</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>48</v>
@@ -1780,10 +1792,10 @@
         <v>42.27501741982778</v>
       </c>
       <c r="AJ11" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AK11" t="n">
-        <v>51.47058823529412</v>
+        <v>52.23880597014925</v>
       </c>
     </row>
     <row r="12">
@@ -1793,19 +1805,19 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C12" t="n">
-        <v>5.2497159313987</v>
+        <v>5.084656558820486</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1813,7 +1825,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>5</v>
       </c>
@@ -1821,21 +1837,25 @@
         <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>33.95819760477713</v>
+        <v>33.95548508619471</v>
       </c>
       <c r="K12" t="n">
-        <v>6.94851675339454</v>
+        <v>3.581631839036636</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>100</v>
+      </c>
+      <c r="N12" t="n">
+        <v>12.19521088909814</v>
+      </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.369324016025808</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1898,10 +1918,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1428004881635027</v>
+        <v>0.128346577530997</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1926,10 +1946,10 @@
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>54.4969426760356</v>
+        <v>57.6398540434237</v>
       </c>
       <c r="K13" t="n">
-        <v>3.576747668692981</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1940,7 +1960,7 @@
         <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>2.33957175316819</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1991,10 +2011,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C14" t="n">
-        <v>8.588576357435054</v>
+        <v>8.605986252277818</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,16 +2042,16 @@
         <v>10.97257403209156</v>
       </c>
       <c r="K14" t="n">
-        <v>7.148219696488267</v>
+        <v>7.365419749194357</v>
       </c>
       <c r="L14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M14" t="n">
-        <v>48.14814814814815</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="N14" t="n">
-        <v>10.713405803398</v>
+        <v>11.43584516509007</v>
       </c>
       <c r="O14" t="n">
         <v>2</v>
@@ -2064,16 +2084,16 @@
         <v>16.11612055393703</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.608698033777037</v>
+        <v>4.415330417651853</v>
       </c>
       <c r="Z14" t="n">
         <v>26</v>
       </c>
       <c r="AA14" t="n">
-        <v>38.46153846153846</v>
+        <v>34.61538461538461</v>
       </c>
       <c r="AB14" t="n">
-        <v>12.59720226487137</v>
+        <v>13.46865860107384</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
@@ -2088,10 +2108,10 @@
         <v>52.77777777777778</v>
       </c>
       <c r="AG14" t="n">
-        <v>25.38026384011567</v>
+        <v>25.32536704608844</v>
       </c>
       <c r="AH14" t="n">
-        <v>27.39751393766211</v>
+        <v>27.45241073168934</v>
       </c>
       <c r="AI14" t="n">
         <v>37.00593802298759</v>
@@ -2110,24 +2130,24 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C15" t="n">
-        <v>13.68419103840131</v>
+        <v>13.43948538026947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -2141,22 +2161,22 @@
         <v>20.43038307058605</v>
       </c>
       <c r="K15" t="n">
-        <v>8.791782312153519</v>
+        <v>6.846328275789726</v>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="M15" t="n">
-        <v>66.66666666666667</v>
+        <v>70</v>
       </c>
       <c r="N15" t="n">
-        <v>15.61607838434473</v>
+        <v>15.0289238728392</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.079748591109686</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2180,20 +2200,16 @@
         <v>80.43478260869566</v>
       </c>
       <c r="X15" t="n">
-        <v>33.58229315482664</v>
+        <v>25.94456260816873</v>
       </c>
       <c r="Y15" t="n">
-        <v>13.43479556353752</v>
+        <v>14.98278588781</v>
       </c>
       <c r="Z15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>28.57142857142857</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>10.69899700373172</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
         <v>10</v>
       </c>
@@ -2229,10 +2245,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C16" t="n">
-        <v>33.20368275984461</v>
+        <v>32.18915644092001</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2257,25 +2273,25 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>20.84566539545038</v>
+        <v>21.6745099724732</v>
       </c>
       <c r="K16" t="n">
-        <v>3.656189865298276</v>
+        <v>1.55239327296246</v>
       </c>
       <c r="L16" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>61.11111111111111</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="N16" t="n">
-        <v>16.19174944747391</v>
+        <v>15.68734159447019</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>6.120049504950487</v>
+        <v>8.318471337579659</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2338,10 +2354,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3266946431089913</v>
+        <v>0.2933928931140198</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2382,7 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>58.07169493011239</v>
+        <v>62.34567359062095</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2383,25 +2399,25 @@
         <v>8.000000000000007</v>
       </c>
       <c r="Q17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R17" t="n">
-        <v>65.21739130434783</v>
+        <v>65.95744680851064</v>
       </c>
       <c r="S17" t="n">
-        <v>47.47414077770186</v>
+        <v>47.88748408618216</v>
       </c>
       <c r="T17" t="n">
-        <v>17.74325052664597</v>
+        <v>18.06996272232848</v>
       </c>
       <c r="U17" t="n">
-        <v>50.77005884206276</v>
+        <v>51.67092456194193</v>
       </c>
       <c r="V17" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="W17" t="n">
-        <v>73.86363636363636</v>
+        <v>74.15730337078652</v>
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
@@ -2443,10 +2459,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06390064979130475</v>
+        <v>0.05966270582172058</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,25 +2487,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>41.93441024417237</v>
+        <v>44.01451546590328</v>
       </c>
       <c r="K18" t="n">
-        <v>2.640261742312822</v>
+        <v>1.041665932436375</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>66.66666666666667</v>
+        <v>50</v>
       </c>
       <c r="N18" t="n">
-        <v>12.28395657351243</v>
+        <v>7.828467810803508</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>7.170420391331844</v>
+        <v>8.86598017252982</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2552,14 +2568,14 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02568354173874119</v>
+        <v>0.02521825673000939</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2569,7 +2585,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2580,25 +2596,25 @@
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>16.0945098434464</v>
+        <v>19.75808205502609</v>
       </c>
       <c r="K19" t="n">
-        <v>3.275644302402747</v>
+        <v>6.034487225029839</v>
       </c>
       <c r="L19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M19" t="n">
-        <v>57.69230769230769</v>
+        <v>68.18181818181819</v>
       </c>
       <c r="N19" t="n">
-        <v>24.49254697987282</v>
+        <v>22.40273625909982</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>6.511076007337779</v>
+        <v>3.739833028620621</v>
       </c>
       <c r="Q19" t="n">
         <v>14</v>
@@ -2621,27 +2637,17 @@
       <c r="W19" t="n">
         <v>71.42857142857143</v>
       </c>
-      <c r="X19" t="n">
-        <v>20.26411217973316</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>13.34606443573016</v>
-      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>66.66666666666667</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>10.82905106195671</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
         <v>10</v>
       </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="n">
         <v>16</v>
       </c>
@@ -2671,10 +2677,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C20" t="n">
-        <v>1.651965436072488</v>
+        <v>1.640211793167899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2702,22 +2708,22 @@
         <v>19.82174384694231</v>
       </c>
       <c r="K20" t="n">
-        <v>7.743362034346446</v>
+        <v>6.976773959899552</v>
       </c>
       <c r="L20" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M20" t="n">
-        <v>57.14285714285715</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N20" t="n">
-        <v>9.77179969240437</v>
+        <v>10.09992405598111</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>2.094456607855055</v>
+        <v>2.826058337890913</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
@@ -2780,24 +2786,24 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8650216543241483</v>
+        <v>0.8471693848153991</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AL_BEKLE_EŞİK</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2811,22 +2817,22 @@
         <v>17.90453399434356</v>
       </c>
       <c r="K21" t="n">
-        <v>6.76742411691853</v>
+        <v>4.56396386761484</v>
       </c>
       <c r="L21" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M21" t="n">
-        <v>45.45454545454545</v>
+        <v>45.94594594594594</v>
       </c>
       <c r="N21" t="n">
-        <v>21.10628509391671</v>
+        <v>13.3870059693234</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1544493962238</v>
+        <v>3.286061474042268</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2853,22 +2859,22 @@
         <v>11.00964066838261</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.821484806114095</v>
+        <v>5.806411733214089</v>
       </c>
       <c r="Z21" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="AA21" t="n">
-        <v>34.14634146341464</v>
+        <v>48.27586206896552</v>
       </c>
       <c r="AB21" t="n">
-        <v>11.66619032230929</v>
+        <v>10.31047239868942</v>
       </c>
       <c r="AC21" t="n">
         <v>4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.1856081823742417</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>40</v>
@@ -2877,10 +2883,10 @@
         <v>62.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>36.06163792090061</v>
+        <v>35.99913792090061</v>
       </c>
       <c r="AH21" t="n">
-        <v>26.43836207909939</v>
+        <v>26.50086207909939</v>
       </c>
       <c r="AI21" t="n">
         <v>47.0324391373011</v>
@@ -2899,10 +2905,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2907376846747536</v>
+        <v>0.2810912968742545</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2916,7 +2922,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2934,22 +2940,22 @@
         <v>26.84577757624037</v>
       </c>
       <c r="K22" t="n">
-        <v>8.314480736683505</v>
+        <v>4.720713775360297</v>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
         <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>12.48981676768944</v>
+        <v>17.88515295453268</v>
       </c>
       <c r="O22" t="n">
         <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>1.55613474011298</v>
+        <v>5.041300841364094</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
@@ -2976,22 +2982,22 @@
         <v>10.71975172264199</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.172395573992802</v>
+        <v>5.418218388268747</v>
       </c>
       <c r="Z22" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AA22" t="n">
-        <v>35.71428571428572</v>
+        <v>40.90909090909091</v>
       </c>
       <c r="AB22" t="n">
-        <v>13.73881392598284</v>
+        <v>15.19884995681324</v>
       </c>
       <c r="AC22" t="n">
         <v>5</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.890395244366728</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3014,19 +3020,19 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5017536730517946</v>
+        <v>0.4896032030383939</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3042,10 +3048,10 @@
         <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>50.26314571687826</v>
+        <v>49.48699344169833</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>8.644220472081043</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3056,7 +3062,7 @@
         <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>5.000000000000004</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
@@ -3074,10 +3080,10 @@
         <v>43.64971778135299</v>
       </c>
       <c r="V23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W23" t="n">
-        <v>82.35294117647059</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
@@ -3119,10 +3125,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1265684906064916</v>
+        <v>0.113789697046526</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3147,13 +3153,13 @@
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>35.82734702356686</v>
+        <v>41.95934437990149</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3224,10 +3230,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C25" t="n">
-        <v>3.223798033711111</v>
+        <v>3.169709415363113</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3255,22 +3261,22 @@
         <v>26.01552790938969</v>
       </c>
       <c r="K25" t="n">
-        <v>4.849074233010997</v>
+        <v>3.089925086250767</v>
       </c>
       <c r="L25" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M25" t="n">
-        <v>68.42105263157895</v>
+        <v>62.5</v>
       </c>
       <c r="N25" t="n">
-        <v>13.65276053951098</v>
+        <v>13.62544328966082</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>3.005201323939732</v>
+        <v>4.762904725792749</v>
       </c>
       <c r="Q25" t="n">
         <v>44</v>
@@ -3333,10 +3339,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4286069570696814</v>
+        <v>0.4141534933569065</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3364,22 +3370,22 @@
         <v>13.95841889083065</v>
       </c>
       <c r="K26" t="n">
-        <v>4.583322796137557</v>
+        <v>1.056568887778475</v>
       </c>
       <c r="L26" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="M26" t="n">
-        <v>45.83333333333334</v>
+        <v>48.27586206896552</v>
       </c>
       <c r="N26" t="n">
-        <v>13.64226975620035</v>
+        <v>13.82346420216283</v>
       </c>
       <c r="O26" t="n">
         <v>6</v>
       </c>
       <c r="P26" t="n">
-        <v>1.354591885193734</v>
+        <v>4.89174644125423</v>
       </c>
       <c r="Q26" t="n">
         <v>32</v>
@@ -3442,10 +3448,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C27" t="n">
-        <v>45.28522079374847</v>
+        <v>40.67725247056389</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3462,11 +3468,7 @@
           <t>VERİ_YETERSİZ</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %77.78: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>5</v>
       </c>
@@ -3474,19 +3476,19 @@
         <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>21.16790601611432</v>
+        <v>29.1894147017516</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M27" t="n">
-        <v>77.77777777777777</v>
+        <v>60</v>
       </c>
       <c r="N27" t="n">
-        <v>27.55321188300974</v>
+        <v>21.87909233352229</v>
       </c>
       <c r="O27" t="n">
         <v>8</v>
@@ -3506,10 +3508,10 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>59.36116514542724</v>
+        <v>57.91892587122813</v>
       </c>
       <c r="Y27" t="n">
-        <v>21.16790601611432</v>
+        <v>29.1894147017516</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -3541,10 +3543,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C28" t="n">
-        <v>1.321161449708689</v>
+        <v>1.242460401955633</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3569,19 +3571,19 @@
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>26.5551888271766</v>
+        <v>28.97658552769321</v>
       </c>
       <c r="K28" t="n">
-        <v>7.345578309870882</v>
+        <v>4.3927635889492</v>
       </c>
       <c r="L28" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M28" t="n">
-        <v>55.55555555555556</v>
+        <v>46.15384615384615</v>
       </c>
       <c r="N28" t="n">
-        <v>15.82052131603536</v>
+        <v>22.48174323579381</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
@@ -3590,25 +3592,25 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R28" t="n">
-        <v>56.41025641025641</v>
+        <v>55</v>
       </c>
       <c r="S28" t="n">
-        <v>61.25836577699111</v>
+        <v>61.28940663256633</v>
       </c>
       <c r="T28" t="n">
-        <v>-4.848109366734697</v>
+        <v>-6.289406632566326</v>
       </c>
       <c r="U28" t="n">
-        <v>40.97569164866947</v>
+        <v>39.82909179893205</v>
       </c>
       <c r="V28" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="W28" t="n">
-        <v>66.12903225806451</v>
+        <v>65.07936507936508</v>
       </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
@@ -3650,14 +3652,14 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3737469102719835</v>
+        <v>0.3977513520522094</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3667,7 +3669,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3681,10 +3683,10 @@
         <v>27.65210909859499</v>
       </c>
       <c r="K29" t="n">
-        <v>12.86198706805328</v>
+        <v>20.11071320683035</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3719,18 +3721,22 @@
         <v>31.20488584758381</v>
       </c>
       <c r="Y29" t="n">
-        <v>13.98034734837454</v>
+        <v>8.455609384578233</v>
       </c>
       <c r="Z29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>10.20546286194248</v>
+      </c>
       <c r="AC29" t="n">
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.687040139804696</v>
       </c>
       <c r="AE29" t="n">
         <v>5</v>
@@ -3761,10 +3767,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3953210697169328</v>
+        <v>0.3897553320671308</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3792,16 +3798,16 @@
         <v>21.04235192254695</v>
       </c>
       <c r="K30" t="n">
-        <v>7.93707753906161</v>
+        <v>6.417428063512776</v>
       </c>
       <c r="L30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M30" t="n">
-        <v>52.63157894736842</v>
+        <v>65</v>
       </c>
       <c r="N30" t="n">
-        <v>11.48365102803138</v>
+        <v>11.10658834140744</v>
       </c>
       <c r="O30" t="n">
         <v>5</v>
@@ -3834,43 +3840,39 @@
         <v>26.71344279693404</v>
       </c>
       <c r="Y30" t="n">
-        <v>14.77542217162011</v>
+        <v>15.97530165653484</v>
       </c>
       <c r="Z30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>22.32041901315758</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AF30" t="n">
-        <v>57.5</v>
+        <v>59.09090909090909</v>
       </c>
       <c r="AG30" t="n">
-        <v>39.50945405858332</v>
+        <v>40.00449457269228</v>
       </c>
       <c r="AH30" t="n">
-        <v>17.99054594141668</v>
+        <v>19.08641451821681</v>
       </c>
       <c r="AI30" t="n">
-        <v>42.19506854199106</v>
+        <v>44.4097537410319</v>
       </c>
       <c r="AJ30" t="n">
         <v>63</v>
       </c>
       <c r="AK30" t="n">
-        <v>52.38095238095238</v>
+        <v>58.73015873015873</v>
       </c>
     </row>
     <row r="31">
@@ -3880,10 +3882,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2601229076479458</v>
+        <v>0.2634590270685997</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3908,10 +3910,10 @@
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>17.8972608580232</v>
+        <v>17.8938886725662</v>
       </c>
       <c r="K31" t="n">
-        <v>16.25343851917638</v>
+        <v>17.73957225548916</v>
       </c>
       <c r="L31" t="n">
         <v>1</v>
@@ -3949,7 +3951,7 @@
         <v>56.41090041471573</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.552742629022233</v>
+        <v>3.328615727463691</v>
       </c>
       <c r="Z31" t="n">
         <v>1</v>
@@ -3960,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="AD31" t="n">
-        <v>5.707086322874366</v>
+        <v>6.901095213169095</v>
       </c>
       <c r="AE31" t="n">
         <v>10</v>
@@ -3991,10 +3993,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C32" t="n">
-        <v>2.290971923095714</v>
+        <v>2.214285920776663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4022,16 +4024,16 @@
         <v>14.66599569135187</v>
       </c>
       <c r="K32" t="n">
-        <v>8.64276194500837</v>
+        <v>5.006148588697523</v>
       </c>
       <c r="L32" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="M32" t="n">
-        <v>51.85185185185185</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="N32" t="n">
-        <v>10.64601903097006</v>
+        <v>10.5201849477087</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -4064,22 +4066,22 @@
         <v>11.59844220999629</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.648495988345578</v>
+        <v>5.907155593528768</v>
       </c>
       <c r="Z32" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AA32" t="n">
-        <v>39.58333333333334</v>
+        <v>27.58620689655172</v>
       </c>
       <c r="AB32" t="n">
-        <v>11.53490202973891</v>
+        <v>9.761054252179616</v>
       </c>
       <c r="AC32" t="n">
         <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>5.497094334581377</v>
+        <v>2.224233330039804</v>
       </c>
       <c r="AE32" t="n">
         <v>26</v>
@@ -4110,10 +4112,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C33" t="n">
-        <v>1.761890963277646</v>
+        <v>1.749900925466952</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4141,16 +4143,16 @@
         <v>13.64170455604291</v>
       </c>
       <c r="K33" t="n">
-        <v>8.170326994998245</v>
+        <v>7.434205215786394</v>
       </c>
       <c r="L33" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M33" t="n">
-        <v>54.54545454545455</v>
+        <v>68.75</v>
       </c>
       <c r="N33" t="n">
-        <v>10.9883450025001</v>
+        <v>11.37987313105728</v>
       </c>
       <c r="O33" t="n">
         <v>4</v>
@@ -4197,10 +4199,10 @@
         <v>48.27586206896552</v>
       </c>
       <c r="AG33" t="n">
-        <v>32.85620062512866</v>
+        <v>32.84251699075537</v>
       </c>
       <c r="AH33" t="n">
-        <v>15.41966144383686</v>
+        <v>15.43334507821015</v>
       </c>
       <c r="AI33" t="n">
         <v>31.38609015268349</v>
@@ -4219,10 +4221,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C34" t="n">
-        <v>0.742562546216917</v>
+        <v>0.7467063813198411</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4247,19 +4249,19 @@
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>17.91852285443199</v>
+        <v>15.02963534236333</v>
       </c>
       <c r="K34" t="n">
-        <v>4.905510166682769</v>
+        <v>5.490930395232607</v>
       </c>
       <c r="L34" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="M34" t="n">
-        <v>57.14285714285715</v>
+        <v>60.52631578947368</v>
       </c>
       <c r="N34" t="n">
-        <v>12.23954432356245</v>
+        <v>14.00949150017786</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -4292,16 +4294,16 @@
         <v>11.67247563853926</v>
       </c>
       <c r="Y34" t="n">
-        <v>6.05965385218089</v>
+        <v>5.535424201855288</v>
       </c>
       <c r="Z34" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA34" t="n">
-        <v>39.1304347826087</v>
+        <v>42.30769230769231</v>
       </c>
       <c r="AB34" t="n">
-        <v>10.82707370702024</v>
+        <v>9.575227046699824</v>
       </c>
       <c r="AC34" t="n">
         <v>2</v>
@@ -4316,10 +4318,10 @@
         <v>57.57575757575758</v>
       </c>
       <c r="AG34" t="n">
-        <v>22.95497821872625</v>
+        <v>23.02681209065788</v>
       </c>
       <c r="AH34" t="n">
-        <v>34.62077935703132</v>
+        <v>34.5489454850997</v>
       </c>
       <c r="AI34" t="n">
         <v>40.80726333731245</v>
@@ -4338,19 +4340,19 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C35" t="n">
-        <v>1.165005468884894</v>
+        <v>1.278340034931181</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BAZ_ORAN_YETERSİZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4366,10 +4368,10 @@
         <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>48.57465762533187</v>
+        <v>53.57236841441497</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>21.53995983178112</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -4380,7 +4382,7 @@
         <v>6</v>
       </c>
       <c r="P35" t="n">
-        <v>6.000000000000005</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>7</v>
@@ -4443,10 +4445,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C36" t="n">
-        <v>0.06944829912170786</v>
+        <v>0.06622355155920685</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4471,25 +4473,25 @@
         <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>21.1181667514496</v>
+        <v>25.04718708238027</v>
       </c>
       <c r="K36" t="n">
-        <v>0.8955286834486209</v>
+        <v>1.253917217794642</v>
       </c>
       <c r="L36" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="M36" t="n">
-        <v>56.52173913043478</v>
+        <v>56.25</v>
       </c>
       <c r="N36" t="n">
-        <v>14.82977244487345</v>
+        <v>14.5909878637283</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>1.094668248398367</v>
+        <v>0.7368433762424687</v>
       </c>
       <c r="Q36" t="n">
         <v>10</v>
@@ -4552,10 +4554,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C37" t="n">
-        <v>0.05403817407846314</v>
+        <v>0.05310185495857245</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4583,22 +4585,22 @@
         <v>28.89715284260867</v>
       </c>
       <c r="K37" t="n">
-        <v>3.922248654927141</v>
+        <v>2.121588472435465</v>
       </c>
       <c r="L37" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="M37" t="n">
-        <v>68.75</v>
+        <v>68.18181818181819</v>
       </c>
       <c r="N37" t="n">
-        <v>16.92641827120465</v>
+        <v>16.97175703824344</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>5.848363968002634</v>
+        <v>7.714736565903579</v>
       </c>
       <c r="Q37" t="n">
         <v>27</v>
@@ -4661,10 +4663,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C38" t="n">
-        <v>1.591352183464562</v>
+        <v>1.558201203509504</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4692,22 +4694,22 @@
         <v>15.42052714918329</v>
       </c>
       <c r="K38" t="n">
-        <v>7.463427032142955</v>
+        <v>5.224753561580053</v>
       </c>
       <c r="L38" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="M38" t="n">
-        <v>61.29032258064516</v>
+        <v>67.5</v>
       </c>
       <c r="N38" t="n">
-        <v>11.24487615979568</v>
+        <v>11.02332507947247</v>
       </c>
       <c r="O38" t="n">
         <v>10</v>
       </c>
       <c r="P38" t="n">
-        <v>2.360405803081589</v>
+        <v>4.53813981671658</v>
       </c>
       <c r="Q38" t="n">
         <v>42</v>
@@ -4748,10 +4750,10 @@
         <v>56.66666666666666</v>
       </c>
       <c r="AG38" t="n">
-        <v>15.45143185980763</v>
+        <v>15.35619376456953</v>
       </c>
       <c r="AH38" t="n">
-        <v>41.21523480685904</v>
+        <v>41.31047290209713</v>
       </c>
       <c r="AI38" t="n">
         <v>39.19730700081361</v>
@@ -4770,10 +4772,10 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C39" t="n">
-        <v>2.722455424306566</v>
+        <v>2.663293774090226</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4801,16 +4803,16 @@
         <v>15.16246653075239</v>
       </c>
       <c r="K39" t="n">
-        <v>12.44596123221329</v>
+        <v>10.0023992303286</v>
       </c>
       <c r="L39" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M39" t="n">
-        <v>61.11111111111111</v>
+        <v>40.90909090909091</v>
       </c>
       <c r="N39" t="n">
-        <v>13.67042644814202</v>
+        <v>16.72571810614035</v>
       </c>
       <c r="O39" t="n">
         <v>5</v>
@@ -4834,31 +4836,31 @@
         <v>49.16636571945582</v>
       </c>
       <c r="V39" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="W39" t="n">
-        <v>67.69230769230769</v>
+        <v>67.1875</v>
       </c>
       <c r="X39" t="n">
-        <v>12.7854155610625</v>
+        <v>13.30501958187764</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.3009736029792154</v>
+        <v>2.914804978399443</v>
       </c>
       <c r="Z39" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="AA39" t="n">
-        <v>39.1304347826087</v>
+        <v>41.07142857142857</v>
       </c>
       <c r="AB39" t="n">
-        <v>12.20529778138521</v>
+        <v>12.57106564064379</v>
       </c>
       <c r="AC39" t="n">
         <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>5.716230742641526</v>
+        <v>3.177822345532844</v>
       </c>
       <c r="AE39" t="n">
         <v>40</v>
@@ -4867,10 +4869,10 @@
         <v>60</v>
       </c>
       <c r="AG39" t="n">
-        <v>39.89436953524482</v>
+        <v>39.64113817054274</v>
       </c>
       <c r="AH39" t="n">
-        <v>20.10563046475518</v>
+        <v>20.35886182945726</v>
       </c>
       <c r="AI39" t="n">
         <v>44.59589366034619</v>
@@ -4889,10 +4891,10 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1849215005189366</v>
+        <v>0.1673015998277285</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4917,25 +4919,25 @@
         <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>29.82535900952999</v>
+        <v>36.97863969531091</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>0.7407341627803543</v>
       </c>
       <c r="L40" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M40" t="n">
-        <v>63.63636363636363</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N40" t="n">
-        <v>12.83266905617622</v>
+        <v>10.91215386819462</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>3.000000000000003</v>
+        <v>2.242653734852729</v>
       </c>
       <c r="Q40" t="n">
         <v>29</v>
@@ -4998,19 +5000,19 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9874808409202831</v>
+        <v>0.9915080414766096</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5026,13 +5028,13 @@
         <v>10</v>
       </c>
       <c r="J41" t="n">
-        <v>51.10100326898552</v>
+        <v>56.07945587151675</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>11.78918744350057</v>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
@@ -5040,7 +5042,7 @@
         <v>10</v>
       </c>
       <c r="P41" t="n">
-        <v>10.00000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>11</v>
@@ -5103,19 +5105,19 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C42" t="n">
-        <v>2.829298895271888</v>
+        <v>2.870370638043823</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5123,11 +5125,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>5</v>
       </c>
@@ -5135,40 +5133,36 @@
         <v>10</v>
       </c>
       <c r="J42" t="n">
-        <v>26.84263279333992</v>
+        <v>34.26285084000703</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>12.9032258064516</v>
       </c>
       <c r="L42" t="n">
-        <v>4</v>
-      </c>
-      <c r="M42" t="n">
-        <v>75</v>
-      </c>
-      <c r="N42" t="n">
-        <v>16.10719482417057</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
         <v>2</v>
       </c>
       <c r="P42" t="n">
-        <v>2.000000000000002</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="S42" t="n">
-        <v>80.95238095238095</v>
+        <v>83.79281537176274</v>
       </c>
       <c r="T42" t="n">
-        <v>-80.95238095238095</v>
+        <v>-50.45948203842941</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>6.149194472039621</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -5212,10 +5206,10 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C43" t="n">
-        <v>5.670926015914056</v>
+        <v>5.453704212283263</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5229,7 +5223,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SATMA_BEKLE</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5244,25 +5238,25 @@
         <v>10</v>
       </c>
       <c r="J43" t="n">
-        <v>26.64182087935456</v>
+        <v>27.29922700949644</v>
       </c>
       <c r="K43" t="n">
-        <v>3.0511605942664</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M43" t="n">
         <v>100</v>
       </c>
       <c r="N43" t="n">
-        <v>15.06274995757913</v>
+        <v>23.4583367455168</v>
       </c>
       <c r="O43" t="n">
         <v>10</v>
       </c>
       <c r="P43" t="n">
-        <v>6.74309669649682</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q43" t="n">
         <v>10</v>
@@ -5285,27 +5279,17 @@
       <c r="W43" t="n">
         <v>66.66666666666667</v>
       </c>
-      <c r="X43" t="n">
-        <v>10.08403361344536</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>6.38864037620076</v>
-      </c>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>46.15384615384615</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>10.80118519534348</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
         <v>2</v>
       </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="n">
         <v>10</v>
       </c>
@@ -5335,10 +5319,10 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C44" t="n">
-        <v>3.667609760292242</v>
+        <v>3.294775376992942</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5363,19 +5347,19 @@
         <v>10</v>
       </c>
       <c r="J44" t="n">
-        <v>28.53738809385965</v>
+        <v>35.65405929895734</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M44" t="n">
-        <v>71.42857142857143</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N44" t="n">
-        <v>19.20931872006684</v>
+        <v>10.36119732950944</v>
       </c>
       <c r="O44" t="n">
         <v>10</v>
@@ -5436,10 +5420,10 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C45" t="n">
-        <v>0.01993042900566817</v>
+        <v>0.01927248856972281</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5464,25 +5448,25 @@
         <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>19.69914397275242</v>
+        <v>20.71528458323236</v>
       </c>
       <c r="K45" t="n">
-        <v>2.105267390581766</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="M45" t="n">
-        <v>55.55555555555556</v>
+        <v>63.82978723404256</v>
       </c>
       <c r="N45" t="n">
-        <v>17.81786928956835</v>
+        <v>16.09991170822055</v>
       </c>
       <c r="O45" t="n">
         <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>7.731954296949861</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q45" t="n">
         <v>38</v>
@@ -5545,14 +5529,14 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C46" t="n">
-        <v>8.819728233083724</v>
+        <v>9.092924128374538</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5562,12 +5546,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -5577,19 +5561,19 @@
         <v>10</v>
       </c>
       <c r="J46" t="n">
-        <v>28.14791119347603</v>
+        <v>28.1449600304398</v>
       </c>
       <c r="K46" t="n">
-        <v>13.25857519788918</v>
+        <v>16.76202563654159</v>
       </c>
       <c r="L46" t="n">
         <v>4</v>
       </c>
       <c r="M46" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N46" t="n">
-        <v>26.46943788476914</v>
+        <v>34.70493427584464</v>
       </c>
       <c r="O46" t="n">
         <v>8</v>
@@ -5618,31 +5602,41 @@
       <c r="W46" t="n">
         <v>65.06024096385542</v>
       </c>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
+      <c r="X46" t="n">
+        <v>17.28857366646963</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.4489337822671136</v>
+      </c>
       <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="inlineStr"/>
-      <c r="AB46" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>48.93617021276596</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>9.640965602971743</v>
+      </c>
       <c r="AC46" t="n">
         <v>3</v>
       </c>
-      <c r="AD46" t="inlineStr"/>
+      <c r="AD46" t="n">
+        <v>2.56257046223225</v>
+      </c>
       <c r="AE46" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF46" t="n">
-        <v>60</v>
+        <v>58.97435897435897</v>
       </c>
       <c r="AG46" t="n">
-        <v>18.63060337209256</v>
+        <v>18.81738412916791</v>
       </c>
       <c r="AH46" t="n">
-        <v>41.36939662790743</v>
+        <v>40.15697484519106</v>
       </c>
       <c r="AI46" t="n">
-        <v>44.59589366034619</v>
+        <v>43.41862288289698</v>
       </c>
       <c r="AJ46" t="n">
         <v>80</v>
@@ -5658,10 +5652,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9821386204738698</v>
+        <v>0.9537831671583509</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5689,22 +5683,22 @@
         <v>18.95305070442179</v>
       </c>
       <c r="K47" t="n">
-        <v>7.96668855640601</v>
+        <v>4.849568087693323</v>
       </c>
       <c r="L47" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M47" t="n">
-        <v>52.63157894736842</v>
+        <v>57.69230769230769</v>
       </c>
       <c r="N47" t="n">
-        <v>17.05870831769058</v>
+        <v>14.85323904429776</v>
       </c>
       <c r="O47" t="n">
         <v>10</v>
       </c>
       <c r="P47" t="n">
-        <v>1.883276657625488</v>
+        <v>4.912210900095459</v>
       </c>
       <c r="Q47" t="n">
         <v>51</v>
@@ -5731,10 +5725,10 @@
         <v>66.65983471422588</v>
       </c>
       <c r="Y47" t="n">
-        <v>12.49629266957479</v>
+        <v>15.02262371533445</v>
       </c>
       <c r="Z47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr"/>
@@ -5745,19 +5739,19 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AF47" t="n">
-        <v>53.65853658536585</v>
+        <v>55</v>
       </c>
       <c r="AG47" t="n">
-        <v>30.36663735610388</v>
+        <v>30.21414525634767</v>
       </c>
       <c r="AH47" t="n">
-        <v>23.29189922926197</v>
+        <v>24.78585474365233</v>
       </c>
       <c r="AI47" t="n">
-        <v>38.74647126766948</v>
+        <v>39.82909179893205</v>
       </c>
       <c r="AJ47" t="n">
         <v>76</v>
@@ -5773,10 +5767,10 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C48" t="n">
-        <v>0.04992880657839122</v>
+        <v>0.04797619310492277</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5801,25 +5795,25 @@
         <v>10</v>
       </c>
       <c r="J48" t="n">
-        <v>27.02060703861709</v>
+        <v>27.01760957409671</v>
       </c>
       <c r="K48" t="n">
-        <v>8.000003111111109</v>
+        <v>3.772081746982936</v>
       </c>
       <c r="L48" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M48" t="n">
-        <v>66.66666666666667</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N48" t="n">
-        <v>11.66660468424351</v>
+        <v>12.20818915794003</v>
       </c>
       <c r="O48" t="n">
         <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>1.851848917847976</v>
+        <v>6.001535430504301</v>
       </c>
       <c r="Q48" t="n">
         <v>47</v>
@@ -5882,10 +5876,10 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2747111601774241</v>
+        <v>0.2718651094331881</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5913,16 +5907,16 @@
         <v>18.76252681801688</v>
       </c>
       <c r="K49" t="n">
-        <v>11.10639865770351</v>
+        <v>9.955318925868383</v>
       </c>
       <c r="L49" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M49" t="n">
-        <v>45</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="N49" t="n">
-        <v>14.92483544763925</v>
+        <v>13.86153369116056</v>
       </c>
       <c r="O49" t="n">
         <v>5</v>
@@ -5946,31 +5940,31 @@
         <v>59.10955707120475</v>
       </c>
       <c r="V49" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="W49" t="n">
-        <v>67.14285714285714</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="X49" t="n">
-        <v>11.68810497984585</v>
+        <v>12.27714841887641</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.5208310430616758</v>
+        <v>2.067944836242097</v>
       </c>
       <c r="Z49" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="AA49" t="n">
-        <v>39.28571428571428</v>
+        <v>41.93548387096774</v>
       </c>
       <c r="AB49" t="n">
-        <v>10.20021926404256</v>
+        <v>10.41455451723006</v>
       </c>
       <c r="AC49" t="n">
         <v>10</v>
       </c>
       <c r="AD49" t="n">
-        <v>9.528797894402985</v>
+        <v>8.099549376855464</v>
       </c>
       <c r="AE49" t="n">
         <v>44</v>
@@ -5979,10 +5973,10 @@
         <v>61.36363636363637</v>
       </c>
       <c r="AG49" t="n">
-        <v>34.41304081092033</v>
+        <v>34.14075060113012</v>
       </c>
       <c r="AH49" t="n">
-        <v>26.95059555271604</v>
+        <v>27.22288576250624</v>
       </c>
       <c r="AI49" t="n">
         <v>46.62357539237828</v>
@@ -6001,10 +5995,10 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7133860804024121</v>
+        <v>0.690529171279506</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6032,16 +6026,16 @@
         <v>16.75569689884803</v>
       </c>
       <c r="K50" t="n">
-        <v>11.10714662599572</v>
+        <v>7.547270672285977</v>
       </c>
       <c r="L50" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="M50" t="n">
-        <v>61.90476190476191</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N50" t="n">
-        <v>15.92581263012463</v>
+        <v>16.43383804039059</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
@@ -6071,25 +6065,25 @@
         <v>70</v>
       </c>
       <c r="X50" t="n">
-        <v>13.15520260429783</v>
+        <v>13.15985019989079</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.809952994794362</v>
+        <v>4.959868290467417</v>
       </c>
       <c r="Z50" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="AA50" t="n">
-        <v>42.85714285714285</v>
+        <v>47.22222222222222</v>
       </c>
       <c r="AB50" t="n">
-        <v>13.02416954739634</v>
+        <v>12.69551196731925</v>
       </c>
       <c r="AC50" t="n">
         <v>5</v>
       </c>
       <c r="AD50" t="n">
-        <v>3.248849656866459</v>
+        <v>0.04222606683168539</v>
       </c>
       <c r="AE50" t="n">
         <v>42</v>
@@ -6120,10 +6114,10 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C51" t="n">
-        <v>0.109925556587129</v>
+        <v>0.09882276402381596</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6148,13 +6142,13 @@
         <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>43.56819286730693</v>
+        <v>49.26796522252411</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -6165,25 +6159,25 @@
         <v>4.000000000000004</v>
       </c>
       <c r="Q51" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R51" t="n">
-        <v>76.92307692307692</v>
+        <v>78.57142857142857</v>
       </c>
       <c r="S51" t="n">
-        <v>37.23345648952936</v>
+        <v>40.37749531170584</v>
       </c>
       <c r="T51" t="n">
-        <v>39.68962043354756</v>
+        <v>38.19393325972273</v>
       </c>
       <c r="U51" t="n">
-        <v>49.7436240532725</v>
+        <v>52.41076941339971</v>
       </c>
       <c r="V51" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W51" t="n">
-        <v>84.61538461538461</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
@@ -6225,10 +6219,10 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C52" t="n">
-        <v>4.493592399942317</v>
+        <v>4.401918337381274</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6242,7 +6236,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -6256,22 +6250,22 @@
         <v>14.1037450661144</v>
       </c>
       <c r="K52" t="n">
-        <v>9.045484078318179</v>
+        <v>6.820840265603145</v>
       </c>
       <c r="L52" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="M52" t="n">
-        <v>65.21739130434783</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="N52" t="n">
-        <v>11.9939935339122</v>
+        <v>14.5070718343432</v>
       </c>
       <c r="O52" t="n">
         <v>10</v>
       </c>
       <c r="P52" t="n">
-        <v>0.8753374151618143</v>
+        <v>2.976160575494524</v>
       </c>
       <c r="Q52" t="n">
         <v>37</v>
@@ -6294,27 +6288,17 @@
       <c r="W52" t="n">
         <v>67.9245283018868</v>
       </c>
-      <c r="X52" t="n">
-        <v>16.53731163255363</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>6.334013002198191</v>
-      </c>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>61.11111111111111</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>13.01782768349203</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
         <v>8</v>
       </c>
-      <c r="AD52" t="n">
-        <v>1.778646711789733</v>
-      </c>
+      <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="n">
         <v>37</v>
       </c>
@@ -6322,10 +6306,10 @@
         <v>67.56756756756756</v>
       </c>
       <c r="AG52" t="n">
-        <v>39.1150650126505</v>
+        <v>38.63667334050754</v>
       </c>
       <c r="AH52" t="n">
-        <v>28.45250255491706</v>
+        <v>28.93089422706003</v>
       </c>
       <c r="AI52" t="n">
         <v>51.4636672419722</v>
@@ -6344,10 +6328,10 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9665230616153951</v>
+        <v>0.8680820946095076</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6372,7 +6356,7 @@
         <v>10</v>
       </c>
       <c r="J53" t="n">
-        <v>43.76257775955705</v>
+        <v>49.49039372911594</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -6441,10 +6425,10 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C54" t="n">
-        <v>0.06472252723631114</v>
+        <v>0.05822751681222214</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6458,7 +6442,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -6469,25 +6453,25 @@
         <v>10</v>
       </c>
       <c r="J54" t="n">
-        <v>28.78472294046982</v>
+        <v>33.9356360530015</v>
       </c>
       <c r="K54" t="n">
-        <v>3.114867323453763</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="M54" t="n">
-        <v>68.42105263157895</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N54" t="n">
-        <v>20.28852740144532</v>
+        <v>17.02423634720306</v>
       </c>
       <c r="O54" t="n">
         <v>10</v>
       </c>
       <c r="P54" t="n">
-        <v>6.67714836401696</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
@@ -6510,27 +6494,17 @@
       <c r="W54" t="n">
         <v>69.09090909090909</v>
       </c>
-      <c r="X54" t="n">
-        <v>14.75410024187049</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>10.14275994834552</v>
-      </c>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>52.38095238095238</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>19.20175943300067</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
         <v>2</v>
       </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD54" t="inlineStr"/>
       <c r="AE54" t="n">
         <v>7</v>
       </c>
@@ -6560,24 +6534,24 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9057044534756745</v>
+        <v>0.902526548621854</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6591,16 +6565,16 @@
         <v>18.57198344066605</v>
       </c>
       <c r="K55" t="n">
-        <v>11.28066684104148</v>
+        <v>10.89020903779956</v>
       </c>
       <c r="L55" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M55" t="n">
-        <v>70.58823529411765</v>
+        <v>72.22222222222223</v>
       </c>
       <c r="N55" t="n">
-        <v>10.39215044032665</v>
+        <v>10.18679260874353</v>
       </c>
       <c r="O55" t="n">
         <v>6</v>
@@ -6630,25 +6604,25 @@
         <v>72.72727272727273</v>
       </c>
       <c r="X55" t="n">
-        <v>23.0932342837701</v>
+        <v>12.80471089360389</v>
       </c>
       <c r="Y55" t="n">
-        <v>9.386360177339515</v>
+        <v>1.697182538422581</v>
       </c>
       <c r="Z55" t="n">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="AA55" t="n">
-        <v>33.33333333333334</v>
+        <v>41.02564102564103</v>
       </c>
       <c r="AB55" t="n">
-        <v>9.513128641038493</v>
+        <v>11.39607037485165</v>
       </c>
       <c r="AC55" t="n">
         <v>3</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.325310398236179</v>
       </c>
       <c r="AE55" t="n">
         <v>44</v>
@@ -6657,10 +6631,10 @@
         <v>59.09090909090909</v>
       </c>
       <c r="AG55" t="n">
-        <v>38.91733479482351</v>
+        <v>38.75429131656264</v>
       </c>
       <c r="AH55" t="n">
-        <v>20.17357429608558</v>
+        <v>20.33661777434645</v>
       </c>
       <c r="AI55" t="n">
         <v>44.4097537410319</v>
@@ -6679,10 +6653,10 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5079177072480308</v>
+        <v>0.4563889361645767</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6707,7 +6681,7 @@
         <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>64.67093832924205</v>
+        <v>68.25510778316647</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -6768,10 +6742,10 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C57" t="n">
-        <v>1.159868760537146</v>
+        <v>1.042559589663295</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6790,7 +6764,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %82.76: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -6800,19 +6774,19 @@
         <v>10</v>
       </c>
       <c r="J57" t="n">
-        <v>23.83722059793512</v>
+        <v>31.54032702436091</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="M57" t="n">
-        <v>82.75862068965517</v>
+        <v>80</v>
       </c>
       <c r="N57" t="n">
-        <v>22.23894895011225</v>
+        <v>19.66117806531419</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
@@ -6881,10 +6855,10 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6217471831372184</v>
+        <v>0.5584921108580606</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6901,11 +6875,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.95: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>5</v>
       </c>
@@ -6913,19 +6883,19 @@
         <v>10</v>
       </c>
       <c r="J58" t="n">
-        <v>21.8968149997821</v>
+        <v>29.46152384854127</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="M58" t="n">
-        <v>78.94736842105263</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="N58" t="n">
-        <v>21.22911893857821</v>
+        <v>10.20382627899074</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
@@ -6994,31 +6964,27 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C59" t="n">
-        <v>0.775026580575391</v>
+        <v>0.7171825971314459</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %90.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_ADAYI</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>5</v>
       </c>
@@ -7029,22 +6995,22 @@
         <v>17.69918671275772</v>
       </c>
       <c r="K59" t="n">
-        <v>13.24023429647689</v>
+        <v>4.788567731736815</v>
       </c>
       <c r="L59" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="M59" t="n">
-        <v>90</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N59" t="n">
-        <v>13.25416669446671</v>
+        <v>15.87482033620665</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.064678082521932</v>
       </c>
       <c r="Q59" t="n">
         <v>45</v>
@@ -7068,25 +7034,25 @@
         <v>65.51724137931035</v>
       </c>
       <c r="X59" t="n">
-        <v>13.24023429647689</v>
+        <v>15.93246724375246</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>9.612406064459211</v>
       </c>
       <c r="Z59" t="n">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="AA59" t="n">
-        <v>41.50943396226415</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="AB59" t="n">
-        <v>13.01623925622412</v>
+        <v>11.01670908381655</v>
       </c>
       <c r="AC59" t="n">
         <v>6</v>
       </c>
       <c r="AD59" t="n">
-        <v>6.000000000000005</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
         <v>42</v>
@@ -7117,10 +7083,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C60" t="n">
-        <v>10.7768141135758</v>
+        <v>10.76388989266434</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7152,7 +7118,7 @@
         <v>29.37042877474947</v>
       </c>
       <c r="K60" t="n">
-        <v>8.448187706343591</v>
+        <v>8.318129943391227</v>
       </c>
       <c r="L60" t="n">
         <v>5</v>
@@ -7208,10 +7174,10 @@
         <v>61.29032258064516</v>
       </c>
       <c r="AG60" t="n">
-        <v>22.37213780671093</v>
+        <v>22.13404256861569</v>
       </c>
       <c r="AH60" t="n">
-        <v>38.91818477393423</v>
+        <v>39.15628001202947</v>
       </c>
       <c r="AI60" t="n">
         <v>43.82410861966073</v>
@@ -7230,10 +7196,10 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5773660260946987</v>
+        <v>0.5187169640073359</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7247,10 +7213,14 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>BAND</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %85.71: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H61" t="n">
         <v>5</v>
       </c>
@@ -7258,7 +7228,7 @@
         <v>10</v>
       </c>
       <c r="J61" t="n">
-        <v>30.49938183033342</v>
+        <v>37.5592812458115</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -7267,10 +7237,10 @@
         <v>7</v>
       </c>
       <c r="M61" t="n">
-        <v>57.14285714285715</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="N61" t="n">
-        <v>13.94629772108441</v>
+        <v>21.73307982684864</v>
       </c>
       <c r="O61" t="n">
         <v>10</v>
@@ -7294,17 +7264,13 @@
         <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="W61" t="n">
-        <v>78.125</v>
-      </c>
-      <c r="X61" t="n">
-        <v>49.99145178651283</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>30.49938183033342</v>
-      </c>
+        <v>78.78787878787878</v>
+      </c>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="n">
         <v>0</v>
       </c>
@@ -7313,9 +7279,7 @@
       <c r="AC61" t="n">
         <v>4</v>
       </c>
-      <c r="AD61" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD61" t="inlineStr"/>
       <c r="AE61" t="n">
         <v>3</v>
       </c>
@@ -7345,10 +7309,10 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C62" t="n">
-        <v>8.937872525081934</v>
+        <v>8.954531258325996</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7405,25 +7369,25 @@
         <v>72.05882352941177</v>
       </c>
       <c r="X62" t="n">
-        <v>12.70675176372491</v>
+        <v>12.71138094020767</v>
       </c>
       <c r="Y62" t="n">
-        <v>4.552934722984093</v>
+        <v>4.378964415869302</v>
       </c>
       <c r="Z62" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AA62" t="n">
-        <v>46.80851063829788</v>
+        <v>47.91666666666666</v>
       </c>
       <c r="AB62" t="n">
-        <v>16.00314046821093</v>
+        <v>16.29841604387125</v>
       </c>
       <c r="AC62" t="n">
         <v>5</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.468390804597707</v>
+        <v>0.6494759028041419</v>
       </c>
       <c r="AE62" t="n">
         <v>27</v>
@@ -7454,10 +7418,10 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C63" t="n">
-        <v>0.09718652235033334</v>
+        <v>0.09000661948474427</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7482,25 +7446,25 @@
         <v>10</v>
       </c>
       <c r="J63" t="n">
-        <v>22.97168268688948</v>
+        <v>28.15011007597982</v>
       </c>
       <c r="K63" t="n">
-        <v>2.826089626654116</v>
+        <v>2.093015721471381</v>
       </c>
       <c r="L63" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M63" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="N63" t="n">
-        <v>13.0731539657678</v>
+        <v>15.31610697611221</v>
       </c>
       <c r="O63" t="n">
         <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>2.114162253217078</v>
+        <v>2.847388000036566</v>
       </c>
       <c r="Q63" t="n">
         <v>4</v>
@@ -7563,10 +7527,10 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1450606425076003</v>
+        <v>0.1388029225867805</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7575,7 +7539,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ALMA_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7594,22 +7558,22 @@
         <v>18.13256048493127</v>
       </c>
       <c r="K64" t="n">
-        <v>6.938491400272384</v>
+        <v>2.325309517372354</v>
       </c>
       <c r="L64" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="M64" t="n">
-        <v>56.66666666666666</v>
+        <v>56.36363636363637</v>
       </c>
       <c r="N64" t="n">
-        <v>13.51095418880734</v>
+        <v>15.37001991988593</v>
       </c>
       <c r="O64" t="n">
         <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.613909007696247</v>
       </c>
       <c r="Q64" t="n">
         <v>55</v>
@@ -7636,16 +7600,16 @@
         <v>11.36363653581267</v>
       </c>
       <c r="Y64" t="n">
-        <v>3.973599707402919</v>
+        <v>8.11604873870454</v>
       </c>
       <c r="Z64" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="AA64" t="n">
-        <v>57.14285714285715</v>
+        <v>60.52631578947368</v>
       </c>
       <c r="AB64" t="n">
-        <v>14.24438709734272</v>
+        <v>15.56881277457089</v>
       </c>
       <c r="AC64" t="n">
         <v>2</v>
@@ -7660,10 +7624,10 @@
         <v>65.21739130434783</v>
       </c>
       <c r="AG64" t="n">
-        <v>34.80250198692476</v>
+        <v>34.66753997536428</v>
       </c>
       <c r="AH64" t="n">
-        <v>30.41488931742307</v>
+        <v>30.54985132898355</v>
       </c>
       <c r="AI64" t="n">
         <v>50.77005884206276</v>
@@ -7682,10 +7646,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C65" t="n">
-        <v>6.29760443433934</v>
+        <v>6.248181799598965</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7713,22 +7677,22 @@
         <v>15.61952021218654</v>
       </c>
       <c r="K65" t="n">
-        <v>5.841307330901535</v>
+        <v>5.010680966988335</v>
       </c>
       <c r="L65" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M65" t="n">
-        <v>58.06451612903226</v>
+        <v>60</v>
       </c>
       <c r="N65" t="n">
-        <v>13.42191900068244</v>
+        <v>12.69743336329745</v>
       </c>
       <c r="O65" t="n">
         <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>3.929177344811863</v>
+        <v>4.751249098727528</v>
       </c>
       <c r="Q65" t="n">
         <v>50</v>
@@ -7752,19 +7716,19 @@
         <v>63.63636363636363</v>
       </c>
       <c r="X65" t="n">
-        <v>24.47056390537039</v>
+        <v>22.6231738829237</v>
       </c>
       <c r="Y65" t="n">
-        <v>10.6905970604911</v>
+        <v>11.39148357160514</v>
       </c>
       <c r="Z65" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA65" t="n">
-        <v>21.42857142857143</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="AB65" t="n">
-        <v>15.00601971697285</v>
+        <v>9.449341539295848</v>
       </c>
       <c r="AC65" t="n">
         <v>4</v>
@@ -7801,10 +7765,10 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4195663394878228</v>
+        <v>0.4141534933569065</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7832,16 +7796,16 @@
         <v>19.90687209731571</v>
       </c>
       <c r="K66" t="n">
-        <v>8.182522747794717</v>
+        <v>6.786854662497421</v>
       </c>
       <c r="L66" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M66" t="n">
-        <v>70.58823529411765</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N66" t="n">
-        <v>13.82481913979146</v>
+        <v>13.91201740958437</v>
       </c>
       <c r="O66" t="n">
         <v>6</v>
@@ -7874,22 +7838,22 @@
         <v>11.49973494118828</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.975085272752687</v>
+        <v>4.226808504232526</v>
       </c>
       <c r="Z66" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="AA66" t="n">
-        <v>37.73584905660378</v>
+        <v>34.88372093023256</v>
       </c>
       <c r="AB66" t="n">
-        <v>11.36272926096687</v>
+        <v>12.98473980190097</v>
       </c>
       <c r="AC66" t="n">
         <v>6</v>
       </c>
       <c r="AD66" t="n">
-        <v>3.117668009037511</v>
+        <v>1.851448686291135</v>
       </c>
       <c r="AE66" t="n">
         <v>41</v>
@@ -7920,10 +7884,10 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C67" t="n">
-        <v>0.02280698526947051</v>
+        <v>0.0215277787601963</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7940,11 +7904,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>5</v>
       </c>
@@ -7952,25 +7912,21 @@
         <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>24.78267910195914</v>
+        <v>29.11419167395997</v>
       </c>
       <c r="K67" t="n">
-        <v>2.777774897119456</v>
+        <v>2.941173587081836</v>
       </c>
       <c r="L67" t="n">
-        <v>3</v>
-      </c>
-      <c r="M67" t="n">
-        <v>100</v>
-      </c>
-      <c r="N67" t="n">
-        <v>10.56848628706042</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>1.189192025322594</v>
+        <v>1.028574258503534</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -8013,10 +7969,10 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C68" t="n">
-        <v>1.265684905448511</v>
+        <v>1.136871814721512</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8041,7 +7997,7 @@
         <v>10</v>
       </c>
       <c r="J68" t="n">
-        <v>77.33380364754903</v>
+        <v>79.64062013450841</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -8118,10 +8074,10 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4216210306347187</v>
+        <v>0.3790939459803217</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8135,12 +8091,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %78.57: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %87.50: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -8150,25 +8106,25 @@
         <v>10</v>
       </c>
       <c r="J69" t="n">
-        <v>24.31886939425941</v>
+        <v>32.02610313357045</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>0.1082861978731975</v>
       </c>
       <c r="L69" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M69" t="n">
-        <v>78.57142857142857</v>
+        <v>87.5</v>
       </c>
       <c r="N69" t="n">
-        <v>20.61256174271245</v>
+        <v>15.67070805735833</v>
       </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>8.000000000000007</v>
+        <v>7.883177409038966</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -8183,12 +8139,8 @@
       <c r="W69" t="n">
         <v>75</v>
       </c>
-      <c r="X69" t="n">
-        <v>45.36848923911108</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>24.31886939425941</v>
-      </c>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="n">
         <v>0</v>
       </c>
@@ -8197,9 +8149,7 @@
       <c r="AC69" t="n">
         <v>6</v>
       </c>
-      <c r="AD69" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD69" t="inlineStr"/>
       <c r="AE69" t="n">
         <v>0</v>
       </c>
@@ -8221,10 +8171,10 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4425788101450749</v>
+        <v>0.4395767714354</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8249,25 +8199,25 @@
         <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>24.98306858684308</v>
+        <v>24.97998743501082</v>
       </c>
       <c r="K70" t="n">
-        <v>6.739348806283552</v>
+        <v>6.010975215781</v>
       </c>
       <c r="L70" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M70" t="n">
-        <v>72.22222222222223</v>
+        <v>69.56521739130434</v>
       </c>
       <c r="N70" t="n">
-        <v>11.2152183575151</v>
+        <v>12.32698847090811</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>1.181055728571434</v>
+        <v>1.876244209781519</v>
       </c>
       <c r="Q70" t="n">
         <v>31</v>
@@ -8294,7 +8244,7 @@
         <v>44.93251946562029</v>
       </c>
       <c r="Y70" t="n">
-        <v>19.92741591513995</v>
+        <v>20.47055307285353</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -8336,10 +8286,10 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C71" t="n">
-        <v>3.0861343126593</v>
+        <v>3.026190883460922</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8367,16 +8317,16 @@
         <v>12.27124607635546</v>
       </c>
       <c r="K71" t="n">
-        <v>6.872725330383345</v>
+        <v>4.796886434519076</v>
       </c>
       <c r="L71" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="M71" t="n">
-        <v>60.97560975609756</v>
+        <v>57.37704918032787</v>
       </c>
       <c r="N71" t="n">
-        <v>14.15337200123552</v>
+        <v>16.65616103163169</v>
       </c>
       <c r="O71" t="n">
         <v>2</v>
@@ -8445,10 +8395,10 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0480795882857085</v>
+        <v>0.04572090414460812</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8473,25 +8423,25 @@
         <v>10</v>
       </c>
       <c r="J72" t="n">
-        <v>43.42065369293228</v>
+        <v>44.53865067152478</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>5.687209748208977</v>
       </c>
       <c r="L72" t="n">
         <v>3</v>
       </c>
       <c r="M72" t="n">
-        <v>33.33333333333334</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N72" t="n">
-        <v>42.84896195445003</v>
+        <v>29.83974685860161</v>
       </c>
       <c r="O72" t="n">
         <v>10</v>
       </c>
       <c r="P72" t="n">
-        <v>10.00000000000001</v>
+        <v>4.080711622594535</v>
       </c>
       <c r="Q72" t="n">
         <v>15</v>
@@ -8554,10 +8504,10 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C73" t="n">
-        <v>0.05362723309580827</v>
+        <v>0.05084656599825781</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8582,25 +8532,25 @@
         <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>31.25840016539586</v>
+        <v>34.37682247076691</v>
       </c>
       <c r="K73" t="n">
-        <v>2.755903193006337</v>
+        <v>2.057611051838348</v>
       </c>
       <c r="L73" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M73" t="n">
-        <v>71.42857142857143</v>
+        <v>60</v>
       </c>
       <c r="N73" t="n">
-        <v>18.25806919375062</v>
+        <v>14.84642094367283</v>
       </c>
       <c r="O73" t="n">
         <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>7.04981084482037</v>
+        <v>7.782260300143085</v>
       </c>
       <c r="Q73" t="n">
         <v>14</v>
@@ -8663,10 +8613,10 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C74" t="n">
-        <v>4.52030334601845</v>
+        <v>4.059524188090549</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8683,7 +8633,11 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %86.67: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H74" t="n">
         <v>5</v>
       </c>
@@ -8691,46 +8645,46 @@
         <v>10</v>
       </c>
       <c r="J74" t="n">
-        <v>25.63813329763319</v>
+        <v>31.56969446071427</v>
       </c>
       <c r="K74" t="n">
-        <v>2.468562238142114</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M74" t="n">
-        <v>62.5</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="N74" t="n">
-        <v>13.14679252584914</v>
+        <v>29.17268056591148</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>5.398180320909107</v>
+        <v>8.000000000000007</v>
       </c>
       <c r="Q74" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R74" t="n">
-        <v>74.07407407407408</v>
+        <v>75</v>
       </c>
       <c r="S74" t="n">
-        <v>72.01788139931887</v>
+        <v>72.05020981088167</v>
       </c>
       <c r="T74" t="n">
-        <v>2.056192674755209</v>
+        <v>2.949790189118332</v>
       </c>
       <c r="U74" t="n">
-        <v>55.32142868544692</v>
+        <v>56.64432968100104</v>
       </c>
       <c r="V74" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="W74" t="n">
-        <v>77.39130434782609</v>
+        <v>77.58620689655173</v>
       </c>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
@@ -8772,10 +8726,10 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1033505762715296</v>
+        <v>0.09451720724664434</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8800,25 +8754,25 @@
         <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>22.07761273851969</v>
+        <v>27.87731931966058</v>
       </c>
       <c r="K75" t="n">
-        <v>1.207251962479439</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M75" t="n">
-        <v>57.14285714285715</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N75" t="n">
-        <v>18.39790111350874</v>
+        <v>23.93019699195603</v>
       </c>
       <c r="O75" t="n">
         <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>4.735577683007719</v>
+        <v>6.000000000000005</v>
       </c>
       <c r="Q75" t="n">
         <v>5</v>
@@ -8881,19 +8835,19 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C76" t="n">
-        <v>1.861543073787306</v>
+        <v>1.805258167388493</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8912,22 +8866,22 @@
         <v>16.69183750728255</v>
       </c>
       <c r="K76" t="n">
-        <v>10.05293361647748</v>
+        <v>6.725415089110864</v>
       </c>
       <c r="L76" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M76" t="n">
-        <v>63.1578947368421</v>
+        <v>50</v>
       </c>
       <c r="N76" t="n">
-        <v>11.15319882028068</v>
+        <v>13.08352042739859</v>
       </c>
       <c r="O76" t="n">
         <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.068233473868442</v>
       </c>
       <c r="Q76" t="n">
         <v>41</v>
@@ -8951,25 +8905,25 @@
         <v>60</v>
       </c>
       <c r="X76" t="n">
-        <v>10.90323779832005</v>
+        <v>10.90779289952064</v>
       </c>
       <c r="Y76" t="n">
-        <v>0.7667081671581588</v>
+        <v>3.771040520298585</v>
       </c>
       <c r="Z76" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AA76" t="n">
-        <v>42.10526315789474</v>
+        <v>34.28571428571428</v>
       </c>
       <c r="AB76" t="n">
-        <v>9.806989393884249</v>
+        <v>9.884375910545893</v>
       </c>
       <c r="AC76" t="n">
         <v>4</v>
       </c>
       <c r="AD76" t="n">
-        <v>3.258273280189394</v>
+        <v>0.237931991512097</v>
       </c>
       <c r="AE76" t="n">
         <v>32</v>
@@ -8978,10 +8932,10 @@
         <v>53.125</v>
       </c>
       <c r="AG76" t="n">
-        <v>26.4186008041787</v>
+        <v>26.2623508041787</v>
       </c>
       <c r="AH76" t="n">
-        <v>26.7063991958213</v>
+        <v>26.8626491958213</v>
       </c>
       <c r="AI76" t="n">
         <v>36.44951711897464</v>
@@ -9000,10 +8954,10 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4623037512973415</v>
+        <v>0.4494180329682161</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9031,22 +8985,22 @@
         <v>24.27505949158866</v>
       </c>
       <c r="K77" t="n">
-        <v>6.806441779307204</v>
+        <v>3.829442954093043</v>
       </c>
       <c r="L77" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M77" t="n">
-        <v>58.8235294117647</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N77" t="n">
-        <v>13.5424507755035</v>
+        <v>11.58042548507006</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>1.11749647381667</v>
+        <v>4.016738342467008</v>
       </c>
       <c r="Q77" t="n">
         <v>26</v>
@@ -9055,10 +9009,10 @@
         <v>57.69230769230769</v>
       </c>
       <c r="S77" t="n">
-        <v>39.12629649762003</v>
+        <v>39.23119160251513</v>
       </c>
       <c r="T77" t="n">
-        <v>18.56601119468766</v>
+        <v>18.46111608979256</v>
       </c>
       <c r="U77" t="n">
         <v>38.94861374659171</v>
@@ -9109,24 +9063,24 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C78" t="n">
-        <v>0.04972333844994962</v>
+        <v>0.04818121937404228</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -9137,25 +9091,25 @@
         <v>10</v>
       </c>
       <c r="J78" t="n">
-        <v>25.8855858461943</v>
+        <v>26.37076169965725</v>
       </c>
       <c r="K78" t="n">
-        <v>6.607933978924518</v>
+        <v>3.982296920275652</v>
       </c>
       <c r="L78" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M78" t="n">
-        <v>50</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="N78" t="n">
-        <v>17.26382553739754</v>
+        <v>22.28174848223805</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>0.0170250900861646</v>
       </c>
       <c r="Q78" t="n">
         <v>46</v>
@@ -9182,7 +9136,7 @@
         <v>36.67113091579677</v>
       </c>
       <c r="Y78" t="n">
-        <v>20.98815429004413</v>
+        <v>23.43862681040029</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -9224,10 +9178,10 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8255717720196152</v>
+        <v>0.8123148686285692</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9252,19 +9206,19 @@
         <v>10</v>
       </c>
       <c r="J79" t="n">
-        <v>22.49215884768965</v>
+        <v>22.48897538733902</v>
       </c>
       <c r="K79" t="n">
-        <v>6.918569327807811</v>
+        <v>5.197366789321189</v>
       </c>
       <c r="L79" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M79" t="n">
-        <v>73.33333333333333</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="N79" t="n">
-        <v>11.33059066455084</v>
+        <v>9.616557330991663</v>
       </c>
       <c r="O79" t="n">
         <v>5</v>
@@ -9311,10 +9265,10 @@
         <v>52.77777777777778</v>
       </c>
       <c r="AG79" t="n">
-        <v>26.07940132552061</v>
+        <v>25.97652066708439</v>
       </c>
       <c r="AH79" t="n">
-        <v>26.69837645225717</v>
+        <v>26.80125711069339</v>
       </c>
       <c r="AI79" t="n">
         <v>37.00593802298759</v>
@@ -9333,10 +9287,10 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1286231817533876</v>
+        <v>0.1250661471787875</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9364,22 +9318,22 @@
         <v>14.36747410815714</v>
       </c>
       <c r="K80" t="n">
-        <v>5.179398307888561</v>
+        <v>2.270694361860293</v>
       </c>
       <c r="L80" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="M80" t="n">
-        <v>62.74509803921568</v>
+        <v>54.92957746478874</v>
       </c>
       <c r="N80" t="n">
-        <v>16.57102549954389</v>
+        <v>13.6635486001159</v>
       </c>
       <c r="O80" t="n">
         <v>10</v>
       </c>
       <c r="P80" t="n">
-        <v>4.583218548180179</v>
+        <v>7.557693517550024</v>
       </c>
       <c r="Q80" t="n">
         <v>39</v>
@@ -9442,14 +9396,14 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C81" t="n">
-        <v>1.174251559731902</v>
+        <v>1.205555652396394</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9470,25 +9424,25 @@
         <v>10</v>
       </c>
       <c r="J81" t="n">
-        <v>11.74169622012081</v>
+        <v>11.738071208683</v>
       </c>
       <c r="K81" t="n">
-        <v>4.478977579451127</v>
+        <v>7.259852302105663</v>
       </c>
       <c r="L81" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="M81" t="n">
-        <v>45.45454545454545</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="N81" t="n">
-        <v>15.20846825806983</v>
+        <v>14.61874063744135</v>
       </c>
       <c r="O81" t="n">
         <v>10</v>
       </c>
       <c r="P81" t="n">
-        <v>5.284338101749153</v>
+        <v>2.554681587828878</v>
       </c>
       <c r="Q81" t="n">
         <v>32</v>
@@ -9515,22 +9469,22 @@
         <v>23.79225853623819</v>
       </c>
       <c r="Y81" t="n">
-        <v>7.78862658181616</v>
+        <v>5.330385539443716</v>
       </c>
       <c r="Z81" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AA81" t="n">
-        <v>55.55555555555556</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="AB81" t="n">
-        <v>10.89853603576646</v>
+        <v>11.39481103130034</v>
       </c>
       <c r="AC81" t="n">
         <v>10</v>
       </c>
       <c r="AD81" t="n">
-        <v>2.398156904306292</v>
+        <v>4.93253773891924</v>
       </c>
       <c r="AE81" t="n">
         <v>29</v>
@@ -9561,19 +9515,19 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C82" t="n">
-        <v>4.756591930014869</v>
+        <v>4.715608905357708</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>VERİ_YETERSİZ</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9592,22 +9546,22 @@
         <v>20.04129707202715</v>
       </c>
       <c r="K82" t="n">
-        <v>6.405730795770159</v>
+        <v>5.48893390567986</v>
       </c>
       <c r="L82" t="n">
+        <v>5</v>
+      </c>
+      <c r="M82" t="n">
+        <v>40</v>
+      </c>
+      <c r="N82" t="n">
+        <v>8.250161350422491</v>
+      </c>
+      <c r="O82" t="n">
         <v>6</v>
       </c>
-      <c r="M82" t="n">
-        <v>50</v>
-      </c>
-      <c r="N82" t="n">
-        <v>8.901881472194736</v>
-      </c>
-      <c r="O82" t="n">
-        <v>4</v>
-      </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>0.4844736555752016</v>
       </c>
       <c r="Q82" t="n">
         <v>8</v>
@@ -9616,10 +9570,10 @@
         <v>75</v>
       </c>
       <c r="S82" t="n">
-        <v>47.7483806022409</v>
+        <v>42.12710084033613</v>
       </c>
       <c r="T82" t="n">
-        <v>27.2516193977591</v>
+        <v>32.87289915966387</v>
       </c>
       <c r="U82" t="n">
         <v>40.92754303101688</v>
@@ -9670,10 +9624,10 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C83" t="n">
-        <v>5.624695640784321</v>
+        <v>5.6638563482829</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9690,7 +9644,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H83" t="n">
         <v>5</v>
       </c>
@@ -9701,16 +9659,16 @@
         <v>17.92531520307596</v>
       </c>
       <c r="K83" t="n">
-        <v>12.52884141283435</v>
+        <v>13.3122987454888</v>
       </c>
       <c r="L83" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M83" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N83" t="n">
-        <v>10.98802159309777</v>
+        <v>9.960217924426816</v>
       </c>
       <c r="O83" t="n">
         <v>10</v>
@@ -9740,25 +9698,25 @@
         <v>61.90476190476191</v>
       </c>
       <c r="X83" t="n">
-        <v>13.35096993457194</v>
+        <v>14.1326592793928</v>
       </c>
       <c r="Y83" t="n">
-        <v>0.7252946509519576</v>
+        <v>0.7187780772686447</v>
       </c>
       <c r="Z83" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AA83" t="n">
-        <v>42.42424242424242</v>
+        <v>41.26984126984127</v>
       </c>
       <c r="AB83" t="n">
-        <v>13.40005366713753</v>
+        <v>13.32779024167623</v>
       </c>
       <c r="AC83" t="n">
         <v>8</v>
       </c>
       <c r="AD83" t="n">
-        <v>7.327853881278523</v>
+        <v>7.333936651583706</v>
       </c>
       <c r="AE83" t="n">
         <v>41</v>
@@ -9767,10 +9725,10 @@
         <v>58.53658536585366</v>
       </c>
       <c r="AG83" t="n">
-        <v>26.94157983411617</v>
+        <v>26.20125515845076</v>
       </c>
       <c r="AH83" t="n">
-        <v>31.59500553173749</v>
+        <v>32.3353302074029</v>
       </c>
       <c r="AI83" t="n">
         <v>43.36710313403013</v>
@@ -9789,10 +9747,10 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C84" t="n">
-        <v>2.037218562153607</v>
+        <v>1.992857266165922</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9820,16 +9778,16 @@
         <v>15.17540634174243</v>
       </c>
       <c r="K84" t="n">
-        <v>7.448321398036839</v>
+        <v>5.108588746141463</v>
       </c>
       <c r="L84" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M84" t="n">
-        <v>51.61290322580645</v>
+        <v>59.45945945945946</v>
       </c>
       <c r="N84" t="n">
-        <v>9.20041578810123</v>
+        <v>10.72431748859645</v>
       </c>
       <c r="O84" t="n">
         <v>5</v>
@@ -9862,16 +9820,16 @@
         <v>10.78590455284552</v>
       </c>
       <c r="Y84" t="n">
-        <v>3.012642418979061</v>
+        <v>5.124583158497331</v>
       </c>
       <c r="Z84" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AA84" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AB84" t="n">
-        <v>11.53232374393195</v>
+        <v>10.73812045799384</v>
       </c>
       <c r="AC84" t="n">
         <v>2</v>
@@ -9886,10 +9844,10 @@
         <v>44.73684210526316</v>
       </c>
       <c r="AG84" t="n">
-        <v>28.42345692786126</v>
+        <v>28.27597343192042</v>
       </c>
       <c r="AH84" t="n">
-        <v>16.31338517740189</v>
+        <v>16.46086867334274</v>
       </c>
       <c r="AI84" t="n">
         <v>30.14640099805125</v>
@@ -9908,10 +9866,10 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C85" t="n">
-        <v>5.943171558344711</v>
+        <v>5.853505836867939</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9936,19 +9894,19 @@
         <v>10</v>
       </c>
       <c r="J85" t="n">
-        <v>18.98569199070202</v>
+        <v>18.37456282113737</v>
       </c>
       <c r="K85" t="n">
-        <v>11.97119731549396</v>
+        <v>10.2818672846597</v>
       </c>
       <c r="L85" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M85" t="n">
-        <v>44.44444444444444</v>
+        <v>50</v>
       </c>
       <c r="N85" t="n">
-        <v>11.58916989402006</v>
+        <v>13.41052121252668</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
@@ -9978,25 +9936,25 @@
         <v>57.89473684210526</v>
       </c>
       <c r="X85" t="n">
-        <v>12.26152885563785</v>
+        <v>12.40638661939042</v>
       </c>
       <c r="Y85" t="n">
-        <v>0.2586206896551757</v>
+        <v>1.890034364261162</v>
       </c>
       <c r="Z85" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="AA85" t="n">
-        <v>38.88888888888889</v>
+        <v>36.20689655172414</v>
       </c>
       <c r="AB85" t="n">
-        <v>10.95647780374587</v>
+        <v>11.21529673051518</v>
       </c>
       <c r="AC85" t="n">
         <v>6</v>
       </c>
       <c r="AD85" t="n">
-        <v>5.756266205704408</v>
+        <v>4.189141856392309</v>
       </c>
       <c r="AE85" t="n">
         <v>33</v>
@@ -10005,10 +9963,10 @@
         <v>42.42424242424242</v>
       </c>
       <c r="AG85" t="n">
-        <v>26.82314114466521</v>
+        <v>26.69573067634565</v>
       </c>
       <c r="AH85" t="n">
-        <v>15.60110127957721</v>
+        <v>15.72851174789677</v>
       </c>
       <c r="AI85" t="n">
         <v>27.23559663341021</v>
@@ -10027,14 +9985,14 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C86" t="n">
-        <v>5.301083014876182</v>
+        <v>5.019048149626844</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -10044,7 +10002,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -10087,25 +10045,25 @@
         <v>70.12987012987013</v>
       </c>
       <c r="X86" t="n">
-        <v>29.49695346934114</v>
+        <v>32.17085292978845</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>8.91162677209304</v>
       </c>
       <c r="Z86" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="AA86" t="n">
-        <v>36</v>
+        <v>37.5</v>
       </c>
       <c r="AB86" t="n">
-        <v>12.51003871173557</v>
+        <v>6.175653080951157</v>
       </c>
       <c r="AC86" t="n">
         <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>6.000000000000005</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
         <v>52</v>
@@ -10114,10 +10072,10 @@
         <v>53.84615384615385</v>
       </c>
       <c r="AG86" t="n">
-        <v>36.77942960227648</v>
+        <v>37.05070960432571</v>
       </c>
       <c r="AH86" t="n">
-        <v>17.06672424387737</v>
+        <v>16.79544424182814</v>
       </c>
       <c r="AI86" t="n">
         <v>40.50361132695787</v>
@@ -10136,10 +10094,10 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C87" t="n">
-        <v>5.896941183214977</v>
+        <v>5.83300318945334</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10167,16 +10125,16 @@
         <v>13.37336922777884</v>
       </c>
       <c r="K87" t="n">
-        <v>10.35241286923014</v>
+        <v>9.155909179198796</v>
       </c>
       <c r="L87" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M87" t="n">
-        <v>50</v>
+        <v>51.61290322580645</v>
       </c>
       <c r="N87" t="n">
-        <v>11.32783601422248</v>
+        <v>11.18903738291068</v>
       </c>
       <c r="O87" t="n">
         <v>5</v>
@@ -10209,16 +10167,16 @@
         <v>15.88967756874082</v>
       </c>
       <c r="Y87" t="n">
-        <v>4.405422755534937</v>
+        <v>5.441913589274384</v>
       </c>
       <c r="Z87" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA87" t="n">
-        <v>47.22222222222222</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="AB87" t="n">
-        <v>10.77883709639034</v>
+        <v>12.62703416236263</v>
       </c>
       <c r="AC87" t="n">
         <v>4</v>
@@ -10233,10 +10191,10 @@
         <v>46.51162790697674</v>
       </c>
       <c r="AG87" t="n">
-        <v>44.54142126429858</v>
+        <v>44.34762281468618</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.970206642678157</v>
+        <v>2.164005092290559</v>
       </c>
       <c r="AI87" t="n">
         <v>32.51105770412182</v>
@@ -10255,10 +10213,10 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C88" t="n">
-        <v>1.018301091006772</v>
+        <v>1.029232915794869</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10286,16 +10244,16 @@
         <v>21.41497098631751</v>
       </c>
       <c r="K88" t="n">
-        <v>8.367326998114976</v>
+        <v>9.530688838694434</v>
       </c>
       <c r="L88" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M88" t="n">
-        <v>65.38461538461539</v>
+        <v>70.83333333333333</v>
       </c>
       <c r="N88" t="n">
-        <v>12.07070712396973</v>
+        <v>11.64918599815829</v>
       </c>
       <c r="O88" t="n">
         <v>3</v>
@@ -10328,22 +10286,22 @@
         <v>12.09536008844403</v>
       </c>
       <c r="Y88" t="n">
-        <v>3.325769315864269</v>
+        <v>2.287937027657561</v>
       </c>
       <c r="Z88" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="AA88" t="n">
-        <v>34.92063492063492</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="AB88" t="n">
-        <v>12.36969129801072</v>
+        <v>12.35246808149002</v>
       </c>
       <c r="AC88" t="n">
         <v>6</v>
       </c>
       <c r="AD88" t="n">
-        <v>2.766229082156613</v>
+        <v>3.798981271527502</v>
       </c>
       <c r="AE88" t="n">
         <v>33</v>
@@ -10352,10 +10310,10 @@
         <v>51.51515151515152</v>
       </c>
       <c r="AG88" t="n">
-        <v>51.79797467441712</v>
+        <v>51.49981766573379</v>
       </c>
       <c r="AH88" t="n">
-        <v>-0.2828231592656039</v>
+        <v>0.01533384941772198</v>
       </c>
       <c r="AI88" t="n">
         <v>35.21837544891414</v>
@@ -10374,10 +10332,10 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C89" t="n">
-        <v>2.13276136865291</v>
+        <v>2.099471126623961</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10391,14 +10349,10 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SAT_BEKLE_EŞİK</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SATMA_BEKLE</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>5</v>
       </c>
@@ -10409,16 +10363,16 @@
         <v>15.60428510343075</v>
       </c>
       <c r="K89" t="n">
-        <v>7.924825598553964</v>
+        <v>6.240228522708891</v>
       </c>
       <c r="L89" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M89" t="n">
-        <v>75</v>
+        <v>71.7948717948718</v>
       </c>
       <c r="N89" t="n">
-        <v>17.36179616620545</v>
+        <v>17.11797808860209</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
@@ -10451,22 +10405,22 @@
         <v>21.41032003314154</v>
       </c>
       <c r="Y89" t="n">
-        <v>8.916071885224808</v>
+        <v>10.33779963051096</v>
       </c>
       <c r="Z89" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AA89" t="n">
-        <v>30.76923076923077</v>
+        <v>40.90909090909091</v>
       </c>
       <c r="AB89" t="n">
-        <v>15.33714453561096</v>
+        <v>17.94417613395044</v>
       </c>
       <c r="AC89" t="n">
         <v>10</v>
       </c>
       <c r="AD89" t="n">
-        <v>1.190032245215999</v>
+        <v>0</v>
       </c>
       <c r="AE89" t="n">
         <v>22</v>
@@ -10497,19 +10451,19 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C90" t="n">
-        <v>2.71218200761107</v>
+        <v>2.675595487605135</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AL_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -10519,7 +10473,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
+          <t>AL_Güncel_Benzer_Başarı_% %77.14: AL yönü değerlendirmeye alınabilir.</t>
         </is>
       </c>
       <c r="H90" t="n">
@@ -10532,22 +10486,22 @@
         <v>19.80512321049643</v>
       </c>
       <c r="K90" t="n">
-        <v>8.253888408463371</v>
+        <v>6.793575994745571</v>
       </c>
       <c r="L90" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M90" t="n">
-        <v>75</v>
+        <v>77.14285714285714</v>
       </c>
       <c r="N90" t="n">
-        <v>17.18741887381497</v>
+        <v>17.21882223659951</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.129678441813575</v>
       </c>
       <c r="Q90" t="n">
         <v>43</v>
@@ -10610,10 +10564,10 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2305354761945859</v>
+        <v>0.222863775141397</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10630,7 +10584,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %78.26: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H91" t="n">
         <v>5</v>
       </c>
@@ -10641,16 +10599,16 @@
         <v>13.48269577863128</v>
       </c>
       <c r="K91" t="n">
-        <v>10.18395595852732</v>
+        <v>6.517282243380462</v>
       </c>
       <c r="L91" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="M91" t="n">
-        <v>54.05405405405406</v>
+        <v>78.26086956521739</v>
       </c>
       <c r="N91" t="n">
-        <v>21.22479696508859</v>
+        <v>15.45536880940638</v>
       </c>
       <c r="O91" t="n">
         <v>6</v>
@@ -10674,31 +10632,31 @@
         <v>46.62357539237828</v>
       </c>
       <c r="V91" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W91" t="n">
-        <v>66.25</v>
+        <v>65.82278481012658</v>
       </c>
       <c r="X91" t="n">
-        <v>11.06778593403772</v>
+        <v>11.07234779368311</v>
       </c>
       <c r="Y91" t="n">
-        <v>0.7957572648790379</v>
+        <v>4.100989706964409</v>
       </c>
       <c r="Z91" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="AA91" t="n">
-        <v>36.20689655172414</v>
+        <v>41.66666666666666</v>
       </c>
       <c r="AB91" t="n">
-        <v>11.67423453823978</v>
+        <v>14.28969354332373</v>
       </c>
       <c r="AC91" t="n">
         <v>5</v>
       </c>
       <c r="AD91" t="n">
-        <v>4.237966662722736</v>
+        <v>0.9374552357615751</v>
       </c>
       <c r="AE91" t="n">
         <v>39</v>
@@ -10716,10 +10674,10 @@
         <v>27.07931000072518</v>
       </c>
       <c r="AJ91" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AK91" t="n">
-        <v>43.66197183098591</v>
+        <v>44.28571428571428</v>
       </c>
     </row>
     <row r="92">
@@ -10729,10 +10687,10 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C92" t="n">
-        <v>1.084872787428834</v>
+        <v>1.075363872477716</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10757,25 +10715,25 @@
         <v>10</v>
       </c>
       <c r="J92" t="n">
-        <v>19.01116781741373</v>
+        <v>19.00784138318122</v>
       </c>
       <c r="K92" t="n">
-        <v>6.969202973030497</v>
+        <v>6.027262587515803</v>
       </c>
       <c r="L92" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M92" t="n">
-        <v>55.55555555555556</v>
+        <v>55</v>
       </c>
       <c r="N92" t="n">
-        <v>15.61979318393709</v>
+        <v>14.39212567476391</v>
       </c>
       <c r="O92" t="n">
         <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>0.9636390646281523</v>
+        <v>1.860594496491785</v>
       </c>
       <c r="Q92" t="n">
         <v>44</v>
@@ -10816,10 +10774,10 @@
         <v>51.92307692307692</v>
       </c>
       <c r="AG92" t="n">
-        <v>39.80652524576674</v>
+        <v>39.33989570018981</v>
       </c>
       <c r="AH92" t="n">
-        <v>12.11655167731018</v>
+        <v>12.58318122288711</v>
       </c>
       <c r="AI92" t="n">
         <v>38.68568276805605</v>
@@ -10838,10 +10796,10 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C93" t="n">
-        <v>0.03903898303194994</v>
+        <v>0.03772487185794109</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10866,25 +10824,25 @@
         <v>10</v>
       </c>
       <c r="J93" t="n">
-        <v>13.488285987287</v>
+        <v>15.09897921000459</v>
       </c>
       <c r="K93" t="n">
-        <v>2.672739041765926</v>
+        <v>1.098899969810452</v>
       </c>
       <c r="L93" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M93" t="n">
-        <v>58.46153846153846</v>
+        <v>58.20895522388059</v>
       </c>
       <c r="N93" t="n">
-        <v>17.93657452806584</v>
+        <v>20.35079972578897</v>
       </c>
       <c r="O93" t="n">
         <v>6</v>
       </c>
       <c r="P93" t="n">
-        <v>3.240646922724633</v>
+        <v>4.84782725791586</v>
       </c>
       <c r="Q93" t="n">
         <v>31</v>
@@ -10925,10 +10883,10 @@
         <v>60.8695652173913</v>
       </c>
       <c r="AG93" t="n">
-        <v>24.81020000375118</v>
+        <v>24.59342804784879</v>
       </c>
       <c r="AH93" t="n">
-        <v>36.05936521364012</v>
+        <v>36.27613716954252</v>
       </c>
       <c r="AI93" t="n">
         <v>40.78552239138171</v>
@@ -10947,10 +10905,10 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C94" t="n">
-        <v>8.465295357089097</v>
+        <v>8.554729633741323</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10978,16 +10936,16 @@
         <v>10.47530442381612</v>
       </c>
       <c r="K94" t="n">
-        <v>8.389422946560909</v>
+        <v>9.534537113175311</v>
       </c>
       <c r="L94" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M94" t="n">
-        <v>52.63157894736842</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="N94" t="n">
-        <v>14.06792694841168</v>
+        <v>12.5269986394487</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
@@ -11002,10 +10960,10 @@
         <v>63.41463414634146</v>
       </c>
       <c r="S94" t="n">
-        <v>41.4511736037438</v>
+        <v>41.67260464834557</v>
       </c>
       <c r="T94" t="n">
-        <v>21.96346054259767</v>
+        <v>21.74202949799589</v>
       </c>
       <c r="U94" t="n">
         <v>48.12070108791201</v>
@@ -11017,40 +10975,40 @@
         <v>70.90909090909091</v>
       </c>
       <c r="X94" t="n">
-        <v>30.64601732980787</v>
+        <v>28.51196913451994</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.964699070308952</v>
+        <v>1.939539098647658</v>
       </c>
       <c r="Z94" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA94" t="n">
-        <v>33.33333333333334</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="AB94" t="n">
-        <v>12.16646182899771</v>
+        <v>12.30020830027664</v>
       </c>
       <c r="AC94" t="n">
         <v>6</v>
       </c>
       <c r="AD94" t="n">
-        <v>3.128037838405162</v>
+        <v>4.140772808968462</v>
       </c>
       <c r="AE94" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AF94" t="n">
-        <v>52.63157894736842</v>
+        <v>51.28205128205128</v>
       </c>
       <c r="AG94" t="n">
-        <v>22.5862579454434</v>
+        <v>22.705940717489</v>
       </c>
       <c r="AH94" t="n">
-        <v>30.04532100192502</v>
+        <v>28.57611056456228</v>
       </c>
       <c r="AI94" t="n">
-        <v>37.25897138449667</v>
+        <v>36.19936288445796</v>
       </c>
       <c r="AJ94" t="n">
         <v>55</v>
@@ -11066,10 +11024,10 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C95" t="n">
-        <v>0.108898220876161</v>
+        <v>0.1033333421494717</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11094,25 +11052,25 @@
         <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>28.23223192098074</v>
+        <v>31.81633072613733</v>
       </c>
       <c r="K95" t="n">
-        <v>1.532574774298978</v>
+        <v>1.408454184260632</v>
       </c>
       <c r="L95" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M95" t="n">
-        <v>21.42857142857143</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N95" t="n">
-        <v>15.6975867986275</v>
+        <v>12.76213106691009</v>
       </c>
       <c r="O95" t="n">
         <v>10</v>
       </c>
       <c r="P95" t="n">
-        <v>8.339614399145923</v>
+        <v>8.472218499779526</v>
       </c>
       <c r="Q95" t="n">
         <v>21</v>
@@ -11175,10 +11133,10 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1232810003459577</v>
+        <v>0.1258862524602921</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11206,22 +11164,22 @@
         <v>11.75188607616355</v>
       </c>
       <c r="K96" t="n">
-        <v>3.77594120144138</v>
+        <v>5.969000062688345</v>
       </c>
       <c r="L96" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="M96" t="n">
-        <v>52.54237288135593</v>
+        <v>70.27027027027027</v>
       </c>
       <c r="N96" t="n">
-        <v>14.28546973432773</v>
+        <v>14.3786929986355</v>
       </c>
       <c r="O96" t="n">
         <v>10</v>
       </c>
       <c r="P96" t="n">
-        <v>5.997593205613039</v>
+        <v>3.803942601069221</v>
       </c>
       <c r="Q96" t="n">
         <v>48</v>
@@ -11262,10 +11220,10 @@
         <v>48.64864864864865</v>
       </c>
       <c r="AG96" t="n">
-        <v>28.92475479189564</v>
+        <v>28.7047522098241</v>
       </c>
       <c r="AH96" t="n">
-        <v>19.723893856753</v>
+        <v>19.94389643882455</v>
       </c>
       <c r="AI96" t="n">
         <v>33.44640430301664</v>
@@ -11284,10 +11242,10 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C97" t="n">
-        <v>1.840996240396314</v>
+        <v>1.793981648777389</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11315,16 +11273,16 @@
         <v>19.39456900406833</v>
       </c>
       <c r="K97" t="n">
-        <v>8.772144647594171</v>
+        <v>5.994367133491085</v>
       </c>
       <c r="L97" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="M97" t="n">
-        <v>46.66666666666666</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="N97" t="n">
-        <v>9.30806921970809</v>
+        <v>11.30722304501826</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11393,10 +11351,10 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6780455019027675</v>
+        <v>0.6786375980541676</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11424,7 +11382,7 @@
         <v>20.0091805261642</v>
       </c>
       <c r="K98" t="n">
-        <v>8.165157070656836</v>
+        <v>8.259611164131986</v>
       </c>
       <c r="L98" t="n">
         <v>14</v>
@@ -11439,7 +11397,7 @@
         <v>10</v>
       </c>
       <c r="P98" t="n">
-        <v>1.696334548975509</v>
+        <v>1.607606767799519</v>
       </c>
       <c r="Q98" t="n">
         <v>49</v>
@@ -11466,7 +11424,7 @@
         <v>30.85778357900837</v>
       </c>
       <c r="Y98" t="n">
-        <v>13.47780447401995</v>
+        <v>13.4022498706226</v>
       </c>
       <c r="Z98" t="n">
         <v>2</v>
@@ -11486,10 +11444,10 @@
         <v>56.86274509803921</v>
       </c>
       <c r="AG98" t="n">
-        <v>36.83192412476235</v>
+        <v>36.5457704476052</v>
       </c>
       <c r="AH98" t="n">
-        <v>20.03082097327687</v>
+        <v>20.31697465043401</v>
       </c>
       <c r="AI98" t="n">
         <v>43.26530210930225</v>
@@ -11508,24 +11466,24 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4951786925307269</v>
+        <v>0.4781217313526218</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_ADAYI</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -11536,25 +11494,25 @@
         <v>10</v>
       </c>
       <c r="J99" t="n">
-        <v>18.77251112788727</v>
+        <v>20.37030253012366</v>
       </c>
       <c r="K99" t="n">
-        <v>4.028367186582016</v>
+        <v>2.460454544556034</v>
       </c>
       <c r="L99" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M99" t="n">
-        <v>58.97435897435897</v>
+        <v>60.46511627906977</v>
       </c>
       <c r="N99" t="n">
-        <v>16.62360548972542</v>
+        <v>13.95002962594736</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>1.502575273833551</v>
       </c>
       <c r="Q99" t="n">
         <v>34</v>
@@ -11581,7 +11539,7 @@
         <v>33.04241514445872</v>
       </c>
       <c r="Y99" t="n">
-        <v>15.50036961967851</v>
+        <v>18.41105001990987</v>
       </c>
       <c r="Z99" t="n">
         <v>0</v>
@@ -11601,10 +11559,10 @@
         <v>43.90243902439025</v>
       </c>
       <c r="AG99" t="n">
-        <v>28.98051503528407</v>
+        <v>28.73661259625969</v>
       </c>
       <c r="AH99" t="n">
-        <v>14.92192398910617</v>
+        <v>15.16582642813056</v>
       </c>
       <c r="AI99" t="n">
         <v>29.89013173655036</v>
@@ -11623,10 +11581,10 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C100" t="n">
-        <v>338.9352262569049</v>
+        <v>336.3623489721172</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11654,7 +11612,7 @@
         <v>16.74333965049621</v>
       </c>
       <c r="K100" t="n">
-        <v>11.74077944543452</v>
+        <v>10.89254860087276</v>
       </c>
       <c r="L100" t="n">
         <v>16</v>
@@ -11678,10 +11636,10 @@
         <v>60.41666666666666</v>
       </c>
       <c r="S100" t="n">
-        <v>36.43012149935151</v>
+        <v>36.18197242087954</v>
       </c>
       <c r="T100" t="n">
-        <v>23.98654516731516</v>
+        <v>24.23469424578713</v>
       </c>
       <c r="U100" t="n">
         <v>46.31040849254725</v>
@@ -11693,25 +11651,25 @@
         <v>64.91228070175438</v>
       </c>
       <c r="X100" t="n">
-        <v>12.25809768500474</v>
+        <v>12.59461100507147</v>
       </c>
       <c r="Y100" t="n">
-        <v>0.4608293301226363</v>
+        <v>1.51167306232981</v>
       </c>
       <c r="Z100" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AA100" t="n">
-        <v>44.82758620689656</v>
+        <v>37.28813559322034</v>
       </c>
       <c r="AB100" t="n">
-        <v>11.57012987101301</v>
+        <v>13.58313602250962</v>
       </c>
       <c r="AC100" t="n">
         <v>8</v>
       </c>
       <c r="AD100" t="n">
-        <v>7.574074225393234</v>
+        <v>6.587914669092121</v>
       </c>
       <c r="AE100" t="n">
         <v>39</v>
@@ -11742,10 +11700,10 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C101" t="n">
-        <v>336.3473485781018</v>
+        <v>331.775282055433</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11773,16 +11731,16 @@
         <v>12.87023644471203</v>
       </c>
       <c r="K101" t="n">
-        <v>6.805904308115474</v>
+        <v>5.3540608445803</v>
       </c>
       <c r="L101" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M101" t="n">
-        <v>47.82608695652174</v>
+        <v>56</v>
       </c>
       <c r="N101" t="n">
-        <v>7.880778017543602</v>
+        <v>8.844762526872907</v>
       </c>
       <c r="O101" t="n">
         <v>2</v>
@@ -11851,10 +11809,10 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C102" t="n">
-        <v>379.6676781025531</v>
+        <v>371.7921250315408</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11879,25 +11837,25 @@
         <v>10</v>
       </c>
       <c r="J102" t="n">
-        <v>13.69784871135864</v>
+        <v>13.69430404448729</v>
       </c>
       <c r="K102" t="n">
-        <v>3.202266151994415</v>
+        <v>1.057361912736088</v>
       </c>
       <c r="L102" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M102" t="n">
-        <v>43.33333333333334</v>
+        <v>58.8235294117647</v>
       </c>
       <c r="N102" t="n">
-        <v>9.259483436088804</v>
+        <v>10.95608993662077</v>
       </c>
       <c r="O102" t="n">
         <v>4</v>
       </c>
       <c r="P102" t="n">
-        <v>0.7729809409714905</v>
+        <v>2.911849301790514</v>
       </c>
       <c r="Q102" t="n">
         <v>29</v>
@@ -11938,10 +11896,10 @@
         <v>53.84615384615385</v>
       </c>
       <c r="AG102" t="n">
-        <v>30.10812270427655</v>
+        <v>30.2042765504304</v>
       </c>
       <c r="AH102" t="n">
-        <v>23.7380311418773</v>
+        <v>23.64187729572345</v>
       </c>
       <c r="AI102" t="n">
         <v>35.45793874685879</v>
@@ -11960,10 +11918,10 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C103" t="n">
-        <v>0.7257141490003528</v>
+        <v>0.7430159767495057</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11980,11 +11938,7 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %88.89: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>5</v>
       </c>
@@ -11995,16 +11949,16 @@
         <v>18.80410934045254</v>
       </c>
       <c r="K103" t="n">
-        <v>13.0996046226314</v>
+        <v>15.79602425338207</v>
       </c>
       <c r="L103" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M103" t="n">
-        <v>88.88888888888889</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N103" t="n">
-        <v>14.82383750962397</v>
+        <v>30.90874213659563</v>
       </c>
       <c r="O103" t="n">
         <v>10</v>
@@ -12034,19 +11988,19 @@
         <v>67.69230769230769</v>
       </c>
       <c r="X103" t="n">
-        <v>13.0996046226314</v>
+        <v>15.79602425338207</v>
       </c>
       <c r="Y103" t="n">
         <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="AA103" t="n">
-        <v>38.33333333333334</v>
+        <v>34.88372093023256</v>
       </c>
       <c r="AB103" t="n">
-        <v>10.42210671372402</v>
+        <v>12.00596571599458</v>
       </c>
       <c r="AC103" t="n">
         <v>8</v>
@@ -12061,10 +12015,10 @@
         <v>59.375</v>
       </c>
       <c r="AG103" t="n">
-        <v>34.05307872219637</v>
+        <v>33.7134645544572</v>
       </c>
       <c r="AH103" t="n">
-        <v>25.32192127780363</v>
+        <v>25.6615354455428</v>
       </c>
       <c r="AI103" t="n">
         <v>42.26002487538288</v>
@@ -12083,14 +12037,14 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C104" t="n">
-        <v>0.05033974283527441</v>
+        <v>0.0469510617593252</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>AL_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -12100,7 +12054,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SAT_ADAYI</t>
+          <t>BAND</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -12111,25 +12065,25 @@
         <v>10</v>
       </c>
       <c r="J104" t="n">
-        <v>11.61049328507885</v>
+        <v>15.18885869861597</v>
       </c>
       <c r="K104" t="n">
-        <v>3.783280297143321</v>
+        <v>0.881056395427815</v>
       </c>
       <c r="L104" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="M104" t="n">
-        <v>51.02040816326531</v>
+        <v>50</v>
       </c>
       <c r="N104" t="n">
-        <v>14.22996646647806</v>
+        <v>14.31908637865321</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>0.2088194767366991</v>
+        <v>3.091703949200064</v>
       </c>
       <c r="Q104" t="n">
         <v>32</v>
@@ -12152,27 +12106,17 @@
       <c r="W104" t="n">
         <v>63.23529411764706</v>
       </c>
-      <c r="X104" t="n">
-        <v>17.89763425757407</v>
-      </c>
-      <c r="Y104" t="n">
-        <v>8.266470492791067</v>
-      </c>
+      <c r="X104" t="inlineStr"/>
+      <c r="Y104" t="inlineStr"/>
       <c r="Z104" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA104" t="n">
-        <v>63.63636363636363</v>
-      </c>
-      <c r="AB104" t="n">
-        <v>14.47578631409413</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA104" t="inlineStr"/>
+      <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="n">
         <v>5</v>
       </c>
-      <c r="AD104" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD104" t="inlineStr"/>
       <c r="AE104" t="n">
         <v>43</v>
       </c>
@@ -12180,10 +12124,10 @@
         <v>55.81395348837209</v>
       </c>
       <c r="AG104" t="n">
-        <v>30.00683953084836</v>
+        <v>29.88054963207664</v>
       </c>
       <c r="AH104" t="n">
-        <v>25.80711395752374</v>
+        <v>25.93340385629545</v>
       </c>
       <c r="AI104" t="n">
         <v>41.1076144528241</v>

--- a/TDA_tr.xlsx
+++ b/TDA_tr.xlsx
@@ -439,7 +439,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3852447637827459</v>
+        <v>0.3917952500973341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,25 +695,25 @@
         <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>22.3316078451137</v>
+        <v>20.27783095137682</v>
       </c>
       <c r="K2" t="n">
-        <v>6.078795173732421</v>
+        <v>7.882499627053452</v>
       </c>
       <c r="L2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M2" t="n">
-        <v>56.25</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N2" t="n">
-        <v>13.7376354826656</v>
+        <v>16.46533826344887</v>
       </c>
       <c r="O2" t="n">
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>3.696502038739746</v>
+        <v>1.962783936474111</v>
       </c>
       <c r="Q2" t="n">
         <v>52</v>
@@ -754,10 +754,10 @@
         <v>53.84615384615385</v>
       </c>
       <c r="AG2" t="n">
-        <v>38.12522537167639</v>
+        <v>38.03032027677129</v>
       </c>
       <c r="AH2" t="n">
-        <v>15.72092847447745</v>
+        <v>15.81583356938255</v>
       </c>
       <c r="AI2" t="n">
         <v>38.56944827051576</v>
@@ -779,7 +779,7 @@
         <v>46283</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6983201990298599</v>
+        <v>0.6982428705135048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>16.52890779617068</v>
       </c>
       <c r="K3" t="n">
-        <v>11.07675891755315</v>
+        <v>11.06445882802323</v>
       </c>
       <c r="L3" t="n">
         <v>21</v>
@@ -849,7 +849,7 @@
         <v>17.17248092970491</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.202349531037709</v>
+        <v>5.212846952814854</v>
       </c>
       <c r="Z3" t="n">
         <v>32</v>
@@ -864,7 +864,7 @@
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.060938161682693</v>
+        <v>5.05042391641628</v>
       </c>
       <c r="AE3" t="n">
         <v>34</v>
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C4" t="n">
-        <v>1.449537109679056</v>
+        <v>1.481527017888978</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,7 +915,11 @@
           <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>5</v>
       </c>
@@ -926,16 +930,16 @@
         <v>18.01811637499802</v>
       </c>
       <c r="K4" t="n">
-        <v>12.30473958413618</v>
+        <v>14.78319859484141</v>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>53.84615384615385</v>
+        <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>19.05893258305035</v>
+        <v>13.79491125283229</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -965,25 +969,25 @@
         <v>62.5</v>
       </c>
       <c r="X4" t="n">
-        <v>14.60802662483958</v>
+        <v>14.86257840023202</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.009708314970837</v>
+        <v>0.06910850034552718</v>
       </c>
       <c r="Z4" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AA4" t="n">
-        <v>40.32258064516129</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.81477285831064</v>
+        <v>13.65117160517739</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>8.15416665021511</v>
+        <v>9.937759336099594</v>
       </c>
       <c r="AE4" t="n">
         <v>39</v>
@@ -992,10 +996,10 @@
         <v>58.97435897435897</v>
       </c>
       <c r="AG4" t="n">
-        <v>38.76889646727108</v>
+        <v>38.72186582069293</v>
       </c>
       <c r="AH4" t="n">
-        <v>20.20546250708789</v>
+        <v>20.25249315366604</v>
       </c>
       <c r="AI4" t="n">
         <v>43.41862288289698</v>
@@ -1014,10 +1018,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2224537322394023</v>
+        <v>0.2211020265978156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,11 +1038,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>5</v>
       </c>
@@ -1046,19 +1046,19 @@
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>21.5381778578712</v>
+        <v>20.04120453690049</v>
       </c>
       <c r="K5" t="n">
-        <v>6.216971830817153</v>
+        <v>5.571560856541136</v>
       </c>
       <c r="L5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M5" t="n">
-        <v>75</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N5" t="n">
-        <v>12.03297387416751</v>
+        <v>10.60285756428638</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -1067,25 +1067,25 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R5" t="n">
-        <v>60.97560975609756</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="S5" t="n">
-        <v>42.75041388884551</v>
+        <v>42.6254040343492</v>
       </c>
       <c r="T5" t="n">
-        <v>18.22519586725205</v>
+        <v>19.27935787041271</v>
       </c>
       <c r="U5" t="n">
-        <v>45.72685693412379</v>
+        <v>46.81404026715268</v>
       </c>
       <c r="V5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W5" t="n">
-        <v>58.73015873015873</v>
+        <v>59.375</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
@@ -1105,10 +1105,10 @@
         <v>52.17391304347826</v>
       </c>
       <c r="AG5" t="n">
-        <v>28.3966466800023</v>
+        <v>28.12908815157421</v>
       </c>
       <c r="AH5" t="n">
-        <v>23.77726636347596</v>
+        <v>24.04482489190405</v>
       </c>
       <c r="AI5" t="n">
         <v>38.13741307280403</v>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C6" t="n">
-        <v>1.345998834137457</v>
+        <v>1.349357595131247</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,7 +1147,11 @@
           <t>ÇELİŞKİLİ_BEKLE</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AL_Güncel_Benzer_Başarı_% %80.00: AL yönü değerlendirmeye alınabilir.</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
@@ -1155,19 +1159,19 @@
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>36.85572424855874</v>
+        <v>31.4340145785041</v>
       </c>
       <c r="K6" t="n">
-        <v>7.12367785757031</v>
+        <v>7.390990741930925</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>33.33333333333334</v>
+        <v>80</v>
       </c>
       <c r="N6" t="n">
-        <v>15.09254522848125</v>
+        <v>9.050404861448257</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
@@ -1200,16 +1204,16 @@
         <v>14.14554587665273</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.151679388935916</v>
+        <v>5.917493392182727</v>
       </c>
       <c r="Z6" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AA6" t="n">
-        <v>58.8235294117647</v>
+        <v>56.60377358490566</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.65498052944222</v>
+        <v>12.81218713473315</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
@@ -1224,10 +1228,10 @@
         <v>45.83333333333334</v>
       </c>
       <c r="AG6" t="n">
-        <v>37.52410598857484</v>
+        <v>37.7519307612779</v>
       </c>
       <c r="AH6" t="n">
-        <v>8.309227344758497</v>
+        <v>8.081402572055431</v>
       </c>
       <c r="AI6" t="n">
         <v>32.57524229286744</v>
@@ -1246,10 +1250,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C7" t="n">
-        <v>2.210185453826818</v>
+        <v>2.213069404315485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1281,7 @@
         <v>15.68018152056624</v>
       </c>
       <c r="K7" t="n">
-        <v>5.947584441989484</v>
+        <v>6.085829668151632</v>
       </c>
       <c r="L7" t="n">
         <v>35</v>
@@ -1286,13 +1290,13 @@
         <v>62.85714285714285</v>
       </c>
       <c r="N7" t="n">
-        <v>13.70711250283193</v>
+        <v>13.14621109633782</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>1.937199011020674</v>
+        <v>1.804360052455745</v>
       </c>
       <c r="Q7" t="n">
         <v>51</v>
@@ -1355,10 +1359,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C8" t="n">
-        <v>0.289292348049088</v>
+        <v>0.2848302288887523</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,11 +1379,7 @@
           <t>BAND</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %75.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>5</v>
       </c>
@@ -1387,25 +1387,21 @@
         <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>30.94951034805541</v>
+        <v>34.08275773542135</v>
       </c>
       <c r="K8" t="n">
-        <v>2.022301722695485</v>
+        <v>5.223315669947004</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>75</v>
-      </c>
-      <c r="N8" t="n">
-        <v>13.22118055964986</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>5.859207424620116</v>
+        <v>2.638848920863324</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1468,10 +1464,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5556217527266317</v>
+        <v>0.5381037273826356</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,16 +1495,16 @@
         <v>17.6457098380072</v>
       </c>
       <c r="K9" t="n">
-        <v>8.482475294182489</v>
+        <v>5.06216508808095</v>
       </c>
       <c r="L9" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M9" t="n">
-        <v>56.52173913043478</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="N9" t="n">
-        <v>8.398768760569258</v>
+        <v>9.828384284093255</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
@@ -1577,10 +1573,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C10" t="n">
-        <v>1.78680575355133</v>
+        <v>1.781725784307699</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,25 +1601,25 @@
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>15.9903344514868</v>
+        <v>15.29309278483361</v>
       </c>
       <c r="K10" t="n">
-        <v>2.459890828245004</v>
+        <v>2.960331557134399</v>
       </c>
       <c r="L10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M10" t="n">
-        <v>57.77777777777778</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="N10" t="n">
-        <v>12.20322904279378</v>
+        <v>11.00681079788877</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>7.359083745652817</v>
+        <v>6.83726279470962</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
@@ -1686,24 +1682,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C11" t="n">
-        <v>7.642361823791678</v>
+        <v>7.735497223417553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1717,16 +1713,16 @@
         <v>16.80962533618998</v>
       </c>
       <c r="K11" t="n">
-        <v>7.004285575876401</v>
+        <v>8.308317906270046</v>
       </c>
       <c r="L11" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="M11" t="n">
-        <v>72.97297297297297</v>
+        <v>60.71428571428572</v>
       </c>
       <c r="N11" t="n">
-        <v>11.7104971159868</v>
+        <v>12.69244321998787</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -1741,10 +1737,10 @@
         <v>60</v>
       </c>
       <c r="S11" t="n">
-        <v>51.68862045129074</v>
+        <v>51.64628174161332</v>
       </c>
       <c r="T11" t="n">
-        <v>8.311379548709262</v>
+        <v>8.353718258386678</v>
       </c>
       <c r="U11" t="n">
         <v>46.18143774758936</v>
@@ -1759,22 +1755,22 @@
         <v>10.26012402231442</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.952870292236476</v>
+        <v>1.77018313134617</v>
       </c>
       <c r="Z11" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="AA11" t="n">
-        <v>45.65217391304348</v>
+        <v>45.28301886792453</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.09169529249605</v>
+        <v>10.74711695665865</v>
       </c>
       <c r="AC11" t="n">
         <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>0.2339583600783124</v>
       </c>
       <c r="AE11" t="n">
         <v>48</v>
@@ -1805,31 +1801,27 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C12" t="n">
-        <v>5.084656558820486</v>
+        <v>5.363619597959058</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BAND</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>SAT_BEKLE_EŞİK</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>5</v>
       </c>
@@ -1840,22 +1832,22 @@
         <v>33.95548508619471</v>
       </c>
       <c r="K12" t="n">
-        <v>3.581631839036636</v>
+        <v>9.26450274338999</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>100</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N12" t="n">
-        <v>12.19521088909814</v>
+        <v>9.453626777376323</v>
       </c>
       <c r="O12" t="n">
         <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>1.369324016025808</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>10</v>
@@ -1878,17 +1870,27 @@
       <c r="W12" t="n">
         <v>72.22222222222223</v>
       </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>10.09937955518285</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.7582938388625671</v>
+      </c>
       <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>14.90245967818364</v>
+      </c>
       <c r="AC12" t="n">
         <v>2</v>
       </c>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>1.251193887297031</v>
+      </c>
       <c r="AE12" t="n">
         <v>5</v>
       </c>
@@ -1918,19 +1920,19 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C13" t="n">
-        <v>0.128346577530997</v>
+        <v>0.1407758037745128</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>BEKLE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AL_BEKLE_EŞİK</t>
+          <t>VERİ_YETERSİZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1946,10 +1948,10 @@
         <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>57.6398540434237</v>
+        <v>55.36814347275225</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>20.1048951048951</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1960,7 +1962,7 @@
         <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>6.000000000000005</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -2011,24 +2013,24 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C14" t="n">
-        <v>8.605986252277818</v>
+        <v>8.847154771418618</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>AL_ADAYI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ÇELİŞKİLİ_BEKLE</t>
+          <t>SAT_BEKLE_EŞİK</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -2042,16 +2044,16 @@
         <v>10.97257403209156</v>
       </c>
       <c r="K14" t="n">
-        <v>7.365419749194357</v>
+        <v>10.37415791456038</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M14" t="n">
-        <v>46.15384615384615</v>
+        <v>35</v>
       </c>
       <c r="N14" t="n">
-        <v>11.43584516509007</v>
+        <v>12.77102326132222</v>
       </c>
       <c r="O14" t="n">
         <v>2</v>
@@ -2084,22 +2086,22 @@
         <v>16.11612055393703</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.415330417651853</v>
+        <v>1.736728274912414</v>
       </c>
       <c r="Z14" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AA14" t="n">
-        <v>34.61538461538461</v>
+        <v>50</v>
       </c>
       <c r="AB14" t="n">
-        <v>13.46865860107384</v>
+        <v>11.42455757959865</v>
       </c>
       <c r="AC14" t="n">
         <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>0.2679248517433286</v>
       </c>
       <c r="AE14" t="n">
         <v>36</v>
@@ -2108,10 +2110,10 @@
         <v>52.77777777777778</v>
       </c>
       <c r="AG14" t="n">
-        <v>25.32536704608844</v>
+        <v>25.26524198596339</v>
       </c>
       <c r="AH14" t="n">
-        <v>27.45241073168934</v>
+        <v>27.51253579181439</v>
       </c>
       <c r="AI14" t="n">
         <v>37.00593802298759</v>
@@ -2130,10 +2132,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C15" t="n">
-        <v>13.43948538026947</v>
+        <v>13.47308456793918</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,22 +2163,22 @@
         <v>20.43038307058605</v>
       </c>
       <c r="K15" t="n">
-        <v>6.846328275789726</v>
+        <v>7.113447866605904</v>
       </c>
       <c r="L15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M15" t="n">
-        <v>70</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="N15" t="n">
-        <v>15.0289238728392</v>
+        <v>16.18879170816904</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>1.079748591109686</v>
+        <v>0.827675843744835</v>
       </c>
       <c r="Q15" t="n">
         <v>39</v>
@@ -2203,7 +2205,7 @@
         <v>25.94456260816873</v>
       </c>
       <c r="Y15" t="n">
-        <v>14.98278588781</v>
+        <v>14.77023985265415</v>
       </c>
       <c r="Z15" t="n">
         <v>2</v>
@@ -2245,10 +2247,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C16" t="n">
-        <v>32.18915644092001</v>
+        <v>31.53623901149566</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,25 +2275,25 @@
         <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>21.6745099724732</v>
+        <v>22.63385309056254</v>
       </c>
       <c r="K16" t="n">
-        <v>1.55239327296246</v>
+        <v>3.916272788656294</v>
       </c>
       <c r="L16" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M16" t="n">
-        <v>61.90476190476191</v>
+        <v>67.74193548387096</v>
       </c>
       <c r="N16" t="n">
-        <v>15.68734159447019</v>
+        <v>13.42733121924828</v>
       </c>
       <c r="O16" t="n">
         <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>8.318471337579659</v>
+        <v>5.854450942170275</v>
       </c>
       <c r="Q16" t="n">
         <v>28</v>
@@ -2354,10 +2356,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2933928931140198</v>
+        <v>0.2639290178479949</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2382,13 +2384,13 @@
         <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>62.34567359062095</v>
+        <v>66.1045102428352</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2431,25 +2433,25 @@
       </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AF17" t="n">
-        <v>56.81818181818182</v>
+        <v>57.77777777777778</v>
       </c>
       <c r="AG17" t="n">
-        <v>39.0143300289399</v>
+        <v>38.55886755093054</v>
       </c>
       <c r="AH17" t="n">
-        <v>17.80385178924193</v>
+        <v>19.21891022684724</v>
       </c>
       <c r="AI17" t="n">
-        <v>42.22414699362943</v>
+        <v>43.30078870920313</v>
       </c>
       <c r="AJ17" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AK17" t="n">
-        <v>52.27272727272727</v>
+        <v>52.80898876404494</v>
       </c>
     </row>
     <row r="18">
@@ -2459,10 +2461,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05966270582172058</v>
+        <v>0.05368742443802381</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,25 +2489,25 @@
         <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>44.01451546590328</v>
+        <v>47.92396197252813</v>
       </c>
       <c r="K18" t="n">
-        <v>1.041665932436375</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>50</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="N18" t="n">
-        <v>7.828467810803508</v>
+        <v>12.45307724571796</v>
       </c>
       <c r="O18" t="n">
         <v>10</v>
       </c>
       <c r="P18" t="n">
-        <v>8.86598017252982</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="Q18" t="n">
         <v>57</v>
@@ -2568,10 +2570,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02521825673000939</v>
+        <v>0.02336017704555234</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2596,25 +2598,25 @@
         <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>19.75808205502609</v>
+        <v>23.2589677042621</v>
       </c>
       <c r="K19" t="n">
-        <v>6.034487225029839</v>
+        <v>2.702702702702675</v>
       </c>
       <c r="L19" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M19" t="n">
-        <v>68.18181818181819</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="N19" t="n">
-        <v>22.40273625909982</v>
+        <v>18.98083023609503</v>
       </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>3.739833028620621</v>
+        <v>7.10526315789477</v>
       </c>
       <c r="Q19" t="n">
         <v>14</v>
@@ -2677,10 +2679,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C20" t="n">
-        <v>1.640211793167899</v>
+        <v>1.638286100694658</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2705,25 +2707,25 @@
         <v>10</v>
       </c>
       <c r="J20" t="n">
-        <v>19.82174384694231</v>
+        <v>18.60809574222461</v>
       </c>
       <c r="K20" t="n">
-        <v>6.976773959899552</v>
+        <v>6.851177759894012</v>
       </c>
       <c r="L20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M20" t="n">
-        <v>52.63157894736842</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="N20" t="n">
-        <v>10.09992405598111</v>
+        <v>10.49308609113228</v>
       </c>
       <c r="O20" t="n">
         <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>2.826058337890913</v>
+        <v>2.946923287248859</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
@@ -2786,10 +2788,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8471693848153991</v>
+        <v>0.8524415483289277</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,22 +2819,22 @@
         <v>17.90453399434356</v>
       </c>
       <c r="K21" t="n">
-        <v>4.56396386761484</v>
+        <v>5.214693609522225</v>
       </c>
       <c r="L21" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M21" t="n">
-        <v>45.94594594594594</v>
+        <v>40</v>
       </c>
       <c r="N21" t="n">
-        <v>13.3870059693234</v>
+        <v>14.78660265938505</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>3.286061474042268</v>
+        <v>2.647259897761756</v>
       </c>
       <c r="Q21" t="n">
         <v>40</v>
@@ -2859,16 +2861,16 @@
         <v>11.00964066838261</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.806411733214089</v>
+        <v>5.220219634951828</v>
       </c>
       <c r="Z21" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AA21" t="n">
-        <v>48.27586206896552</v>
+        <v>48.38709677419355</v>
       </c>
       <c r="AB21" t="n">
-        <v>10.31047239868942</v>
+        <v>10.49159351231262</v>
       </c>
       <c r="AC21" t="n">
         <v>4</v>
@@ -2905,10 +2907,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2810912968742545</v>
+        <v>0.2747894510358394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2922,14 +2924,10 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BAZ_ORAN_YETERSİZ</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>AL_Güncel_Benzer_Başarı_% %100.00: AL yönü değerlendirmeye alınabilir.</t>
-        </is>
-      </c>
+          <t>BAND</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>5</v>
       </c>
@@ -2937,25 +2935,21 @@
         <v>10</v>
       </c>
       <c r="J22" t="n">
-        <v>26.84577757624037</v>
+        <v>31.0854330862011</v>
       </c>
       <c r="K22" t="n">
-        <v>4.720713775360297</v>
+        <v>8.670988654781198</v>
       </c>
       <c r="L22" t="n">
-        <v>9</v>
-      </c>
-      